--- a/ProjectManagement/EvaluationHWAndProject.xlsx
+++ b/ProjectManagement/EvaluationHWAndProject.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gautamramesh/Documents/githubNew/ML26-03-Car-Licence-Plate-Identification-with-a-Jetson-Nano/ProjectManagement/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B2608F9-ABD7-E843-B7E2-806F76677C12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9708DD20-24C4-9149-B723-29A0C79DFC38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20280" yWindow="2480" windowWidth="25400" windowHeight="16760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="620" windowWidth="51200" windowHeight="25260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Report" sheetId="2" r:id="rId1"/>
@@ -274,7 +274,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="882" uniqueCount="407">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="886" uniqueCount="403">
   <si>
     <t>Literature</t>
   </si>
@@ -519,15 +519,9 @@
     <t>spelling/punctuation/grammar</t>
   </si>
   <si>
-    <t>&lt;Project Name&gt;</t>
-  </si>
-  <si>
     <t>Short Description</t>
   </si>
   <si>
-    <t>The nice project is…</t>
-  </si>
-  <si>
     <t>github Project</t>
   </si>
   <si>
@@ -546,12 +540,6 @@
     <t>github Nickname</t>
   </si>
   <si>
-    <t>Wings</t>
-  </si>
-  <si>
-    <t>Elmar</t>
-  </si>
-  <si>
     <t>Study Course:</t>
   </si>
   <si>
@@ -570,9 +558,6 @@
     <t>CPs:</t>
   </si>
   <si>
-    <t xml:space="preserve"> &lt;5&gt; or &lt;10&gt;</t>
-  </si>
-  <si>
     <t>Grading</t>
   </si>
   <si>
@@ -1495,6 +1480,9 @@
   </si>
   <si>
     <t>gautam-GGEZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;10&gt;</t>
   </si>
 </sst>
 </file>
@@ -2101,62 +2089,62 @@
   <sheetData>
     <row r="2" spans="1:6" ht="34" x14ac:dyDescent="0.4">
       <c r="A2" s="37" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="B2" s="37"/>
       <c r="C2" s="37"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="38" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="B6" s="38"/>
       <c r="C6" s="38"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="D10" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>89</v>
-      </c>
       <c r="F10" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="B11" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="C11" s="3">
         <v>7026787</v>
       </c>
       <c r="D11" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
@@ -2164,23 +2152,23 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B14" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B16" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B18" s="4">
         <v>45924</v>
@@ -2188,45 +2176,45 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B19" s="4">
-        <v>45594</v>
+        <v>46051</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B21" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B22" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="24" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="19" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="13"/>
       <c r="B28" s="13" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="C28" s="13"/>
       <c r="D28" s="13"/>
@@ -2237,13 +2225,13 @@
         <v>0</v>
       </c>
       <c r="H28" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="14"/>
       <c r="B29" s="14" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="C29" s="14"/>
       <c r="D29" s="14"/>
@@ -2254,13 +2242,13 @@
         <v>0</v>
       </c>
       <c r="H29" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="12"/>
       <c r="B30" s="12" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="C30" s="12"/>
       <c r="D30" s="12"/>
@@ -2271,13 +2259,13 @@
         <v>0</v>
       </c>
       <c r="H30" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="12"/>
       <c r="B31" s="12" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="C31" s="12"/>
       <c r="D31" s="12"/>
@@ -2288,13 +2276,13 @@
         <v>0</v>
       </c>
       <c r="H31" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="14"/>
       <c r="B32" s="14" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="C32" s="14"/>
       <c r="D32" s="14"/>
@@ -2305,13 +2293,13 @@
         <v>0</v>
       </c>
       <c r="H32" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" s="13"/>
       <c r="B33" s="13" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="C33" s="13"/>
       <c r="D33" s="13"/>
@@ -2322,12 +2310,12 @@
         <v>0</v>
       </c>
       <c r="H33" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="21" x14ac:dyDescent="0.25">
       <c r="A35" s="28" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
@@ -2426,7 +2414,7 @@
         <v>2</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="D44" s="13"/>
       <c r="E44" s="13"/>
@@ -2438,7 +2426,7 @@
       <c r="A45" s="13"/>
       <c r="B45" s="13"/>
       <c r="C45" s="13" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="D45" s="13"/>
       <c r="E45" s="13"/>
@@ -2450,7 +2438,7 @@
       <c r="A46" s="13"/>
       <c r="B46" s="13"/>
       <c r="C46" s="13" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="D46" s="13"/>
       <c r="E46" s="13"/>
@@ -2462,7 +2450,7 @@
       <c r="A47" s="13"/>
       <c r="B47" s="13"/>
       <c r="C47" s="13" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="D47" s="13"/>
       <c r="E47" s="13"/>
@@ -2474,7 +2462,7 @@
       <c r="A48" s="13"/>
       <c r="B48" s="13"/>
       <c r="C48" s="13" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="D48" s="13"/>
       <c r="E48" s="13"/>
@@ -2486,7 +2474,7 @@
       <c r="A49" s="13"/>
       <c r="B49" s="13"/>
       <c r="C49" s="13" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="D49" s="13"/>
       <c r="E49" s="13"/>
@@ -2498,7 +2486,7 @@
       <c r="A50" s="13"/>
       <c r="B50" s="13"/>
       <c r="C50" s="13" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="D50" s="13"/>
       <c r="E50" s="13"/>
@@ -2511,7 +2499,7 @@
       <c r="B51" s="13"/>
       <c r="C51" s="13"/>
       <c r="D51" s="22" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="E51" s="36">
         <v>1</v>
@@ -2530,15 +2518,15 @@
     </row>
     <row r="54" spans="1:7" s="5" customFormat="1" ht="21" x14ac:dyDescent="0.25">
       <c r="A54" s="28" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A55" s="16" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="B55" s="14" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="C55" s="14"/>
       <c r="D55" s="14"/>
@@ -2547,7 +2535,7 @@
         <v>10</v>
       </c>
       <c r="G55" s="39" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.2">
@@ -2566,7 +2554,7 @@
     <row r="57" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A57" s="16"/>
       <c r="B57" s="14" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="C57" s="14"/>
       <c r="D57" s="14"/>
@@ -2579,7 +2567,7 @@
     <row r="58" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A58" s="16"/>
       <c r="B58" s="14" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="C58" s="14"/>
       <c r="D58" s="14"/>
@@ -2592,7 +2580,7 @@
     <row r="59" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A59" s="16"/>
       <c r="B59" s="14" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C59" s="14"/>
       <c r="D59" s="14"/>
@@ -2631,7 +2619,7 @@
     <row r="62" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A62" s="16"/>
       <c r="B62" s="14" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="C62" s="14"/>
       <c r="D62" s="14"/>
@@ -2644,7 +2632,7 @@
     <row r="63" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A63" s="16"/>
       <c r="B63" s="14" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="C63" s="14"/>
       <c r="D63" s="14"/>
@@ -2657,7 +2645,7 @@
     <row r="64" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A64" s="16"/>
       <c r="B64" s="14" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="C64" s="14"/>
       <c r="D64" s="14"/>
@@ -2670,7 +2658,7 @@
     <row r="65" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A65" s="16"/>
       <c r="B65" s="14" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="C65" s="14"/>
       <c r="D65" s="14"/>
@@ -2683,7 +2671,7 @@
     <row r="66" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A66" s="16"/>
       <c r="B66" s="14" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="C66" s="14"/>
       <c r="D66" s="14"/>
@@ -2696,7 +2684,7 @@
     <row r="67" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A67" s="16"/>
       <c r="B67" s="14" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="C67" s="14"/>
       <c r="D67" s="14"/>
@@ -2711,7 +2699,7 @@
       <c r="B68" s="14"/>
       <c r="C68" s="14"/>
       <c r="D68" s="22" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="E68" s="36">
         <v>1</v>
@@ -2732,15 +2720,15 @@
     </row>
     <row r="70" spans="1:7" s="5" customFormat="1" ht="19" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A71" s="16" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="B71" s="14" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="C71" s="14"/>
       <c r="D71" s="14"/>
@@ -2749,7 +2737,7 @@
         <v>10</v>
       </c>
       <c r="G71" s="42" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.2">
@@ -2768,7 +2756,7 @@
     <row r="73" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A73" s="16"/>
       <c r="B73" s="14" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="C73" s="14"/>
       <c r="D73" s="14"/>
@@ -2794,7 +2782,7 @@
     <row r="75" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A75" s="16"/>
       <c r="B75" s="14" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="C75" s="14"/>
       <c r="D75" s="14"/>
@@ -2807,7 +2795,7 @@
     <row r="76" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A76" s="16"/>
       <c r="B76" s="14" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="C76" s="14"/>
       <c r="D76" s="14"/>
@@ -2822,7 +2810,7 @@
       <c r="B77" s="14"/>
       <c r="C77" s="14"/>
       <c r="D77" s="22" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="E77" s="36">
         <v>1</v>
@@ -2846,18 +2834,18 @@
     </row>
     <row r="80" spans="1:7" ht="19" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A81" s="7" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="B81" s="7" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="C81" s="8" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="D81" s="8"/>
       <c r="E81" s="8"/>
@@ -2865,16 +2853,16 @@
         <v>0</v>
       </c>
       <c r="G81" s="43" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A82" s="7"/>
       <c r="B82" s="7" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="C82" s="8" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="D82" s="8"/>
       <c r="E82" s="8"/>
@@ -2887,7 +2875,7 @@
       <c r="A83" s="7"/>
       <c r="B83" s="7"/>
       <c r="C83" s="8" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="D83" s="8"/>
       <c r="E83" s="8"/>
@@ -2900,7 +2888,7 @@
       <c r="A84" s="7"/>
       <c r="B84" s="7"/>
       <c r="C84" s="8" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="D84" s="8"/>
       <c r="E84" s="8"/>
@@ -2914,7 +2902,7 @@
       <c r="B85" s="7"/>
       <c r="C85" s="7"/>
       <c r="D85" s="22" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="E85" s="36">
         <v>1</v>
@@ -2939,15 +2927,15 @@
     </row>
     <row r="88" spans="1:7" ht="21" x14ac:dyDescent="0.25">
       <c r="A88" s="28" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A89" s="15" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="B89" s="13" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="C89" s="13"/>
       <c r="D89" s="13"/>
@@ -2959,7 +2947,7 @@
     <row r="90" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A90" s="15"/>
       <c r="B90" s="13" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C90" s="13"/>
       <c r="D90" s="13"/>
@@ -2971,7 +2959,7 @@
     <row r="91" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A91" s="15"/>
       <c r="B91" s="13" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="C91" s="13"/>
       <c r="D91" s="13"/>
@@ -2995,7 +2983,7 @@
     <row r="93" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A93" s="15"/>
       <c r="B93" s="13" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="C93" s="13"/>
       <c r="D93" s="13"/>
@@ -3007,7 +2995,7 @@
     <row r="94" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A94" s="15"/>
       <c r="B94" s="13" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="C94" s="13"/>
       <c r="D94" s="13"/>
@@ -3019,7 +3007,7 @@
     <row r="95" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A95" s="15"/>
       <c r="B95" s="13" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C95" s="13"/>
       <c r="D95" s="13"/>
@@ -3033,7 +3021,7 @@
       <c r="B96" s="13"/>
       <c r="C96" s="13"/>
       <c r="D96" s="22" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="E96" s="36">
         <v>1</v>
@@ -3054,7 +3042,7 @@
     <row r="98" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="99" spans="1:6" ht="21" x14ac:dyDescent="0.25">
       <c r="A99" s="28" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
     </row>
     <row r="100" spans="1:6" ht="19" x14ac:dyDescent="0.25">
@@ -3127,7 +3115,7 @@
     <row r="106" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A106" s="13"/>
       <c r="B106" s="13" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C106" s="13"/>
       <c r="D106" s="13"/>
@@ -3141,7 +3129,7 @@
       <c r="B107" s="13"/>
       <c r="C107" s="13"/>
       <c r="D107" s="22" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="E107" s="36">
         <v>1</v>
@@ -3160,15 +3148,15 @@
     </row>
     <row r="110" spans="1:6" ht="19" x14ac:dyDescent="0.25">
       <c r="A110" s="5" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A111" s="16" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="B111" s="14" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="C111" s="14"/>
       <c r="D111" s="14"/>
@@ -3266,7 +3254,7 @@
       <c r="B119" s="32"/>
       <c r="C119" s="14"/>
       <c r="D119" s="22" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="E119" s="36">
         <v>1</v>
@@ -3285,43 +3273,43 @@
     </row>
     <row r="123" spans="1:7" ht="19" x14ac:dyDescent="0.25">
       <c r="A123" s="5" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A124" s="11" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="B124" s="12" t="s">
         <v>6</v>
       </c>
       <c r="C124" s="12" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="D124" s="12"/>
       <c r="E124" s="12" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="F124" s="12">
         <v>6</v>
       </c>
       <c r="G124" s="40" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A125" s="11" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="B125" s="12"/>
       <c r="C125" s="12" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="D125" s="12" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="E125" s="12" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="F125" s="12">
         <v>6</v>
@@ -3333,10 +3321,10 @@
       <c r="B126" s="12"/>
       <c r="C126" s="12"/>
       <c r="D126" s="12" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="E126" s="12" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="F126" s="12">
         <v>6</v>
@@ -3347,11 +3335,11 @@
       <c r="A127" s="12"/>
       <c r="B127" s="12"/>
       <c r="C127" s="12" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="D127" s="12"/>
       <c r="E127" s="12" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="F127" s="12">
         <v>6</v>
@@ -3362,11 +3350,11 @@
       <c r="A128" s="12"/>
       <c r="B128" s="12"/>
       <c r="C128" s="12" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="D128" s="12"/>
       <c r="E128" s="12" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="F128" s="12">
         <v>6</v>
@@ -3377,11 +3365,11 @@
       <c r="A129" s="12"/>
       <c r="B129" s="12"/>
       <c r="C129" s="12" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="D129" s="12"/>
       <c r="E129" s="12" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="F129" s="12">
         <v>6</v>
@@ -3393,7 +3381,7 @@
       <c r="B130" s="12"/>
       <c r="C130" s="12"/>
       <c r="D130" s="22" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="E130" s="36">
         <v>1</v>
@@ -3414,17 +3402,17 @@
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A132" s="11" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="B132" s="12" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C132" s="12" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="D132" s="12"/>
       <c r="E132" s="12" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="F132" s="12">
         <v>10</v>
@@ -3435,13 +3423,13 @@
       <c r="A133" s="12"/>
       <c r="B133" s="12"/>
       <c r="C133" s="12" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="D133" s="12" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="E133" s="12" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="F133" s="12">
         <v>5</v>
@@ -3453,10 +3441,10 @@
       <c r="B134" s="12"/>
       <c r="C134" s="12"/>
       <c r="D134" s="12" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="E134" s="12" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="F134" s="12">
         <v>5</v>
@@ -3468,10 +3456,10 @@
       <c r="B135" s="12"/>
       <c r="C135" s="12"/>
       <c r="D135" s="12" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="E135" s="12" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="F135" s="12">
         <v>5</v>
@@ -3486,7 +3474,7 @@
         <v>13</v>
       </c>
       <c r="E136" s="12" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="F136" s="12">
         <v>5</v>
@@ -3497,11 +3485,11 @@
       <c r="A137" s="11"/>
       <c r="B137" s="12"/>
       <c r="C137" s="12" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="D137" s="12"/>
       <c r="E137" s="12" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="F137" s="12">
         <v>10</v>
@@ -3512,11 +3500,11 @@
       <c r="A138" s="12"/>
       <c r="B138" s="12"/>
       <c r="C138" s="12" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="D138" s="12"/>
       <c r="E138" s="12" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="F138" s="12">
         <v>5</v>
@@ -3527,11 +3515,11 @@
       <c r="A139" s="12"/>
       <c r="B139" s="12"/>
       <c r="C139" s="12" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="D139" s="12"/>
       <c r="E139" s="12" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="F139" s="12">
         <v>5</v>
@@ -3543,7 +3531,7 @@
       <c r="B140" s="12"/>
       <c r="C140" s="12"/>
       <c r="D140" s="22" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="E140" s="36">
         <v>1</v>
@@ -3564,17 +3552,17 @@
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A142" s="11" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="B142" s="12" t="s">
         <v>6</v>
       </c>
       <c r="C142" s="12" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="D142" s="12"/>
       <c r="E142" s="12" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="F142" s="12">
         <v>6</v>
@@ -3583,11 +3571,11 @@
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A143" s="11" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="B143" s="12"/>
       <c r="C143" s="12" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="D143" s="12"/>
       <c r="E143" s="12"/>
@@ -3600,7 +3588,7 @@
       <c r="A144" s="11"/>
       <c r="B144" s="12"/>
       <c r="C144" s="12" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="D144" s="12"/>
       <c r="E144" s="12"/>
@@ -3613,13 +3601,13 @@
       <c r="A145" s="11"/>
       <c r="B145" s="12"/>
       <c r="C145" s="12" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="D145" s="12" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="E145" s="12" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="F145" s="12">
         <v>6</v>
@@ -3631,10 +3619,10 @@
       <c r="B146" s="12"/>
       <c r="C146" s="12"/>
       <c r="D146" s="12" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="E146" s="12" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="F146" s="12">
         <v>6</v>
@@ -3645,11 +3633,11 @@
       <c r="A147" s="12"/>
       <c r="B147" s="12"/>
       <c r="C147" s="12" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="D147" s="12"/>
       <c r="E147" s="12" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="F147" s="12">
         <v>6</v>
@@ -3660,11 +3648,11 @@
       <c r="A148" s="12"/>
       <c r="B148" s="12"/>
       <c r="C148" s="12" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="D148" s="12"/>
       <c r="E148" s="12" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="F148" s="12">
         <v>6</v>
@@ -3675,11 +3663,11 @@
       <c r="A149" s="12"/>
       <c r="B149" s="12"/>
       <c r="C149" s="12" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="D149" s="12"/>
       <c r="E149" s="12" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="F149" s="12">
         <v>6</v>
@@ -3691,7 +3679,7 @@
       <c r="B150" s="12"/>
       <c r="C150" s="12"/>
       <c r="D150" s="22" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="E150" s="36">
         <v>1</v>
@@ -3712,17 +3700,17 @@
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A152" s="11" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="B152" s="12" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C152" s="12" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="D152" s="12"/>
       <c r="E152" s="12" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="F152" s="12">
         <v>10</v>
@@ -3733,13 +3721,13 @@
       <c r="A153" s="12"/>
       <c r="B153" s="12"/>
       <c r="C153" s="12" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="D153" s="12" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="E153" s="12" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="F153" s="12">
         <v>5</v>
@@ -3751,10 +3739,10 @@
       <c r="B154" s="12"/>
       <c r="C154" s="12"/>
       <c r="D154" s="12" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="E154" s="12" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="F154" s="12">
         <v>5</v>
@@ -3766,10 +3754,10 @@
       <c r="B155" s="12"/>
       <c r="C155" s="12"/>
       <c r="D155" s="12" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="E155" s="12" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="F155" s="12">
         <v>5</v>
@@ -3784,7 +3772,7 @@
         <v>13</v>
       </c>
       <c r="E156" s="12" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="F156" s="12">
         <v>5</v>
@@ -3795,7 +3783,7 @@
       <c r="A157" s="11"/>
       <c r="B157" s="12"/>
       <c r="C157" s="12" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="D157" s="12"/>
       <c r="E157" s="12"/>
@@ -3808,11 +3796,11 @@
       <c r="A158" s="11"/>
       <c r="B158" s="12"/>
       <c r="C158" s="12" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="D158" s="12"/>
       <c r="E158" s="12" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="F158" s="12">
         <v>10</v>
@@ -3823,11 +3811,11 @@
       <c r="A159" s="12"/>
       <c r="B159" s="12"/>
       <c r="C159" s="12" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="D159" s="12"/>
       <c r="E159" s="12" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="F159" s="12">
         <v>5</v>
@@ -3838,11 +3826,11 @@
       <c r="A160" s="12"/>
       <c r="B160" s="12"/>
       <c r="C160" s="12" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="D160" s="12"/>
       <c r="E160" s="12" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="F160" s="12">
         <v>5</v>
@@ -3854,7 +3842,7 @@
       <c r="B161" s="12"/>
       <c r="C161" s="12"/>
       <c r="D161" s="22" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="E161" s="36">
         <v>1</v>
@@ -3878,10 +3866,10 @@
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A164" s="16" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="B164" s="14" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C164" s="14" t="s">
         <v>54</v>
@@ -3896,7 +3884,7 @@
       <c r="A165" s="16"/>
       <c r="B165" s="14"/>
       <c r="C165" s="14" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="D165" s="14"/>
       <c r="E165" s="14"/>
@@ -3908,7 +3896,7 @@
       <c r="A166" s="16"/>
       <c r="B166" s="14"/>
       <c r="C166" s="14" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="D166" s="14"/>
       <c r="E166" s="14"/>
@@ -3921,7 +3909,7 @@
       <c r="B167" s="14"/>
       <c r="C167" s="14"/>
       <c r="D167" s="22" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="E167" s="36">
         <v>1</v>
@@ -3941,10 +3929,10 @@
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A169" s="16" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="B169" s="14" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C169" s="14" t="s">
         <v>54</v>
@@ -3959,7 +3947,7 @@
       <c r="A170" s="16"/>
       <c r="B170" s="14"/>
       <c r="C170" s="14" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="D170" s="14"/>
       <c r="E170" s="14"/>
@@ -3971,7 +3959,7 @@
       <c r="A171" s="16"/>
       <c r="B171" s="14"/>
       <c r="C171" s="14" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="D171" s="14"/>
       <c r="E171" s="14"/>
@@ -3983,7 +3971,7 @@
       <c r="A172" s="16"/>
       <c r="B172" s="14"/>
       <c r="C172" s="14" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="D172" s="14"/>
       <c r="E172" s="14"/>
@@ -3995,7 +3983,7 @@
       <c r="A173" s="16"/>
       <c r="B173" s="14"/>
       <c r="C173" s="14" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="D173" s="14"/>
       <c r="E173" s="14"/>
@@ -4008,7 +3996,7 @@
       <c r="B174" s="14"/>
       <c r="C174" s="14"/>
       <c r="D174" s="22" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="E174" s="36">
         <v>1</v>
@@ -4028,17 +4016,17 @@
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A176" s="16" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="B176" s="14" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="C176" s="14" t="s">
         <v>6</v>
       </c>
       <c r="D176" s="14"/>
       <c r="E176" s="14" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="F176" s="14">
         <v>6</v>
@@ -4046,11 +4034,11 @@
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A177" s="16" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="B177" s="14"/>
       <c r="C177" s="14" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="D177" s="14"/>
       <c r="E177" s="14"/>
@@ -4062,7 +4050,7 @@
       <c r="A178" s="16"/>
       <c r="B178" s="14"/>
       <c r="C178" s="14" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="D178" s="14"/>
       <c r="E178" s="14"/>
@@ -4074,7 +4062,7 @@
       <c r="A179" s="16"/>
       <c r="B179" s="14"/>
       <c r="C179" s="14" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="D179" s="14"/>
       <c r="E179" s="14"/>
@@ -4086,7 +4074,7 @@
       <c r="A180" s="16"/>
       <c r="B180" s="14"/>
       <c r="C180" s="14" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="D180" s="14"/>
       <c r="E180" s="14"/>
@@ -4098,13 +4086,13 @@
       <c r="A181" s="16"/>
       <c r="B181" s="14"/>
       <c r="C181" s="14" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="D181" s="14" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="E181" s="14" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="F181" s="14">
         <v>6</v>
@@ -4115,10 +4103,10 @@
       <c r="B182" s="14"/>
       <c r="C182" s="14"/>
       <c r="D182" s="14" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="E182" s="14" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="F182" s="14">
         <v>6</v>
@@ -4128,11 +4116,11 @@
       <c r="A183" s="14"/>
       <c r="B183" s="14"/>
       <c r="C183" s="14" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="D183" s="14"/>
       <c r="E183" s="14" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="F183" s="14">
         <v>6</v>
@@ -4142,11 +4130,11 @@
       <c r="A184" s="14"/>
       <c r="B184" s="14"/>
       <c r="C184" s="14" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="D184" s="14"/>
       <c r="E184" s="14" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="F184" s="14">
         <v>6</v>
@@ -4156,11 +4144,11 @@
       <c r="A185" s="14"/>
       <c r="B185" s="14"/>
       <c r="C185" s="14" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="D185" s="14"/>
       <c r="E185" s="14" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="F185" s="14">
         <v>6</v>
@@ -4171,7 +4159,7 @@
       <c r="B186" s="14"/>
       <c r="C186" s="14"/>
       <c r="D186" s="22" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="E186" s="36">
         <v>1</v>
@@ -4190,17 +4178,17 @@
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A188" s="16" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="B188" s="14" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C188" s="14" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="D188" s="14"/>
       <c r="E188" s="14" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="F188" s="14">
         <v>10</v>
@@ -4208,7 +4196,7 @@
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A189" s="14" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="B189" s="14"/>
       <c r="C189" s="14" t="s">
@@ -4224,7 +4212,7 @@
       <c r="A190" s="16"/>
       <c r="B190" s="14"/>
       <c r="C190" s="14" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="D190" s="14"/>
       <c r="E190" s="14"/>
@@ -4236,13 +4224,13 @@
       <c r="A191" s="14"/>
       <c r="B191" s="14"/>
       <c r="C191" s="14" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="D191" s="14" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="E191" s="14" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="F191" s="14">
         <v>5</v>
@@ -4253,10 +4241,10 @@
       <c r="B192" s="14"/>
       <c r="C192" s="14"/>
       <c r="D192" s="14" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="E192" s="14" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="F192" s="14">
         <v>5</v>
@@ -4267,10 +4255,10 @@
       <c r="B193" s="14"/>
       <c r="C193" s="14"/>
       <c r="D193" s="14" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="E193" s="14" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="F193" s="14">
         <v>5</v>
@@ -4284,7 +4272,7 @@
         <v>13</v>
       </c>
       <c r="E194" s="14" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="F194" s="14">
         <v>5</v>
@@ -4294,11 +4282,11 @@
       <c r="A195" s="14"/>
       <c r="B195" s="14"/>
       <c r="C195" s="14" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="D195" s="14"/>
       <c r="E195" s="14" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="F195" s="14">
         <v>5</v>
@@ -4308,11 +4296,11 @@
       <c r="A196" s="14"/>
       <c r="B196" s="14"/>
       <c r="C196" s="14" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="D196" s="14"/>
       <c r="E196" s="14" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="F196" s="14">
         <v>5</v>
@@ -4323,7 +4311,7 @@
       <c r="B197" s="14"/>
       <c r="C197" s="14"/>
       <c r="D197" s="22" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="E197" s="36">
         <v>1</v>
@@ -4342,7 +4330,7 @@
     </row>
     <row r="199" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A199" s="16" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="B199" s="14" t="s">
         <v>54</v>
@@ -4357,7 +4345,7 @@
     <row r="200" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A200" s="16"/>
       <c r="B200" s="14" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="C200" s="14"/>
       <c r="D200" s="14"/>
@@ -4369,7 +4357,7 @@
     <row r="201" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A201" s="16"/>
       <c r="B201" s="14" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="C201" s="14"/>
       <c r="D201" s="14"/>
@@ -4383,7 +4371,7 @@
       <c r="B202" s="14"/>
       <c r="C202" s="14"/>
       <c r="D202" s="22" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="E202" s="36">
         <v>1</v>
@@ -4406,7 +4394,7 @@
     </row>
     <row r="205" spans="1:9" s="5" customFormat="1" ht="19" x14ac:dyDescent="0.25">
       <c r="A205" s="5" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
     </row>
     <row r="206" spans="1:9" x14ac:dyDescent="0.2">
@@ -4454,7 +4442,7 @@
       <c r="A209" s="1"/>
       <c r="B209" s="12"/>
       <c r="C209" s="12" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="D209" s="12"/>
       <c r="E209" s="12"/>
@@ -4466,7 +4454,7 @@
       <c r="A210" s="1"/>
       <c r="B210" s="12"/>
       <c r="C210" s="12" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="D210" s="12"/>
       <c r="E210" s="12"/>
@@ -4502,7 +4490,7 @@
       <c r="A213" s="1"/>
       <c r="B213" s="12"/>
       <c r="C213" s="12" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D213" s="12"/>
       <c r="E213" s="12"/>
@@ -4515,7 +4503,7 @@
       <c r="B214" s="12"/>
       <c r="C214" s="12"/>
       <c r="D214" s="22" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="E214" s="36">
         <v>1</v>
@@ -4623,7 +4611,7 @@
       <c r="A223" s="1"/>
       <c r="B223" s="13"/>
       <c r="C223" s="13" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D223" s="13"/>
       <c r="E223" s="13"/>
@@ -4636,7 +4624,7 @@
       <c r="B224" s="13"/>
       <c r="C224" s="13"/>
       <c r="D224" s="22" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="E224" s="36">
         <v>1</v>
@@ -4744,7 +4732,7 @@
       <c r="A233" s="1"/>
       <c r="B233" s="14"/>
       <c r="C233" s="14" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D233" s="14"/>
       <c r="E233" s="14"/>
@@ -4757,7 +4745,7 @@
       <c r="B234" s="14"/>
       <c r="C234" s="14"/>
       <c r="D234" s="22" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="E234" s="36">
         <v>1</v>
@@ -4777,7 +4765,7 @@
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A236" s="15" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="B236" s="13" t="s">
         <v>22</v>
@@ -4879,7 +4867,7 @@
       <c r="A244" s="15"/>
       <c r="B244" s="13"/>
       <c r="C244" s="13" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D244" s="13"/>
       <c r="E244" s="13"/>
@@ -4892,7 +4880,7 @@
       <c r="B245" s="13"/>
       <c r="C245" s="13"/>
       <c r="D245" s="22" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="E245" s="36">
         <v>1</v>
@@ -4923,15 +4911,15 @@
     </row>
     <row r="248" spans="1:6" ht="19" x14ac:dyDescent="0.25">
       <c r="A248" s="5" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A249" s="11" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="B249" s="12" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="C249" s="12"/>
       <c r="D249" s="12"/>
@@ -4942,7 +4930,7 @@
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A250" s="11" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="B250" s="12" t="s">
         <v>65</v>
@@ -4969,7 +4957,7 @@
     <row r="252" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A252" s="11"/>
       <c r="B252" s="12" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="C252" s="12"/>
       <c r="D252" s="12"/>
@@ -4993,7 +4981,7 @@
     <row r="254" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A254" s="11"/>
       <c r="B254" s="12" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="C254" s="12"/>
       <c r="D254" s="12"/>
@@ -5007,7 +4995,7 @@
       <c r="B255" s="12"/>
       <c r="C255" s="12"/>
       <c r="D255" s="22" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="E255" s="36">
         <v>1</v>
@@ -5027,11 +5015,11 @@
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A257" s="11" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="B257" s="12"/>
       <c r="C257" s="12" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D257" s="12"/>
       <c r="E257" s="12"/>
@@ -5039,12 +5027,12 @@
         <v>5</v>
       </c>
       <c r="G257" s="41" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A258" s="11" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="B258" s="12"/>
       <c r="C258" s="12" t="s">
@@ -5059,7 +5047,7 @@
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A259" s="11" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="B259" s="12"/>
       <c r="C259" s="12" t="s">
@@ -5076,7 +5064,7 @@
       <c r="A260" s="11"/>
       <c r="B260" s="12"/>
       <c r="C260" s="12" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="D260" s="12"/>
       <c r="E260" s="12"/>
@@ -5089,7 +5077,7 @@
       <c r="A261" s="11"/>
       <c r="B261" s="12"/>
       <c r="C261" s="12" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="D261" s="12"/>
       <c r="E261" s="12"/>
@@ -5102,7 +5090,7 @@
       <c r="A262" s="11"/>
       <c r="B262" s="12"/>
       <c r="C262" s="12" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="D262" s="12"/>
       <c r="E262" s="12"/>
@@ -5116,7 +5104,7 @@
       <c r="B263" s="12"/>
       <c r="C263" s="12"/>
       <c r="D263" s="22" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="E263" s="36">
         <v>1</v>
@@ -5137,7 +5125,7 @@
     </row>
     <row r="265" spans="1:7" ht="19" x14ac:dyDescent="0.25">
       <c r="A265" s="5" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.2">
@@ -5188,7 +5176,7 @@
       <c r="A270" s="8"/>
       <c r="B270" s="8"/>
       <c r="C270" s="8" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="D270" s="8"/>
       <c r="E270" s="8"/>
@@ -5198,7 +5186,7 @@
     </row>
     <row r="272" spans="1:7" ht="19" x14ac:dyDescent="0.25">
       <c r="A272" s="5" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.2">
@@ -5206,7 +5194,7 @@
         <v>75</v>
       </c>
       <c r="B273" s="12" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="C273" s="12" t="s">
         <v>73</v>
@@ -5224,7 +5212,7 @@
       <c r="B274" s="12"/>
       <c r="C274" s="12"/>
       <c r="D274" s="12" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="E274" s="12"/>
       <c r="F274" s="12">
@@ -5236,7 +5224,7 @@
       <c r="B275" s="12"/>
       <c r="C275" s="12"/>
       <c r="D275" s="12" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="E275" s="12"/>
       <c r="F275" s="12">
@@ -5248,7 +5236,7 @@
       <c r="B276" s="12"/>
       <c r="C276" s="12"/>
       <c r="D276" s="12" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="E276" s="12"/>
       <c r="F276" s="12">
@@ -5260,7 +5248,7 @@
       <c r="B277" s="12"/>
       <c r="C277" s="12"/>
       <c r="D277" s="12" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="E277" s="12"/>
       <c r="F277" s="12">
@@ -5272,7 +5260,7 @@
       <c r="B278" s="12"/>
       <c r="C278" s="12"/>
       <c r="D278" s="12" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="E278" s="12"/>
       <c r="F278" s="12">
@@ -5283,10 +5271,10 @@
       <c r="A279" s="12"/>
       <c r="B279" s="12"/>
       <c r="C279" s="12" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="D279" s="12" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="E279" s="12"/>
       <c r="F279" s="12">
@@ -5298,7 +5286,7 @@
       <c r="B280" s="12"/>
       <c r="C280" s="12"/>
       <c r="D280" s="12" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="E280" s="12"/>
       <c r="F280" s="12">
@@ -5334,7 +5322,7 @@
       <c r="B283" s="12"/>
       <c r="C283" s="12"/>
       <c r="D283" s="12" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="E283" s="12"/>
       <c r="F283" s="12">
@@ -5346,7 +5334,7 @@
       <c r="B284" s="12"/>
       <c r="C284" s="12"/>
       <c r="D284" s="22" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="E284" s="36">
         <v>1</v>
@@ -5365,7 +5353,7 @@
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A286" s="7" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="B286" s="8" t="s">
         <v>74</v>
@@ -5383,7 +5371,7 @@
         <v>21</v>
       </c>
       <c r="C287" s="8" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="D287" s="8"/>
       <c r="E287" s="8"/>
@@ -5407,7 +5395,7 @@
       <c r="A289" s="8"/>
       <c r="B289" s="8"/>
       <c r="C289" s="8" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="D289" s="8"/>
       <c r="E289" s="8"/>
@@ -5419,7 +5407,7 @@
       <c r="A290" s="8"/>
       <c r="B290" s="8"/>
       <c r="C290" s="8" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="D290" s="8"/>
       <c r="E290" s="8"/>
@@ -5431,7 +5419,7 @@
       <c r="A291" s="8"/>
       <c r="B291" s="8"/>
       <c r="C291" s="8" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="D291" s="8"/>
       <c r="E291" s="8"/>
@@ -5443,7 +5431,7 @@
       <c r="A292" s="8"/>
       <c r="B292" s="8"/>
       <c r="C292" s="8" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="D292" s="8"/>
       <c r="E292" s="8"/>
@@ -5456,7 +5444,7 @@
       <c r="B293" s="8"/>
       <c r="C293" s="8"/>
       <c r="D293" s="22" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="E293" s="36">
         <v>1</v>
@@ -5475,10 +5463,10 @@
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A296" s="7" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="B296" s="8" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="C296" s="8"/>
       <c r="D296" s="8"/>
@@ -5489,10 +5477,10 @@
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A297" s="7" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="B297" s="8" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="C297" s="8"/>
       <c r="D297" s="8"/>
@@ -5504,7 +5492,7 @@
     <row r="298" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A298" s="8"/>
       <c r="B298" s="8" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="C298" s="8"/>
       <c r="D298" s="8"/>
@@ -5516,7 +5504,7 @@
     <row r="299" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A299" s="8"/>
       <c r="B299" s="8" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="C299" s="8"/>
       <c r="D299" s="8"/>
@@ -5530,7 +5518,7 @@
       <c r="B300" s="8"/>
       <c r="C300" s="8"/>
       <c r="D300" s="22" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="E300" s="36">
         <v>1</v>
@@ -5549,10 +5537,10 @@
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A303" s="16" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="B303" s="14" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="C303" s="14"/>
       <c r="D303" s="14"/>
@@ -5564,7 +5552,7 @@
     <row r="304" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A304" s="14"/>
       <c r="B304" s="14" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="C304" s="14"/>
       <c r="D304" s="14"/>
@@ -5576,7 +5564,7 @@
     <row r="305" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A305" s="14"/>
       <c r="B305" s="14" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C305" s="14"/>
       <c r="D305" s="14"/>
@@ -5587,10 +5575,10 @@
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A306" s="16" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="B306" s="14" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="C306" s="14"/>
       <c r="D306" s="14"/>
@@ -5602,7 +5590,7 @@
     <row r="307" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A307" s="14"/>
       <c r="B307" s="14" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="C307" s="14"/>
       <c r="D307" s="14"/>
@@ -5613,14 +5601,14 @@
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A308" s="16" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="B308" s="14"/>
       <c r="C308" s="14" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="D308" s="14" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="E308" s="14"/>
       <c r="F308" s="14">
@@ -5631,7 +5619,7 @@
       <c r="A309" s="14"/>
       <c r="B309" s="14"/>
       <c r="C309" s="14" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="D309" s="14"/>
       <c r="E309" s="14"/>
@@ -5643,7 +5631,7 @@
       <c r="A310" s="14"/>
       <c r="B310" s="14"/>
       <c r="C310" s="14" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="D310" s="14"/>
       <c r="E310" s="14"/>
@@ -5656,7 +5644,7 @@
       <c r="B311" s="14"/>
       <c r="C311" s="14"/>
       <c r="D311" s="22" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="E311" s="36">
         <v>1</v>
@@ -5678,7 +5666,7 @@
         <v>35</v>
       </c>
       <c r="B313" s="12" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="C313" s="12"/>
       <c r="D313" s="12"/>
@@ -5690,7 +5678,7 @@
     <row r="314" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A314" s="12"/>
       <c r="B314" s="12" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="C314" s="12"/>
       <c r="D314" s="12"/>
@@ -5702,12 +5690,12 @@
     <row r="315" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A315" s="11"/>
       <c r="B315" s="12" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="C315" s="12"/>
       <c r="D315" s="12"/>
       <c r="E315" s="12" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="F315" s="12">
         <v>10</v>
@@ -5716,12 +5704,12 @@
     <row r="316" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A316" s="12"/>
       <c r="B316" s="12" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="C316" s="12"/>
       <c r="D316" s="12"/>
       <c r="E316" s="12" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="F316" s="12">
         <v>10</v>
@@ -5730,12 +5718,12 @@
     <row r="317" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A317" s="11"/>
       <c r="B317" s="12" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C317" s="12"/>
       <c r="D317" s="12"/>
       <c r="E317" s="12" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="F317" s="12">
         <v>10</v>
@@ -5744,12 +5732,12 @@
     <row r="318" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A318" s="11"/>
       <c r="B318" s="12" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="C318" s="12"/>
       <c r="D318" s="12"/>
       <c r="E318" s="12" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="F318" s="12">
         <v>5</v>
@@ -5758,7 +5746,7 @@
     <row r="319" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A319" s="11"/>
       <c r="B319" s="12" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="C319" s="12"/>
       <c r="D319" s="12"/>
@@ -5770,7 +5758,7 @@
     <row r="320" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A320" s="12"/>
       <c r="B320" s="12" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="C320" s="12"/>
       <c r="D320" s="12"/>
@@ -5782,7 +5770,7 @@
     <row r="321" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A321" s="12"/>
       <c r="B321" s="12" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="C321" s="12"/>
       <c r="D321" s="12"/>
@@ -5808,7 +5796,7 @@
       <c r="B323" s="12"/>
       <c r="C323" s="12"/>
       <c r="D323" s="22" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="E323" s="36">
         <v>1</v>
@@ -5827,10 +5815,10 @@
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A326" s="7" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="B326" s="8" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="C326" s="8"/>
       <c r="D326" s="8"/>
@@ -5842,7 +5830,7 @@
     <row r="327" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A327" s="7"/>
       <c r="B327" s="8" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="C327" s="8"/>
       <c r="D327" s="8"/>
@@ -5854,10 +5842,10 @@
     <row r="328" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A328" s="7"/>
       <c r="B328" s="8" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="C328" s="8" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="D328" s="8"/>
       <c r="E328" s="8"/>
@@ -5881,7 +5869,7 @@
       <c r="A330" s="7"/>
       <c r="B330" s="8"/>
       <c r="C330" s="8" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="D330" s="8"/>
       <c r="E330" s="8"/>
@@ -5893,7 +5881,7 @@
       <c r="A331" s="7"/>
       <c r="B331" s="8"/>
       <c r="C331" s="8" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="D331" s="8"/>
       <c r="E331" s="8"/>
@@ -5918,7 +5906,7 @@
       <c r="B333" s="8"/>
       <c r="C333" s="8"/>
       <c r="D333" s="22" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="E333" s="36">
         <v>1</v>
@@ -5965,7 +5953,7 @@
     <row r="337" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A337" s="7"/>
       <c r="B337" s="8" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="C337" s="8"/>
       <c r="D337" s="8"/>
@@ -5977,7 +5965,7 @@
     <row r="338" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A338" s="7"/>
       <c r="B338" s="8" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="C338" s="8"/>
       <c r="D338" s="8"/>
@@ -6064,7 +6052,7 @@
       <c r="A345" s="7"/>
       <c r="B345" s="7"/>
       <c r="C345" s="8" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="D345" s="8"/>
       <c r="E345" s="8"/>
@@ -6139,7 +6127,7 @@
       <c r="B351" s="7"/>
       <c r="C351" s="8"/>
       <c r="D351" s="22" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="E351" s="36">
         <v>1</v>
@@ -6158,15 +6146,15 @@
     </row>
     <row r="353" spans="1:6" ht="19" x14ac:dyDescent="0.25">
       <c r="A353" s="5" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
     </row>
     <row r="354" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A354" s="13" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="B354" s="13" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="C354" s="13"/>
       <c r="D354" s="13"/>
@@ -6178,7 +6166,7 @@
     <row r="355" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A355" s="13"/>
       <c r="B355" s="13" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="C355" s="13" t="s">
         <v>65</v>
@@ -6193,7 +6181,7 @@
       <c r="A356" s="13"/>
       <c r="B356" s="13"/>
       <c r="C356" s="13" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="D356" s="13"/>
       <c r="E356" s="13"/>
@@ -6205,7 +6193,7 @@
       <c r="A357" s="13"/>
       <c r="B357" s="13"/>
       <c r="C357" s="13" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="D357" s="13"/>
       <c r="E357" s="13"/>
@@ -6216,7 +6204,7 @@
     <row r="358" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A358" s="13"/>
       <c r="B358" s="13" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="C358" s="13" t="s">
         <v>65</v>
@@ -6231,7 +6219,7 @@
       <c r="A359" s="13"/>
       <c r="B359" s="13"/>
       <c r="C359" s="13" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="D359" s="13"/>
       <c r="E359" s="13"/>
@@ -6243,7 +6231,7 @@
       <c r="A360" s="13"/>
       <c r="B360" s="13"/>
       <c r="C360" s="13" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="D360" s="13"/>
       <c r="E360" s="13"/>
@@ -6256,7 +6244,7 @@
       <c r="B361" s="13"/>
       <c r="C361" s="13"/>
       <c r="D361" s="22" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="E361" s="36">
         <v>1</v>
@@ -6275,16 +6263,16 @@
     </row>
     <row r="363" spans="1:6" s="18" customFormat="1" ht="19" x14ac:dyDescent="0.25">
       <c r="A363" s="5" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
     </row>
     <row r="364" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A364" s="15" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="B364" s="13"/>
       <c r="C364" s="13" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="D364" s="13"/>
       <c r="E364" s="13">
@@ -6298,7 +6286,7 @@
       <c r="A365" s="13"/>
       <c r="B365" s="13"/>
       <c r="C365" s="13" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="D365" s="13"/>
       <c r="E365" s="13">
@@ -6326,7 +6314,7 @@
       <c r="A367" s="13"/>
       <c r="B367" s="13"/>
       <c r="C367" s="13" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="D367" s="13"/>
       <c r="E367" s="13">
@@ -6340,7 +6328,7 @@
       <c r="A368" s="13"/>
       <c r="B368" s="13"/>
       <c r="C368" s="13" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="D368" s="13"/>
       <c r="E368" s="13">
@@ -6354,7 +6342,7 @@
       <c r="A369" s="13"/>
       <c r="B369" s="13"/>
       <c r="C369" s="13" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="D369" s="13"/>
       <c r="E369" s="13">
@@ -6369,7 +6357,7 @@
       <c r="B370" s="13"/>
       <c r="C370" s="13"/>
       <c r="D370" s="22" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="E370" s="36">
         <v>1</v>
@@ -6391,7 +6379,7 @@
         <v>44</v>
       </c>
       <c r="B372" s="17" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="C372" s="17"/>
       <c r="D372" s="13"/>
@@ -6415,7 +6403,7 @@
     <row r="374" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A374" s="15"/>
       <c r="B374" s="17" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="C374" s="17"/>
       <c r="D374" s="13"/>
@@ -6434,7 +6422,7 @@
     </row>
     <row r="376" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A376" s="15" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="B376" s="13" t="s">
         <v>77</v>
@@ -6449,7 +6437,7 @@
     <row r="377" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A377" s="15"/>
       <c r="B377" s="13" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C377" s="13"/>
       <c r="D377" s="13"/>
@@ -6461,7 +6449,7 @@
     <row r="378" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A378" s="15"/>
       <c r="B378" s="13" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="C378" s="13"/>
       <c r="D378" s="13"/>
@@ -6480,7 +6468,7 @@
     </row>
     <row r="380" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A380" s="15" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="B380" s="13" t="s">
         <v>77</v>
@@ -6495,7 +6483,7 @@
     <row r="381" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A381" s="15"/>
       <c r="B381" s="13" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C381" s="13"/>
       <c r="D381" s="13"/>
@@ -6507,7 +6495,7 @@
     <row r="382" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A382" s="15"/>
       <c r="B382" s="13" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="C382" s="13"/>
       <c r="D382" s="13"/>
@@ -6521,7 +6509,7 @@
       <c r="B383" s="13"/>
       <c r="C383" s="13"/>
       <c r="D383" s="22" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="E383" s="36">
         <v>1</v>
@@ -6544,7 +6532,7 @@
         <v>45</v>
       </c>
       <c r="B385" s="14" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="C385" s="14"/>
       <c r="D385" s="14"/>
@@ -6556,7 +6544,7 @@
     </row>
     <row r="386" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A386" s="16" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="B386" s="14" t="s">
         <v>50</v>
@@ -6574,7 +6562,7 @@
       <c r="B387" s="14"/>
       <c r="C387" s="14"/>
       <c r="D387" s="22" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="E387" s="36">
         <v>1</v>
@@ -6596,15 +6584,15 @@
     </row>
     <row r="391" spans="1:13" ht="19" x14ac:dyDescent="0.25">
       <c r="A391" s="5" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
     </row>
     <row r="392" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A392" s="11" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B392" s="12" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C392" s="12"/>
       <c r="D392" s="12"/>
@@ -6616,7 +6604,7 @@
     <row r="393" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A393" s="12"/>
       <c r="B393" s="12" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="C393" s="12"/>
       <c r="D393" s="12"/>
@@ -6628,7 +6616,7 @@
     <row r="394" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A394" s="12"/>
       <c r="B394" s="12" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="C394" s="12"/>
       <c r="D394" s="12"/>
@@ -6640,7 +6628,7 @@
     <row r="395" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A395" s="12"/>
       <c r="B395" s="12" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="C395" s="12"/>
       <c r="D395" s="12"/>
@@ -6651,7 +6639,7 @@
     </row>
     <row r="396" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A396" s="11" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="B396" s="12"/>
       <c r="C396" s="12"/>
@@ -6662,7 +6650,7 @@
     <row r="397" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A397" s="11"/>
       <c r="B397" s="12" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="C397" s="12"/>
       <c r="D397" s="12"/>
@@ -6674,7 +6662,7 @@
     <row r="398" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A398" s="12"/>
       <c r="B398" s="12" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="C398" s="12"/>
       <c r="D398" s="12"/>
@@ -6686,7 +6674,7 @@
     <row r="399" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A399" s="12"/>
       <c r="B399" s="12" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="C399" s="12"/>
       <c r="D399" s="12"/>
@@ -6698,7 +6686,7 @@
     <row r="400" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A400" s="12"/>
       <c r="B400" s="12" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C400" s="12"/>
       <c r="D400" s="12"/>
@@ -6717,10 +6705,10 @@
     </row>
     <row r="402" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A402" s="12" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="B402" s="12" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="C402" s="12"/>
       <c r="D402" s="12"/>
@@ -6732,7 +6720,7 @@
     <row r="403" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A403" s="12"/>
       <c r="B403" s="12" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="C403" s="12"/>
       <c r="D403" s="12"/>
@@ -6744,7 +6732,7 @@
     <row r="404" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A404" s="12"/>
       <c r="B404" s="12" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="C404" s="12"/>
       <c r="D404" s="12"/>
@@ -6758,7 +6746,7 @@
       <c r="B405" s="12"/>
       <c r="C405" s="12"/>
       <c r="D405" s="22" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="E405" s="36">
         <v>1</v>
@@ -6777,7 +6765,7 @@
     </row>
     <row r="407" spans="1:6" ht="19" x14ac:dyDescent="0.25">
       <c r="A407" s="5" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
     </row>
     <row r="408" spans="1:6" x14ac:dyDescent="0.2">
@@ -6788,7 +6776,7 @@
         <v>41</v>
       </c>
       <c r="C408" s="8" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="D408" s="8"/>
       <c r="E408" s="8"/>
@@ -6800,7 +6788,7 @@
       <c r="A409" s="7"/>
       <c r="B409" s="8"/>
       <c r="C409" s="8" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="D409" s="8"/>
       <c r="E409" s="8"/>
@@ -6812,7 +6800,7 @@
       <c r="A410" s="7"/>
       <c r="B410" s="8"/>
       <c r="C410" s="8" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="D410" s="8"/>
       <c r="E410" s="8"/>
@@ -6824,7 +6812,7 @@
       <c r="A411" s="7"/>
       <c r="B411" s="8"/>
       <c r="C411" s="8" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="D411" s="8"/>
       <c r="E411" s="8"/>
@@ -6836,7 +6824,7 @@
       <c r="A412" s="7"/>
       <c r="B412" s="8"/>
       <c r="C412" s="8" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="D412" s="8"/>
       <c r="E412" s="8"/>
@@ -6883,7 +6871,7 @@
     <row r="416" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A416" s="8"/>
       <c r="B416" s="8" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C416" s="8"/>
       <c r="D416" s="8"/>
@@ -6897,7 +6885,7 @@
       <c r="B417" s="8"/>
       <c r="C417" s="8"/>
       <c r="D417" s="22" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="E417" s="36">
         <v>1</v>
@@ -6916,10 +6904,10 @@
     </row>
     <row r="419" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A419" s="14" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="B419" s="14" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C419" s="14"/>
       <c r="D419" s="14"/>
@@ -6931,7 +6919,7 @@
     <row r="420" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A420" s="14"/>
       <c r="B420" s="14" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="C420" s="14"/>
       <c r="D420" s="14"/>
@@ -6943,7 +6931,7 @@
     <row r="421" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A421" s="14"/>
       <c r="B421" s="14" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="C421" s="14"/>
       <c r="D421" s="14"/>
@@ -6955,7 +6943,7 @@
     <row r="422" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A422" s="14"/>
       <c r="B422" s="14" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="C422" s="14"/>
       <c r="D422" s="14"/>
@@ -6967,7 +6955,7 @@
     <row r="423" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A423" s="14"/>
       <c r="B423" s="14" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="C423" s="14"/>
       <c r="D423" s="14"/>
@@ -6979,7 +6967,7 @@
     <row r="424" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A424" s="14"/>
       <c r="B424" s="14" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="C424" s="14"/>
       <c r="D424" s="14"/>
@@ -6991,7 +6979,7 @@
     <row r="425" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A425" s="14"/>
       <c r="B425" s="14" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="C425" s="14"/>
       <c r="D425" s="14"/>
@@ -7003,7 +6991,7 @@
     <row r="426" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A426" s="14"/>
       <c r="B426" s="14" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="C426" s="14"/>
       <c r="D426" s="14"/>
@@ -7015,7 +7003,7 @@
     <row r="427" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A427" s="14"/>
       <c r="B427" s="14" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="C427" s="14"/>
       <c r="D427" s="14"/>
@@ -7029,7 +7017,7 @@
       <c r="B428" s="14"/>
       <c r="C428" s="14"/>
       <c r="D428" s="22" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="E428" s="36">
         <v>1</v>
@@ -7048,10 +7036,10 @@
     </row>
     <row r="430" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A430" s="8" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="B430" s="8" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C430" s="8"/>
       <c r="D430" s="8"/>
@@ -7063,7 +7051,7 @@
     <row r="431" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A431" s="8"/>
       <c r="B431" s="8" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="C431" s="8"/>
       <c r="D431" s="8"/>
@@ -7087,7 +7075,7 @@
     <row r="433" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A433" s="8"/>
       <c r="B433" s="8" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="C433" s="8"/>
       <c r="D433" s="8"/>
@@ -7099,7 +7087,7 @@
     <row r="434" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A434" s="8"/>
       <c r="B434" s="8" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="C434" s="8"/>
       <c r="D434" s="8"/>
@@ -7111,7 +7099,7 @@
     <row r="435" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A435" s="8"/>
       <c r="B435" s="8" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="C435" s="8"/>
       <c r="D435" s="8"/>
@@ -7123,7 +7111,7 @@
     <row r="436" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A436" s="8"/>
       <c r="B436" s="8" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="C436" s="8"/>
       <c r="D436" s="8"/>
@@ -7137,7 +7125,7 @@
       <c r="B437" s="8"/>
       <c r="C437" s="8"/>
       <c r="D437" s="22" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="E437" s="36">
         <v>1</v>
@@ -7156,14 +7144,14 @@
     </row>
     <row r="439" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A439" s="7" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="B439" s="7"/>
       <c r="C439" s="8" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="D439" s="8" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="E439" s="8"/>
       <c r="F439" s="8">
@@ -7175,7 +7163,7 @@
       <c r="B440" s="7"/>
       <c r="C440" s="8"/>
       <c r="D440" s="8" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="E440" s="8"/>
       <c r="F440" s="8">
@@ -7187,7 +7175,7 @@
       <c r="B441" s="7"/>
       <c r="C441" s="8"/>
       <c r="D441" s="8" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="E441" s="8"/>
       <c r="F441" s="8">
@@ -7198,10 +7186,10 @@
       <c r="A442" s="7"/>
       <c r="B442" s="7"/>
       <c r="C442" s="8" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="D442" s="8" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="E442" s="8"/>
       <c r="F442" s="8">
@@ -7213,7 +7201,7 @@
       <c r="B443" s="7"/>
       <c r="C443" s="8"/>
       <c r="D443" s="8" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="E443" s="8"/>
       <c r="F443" s="8">
@@ -7225,7 +7213,7 @@
       <c r="B444" s="7"/>
       <c r="C444" s="8"/>
       <c r="D444" s="8" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="E444" s="8"/>
       <c r="F444" s="8">
@@ -7237,7 +7225,7 @@
       <c r="B445" s="7"/>
       <c r="C445" s="8"/>
       <c r="D445" s="8" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="E445" s="8"/>
       <c r="F445" s="8">
@@ -7249,7 +7237,7 @@
       <c r="B446" s="7"/>
       <c r="C446" s="8"/>
       <c r="D446" s="8" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="E446" s="8"/>
       <c r="F446" s="8">
@@ -7268,18 +7256,18 @@
     </row>
     <row r="448" spans="1:6" ht="19" x14ac:dyDescent="0.25">
       <c r="A448" s="5" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
     </row>
     <row r="449" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A449" s="7" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="B449" s="7" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="C449" s="8" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="D449" s="8"/>
       <c r="E449" s="8"/>
@@ -7291,7 +7279,7 @@
       <c r="A450" s="7"/>
       <c r="B450" s="8"/>
       <c r="C450" s="8" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="D450" s="8"/>
       <c r="E450" s="8"/>
@@ -7302,10 +7290,10 @@
     <row r="451" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A451" s="8"/>
       <c r="B451" s="7" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="C451" s="8" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="D451" s="8"/>
       <c r="E451" s="8"/>
@@ -7315,7 +7303,7 @@
       <c r="A452" s="8"/>
       <c r="B452" s="8"/>
       <c r="C452" s="8" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="D452" s="8"/>
       <c r="E452" s="8"/>
@@ -7327,7 +7315,7 @@
       <c r="A453" s="8"/>
       <c r="B453" s="8"/>
       <c r="C453" s="8" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="D453" s="8"/>
       <c r="E453" s="8"/>
@@ -7339,7 +7327,7 @@
       <c r="A454" s="8"/>
       <c r="B454" s="8"/>
       <c r="C454" s="8" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="D454" s="8"/>
       <c r="E454" s="8"/>
@@ -7351,7 +7339,7 @@
       <c r="A455" s="8"/>
       <c r="B455" s="8"/>
       <c r="C455" s="8" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="D455" s="8"/>
       <c r="E455" s="8"/>
@@ -7364,7 +7352,7 @@
       <c r="B456" s="8"/>
       <c r="C456" s="8"/>
       <c r="D456" s="22" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="E456" s="36">
         <v>1</v>
@@ -7382,15 +7370,15 @@
     </row>
     <row r="458" spans="1:6" ht="21" x14ac:dyDescent="0.25">
       <c r="A458" s="28" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
     </row>
     <row r="459" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A459" s="11" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="B459" s="12" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="C459" s="12"/>
       <c r="D459" s="12"/>
@@ -7401,10 +7389,10 @@
     </row>
     <row r="460" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A460" s="11" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="B460" s="12" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="C460" s="12" t="s">
         <v>54</v>
@@ -7419,7 +7407,7 @@
       <c r="A461" s="11"/>
       <c r="B461" s="12"/>
       <c r="C461" s="12" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="D461" s="12"/>
       <c r="E461" s="12"/>
@@ -7432,7 +7420,7 @@
       <c r="B462" s="12"/>
       <c r="C462" s="12"/>
       <c r="D462" s="22" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="E462" s="36">
         <v>1</v>
@@ -7455,18 +7443,18 @@
     </row>
     <row r="465" spans="1:6" ht="19" x14ac:dyDescent="0.25">
       <c r="A465" s="5" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
     </row>
     <row r="466" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A466" s="15" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="B466" s="13" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="C466" s="13" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="D466" s="13"/>
       <c r="E466" s="13"/>
@@ -7476,7 +7464,7 @@
     </row>
     <row r="467" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A467" s="13" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="B467" s="13" t="s">
         <v>7</v>
@@ -7493,7 +7481,7 @@
         <v>0</v>
       </c>
       <c r="B468" s="13" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="C468" s="13"/>
       <c r="D468" s="13"/>
@@ -7505,7 +7493,7 @@
     <row r="469" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A469" s="13"/>
       <c r="B469" s="13" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="C469" s="13"/>
       <c r="D469" s="13"/>
@@ -7519,7 +7507,7 @@
       <c r="B470" s="13"/>
       <c r="C470" s="13"/>
       <c r="D470" s="22" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="E470" s="36">
         <v>1</v>
@@ -7538,13 +7526,13 @@
     </row>
     <row r="473" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A473" s="16" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="B473" s="14" t="s">
         <v>42</v>
       </c>
       <c r="C473" s="14" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="D473" s="14"/>
       <c r="E473" s="14"/>
@@ -7554,10 +7542,10 @@
     </row>
     <row r="474" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A474" s="14" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="B474" s="14" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="C474" s="14"/>
       <c r="D474" s="14"/>
@@ -7569,7 +7557,7 @@
     <row r="475" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A475" s="14"/>
       <c r="B475" s="14" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="C475" s="14"/>
       <c r="D475" s="14"/>
@@ -7583,7 +7571,7 @@
       <c r="B476" s="14"/>
       <c r="C476" s="14"/>
       <c r="D476" s="22" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="E476" s="36">
         <v>1</v>
@@ -7602,13 +7590,13 @@
     </row>
     <row r="478" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A478" s="11" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="B478" s="12" t="s">
         <v>42</v>
       </c>
       <c r="C478" s="12" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="D478" s="12"/>
       <c r="E478" s="12"/>
@@ -7618,10 +7606,10 @@
     </row>
     <row r="479" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A479" s="12" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="B479" s="12" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="C479" s="12"/>
       <c r="D479" s="12"/>
@@ -7633,7 +7621,7 @@
     <row r="480" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A480" s="12"/>
       <c r="B480" s="12" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="C480" s="12"/>
       <c r="D480" s="12"/>
@@ -7647,7 +7635,7 @@
       <c r="B481" s="12"/>
       <c r="C481" s="12"/>
       <c r="D481" s="22" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="E481" s="36">
         <v>1</v>
@@ -7666,15 +7654,15 @@
     </row>
     <row r="487" spans="1:6" ht="19" x14ac:dyDescent="0.25">
       <c r="A487" s="5" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
     </row>
     <row r="488" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A488" s="14" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="B488" s="14" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="C488" s="14"/>
       <c r="D488" s="14"/>
@@ -7685,10 +7673,10 @@
     </row>
     <row r="489" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A489" s="14" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="B489" s="14" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C489" s="14"/>
       <c r="D489" s="14"/>
@@ -7700,7 +7688,7 @@
     <row r="490" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A490" s="14"/>
       <c r="B490" s="14" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="C490" s="14"/>
       <c r="D490" s="14"/>
@@ -7712,7 +7700,7 @@
     <row r="491" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A491" s="14"/>
       <c r="B491" s="14" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="C491" s="14"/>
       <c r="D491" s="14"/>
@@ -7724,7 +7712,7 @@
     <row r="492" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A492" s="14"/>
       <c r="B492" s="14" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="C492" s="14"/>
       <c r="D492" s="14"/>
@@ -7736,7 +7724,7 @@
     <row r="493" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A493" s="14"/>
       <c r="B493" s="14" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="C493" s="14"/>
       <c r="D493" s="14"/>
@@ -7748,7 +7736,7 @@
     <row r="494" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A494" s="14"/>
       <c r="B494" s="14" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="C494" s="14"/>
       <c r="D494" s="14"/>
@@ -7784,7 +7772,7 @@
     <row r="497" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A497" s="14"/>
       <c r="B497" s="14" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="C497" s="14"/>
       <c r="D497" s="14"/>
@@ -7796,7 +7784,7 @@
     <row r="498" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A498" s="14"/>
       <c r="B498" s="14" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="C498" s="14"/>
       <c r="D498" s="14"/>
@@ -7810,7 +7798,7 @@
       <c r="B499" s="14"/>
       <c r="C499" s="14"/>
       <c r="D499" s="22" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="E499" s="36">
         <v>1</v>
@@ -7829,10 +7817,10 @@
     </row>
     <row r="502" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A502" s="12" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="B502" s="12" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="C502" s="12"/>
       <c r="D502" s="12"/>
@@ -7843,10 +7831,10 @@
     </row>
     <row r="503" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A503" s="12" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="B503" s="12" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C503" s="12"/>
       <c r="D503" s="12"/>
@@ -7858,7 +7846,7 @@
     <row r="504" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A504" s="12"/>
       <c r="B504" s="12" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="C504" s="12"/>
       <c r="D504" s="12"/>
@@ -7870,7 +7858,7 @@
     <row r="505" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A505" s="12"/>
       <c r="B505" s="12" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="C505" s="12"/>
       <c r="D505" s="12"/>
@@ -7882,7 +7870,7 @@
     <row r="506" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A506" s="12"/>
       <c r="B506" s="12" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="C506" s="12"/>
       <c r="D506" s="12"/>
@@ -7894,7 +7882,7 @@
     <row r="507" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A507" s="12"/>
       <c r="B507" s="12" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="C507" s="12"/>
       <c r="D507" s="12"/>
@@ -7906,7 +7894,7 @@
     <row r="508" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A508" s="12"/>
       <c r="B508" s="12" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="C508" s="12"/>
       <c r="D508" s="12"/>
@@ -7942,7 +7930,7 @@
     <row r="511" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A511" s="12"/>
       <c r="B511" s="12" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="C511" s="12"/>
       <c r="D511" s="12"/>
@@ -7954,7 +7942,7 @@
     <row r="512" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A512" s="12"/>
       <c r="B512" s="12" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="C512" s="12"/>
       <c r="D512" s="12"/>
@@ -7968,7 +7956,7 @@
       <c r="B513" s="12"/>
       <c r="C513" s="12"/>
       <c r="D513" s="22" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="E513" s="36">
         <v>1</v>
@@ -7987,10 +7975,10 @@
     </row>
     <row r="516" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A516" s="13" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="B516" s="13" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="C516" s="13"/>
       <c r="D516" s="13"/>
@@ -8001,10 +7989,10 @@
     </row>
     <row r="517" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A517" s="13" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="B517" s="13" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C517" s="13"/>
       <c r="D517" s="13"/>
@@ -8016,7 +8004,7 @@
     <row r="518" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A518" s="13"/>
       <c r="B518" s="13" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="C518" s="13"/>
       <c r="D518" s="13"/>
@@ -8028,7 +8016,7 @@
     <row r="519" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A519" s="13"/>
       <c r="B519" s="13" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="C519" s="13"/>
       <c r="D519" s="13"/>
@@ -8040,7 +8028,7 @@
     <row r="520" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A520" s="13"/>
       <c r="B520" s="13" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="C520" s="13"/>
       <c r="D520" s="13"/>
@@ -8052,7 +8040,7 @@
     <row r="521" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A521" s="13"/>
       <c r="B521" s="13" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="C521" s="13"/>
       <c r="D521" s="13"/>
@@ -8064,7 +8052,7 @@
     <row r="522" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A522" s="13"/>
       <c r="B522" s="13" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="C522" s="13"/>
       <c r="D522" s="13"/>
@@ -8100,7 +8088,7 @@
     <row r="525" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A525" s="13"/>
       <c r="B525" s="13" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="C525" s="13"/>
       <c r="D525" s="13"/>
@@ -8112,7 +8100,7 @@
     <row r="526" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A526" s="13"/>
       <c r="B526" s="13" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="C526" s="13"/>
       <c r="D526" s="13"/>
@@ -8126,7 +8114,7 @@
       <c r="B527" s="13"/>
       <c r="C527" s="13"/>
       <c r="D527" s="22" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="E527" s="36">
         <v>1</v>
@@ -8145,12 +8133,12 @@
     </row>
     <row r="530" spans="1:6" ht="21" x14ac:dyDescent="0.25">
       <c r="A530" s="28" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
     </row>
     <row r="531" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A531" s="16" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="B531" s="14"/>
       <c r="C531" s="14"/>
@@ -8205,7 +8193,7 @@
       <c r="B536" s="14"/>
       <c r="C536" s="14"/>
       <c r="D536" s="22" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="E536" s="36">
         <v>1</v>
@@ -8224,7 +8212,7 @@
     </row>
     <row r="539" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A539" s="11" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="B539" s="12"/>
       <c r="C539" s="12"/>
@@ -8279,7 +8267,7 @@
       <c r="B544" s="12"/>
       <c r="C544" s="12"/>
       <c r="D544" s="22" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="E544" s="36">
         <v>1</v>
@@ -8298,7 +8286,7 @@
     </row>
     <row r="547" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A547" s="15" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="B547" s="13"/>
       <c r="C547" s="13"/>
@@ -8353,7 +8341,7 @@
       <c r="B552" s="13"/>
       <c r="C552" s="13"/>
       <c r="D552" s="22" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="E552" s="36">
         <v>1</v>
@@ -8373,7 +8361,7 @@
     <row r="556" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A556" s="7"/>
       <c r="B556" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="E556">
         <f>E438+E418+E334+E14</f>
@@ -8390,10 +8378,10 @@
     </row>
     <row r="557" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A557" s="11" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="B557" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="E557">
         <f>E30+E31+E131+E141+E151+E162+E215+E256+E264+E285+E324+E406+E463+E482+E514+E545</f>
@@ -8410,10 +8398,10 @@
     </row>
     <row r="558" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A558" s="15" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="B558" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="E558">
         <f>E28+E33+E52+E97+E108+E225+E246+E312+E362+E371+E384+E471+E528+E553</f>
@@ -8430,10 +8418,10 @@
     </row>
     <row r="559" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A559" s="16" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="B559" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="E559">
         <f>E29+E32+E69+E78+E120+E168+E175+E187+E198+E203+E235+E388+E429+E477+E500+E537</f>
@@ -8450,18 +8438,18 @@
     </row>
     <row r="563" spans="4:7" x14ac:dyDescent="0.2">
       <c r="F563" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="G563" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
     </row>
     <row r="564" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D564" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="G564" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
     </row>
     <row r="565" spans="4:7" x14ac:dyDescent="0.2">
@@ -8554,7 +8542,7 @@
     </row>
     <row r="575" spans="4:7" x14ac:dyDescent="0.2">
       <c r="E575" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
     </row>
   </sheetData>
@@ -8594,56 +8582,59 @@
   <sheetData>
     <row r="1" spans="1:4" ht="34" x14ac:dyDescent="0.4">
       <c r="A1" s="37" t="s">
-        <v>81</v>
+        <v>392</v>
       </c>
       <c r="B1" s="37"/>
       <c r="C1" s="37"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="38" t="s">
-        <v>83</v>
+        <v>393</v>
       </c>
       <c r="B5" s="38"/>
       <c r="C5" s="38"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="D9" s="1" t="s">
         <v>87</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>90</v>
+        <v>398</v>
       </c>
       <c r="B10" t="s">
-        <v>91</v>
+        <v>399</v>
       </c>
       <c r="C10" s="3">
-        <v>1234567</v>
+        <v>7026787</v>
+      </c>
+      <c r="D10" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
@@ -8651,61 +8642,61 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B15">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B17" s="4">
-        <v>45351</v>
+        <v>45924</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B18" s="4">
-        <v>45594</v>
+        <v>46051</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B21" t="s">
-        <v>98</v>
+        <v>402</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="24" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="H23" s="21"/>
     </row>
     <row r="25" spans="1:8" ht="19" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="G25" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
@@ -8769,7 +8760,7 @@
       <c r="A32" s="15"/>
       <c r="B32" s="13"/>
       <c r="C32" s="22" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="D32" s="22">
         <f>-SUM(D26:D31)</f>
@@ -8793,7 +8784,7 @@
         <v>45</v>
       </c>
       <c r="B34" s="24" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="C34" s="24"/>
       <c r="D34" s="24"/>
@@ -8818,7 +8809,7 @@
       <c r="A36" s="16"/>
       <c r="B36" s="14"/>
       <c r="C36" s="22" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="D36" s="22">
         <f>-SUM(D34:D35)</f>
@@ -8843,7 +8834,7 @@
     </row>
     <row r="39" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A39" s="7" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="B39" s="9" t="s">
         <v>7</v>
@@ -8931,7 +8922,7 @@
       <c r="A46" s="7"/>
       <c r="B46" s="9"/>
       <c r="C46" s="22" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="D46" s="22">
         <f>-SUM(D39:D45)</f>
@@ -8978,7 +8969,7 @@
     <row r="51" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A51" s="26"/>
       <c r="B51" s="29" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="C51" s="27"/>
       <c r="D51" s="27"/>
@@ -8995,7 +8986,7 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A53" s="26" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="B53" s="27" t="s">
         <v>77</v>
@@ -9009,7 +9000,7 @@
     <row r="54" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A54" s="26"/>
       <c r="B54" s="27" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C54" s="27"/>
       <c r="D54" s="27"/>
@@ -9020,7 +9011,7 @@
     <row r="55" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A55" s="26"/>
       <c r="B55" s="27" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="C55" s="27"/>
       <c r="D55" s="27"/>
@@ -9037,7 +9028,7 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A57" s="26" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="B57" s="27" t="s">
         <v>77</v>
@@ -9051,7 +9042,7 @@
     <row r="58" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A58" s="26"/>
       <c r="B58" s="27" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C58" s="27"/>
       <c r="D58" s="27"/>
@@ -9062,7 +9053,7 @@
     <row r="59" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A59" s="26"/>
       <c r="B59" s="27" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="C59" s="27"/>
       <c r="D59" s="27"/>
@@ -9074,7 +9065,7 @@
       <c r="A60" s="15"/>
       <c r="B60" s="13"/>
       <c r="C60" s="22" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="D60" s="22">
         <f>-SUM(D49:D59)</f>
@@ -9119,7 +9110,7 @@
     <row r="65" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A65" s="15"/>
       <c r="B65" s="13" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="C65" s="13"/>
       <c r="D65" s="13"/>
@@ -9142,7 +9133,7 @@
       <c r="A67" s="15"/>
       <c r="B67" s="13"/>
       <c r="C67" s="22" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="D67" s="22">
         <f>-SUM(D63:D66)</f>
@@ -9165,7 +9156,7 @@
         <v>35</v>
       </c>
       <c r="B72" s="31" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="C72" s="31"/>
       <c r="D72" s="31"/>
@@ -9176,7 +9167,7 @@
     <row r="73" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A73" s="30"/>
       <c r="B73" s="31" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="C73" s="31"/>
       <c r="D73" s="31"/>
@@ -9187,7 +9178,7 @@
     <row r="74" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A74" s="30"/>
       <c r="B74" s="31" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C74" s="31"/>
       <c r="D74" s="31"/>
@@ -9198,7 +9189,7 @@
     <row r="75" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A75" s="30"/>
       <c r="B75" s="31" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="C75" s="31"/>
       <c r="D75" s="31"/>
@@ -9210,7 +9201,7 @@
       <c r="A76" s="11"/>
       <c r="B76" s="12"/>
       <c r="C76" s="22" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="D76" s="22">
         <f>-SUM(D72:D75)</f>
@@ -9277,7 +9268,7 @@
     <row r="83" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A83" s="7"/>
       <c r="B83" s="8" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="C83" s="8"/>
       <c r="D83" s="8"/>
@@ -9346,7 +9337,7 @@
       <c r="A89" s="7"/>
       <c r="B89" s="8"/>
       <c r="C89" s="22" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="D89" s="22">
         <f>-SUM(D79:D88)</f>
@@ -9366,10 +9357,10 @@
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A91" s="11" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="B91" s="12" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="C91" s="12"/>
       <c r="D91" s="12"/>
@@ -9391,7 +9382,7 @@
     <row r="93" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A93" s="11"/>
       <c r="B93" s="12" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="C93" s="12"/>
       <c r="D93" s="12"/>
@@ -9403,7 +9394,7 @@
       <c r="A94" s="11"/>
       <c r="B94" s="12"/>
       <c r="C94" s="22" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="D94" s="22">
         <f>-SUM(D91:D93)</f>
@@ -9460,7 +9451,7 @@
     <row r="99" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B99" s="31"/>
       <c r="C99" s="31" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="D99" s="31"/>
       <c r="E99" s="31">
@@ -9470,7 +9461,7 @@
     <row r="100" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B100" s="31"/>
       <c r="C100" s="31" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="D100" s="31"/>
       <c r="E100" s="31">
@@ -9500,7 +9491,7 @@
     <row r="103" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B103" s="31"/>
       <c r="C103" s="31" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D103" s="31"/>
       <c r="E103" s="31">
@@ -9510,7 +9501,7 @@
     <row r="104" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B104" s="12"/>
       <c r="C104" s="22" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="D104" s="22">
         <f>-SUM(D96:D103)</f>
@@ -9603,7 +9594,7 @@
     <row r="113" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B113" s="25"/>
       <c r="C113" s="25" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D113" s="25"/>
       <c r="E113" s="25">
@@ -9613,7 +9604,7 @@
     <row r="114" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B114" s="13"/>
       <c r="C114" s="22" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="D114" s="22">
         <f>-SUM(D106:D113)</f>
@@ -9706,7 +9697,7 @@
     <row r="123" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B123" s="24"/>
       <c r="C123" s="24" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D123" s="24"/>
       <c r="E123" s="24">
@@ -9716,7 +9707,7 @@
     <row r="124" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B124" s="14"/>
       <c r="C124" s="22" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="D124" s="22">
         <f>-SUM(D116:D123)</f>
@@ -9736,13 +9727,13 @@
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A127" s="31" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="B127" s="31" t="s">
         <v>6</v>
       </c>
       <c r="C127" s="31" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="D127" s="31"/>
       <c r="E127" s="31">
@@ -9753,10 +9744,10 @@
       <c r="A128" s="31"/>
       <c r="B128" s="31"/>
       <c r="C128" s="31" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="D128" s="31" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="E128" s="31">
         <v>5</v>
@@ -9767,7 +9758,7 @@
       <c r="B129" s="31"/>
       <c r="C129" s="31"/>
       <c r="D129" s="31" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="E129" s="31">
         <v>5</v>
@@ -9777,7 +9768,7 @@
       <c r="A130" s="31"/>
       <c r="B130" s="31"/>
       <c r="C130" s="31" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="D130" s="31"/>
       <c r="E130" s="31">
@@ -9788,7 +9779,7 @@
       <c r="A131" s="31"/>
       <c r="B131" s="31"/>
       <c r="C131" s="31" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="D131" s="31"/>
       <c r="E131" s="31">
@@ -9799,7 +9790,7 @@
       <c r="A132" s="31"/>
       <c r="B132" s="31"/>
       <c r="C132" s="31" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="D132" s="31"/>
       <c r="E132" s="31">
@@ -9810,7 +9801,7 @@
       <c r="A133" s="12"/>
       <c r="B133" s="12"/>
       <c r="C133" s="22" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="D133" s="22">
         <f>-SUM(D127:D132)</f>
@@ -9831,13 +9822,13 @@
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A135" s="31" t="s">
+        <v>109</v>
+      </c>
+      <c r="B135" s="31" t="s">
         <v>114</v>
       </c>
-      <c r="B135" s="31" t="s">
-        <v>119</v>
-      </c>
       <c r="C135" s="31" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="D135" s="31"/>
       <c r="E135" s="31">
@@ -9848,7 +9839,7 @@
       <c r="A136" s="31"/>
       <c r="B136" s="31"/>
       <c r="C136" s="31" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="D136" s="31"/>
       <c r="E136" s="31">
@@ -9859,7 +9850,7 @@
       <c r="A137" s="31"/>
       <c r="B137" s="31"/>
       <c r="C137" s="31" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="D137" s="31"/>
       <c r="E137" s="31">
@@ -9870,10 +9861,10 @@
       <c r="A138" s="31"/>
       <c r="B138" s="31"/>
       <c r="C138" s="31" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="D138" s="31" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="E138" s="31">
         <v>5</v>
@@ -9884,7 +9875,7 @@
       <c r="B139" s="31"/>
       <c r="C139" s="31"/>
       <c r="D139" s="31" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="E139" s="31">
         <v>5</v>
@@ -9895,7 +9886,7 @@
       <c r="B140" s="31"/>
       <c r="C140" s="31"/>
       <c r="D140" s="31" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="E140" s="31">
         <v>5</v>
@@ -9916,7 +9907,7 @@
       <c r="A142" s="11"/>
       <c r="B142" s="12"/>
       <c r="C142" s="22" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="D142" s="22">
         <f>-SUM(D135:D141)</f>
@@ -9936,10 +9927,10 @@
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A144" s="26" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="B144" s="27" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C144" s="27" t="s">
         <v>54</v>
@@ -9953,7 +9944,7 @@
       <c r="A145" s="26"/>
       <c r="B145" s="27"/>
       <c r="C145" s="27" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="D145" s="27"/>
       <c r="E145" s="27">
@@ -9964,7 +9955,7 @@
       <c r="A146" s="26"/>
       <c r="B146" s="27"/>
       <c r="C146" s="27" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="D146" s="27"/>
       <c r="E146" s="27">
@@ -9975,7 +9966,7 @@
       <c r="A147" s="26"/>
       <c r="B147" s="27"/>
       <c r="C147" s="27" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="D147" s="27"/>
       <c r="E147" s="27">
@@ -9986,7 +9977,7 @@
       <c r="A148" s="26"/>
       <c r="B148" s="27"/>
       <c r="C148" s="27" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="D148" s="27"/>
       <c r="E148" s="27">
@@ -9997,7 +9988,7 @@
       <c r="A149" s="15"/>
       <c r="B149" s="13"/>
       <c r="C149" s="22" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="D149" s="22">
         <f>-SUM(D144:D148)</f>
@@ -10017,10 +10008,10 @@
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A151" s="23" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="B151" s="24" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C151" s="24" t="s">
         <v>54</v>
@@ -10034,7 +10025,7 @@
       <c r="A152" s="23"/>
       <c r="B152" s="24"/>
       <c r="C152" s="24" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="D152" s="24"/>
       <c r="E152" s="24">
@@ -10045,7 +10036,7 @@
       <c r="A153" s="23"/>
       <c r="B153" s="24"/>
       <c r="C153" s="24" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="D153" s="24"/>
       <c r="E153" s="24">
@@ -10056,7 +10047,7 @@
       <c r="A154" s="16"/>
       <c r="B154" s="14"/>
       <c r="C154" s="22" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="D154" s="22">
         <f>-SUM(D151:D153)</f>
@@ -10076,10 +10067,10 @@
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A157" s="16" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B157" s="14" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C157" s="14"/>
       <c r="D157" s="14"/>
@@ -10090,7 +10081,7 @@
     <row r="158" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A158" s="16"/>
       <c r="B158" s="14" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="C158" s="14"/>
       <c r="D158" s="14"/>
@@ -10101,7 +10092,7 @@
     <row r="159" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A159" s="16"/>
       <c r="B159" s="14" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="C159" s="14"/>
       <c r="D159" s="14"/>
@@ -10112,7 +10103,7 @@
     <row r="160" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A160" s="16"/>
       <c r="B160" s="14" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="C160" s="14"/>
       <c r="D160" s="14"/>
@@ -10123,7 +10114,7 @@
     <row r="161" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A161" s="16"/>
       <c r="B161" s="14" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="C161" s="14"/>
       <c r="D161" s="14"/>
@@ -10135,7 +10126,7 @@
       <c r="A162" s="16"/>
       <c r="B162" s="14"/>
       <c r="C162" s="22" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="D162" s="22">
         <f>-SUM(D157:D161)</f>
@@ -10155,10 +10146,10 @@
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A164" s="30" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="B164" s="31" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="C164" s="31"/>
       <c r="D164" s="31"/>
@@ -10191,7 +10182,7 @@
     <row r="167" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A167" s="30"/>
       <c r="B167" s="31" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="C167" s="31"/>
       <c r="D167" s="31"/>
@@ -10213,7 +10204,7 @@
     <row r="169" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A169" s="30"/>
       <c r="B169" s="31" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="C169" s="31"/>
       <c r="D169" s="31"/>
@@ -10225,7 +10216,7 @@
       <c r="A170" s="11"/>
       <c r="B170" s="12"/>
       <c r="C170" s="22" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="D170" s="22">
         <f>-SUM(D164:D169)</f>
@@ -10245,10 +10236,10 @@
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A172" s="26" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="B172" s="27" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C172" s="27"/>
       <c r="D172" s="27"/>
@@ -10259,7 +10250,7 @@
     <row r="173" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A173" s="26"/>
       <c r="B173" s="27" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="C173" s="27"/>
       <c r="D173" s="27"/>
@@ -10281,7 +10272,7 @@
     <row r="175" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A175" s="26"/>
       <c r="B175" s="27" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="C175" s="27"/>
       <c r="D175" s="27"/>
@@ -10292,7 +10283,7 @@
     <row r="176" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A176" s="26"/>
       <c r="B176" s="27" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="C176" s="27"/>
       <c r="D176" s="27"/>
@@ -10303,7 +10294,7 @@
     <row r="177" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A177" s="26"/>
       <c r="B177" s="27" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C177" s="27"/>
       <c r="D177" s="27"/>
@@ -10315,7 +10306,7 @@
       <c r="A178" s="15"/>
       <c r="B178" s="13"/>
       <c r="C178" s="22" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="D178" s="22">
         <f>-SUM(D172:D177)</f>
@@ -10335,7 +10326,7 @@
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A180" s="23" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="B180" s="24" t="s">
         <v>50</v>
@@ -10349,7 +10340,7 @@
     <row r="181" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A181" s="23"/>
       <c r="B181" s="24" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="C181" s="24"/>
       <c r="D181" s="24"/>
@@ -10360,7 +10351,7 @@
     <row r="182" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A182" s="23"/>
       <c r="B182" s="24" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="C182" s="24"/>
       <c r="D182" s="24"/>
@@ -10371,7 +10362,7 @@
     <row r="183" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A183" s="23"/>
       <c r="B183" s="24" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C183" s="24"/>
       <c r="D183" s="24"/>
@@ -10404,7 +10395,7 @@
     <row r="186" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A186" s="23"/>
       <c r="B186" s="24" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="C186" s="24"/>
       <c r="D186" s="24"/>
@@ -10415,7 +10406,7 @@
     <row r="187" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A187" s="23"/>
       <c r="B187" s="24" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="C187" s="24"/>
       <c r="D187" s="24"/>
@@ -10426,7 +10417,7 @@
     <row r="188" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A188" s="23"/>
       <c r="B188" s="24" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="C188" s="24"/>
       <c r="D188" s="24"/>
@@ -10437,7 +10428,7 @@
     <row r="189" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A189" s="23"/>
       <c r="B189" s="24" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="C189" s="24"/>
       <c r="D189" s="24"/>
@@ -10449,7 +10440,7 @@
       <c r="A190" s="16"/>
       <c r="B190" s="14"/>
       <c r="C190" s="22" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="D190" s="22">
         <f>-SUM(D180:D189)</f>
@@ -10469,13 +10460,13 @@
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A194" s="7" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="B194" s="8" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C194" s="8" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="D194" s="8"/>
       <c r="E194" s="8">
@@ -10486,7 +10477,7 @@
       <c r="A195" s="7"/>
       <c r="B195" s="8"/>
       <c r="C195" s="8" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D195" s="8"/>
       <c r="E195" s="8">
@@ -10497,7 +10488,7 @@
       <c r="A196" s="7"/>
       <c r="B196" s="8"/>
       <c r="C196" s="8" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="D196" s="8"/>
       <c r="E196" s="8">
@@ -10507,10 +10498,10 @@
     <row r="197" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A197" s="7"/>
       <c r="B197" s="8" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="C197" s="8" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="D197" s="8"/>
       <c r="E197" s="8">
@@ -10521,7 +10512,7 @@
       <c r="A198" s="7"/>
       <c r="B198" s="8"/>
       <c r="C198" s="8" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="D198" s="8"/>
       <c r="E198" s="8">
@@ -10532,7 +10523,7 @@
       <c r="A199" s="7"/>
       <c r="B199" s="8"/>
       <c r="C199" s="8" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="D199" s="8"/>
       <c r="E199" s="8">
@@ -10543,7 +10534,7 @@
       <c r="A200" s="7"/>
       <c r="B200" s="8"/>
       <c r="C200" s="8" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="D200" s="8"/>
       <c r="E200" s="8">
@@ -10554,7 +10545,7 @@
       <c r="A201" s="7"/>
       <c r="B201" s="8"/>
       <c r="C201" s="8" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="D201" s="8"/>
       <c r="E201" s="8">
@@ -10564,7 +10555,7 @@
     <row r="202" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A202" s="7"/>
       <c r="B202" s="8" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="C202" s="8"/>
       <c r="D202" s="8"/>
@@ -10575,10 +10566,10 @@
     <row r="203" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A203" s="7"/>
       <c r="B203" s="8" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="C203" s="8" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="D203" s="8"/>
       <c r="E203" s="8">
@@ -10589,7 +10580,7 @@
       <c r="A204" s="7"/>
       <c r="B204" s="8"/>
       <c r="C204" s="8" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="D204" s="8"/>
       <c r="E204" s="8">
@@ -10611,7 +10602,7 @@
       <c r="A206" s="7"/>
       <c r="B206" s="8"/>
       <c r="C206" s="8" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="D206" s="8"/>
       <c r="E206" s="8">
@@ -10685,7 +10676,7 @@
       <c r="A212" s="7"/>
       <c r="B212" s="8"/>
       <c r="C212" s="22" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="D212" s="22">
         <f>-SUM(D194:D211)</f>
@@ -10706,7 +10697,7 @@
     <row r="218" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A218" s="7"/>
       <c r="B218" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="D218">
         <f>D213+D90+D47</f>
@@ -10722,9 +10713,11 @@
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A219" s="11"/>
+      <c r="A219" s="11" t="s">
+        <v>396</v>
+      </c>
       <c r="B219" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="D219">
         <f>D171+D105+D77+D143+D134+D95</f>
@@ -10740,9 +10733,11 @@
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A220" s="15"/>
+      <c r="A220" s="15" t="s">
+        <v>395</v>
+      </c>
       <c r="B220" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="D220">
         <f>D179+D150+D115+D61+D33+D68</f>
@@ -10758,9 +10753,11 @@
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A221" s="16"/>
+      <c r="A221" s="16" t="s">
+        <v>397</v>
+      </c>
       <c r="B221" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="D221">
         <f>D191+D155+D125+D37+D163</f>
@@ -10777,18 +10774,18 @@
     </row>
     <row r="226" spans="4:7" x14ac:dyDescent="0.2">
       <c r="F226" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="G226" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
     </row>
     <row r="227" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D227" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="G227" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
     </row>
     <row r="228" spans="4:7" x14ac:dyDescent="0.2">
@@ -10881,7 +10878,7 @@
     </row>
     <row r="238" spans="4:7" x14ac:dyDescent="0.2">
       <c r="E238" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
     </row>
     <row r="1047724" spans="5:5" x14ac:dyDescent="0.2">
@@ -10916,7 +10913,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="26" x14ac:dyDescent="0.3">
       <c r="A1" s="44" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="B1" s="44"/>
       <c r="C1" s="44"/>
@@ -10927,7 +10924,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="D4" s="20">
         <v>-1</v>
@@ -10943,7 +10940,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="D6" s="20">
         <v>-0.5</v>
@@ -10951,7 +10948,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="D7" s="20">
         <v>-0.5</v>
@@ -10959,7 +10956,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B8" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="D8" s="20">
         <v>-1</v>
@@ -10967,7 +10964,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="D9" s="20">
         <v>-1</v>
@@ -10975,7 +10972,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="D10" s="20">
         <v>-0.5</v>
@@ -10983,7 +10980,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B11" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="D11" s="20">
         <v>-0.5</v>
@@ -10991,7 +10988,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B12" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="D12" s="20">
         <v>-0.5</v>
@@ -10999,7 +10996,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="D13" s="20">
         <v>-0.5</v>
@@ -11007,7 +11004,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B14" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="D14" s="20">
         <v>-1</v>
@@ -11015,7 +11012,7 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B15" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="D15" s="20">
         <v>-0.3</v>
@@ -11023,7 +11020,7 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="D16" s="20">
         <v>-1</v>
@@ -11031,7 +11028,7 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B17" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="D17" s="20">
         <v>-0.2</v>
@@ -11039,7 +11036,7 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B18" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="D18" s="20">
         <v>-1</v>
@@ -11050,10 +11047,10 @@
         <v>42</v>
       </c>
       <c r="B22" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C22" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="D22" s="20">
         <v>-0.25</v>
@@ -11061,7 +11058,7 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="C23" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D23" s="20">
         <v>-0.25</v>
@@ -11069,7 +11066,7 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="C24" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="D24" s="20">
         <v>-0.25</v>
@@ -11077,10 +11074,10 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B25" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="C25" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="D25" s="20">
         <v>-0.25</v>
@@ -11088,7 +11085,7 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="C26" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="D26" s="20">
         <v>-0.25</v>
@@ -11096,7 +11093,7 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="C27" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="D27" s="20">
         <v>-0.25</v>
@@ -11104,7 +11101,7 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="C28" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="D28" s="20">
         <v>-0.25</v>
@@ -11112,15 +11109,15 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B30" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B31" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="C31" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="D31" s="20">
         <v>-0.25</v>
@@ -11128,7 +11125,7 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="C32" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="D32" s="20">
         <v>-0.25</v>
@@ -11136,7 +11133,7 @@
     </row>
     <row r="33" spans="2:4" x14ac:dyDescent="0.2">
       <c r="C33" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="D33" s="20">
         <v>-0.25</v>
@@ -11144,7 +11141,7 @@
     </row>
     <row r="34" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B34" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="D34" s="20">
         <v>-1</v>
@@ -11152,10 +11149,10 @@
     </row>
     <row r="35" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B35" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="C35" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="D35" s="20">
         <v>-1</v>
@@ -11163,7 +11160,7 @@
     </row>
     <row r="36" spans="2:4" x14ac:dyDescent="0.2">
       <c r="C36" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="D36" s="20">
         <v>-1</v>
@@ -11171,7 +11168,7 @@
     </row>
     <row r="37" spans="2:4" x14ac:dyDescent="0.2">
       <c r="C37" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="D37" s="20">
         <v>-1</v>

--- a/ProjectManagement/EvaluationHWAndProject.xlsx
+++ b/ProjectManagement/EvaluationHWAndProject.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10112"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gautamramesh/Documents/githubNew/ML26-03-Car-Licence-Plate-Identification-with-a-Jetson-Nano/ProjectManagement/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\gthub\ML26-03-Car-Licence-Plate-Identification-with-a-Jetson-Nano\ProjectManagement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9708DD20-24C4-9149-B723-29A0C79DFC38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E26A49B6-0E61-44F0-A8A2-B7FAB6E4F401}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="620" windowWidth="51200" windowHeight="25260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Report" sheetId="2" r:id="rId1"/>
@@ -274,7 +274,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="886" uniqueCount="403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="886" uniqueCount="404">
   <si>
     <t>Literature</t>
   </si>
@@ -1483,6 +1483,9 @@
   </si>
   <si>
     <t xml:space="preserve">  &lt;10&gt;</t>
+  </si>
+  <si>
+    <t>Shubhankar Dumka</t>
   </si>
 </sst>
 </file>
@@ -2078,45 +2081,45 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:M575"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:6" ht="34" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:6" ht="33.6" x14ac:dyDescent="0.65">
       <c r="A2" s="37" t="s">
         <v>392</v>
       </c>
       <c r="B2" s="37"/>
       <c r="C2" s="37"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="38" t="s">
         <v>393</v>
       </c>
       <c r="B6" s="38"/>
       <c r="C6" s="38"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="2" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>84</v>
       </c>
@@ -2133,7 +2136,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>398</v>
       </c>
@@ -2147,10 +2150,10 @@
         <v>401</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="C12" s="3"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>88</v>
       </c>
@@ -2158,7 +2161,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>89</v>
       </c>
@@ -2166,7 +2169,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>90</v>
       </c>
@@ -2174,7 +2177,7 @@
         <v>45924</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>91</v>
       </c>
@@ -2182,7 +2185,7 @@
         <v>46051</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>92</v>
       </c>
@@ -2190,7 +2193,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>93</v>
       </c>
@@ -2198,12 +2201,12 @@
         <v>218</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="24" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" ht="23.4" x14ac:dyDescent="0.45">
       <c r="A25" s="6" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="19" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" ht="18" x14ac:dyDescent="0.35">
       <c r="A27" s="5" t="s">
         <v>95</v>
       </c>
@@ -2211,7 +2214,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="13"/>
       <c r="B28" s="13" t="s">
         <v>166</v>
@@ -2228,7 +2231,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="14"/>
       <c r="B29" s="14" t="s">
         <v>166</v>
@@ -2245,7 +2248,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="12"/>
       <c r="B30" s="12" t="s">
         <v>166</v>
@@ -2262,7 +2265,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="12"/>
       <c r="B31" s="12" t="s">
         <v>167</v>
@@ -2279,7 +2282,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="14"/>
       <c r="B32" s="14" t="s">
         <v>167</v>
@@ -2296,7 +2299,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="13"/>
       <c r="B33" s="13" t="s">
         <v>167</v>
@@ -2313,12 +2316,12 @@
         <v>391</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" ht="21" x14ac:dyDescent="0.4">
       <c r="A35" s="28" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="15" t="s">
         <v>0</v>
       </c>
@@ -2328,7 +2331,7 @@
       <c r="E36" s="13"/>
       <c r="F36" s="13"/>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="15"/>
       <c r="B37" s="13" t="s">
         <v>3</v>
@@ -2340,7 +2343,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="13"/>
       <c r="B38" s="13" t="s">
         <v>28</v>
@@ -2352,7 +2355,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="13"/>
       <c r="B39" s="13" t="s">
         <v>4</v>
@@ -2364,7 +2367,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="13"/>
       <c r="B40" s="13" t="s">
         <v>5</v>
@@ -2376,7 +2379,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="13"/>
       <c r="B41" s="13" t="s">
         <v>6</v>
@@ -2388,7 +2391,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="13"/>
       <c r="B42" s="13" t="s">
         <v>1</v>
@@ -2400,7 +2403,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="15"/>
       <c r="B43" s="13"/>
       <c r="C43" s="13"/>
@@ -2408,7 +2411,7 @@
       <c r="E43" s="13"/>
       <c r="F43" s="13"/>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="15"/>
       <c r="B44" s="13" t="s">
         <v>2</v>
@@ -2422,7 +2425,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="13"/>
       <c r="B45" s="13"/>
       <c r="C45" s="13" t="s">
@@ -2434,7 +2437,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="13"/>
       <c r="B46" s="13"/>
       <c r="C46" s="13" t="s">
@@ -2446,7 +2449,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="13"/>
       <c r="B47" s="13"/>
       <c r="C47" s="13" t="s">
@@ -2458,7 +2461,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="13"/>
       <c r="B48" s="13"/>
       <c r="C48" s="13" t="s">
@@ -2470,7 +2473,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" s="13"/>
       <c r="B49" s="13"/>
       <c r="C49" s="13" t="s">
@@ -2482,7 +2485,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="13"/>
       <c r="B50" s="13"/>
       <c r="C50" s="13" t="s">
@@ -2494,7 +2497,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" s="13"/>
       <c r="B51" s="13"/>
       <c r="C51" s="13"/>
@@ -2506,7 +2509,7 @@
       </c>
       <c r="F51" s="13"/>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="E52">
         <f>SUM(E36:E50)*E51</f>
         <v>0</v>
@@ -2516,12 +2519,12 @@
         <v>100</v>
       </c>
     </row>
-    <row r="54" spans="1:7" s="5" customFormat="1" ht="21" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" s="5" customFormat="1" ht="21" x14ac:dyDescent="0.4">
       <c r="A54" s="28" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" s="16" t="s">
         <v>135</v>
       </c>
@@ -2538,7 +2541,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" s="16"/>
       <c r="B56" s="14" t="s">
         <v>50</v>
@@ -2551,7 +2554,7 @@
       </c>
       <c r="G56" s="39"/>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" s="16"/>
       <c r="B57" s="14" t="s">
         <v>233</v>
@@ -2564,7 +2567,7 @@
       </c>
       <c r="G57" s="39"/>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" s="16"/>
       <c r="B58" s="14" t="s">
         <v>136</v>
@@ -2577,7 +2580,7 @@
       </c>
       <c r="G58" s="39"/>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" s="16"/>
       <c r="B59" s="14" t="s">
         <v>137</v>
@@ -2590,7 +2593,7 @@
       </c>
       <c r="G59" s="39"/>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" s="16"/>
       <c r="B60" s="14" t="s">
         <v>55</v>
@@ -2603,7 +2606,7 @@
       </c>
       <c r="G60" s="39"/>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" s="16"/>
       <c r="B61" s="14" t="s">
         <v>54</v>
@@ -2616,7 +2619,7 @@
       </c>
       <c r="G61" s="39"/>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" s="16"/>
       <c r="B62" s="14" t="s">
         <v>138</v>
@@ -2629,7 +2632,7 @@
       </c>
       <c r="G62" s="39"/>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" s="16"/>
       <c r="B63" s="14" t="s">
         <v>139</v>
@@ -2642,7 +2645,7 @@
       </c>
       <c r="G63" s="39"/>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" s="16"/>
       <c r="B64" s="14" t="s">
         <v>140</v>
@@ -2655,7 +2658,7 @@
       </c>
       <c r="G64" s="39"/>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" s="16"/>
       <c r="B65" s="14" t="s">
         <v>323</v>
@@ -2668,7 +2671,7 @@
       </c>
       <c r="G65" s="39"/>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" s="16"/>
       <c r="B66" s="14" t="s">
         <v>324</v>
@@ -2681,7 +2684,7 @@
       </c>
       <c r="G66" s="39"/>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" s="16"/>
       <c r="B67" s="14" t="s">
         <v>141</v>
@@ -2694,7 +2697,7 @@
       </c>
       <c r="G67" s="39"/>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" s="16"/>
       <c r="B68" s="14"/>
       <c r="C68" s="14"/>
@@ -2707,7 +2710,7 @@
       <c r="F68" s="14"/>
       <c r="G68" s="39"/>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" s="1"/>
       <c r="E69">
         <f>-SUM(E55:E67)*E68</f>
@@ -2718,12 +2721,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="70" spans="1:7" s="5" customFormat="1" ht="19" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" s="5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A70" s="5" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" s="16" t="s">
         <v>135</v>
       </c>
@@ -2740,7 +2743,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" s="16"/>
       <c r="B72" s="14" t="s">
         <v>46</v>
@@ -2753,7 +2756,7 @@
       </c>
       <c r="G72" s="42"/>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" s="16"/>
       <c r="B73" s="14" t="s">
         <v>344</v>
@@ -2766,7 +2769,7 @@
       </c>
       <c r="G73" s="42"/>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" s="16"/>
       <c r="B74" s="14" t="s">
         <v>70</v>
@@ -2779,7 +2782,7 @@
       </c>
       <c r="G74" s="42"/>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" s="16"/>
       <c r="B75" s="14" t="s">
         <v>345</v>
@@ -2792,7 +2795,7 @@
       </c>
       <c r="G75" s="42"/>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" s="16"/>
       <c r="B76" s="14" t="s">
         <v>346</v>
@@ -2805,7 +2808,7 @@
       </c>
       <c r="G76" s="42"/>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" s="16"/>
       <c r="B77" s="14"/>
       <c r="C77" s="14"/>
@@ -2818,7 +2821,7 @@
       <c r="F77" s="14"/>
       <c r="G77" s="42"/>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" s="1"/>
       <c r="E78">
         <f>-SUM(E71:E76)*E77</f>
@@ -2829,15 +2832,15 @@
         <v>40</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" s="1"/>
     </row>
-    <row r="80" spans="1:7" ht="19" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A80" s="5" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" s="7" t="s">
         <v>380</v>
       </c>
@@ -2856,7 +2859,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" s="7"/>
       <c r="B82" s="7" t="s">
         <v>382</v>
@@ -2871,7 +2874,7 @@
       </c>
       <c r="G82" s="43"/>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" s="7"/>
       <c r="B83" s="7"/>
       <c r="C83" s="8" t="s">
@@ -2884,7 +2887,7 @@
       </c>
       <c r="G83" s="43"/>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" s="7"/>
       <c r="B84" s="7"/>
       <c r="C84" s="8" t="s">
@@ -2897,7 +2900,7 @@
       </c>
       <c r="G84" s="43"/>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" s="7"/>
       <c r="B85" s="7"/>
       <c r="C85" s="7"/>
@@ -2910,7 +2913,7 @@
       <c r="F85" s="7"/>
       <c r="G85" s="43"/>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="E86">
@@ -2922,15 +2925,15 @@
         <v>50</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" s="1"/>
     </row>
-    <row r="88" spans="1:7" ht="21" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:7" ht="21" x14ac:dyDescent="0.4">
       <c r="A88" s="28" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" s="15" t="s">
         <v>317</v>
       </c>
@@ -2944,7 +2947,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" s="15"/>
       <c r="B90" s="13" t="s">
         <v>131</v>
@@ -2956,7 +2959,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" s="15"/>
       <c r="B91" s="13" t="s">
         <v>235</v>
@@ -2968,7 +2971,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" s="15"/>
       <c r="B92" s="13" t="s">
         <v>8</v>
@@ -2980,7 +2983,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" s="15"/>
       <c r="B93" s="13" t="s">
         <v>132</v>
@@ -2992,7 +2995,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" s="15"/>
       <c r="B94" s="13" t="s">
         <v>133</v>
@@ -3004,7 +3007,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" s="15"/>
       <c r="B95" s="13" t="s">
         <v>134</v>
@@ -3016,7 +3019,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" s="15"/>
       <c r="B96" s="13"/>
       <c r="C96" s="13"/>
@@ -3028,7 +3031,7 @@
       </c>
       <c r="F96" s="13"/>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97" s="1"/>
       <c r="E97">
         <f>SUM(E89:E95)*E96</f>
@@ -3039,18 +3042,18 @@
         <v>40</v>
       </c>
     </row>
-    <row r="98" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="99" spans="1:6" ht="21" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="99" spans="1:6" ht="21" x14ac:dyDescent="0.4">
       <c r="A99" s="28" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="100" spans="1:6" ht="19" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A100" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A101" s="15" t="s">
         <v>7</v>
       </c>
@@ -3064,7 +3067,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A102" s="13"/>
       <c r="B102" s="13" t="s">
         <v>9</v>
@@ -3076,7 +3079,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103" s="13"/>
       <c r="B103" s="13" t="s">
         <v>10</v>
@@ -3088,7 +3091,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A104" s="13"/>
       <c r="B104" s="13" t="s">
         <v>11</v>
@@ -3100,7 +3103,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105" s="13"/>
       <c r="B105" s="13" t="s">
         <v>12</v>
@@ -3112,7 +3115,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106" s="13"/>
       <c r="B106" s="13" t="s">
         <v>100</v>
@@ -3124,7 +3127,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107" s="13"/>
       <c r="B107" s="13"/>
       <c r="C107" s="13"/>
@@ -3136,7 +3139,7 @@
       </c>
       <c r="F107" s="13"/>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E108">
         <f>SUM(E101:E106)*E107</f>
         <v>0</v>
@@ -3146,12 +3149,12 @@
         <v>35</v>
       </c>
     </row>
-    <row r="110" spans="1:6" ht="19" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A110" s="5" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A111" s="16" t="s">
         <v>275</v>
       </c>
@@ -3165,7 +3168,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A112" s="16"/>
       <c r="B112" s="14" t="s">
         <v>14</v>
@@ -3177,7 +3180,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" s="14"/>
       <c r="B113" s="14" t="s">
         <v>15</v>
@@ -3189,7 +3192,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114" s="14"/>
       <c r="B114" s="14" t="s">
         <v>16</v>
@@ -3201,7 +3204,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A115" s="14"/>
       <c r="B115" s="14" t="s">
         <v>17</v>
@@ -3213,7 +3216,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116" s="14"/>
       <c r="B116" s="14" t="s">
         <v>18</v>
@@ -3225,7 +3228,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A117" s="14"/>
       <c r="B117" s="14" t="s">
         <v>20</v>
@@ -3237,7 +3240,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="118" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A118" s="14"/>
       <c r="B118" s="32" t="s">
         <v>19</v>
@@ -3249,7 +3252,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A119" s="14"/>
       <c r="B119" s="32"/>
       <c r="C119" s="14"/>
@@ -3261,7 +3264,7 @@
       </c>
       <c r="F119" s="14"/>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="E120">
         <f>SUM(E111:E118)*E119</f>
         <v>0</v>
@@ -3271,12 +3274,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="123" spans="1:7" ht="19" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A123" s="5" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A124" s="11" t="s">
         <v>335</v>
       </c>
@@ -3297,7 +3300,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A125" s="11" t="s">
         <v>330</v>
       </c>
@@ -3316,7 +3319,7 @@
       </c>
       <c r="G125" s="40"/>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A126" s="12"/>
       <c r="B126" s="12"/>
       <c r="C126" s="12"/>
@@ -3331,7 +3334,7 @@
       </c>
       <c r="G126" s="40"/>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A127" s="12"/>
       <c r="B127" s="12"/>
       <c r="C127" s="12" t="s">
@@ -3346,7 +3349,7 @@
       </c>
       <c r="G127" s="40"/>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A128" s="12"/>
       <c r="B128" s="12"/>
       <c r="C128" s="12" t="s">
@@ -3361,7 +3364,7 @@
       </c>
       <c r="G128" s="40"/>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A129" s="12"/>
       <c r="B129" s="12"/>
       <c r="C129" s="12" t="s">
@@ -3376,7 +3379,7 @@
       </c>
       <c r="G129" s="40"/>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A130" s="12"/>
       <c r="B130" s="12"/>
       <c r="C130" s="12"/>
@@ -3389,7 +3392,7 @@
       <c r="F130" s="12"/>
       <c r="G130" s="40"/>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
       <c r="E131">
         <f>SUM(E124:E129)*E130</f>
         <v>0</v>
@@ -3400,7 +3403,7 @@
       </c>
       <c r="G131" s="40"/>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A132" s="11" t="s">
         <v>276</v>
       </c>
@@ -3419,7 +3422,7 @@
       </c>
       <c r="G132" s="40"/>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A133" s="12"/>
       <c r="B133" s="12"/>
       <c r="C133" s="12" t="s">
@@ -3436,7 +3439,7 @@
       </c>
       <c r="G133" s="40"/>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A134" s="12"/>
       <c r="B134" s="12"/>
       <c r="C134" s="12"/>
@@ -3451,7 +3454,7 @@
       </c>
       <c r="G134" s="40"/>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A135" s="11"/>
       <c r="B135" s="12"/>
       <c r="C135" s="12"/>
@@ -3466,7 +3469,7 @@
       </c>
       <c r="G135" s="40"/>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A136" s="11"/>
       <c r="B136" s="12"/>
       <c r="C136" s="12"/>
@@ -3481,7 +3484,7 @@
       </c>
       <c r="G136" s="40"/>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A137" s="11"/>
       <c r="B137" s="12"/>
       <c r="C137" s="12" t="s">
@@ -3496,7 +3499,7 @@
       </c>
       <c r="G137" s="40"/>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A138" s="12"/>
       <c r="B138" s="12"/>
       <c r="C138" s="12" t="s">
@@ -3511,7 +3514,7 @@
       </c>
       <c r="G138" s="40"/>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A139" s="12"/>
       <c r="B139" s="12"/>
       <c r="C139" s="12" t="s">
@@ -3526,7 +3529,7 @@
       </c>
       <c r="G139" s="40"/>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A140" s="12"/>
       <c r="B140" s="12"/>
       <c r="C140" s="12"/>
@@ -3539,7 +3542,7 @@
       <c r="F140" s="12"/>
       <c r="G140" s="40"/>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
       <c r="E141">
         <f>SUM(E132:E139)*E140</f>
         <v>0</v>
@@ -3550,7 +3553,7 @@
       </c>
       <c r="G141" s="40"/>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A142" s="11" t="s">
         <v>333</v>
       </c>
@@ -3569,7 +3572,7 @@
       </c>
       <c r="G142" s="40"/>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A143" s="11" t="s">
         <v>334</v>
       </c>
@@ -3584,7 +3587,7 @@
       </c>
       <c r="G143" s="40"/>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A144" s="11"/>
       <c r="B144" s="12"/>
       <c r="C144" s="12" t="s">
@@ -3597,7 +3600,7 @@
       </c>
       <c r="G144" s="40"/>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A145" s="11"/>
       <c r="B145" s="12"/>
       <c r="C145" s="12" t="s">
@@ -3614,7 +3617,7 @@
       </c>
       <c r="G145" s="40"/>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A146" s="12"/>
       <c r="B146" s="12"/>
       <c r="C146" s="12"/>
@@ -3629,7 +3632,7 @@
       </c>
       <c r="G146" s="40"/>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A147" s="12"/>
       <c r="B147" s="12"/>
       <c r="C147" s="12" t="s">
@@ -3644,7 +3647,7 @@
       </c>
       <c r="G147" s="40"/>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A148" s="12"/>
       <c r="B148" s="12"/>
       <c r="C148" s="12" t="s">
@@ -3659,7 +3662,7 @@
       </c>
       <c r="G148" s="40"/>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A149" s="12"/>
       <c r="B149" s="12"/>
       <c r="C149" s="12" t="s">
@@ -3674,7 +3677,7 @@
       </c>
       <c r="G149" s="40"/>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A150" s="12"/>
       <c r="B150" s="12"/>
       <c r="C150" s="12"/>
@@ -3687,7 +3690,7 @@
       <c r="F150" s="12"/>
       <c r="G150" s="40"/>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
       <c r="E151">
         <f>SUM(E142:E149)*E150</f>
         <v>0</v>
@@ -3698,7 +3701,7 @@
       </c>
       <c r="G151" s="40"/>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A152" s="11" t="s">
         <v>338</v>
       </c>
@@ -3717,7 +3720,7 @@
       </c>
       <c r="G152" s="40"/>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A153" s="12"/>
       <c r="B153" s="12"/>
       <c r="C153" s="12" t="s">
@@ -3734,7 +3737,7 @@
       </c>
       <c r="G153" s="40"/>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A154" s="12"/>
       <c r="B154" s="12"/>
       <c r="C154" s="12"/>
@@ -3749,7 +3752,7 @@
       </c>
       <c r="G154" s="40"/>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A155" s="11"/>
       <c r="B155" s="12"/>
       <c r="C155" s="12"/>
@@ -3764,7 +3767,7 @@
       </c>
       <c r="G155" s="40"/>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A156" s="11"/>
       <c r="B156" s="12"/>
       <c r="C156" s="12"/>
@@ -3779,7 +3782,7 @@
       </c>
       <c r="G156" s="40"/>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A157" s="11"/>
       <c r="B157" s="12"/>
       <c r="C157" s="12" t="s">
@@ -3792,7 +3795,7 @@
       </c>
       <c r="G157" s="40"/>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A158" s="11"/>
       <c r="B158" s="12"/>
       <c r="C158" s="12" t="s">
@@ -3807,7 +3810,7 @@
       </c>
       <c r="G158" s="40"/>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A159" s="12"/>
       <c r="B159" s="12"/>
       <c r="C159" s="12" t="s">
@@ -3822,7 +3825,7 @@
       </c>
       <c r="G159" s="40"/>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A160" s="12"/>
       <c r="B160" s="12"/>
       <c r="C160" s="12" t="s">
@@ -3837,7 +3840,7 @@
       </c>
       <c r="G160" s="40"/>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A161" s="12"/>
       <c r="B161" s="12"/>
       <c r="C161" s="12"/>
@@ -3850,7 +3853,7 @@
       <c r="F161" s="12"/>
       <c r="G161" s="40"/>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.3">
       <c r="E162">
         <f>SUM(E152:E160)*E161</f>
         <v>0</v>
@@ -3861,10 +3864,10 @@
       </c>
       <c r="G162" s="40"/>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.3">
       <c r="G163" s="35"/>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A164" s="16" t="s">
         <v>125</v>
       </c>
@@ -3880,7 +3883,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A165" s="16"/>
       <c r="B165" s="14"/>
       <c r="C165" s="14" t="s">
@@ -3892,7 +3895,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A166" s="16"/>
       <c r="B166" s="14"/>
       <c r="C166" s="14" t="s">
@@ -3904,7 +3907,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A167" s="16"/>
       <c r="B167" s="14"/>
       <c r="C167" s="14"/>
@@ -3916,7 +3919,7 @@
       </c>
       <c r="F167" s="14"/>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A168" s="1"/>
       <c r="E168">
         <f>-SUM(E164:E166)*E167</f>
@@ -3927,7 +3930,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A169" s="16" t="s">
         <v>125</v>
       </c>
@@ -3943,7 +3946,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A170" s="16"/>
       <c r="B170" s="14"/>
       <c r="C170" s="14" t="s">
@@ -3955,7 +3958,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A171" s="16"/>
       <c r="B171" s="14"/>
       <c r="C171" s="14" t="s">
@@ -3967,7 +3970,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A172" s="16"/>
       <c r="B172" s="14"/>
       <c r="C172" s="14" t="s">
@@ -3979,7 +3982,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A173" s="16"/>
       <c r="B173" s="14"/>
       <c r="C173" s="14" t="s">
@@ -3991,7 +3994,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A174" s="16"/>
       <c r="B174" s="14"/>
       <c r="C174" s="14"/>
@@ -4003,7 +4006,7 @@
       </c>
       <c r="F174" s="14"/>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A175" s="1"/>
       <c r="E175">
         <f>-SUM(E169:E173)*E174</f>
@@ -4014,7 +4017,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A176" s="16" t="s">
         <v>339</v>
       </c>
@@ -4032,7 +4035,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A177" s="16" t="s">
         <v>340</v>
       </c>
@@ -4046,7 +4049,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A178" s="16"/>
       <c r="B178" s="14"/>
       <c r="C178" s="14" t="s">
@@ -4058,7 +4061,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A179" s="16"/>
       <c r="B179" s="14"/>
       <c r="C179" s="14" t="s">
@@ -4070,7 +4073,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A180" s="16"/>
       <c r="B180" s="14"/>
       <c r="C180" s="14" t="s">
@@ -4082,7 +4085,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A181" s="16"/>
       <c r="B181" s="14"/>
       <c r="C181" s="14" t="s">
@@ -4098,7 +4101,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A182" s="14"/>
       <c r="B182" s="14"/>
       <c r="C182" s="14"/>
@@ -4112,7 +4115,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A183" s="14"/>
       <c r="B183" s="14"/>
       <c r="C183" s="14" t="s">
@@ -4126,7 +4129,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A184" s="14"/>
       <c r="B184" s="14"/>
       <c r="C184" s="14" t="s">
@@ -4140,7 +4143,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A185" s="14"/>
       <c r="B185" s="14"/>
       <c r="C185" s="14" t="s">
@@ -4154,7 +4157,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A186" s="14"/>
       <c r="B186" s="14"/>
       <c r="C186" s="14"/>
@@ -4166,7 +4169,7 @@
       </c>
       <c r="F186" s="14"/>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E187">
         <f>SUM(E176:E185)*E186</f>
         <v>0</v>
@@ -4176,7 +4179,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A188" s="16" t="s">
         <v>339</v>
       </c>
@@ -4194,7 +4197,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A189" s="14" t="s">
         <v>340</v>
       </c>
@@ -4208,7 +4211,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A190" s="16"/>
       <c r="B190" s="14"/>
       <c r="C190" s="14" t="s">
@@ -4220,7 +4223,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A191" s="14"/>
       <c r="B191" s="14"/>
       <c r="C191" s="14" t="s">
@@ -4236,7 +4239,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A192" s="14"/>
       <c r="B192" s="14"/>
       <c r="C192" s="14"/>
@@ -4250,7 +4253,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A193" s="16"/>
       <c r="B193" s="14"/>
       <c r="C193" s="14"/>
@@ -4264,7 +4267,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A194" s="16"/>
       <c r="B194" s="14"/>
       <c r="C194" s="14"/>
@@ -4278,7 +4281,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A195" s="14"/>
       <c r="B195" s="14"/>
       <c r="C195" s="14" t="s">
@@ -4292,7 +4295,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A196" s="14"/>
       <c r="B196" s="14"/>
       <c r="C196" s="14" t="s">
@@ -4306,7 +4309,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A197" s="14"/>
       <c r="B197" s="14"/>
       <c r="C197" s="14"/>
@@ -4318,7 +4321,7 @@
       </c>
       <c r="F197" s="14"/>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E198">
         <f>SUM(E188:E196)*E197</f>
         <v>0</v>
@@ -4328,7 +4331,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A199" s="16" t="s">
         <v>342</v>
       </c>
@@ -4342,7 +4345,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A200" s="16"/>
       <c r="B200" s="14" t="s">
         <v>127</v>
@@ -4354,7 +4357,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A201" s="16"/>
       <c r="B201" s="14" t="s">
         <v>124</v>
@@ -4366,7 +4369,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A202" s="16"/>
       <c r="B202" s="14"/>
       <c r="C202" s="14"/>
@@ -4378,7 +4381,7 @@
       </c>
       <c r="F202" s="14"/>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A203" s="1"/>
       <c r="E203">
         <f>SUM(E199:E201)*E202</f>
@@ -4389,15 +4392,15 @@
         <v>60</v>
       </c>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A204" s="1"/>
     </row>
-    <row r="205" spans="1:9" s="5" customFormat="1" ht="19" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:9" s="5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A205" s="5" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A206" s="1" t="s">
         <v>62</v>
       </c>
@@ -4414,7 +4417,7 @@
       </c>
       <c r="I206" s="1"/>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A207" s="1"/>
       <c r="B207" s="12"/>
       <c r="C207" s="12" t="s">
@@ -4426,7 +4429,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A208" s="1"/>
       <c r="B208" s="12"/>
       <c r="C208" s="12" t="s">
@@ -4438,7 +4441,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A209" s="1"/>
       <c r="B209" s="12"/>
       <c r="C209" s="12" t="s">
@@ -4450,7 +4453,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A210" s="1"/>
       <c r="B210" s="12"/>
       <c r="C210" s="12" t="s">
@@ -4462,7 +4465,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A211" s="1"/>
       <c r="B211" s="12"/>
       <c r="C211" s="12" t="s">
@@ -4474,7 +4477,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A212" s="1"/>
       <c r="B212" s="12"/>
       <c r="C212" s="12" t="s">
@@ -4486,7 +4489,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A213" s="1"/>
       <c r="B213" s="12"/>
       <c r="C213" s="12" t="s">
@@ -4498,7 +4501,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A214" s="1"/>
       <c r="B214" s="12"/>
       <c r="C214" s="12"/>
@@ -4510,7 +4513,7 @@
       </c>
       <c r="F214" s="12"/>
     </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A215" s="1"/>
       <c r="E215">
         <f>-SUM(E206:E213)*E214</f>
@@ -4521,7 +4524,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A216" s="1"/>
       <c r="B216" s="13" t="s">
         <v>63</v>
@@ -4535,7 +4538,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A217" s="1"/>
       <c r="B217" s="13"/>
       <c r="C217" s="13" t="s">
@@ -4547,7 +4550,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A218" s="1"/>
       <c r="B218" s="13"/>
       <c r="C218" s="13" t="s">
@@ -4559,7 +4562,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A219" s="1"/>
       <c r="B219" s="13"/>
       <c r="C219" s="13" t="s">
@@ -4571,7 +4574,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A220" s="1"/>
       <c r="B220" s="13"/>
       <c r="C220" s="13" t="s">
@@ -4583,7 +4586,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A221" s="1"/>
       <c r="B221" s="13"/>
       <c r="C221" s="13" t="s">
@@ -4595,7 +4598,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A222" s="1"/>
       <c r="B222" s="13"/>
       <c r="C222" s="13" t="s">
@@ -4607,7 +4610,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A223" s="1"/>
       <c r="B223" s="13"/>
       <c r="C223" s="13" t="s">
@@ -4619,7 +4622,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A224" s="1"/>
       <c r="B224" s="13"/>
       <c r="C224" s="13"/>
@@ -4631,7 +4634,7 @@
       </c>
       <c r="F224" s="13"/>
     </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A225" s="1"/>
       <c r="E225">
         <f>-SUM(E216:E223)*E224</f>
@@ -4642,7 +4645,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A226" s="1"/>
       <c r="B226" s="14" t="s">
         <v>63</v>
@@ -4656,7 +4659,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A227" s="1"/>
       <c r="B227" s="14"/>
       <c r="C227" s="14" t="s">
@@ -4668,7 +4671,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A228" s="1"/>
       <c r="B228" s="14"/>
       <c r="C228" s="14" t="s">
@@ -4680,7 +4683,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A229" s="1"/>
       <c r="B229" s="14"/>
       <c r="C229" s="14" t="s">
@@ -4692,7 +4695,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A230" s="1"/>
       <c r="B230" s="14"/>
       <c r="C230" s="14" t="s">
@@ -4704,7 +4707,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A231" s="1"/>
       <c r="B231" s="14"/>
       <c r="C231" s="14" t="s">
@@ -4716,7 +4719,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A232" s="1"/>
       <c r="B232" s="14"/>
       <c r="C232" s="14" t="s">
@@ -4728,7 +4731,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A233" s="1"/>
       <c r="B233" s="14"/>
       <c r="C233" s="14" t="s">
@@ -4740,7 +4743,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A234" s="1"/>
       <c r="B234" s="14"/>
       <c r="C234" s="14"/>
@@ -4752,7 +4755,7 @@
       </c>
       <c r="F234" s="14"/>
     </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A235" s="1"/>
       <c r="E235">
         <f>-SUM(E226:E233)*E234</f>
@@ -4763,7 +4766,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A236" s="15" t="s">
         <v>277</v>
       </c>
@@ -4779,7 +4782,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A237" s="13"/>
       <c r="B237" s="13"/>
       <c r="C237" s="13" t="s">
@@ -4791,7 +4794,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A238" s="13"/>
       <c r="B238" s="13"/>
       <c r="C238" s="13" t="s">
@@ -4803,7 +4806,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A239" s="13"/>
       <c r="B239" s="13"/>
       <c r="C239" s="13" t="s">
@@ -4815,7 +4818,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A240" s="13"/>
       <c r="B240" s="13"/>
       <c r="C240" s="13" t="s">
@@ -4827,7 +4830,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A241" s="13"/>
       <c r="B241" s="13"/>
       <c r="C241" s="13" t="s">
@@ -4839,7 +4842,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A242" s="13"/>
       <c r="B242" s="13"/>
       <c r="C242" s="13" t="s">
@@ -4851,7 +4854,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A243" s="13"/>
       <c r="B243" s="13"/>
       <c r="C243" s="13" t="s">
@@ -4863,7 +4866,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A244" s="15"/>
       <c r="B244" s="13"/>
       <c r="C244" s="13" t="s">
@@ -4875,7 +4878,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A245" s="13"/>
       <c r="B245" s="13"/>
       <c r="C245" s="13"/>
@@ -4887,7 +4890,7 @@
       </c>
       <c r="F245" s="13"/>
     </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A246" s="33"/>
       <c r="B246" s="33"/>
       <c r="C246" s="33"/>
@@ -4901,7 +4904,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A247" s="33"/>
       <c r="B247" s="33"/>
       <c r="C247" s="33"/>
@@ -4909,12 +4912,12 @@
       <c r="E247" s="33"/>
       <c r="F247" s="33"/>
     </row>
-    <row r="248" spans="1:6" ht="19" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A248" s="5" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A249" s="11" t="s">
         <v>206</v>
       </c>
@@ -4928,7 +4931,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A250" s="11" t="s">
         <v>325</v>
       </c>
@@ -4942,7 +4945,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A251" s="11"/>
       <c r="B251" s="12" t="s">
         <v>50</v>
@@ -4954,7 +4957,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A252" s="11"/>
       <c r="B252" s="12" t="s">
         <v>207</v>
@@ -4966,7 +4969,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A253" s="11"/>
       <c r="B253" s="12" t="s">
         <v>51</v>
@@ -4978,7 +4981,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A254" s="11"/>
       <c r="B254" s="12" t="s">
         <v>234</v>
@@ -4990,7 +4993,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A255" s="11"/>
       <c r="B255" s="12"/>
       <c r="C255" s="12"/>
@@ -5002,7 +5005,7 @@
       </c>
       <c r="F255" s="12"/>
     </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A256" s="1"/>
       <c r="E256">
         <f>SUM(E249:E254)*E255</f>
@@ -5013,7 +5016,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A257" s="11" t="s">
         <v>386</v>
       </c>
@@ -5030,7 +5033,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A258" s="11" t="s">
         <v>327</v>
       </c>
@@ -5045,7 +5048,7 @@
       </c>
       <c r="G258" s="41"/>
     </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A259" s="11" t="s">
         <v>326</v>
       </c>
@@ -5060,7 +5063,7 @@
       </c>
       <c r="G259" s="41"/>
     </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A260" s="11"/>
       <c r="B260" s="12"/>
       <c r="C260" s="12" t="s">
@@ -5073,7 +5076,7 @@
       </c>
       <c r="G260" s="41"/>
     </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A261" s="11"/>
       <c r="B261" s="12"/>
       <c r="C261" s="12" t="s">
@@ -5086,7 +5089,7 @@
       </c>
       <c r="G261" s="41"/>
     </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A262" s="11"/>
       <c r="B262" s="12"/>
       <c r="C262" s="12" t="s">
@@ -5099,7 +5102,7 @@
       </c>
       <c r="G262" s="41"/>
     </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A263" s="11"/>
       <c r="B263" s="12"/>
       <c r="C263" s="12"/>
@@ -5112,7 +5115,7 @@
       <c r="F263" s="12"/>
       <c r="G263" s="41"/>
     </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A264" s="1"/>
       <c r="E264">
         <f>SUM(E257:E262)*E263</f>
@@ -5123,12 +5126,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="265" spans="1:7" ht="19" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A265" s="5" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A266" s="7" t="s">
         <v>29</v>
       </c>
@@ -5140,7 +5143,7 @@
       <c r="E266" s="8"/>
       <c r="F266" s="8"/>
     </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A267" s="8"/>
       <c r="B267" s="8"/>
       <c r="C267" s="8" t="s">
@@ -5152,7 +5155,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="268" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A268" s="8"/>
       <c r="B268" s="8"/>
       <c r="C268" s="8" t="s">
@@ -5162,7 +5165,7 @@
       <c r="E268" s="8"/>
       <c r="F268" s="8"/>
     </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A269" s="8"/>
       <c r="B269" s="8"/>
       <c r="C269" s="8" t="s">
@@ -5172,7 +5175,7 @@
       <c r="E269" s="8"/>
       <c r="F269" s="8"/>
     </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A270" s="8"/>
       <c r="B270" s="8"/>
       <c r="C270" s="8" t="s">
@@ -5184,12 +5187,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="272" spans="1:7" ht="19" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A272" s="5" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A273" s="12" t="s">
         <v>75</v>
       </c>
@@ -5207,7 +5210,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A274" s="12"/>
       <c r="B274" s="12"/>
       <c r="C274" s="12"/>
@@ -5219,7 +5222,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A275" s="12"/>
       <c r="B275" s="12"/>
       <c r="C275" s="12"/>
@@ -5231,7 +5234,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A276" s="12"/>
       <c r="B276" s="12"/>
       <c r="C276" s="12"/>
@@ -5243,7 +5246,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A277" s="12"/>
       <c r="B277" s="12"/>
       <c r="C277" s="12"/>
@@ -5255,7 +5258,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A278" s="12"/>
       <c r="B278" s="12"/>
       <c r="C278" s="12"/>
@@ -5267,7 +5270,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A279" s="12"/>
       <c r="B279" s="12"/>
       <c r="C279" s="12" t="s">
@@ -5281,7 +5284,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A280" s="12"/>
       <c r="B280" s="12"/>
       <c r="C280" s="12"/>
@@ -5293,7 +5296,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A281" s="12"/>
       <c r="B281" s="12"/>
       <c r="C281" s="12"/>
@@ -5305,7 +5308,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A282" s="12"/>
       <c r="B282" s="12"/>
       <c r="C282" s="12"/>
@@ -5317,7 +5320,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="283" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A283" s="12"/>
       <c r="B283" s="12"/>
       <c r="C283" s="12"/>
@@ -5329,7 +5332,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="284" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A284" s="12"/>
       <c r="B284" s="12"/>
       <c r="C284" s="12"/>
@@ -5341,7 +5344,7 @@
       </c>
       <c r="F284" s="12"/>
     </row>
-    <row r="285" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E285">
         <f>SUM(E273:E283)*E284</f>
         <v>0</v>
@@ -5351,7 +5354,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="286" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A286" s="7" t="s">
         <v>293</v>
       </c>
@@ -5365,7 +5368,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="287" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A287" s="8"/>
       <c r="B287" s="8" t="s">
         <v>21</v>
@@ -5379,7 +5382,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="288" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A288" s="8"/>
       <c r="B288" s="8"/>
       <c r="C288" s="8" t="s">
@@ -5391,7 +5394,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="289" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A289" s="8"/>
       <c r="B289" s="8"/>
       <c r="C289" s="8" t="s">
@@ -5403,7 +5406,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="290" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A290" s="8"/>
       <c r="B290" s="8"/>
       <c r="C290" s="8" t="s">
@@ -5415,7 +5418,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="291" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A291" s="8"/>
       <c r="B291" s="8"/>
       <c r="C291" s="8" t="s">
@@ -5427,7 +5430,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="292" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A292" s="8"/>
       <c r="B292" s="8"/>
       <c r="C292" s="8" t="s">
@@ -5439,7 +5442,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="293" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A293" s="8"/>
       <c r="B293" s="8"/>
       <c r="C293" s="8"/>
@@ -5451,7 +5454,7 @@
       </c>
       <c r="F293" s="8"/>
     </row>
-    <row r="294" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E294">
         <f>SUM(E286:E292)*E293</f>
         <v>0</v>
@@ -5461,7 +5464,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="296" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A296" s="7" t="s">
         <v>299</v>
       </c>
@@ -5475,7 +5478,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="297" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A297" s="7" t="s">
         <v>301</v>
       </c>
@@ -5489,7 +5492,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="298" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A298" s="8"/>
       <c r="B298" s="8" t="s">
         <v>303</v>
@@ -5501,7 +5504,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="299" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A299" s="8"/>
       <c r="B299" s="8" t="s">
         <v>304</v>
@@ -5513,7 +5516,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="300" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A300" s="8"/>
       <c r="B300" s="8"/>
       <c r="C300" s="8"/>
@@ -5525,7 +5528,7 @@
       </c>
       <c r="F300" s="8"/>
     </row>
-    <row r="301" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E301">
         <f>SUM(E296:E299)*E300</f>
         <v>0</v>
@@ -5535,7 +5538,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="303" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A303" s="16" t="s">
         <v>305</v>
       </c>
@@ -5549,7 +5552,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="304" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A304" s="14"/>
       <c r="B304" s="14" t="s">
         <v>307</v>
@@ -5561,7 +5564,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="305" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A305" s="14"/>
       <c r="B305" s="14" t="s">
         <v>134</v>
@@ -5573,7 +5576,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="306" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A306" s="16" t="s">
         <v>308</v>
       </c>
@@ -5587,7 +5590,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="307" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A307" s="14"/>
       <c r="B307" s="14" t="s">
         <v>310</v>
@@ -5599,7 +5602,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="308" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A308" s="16" t="s">
         <v>359</v>
       </c>
@@ -5615,7 +5618,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="309" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A309" s="14"/>
       <c r="B309" s="14"/>
       <c r="C309" s="14" t="s">
@@ -5627,7 +5630,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="310" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A310" s="14"/>
       <c r="B310" s="14"/>
       <c r="C310" s="14" t="s">
@@ -5639,7 +5642,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="311" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A311" s="14"/>
       <c r="B311" s="14"/>
       <c r="C311" s="14"/>
@@ -5651,7 +5654,7 @@
       </c>
       <c r="F311" s="14"/>
     </row>
-    <row r="312" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E312">
         <f>SUM(E303:E310)*E311</f>
         <v>0</v>
@@ -5661,7 +5664,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="313" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A313" s="11" t="s">
         <v>35</v>
       </c>
@@ -5675,7 +5678,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="314" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A314" s="12"/>
       <c r="B314" s="12" t="s">
         <v>251</v>
@@ -5687,7 +5690,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="315" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A315" s="11"/>
       <c r="B315" s="12" t="s">
         <v>320</v>
@@ -5701,7 +5704,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="316" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A316" s="12"/>
       <c r="B316" s="12" t="s">
         <v>312</v>
@@ -5715,7 +5718,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="317" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A317" s="11"/>
       <c r="B317" s="12" t="s">
         <v>230</v>
@@ -5729,7 +5732,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="318" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A318" s="11"/>
       <c r="B318" s="12" t="s">
         <v>321</v>
@@ -5743,7 +5746,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="319" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A319" s="11"/>
       <c r="B319" s="12" t="s">
         <v>322</v>
@@ -5755,7 +5758,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="320" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A320" s="12"/>
       <c r="B320" s="12" t="s">
         <v>313</v>
@@ -5767,7 +5770,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="321" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A321" s="12"/>
       <c r="B321" s="12" t="s">
         <v>314</v>
@@ -5779,7 +5782,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="322" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A322" s="12"/>
       <c r="B322" s="12" t="s">
         <v>40</v>
@@ -5791,7 +5794,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="323" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A323" s="12"/>
       <c r="B323" s="12"/>
       <c r="C323" s="12"/>
@@ -5803,7 +5806,7 @@
       </c>
       <c r="F323" s="12"/>
     </row>
-    <row r="324" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E324">
         <f>SUM(E313:E322)*E323</f>
         <v>0</v>
@@ -5813,7 +5816,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="326" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A326" s="7" t="s">
         <v>347</v>
       </c>
@@ -5827,7 +5830,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="327" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A327" s="7"/>
       <c r="B327" s="8" t="s">
         <v>191</v>
@@ -5839,7 +5842,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="328" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A328" s="7"/>
       <c r="B328" s="8" t="s">
         <v>192</v>
@@ -5853,7 +5856,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="329" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A329" s="7"/>
       <c r="B329" s="8"/>
       <c r="C329" s="8" t="s">
@@ -5865,7 +5868,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="330" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A330" s="7"/>
       <c r="B330" s="8"/>
       <c r="C330" s="8" t="s">
@@ -5877,7 +5880,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="331" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A331" s="7"/>
       <c r="B331" s="8"/>
       <c r="C331" s="8" t="s">
@@ -5889,7 +5892,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="332" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A332" s="7"/>
       <c r="B332" s="8"/>
       <c r="C332" s="8" t="s">
@@ -5901,7 +5904,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="333" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A333" s="7"/>
       <c r="B333" s="8"/>
       <c r="C333" s="8"/>
@@ -5913,7 +5916,7 @@
       </c>
       <c r="F333" s="8"/>
     </row>
-    <row r="334" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A334" s="1"/>
       <c r="E334">
         <f>SUM(E326:E332)*E333</f>
@@ -5924,7 +5927,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="335" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A335" s="7" t="s">
         <v>78</v>
       </c>
@@ -5938,7 +5941,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="336" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A336" s="7"/>
       <c r="B336" s="8" t="s">
         <v>46</v>
@@ -5950,7 +5953,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="337" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A337" s="7"/>
       <c r="B337" s="8" t="s">
         <v>358</v>
@@ -5962,7 +5965,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="338" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A338" s="7"/>
       <c r="B338" s="8" t="s">
         <v>169</v>
@@ -5974,7 +5977,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="339" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A339" s="7"/>
       <c r="B339" s="8" t="s">
         <v>77</v>
@@ -5986,7 +5989,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="340" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A340" s="7"/>
       <c r="B340" s="8" t="s">
         <v>79</v>
@@ -5998,7 +6001,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="341" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A341" s="7"/>
       <c r="B341" s="7" t="s">
         <v>57</v>
@@ -6012,7 +6015,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="342" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A342" s="7"/>
       <c r="B342" s="7"/>
       <c r="C342" s="8" t="s">
@@ -6024,7 +6027,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="343" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A343" s="7"/>
       <c r="B343" s="7"/>
       <c r="C343" s="8" t="s">
@@ -6036,7 +6039,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="344" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A344" s="7"/>
       <c r="B344" s="7"/>
       <c r="C344" s="8" t="s">
@@ -6048,7 +6051,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="345" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A345" s="7"/>
       <c r="B345" s="7"/>
       <c r="C345" s="8" t="s">
@@ -6060,7 +6063,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="346" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A346" s="7"/>
       <c r="B346" s="7"/>
       <c r="C346" s="8" t="s">
@@ -6074,7 +6077,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="347" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A347" s="7"/>
       <c r="B347" s="7"/>
       <c r="C347" s="8"/>
@@ -6086,7 +6089,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="348" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A348" s="7"/>
       <c r="B348" s="7"/>
       <c r="C348" s="8"/>
@@ -6098,7 +6101,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="349" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A349" s="7"/>
       <c r="B349" s="7"/>
       <c r="C349" s="8"/>
@@ -6110,7 +6113,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="350" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A350" s="7"/>
       <c r="B350" s="7"/>
       <c r="C350" s="8"/>
@@ -6122,7 +6125,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="351" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A351" s="7"/>
       <c r="B351" s="7"/>
       <c r="C351" s="8"/>
@@ -6134,7 +6137,7 @@
       </c>
       <c r="F351" s="8"/>
     </row>
-    <row r="352" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E352">
         <f>SUM(E335:E350)*E351</f>
         <v>0</v>
@@ -6144,12 +6147,12 @@
         <v>160</v>
       </c>
     </row>
-    <row r="353" spans="1:6" ht="19" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A353" s="5" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="354" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A354" s="13" t="s">
         <v>220</v>
       </c>
@@ -6163,7 +6166,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="355" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A355" s="13"/>
       <c r="B355" s="13" t="s">
         <v>387</v>
@@ -6177,7 +6180,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="356" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A356" s="13"/>
       <c r="B356" s="13"/>
       <c r="C356" s="13" t="s">
@@ -6189,7 +6192,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="357" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A357" s="13"/>
       <c r="B357" s="13"/>
       <c r="C357" s="13" t="s">
@@ -6201,7 +6204,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="358" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A358" s="13"/>
       <c r="B358" s="13" t="s">
         <v>388</v>
@@ -6215,7 +6218,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="359" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A359" s="13"/>
       <c r="B359" s="13"/>
       <c r="C359" s="13" t="s">
@@ -6227,7 +6230,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="360" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A360" s="13"/>
       <c r="B360" s="13"/>
       <c r="C360" s="13" t="s">
@@ -6239,7 +6242,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="361" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A361" s="13"/>
       <c r="B361" s="13"/>
       <c r="C361" s="13"/>
@@ -6251,7 +6254,7 @@
       </c>
       <c r="F361" s="13"/>
     </row>
-    <row r="362" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E362">
         <f>SUM(E354:E360)*E361</f>
         <v>0</v>
@@ -6261,12 +6264,12 @@
         <v>190</v>
       </c>
     </row>
-    <row r="363" spans="1:6" s="18" customFormat="1" ht="19" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:6" s="18" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A363" s="5" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="364" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A364" s="15" t="s">
         <v>361</v>
       </c>
@@ -6282,7 +6285,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="365" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A365" s="13"/>
       <c r="B365" s="13"/>
       <c r="C365" s="13" t="s">
@@ -6296,7 +6299,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="366" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A366" s="13"/>
       <c r="B366" s="13"/>
       <c r="C366" s="13" t="s">
@@ -6310,7 +6313,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="367" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A367" s="13"/>
       <c r="B367" s="13"/>
       <c r="C367" s="13" t="s">
@@ -6324,7 +6327,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="368" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A368" s="13"/>
       <c r="B368" s="13"/>
       <c r="C368" s="13" t="s">
@@ -6338,7 +6341,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="369" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A369" s="13"/>
       <c r="B369" s="13"/>
       <c r="C369" s="13" t="s">
@@ -6352,7 +6355,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="370" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A370" s="13"/>
       <c r="B370" s="13"/>
       <c r="C370" s="13"/>
@@ -6364,7 +6367,7 @@
       </c>
       <c r="F370" s="13"/>
     </row>
-    <row r="371" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E371">
         <f>SUM(E364:E369)*E370</f>
         <v>0</v>
@@ -6374,7 +6377,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="372" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A372" s="15" t="s">
         <v>44</v>
       </c>
@@ -6388,7 +6391,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="373" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A373" s="15"/>
       <c r="B373" s="17" t="s">
         <v>77</v>
@@ -6400,7 +6403,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="374" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A374" s="15"/>
       <c r="B374" s="17" t="s">
         <v>124</v>
@@ -6412,7 +6415,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="375" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A375" s="15"/>
       <c r="B375" s="13"/>
       <c r="C375" s="13"/>
@@ -6420,7 +6423,7 @@
       <c r="E375" s="13"/>
       <c r="F375" s="13"/>
     </row>
-    <row r="376" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A376" s="15" t="s">
         <v>122</v>
       </c>
@@ -6434,7 +6437,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="377" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A377" s="15"/>
       <c r="B377" s="13" t="s">
         <v>123</v>
@@ -6446,7 +6449,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="378" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A378" s="15"/>
       <c r="B378" s="13" t="s">
         <v>124</v>
@@ -6458,7 +6461,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="379" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A379" s="15"/>
       <c r="B379" s="13"/>
       <c r="C379" s="13"/>
@@ -6466,7 +6469,7 @@
       <c r="E379" s="13"/>
       <c r="F379" s="13"/>
     </row>
-    <row r="380" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A380" s="15" t="s">
         <v>227</v>
       </c>
@@ -6480,7 +6483,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="381" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A381" s="15"/>
       <c r="B381" s="13" t="s">
         <v>123</v>
@@ -6492,7 +6495,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="382" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A382" s="15"/>
       <c r="B382" s="13" t="s">
         <v>124</v>
@@ -6504,7 +6507,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="383" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A383" s="15"/>
       <c r="B383" s="13"/>
       <c r="C383" s="13"/>
@@ -6516,7 +6519,7 @@
       </c>
       <c r="F383" s="13"/>
     </row>
-    <row r="384" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A384" s="1"/>
       <c r="E384">
         <f>SUM(E372:E382)*E383</f>
@@ -6527,7 +6530,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="385" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A385" s="16" t="s">
         <v>45</v>
       </c>
@@ -6542,7 +6545,7 @@
       </c>
       <c r="M385" s="20"/>
     </row>
-    <row r="386" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A386" s="16" t="s">
         <v>357</v>
       </c>
@@ -6557,7 +6560,7 @@
       </c>
       <c r="M386" s="20"/>
     </row>
-    <row r="387" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A387" s="16"/>
       <c r="B387" s="14"/>
       <c r="C387" s="14"/>
@@ -6570,7 +6573,7 @@
       <c r="F387" s="14"/>
       <c r="M387" s="20"/>
     </row>
-    <row r="388" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A388" s="1"/>
       <c r="E388">
         <f>SUM(E385:E386)*E387</f>
@@ -6582,12 +6585,12 @@
       </c>
       <c r="M388" s="20"/>
     </row>
-    <row r="391" spans="1:13" ht="19" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:13" ht="18" x14ac:dyDescent="0.35">
       <c r="A391" s="5" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="392" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A392" s="11" t="s">
         <v>104</v>
       </c>
@@ -6601,7 +6604,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="393" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A393" s="12"/>
       <c r="B393" s="12" t="s">
         <v>106</v>
@@ -6613,7 +6616,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="394" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A394" s="12"/>
       <c r="B394" s="12" t="s">
         <v>107</v>
@@ -6625,7 +6628,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="395" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A395" s="12"/>
       <c r="B395" s="12" t="s">
         <v>108</v>
@@ -6637,7 +6640,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="396" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A396" s="11" t="s">
         <v>120</v>
       </c>
@@ -6647,7 +6650,7 @@
       <c r="E396" s="12"/>
       <c r="F396" s="12"/>
     </row>
-    <row r="397" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A397" s="11"/>
       <c r="B397" s="12" t="s">
         <v>142</v>
@@ -6659,7 +6662,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="398" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A398" s="12"/>
       <c r="B398" s="12" t="s">
         <v>143</v>
@@ -6671,7 +6674,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="399" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A399" s="12"/>
       <c r="B399" s="12" t="s">
         <v>144</v>
@@ -6683,7 +6686,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="400" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A400" s="12"/>
       <c r="B400" s="12" t="s">
         <v>145</v>
@@ -6695,7 +6698,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="401" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A401" s="12"/>
       <c r="B401" s="12"/>
       <c r="C401" s="12"/>
@@ -6703,7 +6706,7 @@
       <c r="E401" s="12"/>
       <c r="F401" s="12"/>
     </row>
-    <row r="402" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A402" s="12" t="s">
         <v>146</v>
       </c>
@@ -6717,7 +6720,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="403" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A403" s="12"/>
       <c r="B403" s="12" t="s">
         <v>148</v>
@@ -6729,7 +6732,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="404" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A404" s="12"/>
       <c r="B404" s="12" t="s">
         <v>149</v>
@@ -6741,7 +6744,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="405" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A405" s="12"/>
       <c r="B405" s="12"/>
       <c r="C405" s="12"/>
@@ -6753,7 +6756,7 @@
       </c>
       <c r="F405" s="12"/>
     </row>
-    <row r="406" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E406">
         <f>SUM(E392:E404)*E405</f>
         <v>0</v>
@@ -6763,12 +6766,12 @@
         <v>120</v>
       </c>
     </row>
-    <row r="407" spans="1:6" ht="19" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A407" s="5" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="408" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A408" s="7" t="s">
         <v>40</v>
       </c>
@@ -6784,7 +6787,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="409" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A409" s="7"/>
       <c r="B409" s="8"/>
       <c r="C409" s="8" t="s">
@@ -6796,7 +6799,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="410" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A410" s="7"/>
       <c r="B410" s="8"/>
       <c r="C410" s="8" t="s">
@@ -6808,7 +6811,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="411" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A411" s="7"/>
       <c r="B411" s="8"/>
       <c r="C411" s="8" t="s">
@@ -6820,7 +6823,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="412" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A412" s="7"/>
       <c r="B412" s="8"/>
       <c r="C412" s="8" t="s">
@@ -6832,7 +6835,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="413" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A413" s="8"/>
       <c r="B413" s="8" t="s">
         <v>13</v>
@@ -6844,7 +6847,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="414" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A414" s="8"/>
       <c r="B414" s="8" t="s">
         <v>43</v>
@@ -6856,7 +6859,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="415" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A415" s="8"/>
       <c r="B415" s="8" t="s">
         <v>80</v>
@@ -6868,7 +6871,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="416" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A416" s="8"/>
       <c r="B416" s="8" t="s">
         <v>99</v>
@@ -6880,7 +6883,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="417" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A417" s="8"/>
       <c r="B417" s="8"/>
       <c r="C417" s="8"/>
@@ -6892,7 +6895,7 @@
       </c>
       <c r="F417" s="8"/>
     </row>
-    <row r="418" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E418">
         <f>SUM(E408:E416)*E417</f>
         <v>0</v>
@@ -6902,7 +6905,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="419" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A419" s="14" t="s">
         <v>150</v>
       </c>
@@ -6916,7 +6919,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="420" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A420" s="14"/>
       <c r="B420" s="14" t="s">
         <v>152</v>
@@ -6928,7 +6931,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="421" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A421" s="14"/>
       <c r="B421" s="14" t="s">
         <v>153</v>
@@ -6940,7 +6943,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="422" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A422" s="14"/>
       <c r="B422" s="14" t="s">
         <v>154</v>
@@ -6952,7 +6955,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="423" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A423" s="14"/>
       <c r="B423" s="14" t="s">
         <v>155</v>
@@ -6964,7 +6967,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="424" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A424" s="14"/>
       <c r="B424" s="14" t="s">
         <v>258</v>
@@ -6976,7 +6979,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="425" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A425" s="14"/>
       <c r="B425" s="14" t="s">
         <v>156</v>
@@ -6988,7 +6991,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="426" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A426" s="14"/>
       <c r="B426" s="14" t="s">
         <v>259</v>
@@ -7000,7 +7003,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="427" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A427" s="14"/>
       <c r="B427" s="14" t="s">
         <v>157</v>
@@ -7012,7 +7015,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="428" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A428" s="14"/>
       <c r="B428" s="14"/>
       <c r="C428" s="14"/>
@@ -7024,7 +7027,7 @@
       </c>
       <c r="F428" s="14"/>
     </row>
-    <row r="429" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E429">
         <f>SUM(E419:E427)*E428</f>
         <v>0</v>
@@ -7034,7 +7037,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="430" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A430" s="8" t="s">
         <v>158</v>
       </c>
@@ -7048,7 +7051,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="431" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A431" s="8"/>
       <c r="B431" s="8" t="s">
         <v>160</v>
@@ -7060,7 +7063,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="432" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A432" s="8"/>
       <c r="B432" s="8" t="s">
         <v>8</v>
@@ -7072,7 +7075,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="433" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A433" s="8"/>
       <c r="B433" s="8" t="s">
         <v>161</v>
@@ -7084,7 +7087,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="434" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A434" s="8"/>
       <c r="B434" s="8" t="s">
         <v>162</v>
@@ -7096,7 +7099,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="435" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A435" s="8"/>
       <c r="B435" s="8" t="s">
         <v>163</v>
@@ -7108,7 +7111,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="436" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A436" s="8"/>
       <c r="B436" s="8" t="s">
         <v>164</v>
@@ -7120,7 +7123,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="437" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A437" s="8"/>
       <c r="B437" s="8"/>
       <c r="C437" s="8"/>
@@ -7132,7 +7135,7 @@
       </c>
       <c r="F437" s="8"/>
     </row>
-    <row r="438" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E438">
         <f>SUM(E430:E436)*E437</f>
         <v>0</v>
@@ -7142,7 +7145,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="439" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A439" s="7" t="s">
         <v>362</v>
       </c>
@@ -7158,7 +7161,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="440" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A440" s="7"/>
       <c r="B440" s="7"/>
       <c r="C440" s="8"/>
@@ -7170,7 +7173,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="441" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A441" s="7"/>
       <c r="B441" s="7"/>
       <c r="C441" s="8"/>
@@ -7182,7 +7185,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="442" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A442" s="7"/>
       <c r="B442" s="7"/>
       <c r="C442" s="8" t="s">
@@ -7196,7 +7199,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="443" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A443" s="7"/>
       <c r="B443" s="7"/>
       <c r="C443" s="8"/>
@@ -7208,7 +7211,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="444" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A444" s="7"/>
       <c r="B444" s="7"/>
       <c r="C444" s="8"/>
@@ -7220,7 +7223,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="445" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A445" s="7"/>
       <c r="B445" s="7"/>
       <c r="C445" s="8"/>
@@ -7232,7 +7235,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="446" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A446" s="7"/>
       <c r="B446" s="7"/>
       <c r="C446" s="8"/>
@@ -7244,7 +7247,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="447" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E447">
         <f>SUM(E439:E446)</f>
         <v>0</v>
@@ -7254,12 +7257,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="448" spans="1:6" ht="19" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A448" s="5" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="449" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A449" s="7" t="s">
         <v>265</v>
       </c>
@@ -7275,7 +7278,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="450" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A450" s="7"/>
       <c r="B450" s="8"/>
       <c r="C450" s="8" t="s">
@@ -7287,7 +7290,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="451" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A451" s="8"/>
       <c r="B451" s="7" t="s">
         <v>266</v>
@@ -7299,7 +7302,7 @@
       <c r="E451" s="8"/>
       <c r="F451" s="8"/>
     </row>
-    <row r="452" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A452" s="8"/>
       <c r="B452" s="8"/>
       <c r="C452" s="8" t="s">
@@ -7311,7 +7314,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="453" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A453" s="8"/>
       <c r="B453" s="8"/>
       <c r="C453" s="8" t="s">
@@ -7323,7 +7326,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="454" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A454" s="8"/>
       <c r="B454" s="8"/>
       <c r="C454" s="8" t="s">
@@ -7335,7 +7338,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="455" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A455" s="8"/>
       <c r="B455" s="8"/>
       <c r="C455" s="8" t="s">
@@ -7347,7 +7350,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="456" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A456" s="8"/>
       <c r="B456" s="8"/>
       <c r="C456" s="8"/>
@@ -7358,7 +7361,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="457" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E457">
         <f>SUM(E449:E455)*E456</f>
         <v>0</v>
@@ -7368,12 +7371,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="458" spans="1:6" ht="21" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:6" ht="21" x14ac:dyDescent="0.4">
       <c r="A458" s="28" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="459" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A459" s="11" t="s">
         <v>369</v>
       </c>
@@ -7387,7 +7390,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="460" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A460" s="11" t="s">
         <v>371</v>
       </c>
@@ -7403,7 +7406,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="461" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A461" s="11"/>
       <c r="B461" s="12"/>
       <c r="C461" s="12" t="s">
@@ -7415,7 +7418,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="462" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A462" s="11"/>
       <c r="B462" s="12"/>
       <c r="C462" s="12"/>
@@ -7427,7 +7430,7 @@
       </c>
       <c r="F462" s="12"/>
     </row>
-    <row r="463" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A463" s="1"/>
       <c r="E463">
         <f>SUM(E459:E461)*E462</f>
@@ -7438,15 +7441,15 @@
         <v>50</v>
       </c>
     </row>
-    <row r="464" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A464" s="1"/>
     </row>
-    <row r="465" spans="1:6" ht="19" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A465" s="5" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="466" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A466" s="15" t="s">
         <v>348</v>
       </c>
@@ -7462,7 +7465,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="467" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A467" s="13" t="s">
         <v>355</v>
       </c>
@@ -7476,7 +7479,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="468" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A468" s="13" t="s">
         <v>0</v>
       </c>
@@ -7490,7 +7493,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="469" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A469" s="13"/>
       <c r="B469" s="13" t="s">
         <v>350</v>
@@ -7502,7 +7505,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="470" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A470" s="13"/>
       <c r="B470" s="13"/>
       <c r="C470" s="13"/>
@@ -7514,7 +7517,7 @@
       </c>
       <c r="F470" s="13"/>
     </row>
-    <row r="471" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E471">
         <f>SUM(E466:E469)*E470</f>
         <v>0</v>
@@ -7524,7 +7527,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="473" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A473" s="16" t="s">
         <v>348</v>
       </c>
@@ -7540,7 +7543,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="474" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A474" s="14" t="s">
         <v>135</v>
       </c>
@@ -7554,7 +7557,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="475" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A475" s="14"/>
       <c r="B475" s="14" t="s">
         <v>228</v>
@@ -7566,7 +7569,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="476" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A476" s="14"/>
       <c r="B476" s="14"/>
       <c r="C476" s="14"/>
@@ -7578,7 +7581,7 @@
       </c>
       <c r="F476" s="14"/>
     </row>
-    <row r="477" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E477">
         <f>SUM(E473:E475)*E476</f>
         <v>0</v>
@@ -7588,7 +7591,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="478" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A478" s="11" t="s">
         <v>348</v>
       </c>
@@ -7604,7 +7607,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="479" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A479" s="12" t="s">
         <v>353</v>
       </c>
@@ -7618,7 +7621,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="480" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A480" s="12"/>
       <c r="B480" s="12" t="s">
         <v>354</v>
@@ -7630,7 +7633,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="481" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A481" s="12"/>
       <c r="B481" s="12"/>
       <c r="C481" s="12"/>
@@ -7642,7 +7645,7 @@
       </c>
       <c r="F481" s="12"/>
     </row>
-    <row r="482" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E482">
         <f>SUM(E478:E480)*E481</f>
         <v>0</v>
@@ -7652,12 +7655,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="487" spans="1:6" ht="19" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A487" s="5" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="488" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A488" s="14" t="s">
         <v>265</v>
       </c>
@@ -7671,7 +7674,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="489" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A489" s="14" t="s">
         <v>270</v>
       </c>
@@ -7685,7 +7688,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="490" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A490" s="14"/>
       <c r="B490" s="14" t="s">
         <v>268</v>
@@ -7697,7 +7700,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="491" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A491" s="14"/>
       <c r="B491" s="14" t="s">
         <v>267</v>
@@ -7709,7 +7712,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="492" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A492" s="14"/>
       <c r="B492" s="14" t="s">
         <v>269</v>
@@ -7721,7 +7724,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="493" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A493" s="14"/>
       <c r="B493" s="14" t="s">
         <v>271</v>
@@ -7733,7 +7736,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="494" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A494" s="14"/>
       <c r="B494" s="14" t="s">
         <v>272</v>
@@ -7745,7 +7748,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="495" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A495" s="14"/>
       <c r="B495" s="14" t="s">
         <v>26</v>
@@ -7757,7 +7760,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="496" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A496" s="14"/>
       <c r="B496" s="14" t="s">
         <v>27</v>
@@ -7769,7 +7772,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="497" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A497" s="14"/>
       <c r="B497" s="14" t="s">
         <v>273</v>
@@ -7781,7 +7784,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="498" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A498" s="14"/>
       <c r="B498" s="14" t="s">
         <v>274</v>
@@ -7793,7 +7796,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="499" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A499" s="14"/>
       <c r="B499" s="14"/>
       <c r="C499" s="14"/>
@@ -7805,7 +7808,7 @@
       </c>
       <c r="F499" s="14"/>
     </row>
-    <row r="500" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E500">
         <f>SUM(E488:E498)*E499</f>
         <v>0</v>
@@ -7815,7 +7818,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="502" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A502" s="12" t="s">
         <v>265</v>
       </c>
@@ -7829,7 +7832,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="503" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A503" s="12" t="s">
         <v>270</v>
       </c>
@@ -7843,7 +7846,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="504" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A504" s="12"/>
       <c r="B504" s="12" t="s">
         <v>268</v>
@@ -7855,7 +7858,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="505" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A505" s="12"/>
       <c r="B505" s="12" t="s">
         <v>267</v>
@@ -7867,7 +7870,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="506" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A506" s="12"/>
       <c r="B506" s="12" t="s">
         <v>269</v>
@@ -7879,7 +7882,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="507" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A507" s="12"/>
       <c r="B507" s="12" t="s">
         <v>271</v>
@@ -7891,7 +7894,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="508" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A508" s="12"/>
       <c r="B508" s="12" t="s">
         <v>272</v>
@@ -7903,7 +7906,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="509" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A509" s="12"/>
       <c r="B509" s="12" t="s">
         <v>26</v>
@@ -7915,7 +7918,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="510" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A510" s="12"/>
       <c r="B510" s="12" t="s">
         <v>27</v>
@@ -7927,7 +7930,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="511" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A511" s="12"/>
       <c r="B511" s="12" t="s">
         <v>273</v>
@@ -7939,7 +7942,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="512" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A512" s="12"/>
       <c r="B512" s="12" t="s">
         <v>274</v>
@@ -7951,7 +7954,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="513" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A513" s="12"/>
       <c r="B513" s="12"/>
       <c r="C513" s="12"/>
@@ -7963,7 +7966,7 @@
       </c>
       <c r="F513" s="12"/>
     </row>
-    <row r="514" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E514">
         <f>SUM(E502:E512)*E513</f>
         <v>0</v>
@@ -7973,7 +7976,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="516" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A516" s="13" t="s">
         <v>265</v>
       </c>
@@ -7987,7 +7990,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="517" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="517" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A517" s="13" t="s">
         <v>270</v>
       </c>
@@ -8001,7 +8004,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="518" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="518" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A518" s="13"/>
       <c r="B518" s="13" t="s">
         <v>268</v>
@@ -8013,7 +8016,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="519" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="519" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A519" s="13"/>
       <c r="B519" s="13" t="s">
         <v>267</v>
@@ -8025,7 +8028,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="520" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="520" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A520" s="13"/>
       <c r="B520" s="13" t="s">
         <v>269</v>
@@ -8037,7 +8040,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="521" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="521" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A521" s="13"/>
       <c r="B521" s="13" t="s">
         <v>271</v>
@@ -8049,7 +8052,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="522" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="522" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A522" s="13"/>
       <c r="B522" s="13" t="s">
         <v>272</v>
@@ -8061,7 +8064,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="523" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A523" s="13"/>
       <c r="B523" s="13" t="s">
         <v>26</v>
@@ -8073,7 +8076,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="524" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="524" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A524" s="13"/>
       <c r="B524" s="13" t="s">
         <v>27</v>
@@ -8085,7 +8088,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="525" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="525" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A525" s="13"/>
       <c r="B525" s="13" t="s">
         <v>273</v>
@@ -8097,7 +8100,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="526" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="526" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A526" s="13"/>
       <c r="B526" s="13" t="s">
         <v>274</v>
@@ -8109,7 +8112,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="527" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="527" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A527" s="13"/>
       <c r="B527" s="13"/>
       <c r="C527" s="13"/>
@@ -8121,7 +8124,7 @@
       </c>
       <c r="F527" s="13"/>
     </row>
-    <row r="528" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="528" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E528">
         <f>SUM(E516:E526)*E527</f>
         <v>0</v>
@@ -8131,12 +8134,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="530" spans="1:6" ht="21" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:6" ht="21" x14ac:dyDescent="0.4">
       <c r="A530" s="28" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="531" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A531" s="16" t="s">
         <v>375</v>
       </c>
@@ -8148,7 +8151,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="532" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A532" s="14"/>
       <c r="B532" s="14"/>
       <c r="C532" s="14"/>
@@ -8158,7 +8161,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="533" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A533" s="14"/>
       <c r="B533" s="14"/>
       <c r="C533" s="14"/>
@@ -8168,7 +8171,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="534" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A534" s="14"/>
       <c r="B534" s="14"/>
       <c r="C534" s="14"/>
@@ -8178,7 +8181,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="535" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A535" s="14"/>
       <c r="B535" s="14"/>
       <c r="C535" s="14"/>
@@ -8188,7 +8191,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="536" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A536" s="14"/>
       <c r="B536" s="14"/>
       <c r="C536" s="14"/>
@@ -8200,7 +8203,7 @@
       </c>
       <c r="F536" s="14"/>
     </row>
-    <row r="537" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="537" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E537">
         <f>SUM(E531:E535)*E536</f>
         <v>0</v>
@@ -8210,7 +8213,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="539" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="539" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A539" s="11" t="s">
         <v>375</v>
       </c>
@@ -8222,7 +8225,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="540" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="540" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A540" s="12"/>
       <c r="B540" s="12"/>
       <c r="C540" s="12"/>
@@ -8232,7 +8235,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="541" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="541" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A541" s="12"/>
       <c r="B541" s="12"/>
       <c r="C541" s="12"/>
@@ -8242,7 +8245,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="542" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="542" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A542" s="12"/>
       <c r="B542" s="12"/>
       <c r="C542" s="12"/>
@@ -8252,7 +8255,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="543" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="543" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A543" s="12"/>
       <c r="B543" s="12"/>
       <c r="C543" s="12"/>
@@ -8262,7 +8265,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="544" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="544" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A544" s="12"/>
       <c r="B544" s="12"/>
       <c r="C544" s="12"/>
@@ -8274,7 +8277,7 @@
       </c>
       <c r="F544" s="12"/>
     </row>
-    <row r="545" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="545" spans="1:8" x14ac:dyDescent="0.3">
       <c r="E545">
         <f>SUM(E539:E543)*E544</f>
         <v>0</v>
@@ -8284,7 +8287,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="547" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="547" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A547" s="15" t="s">
         <v>375</v>
       </c>
@@ -8296,7 +8299,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="548" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="548" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A548" s="13"/>
       <c r="B548" s="13"/>
       <c r="C548" s="13"/>
@@ -8306,7 +8309,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="549" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="549" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A549" s="13"/>
       <c r="B549" s="13"/>
       <c r="C549" s="13"/>
@@ -8316,7 +8319,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="550" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="550" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A550" s="13"/>
       <c r="B550" s="13"/>
       <c r="C550" s="13"/>
@@ -8326,7 +8329,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="551" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="551" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A551" s="13"/>
       <c r="B551" s="13"/>
       <c r="C551" s="13"/>
@@ -8336,7 +8339,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="552" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="552" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A552" s="13"/>
       <c r="B552" s="13"/>
       <c r="C552" s="13"/>
@@ -8348,7 +8351,7 @@
       </c>
       <c r="F552" s="13"/>
     </row>
-    <row r="553" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="553" spans="1:8" x14ac:dyDescent="0.3">
       <c r="E553">
         <f>SUM(E547:E551)*E552</f>
         <v>0</v>
@@ -8358,7 +8361,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="556" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="556" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A556" s="7"/>
       <c r="B556" t="s">
         <v>213</v>
@@ -8376,7 +8379,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="557" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="557" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A557" s="11" t="s">
         <v>396</v>
       </c>
@@ -8396,9 +8399,9 @@
         <v>-3.5137034434293744E-2</v>
       </c>
     </row>
-    <row r="558" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="558" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A558" s="15" t="s">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="B558" t="s">
         <v>215</v>
@@ -8416,7 +8419,7 @@
         <v>-3.5971223021582732E-2</v>
       </c>
     </row>
-    <row r="559" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="559" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A559" s="16" t="s">
         <v>397</v>
       </c>
@@ -8436,7 +8439,7 @@
         <v>-3.5739814152966405E-2</v>
       </c>
     </row>
-    <row r="563" spans="4:7" x14ac:dyDescent="0.2">
+    <row r="563" spans="4:7" x14ac:dyDescent="0.3">
       <c r="F563" t="s">
         <v>260</v>
       </c>
@@ -8444,7 +8447,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="564" spans="4:7" x14ac:dyDescent="0.2">
+    <row r="564" spans="4:7" x14ac:dyDescent="0.3">
       <c r="D564" t="s">
         <v>262</v>
       </c>
@@ -8452,7 +8455,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="565" spans="4:7" x14ac:dyDescent="0.2">
+    <row r="565" spans="4:7" x14ac:dyDescent="0.3">
       <c r="F565">
         <v>45</v>
       </c>
@@ -8460,7 +8463,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="566" spans="4:7" x14ac:dyDescent="0.2">
+    <row r="566" spans="4:7" x14ac:dyDescent="0.3">
       <c r="F566">
         <f>F565+(F574-F565)/9</f>
         <v>50</v>
@@ -8469,7 +8472,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="567" spans="4:7" x14ac:dyDescent="0.2">
+    <row r="567" spans="4:7" x14ac:dyDescent="0.3">
       <c r="F567">
         <f>F566+(F574-F565)/9</f>
         <v>55</v>
@@ -8478,7 +8481,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="568" spans="4:7" x14ac:dyDescent="0.2">
+    <row r="568" spans="4:7" x14ac:dyDescent="0.3">
       <c r="F568">
         <f>F567+(F574-F565)/9</f>
         <v>60</v>
@@ -8487,7 +8490,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="569" spans="4:7" x14ac:dyDescent="0.2">
+    <row r="569" spans="4:7" x14ac:dyDescent="0.3">
       <c r="F569">
         <f>F568+(F574-F565)/9</f>
         <v>65</v>
@@ -8496,7 +8499,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="570" spans="4:7" x14ac:dyDescent="0.2">
+    <row r="570" spans="4:7" x14ac:dyDescent="0.3">
       <c r="F570">
         <f>F569+(F574-F565)/9</f>
         <v>70</v>
@@ -8505,7 +8508,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="571" spans="4:7" x14ac:dyDescent="0.2">
+    <row r="571" spans="4:7" x14ac:dyDescent="0.3">
       <c r="F571">
         <f>F570+(F574-F565)/9</f>
         <v>75</v>
@@ -8514,7 +8517,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="572" spans="4:7" x14ac:dyDescent="0.2">
+    <row r="572" spans="4:7" x14ac:dyDescent="0.3">
       <c r="F572">
         <f>F571+(F574-F565)/9</f>
         <v>80</v>
@@ -8523,7 +8526,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="573" spans="4:7" x14ac:dyDescent="0.2">
+    <row r="573" spans="4:7" x14ac:dyDescent="0.3">
       <c r="F573">
         <f>F572+(F574-F565)/9</f>
         <v>85</v>
@@ -8532,7 +8535,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="574" spans="4:7" x14ac:dyDescent="0.2">
+    <row r="574" spans="4:7" x14ac:dyDescent="0.3">
       <c r="F574">
         <v>90</v>
       </c>
@@ -8540,7 +8543,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="575" spans="4:7" x14ac:dyDescent="0.2">
+    <row r="575" spans="4:7" x14ac:dyDescent="0.3">
       <c r="E575" t="s">
         <v>264</v>
       </c>
@@ -8570,46 +8573,46 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:L1047724"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="31.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.1640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="31.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.44140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="34" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" ht="33.6" x14ac:dyDescent="0.65">
       <c r="A1" s="37" t="s">
         <v>392</v>
       </c>
       <c r="B1" s="37"/>
       <c r="C1" s="37"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="38" t="s">
         <v>393</v>
       </c>
       <c r="B5" s="38"/>
       <c r="C5" s="38"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="2" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>84</v>
       </c>
@@ -8623,7 +8626,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>398</v>
       </c>
@@ -8637,15 +8640,15 @@
         <v>401</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C11" s="3"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>89</v>
       </c>
@@ -8653,7 +8656,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>90</v>
       </c>
@@ -8661,7 +8664,7 @@
         <v>45924</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>91</v>
       </c>
@@ -8669,12 +8672,12 @@
         <v>46051</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>93</v>
       </c>
@@ -8682,13 +8685,13 @@
         <v>402</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="24" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" ht="23.4" x14ac:dyDescent="0.45">
       <c r="A23" s="6" t="s">
         <v>94</v>
       </c>
       <c r="H23" s="21"/>
     </row>
-    <row r="25" spans="1:8" ht="19" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" ht="18" x14ac:dyDescent="0.35">
       <c r="A25" s="5" t="s">
         <v>95</v>
       </c>
@@ -8699,7 +8702,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="15" t="s">
         <v>36</v>
       </c>
@@ -8712,7 +8715,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="15"/>
       <c r="B28" s="13" t="s">
         <v>37</v>
@@ -8723,7 +8726,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="15"/>
       <c r="B29" s="13" t="s">
         <v>38</v>
@@ -8734,7 +8737,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="15"/>
       <c r="B30" s="13" t="s">
         <v>19</v>
@@ -8745,7 +8748,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="15"/>
       <c r="B31" s="13" t="s">
         <v>39</v>
@@ -8756,7 +8759,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="15"/>
       <c r="B32" s="13"/>
       <c r="C32" s="22" t="s">
@@ -8768,7 +8771,7 @@
       </c>
       <c r="E32" s="13"/>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D33">
         <f>-SUM(D27:D32)</f>
         <v>0</v>
@@ -8779,7 +8782,7 @@
       </c>
       <c r="L33" s="20"/>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" s="23" t="s">
         <v>45</v>
       </c>
@@ -8793,7 +8796,7 @@
       </c>
       <c r="L34" s="20"/>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" s="23"/>
       <c r="B35" s="24" t="s">
         <v>50</v>
@@ -8805,7 +8808,7 @@
       </c>
       <c r="L35" s="20"/>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" s="16"/>
       <c r="B36" s="14"/>
       <c r="C36" s="22" t="s">
@@ -8818,7 +8821,7 @@
       <c r="E36" s="14"/>
       <c r="L36" s="20"/>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D37">
         <f>-SUM(D34:D36)</f>
         <v>0</v>
@@ -8829,10 +8832,10 @@
       </c>
       <c r="L37" s="20"/>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="L38" s="20"/>
     </row>
-    <row r="39" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" s="7" t="s">
         <v>98</v>
       </c>
@@ -8846,7 +8849,7 @@
       </c>
       <c r="L39" s="20"/>
     </row>
-    <row r="40" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" s="7"/>
       <c r="B40" s="10" t="s">
         <v>47</v>
@@ -8858,7 +8861,7 @@
       </c>
       <c r="L40" s="20"/>
     </row>
-    <row r="41" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" s="7"/>
       <c r="B41" s="9" t="s">
         <v>48</v>
@@ -8870,7 +8873,7 @@
       </c>
       <c r="L41" s="20"/>
     </row>
-    <row r="42" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" s="7"/>
       <c r="B42" s="9" t="s">
         <v>49</v>
@@ -8882,7 +8885,7 @@
       </c>
       <c r="L42" s="20"/>
     </row>
-    <row r="43" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" s="7"/>
       <c r="B43" s="9" t="s">
         <v>50</v>
@@ -8894,7 +8897,7 @@
       </c>
       <c r="L43" s="20"/>
     </row>
-    <row r="44" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" s="7"/>
       <c r="B44" s="9" t="s">
         <v>51</v>
@@ -8906,7 +8909,7 @@
       </c>
       <c r="L44" s="20"/>
     </row>
-    <row r="45" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" s="7"/>
       <c r="B45" s="9" t="s">
         <v>52</v>
@@ -8918,7 +8921,7 @@
       </c>
       <c r="L45" s="20"/>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" s="7"/>
       <c r="B46" s="9"/>
       <c r="C46" s="22" t="s">
@@ -8931,7 +8934,7 @@
       <c r="E46" s="8"/>
       <c r="L46" s="20"/>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D47">
         <f>-SUM(D39:D46)</f>
         <v>0</v>
@@ -8942,7 +8945,7 @@
       </c>
       <c r="L47" s="20"/>
     </row>
-    <row r="49" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" s="26" t="s">
         <v>44</v>
       </c>
@@ -8955,7 +8958,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" s="26"/>
       <c r="B50" s="29" t="s">
         <v>77</v>
@@ -8966,7 +8969,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" s="26"/>
       <c r="B51" s="29" t="s">
         <v>124</v>
@@ -8977,14 +8980,14 @@
         <v>5</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" s="26"/>
       <c r="B52" s="27"/>
       <c r="C52" s="27"/>
       <c r="D52" s="27"/>
       <c r="E52" s="27"/>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" s="26" t="s">
         <v>122</v>
       </c>
@@ -8997,7 +9000,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" s="26"/>
       <c r="B54" s="27" t="s">
         <v>123</v>
@@ -9008,7 +9011,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" s="26"/>
       <c r="B55" s="27" t="s">
         <v>124</v>
@@ -9019,14 +9022,14 @@
         <v>5</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" s="26"/>
       <c r="B56" s="27"/>
       <c r="C56" s="27"/>
       <c r="D56" s="27"/>
       <c r="E56" s="27"/>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" s="26" t="s">
         <v>227</v>
       </c>
@@ -9039,7 +9042,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" s="26"/>
       <c r="B58" s="27" t="s">
         <v>123</v>
@@ -9050,7 +9053,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" s="26"/>
       <c r="B59" s="27" t="s">
         <v>124</v>
@@ -9061,7 +9064,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" s="15"/>
       <c r="B60" s="13"/>
       <c r="C60" s="22" t="s">
@@ -9073,7 +9076,7 @@
       </c>
       <c r="E60" s="13"/>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D61">
         <f>-SUM(D49:D60)</f>
         <v>0</v>
@@ -9083,7 +9086,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" s="15" t="s">
         <v>78</v>
       </c>
@@ -9096,7 +9099,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" s="15"/>
       <c r="B64" s="13" t="s">
         <v>46</v>
@@ -9107,7 +9110,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" s="15"/>
       <c r="B65" s="13" t="s">
         <v>247</v>
@@ -9118,7 +9121,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" s="15"/>
       <c r="B66" s="13" t="s">
         <v>79</v>
@@ -9129,7 +9132,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" s="15"/>
       <c r="B67" s="13"/>
       <c r="C67" s="22" t="s">
@@ -9141,7 +9144,7 @@
       </c>
       <c r="E67" s="13"/>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D68">
         <f>-SUM(D63:D67)</f>
         <v>0</v>
@@ -9151,7 +9154,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" s="30" t="s">
         <v>35</v>
       </c>
@@ -9164,7 +9167,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" s="30"/>
       <c r="B73" s="31" t="s">
         <v>229</v>
@@ -9175,7 +9178,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" s="30"/>
       <c r="B74" s="31" t="s">
         <v>230</v>
@@ -9186,7 +9189,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" s="30"/>
       <c r="B75" s="31" t="s">
         <v>228</v>
@@ -9197,7 +9200,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" s="11"/>
       <c r="B76" s="12"/>
       <c r="C76" s="22" t="s">
@@ -9209,7 +9212,7 @@
       </c>
       <c r="E76" s="12"/>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D77">
         <f>-SUM(D72:D76)</f>
         <v>0</v>
@@ -9219,7 +9222,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" s="7" t="s">
         <v>57</v>
       </c>
@@ -9232,7 +9235,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" s="7"/>
       <c r="B80" s="8" t="s">
         <v>60</v>
@@ -9243,7 +9246,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" s="7"/>
       <c r="B81" s="8" t="s">
         <v>59</v>
@@ -9254,7 +9257,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" s="7"/>
       <c r="B82" s="8" t="s">
         <v>56</v>
@@ -9265,7 +9268,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" s="7"/>
       <c r="B83" s="8" t="s">
         <v>231</v>
@@ -9276,7 +9279,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" s="7"/>
       <c r="B84" s="8" t="s">
         <v>61</v>
@@ -9289,7 +9292,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" s="7"/>
       <c r="B85" s="8"/>
       <c r="C85" s="8" t="s">
@@ -9300,7 +9303,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" s="7"/>
       <c r="B86" s="8"/>
       <c r="C86" s="8" t="s">
@@ -9311,7 +9314,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" s="7"/>
       <c r="B87" s="8"/>
       <c r="C87" s="8" t="s">
@@ -9322,7 +9325,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" s="7"/>
       <c r="B88" s="8"/>
       <c r="C88" s="8" t="s">
@@ -9333,7 +9336,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" s="7"/>
       <c r="B89" s="8"/>
       <c r="C89" s="22" t="s">
@@ -9345,7 +9348,7 @@
       </c>
       <c r="E89" s="8"/>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="D90">
         <f>-SUM(D79:D89)</f>
         <v>0</v>
@@ -9355,7 +9358,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" s="11" t="s">
         <v>168</v>
       </c>
@@ -9368,7 +9371,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" s="11"/>
       <c r="B92" s="12" t="s">
         <v>77</v>
@@ -9379,7 +9382,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" s="11"/>
       <c r="B93" s="12" t="s">
         <v>170</v>
@@ -9390,7 +9393,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" s="11"/>
       <c r="B94" s="12"/>
       <c r="C94" s="22" t="s">
@@ -9402,7 +9405,7 @@
       </c>
       <c r="E94" s="12"/>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="D95">
         <f>-SUM(D91:D94)</f>
         <v>0</v>
@@ -9412,7 +9415,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
         <v>62</v>
       </c>
@@ -9428,7 +9431,7 @@
       </c>
       <c r="H96" s="1"/>
     </row>
-    <row r="97" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="97" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B97" s="31"/>
       <c r="C97" s="31" t="s">
         <v>65</v>
@@ -9438,7 +9441,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="98" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="98" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B98" s="31"/>
       <c r="C98" s="31" t="s">
         <v>53</v>
@@ -9448,7 +9451,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="99" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="99" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B99" s="31"/>
       <c r="C99" s="31" t="s">
         <v>249</v>
@@ -9458,7 +9461,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="100" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="100" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B100" s="31"/>
       <c r="C100" s="31" t="s">
         <v>248</v>
@@ -9468,7 +9471,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="101" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="101" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B101" s="31"/>
       <c r="C101" s="31" t="s">
         <v>67</v>
@@ -9478,7 +9481,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="102" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="102" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B102" s="31"/>
       <c r="C102" s="31" t="s">
         <v>68</v>
@@ -9488,7 +9491,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="103" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="103" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B103" s="31"/>
       <c r="C103" s="31" t="s">
         <v>97</v>
@@ -9498,7 +9501,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="104" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="104" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B104" s="12"/>
       <c r="C104" s="22" t="s">
         <v>236</v>
@@ -9509,7 +9512,7 @@
       </c>
       <c r="E104" s="12"/>
     </row>
-    <row r="105" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="105" spans="2:5" x14ac:dyDescent="0.3">
       <c r="D105">
         <f>-SUM(D96:D104)</f>
         <v>0</v>
@@ -9519,7 +9522,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="106" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="106" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B106" s="25" t="s">
         <v>63</v>
       </c>
@@ -9531,7 +9534,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="107" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="107" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B107" s="25"/>
       <c r="C107" s="25" t="s">
         <v>65</v>
@@ -9541,7 +9544,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="108" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="108" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B108" s="25"/>
       <c r="C108" s="25" t="s">
         <v>53</v>
@@ -9551,7 +9554,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="109" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="109" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B109" s="25"/>
       <c r="C109" s="25" t="s">
         <v>66</v>
@@ -9561,7 +9564,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="110" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="110" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B110" s="25"/>
       <c r="C110" s="25" t="s">
         <v>52</v>
@@ -9571,7 +9574,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="111" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="111" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B111" s="25"/>
       <c r="C111" s="25" t="s">
         <v>67</v>
@@ -9581,7 +9584,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="112" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="112" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B112" s="25"/>
       <c r="C112" s="25" t="s">
         <v>68</v>
@@ -9591,7 +9594,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B113" s="25"/>
       <c r="C113" s="25" t="s">
         <v>97</v>
@@ -9601,7 +9604,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B114" s="13"/>
       <c r="C114" s="22" t="s">
         <v>236</v>
@@ -9612,7 +9615,7 @@
       </c>
       <c r="E114" s="13"/>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D115">
         <f>-SUM(D106:D114)</f>
         <v>0</v>
@@ -9622,7 +9625,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B116" s="24" t="s">
         <v>63</v>
       </c>
@@ -9634,7 +9637,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B117" s="24"/>
       <c r="C117" s="24" t="s">
         <v>65</v>
@@ -9644,7 +9647,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B118" s="24"/>
       <c r="C118" s="24" t="s">
         <v>53</v>
@@ -9654,7 +9657,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B119" s="24"/>
       <c r="C119" s="24" t="s">
         <v>66</v>
@@ -9664,7 +9667,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B120" s="24"/>
       <c r="C120" s="24" t="s">
         <v>52</v>
@@ -9674,7 +9677,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B121" s="24"/>
       <c r="C121" s="24" t="s">
         <v>67</v>
@@ -9684,7 +9687,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B122" s="24"/>
       <c r="C122" s="24" t="s">
         <v>68</v>
@@ -9694,7 +9697,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B123" s="24"/>
       <c r="C123" s="24" t="s">
         <v>97</v>
@@ -9704,7 +9707,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B124" s="14"/>
       <c r="C124" s="22" t="s">
         <v>236</v>
@@ -9715,7 +9718,7 @@
       </c>
       <c r="E124" s="14"/>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D125">
         <f>-SUM(D116:D124)</f>
         <v>0</v>
@@ -9725,7 +9728,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A127" s="31" t="s">
         <v>109</v>
       </c>
@@ -9740,7 +9743,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A128" s="31"/>
       <c r="B128" s="31"/>
       <c r="C128" s="31" t="s">
@@ -9753,7 +9756,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A129" s="31"/>
       <c r="B129" s="31"/>
       <c r="C129" s="31"/>
@@ -9764,7 +9767,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A130" s="31"/>
       <c r="B130" s="31"/>
       <c r="C130" s="31" t="s">
@@ -9775,7 +9778,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A131" s="31"/>
       <c r="B131" s="31"/>
       <c r="C131" s="31" t="s">
@@ -9786,7 +9789,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A132" s="31"/>
       <c r="B132" s="31"/>
       <c r="C132" s="31" t="s">
@@ -9797,7 +9800,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A133" s="12"/>
       <c r="B133" s="12"/>
       <c r="C133" s="22" t="s">
@@ -9809,7 +9812,7 @@
       </c>
       <c r="E133" s="12"/>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A134"/>
       <c r="D134">
         <f>-SUM(D127:D133)</f>
@@ -9820,7 +9823,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A135" s="31" t="s">
         <v>109</v>
       </c>
@@ -9835,7 +9838,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A136" s="31"/>
       <c r="B136" s="31"/>
       <c r="C136" s="31" t="s">
@@ -9846,7 +9849,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A137" s="31"/>
       <c r="B137" s="31"/>
       <c r="C137" s="31" t="s">
@@ -9857,7 +9860,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A138" s="31"/>
       <c r="B138" s="31"/>
       <c r="C138" s="31" t="s">
@@ -9870,7 +9873,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A139" s="31"/>
       <c r="B139" s="31"/>
       <c r="C139" s="31"/>
@@ -9881,7 +9884,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A140" s="30"/>
       <c r="B140" s="31"/>
       <c r="C140" s="31"/>
@@ -9892,7 +9895,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A141" s="30"/>
       <c r="B141" s="31"/>
       <c r="C141" s="31"/>
@@ -9903,7 +9906,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A142" s="11"/>
       <c r="B142" s="12"/>
       <c r="C142" s="22" t="s">
@@ -9915,7 +9918,7 @@
       </c>
       <c r="E142" s="12"/>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D143">
         <f>-SUM(D135:D142)</f>
         <v>0</v>
@@ -9925,7 +9928,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A144" s="26" t="s">
         <v>125</v>
       </c>
@@ -9940,7 +9943,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A145" s="26"/>
       <c r="B145" s="27"/>
       <c r="C145" s="27" t="s">
@@ -9951,7 +9954,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A146" s="26"/>
       <c r="B146" s="27"/>
       <c r="C146" s="27" t="s">
@@ -9962,7 +9965,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A147" s="26"/>
       <c r="B147" s="27"/>
       <c r="C147" s="27" t="s">
@@ -9973,7 +9976,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A148" s="26"/>
       <c r="B148" s="27"/>
       <c r="C148" s="27" t="s">
@@ -9984,7 +9987,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A149" s="15"/>
       <c r="B149" s="13"/>
       <c r="C149" s="22" t="s">
@@ -9996,7 +9999,7 @@
       </c>
       <c r="E149" s="13"/>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D150">
         <f>-SUM(D144:D149)</f>
         <v>0</v>
@@ -10006,7 +10009,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A151" s="23" t="s">
         <v>125</v>
       </c>
@@ -10021,7 +10024,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A152" s="23"/>
       <c r="B152" s="24"/>
       <c r="C152" s="24" t="s">
@@ -10032,7 +10035,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A153" s="23"/>
       <c r="B153" s="24"/>
       <c r="C153" s="24" t="s">
@@ -10043,7 +10046,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A154" s="16"/>
       <c r="B154" s="14"/>
       <c r="C154" s="22" t="s">
@@ -10055,7 +10058,7 @@
       </c>
       <c r="E154" s="14"/>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D155">
         <f>-SUM(D151:D154)</f>
         <v>0</v>
@@ -10065,7 +10068,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A157" s="16" t="s">
         <v>119</v>
       </c>
@@ -10078,7 +10081,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A158" s="16"/>
       <c r="B158" s="14" t="s">
         <v>121</v>
@@ -10089,7 +10092,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A159" s="16"/>
       <c r="B159" s="14" t="s">
         <v>224</v>
@@ -10100,7 +10103,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A160" s="16"/>
       <c r="B160" s="14" t="s">
         <v>232</v>
@@ -10111,7 +10114,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A161" s="16"/>
       <c r="B161" s="14" t="s">
         <v>225</v>
@@ -10122,7 +10125,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A162" s="16"/>
       <c r="B162" s="14"/>
       <c r="C162" s="22" t="s">
@@ -10134,7 +10137,7 @@
       </c>
       <c r="E162" s="14"/>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D163">
         <f>-SUM(D157:D162)</f>
         <v>0</v>
@@ -10144,7 +10147,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A164" s="30" t="s">
         <v>206</v>
       </c>
@@ -10157,7 +10160,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A165" s="30"/>
       <c r="B165" s="31" t="s">
         <v>65</v>
@@ -10168,7 +10171,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A166" s="30"/>
       <c r="B166" s="31" t="s">
         <v>50</v>
@@ -10179,7 +10182,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A167" s="30"/>
       <c r="B167" s="31" t="s">
         <v>207</v>
@@ -10190,7 +10193,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A168" s="30"/>
       <c r="B168" s="31" t="s">
         <v>51</v>
@@ -10201,7 +10204,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A169" s="30"/>
       <c r="B169" s="31" t="s">
         <v>234</v>
@@ -10212,7 +10215,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A170" s="11"/>
       <c r="B170" s="12"/>
       <c r="C170" s="22" t="s">
@@ -10224,7 +10227,7 @@
       </c>
       <c r="E170" s="12"/>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D171">
         <f>-SUM(D164:D170)</f>
         <v>0</v>
@@ -10234,7 +10237,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A172" s="26" t="s">
         <v>130</v>
       </c>
@@ -10247,7 +10250,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A173" s="26"/>
       <c r="B173" s="27" t="s">
         <v>235</v>
@@ -10258,7 +10261,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A174" s="26"/>
       <c r="B174" s="27" t="s">
         <v>8</v>
@@ -10269,7 +10272,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A175" s="26"/>
       <c r="B175" s="27" t="s">
         <v>132</v>
@@ -10280,7 +10283,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A176" s="26"/>
       <c r="B176" s="27" t="s">
         <v>133</v>
@@ -10291,7 +10294,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A177" s="26"/>
       <c r="B177" s="27" t="s">
         <v>134</v>
@@ -10302,7 +10305,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A178" s="15"/>
       <c r="B178" s="13"/>
       <c r="C178" s="22" t="s">
@@ -10314,7 +10317,7 @@
       </c>
       <c r="E178" s="13"/>
     </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D179">
         <f>-SUM(D172:D178)</f>
         <v>0</v>
@@ -10324,7 +10327,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A180" s="23" t="s">
         <v>135</v>
       </c>
@@ -10337,7 +10340,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A181" s="23"/>
       <c r="B181" s="24" t="s">
         <v>233</v>
@@ -10348,7 +10351,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A182" s="23"/>
       <c r="B182" s="24" t="s">
         <v>136</v>
@@ -10359,7 +10362,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A183" s="23"/>
       <c r="B183" s="24" t="s">
         <v>137</v>
@@ -10370,7 +10373,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A184" s="23"/>
       <c r="B184" s="24" t="s">
         <v>55</v>
@@ -10381,7 +10384,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A185" s="23"/>
       <c r="B185" s="24" t="s">
         <v>54</v>
@@ -10392,7 +10395,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A186" s="23"/>
       <c r="B186" s="24" t="s">
         <v>138</v>
@@ -10403,7 +10406,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A187" s="23"/>
       <c r="B187" s="24" t="s">
         <v>139</v>
@@ -10414,7 +10417,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A188" s="23"/>
       <c r="B188" s="24" t="s">
         <v>140</v>
@@ -10425,7 +10428,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A189" s="23"/>
       <c r="B189" s="24" t="s">
         <v>141</v>
@@ -10436,7 +10439,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A190" s="16"/>
       <c r="B190" s="14"/>
       <c r="C190" s="22" t="s">
@@ -10448,7 +10451,7 @@
       </c>
       <c r="E190" s="14"/>
     </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D191">
         <f>-SUM(D180:D190)</f>
         <v>0</v>
@@ -10458,7 +10461,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A194" s="7" t="s">
         <v>171</v>
       </c>
@@ -10473,7 +10476,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A195" s="7"/>
       <c r="B195" s="8"/>
       <c r="C195" s="8" t="s">
@@ -10484,7 +10487,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A196" s="7"/>
       <c r="B196" s="8"/>
       <c r="C196" s="8" t="s">
@@ -10495,7 +10498,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A197" s="7"/>
       <c r="B197" s="8" t="s">
         <v>176</v>
@@ -10508,7 +10511,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A198" s="7"/>
       <c r="B198" s="8"/>
       <c r="C198" s="8" t="s">
@@ -10519,7 +10522,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A199" s="7"/>
       <c r="B199" s="8"/>
       <c r="C199" s="8" t="s">
@@ -10530,7 +10533,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A200" s="7"/>
       <c r="B200" s="8"/>
       <c r="C200" s="8" t="s">
@@ -10541,7 +10544,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A201" s="7"/>
       <c r="B201" s="8"/>
       <c r="C201" s="8" t="s">
@@ -10552,7 +10555,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A202" s="7"/>
       <c r="B202" s="8" t="s">
         <v>182</v>
@@ -10563,7 +10566,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A203" s="7"/>
       <c r="B203" s="8" t="s">
         <v>204</v>
@@ -10576,7 +10579,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A204" s="7"/>
       <c r="B204" s="8"/>
       <c r="C204" s="8" t="s">
@@ -10587,7 +10590,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A205" s="7"/>
       <c r="B205" s="8"/>
       <c r="C205" s="8" t="s">
@@ -10598,7 +10601,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A206" s="7"/>
       <c r="B206" s="8"/>
       <c r="C206" s="8" t="s">
@@ -10609,7 +10612,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A207" s="7"/>
       <c r="B207" s="8" t="str">
         <f>Report!B408</f>
@@ -10624,7 +10627,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A208" s="7"/>
       <c r="B208" s="8"/>
       <c r="C208" s="8" t="str">
@@ -10636,7 +10639,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A209" s="7"/>
       <c r="B209" s="8"/>
       <c r="C209" s="8" t="str">
@@ -10648,7 +10651,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A210" s="7"/>
       <c r="B210" s="8"/>
       <c r="C210" s="8" t="str">
@@ -10660,7 +10663,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A211" s="7"/>
       <c r="B211" s="8"/>
       <c r="C211" s="8" t="str">
@@ -10672,7 +10675,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A212" s="7"/>
       <c r="B212" s="8"/>
       <c r="C212" s="22" t="s">
@@ -10684,7 +10687,7 @@
       </c>
       <c r="E212" s="8"/>
     </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:7" x14ac:dyDescent="0.3">
       <c r="D213">
         <f>-SUM(D194:D212)</f>
         <v>0</v>
@@ -10694,7 +10697,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A218" s="7"/>
       <c r="B218" t="s">
         <v>213</v>
@@ -10712,7 +10715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A219" s="11" t="s">
         <v>396</v>
       </c>
@@ -10732,7 +10735,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A220" s="15" t="s">
         <v>395</v>
       </c>
@@ -10752,7 +10755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A221" s="16" t="s">
         <v>397</v>
       </c>
@@ -10772,7 +10775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="4:7" x14ac:dyDescent="0.2">
+    <row r="226" spans="4:7" x14ac:dyDescent="0.3">
       <c r="F226" t="s">
         <v>260</v>
       </c>
@@ -10780,7 +10783,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="227" spans="4:7" x14ac:dyDescent="0.2">
+    <row r="227" spans="4:7" x14ac:dyDescent="0.3">
       <c r="D227" t="s">
         <v>262</v>
       </c>
@@ -10788,7 +10791,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="228" spans="4:7" x14ac:dyDescent="0.2">
+    <row r="228" spans="4:7" x14ac:dyDescent="0.3">
       <c r="F228">
         <v>45</v>
       </c>
@@ -10796,7 +10799,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="229" spans="4:7" x14ac:dyDescent="0.2">
+    <row r="229" spans="4:7" x14ac:dyDescent="0.3">
       <c r="F229">
         <f>F228+(F237-F228)/9</f>
         <v>50</v>
@@ -10805,7 +10808,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="230" spans="4:7" x14ac:dyDescent="0.2">
+    <row r="230" spans="4:7" x14ac:dyDescent="0.3">
       <c r="F230">
         <f>F229+(F237-F228)/9</f>
         <v>55</v>
@@ -10814,7 +10817,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="231" spans="4:7" x14ac:dyDescent="0.2">
+    <row r="231" spans="4:7" x14ac:dyDescent="0.3">
       <c r="F231">
         <f>F230+(F237-F228)/9</f>
         <v>60</v>
@@ -10823,7 +10826,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="232" spans="4:7" x14ac:dyDescent="0.2">
+    <row r="232" spans="4:7" x14ac:dyDescent="0.3">
       <c r="F232">
         <f>F231+(F237-F228)/9</f>
         <v>65</v>
@@ -10832,7 +10835,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="233" spans="4:7" x14ac:dyDescent="0.2">
+    <row r="233" spans="4:7" x14ac:dyDescent="0.3">
       <c r="F233">
         <f>F232+(F237-F228)/9</f>
         <v>70</v>
@@ -10841,7 +10844,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="234" spans="4:7" x14ac:dyDescent="0.2">
+    <row r="234" spans="4:7" x14ac:dyDescent="0.3">
       <c r="F234">
         <f>F233+(F237-F228)/9</f>
         <v>75</v>
@@ -10850,7 +10853,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="235" spans="4:7" x14ac:dyDescent="0.2">
+    <row r="235" spans="4:7" x14ac:dyDescent="0.3">
       <c r="F235">
         <f>F234+(F237-F228)/9</f>
         <v>80</v>
@@ -10859,7 +10862,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="236" spans="4:7" x14ac:dyDescent="0.2">
+    <row r="236" spans="4:7" x14ac:dyDescent="0.3">
       <c r="F236">
         <f>F235+(F237-F228)/9</f>
         <v>85</v>
@@ -10868,7 +10871,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="237" spans="4:7" x14ac:dyDescent="0.2">
+    <row r="237" spans="4:7" x14ac:dyDescent="0.3">
       <c r="F237">
         <v>90</v>
       </c>
@@ -10876,12 +10879,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="238" spans="4:7" x14ac:dyDescent="0.2">
+    <row r="238" spans="4:7" x14ac:dyDescent="0.3">
       <c r="E238" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="1047724" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="1047724" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E1047724" s="8"/>
     </row>
   </sheetData>
@@ -10904,14 +10907,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D37"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="35.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5" style="20"/>
+    <col min="2" max="2" width="35.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.44140625" style="20"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="26" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="25.8" x14ac:dyDescent="0.5">
       <c r="A1" s="44" t="s">
         <v>253</v>
       </c>
@@ -10919,10 +10922,10 @@
       <c r="C1" s="44"/>
       <c r="D1" s="44"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>237</v>
       </c>
@@ -10930,7 +10933,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>42</v>
       </c>
@@ -10938,7 +10941,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>239</v>
       </c>
@@ -10946,7 +10949,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>240</v>
       </c>
@@ -10954,7 +10957,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>241</v>
       </c>
@@ -10962,7 +10965,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>242</v>
       </c>
@@ -10970,7 +10973,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>204</v>
       </c>
@@ -10978,7 +10981,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>238</v>
       </c>
@@ -10986,7 +10989,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>244</v>
       </c>
@@ -10994,7 +10997,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>243</v>
       </c>
@@ -11002,7 +11005,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>245</v>
       </c>
@@ -11010,7 +11013,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>246</v>
       </c>
@@ -11018,7 +11021,7 @@
         <v>-0.3</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>252</v>
       </c>
@@ -11026,7 +11029,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>254</v>
       </c>
@@ -11034,7 +11037,7 @@
         <v>-0.2</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>255</v>
       </c>
@@ -11042,7 +11045,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>42</v>
       </c>
@@ -11056,7 +11059,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C23" t="s">
         <v>174</v>
       </c>
@@ -11064,7 +11067,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C24" t="s">
         <v>175</v>
       </c>
@@ -11072,7 +11075,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
         <v>176</v>
       </c>
@@ -11083,7 +11086,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C26" t="s">
         <v>178</v>
       </c>
@@ -11091,7 +11094,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C27" t="s">
         <v>179</v>
       </c>
@@ -11099,7 +11102,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C28" t="s">
         <v>180</v>
       </c>
@@ -11107,12 +11110,12 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
         <v>192</v>
       </c>
@@ -11123,7 +11126,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C32" t="s">
         <v>196</v>
       </c>
@@ -11131,7 +11134,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C33" t="s">
         <v>179</v>
       </c>
@@ -11139,7 +11142,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B34" t="s">
         <v>250</v>
       </c>
@@ -11147,7 +11150,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B35" t="s">
         <v>197</v>
       </c>
@@ -11158,7 +11161,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C36" t="s">
         <v>199</v>
       </c>
@@ -11166,7 +11169,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C37" t="s">
         <v>200</v>
       </c>
@@ -11181,4 +11184,10 @@
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{defa4170-0d19-0005-0004-bc88714345d2}" enabled="1" method="Standard" siteId="{4f455e02-c0f5-4dd7-8284-c56491661975}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>
--- a/ProjectManagement/EvaluationHWAndProject.xlsx
+++ b/ProjectManagement/EvaluationHWAndProject.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11122"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\gthub\ML26-03-Car-Licence-Plate-Identification-with-a-Jetson-Nano\ProjectManagement\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sid/Documents/GitHub/ML26-03-Car-Licence-Plate-Identification-with-a-Jetson-Nano/ProjectManagement/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E26A49B6-0E61-44F0-A8A2-B7FAB6E4F401}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EB73112-5C7D-D247-8157-E9C03D750F7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="800" windowWidth="36000" windowHeight="22580" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Report" sheetId="2" r:id="rId1"/>
@@ -1461,9 +1461,6 @@
     <t>Winter</t>
   </si>
   <si>
-    <t>Vedant Ramkrishna Purohit</t>
-  </si>
-  <si>
     <t>Siddhanth Sharma</t>
   </si>
   <si>
@@ -1486,6 +1483,9 @@
   </si>
   <si>
     <t>Shubhankar Dumka</t>
+  </si>
+  <si>
+    <t>Shubhankar Dhumka</t>
   </si>
 </sst>
 </file>
@@ -1644,7 +1644,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1683,30 +1683,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="-0.249977111117893"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="-0.249977111117893"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="-0.249977111117893"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1724,7 +1700,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1756,23 +1732,13 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -1782,24 +1748,38 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="255"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2081,45 +2061,45 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:M575"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:6" ht="33.6" x14ac:dyDescent="0.65">
-      <c r="A2" s="37" t="s">
+    <row r="2" spans="1:6" ht="34" x14ac:dyDescent="0.4">
+      <c r="A2" s="29" t="s">
         <v>392</v>
       </c>
-      <c r="B2" s="37"/>
-      <c r="C2" s="37"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="38" t="s">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" s="30" t="s">
         <v>393</v>
       </c>
-      <c r="B6" s="38"/>
-      <c r="C6" s="38"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B6" s="30"/>
+      <c r="C6" s="30"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>84</v>
       </c>
@@ -2136,32 +2116,32 @@
         <v>165</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
+        <v>397</v>
+      </c>
+      <c r="B11" t="s">
         <v>398</v>
-      </c>
-      <c r="B11" t="s">
-        <v>399</v>
       </c>
       <c r="C11" s="3">
         <v>7026787</v>
       </c>
       <c r="D11" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C12" s="3"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>88</v>
       </c>
       <c r="B14" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>89</v>
       </c>
@@ -2169,7 +2149,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>90</v>
       </c>
@@ -2177,7 +2157,7 @@
         <v>45924</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>91</v>
       </c>
@@ -2185,7 +2165,7 @@
         <v>46051</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>92</v>
       </c>
@@ -2193,7 +2173,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>93</v>
       </c>
@@ -2201,12 +2181,12 @@
         <v>218</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="23.4" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:8" ht="24" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="18" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:8" ht="19" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
         <v>95</v>
       </c>
@@ -2214,7 +2194,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="13"/>
       <c r="B28" s="13" t="s">
         <v>166</v>
@@ -2231,7 +2211,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="14"/>
       <c r="B29" s="14" t="s">
         <v>166</v>
@@ -2248,7 +2228,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="12"/>
       <c r="B30" s="12" t="s">
         <v>166</v>
@@ -2265,7 +2245,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="12"/>
       <c r="B31" s="12" t="s">
         <v>167</v>
@@ -2282,7 +2262,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="14"/>
       <c r="B32" s="14" t="s">
         <v>167</v>
@@ -2299,7 +2279,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" s="13"/>
       <c r="B33" s="13" t="s">
         <v>167</v>
@@ -2316,12 +2296,12 @@
         <v>391</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="21" x14ac:dyDescent="0.4">
-      <c r="A35" s="28" t="s">
+    <row r="35" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A35" s="23" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" s="15" t="s">
         <v>0</v>
       </c>
@@ -2331,7 +2311,7 @@
       <c r="E36" s="13"/>
       <c r="F36" s="13"/>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" s="15"/>
       <c r="B37" s="13" t="s">
         <v>3</v>
@@ -2343,7 +2323,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" s="13"/>
       <c r="B38" s="13" t="s">
         <v>28</v>
@@ -2355,7 +2335,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" s="13"/>
       <c r="B39" s="13" t="s">
         <v>4</v>
@@ -2367,7 +2347,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" s="13"/>
       <c r="B40" s="13" t="s">
         <v>5</v>
@@ -2379,7 +2359,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" s="13"/>
       <c r="B41" s="13" t="s">
         <v>6</v>
@@ -2391,7 +2371,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" s="13"/>
       <c r="B42" s="13" t="s">
         <v>1</v>
@@ -2403,7 +2383,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" s="15"/>
       <c r="B43" s="13"/>
       <c r="C43" s="13"/>
@@ -2411,7 +2391,7 @@
       <c r="E43" s="13"/>
       <c r="F43" s="13"/>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" s="15"/>
       <c r="B44" s="13" t="s">
         <v>2</v>
@@ -2425,7 +2405,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" s="13"/>
       <c r="B45" s="13"/>
       <c r="C45" s="13" t="s">
@@ -2437,7 +2417,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" s="13"/>
       <c r="B46" s="13"/>
       <c r="C46" s="13" t="s">
@@ -2449,7 +2429,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" s="13"/>
       <c r="B47" s="13"/>
       <c r="C47" s="13" t="s">
@@ -2461,7 +2441,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" s="13"/>
       <c r="B48" s="13"/>
       <c r="C48" s="13" t="s">
@@ -2473,7 +2453,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="13"/>
       <c r="B49" s="13"/>
       <c r="C49" s="13" t="s">
@@ -2485,7 +2465,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="13"/>
       <c r="B50" s="13"/>
       <c r="C50" s="13" t="s">
@@ -2497,19 +2477,19 @@
         <v>5</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" s="13"/>
       <c r="B51" s="13"/>
       <c r="C51" s="13"/>
       <c r="D51" s="22" t="s">
         <v>389</v>
       </c>
-      <c r="E51" s="36">
+      <c r="E51" s="28">
         <v>1</v>
       </c>
       <c r="F51" s="13"/>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="E52">
         <f>SUM(E36:E50)*E51</f>
         <v>0</v>
@@ -2519,12 +2499,12 @@
         <v>100</v>
       </c>
     </row>
-    <row r="54" spans="1:7" s="5" customFormat="1" ht="21" x14ac:dyDescent="0.4">
-      <c r="A54" s="28" t="s">
+    <row r="54" spans="1:7" s="5" customFormat="1" ht="21" x14ac:dyDescent="0.25">
+      <c r="A54" s="23" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A55" s="16" t="s">
         <v>135</v>
       </c>
@@ -2537,11 +2517,11 @@
       <c r="F55" s="14">
         <v>10</v>
       </c>
-      <c r="G55" s="39" t="s">
+      <c r="G55" s="31" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A56" s="16"/>
       <c r="B56" s="14" t="s">
         <v>50</v>
@@ -2552,9 +2532,9 @@
       <c r="F56" s="14">
         <v>5</v>
       </c>
-      <c r="G56" s="39"/>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G56" s="31"/>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A57" s="16"/>
       <c r="B57" s="14" t="s">
         <v>233</v>
@@ -2565,9 +2545,9 @@
       <c r="F57" s="14">
         <v>5</v>
       </c>
-      <c r="G57" s="39"/>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G57" s="31"/>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A58" s="16"/>
       <c r="B58" s="14" t="s">
         <v>136</v>
@@ -2578,9 +2558,9 @@
       <c r="F58" s="14">
         <v>5</v>
       </c>
-      <c r="G58" s="39"/>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G58" s="31"/>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A59" s="16"/>
       <c r="B59" s="14" t="s">
         <v>137</v>
@@ -2591,9 +2571,9 @@
       <c r="F59" s="14">
         <v>10</v>
       </c>
-      <c r="G59" s="39"/>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G59" s="31"/>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A60" s="16"/>
       <c r="B60" s="14" t="s">
         <v>55</v>
@@ -2604,9 +2584,9 @@
       <c r="F60" s="14">
         <v>5</v>
       </c>
-      <c r="G60" s="39"/>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G60" s="31"/>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A61" s="16"/>
       <c r="B61" s="14" t="s">
         <v>54</v>
@@ -2617,9 +2597,9 @@
       <c r="F61" s="14">
         <v>10</v>
       </c>
-      <c r="G61" s="39"/>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G61" s="31"/>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A62" s="16"/>
       <c r="B62" s="14" t="s">
         <v>138</v>
@@ -2630,9 +2610,9 @@
       <c r="F62" s="14">
         <v>5</v>
       </c>
-      <c r="G62" s="39"/>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G62" s="31"/>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A63" s="16"/>
       <c r="B63" s="14" t="s">
         <v>139</v>
@@ -2643,9 +2623,9 @@
       <c r="F63" s="14">
         <v>5</v>
       </c>
-      <c r="G63" s="39"/>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G63" s="31"/>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A64" s="16"/>
       <c r="B64" s="14" t="s">
         <v>140</v>
@@ -2656,9 +2636,9 @@
       <c r="F64" s="14">
         <v>5</v>
       </c>
-      <c r="G64" s="39"/>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G64" s="31"/>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A65" s="16"/>
       <c r="B65" s="14" t="s">
         <v>323</v>
@@ -2669,9 +2649,9 @@
       <c r="F65" s="14">
         <v>5</v>
       </c>
-      <c r="G65" s="39"/>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G65" s="31"/>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A66" s="16"/>
       <c r="B66" s="14" t="s">
         <v>324</v>
@@ -2682,9 +2662,9 @@
       <c r="F66" s="14">
         <v>5</v>
       </c>
-      <c r="G66" s="39"/>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G66" s="31"/>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A67" s="16"/>
       <c r="B67" s="14" t="s">
         <v>141</v>
@@ -2695,22 +2675,22 @@
       <c r="F67" s="14">
         <v>5</v>
       </c>
-      <c r="G67" s="39"/>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G67" s="31"/>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A68" s="16"/>
       <c r="B68" s="14"/>
       <c r="C68" s="14"/>
       <c r="D68" s="22" t="s">
         <v>389</v>
       </c>
-      <c r="E68" s="36">
+      <c r="E68" s="28">
         <v>1</v>
       </c>
       <c r="F68" s="14"/>
-      <c r="G68" s="39"/>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G68" s="31"/>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A69" s="1"/>
       <c r="E69">
         <f>-SUM(E55:E67)*E68</f>
@@ -2721,12 +2701,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="70" spans="1:7" s="5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:7" s="5" customFormat="1" ht="19" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A71" s="16" t="s">
         <v>135</v>
       </c>
@@ -2739,11 +2719,11 @@
       <c r="F71" s="14">
         <v>10</v>
       </c>
-      <c r="G71" s="42" t="s">
+      <c r="G71" s="34" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A72" s="16"/>
       <c r="B72" s="14" t="s">
         <v>46</v>
@@ -2754,9 +2734,9 @@
       <c r="F72" s="14">
         <v>5</v>
       </c>
-      <c r="G72" s="42"/>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G72" s="34"/>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A73" s="16"/>
       <c r="B73" s="14" t="s">
         <v>344</v>
@@ -2767,9 +2747,9 @@
       <c r="F73" s="14">
         <v>5</v>
       </c>
-      <c r="G73" s="42"/>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G73" s="34"/>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A74" s="16"/>
       <c r="B74" s="14" t="s">
         <v>70</v>
@@ -2780,9 +2760,9 @@
       <c r="F74" s="14">
         <v>5</v>
       </c>
-      <c r="G74" s="42"/>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G74" s="34"/>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A75" s="16"/>
       <c r="B75" s="14" t="s">
         <v>345</v>
@@ -2793,9 +2773,9 @@
       <c r="F75" s="14">
         <v>10</v>
       </c>
-      <c r="G75" s="42"/>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G75" s="34"/>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A76" s="16"/>
       <c r="B76" s="14" t="s">
         <v>346</v>
@@ -2806,22 +2786,22 @@
       <c r="F76" s="14">
         <v>5</v>
       </c>
-      <c r="G76" s="42"/>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G76" s="34"/>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A77" s="16"/>
       <c r="B77" s="14"/>
       <c r="C77" s="14"/>
       <c r="D77" s="22" t="s">
         <v>389</v>
       </c>
-      <c r="E77" s="36">
+      <c r="E77" s="28">
         <v>1</v>
       </c>
       <c r="F77" s="14"/>
-      <c r="G77" s="42"/>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G77" s="34"/>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A78" s="1"/>
       <c r="E78">
         <f>-SUM(E71:E76)*E77</f>
@@ -2832,15 +2812,15 @@
         <v>40</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A79" s="1"/>
     </row>
-    <row r="80" spans="1:7" ht="18" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:7" ht="19" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A81" s="7" t="s">
         <v>380</v>
       </c>
@@ -2855,11 +2835,11 @@
       <c r="F81" s="8">
         <v>0</v>
       </c>
-      <c r="G81" s="43" t="s">
+      <c r="G81" s="35" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A82" s="7"/>
       <c r="B82" s="7" t="s">
         <v>382</v>
@@ -2872,9 +2852,9 @@
       <c r="F82" s="8">
         <v>30</v>
       </c>
-      <c r="G82" s="43"/>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G82" s="35"/>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A83" s="7"/>
       <c r="B83" s="7"/>
       <c r="C83" s="8" t="s">
@@ -2885,9 +2865,9 @@
       <c r="F83" s="8">
         <v>10</v>
       </c>
-      <c r="G83" s="43"/>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G83" s="35"/>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A84" s="7"/>
       <c r="B84" s="7"/>
       <c r="C84" s="8" t="s">
@@ -2898,22 +2878,22 @@
       <c r="F84" s="8">
         <v>10</v>
       </c>
-      <c r="G84" s="43"/>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G84" s="35"/>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A85" s="7"/>
       <c r="B85" s="7"/>
       <c r="C85" s="7"/>
       <c r="D85" s="22" t="s">
         <v>389</v>
       </c>
-      <c r="E85" s="36">
+      <c r="E85" s="28">
         <v>1</v>
       </c>
       <c r="F85" s="7"/>
-      <c r="G85" s="43"/>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G85" s="35"/>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="E86">
@@ -2925,15 +2905,15 @@
         <v>50</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A87" s="1"/>
     </row>
-    <row r="88" spans="1:7" ht="21" x14ac:dyDescent="0.4">
-      <c r="A88" s="28" t="s">
+    <row r="88" spans="1:7" ht="21" x14ac:dyDescent="0.25">
+      <c r="A88" s="23" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A89" s="15" t="s">
         <v>317</v>
       </c>
@@ -2947,7 +2927,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A90" s="15"/>
       <c r="B90" s="13" t="s">
         <v>131</v>
@@ -2959,7 +2939,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A91" s="15"/>
       <c r="B91" s="13" t="s">
         <v>235</v>
@@ -2971,7 +2951,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A92" s="15"/>
       <c r="B92" s="13" t="s">
         <v>8</v>
@@ -2983,7 +2963,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A93" s="15"/>
       <c r="B93" s="13" t="s">
         <v>132</v>
@@ -2995,7 +2975,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A94" s="15"/>
       <c r="B94" s="13" t="s">
         <v>133</v>
@@ -3007,7 +2987,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A95" s="15"/>
       <c r="B95" s="13" t="s">
         <v>134</v>
@@ -3019,19 +2999,19 @@
         <v>5</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A96" s="15"/>
       <c r="B96" s="13"/>
       <c r="C96" s="13"/>
       <c r="D96" s="22" t="s">
         <v>389</v>
       </c>
-      <c r="E96" s="36">
+      <c r="E96" s="28">
         <v>1</v>
       </c>
       <c r="F96" s="13"/>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A97" s="1"/>
       <c r="E97">
         <f>SUM(E89:E95)*E96</f>
@@ -3042,18 +3022,18 @@
         <v>40</v>
       </c>
     </row>
-    <row r="98" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="99" spans="1:6" ht="21" x14ac:dyDescent="0.4">
-      <c r="A99" s="28" t="s">
+    <row r="98" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="99" spans="1:6" ht="21" x14ac:dyDescent="0.25">
+      <c r="A99" s="23" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="100" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:6" ht="19" x14ac:dyDescent="0.25">
       <c r="A100" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A101" s="15" t="s">
         <v>7</v>
       </c>
@@ -3067,7 +3047,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A102" s="13"/>
       <c r="B102" s="13" t="s">
         <v>9</v>
@@ -3079,7 +3059,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A103" s="13"/>
       <c r="B103" s="13" t="s">
         <v>10</v>
@@ -3091,7 +3071,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A104" s="13"/>
       <c r="B104" s="13" t="s">
         <v>11</v>
@@ -3103,7 +3083,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A105" s="13"/>
       <c r="B105" s="13" t="s">
         <v>12</v>
@@ -3115,7 +3095,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A106" s="13"/>
       <c r="B106" s="13" t="s">
         <v>100</v>
@@ -3127,19 +3107,19 @@
         <v>5</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A107" s="13"/>
       <c r="B107" s="13"/>
       <c r="C107" s="13"/>
       <c r="D107" s="22" t="s">
         <v>389</v>
       </c>
-      <c r="E107" s="36">
+      <c r="E107" s="28">
         <v>1</v>
       </c>
       <c r="F107" s="13"/>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
       <c r="E108">
         <f>SUM(E101:E106)*E107</f>
         <v>0</v>
@@ -3149,12 +3129,12 @@
         <v>35</v>
       </c>
     </row>
-    <row r="110" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:6" ht="19" x14ac:dyDescent="0.25">
       <c r="A110" s="5" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A111" s="16" t="s">
         <v>275</v>
       </c>
@@ -3168,7 +3148,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A112" s="16"/>
       <c r="B112" s="14" t="s">
         <v>14</v>
@@ -3180,7 +3160,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A113" s="14"/>
       <c r="B113" s="14" t="s">
         <v>15</v>
@@ -3192,7 +3172,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A114" s="14"/>
       <c r="B114" s="14" t="s">
         <v>16</v>
@@ -3204,7 +3184,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A115" s="14"/>
       <c r="B115" s="14" t="s">
         <v>17</v>
@@ -3216,7 +3196,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A116" s="14"/>
       <c r="B116" s="14" t="s">
         <v>18</v>
@@ -3228,7 +3208,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A117" s="14"/>
       <c r="B117" s="14" t="s">
         <v>20</v>
@@ -3240,9 +3220,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A118" s="14"/>
-      <c r="B118" s="32" t="s">
+      <c r="B118" s="24" t="s">
         <v>19</v>
       </c>
       <c r="C118" s="14"/>
@@ -3252,19 +3232,19 @@
         <v>5</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A119" s="14"/>
-      <c r="B119" s="32"/>
+      <c r="B119" s="24"/>
       <c r="C119" s="14"/>
       <c r="D119" s="22" t="s">
         <v>389</v>
       </c>
-      <c r="E119" s="36">
+      <c r="E119" s="28">
         <v>1</v>
       </c>
       <c r="F119" s="14"/>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.2">
       <c r="E120">
         <f>SUM(E111:E118)*E119</f>
         <v>0</v>
@@ -3274,12 +3254,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="123" spans="1:7" ht="18" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:7" ht="19" x14ac:dyDescent="0.25">
       <c r="A123" s="5" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A124" s="11" t="s">
         <v>335</v>
       </c>
@@ -3296,11 +3276,11 @@
       <c r="F124" s="12">
         <v>6</v>
       </c>
-      <c r="G124" s="40" t="s">
+      <c r="G124" s="32" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A125" s="11" t="s">
         <v>330</v>
       </c>
@@ -3317,9 +3297,9 @@
       <c r="F125" s="12">
         <v>6</v>
       </c>
-      <c r="G125" s="40"/>
-    </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G125" s="32"/>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A126" s="12"/>
       <c r="B126" s="12"/>
       <c r="C126" s="12"/>
@@ -3332,9 +3312,9 @@
       <c r="F126" s="12">
         <v>6</v>
       </c>
-      <c r="G126" s="40"/>
-    </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G126" s="32"/>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A127" s="12"/>
       <c r="B127" s="12"/>
       <c r="C127" s="12" t="s">
@@ -3347,9 +3327,9 @@
       <c r="F127" s="12">
         <v>6</v>
       </c>
-      <c r="G127" s="40"/>
-    </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G127" s="32"/>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A128" s="12"/>
       <c r="B128" s="12"/>
       <c r="C128" s="12" t="s">
@@ -3362,9 +3342,9 @@
       <c r="F128" s="12">
         <v>6</v>
       </c>
-      <c r="G128" s="40"/>
-    </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G128" s="32"/>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A129" s="12"/>
       <c r="B129" s="12"/>
       <c r="C129" s="12" t="s">
@@ -3377,22 +3357,22 @@
       <c r="F129" s="12">
         <v>6</v>
       </c>
-      <c r="G129" s="40"/>
-    </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G129" s="32"/>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A130" s="12"/>
       <c r="B130" s="12"/>
       <c r="C130" s="12"/>
       <c r="D130" s="22" t="s">
         <v>389</v>
       </c>
-      <c r="E130" s="36">
+      <c r="E130" s="28">
         <v>1</v>
       </c>
       <c r="F130" s="12"/>
-      <c r="G130" s="40"/>
-    </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G130" s="32"/>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
       <c r="E131">
         <f>SUM(E124:E129)*E130</f>
         <v>0</v>
@@ -3401,9 +3381,9 @@
         <f>SUM(F124:F129)</f>
         <v>36</v>
       </c>
-      <c r="G131" s="40"/>
-    </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G131" s="32"/>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A132" s="11" t="s">
         <v>276</v>
       </c>
@@ -3420,9 +3400,9 @@
       <c r="F132" s="12">
         <v>10</v>
       </c>
-      <c r="G132" s="40"/>
-    </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G132" s="32"/>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A133" s="12"/>
       <c r="B133" s="12"/>
       <c r="C133" s="12" t="s">
@@ -3437,9 +3417,9 @@
       <c r="F133" s="12">
         <v>5</v>
       </c>
-      <c r="G133" s="40"/>
-    </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G133" s="32"/>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A134" s="12"/>
       <c r="B134" s="12"/>
       <c r="C134" s="12"/>
@@ -3452,9 +3432,9 @@
       <c r="F134" s="12">
         <v>5</v>
       </c>
-      <c r="G134" s="40"/>
-    </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G134" s="32"/>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A135" s="11"/>
       <c r="B135" s="12"/>
       <c r="C135" s="12"/>
@@ -3467,9 +3447,9 @@
       <c r="F135" s="12">
         <v>5</v>
       </c>
-      <c r="G135" s="40"/>
-    </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G135" s="32"/>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A136" s="11"/>
       <c r="B136" s="12"/>
       <c r="C136" s="12"/>
@@ -3482,9 +3462,9 @@
       <c r="F136" s="12">
         <v>5</v>
       </c>
-      <c r="G136" s="40"/>
-    </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G136" s="32"/>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A137" s="11"/>
       <c r="B137" s="12"/>
       <c r="C137" s="12" t="s">
@@ -3497,9 +3477,9 @@
       <c r="F137" s="12">
         <v>10</v>
       </c>
-      <c r="G137" s="40"/>
-    </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G137" s="32"/>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A138" s="12"/>
       <c r="B138" s="12"/>
       <c r="C138" s="12" t="s">
@@ -3512,9 +3492,9 @@
       <c r="F138" s="12">
         <v>5</v>
       </c>
-      <c r="G138" s="40"/>
-    </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G138" s="32"/>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A139" s="12"/>
       <c r="B139" s="12"/>
       <c r="C139" s="12" t="s">
@@ -3527,22 +3507,22 @@
       <c r="F139" s="12">
         <v>5</v>
       </c>
-      <c r="G139" s="40"/>
-    </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G139" s="32"/>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A140" s="12"/>
       <c r="B140" s="12"/>
       <c r="C140" s="12"/>
       <c r="D140" s="22" t="s">
         <v>389</v>
       </c>
-      <c r="E140" s="36">
+      <c r="E140" s="28">
         <v>1</v>
       </c>
       <c r="F140" s="12"/>
-      <c r="G140" s="40"/>
-    </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G140" s="32"/>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
       <c r="E141">
         <f>SUM(E132:E139)*E140</f>
         <v>0</v>
@@ -3551,9 +3531,9 @@
         <f>SUM(F132:F139)</f>
         <v>50</v>
       </c>
-      <c r="G141" s="40"/>
-    </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G141" s="32"/>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A142" s="11" t="s">
         <v>333</v>
       </c>
@@ -3570,9 +3550,9 @@
       <c r="F142" s="12">
         <v>6</v>
       </c>
-      <c r="G142" s="40"/>
-    </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G142" s="32"/>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A143" s="11" t="s">
         <v>334</v>
       </c>
@@ -3585,9 +3565,9 @@
       <c r="F143" s="12">
         <v>6</v>
       </c>
-      <c r="G143" s="40"/>
-    </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G143" s="32"/>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A144" s="11"/>
       <c r="B144" s="12"/>
       <c r="C144" s="12" t="s">
@@ -3598,9 +3578,9 @@
       <c r="F144" s="12">
         <v>10</v>
       </c>
-      <c r="G144" s="40"/>
-    </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G144" s="32"/>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A145" s="11"/>
       <c r="B145" s="12"/>
       <c r="C145" s="12" t="s">
@@ -3615,9 +3595,9 @@
       <c r="F145" s="12">
         <v>6</v>
       </c>
-      <c r="G145" s="40"/>
-    </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G145" s="32"/>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A146" s="12"/>
       <c r="B146" s="12"/>
       <c r="C146" s="12"/>
@@ -3630,9 +3610,9 @@
       <c r="F146" s="12">
         <v>6</v>
       </c>
-      <c r="G146" s="40"/>
-    </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G146" s="32"/>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A147" s="12"/>
       <c r="B147" s="12"/>
       <c r="C147" s="12" t="s">
@@ -3645,9 +3625,9 @@
       <c r="F147" s="12">
         <v>6</v>
       </c>
-      <c r="G147" s="40"/>
-    </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G147" s="32"/>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A148" s="12"/>
       <c r="B148" s="12"/>
       <c r="C148" s="12" t="s">
@@ -3660,9 +3640,9 @@
       <c r="F148" s="12">
         <v>6</v>
       </c>
-      <c r="G148" s="40"/>
-    </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G148" s="32"/>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A149" s="12"/>
       <c r="B149" s="12"/>
       <c r="C149" s="12" t="s">
@@ -3675,22 +3655,22 @@
       <c r="F149" s="12">
         <v>6</v>
       </c>
-      <c r="G149" s="40"/>
-    </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G149" s="32"/>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A150" s="12"/>
       <c r="B150" s="12"/>
       <c r="C150" s="12"/>
       <c r="D150" s="22" t="s">
         <v>389</v>
       </c>
-      <c r="E150" s="36">
+      <c r="E150" s="28">
         <v>1</v>
       </c>
       <c r="F150" s="12"/>
-      <c r="G150" s="40"/>
-    </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G150" s="32"/>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.2">
       <c r="E151">
         <f>SUM(E142:E149)*E150</f>
         <v>0</v>
@@ -3699,9 +3679,9 @@
         <f>SUM(F142:F149)</f>
         <v>52</v>
       </c>
-      <c r="G151" s="40"/>
-    </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G151" s="32"/>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A152" s="11" t="s">
         <v>338</v>
       </c>
@@ -3718,9 +3698,9 @@
       <c r="F152" s="12">
         <v>10</v>
       </c>
-      <c r="G152" s="40"/>
-    </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G152" s="32"/>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A153" s="12"/>
       <c r="B153" s="12"/>
       <c r="C153" s="12" t="s">
@@ -3735,9 +3715,9 @@
       <c r="F153" s="12">
         <v>5</v>
       </c>
-      <c r="G153" s="40"/>
-    </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G153" s="32"/>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A154" s="12"/>
       <c r="B154" s="12"/>
       <c r="C154" s="12"/>
@@ -3750,9 +3730,9 @@
       <c r="F154" s="12">
         <v>5</v>
       </c>
-      <c r="G154" s="40"/>
-    </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G154" s="32"/>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A155" s="11"/>
       <c r="B155" s="12"/>
       <c r="C155" s="12"/>
@@ -3765,9 +3745,9 @@
       <c r="F155" s="12">
         <v>5</v>
       </c>
-      <c r="G155" s="40"/>
-    </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G155" s="32"/>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A156" s="11"/>
       <c r="B156" s="12"/>
       <c r="C156" s="12"/>
@@ -3780,9 +3760,9 @@
       <c r="F156" s="12">
         <v>5</v>
       </c>
-      <c r="G156" s="40"/>
-    </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G156" s="32"/>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A157" s="11"/>
       <c r="B157" s="12"/>
       <c r="C157" s="12" t="s">
@@ -3793,9 +3773,9 @@
       <c r="F157" s="12">
         <v>10</v>
       </c>
-      <c r="G157" s="40"/>
-    </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G157" s="32"/>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A158" s="11"/>
       <c r="B158" s="12"/>
       <c r="C158" s="12" t="s">
@@ -3808,9 +3788,9 @@
       <c r="F158" s="12">
         <v>10</v>
       </c>
-      <c r="G158" s="40"/>
-    </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G158" s="32"/>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A159" s="12"/>
       <c r="B159" s="12"/>
       <c r="C159" s="12" t="s">
@@ -3823,9 +3803,9 @@
       <c r="F159" s="12">
         <v>5</v>
       </c>
-      <c r="G159" s="40"/>
-    </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G159" s="32"/>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A160" s="12"/>
       <c r="B160" s="12"/>
       <c r="C160" s="12" t="s">
@@ -3838,22 +3818,22 @@
       <c r="F160" s="12">
         <v>5</v>
       </c>
-      <c r="G160" s="40"/>
-    </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G160" s="32"/>
+    </row>
+    <row r="161" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A161" s="12"/>
       <c r="B161" s="12"/>
       <c r="C161" s="12"/>
       <c r="D161" s="22" t="s">
         <v>389</v>
       </c>
-      <c r="E161" s="36">
+      <c r="E161" s="28">
         <v>1</v>
       </c>
       <c r="F161" s="12"/>
-      <c r="G161" s="40"/>
-    </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G161" s="32"/>
+    </row>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.2">
       <c r="E162">
         <f>SUM(E152:E160)*E161</f>
         <v>0</v>
@@ -3862,12 +3842,12 @@
         <f>SUM(F152:F160)</f>
         <v>60</v>
       </c>
-      <c r="G162" s="40"/>
-    </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="G163" s="35"/>
-    </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G162" s="32"/>
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G163" s="27"/>
+    </row>
+    <row r="164" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A164" s="16" t="s">
         <v>125</v>
       </c>
@@ -3883,7 +3863,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A165" s="16"/>
       <c r="B165" s="14"/>
       <c r="C165" s="14" t="s">
@@ -3895,7 +3875,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A166" s="16"/>
       <c r="B166" s="14"/>
       <c r="C166" s="14" t="s">
@@ -3907,19 +3887,19 @@
         <v>20</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A167" s="16"/>
       <c r="B167" s="14"/>
       <c r="C167" s="14"/>
       <c r="D167" s="22" t="s">
         <v>389</v>
       </c>
-      <c r="E167" s="36">
+      <c r="E167" s="28">
         <v>1</v>
       </c>
       <c r="F167" s="14"/>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A168" s="1"/>
       <c r="E168">
         <f>-SUM(E164:E166)*E167</f>
@@ -3930,7 +3910,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A169" s="16" t="s">
         <v>125</v>
       </c>
@@ -3946,7 +3926,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A170" s="16"/>
       <c r="B170" s="14"/>
       <c r="C170" s="14" t="s">
@@ -3958,7 +3938,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A171" s="16"/>
       <c r="B171" s="14"/>
       <c r="C171" s="14" t="s">
@@ -3970,7 +3950,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A172" s="16"/>
       <c r="B172" s="14"/>
       <c r="C172" s="14" t="s">
@@ -3982,7 +3962,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A173" s="16"/>
       <c r="B173" s="14"/>
       <c r="C173" s="14" t="s">
@@ -3994,19 +3974,19 @@
         <v>15</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A174" s="16"/>
       <c r="B174" s="14"/>
       <c r="C174" s="14"/>
       <c r="D174" s="22" t="s">
         <v>389</v>
       </c>
-      <c r="E174" s="36">
+      <c r="E174" s="28">
         <v>1</v>
       </c>
       <c r="F174" s="14"/>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A175" s="1"/>
       <c r="E175">
         <f>-SUM(E169:E173)*E174</f>
@@ -4017,7 +3997,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A176" s="16" t="s">
         <v>339</v>
       </c>
@@ -4035,7 +4015,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A177" s="16" t="s">
         <v>340</v>
       </c>
@@ -4049,7 +4029,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A178" s="16"/>
       <c r="B178" s="14"/>
       <c r="C178" s="14" t="s">
@@ -4061,7 +4041,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A179" s="16"/>
       <c r="B179" s="14"/>
       <c r="C179" s="14" t="s">
@@ -4073,7 +4053,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A180" s="16"/>
       <c r="B180" s="14"/>
       <c r="C180" s="14" t="s">
@@ -4085,7 +4065,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A181" s="16"/>
       <c r="B181" s="14"/>
       <c r="C181" s="14" t="s">
@@ -4101,7 +4081,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A182" s="14"/>
       <c r="B182" s="14"/>
       <c r="C182" s="14"/>
@@ -4115,7 +4095,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A183" s="14"/>
       <c r="B183" s="14"/>
       <c r="C183" s="14" t="s">
@@ -4129,7 +4109,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A184" s="14"/>
       <c r="B184" s="14"/>
       <c r="C184" s="14" t="s">
@@ -4143,7 +4123,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A185" s="14"/>
       <c r="B185" s="14"/>
       <c r="C185" s="14" t="s">
@@ -4157,19 +4137,19 @@
         <v>6</v>
       </c>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A186" s="14"/>
       <c r="B186" s="14"/>
       <c r="C186" s="14"/>
       <c r="D186" s="22" t="s">
         <v>389</v>
       </c>
-      <c r="E186" s="36">
+      <c r="E186" s="28">
         <v>1</v>
       </c>
       <c r="F186" s="14"/>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.2">
       <c r="E187">
         <f>SUM(E176:E185)*E186</f>
         <v>0</v>
@@ -4179,7 +4159,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A188" s="16" t="s">
         <v>339</v>
       </c>
@@ -4197,7 +4177,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A189" s="14" t="s">
         <v>340</v>
       </c>
@@ -4211,7 +4191,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A190" s="16"/>
       <c r="B190" s="14"/>
       <c r="C190" s="14" t="s">
@@ -4223,7 +4203,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A191" s="14"/>
       <c r="B191" s="14"/>
       <c r="C191" s="14" t="s">
@@ -4239,7 +4219,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A192" s="14"/>
       <c r="B192" s="14"/>
       <c r="C192" s="14"/>
@@ -4253,7 +4233,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A193" s="16"/>
       <c r="B193" s="14"/>
       <c r="C193" s="14"/>
@@ -4267,7 +4247,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A194" s="16"/>
       <c r="B194" s="14"/>
       <c r="C194" s="14"/>
@@ -4281,7 +4261,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A195" s="14"/>
       <c r="B195" s="14"/>
       <c r="C195" s="14" t="s">
@@ -4295,7 +4275,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A196" s="14"/>
       <c r="B196" s="14"/>
       <c r="C196" s="14" t="s">
@@ -4309,19 +4289,19 @@
         <v>5</v>
       </c>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A197" s="14"/>
       <c r="B197" s="14"/>
       <c r="C197" s="14"/>
       <c r="D197" s="22" t="s">
         <v>389</v>
       </c>
-      <c r="E197" s="36">
+      <c r="E197" s="28">
         <v>1</v>
       </c>
       <c r="F197" s="14"/>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.2">
       <c r="E198">
         <f>SUM(E188:E196)*E197</f>
         <v>0</v>
@@ -4331,7 +4311,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A199" s="16" t="s">
         <v>342</v>
       </c>
@@ -4345,7 +4325,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A200" s="16"/>
       <c r="B200" s="14" t="s">
         <v>127</v>
@@ -4357,7 +4337,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A201" s="16"/>
       <c r="B201" s="14" t="s">
         <v>124</v>
@@ -4369,19 +4349,19 @@
         <v>20</v>
       </c>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A202" s="16"/>
       <c r="B202" s="14"/>
       <c r="C202" s="14"/>
       <c r="D202" s="22" t="s">
         <v>389</v>
       </c>
-      <c r="E202" s="36">
+      <c r="E202" s="28">
         <v>1</v>
       </c>
       <c r="F202" s="14"/>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A203" s="1"/>
       <c r="E203">
         <f>SUM(E199:E201)*E202</f>
@@ -4392,15 +4372,15 @@
         <v>60</v>
       </c>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A204" s="1"/>
     </row>
-    <row r="205" spans="1:9" s="5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:9" s="5" customFormat="1" ht="19" x14ac:dyDescent="0.25">
       <c r="A205" s="5" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A206" s="1" t="s">
         <v>62</v>
       </c>
@@ -4417,7 +4397,7 @@
       </c>
       <c r="I206" s="1"/>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A207" s="1"/>
       <c r="B207" s="12"/>
       <c r="C207" s="12" t="s">
@@ -4429,7 +4409,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A208" s="1"/>
       <c r="B208" s="12"/>
       <c r="C208" s="12" t="s">
@@ -4441,7 +4421,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A209" s="1"/>
       <c r="B209" s="12"/>
       <c r="C209" s="12" t="s">
@@ -4453,7 +4433,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A210" s="1"/>
       <c r="B210" s="12"/>
       <c r="C210" s="12" t="s">
@@ -4465,7 +4445,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A211" s="1"/>
       <c r="B211" s="12"/>
       <c r="C211" s="12" t="s">
@@ -4477,7 +4457,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A212" s="1"/>
       <c r="B212" s="12"/>
       <c r="C212" s="12" t="s">
@@ -4489,7 +4469,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A213" s="1"/>
       <c r="B213" s="12"/>
       <c r="C213" s="12" t="s">
@@ -4501,19 +4481,19 @@
         <v>5</v>
       </c>
     </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A214" s="1"/>
       <c r="B214" s="12"/>
       <c r="C214" s="12"/>
       <c r="D214" s="22" t="s">
         <v>389</v>
       </c>
-      <c r="E214" s="36">
+      <c r="E214" s="28">
         <v>1</v>
       </c>
       <c r="F214" s="12"/>
     </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A215" s="1"/>
       <c r="E215">
         <f>-SUM(E206:E213)*E214</f>
@@ -4524,7 +4504,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A216" s="1"/>
       <c r="B216" s="13" t="s">
         <v>63</v>
@@ -4538,7 +4518,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A217" s="1"/>
       <c r="B217" s="13"/>
       <c r="C217" s="13" t="s">
@@ -4550,7 +4530,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A218" s="1"/>
       <c r="B218" s="13"/>
       <c r="C218" s="13" t="s">
@@ -4562,7 +4542,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A219" s="1"/>
       <c r="B219" s="13"/>
       <c r="C219" s="13" t="s">
@@ -4574,7 +4554,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A220" s="1"/>
       <c r="B220" s="13"/>
       <c r="C220" s="13" t="s">
@@ -4586,7 +4566,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A221" s="1"/>
       <c r="B221" s="13"/>
       <c r="C221" s="13" t="s">
@@ -4598,7 +4578,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A222" s="1"/>
       <c r="B222" s="13"/>
       <c r="C222" s="13" t="s">
@@ -4610,7 +4590,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A223" s="1"/>
       <c r="B223" s="13"/>
       <c r="C223" s="13" t="s">
@@ -4622,19 +4602,19 @@
         <v>5</v>
       </c>
     </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A224" s="1"/>
       <c r="B224" s="13"/>
       <c r="C224" s="13"/>
       <c r="D224" s="22" t="s">
         <v>389</v>
       </c>
-      <c r="E224" s="36">
+      <c r="E224" s="28">
         <v>1</v>
       </c>
       <c r="F224" s="13"/>
     </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A225" s="1"/>
       <c r="E225">
         <f>-SUM(E216:E223)*E224</f>
@@ -4645,7 +4625,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A226" s="1"/>
       <c r="B226" s="14" t="s">
         <v>63</v>
@@ -4659,7 +4639,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A227" s="1"/>
       <c r="B227" s="14"/>
       <c r="C227" s="14" t="s">
@@ -4671,7 +4651,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A228" s="1"/>
       <c r="B228" s="14"/>
       <c r="C228" s="14" t="s">
@@ -4683,7 +4663,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A229" s="1"/>
       <c r="B229" s="14"/>
       <c r="C229" s="14" t="s">
@@ -4695,7 +4675,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A230" s="1"/>
       <c r="B230" s="14"/>
       <c r="C230" s="14" t="s">
@@ -4707,7 +4687,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A231" s="1"/>
       <c r="B231" s="14"/>
       <c r="C231" s="14" t="s">
@@ -4719,7 +4699,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A232" s="1"/>
       <c r="B232" s="14"/>
       <c r="C232" s="14" t="s">
@@ -4731,7 +4711,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A233" s="1"/>
       <c r="B233" s="14"/>
       <c r="C233" s="14" t="s">
@@ -4743,19 +4723,19 @@
         <v>5</v>
       </c>
     </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A234" s="1"/>
       <c r="B234" s="14"/>
       <c r="C234" s="14"/>
       <c r="D234" s="22" t="s">
         <v>389</v>
       </c>
-      <c r="E234" s="36">
+      <c r="E234" s="28">
         <v>1</v>
       </c>
       <c r="F234" s="14"/>
     </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A235" s="1"/>
       <c r="E235">
         <f>-SUM(E226:E233)*E234</f>
@@ -4766,7 +4746,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A236" s="15" t="s">
         <v>277</v>
       </c>
@@ -4782,7 +4762,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A237" s="13"/>
       <c r="B237" s="13"/>
       <c r="C237" s="13" t="s">
@@ -4794,7 +4774,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A238" s="13"/>
       <c r="B238" s="13"/>
       <c r="C238" s="13" t="s">
@@ -4806,7 +4786,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A239" s="13"/>
       <c r="B239" s="13"/>
       <c r="C239" s="13" t="s">
@@ -4818,7 +4798,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A240" s="13"/>
       <c r="B240" s="13"/>
       <c r="C240" s="13" t="s">
@@ -4830,7 +4810,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A241" s="13"/>
       <c r="B241" s="13"/>
       <c r="C241" s="13" t="s">
@@ -4842,7 +4822,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A242" s="13"/>
       <c r="B242" s="13"/>
       <c r="C242" s="13" t="s">
@@ -4854,7 +4834,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A243" s="13"/>
       <c r="B243" s="13"/>
       <c r="C243" s="13" t="s">
@@ -4866,7 +4846,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A244" s="15"/>
       <c r="B244" s="13"/>
       <c r="C244" s="13" t="s">
@@ -4878,46 +4858,46 @@
         <v>10</v>
       </c>
     </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A245" s="13"/>
       <c r="B245" s="13"/>
       <c r="C245" s="13"/>
       <c r="D245" s="22" t="s">
         <v>389</v>
       </c>
-      <c r="E245" s="36">
+      <c r="E245" s="28">
         <v>1</v>
       </c>
       <c r="F245" s="13"/>
     </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A246" s="33"/>
-      <c r="B246" s="33"/>
-      <c r="C246" s="33"/>
-      <c r="D246" s="33"/>
-      <c r="E246" s="34">
+    <row r="246" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A246" s="25"/>
+      <c r="B246" s="25"/>
+      <c r="C246" s="25"/>
+      <c r="D246" s="25"/>
+      <c r="E246" s="26">
         <f>SUM(E236:E244)*E245</f>
         <v>0</v>
       </c>
-      <c r="F246" s="34">
+      <c r="F246" s="26">
         <f>SUM(F236:F245)</f>
         <v>120</v>
       </c>
     </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A247" s="33"/>
-      <c r="B247" s="33"/>
-      <c r="C247" s="33"/>
-      <c r="D247" s="33"/>
-      <c r="E247" s="33"/>
-      <c r="F247" s="33"/>
-    </row>
-    <row r="248" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A247" s="25"/>
+      <c r="B247" s="25"/>
+      <c r="C247" s="25"/>
+      <c r="D247" s="25"/>
+      <c r="E247" s="25"/>
+      <c r="F247" s="25"/>
+    </row>
+    <row r="248" spans="1:6" ht="19" x14ac:dyDescent="0.25">
       <c r="A248" s="5" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A249" s="11" t="s">
         <v>206</v>
       </c>
@@ -4931,7 +4911,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A250" s="11" t="s">
         <v>325</v>
       </c>
@@ -4945,7 +4925,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A251" s="11"/>
       <c r="B251" s="12" t="s">
         <v>50</v>
@@ -4957,7 +4937,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A252" s="11"/>
       <c r="B252" s="12" t="s">
         <v>207</v>
@@ -4969,7 +4949,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A253" s="11"/>
       <c r="B253" s="12" t="s">
         <v>51</v>
@@ -4981,7 +4961,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A254" s="11"/>
       <c r="B254" s="12" t="s">
         <v>234</v>
@@ -4993,19 +4973,19 @@
         <v>5</v>
       </c>
     </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A255" s="11"/>
       <c r="B255" s="12"/>
       <c r="C255" s="12"/>
       <c r="D255" s="22" t="s">
         <v>389</v>
       </c>
-      <c r="E255" s="36">
+      <c r="E255" s="28">
         <v>1</v>
       </c>
       <c r="F255" s="12"/>
     </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A256" s="1"/>
       <c r="E256">
         <f>SUM(E249:E254)*E255</f>
@@ -5016,7 +4996,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A257" s="11" t="s">
         <v>386</v>
       </c>
@@ -5029,11 +5009,11 @@
       <c r="F257" s="12">
         <v>5</v>
       </c>
-      <c r="G257" s="41" t="s">
+      <c r="G257" s="33" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A258" s="11" t="s">
         <v>327</v>
       </c>
@@ -5046,9 +5026,9 @@
       <c r="F258" s="12">
         <v>10</v>
       </c>
-      <c r="G258" s="41"/>
-    </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G258" s="33"/>
+    </row>
+    <row r="259" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A259" s="11" t="s">
         <v>326</v>
       </c>
@@ -5061,9 +5041,9 @@
       <c r="F259" s="12">
         <v>10</v>
       </c>
-      <c r="G259" s="41"/>
-    </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G259" s="33"/>
+    </row>
+    <row r="260" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A260" s="11"/>
       <c r="B260" s="12"/>
       <c r="C260" s="12" t="s">
@@ -5074,9 +5054,9 @@
       <c r="F260" s="12">
         <v>5</v>
       </c>
-      <c r="G260" s="41"/>
-    </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G260" s="33"/>
+    </row>
+    <row r="261" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A261" s="11"/>
       <c r="B261" s="12"/>
       <c r="C261" s="12" t="s">
@@ -5087,9 +5067,9 @@
       <c r="F261" s="12">
         <v>5</v>
       </c>
-      <c r="G261" s="41"/>
-    </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G261" s="33"/>
+    </row>
+    <row r="262" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A262" s="11"/>
       <c r="B262" s="12"/>
       <c r="C262" s="12" t="s">
@@ -5100,22 +5080,22 @@
       <c r="F262" s="12">
         <v>5</v>
       </c>
-      <c r="G262" s="41"/>
-    </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G262" s="33"/>
+    </row>
+    <row r="263" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A263" s="11"/>
       <c r="B263" s="12"/>
       <c r="C263" s="12"/>
       <c r="D263" s="22" t="s">
         <v>389</v>
       </c>
-      <c r="E263" s="36">
+      <c r="E263" s="28">
         <v>1</v>
       </c>
       <c r="F263" s="12"/>
-      <c r="G263" s="41"/>
-    </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G263" s="33"/>
+    </row>
+    <row r="264" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A264" s="1"/>
       <c r="E264">
         <f>SUM(E257:E262)*E263</f>
@@ -5126,12 +5106,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="265" spans="1:7" ht="18" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:7" ht="19" x14ac:dyDescent="0.25">
       <c r="A265" s="5" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A266" s="7" t="s">
         <v>29</v>
       </c>
@@ -5143,7 +5123,7 @@
       <c r="E266" s="8"/>
       <c r="F266" s="8"/>
     </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A267" s="8"/>
       <c r="B267" s="8"/>
       <c r="C267" s="8" t="s">
@@ -5155,7 +5135,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="268" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A268" s="8"/>
       <c r="B268" s="8"/>
       <c r="C268" s="8" t="s">
@@ -5165,7 +5145,7 @@
       <c r="E268" s="8"/>
       <c r="F268" s="8"/>
     </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A269" s="8"/>
       <c r="B269" s="8"/>
       <c r="C269" s="8" t="s">
@@ -5175,7 +5155,7 @@
       <c r="E269" s="8"/>
       <c r="F269" s="8"/>
     </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A270" s="8"/>
       <c r="B270" s="8"/>
       <c r="C270" s="8" t="s">
@@ -5187,12 +5167,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="272" spans="1:7" ht="18" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:7" ht="19" x14ac:dyDescent="0.25">
       <c r="A272" s="5" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A273" s="12" t="s">
         <v>75</v>
       </c>
@@ -5210,7 +5190,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A274" s="12"/>
       <c r="B274" s="12"/>
       <c r="C274" s="12"/>
@@ -5222,7 +5202,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A275" s="12"/>
       <c r="B275" s="12"/>
       <c r="C275" s="12"/>
@@ -5234,7 +5214,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A276" s="12"/>
       <c r="B276" s="12"/>
       <c r="C276" s="12"/>
@@ -5246,7 +5226,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A277" s="12"/>
       <c r="B277" s="12"/>
       <c r="C277" s="12"/>
@@ -5258,7 +5238,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A278" s="12"/>
       <c r="B278" s="12"/>
       <c r="C278" s="12"/>
@@ -5270,7 +5250,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A279" s="12"/>
       <c r="B279" s="12"/>
       <c r="C279" s="12" t="s">
@@ -5284,7 +5264,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A280" s="12"/>
       <c r="B280" s="12"/>
       <c r="C280" s="12"/>
@@ -5296,7 +5276,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A281" s="12"/>
       <c r="B281" s="12"/>
       <c r="C281" s="12"/>
@@ -5308,7 +5288,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A282" s="12"/>
       <c r="B282" s="12"/>
       <c r="C282" s="12"/>
@@ -5320,7 +5300,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="283" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A283" s="12"/>
       <c r="B283" s="12"/>
       <c r="C283" s="12"/>
@@ -5332,19 +5312,19 @@
         <v>5</v>
       </c>
     </row>
-    <row r="284" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A284" s="12"/>
       <c r="B284" s="12"/>
       <c r="C284" s="12"/>
       <c r="D284" s="22" t="s">
         <v>389</v>
       </c>
-      <c r="E284" s="36">
+      <c r="E284" s="28">
         <v>1</v>
       </c>
       <c r="F284" s="12"/>
     </row>
-    <row r="285" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:6" x14ac:dyDescent="0.2">
       <c r="E285">
         <f>SUM(E273:E283)*E284</f>
         <v>0</v>
@@ -5354,7 +5334,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="286" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A286" s="7" t="s">
         <v>293</v>
       </c>
@@ -5368,7 +5348,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="287" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A287" s="8"/>
       <c r="B287" s="8" t="s">
         <v>21</v>
@@ -5382,7 +5362,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="288" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A288" s="8"/>
       <c r="B288" s="8"/>
       <c r="C288" s="8" t="s">
@@ -5394,7 +5374,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="289" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A289" s="8"/>
       <c r="B289" s="8"/>
       <c r="C289" s="8" t="s">
@@ -5406,7 +5386,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="290" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A290" s="8"/>
       <c r="B290" s="8"/>
       <c r="C290" s="8" t="s">
@@ -5418,7 +5398,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="291" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A291" s="8"/>
       <c r="B291" s="8"/>
       <c r="C291" s="8" t="s">
@@ -5430,7 +5410,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="292" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A292" s="8"/>
       <c r="B292" s="8"/>
       <c r="C292" s="8" t="s">
@@ -5442,19 +5422,19 @@
         <v>5</v>
       </c>
     </row>
-    <row r="293" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A293" s="8"/>
       <c r="B293" s="8"/>
       <c r="C293" s="8"/>
       <c r="D293" s="22" t="s">
         <v>389</v>
       </c>
-      <c r="E293" s="36">
+      <c r="E293" s="28">
         <v>1</v>
       </c>
       <c r="F293" s="8"/>
     </row>
-    <row r="294" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:6" x14ac:dyDescent="0.2">
       <c r="E294">
         <f>SUM(E286:E292)*E293</f>
         <v>0</v>
@@ -5464,7 +5444,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="296" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A296" s="7" t="s">
         <v>299</v>
       </c>
@@ -5478,7 +5458,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="297" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A297" s="7" t="s">
         <v>301</v>
       </c>
@@ -5492,7 +5472,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="298" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A298" s="8"/>
       <c r="B298" s="8" t="s">
         <v>303</v>
@@ -5504,7 +5484,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="299" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A299" s="8"/>
       <c r="B299" s="8" t="s">
         <v>304</v>
@@ -5516,19 +5496,19 @@
         <v>5</v>
       </c>
     </row>
-    <row r="300" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A300" s="8"/>
       <c r="B300" s="8"/>
       <c r="C300" s="8"/>
       <c r="D300" s="22" t="s">
         <v>389</v>
       </c>
-      <c r="E300" s="36">
+      <c r="E300" s="28">
         <v>1</v>
       </c>
       <c r="F300" s="8"/>
     </row>
-    <row r="301" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:6" x14ac:dyDescent="0.2">
       <c r="E301">
         <f>SUM(E296:E299)*E300</f>
         <v>0</v>
@@ -5538,7 +5518,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="303" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A303" s="16" t="s">
         <v>305</v>
       </c>
@@ -5552,7 +5532,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="304" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A304" s="14"/>
       <c r="B304" s="14" t="s">
         <v>307</v>
@@ -5564,7 +5544,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="305" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A305" s="14"/>
       <c r="B305" s="14" t="s">
         <v>134</v>
@@ -5576,7 +5556,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="306" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A306" s="16" t="s">
         <v>308</v>
       </c>
@@ -5590,7 +5570,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="307" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A307" s="14"/>
       <c r="B307" s="14" t="s">
         <v>310</v>
@@ -5602,7 +5582,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="308" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A308" s="16" t="s">
         <v>359</v>
       </c>
@@ -5618,7 +5598,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="309" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A309" s="14"/>
       <c r="B309" s="14"/>
       <c r="C309" s="14" t="s">
@@ -5630,7 +5610,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="310" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A310" s="14"/>
       <c r="B310" s="14"/>
       <c r="C310" s="14" t="s">
@@ -5642,19 +5622,19 @@
         <v>5</v>
       </c>
     </row>
-    <row r="311" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A311" s="14"/>
       <c r="B311" s="14"/>
       <c r="C311" s="14"/>
       <c r="D311" s="22" t="s">
         <v>389</v>
       </c>
-      <c r="E311" s="36">
+      <c r="E311" s="28">
         <v>1</v>
       </c>
       <c r="F311" s="14"/>
     </row>
-    <row r="312" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:6" x14ac:dyDescent="0.2">
       <c r="E312">
         <f>SUM(E303:E310)*E311</f>
         <v>0</v>
@@ -5664,7 +5644,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="313" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A313" s="11" t="s">
         <v>35</v>
       </c>
@@ -5678,7 +5658,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="314" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A314" s="12"/>
       <c r="B314" s="12" t="s">
         <v>251</v>
@@ -5690,7 +5670,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="315" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A315" s="11"/>
       <c r="B315" s="12" t="s">
         <v>320</v>
@@ -5704,7 +5684,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="316" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A316" s="12"/>
       <c r="B316" s="12" t="s">
         <v>312</v>
@@ -5718,7 +5698,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="317" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A317" s="11"/>
       <c r="B317" s="12" t="s">
         <v>230</v>
@@ -5732,7 +5712,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="318" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A318" s="11"/>
       <c r="B318" s="12" t="s">
         <v>321</v>
@@ -5746,7 +5726,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="319" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A319" s="11"/>
       <c r="B319" s="12" t="s">
         <v>322</v>
@@ -5758,7 +5738,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="320" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A320" s="12"/>
       <c r="B320" s="12" t="s">
         <v>313</v>
@@ -5770,7 +5750,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="321" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A321" s="12"/>
       <c r="B321" s="12" t="s">
         <v>314</v>
@@ -5782,7 +5762,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="322" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A322" s="12"/>
       <c r="B322" s="12" t="s">
         <v>40</v>
@@ -5794,19 +5774,19 @@
         <v>10</v>
       </c>
     </row>
-    <row r="323" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A323" s="12"/>
       <c r="B323" s="12"/>
       <c r="C323" s="12"/>
       <c r="D323" s="22" t="s">
         <v>389</v>
       </c>
-      <c r="E323" s="36">
+      <c r="E323" s="28">
         <v>1</v>
       </c>
       <c r="F323" s="12"/>
     </row>
-    <row r="324" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:6" x14ac:dyDescent="0.2">
       <c r="E324">
         <f>SUM(E313:E322)*E323</f>
         <v>0</v>
@@ -5816,7 +5796,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="326" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A326" s="7" t="s">
         <v>347</v>
       </c>
@@ -5830,7 +5810,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="327" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A327" s="7"/>
       <c r="B327" s="8" t="s">
         <v>191</v>
@@ -5842,7 +5822,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="328" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A328" s="7"/>
       <c r="B328" s="8" t="s">
         <v>192</v>
@@ -5856,7 +5836,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="329" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A329" s="7"/>
       <c r="B329" s="8"/>
       <c r="C329" s="8" t="s">
@@ -5868,7 +5848,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="330" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A330" s="7"/>
       <c r="B330" s="8"/>
       <c r="C330" s="8" t="s">
@@ -5880,7 +5860,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="331" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A331" s="7"/>
       <c r="B331" s="8"/>
       <c r="C331" s="8" t="s">
@@ -5892,7 +5872,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="332" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A332" s="7"/>
       <c r="B332" s="8"/>
       <c r="C332" s="8" t="s">
@@ -5904,19 +5884,19 @@
         <v>10</v>
       </c>
     </row>
-    <row r="333" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A333" s="7"/>
       <c r="B333" s="8"/>
       <c r="C333" s="8"/>
       <c r="D333" s="22" t="s">
         <v>389</v>
       </c>
-      <c r="E333" s="36">
+      <c r="E333" s="28">
         <v>1</v>
       </c>
       <c r="F333" s="8"/>
     </row>
-    <row r="334" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A334" s="1"/>
       <c r="E334">
         <f>SUM(E326:E332)*E333</f>
@@ -5927,7 +5907,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="335" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A335" s="7" t="s">
         <v>78</v>
       </c>
@@ -5941,7 +5921,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="336" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A336" s="7"/>
       <c r="B336" s="8" t="s">
         <v>46</v>
@@ -5953,7 +5933,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="337" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A337" s="7"/>
       <c r="B337" s="8" t="s">
         <v>358</v>
@@ -5965,7 +5945,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="338" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A338" s="7"/>
       <c r="B338" s="8" t="s">
         <v>169</v>
@@ -5977,7 +5957,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="339" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A339" s="7"/>
       <c r="B339" s="8" t="s">
         <v>77</v>
@@ -5989,7 +5969,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="340" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A340" s="7"/>
       <c r="B340" s="8" t="s">
         <v>79</v>
@@ -6001,7 +5981,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="341" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A341" s="7"/>
       <c r="B341" s="7" t="s">
         <v>57</v>
@@ -6015,7 +5995,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="342" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A342" s="7"/>
       <c r="B342" s="7"/>
       <c r="C342" s="8" t="s">
@@ -6027,7 +6007,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="343" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A343" s="7"/>
       <c r="B343" s="7"/>
       <c r="C343" s="8" t="s">
@@ -6039,7 +6019,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="344" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A344" s="7"/>
       <c r="B344" s="7"/>
       <c r="C344" s="8" t="s">
@@ -6051,7 +6031,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="345" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A345" s="7"/>
       <c r="B345" s="7"/>
       <c r="C345" s="8" t="s">
@@ -6063,7 +6043,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="346" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A346" s="7"/>
       <c r="B346" s="7"/>
       <c r="C346" s="8" t="s">
@@ -6077,7 +6057,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="347" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A347" s="7"/>
       <c r="B347" s="7"/>
       <c r="C347" s="8"/>
@@ -6089,7 +6069,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="348" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A348" s="7"/>
       <c r="B348" s="7"/>
       <c r="C348" s="8"/>
@@ -6101,7 +6081,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="349" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A349" s="7"/>
       <c r="B349" s="7"/>
       <c r="C349" s="8"/>
@@ -6113,7 +6093,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="350" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A350" s="7"/>
       <c r="B350" s="7"/>
       <c r="C350" s="8"/>
@@ -6125,19 +6105,19 @@
         <v>3</v>
       </c>
     </row>
-    <row r="351" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A351" s="7"/>
       <c r="B351" s="7"/>
       <c r="C351" s="8"/>
       <c r="D351" s="22" t="s">
         <v>389</v>
       </c>
-      <c r="E351" s="36">
+      <c r="E351" s="28">
         <v>1</v>
       </c>
       <c r="F351" s="8"/>
     </row>
-    <row r="352" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:6" x14ac:dyDescent="0.2">
       <c r="E352">
         <f>SUM(E335:E350)*E351</f>
         <v>0</v>
@@ -6147,12 +6127,12 @@
         <v>160</v>
       </c>
     </row>
-    <row r="353" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:6" ht="19" x14ac:dyDescent="0.25">
       <c r="A353" s="5" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="354" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A354" s="13" t="s">
         <v>220</v>
       </c>
@@ -6166,7 +6146,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="355" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A355" s="13"/>
       <c r="B355" s="13" t="s">
         <v>387</v>
@@ -6180,7 +6160,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="356" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A356" s="13"/>
       <c r="B356" s="13"/>
       <c r="C356" s="13" t="s">
@@ -6192,7 +6172,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="357" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A357" s="13"/>
       <c r="B357" s="13"/>
       <c r="C357" s="13" t="s">
@@ -6204,7 +6184,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="358" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A358" s="13"/>
       <c r="B358" s="13" t="s">
         <v>388</v>
@@ -6218,7 +6198,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="359" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A359" s="13"/>
       <c r="B359" s="13"/>
       <c r="C359" s="13" t="s">
@@ -6230,7 +6210,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="360" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A360" s="13"/>
       <c r="B360" s="13"/>
       <c r="C360" s="13" t="s">
@@ -6242,19 +6222,19 @@
         <v>30</v>
       </c>
     </row>
-    <row r="361" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A361" s="13"/>
       <c r="B361" s="13"/>
       <c r="C361" s="13"/>
       <c r="D361" s="22" t="s">
         <v>389</v>
       </c>
-      <c r="E361" s="36">
+      <c r="E361" s="28">
         <v>1</v>
       </c>
       <c r="F361" s="13"/>
     </row>
-    <row r="362" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:6" x14ac:dyDescent="0.2">
       <c r="E362">
         <f>SUM(E354:E360)*E361</f>
         <v>0</v>
@@ -6264,12 +6244,12 @@
         <v>190</v>
       </c>
     </row>
-    <row r="363" spans="1:6" s="18" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:6" s="18" customFormat="1" ht="19" x14ac:dyDescent="0.25">
       <c r="A363" s="5" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="364" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A364" s="15" t="s">
         <v>361</v>
       </c>
@@ -6285,7 +6265,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="365" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A365" s="13"/>
       <c r="B365" s="13"/>
       <c r="C365" s="13" t="s">
@@ -6299,7 +6279,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="366" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A366" s="13"/>
       <c r="B366" s="13"/>
       <c r="C366" s="13" t="s">
@@ -6313,7 +6293,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="367" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A367" s="13"/>
       <c r="B367" s="13"/>
       <c r="C367" s="13" t="s">
@@ -6327,7 +6307,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="368" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A368" s="13"/>
       <c r="B368" s="13"/>
       <c r="C368" s="13" t="s">
@@ -6341,7 +6321,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="369" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A369" s="13"/>
       <c r="B369" s="13"/>
       <c r="C369" s="13" t="s">
@@ -6355,19 +6335,19 @@
         <v>5</v>
       </c>
     </row>
-    <row r="370" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A370" s="13"/>
       <c r="B370" s="13"/>
       <c r="C370" s="13"/>
       <c r="D370" s="22" t="s">
         <v>389</v>
       </c>
-      <c r="E370" s="36">
+      <c r="E370" s="28">
         <v>1</v>
       </c>
       <c r="F370" s="13"/>
     </row>
-    <row r="371" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:6" x14ac:dyDescent="0.2">
       <c r="E371">
         <f>SUM(E364:E369)*E370</f>
         <v>0</v>
@@ -6377,7 +6357,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="372" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A372" s="15" t="s">
         <v>44</v>
       </c>
@@ -6391,7 +6371,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="373" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A373" s="15"/>
       <c r="B373" s="17" t="s">
         <v>77</v>
@@ -6403,7 +6383,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="374" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A374" s="15"/>
       <c r="B374" s="17" t="s">
         <v>124</v>
@@ -6415,7 +6395,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="375" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A375" s="15"/>
       <c r="B375" s="13"/>
       <c r="C375" s="13"/>
@@ -6423,7 +6403,7 @@
       <c r="E375" s="13"/>
       <c r="F375" s="13"/>
     </row>
-    <row r="376" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A376" s="15" t="s">
         <v>122</v>
       </c>
@@ -6437,7 +6417,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="377" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A377" s="15"/>
       <c r="B377" s="13" t="s">
         <v>123</v>
@@ -6449,7 +6429,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="378" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A378" s="15"/>
       <c r="B378" s="13" t="s">
         <v>124</v>
@@ -6461,7 +6441,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="379" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A379" s="15"/>
       <c r="B379" s="13"/>
       <c r="C379" s="13"/>
@@ -6469,7 +6449,7 @@
       <c r="E379" s="13"/>
       <c r="F379" s="13"/>
     </row>
-    <row r="380" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A380" s="15" t="s">
         <v>227</v>
       </c>
@@ -6483,7 +6463,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="381" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A381" s="15"/>
       <c r="B381" s="13" t="s">
         <v>123</v>
@@ -6495,7 +6475,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="382" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A382" s="15"/>
       <c r="B382" s="13" t="s">
         <v>124</v>
@@ -6507,19 +6487,19 @@
         <v>5</v>
       </c>
     </row>
-    <row r="383" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A383" s="15"/>
       <c r="B383" s="13"/>
       <c r="C383" s="13"/>
       <c r="D383" s="22" t="s">
         <v>389</v>
       </c>
-      <c r="E383" s="36">
+      <c r="E383" s="28">
         <v>1</v>
       </c>
       <c r="F383" s="13"/>
     </row>
-    <row r="384" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A384" s="1"/>
       <c r="E384">
         <f>SUM(E372:E382)*E383</f>
@@ -6530,7 +6510,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="385" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A385" s="16" t="s">
         <v>45</v>
       </c>
@@ -6545,7 +6525,7 @@
       </c>
       <c r="M385" s="20"/>
     </row>
-    <row r="386" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A386" s="16" t="s">
         <v>357</v>
       </c>
@@ -6560,20 +6540,20 @@
       </c>
       <c r="M386" s="20"/>
     </row>
-    <row r="387" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A387" s="16"/>
       <c r="B387" s="14"/>
       <c r="C387" s="14"/>
       <c r="D387" s="22" t="s">
         <v>389</v>
       </c>
-      <c r="E387" s="36">
+      <c r="E387" s="28">
         <v>1</v>
       </c>
       <c r="F387" s="14"/>
       <c r="M387" s="20"/>
     </row>
-    <row r="388" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A388" s="1"/>
       <c r="E388">
         <f>SUM(E385:E386)*E387</f>
@@ -6585,12 +6565,12 @@
       </c>
       <c r="M388" s="20"/>
     </row>
-    <row r="391" spans="1:13" ht="18" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:13" ht="19" x14ac:dyDescent="0.25">
       <c r="A391" s="5" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="392" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A392" s="11" t="s">
         <v>104</v>
       </c>
@@ -6604,7 +6584,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="393" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A393" s="12"/>
       <c r="B393" s="12" t="s">
         <v>106</v>
@@ -6616,7 +6596,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="394" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A394" s="12"/>
       <c r="B394" s="12" t="s">
         <v>107</v>
@@ -6628,7 +6608,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="395" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A395" s="12"/>
       <c r="B395" s="12" t="s">
         <v>108</v>
@@ -6640,7 +6620,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="396" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A396" s="11" t="s">
         <v>120</v>
       </c>
@@ -6650,7 +6630,7 @@
       <c r="E396" s="12"/>
       <c r="F396" s="12"/>
     </row>
-    <row r="397" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A397" s="11"/>
       <c r="B397" s="12" t="s">
         <v>142</v>
@@ -6662,7 +6642,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="398" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A398" s="12"/>
       <c r="B398" s="12" t="s">
         <v>143</v>
@@ -6674,7 +6654,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="399" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A399" s="12"/>
       <c r="B399" s="12" t="s">
         <v>144</v>
@@ -6686,7 +6666,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="400" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A400" s="12"/>
       <c r="B400" s="12" t="s">
         <v>145</v>
@@ -6698,7 +6678,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="401" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A401" s="12"/>
       <c r="B401" s="12"/>
       <c r="C401" s="12"/>
@@ -6706,7 +6686,7 @@
       <c r="E401" s="12"/>
       <c r="F401" s="12"/>
     </row>
-    <row r="402" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A402" s="12" t="s">
         <v>146</v>
       </c>
@@ -6720,7 +6700,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="403" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A403" s="12"/>
       <c r="B403" s="12" t="s">
         <v>148</v>
@@ -6732,7 +6712,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="404" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A404" s="12"/>
       <c r="B404" s="12" t="s">
         <v>149</v>
@@ -6744,19 +6724,19 @@
         <v>15</v>
       </c>
     </row>
-    <row r="405" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A405" s="12"/>
       <c r="B405" s="12"/>
       <c r="C405" s="12"/>
       <c r="D405" s="22" t="s">
         <v>389</v>
       </c>
-      <c r="E405" s="36">
+      <c r="E405" s="28">
         <v>1</v>
       </c>
       <c r="F405" s="12"/>
     </row>
-    <row r="406" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:6" x14ac:dyDescent="0.2">
       <c r="E406">
         <f>SUM(E392:E404)*E405</f>
         <v>0</v>
@@ -6766,12 +6746,12 @@
         <v>120</v>
       </c>
     </row>
-    <row r="407" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:6" ht="19" x14ac:dyDescent="0.25">
       <c r="A407" s="5" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="408" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A408" s="7" t="s">
         <v>40</v>
       </c>
@@ -6787,7 +6767,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="409" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A409" s="7"/>
       <c r="B409" s="8"/>
       <c r="C409" s="8" t="s">
@@ -6799,7 +6779,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="410" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A410" s="7"/>
       <c r="B410" s="8"/>
       <c r="C410" s="8" t="s">
@@ -6811,7 +6791,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="411" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A411" s="7"/>
       <c r="B411" s="8"/>
       <c r="C411" s="8" t="s">
@@ -6823,7 +6803,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="412" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A412" s="7"/>
       <c r="B412" s="8"/>
       <c r="C412" s="8" t="s">
@@ -6835,7 +6815,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="413" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A413" s="8"/>
       <c r="B413" s="8" t="s">
         <v>13</v>
@@ -6847,7 +6827,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="414" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A414" s="8"/>
       <c r="B414" s="8" t="s">
         <v>43</v>
@@ -6859,7 +6839,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="415" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A415" s="8"/>
       <c r="B415" s="8" t="s">
         <v>80</v>
@@ -6871,7 +6851,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="416" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A416" s="8"/>
       <c r="B416" s="8" t="s">
         <v>99</v>
@@ -6883,19 +6863,19 @@
         <v>5</v>
       </c>
     </row>
-    <row r="417" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A417" s="8"/>
       <c r="B417" s="8"/>
       <c r="C417" s="8"/>
       <c r="D417" s="22" t="s">
         <v>389</v>
       </c>
-      <c r="E417" s="36">
+      <c r="E417" s="28">
         <v>1</v>
       </c>
       <c r="F417" s="8"/>
     </row>
-    <row r="418" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:6" x14ac:dyDescent="0.2">
       <c r="E418">
         <f>SUM(E408:E416)*E417</f>
         <v>0</v>
@@ -6905,7 +6885,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="419" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A419" s="14" t="s">
         <v>150</v>
       </c>
@@ -6919,7 +6899,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="420" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A420" s="14"/>
       <c r="B420" s="14" t="s">
         <v>152</v>
@@ -6931,7 +6911,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="421" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A421" s="14"/>
       <c r="B421" s="14" t="s">
         <v>153</v>
@@ -6943,7 +6923,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="422" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A422" s="14"/>
       <c r="B422" s="14" t="s">
         <v>154</v>
@@ -6955,7 +6935,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="423" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A423" s="14"/>
       <c r="B423" s="14" t="s">
         <v>155</v>
@@ -6967,7 +6947,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="424" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A424" s="14"/>
       <c r="B424" s="14" t="s">
         <v>258</v>
@@ -6979,7 +6959,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="425" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A425" s="14"/>
       <c r="B425" s="14" t="s">
         <v>156</v>
@@ -6991,7 +6971,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="426" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A426" s="14"/>
       <c r="B426" s="14" t="s">
         <v>259</v>
@@ -7003,7 +6983,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="427" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A427" s="14"/>
       <c r="B427" s="14" t="s">
         <v>157</v>
@@ -7015,19 +6995,19 @@
         <v>4</v>
       </c>
     </row>
-    <row r="428" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A428" s="14"/>
       <c r="B428" s="14"/>
       <c r="C428" s="14"/>
       <c r="D428" s="22" t="s">
         <v>389</v>
       </c>
-      <c r="E428" s="36">
+      <c r="E428" s="28">
         <v>1</v>
       </c>
       <c r="F428" s="14"/>
     </row>
-    <row r="429" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:6" x14ac:dyDescent="0.2">
       <c r="E429">
         <f>SUM(E419:E427)*E428</f>
         <v>0</v>
@@ -7037,7 +7017,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="430" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A430" s="8" t="s">
         <v>158</v>
       </c>
@@ -7051,7 +7031,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="431" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A431" s="8"/>
       <c r="B431" s="8" t="s">
         <v>160</v>
@@ -7063,7 +7043,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="432" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A432" s="8"/>
       <c r="B432" s="8" t="s">
         <v>8</v>
@@ -7075,7 +7055,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="433" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A433" s="8"/>
       <c r="B433" s="8" t="s">
         <v>161</v>
@@ -7087,7 +7067,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="434" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A434" s="8"/>
       <c r="B434" s="8" t="s">
         <v>162</v>
@@ -7099,7 +7079,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="435" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A435" s="8"/>
       <c r="B435" s="8" t="s">
         <v>163</v>
@@ -7111,7 +7091,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="436" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A436" s="8"/>
       <c r="B436" s="8" t="s">
         <v>164</v>
@@ -7123,19 +7103,19 @@
         <v>3</v>
       </c>
     </row>
-    <row r="437" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A437" s="8"/>
       <c r="B437" s="8"/>
       <c r="C437" s="8"/>
       <c r="D437" s="22" t="s">
         <v>389</v>
       </c>
-      <c r="E437" s="36">
+      <c r="E437" s="28">
         <v>1</v>
       </c>
       <c r="F437" s="8"/>
     </row>
-    <row r="438" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:6" x14ac:dyDescent="0.2">
       <c r="E438">
         <f>SUM(E430:E436)*E437</f>
         <v>0</v>
@@ -7145,7 +7125,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="439" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A439" s="7" t="s">
         <v>362</v>
       </c>
@@ -7161,7 +7141,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="440" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A440" s="7"/>
       <c r="B440" s="7"/>
       <c r="C440" s="8"/>
@@ -7173,7 +7153,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="441" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A441" s="7"/>
       <c r="B441" s="7"/>
       <c r="C441" s="8"/>
@@ -7185,7 +7165,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="442" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A442" s="7"/>
       <c r="B442" s="7"/>
       <c r="C442" s="8" t="s">
@@ -7199,7 +7179,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="443" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A443" s="7"/>
       <c r="B443" s="7"/>
       <c r="C443" s="8"/>
@@ -7211,7 +7191,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="444" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A444" s="7"/>
       <c r="B444" s="7"/>
       <c r="C444" s="8"/>
@@ -7223,7 +7203,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="445" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A445" s="7"/>
       <c r="B445" s="7"/>
       <c r="C445" s="8"/>
@@ -7235,7 +7215,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="446" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A446" s="7"/>
       <c r="B446" s="7"/>
       <c r="C446" s="8"/>
@@ -7247,7 +7227,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="447" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:6" x14ac:dyDescent="0.2">
       <c r="E447">
         <f>SUM(E439:E446)</f>
         <v>0</v>
@@ -7257,12 +7237,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="448" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:6" ht="19" x14ac:dyDescent="0.25">
       <c r="A448" s="5" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="449" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A449" s="7" t="s">
         <v>265</v>
       </c>
@@ -7278,7 +7258,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="450" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A450" s="7"/>
       <c r="B450" s="8"/>
       <c r="C450" s="8" t="s">
@@ -7290,7 +7270,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="451" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A451" s="8"/>
       <c r="B451" s="7" t="s">
         <v>266</v>
@@ -7302,7 +7282,7 @@
       <c r="E451" s="8"/>
       <c r="F451" s="8"/>
     </row>
-    <row r="452" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A452" s="8"/>
       <c r="B452" s="8"/>
       <c r="C452" s="8" t="s">
@@ -7314,7 +7294,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="453" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A453" s="8"/>
       <c r="B453" s="8"/>
       <c r="C453" s="8" t="s">
@@ -7326,7 +7306,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="454" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A454" s="8"/>
       <c r="B454" s="8"/>
       <c r="C454" s="8" t="s">
@@ -7338,7 +7318,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="455" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A455" s="8"/>
       <c r="B455" s="8"/>
       <c r="C455" s="8" t="s">
@@ -7350,18 +7330,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="456" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A456" s="8"/>
       <c r="B456" s="8"/>
       <c r="C456" s="8"/>
       <c r="D456" s="22" t="s">
         <v>389</v>
       </c>
-      <c r="E456" s="36">
+      <c r="E456" s="28">
         <v>1</v>
       </c>
     </row>
-    <row r="457" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:6" x14ac:dyDescent="0.2">
       <c r="E457">
         <f>SUM(E449:E455)*E456</f>
         <v>0</v>
@@ -7371,12 +7351,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="458" spans="1:6" ht="21" x14ac:dyDescent="0.4">
-      <c r="A458" s="28" t="s">
+    <row r="458" spans="1:6" ht="21" x14ac:dyDescent="0.25">
+      <c r="A458" s="23" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="459" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A459" s="11" t="s">
         <v>369</v>
       </c>
@@ -7390,7 +7370,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="460" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A460" s="11" t="s">
         <v>371</v>
       </c>
@@ -7406,7 +7386,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="461" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A461" s="11"/>
       <c r="B461" s="12"/>
       <c r="C461" s="12" t="s">
@@ -7418,19 +7398,19 @@
         <v>20</v>
       </c>
     </row>
-    <row r="462" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A462" s="11"/>
       <c r="B462" s="12"/>
       <c r="C462" s="12"/>
       <c r="D462" s="22" t="s">
         <v>389</v>
       </c>
-      <c r="E462" s="36">
+      <c r="E462" s="28">
         <v>1</v>
       </c>
       <c r="F462" s="12"/>
     </row>
-    <row r="463" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A463" s="1"/>
       <c r="E463">
         <f>SUM(E459:E461)*E462</f>
@@ -7441,15 +7421,15 @@
         <v>50</v>
       </c>
     </row>
-    <row r="464" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A464" s="1"/>
     </row>
-    <row r="465" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:6" ht="19" x14ac:dyDescent="0.25">
       <c r="A465" s="5" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="466" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A466" s="15" t="s">
         <v>348</v>
       </c>
@@ -7465,7 +7445,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="467" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A467" s="13" t="s">
         <v>355</v>
       </c>
@@ -7479,7 +7459,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="468" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A468" s="13" t="s">
         <v>0</v>
       </c>
@@ -7493,7 +7473,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="469" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A469" s="13"/>
       <c r="B469" s="13" t="s">
         <v>350</v>
@@ -7505,19 +7485,19 @@
         <v>10</v>
       </c>
     </row>
-    <row r="470" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A470" s="13"/>
       <c r="B470" s="13"/>
       <c r="C470" s="13"/>
       <c r="D470" s="22" t="s">
         <v>389</v>
       </c>
-      <c r="E470" s="36">
+      <c r="E470" s="28">
         <v>1</v>
       </c>
       <c r="F470" s="13"/>
     </row>
-    <row r="471" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:6" x14ac:dyDescent="0.2">
       <c r="E471">
         <f>SUM(E466:E469)*E470</f>
         <v>0</v>
@@ -7527,7 +7507,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="473" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A473" s="16" t="s">
         <v>348</v>
       </c>
@@ -7543,7 +7523,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="474" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A474" s="14" t="s">
         <v>135</v>
       </c>
@@ -7557,7 +7537,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="475" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A475" s="14"/>
       <c r="B475" s="14" t="s">
         <v>228</v>
@@ -7569,19 +7549,19 @@
         <v>20</v>
       </c>
     </row>
-    <row r="476" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A476" s="14"/>
       <c r="B476" s="14"/>
       <c r="C476" s="14"/>
       <c r="D476" s="22" t="s">
         <v>389</v>
       </c>
-      <c r="E476" s="36">
+      <c r="E476" s="28">
         <v>1</v>
       </c>
       <c r="F476" s="14"/>
     </row>
-    <row r="477" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:6" x14ac:dyDescent="0.2">
       <c r="E477">
         <f>SUM(E473:E475)*E476</f>
         <v>0</v>
@@ -7591,7 +7571,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="478" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A478" s="11" t="s">
         <v>348</v>
       </c>
@@ -7607,7 +7587,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="479" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A479" s="12" t="s">
         <v>353</v>
       </c>
@@ -7621,7 +7601,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="480" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A480" s="12"/>
       <c r="B480" s="12" t="s">
         <v>354</v>
@@ -7633,19 +7613,19 @@
         <v>40</v>
       </c>
     </row>
-    <row r="481" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A481" s="12"/>
       <c r="B481" s="12"/>
       <c r="C481" s="12"/>
       <c r="D481" s="22" t="s">
         <v>389</v>
       </c>
-      <c r="E481" s="36">
+      <c r="E481" s="28">
         <v>1</v>
       </c>
       <c r="F481" s="12"/>
     </row>
-    <row r="482" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:6" x14ac:dyDescent="0.2">
       <c r="E482">
         <f>SUM(E478:E480)*E481</f>
         <v>0</v>
@@ -7655,12 +7635,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="487" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:6" ht="19" x14ac:dyDescent="0.25">
       <c r="A487" s="5" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="488" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A488" s="14" t="s">
         <v>265</v>
       </c>
@@ -7674,7 +7654,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="489" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A489" s="14" t="s">
         <v>270</v>
       </c>
@@ -7688,7 +7668,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="490" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A490" s="14"/>
       <c r="B490" s="14" t="s">
         <v>268</v>
@@ -7700,7 +7680,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="491" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A491" s="14"/>
       <c r="B491" s="14" t="s">
         <v>267</v>
@@ -7712,7 +7692,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="492" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A492" s="14"/>
       <c r="B492" s="14" t="s">
         <v>269</v>
@@ -7724,7 +7704,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="493" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A493" s="14"/>
       <c r="B493" s="14" t="s">
         <v>271</v>
@@ -7736,7 +7716,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="494" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A494" s="14"/>
       <c r="B494" s="14" t="s">
         <v>272</v>
@@ -7748,7 +7728,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="495" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A495" s="14"/>
       <c r="B495" s="14" t="s">
         <v>26</v>
@@ -7760,7 +7740,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="496" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A496" s="14"/>
       <c r="B496" s="14" t="s">
         <v>27</v>
@@ -7772,7 +7752,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="497" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A497" s="14"/>
       <c r="B497" s="14" t="s">
         <v>273</v>
@@ -7784,7 +7764,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="498" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A498" s="14"/>
       <c r="B498" s="14" t="s">
         <v>274</v>
@@ -7796,19 +7776,19 @@
         <v>5</v>
       </c>
     </row>
-    <row r="499" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A499" s="14"/>
       <c r="B499" s="14"/>
       <c r="C499" s="14"/>
       <c r="D499" s="22" t="s">
         <v>389</v>
       </c>
-      <c r="E499" s="36">
+      <c r="E499" s="28">
         <v>1</v>
       </c>
       <c r="F499" s="14"/>
     </row>
-    <row r="500" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:6" x14ac:dyDescent="0.2">
       <c r="E500">
         <f>SUM(E488:E498)*E499</f>
         <v>0</v>
@@ -7818,7 +7798,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="502" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A502" s="12" t="s">
         <v>265</v>
       </c>
@@ -7832,7 +7812,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="503" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A503" s="12" t="s">
         <v>270</v>
       </c>
@@ -7846,7 +7826,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="504" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A504" s="12"/>
       <c r="B504" s="12" t="s">
         <v>268</v>
@@ -7858,7 +7838,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="505" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A505" s="12"/>
       <c r="B505" s="12" t="s">
         <v>267</v>
@@ -7870,7 +7850,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="506" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A506" s="12"/>
       <c r="B506" s="12" t="s">
         <v>269</v>
@@ -7882,7 +7862,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="507" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A507" s="12"/>
       <c r="B507" s="12" t="s">
         <v>271</v>
@@ -7894,7 +7874,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="508" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A508" s="12"/>
       <c r="B508" s="12" t="s">
         <v>272</v>
@@ -7906,7 +7886,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="509" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A509" s="12"/>
       <c r="B509" s="12" t="s">
         <v>26</v>
@@ -7918,7 +7898,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="510" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A510" s="12"/>
       <c r="B510" s="12" t="s">
         <v>27</v>
@@ -7930,7 +7910,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="511" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A511" s="12"/>
       <c r="B511" s="12" t="s">
         <v>273</v>
@@ -7942,7 +7922,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="512" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A512" s="12"/>
       <c r="B512" s="12" t="s">
         <v>274</v>
@@ -7954,19 +7934,19 @@
         <v>5</v>
       </c>
     </row>
-    <row r="513" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A513" s="12"/>
       <c r="B513" s="12"/>
       <c r="C513" s="12"/>
       <c r="D513" s="22" t="s">
         <v>389</v>
       </c>
-      <c r="E513" s="36">
+      <c r="E513" s="28">
         <v>1</v>
       </c>
       <c r="F513" s="12"/>
     </row>
-    <row r="514" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:6" x14ac:dyDescent="0.2">
       <c r="E514">
         <f>SUM(E502:E512)*E513</f>
         <v>0</v>
@@ -7976,7 +7956,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="516" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A516" s="13" t="s">
         <v>265</v>
       </c>
@@ -7990,7 +7970,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="517" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A517" s="13" t="s">
         <v>270</v>
       </c>
@@ -8004,7 +7984,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="518" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A518" s="13"/>
       <c r="B518" s="13" t="s">
         <v>268</v>
@@ -8016,7 +7996,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="519" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A519" s="13"/>
       <c r="B519" s="13" t="s">
         <v>267</v>
@@ -8028,7 +8008,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="520" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A520" s="13"/>
       <c r="B520" s="13" t="s">
         <v>269</v>
@@ -8040,7 +8020,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="521" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A521" s="13"/>
       <c r="B521" s="13" t="s">
         <v>271</v>
@@ -8052,7 +8032,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="522" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A522" s="13"/>
       <c r="B522" s="13" t="s">
         <v>272</v>
@@ -8064,7 +8044,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="523" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A523" s="13"/>
       <c r="B523" s="13" t="s">
         <v>26</v>
@@ -8076,7 +8056,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="524" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A524" s="13"/>
       <c r="B524" s="13" t="s">
         <v>27</v>
@@ -8088,7 +8068,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="525" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A525" s="13"/>
       <c r="B525" s="13" t="s">
         <v>273</v>
@@ -8100,7 +8080,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="526" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A526" s="13"/>
       <c r="B526" s="13" t="s">
         <v>274</v>
@@ -8112,19 +8092,19 @@
         <v>5</v>
       </c>
     </row>
-    <row r="527" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A527" s="13"/>
       <c r="B527" s="13"/>
       <c r="C527" s="13"/>
       <c r="D527" s="22" t="s">
         <v>389</v>
       </c>
-      <c r="E527" s="36">
+      <c r="E527" s="28">
         <v>1</v>
       </c>
       <c r="F527" s="13"/>
     </row>
-    <row r="528" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:6" x14ac:dyDescent="0.2">
       <c r="E528">
         <f>SUM(E516:E526)*E527</f>
         <v>0</v>
@@ -8134,12 +8114,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="530" spans="1:6" ht="21" x14ac:dyDescent="0.4">
-      <c r="A530" s="28" t="s">
+    <row r="530" spans="1:6" ht="21" x14ac:dyDescent="0.25">
+      <c r="A530" s="23" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="531" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A531" s="16" t="s">
         <v>375</v>
       </c>
@@ -8151,7 +8131,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="532" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A532" s="14"/>
       <c r="B532" s="14"/>
       <c r="C532" s="14"/>
@@ -8161,7 +8141,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="533" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A533" s="14"/>
       <c r="B533" s="14"/>
       <c r="C533" s="14"/>
@@ -8171,7 +8151,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="534" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A534" s="14"/>
       <c r="B534" s="14"/>
       <c r="C534" s="14"/>
@@ -8181,7 +8161,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="535" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A535" s="14"/>
       <c r="B535" s="14"/>
       <c r="C535" s="14"/>
@@ -8191,19 +8171,19 @@
         <v>30</v>
       </c>
     </row>
-    <row r="536" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A536" s="14"/>
       <c r="B536" s="14"/>
       <c r="C536" s="14"/>
       <c r="D536" s="22" t="s">
         <v>389</v>
       </c>
-      <c r="E536" s="36">
+      <c r="E536" s="28">
         <v>1</v>
       </c>
       <c r="F536" s="14"/>
     </row>
-    <row r="537" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:6" x14ac:dyDescent="0.2">
       <c r="E537">
         <f>SUM(E531:E535)*E536</f>
         <v>0</v>
@@ -8213,7 +8193,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="539" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A539" s="11" t="s">
         <v>375</v>
       </c>
@@ -8225,7 +8205,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="540" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A540" s="12"/>
       <c r="B540" s="12"/>
       <c r="C540" s="12"/>
@@ -8235,7 +8215,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="541" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A541" s="12"/>
       <c r="B541" s="12"/>
       <c r="C541" s="12"/>
@@ -8245,7 +8225,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="542" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A542" s="12"/>
       <c r="B542" s="12"/>
       <c r="C542" s="12"/>
@@ -8255,7 +8235,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="543" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A543" s="12"/>
       <c r="B543" s="12"/>
       <c r="C543" s="12"/>
@@ -8265,19 +8245,19 @@
         <v>30</v>
       </c>
     </row>
-    <row r="544" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A544" s="12"/>
       <c r="B544" s="12"/>
       <c r="C544" s="12"/>
       <c r="D544" s="22" t="s">
         <v>389</v>
       </c>
-      <c r="E544" s="36">
+      <c r="E544" s="28">
         <v>1</v>
       </c>
       <c r="F544" s="12"/>
     </row>
-    <row r="545" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:8" x14ac:dyDescent="0.2">
       <c r="E545">
         <f>SUM(E539:E543)*E544</f>
         <v>0</v>
@@ -8287,7 +8267,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="547" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A547" s="15" t="s">
         <v>375</v>
       </c>
@@ -8299,7 +8279,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="548" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A548" s="13"/>
       <c r="B548" s="13"/>
       <c r="C548" s="13"/>
@@ -8309,7 +8289,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="549" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A549" s="13"/>
       <c r="B549" s="13"/>
       <c r="C549" s="13"/>
@@ -8319,7 +8299,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="550" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A550" s="13"/>
       <c r="B550" s="13"/>
       <c r="C550" s="13"/>
@@ -8329,7 +8309,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="551" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A551" s="13"/>
       <c r="B551" s="13"/>
       <c r="C551" s="13"/>
@@ -8339,19 +8319,19 @@
         <v>30</v>
       </c>
     </row>
-    <row r="552" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A552" s="13"/>
       <c r="B552" s="13"/>
       <c r="C552" s="13"/>
       <c r="D552" s="22" t="s">
         <v>389</v>
       </c>
-      <c r="E552" s="36">
+      <c r="E552" s="28">
         <v>1</v>
       </c>
       <c r="F552" s="13"/>
     </row>
-    <row r="553" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:8" x14ac:dyDescent="0.2">
       <c r="E553">
         <f>SUM(E547:E551)*E552</f>
         <v>0</v>
@@ -8361,7 +8341,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="556" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A556" s="7"/>
       <c r="B556" t="s">
         <v>213</v>
@@ -8379,9 +8359,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="557" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A557" s="11" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B557" t="s">
         <v>214</v>
@@ -8399,9 +8379,9 @@
         <v>-3.5137034434293744E-2</v>
       </c>
     </row>
-    <row r="558" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A558" s="15" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B558" t="s">
         <v>215</v>
@@ -8419,9 +8399,9 @@
         <v>-3.5971223021582732E-2</v>
       </c>
     </row>
-    <row r="559" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A559" s="16" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B559" t="s">
         <v>216</v>
@@ -8439,7 +8419,7 @@
         <v>-3.5739814152966405E-2</v>
       </c>
     </row>
-    <row r="563" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="563" spans="4:7" x14ac:dyDescent="0.2">
       <c r="F563" t="s">
         <v>260</v>
       </c>
@@ -8447,7 +8427,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="564" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="564" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D564" t="s">
         <v>262</v>
       </c>
@@ -8455,7 +8435,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="565" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="565" spans="4:7" x14ac:dyDescent="0.2">
       <c r="F565">
         <v>45</v>
       </c>
@@ -8463,7 +8443,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="566" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="566" spans="4:7" x14ac:dyDescent="0.2">
       <c r="F566">
         <f>F565+(F574-F565)/9</f>
         <v>50</v>
@@ -8472,7 +8452,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="567" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="567" spans="4:7" x14ac:dyDescent="0.2">
       <c r="F567">
         <f>F566+(F574-F565)/9</f>
         <v>55</v>
@@ -8481,7 +8461,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="568" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="568" spans="4:7" x14ac:dyDescent="0.2">
       <c r="F568">
         <f>F567+(F574-F565)/9</f>
         <v>60</v>
@@ -8490,7 +8470,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="569" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="569" spans="4:7" x14ac:dyDescent="0.2">
       <c r="F569">
         <f>F568+(F574-F565)/9</f>
         <v>65</v>
@@ -8499,7 +8479,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="570" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="570" spans="4:7" x14ac:dyDescent="0.2">
       <c r="F570">
         <f>F569+(F574-F565)/9</f>
         <v>70</v>
@@ -8508,7 +8488,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="571" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="571" spans="4:7" x14ac:dyDescent="0.2">
       <c r="F571">
         <f>F570+(F574-F565)/9</f>
         <v>75</v>
@@ -8517,7 +8497,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="572" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="572" spans="4:7" x14ac:dyDescent="0.2">
       <c r="F572">
         <f>F571+(F574-F565)/9</f>
         <v>80</v>
@@ -8526,7 +8506,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="573" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="573" spans="4:7" x14ac:dyDescent="0.2">
       <c r="F573">
         <f>F572+(F574-F565)/9</f>
         <v>85</v>
@@ -8535,7 +8515,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="574" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="574" spans="4:7" x14ac:dyDescent="0.2">
       <c r="F574">
         <v>90</v>
       </c>
@@ -8543,7 +8523,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="575" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="575" spans="4:7" x14ac:dyDescent="0.2">
       <c r="E575" t="s">
         <v>264</v>
       </c>
@@ -8573,46 +8553,45 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:L1047724"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="31.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="31.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="27.5" customWidth="1"/>
+    <col min="5" max="5" width="14.5" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="33.6" x14ac:dyDescent="0.65">
-      <c r="A1" s="37" t="s">
+    <row r="1" spans="1:4" ht="34" x14ac:dyDescent="0.4">
+      <c r="A1" s="29" t="s">
         <v>392</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="38" t="s">
+    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="30" t="s">
         <v>393</v>
       </c>
-      <c r="B5" s="38"/>
-      <c r="C5" s="38"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B5" s="30"/>
+      <c r="C5" s="30"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>84</v>
       </c>
@@ -8626,29 +8605,29 @@
         <v>87</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="B10" t="s">
         <v>398</v>
-      </c>
-      <c r="B10" t="s">
-        <v>399</v>
       </c>
       <c r="C10" s="3">
         <v>7026787</v>
       </c>
       <c r="D10" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="C11" s="3"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>89</v>
       </c>
@@ -8656,7 +8635,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>90</v>
       </c>
@@ -8664,7 +8643,7 @@
         <v>45924</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>91</v>
       </c>
@@ -8672,26 +8651,26 @@
         <v>46051</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>93</v>
       </c>
       <c r="B21" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="23.4" x14ac:dyDescent="0.45">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="24" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
         <v>94</v>
       </c>
       <c r="H23" s="21"/>
     </row>
-    <row r="25" spans="1:8" ht="18" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8" ht="19" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>95</v>
       </c>
@@ -8702,7 +8681,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" s="15" t="s">
         <v>36</v>
       </c>
@@ -8715,7 +8694,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="15"/>
       <c r="B28" s="13" t="s">
         <v>37</v>
@@ -8726,7 +8705,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="15"/>
       <c r="B29" s="13" t="s">
         <v>38</v>
@@ -8737,7 +8716,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="15"/>
       <c r="B30" s="13" t="s">
         <v>19</v>
@@ -8748,7 +8727,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="15"/>
       <c r="B31" s="13" t="s">
         <v>39</v>
@@ -8759,7 +8738,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="15"/>
       <c r="B32" s="13"/>
       <c r="C32" s="22" t="s">
@@ -8771,7 +8750,7 @@
       </c>
       <c r="E32" s="13"/>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D33">
         <f>-SUM(D27:D32)</f>
         <v>0</v>
@@ -8782,33 +8761,33 @@
       </c>
       <c r="L33" s="20"/>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A34" s="23" t="s">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A34" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="B34" s="24" t="s">
+      <c r="B34" s="38" t="s">
         <v>226</v>
       </c>
-      <c r="C34" s="24"/>
-      <c r="D34" s="24"/>
-      <c r="E34" s="24">
+      <c r="C34" s="16"/>
+      <c r="D34" s="16"/>
+      <c r="E34" s="16">
         <v>5</v>
       </c>
       <c r="L34" s="20"/>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A35" s="23"/>
-      <c r="B35" s="24" t="s">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A35" s="16"/>
+      <c r="B35" s="38" t="s">
         <v>50</v>
       </c>
-      <c r="C35" s="24"/>
-      <c r="D35" s="24"/>
-      <c r="E35" s="24">
+      <c r="C35" s="16"/>
+      <c r="D35" s="16"/>
+      <c r="E35" s="16">
         <v>5</v>
       </c>
       <c r="L35" s="20"/>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A36" s="16"/>
       <c r="B36" s="14"/>
       <c r="C36" s="22" t="s">
@@ -8821,7 +8800,7 @@
       <c r="E36" s="14"/>
       <c r="L36" s="20"/>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D37">
         <f>-SUM(D34:D36)</f>
         <v>0</v>
@@ -8832,10 +8811,10 @@
       </c>
       <c r="L37" s="20"/>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
       <c r="L38" s="20"/>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A39" s="7" t="s">
         <v>98</v>
       </c>
@@ -8849,7 +8828,7 @@
       </c>
       <c r="L39" s="20"/>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A40" s="7"/>
       <c r="B40" s="10" t="s">
         <v>47</v>
@@ -8861,7 +8840,7 @@
       </c>
       <c r="L40" s="20"/>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A41" s="7"/>
       <c r="B41" s="9" t="s">
         <v>48</v>
@@ -8873,7 +8852,7 @@
       </c>
       <c r="L41" s="20"/>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A42" s="7"/>
       <c r="B42" s="9" t="s">
         <v>49</v>
@@ -8885,7 +8864,7 @@
       </c>
       <c r="L42" s="20"/>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A43" s="7"/>
       <c r="B43" s="9" t="s">
         <v>50</v>
@@ -8897,7 +8876,7 @@
       </c>
       <c r="L43" s="20"/>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A44" s="7"/>
       <c r="B44" s="9" t="s">
         <v>51</v>
@@ -8909,7 +8888,7 @@
       </c>
       <c r="L44" s="20"/>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A45" s="7"/>
       <c r="B45" s="9" t="s">
         <v>52</v>
@@ -8921,7 +8900,7 @@
       </c>
       <c r="L45" s="20"/>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A46" s="7"/>
       <c r="B46" s="9"/>
       <c r="C46" s="22" t="s">
@@ -8934,7 +8913,7 @@
       <c r="E46" s="8"/>
       <c r="L46" s="20"/>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D47">
         <f>-SUM(D39:D46)</f>
         <v>0</v>
@@ -8945,126 +8924,126 @@
       </c>
       <c r="L47" s="20"/>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A49" s="26" t="s">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A49" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="B49" s="29" t="s">
+      <c r="B49" s="37" t="s">
         <v>76</v>
       </c>
-      <c r="C49" s="27"/>
-      <c r="D49" s="27"/>
-      <c r="E49" s="27">
+      <c r="C49" s="15"/>
+      <c r="D49" s="15"/>
+      <c r="E49" s="15">
         <v>10</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A50" s="26"/>
-      <c r="B50" s="29" t="s">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A50" s="15"/>
+      <c r="B50" s="37" t="s">
         <v>77</v>
       </c>
-      <c r="C50" s="27"/>
-      <c r="D50" s="27"/>
-      <c r="E50" s="27">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A51" s="26"/>
-      <c r="B51" s="29" t="s">
+      <c r="C50" s="15"/>
+      <c r="D50" s="15"/>
+      <c r="E50" s="15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A51" s="15"/>
+      <c r="B51" s="37" t="s">
         <v>124</v>
       </c>
-      <c r="C51" s="27"/>
-      <c r="D51" s="27"/>
-      <c r="E51" s="27">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A52" s="26"/>
-      <c r="B52" s="27"/>
-      <c r="C52" s="27"/>
-      <c r="D52" s="27"/>
-      <c r="E52" s="27"/>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A53" s="26" t="s">
+      <c r="C51" s="15"/>
+      <c r="D51" s="15"/>
+      <c r="E51" s="15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A52" s="15"/>
+      <c r="B52" s="37"/>
+      <c r="C52" s="15"/>
+      <c r="D52" s="15"/>
+      <c r="E52" s="15"/>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A53" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="B53" s="27" t="s">
+      <c r="B53" s="37" t="s">
         <v>77</v>
       </c>
-      <c r="C53" s="27"/>
-      <c r="D53" s="27"/>
-      <c r="E53" s="27">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A54" s="26"/>
-      <c r="B54" s="27" t="s">
+      <c r="C53" s="15"/>
+      <c r="D53" s="15"/>
+      <c r="E53" s="15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A54" s="15"/>
+      <c r="B54" s="37" t="s">
         <v>123</v>
       </c>
-      <c r="C54" s="27"/>
-      <c r="D54" s="27"/>
-      <c r="E54" s="27">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A55" s="26"/>
-      <c r="B55" s="27" t="s">
+      <c r="C54" s="15"/>
+      <c r="D54" s="15"/>
+      <c r="E54" s="15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A55" s="15"/>
+      <c r="B55" s="37" t="s">
         <v>124</v>
       </c>
-      <c r="C55" s="27"/>
-      <c r="D55" s="27"/>
-      <c r="E55" s="27">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A56" s="26"/>
-      <c r="B56" s="27"/>
-      <c r="C56" s="27"/>
-      <c r="D56" s="27"/>
-      <c r="E56" s="27"/>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A57" s="26" t="s">
+      <c r="C55" s="15"/>
+      <c r="D55" s="15"/>
+      <c r="E55" s="15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A56" s="15"/>
+      <c r="B56" s="37"/>
+      <c r="C56" s="15"/>
+      <c r="D56" s="15"/>
+      <c r="E56" s="15"/>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A57" s="15" t="s">
         <v>227</v>
       </c>
-      <c r="B57" s="27" t="s">
+      <c r="B57" s="37" t="s">
         <v>77</v>
       </c>
-      <c r="C57" s="27"/>
-      <c r="D57" s="27"/>
-      <c r="E57" s="27">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A58" s="26"/>
-      <c r="B58" s="27" t="s">
+      <c r="C57" s="15"/>
+      <c r="D57" s="15"/>
+      <c r="E57" s="15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A58" s="15"/>
+      <c r="B58" s="37" t="s">
         <v>123</v>
       </c>
-      <c r="C58" s="27"/>
-      <c r="D58" s="27"/>
-      <c r="E58" s="27">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A59" s="26"/>
-      <c r="B59" s="27" t="s">
+      <c r="C58" s="15"/>
+      <c r="D58" s="15"/>
+      <c r="E58" s="15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A59" s="15"/>
+      <c r="B59" s="37" t="s">
         <v>124</v>
       </c>
-      <c r="C59" s="27"/>
-      <c r="D59" s="27"/>
-      <c r="E59" s="27">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C59" s="15"/>
+      <c r="D59" s="15"/>
+      <c r="E59" s="15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A60" s="15"/>
       <c r="B60" s="13"/>
       <c r="C60" s="22" t="s">
@@ -9076,7 +9055,7 @@
       </c>
       <c r="E60" s="13"/>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
       <c r="D61">
         <f>-SUM(D49:D60)</f>
         <v>0</v>
@@ -9086,7 +9065,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A63" s="15" t="s">
         <v>78</v>
       </c>
@@ -9099,7 +9078,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A64" s="15"/>
       <c r="B64" s="13" t="s">
         <v>46</v>
@@ -9110,7 +9089,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A65" s="15"/>
       <c r="B65" s="13" t="s">
         <v>247</v>
@@ -9121,7 +9100,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A66" s="15"/>
       <c r="B66" s="13" t="s">
         <v>79</v>
@@ -9132,7 +9111,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A67" s="15"/>
       <c r="B67" s="13"/>
       <c r="C67" s="22" t="s">
@@ -9144,7 +9123,7 @@
       </c>
       <c r="E67" s="13"/>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
       <c r="D68">
         <f>-SUM(D63:D67)</f>
         <v>0</v>
@@ -9154,53 +9133,53 @@
         <v>40</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A72" s="30" t="s">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A72" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="B72" s="31" t="s">
+      <c r="B72" s="39" t="s">
         <v>251</v>
       </c>
-      <c r="C72" s="31"/>
-      <c r="D72" s="31"/>
-      <c r="E72" s="31">
+      <c r="C72" s="11"/>
+      <c r="D72" s="11"/>
+      <c r="E72" s="11">
         <v>10</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A73" s="30"/>
-      <c r="B73" s="31" t="s">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A73" s="11"/>
+      <c r="B73" s="39" t="s">
         <v>229</v>
       </c>
-      <c r="C73" s="31"/>
-      <c r="D73" s="31"/>
-      <c r="E73" s="31">
+      <c r="C73" s="11"/>
+      <c r="D73" s="11"/>
+      <c r="E73" s="11">
         <v>10</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A74" s="30"/>
-      <c r="B74" s="31" t="s">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A74" s="11"/>
+      <c r="B74" s="39" t="s">
         <v>230</v>
       </c>
-      <c r="C74" s="31"/>
-      <c r="D74" s="31"/>
-      <c r="E74" s="31">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A75" s="30"/>
-      <c r="B75" s="31" t="s">
+      <c r="C74" s="11"/>
+      <c r="D74" s="11"/>
+      <c r="E74" s="11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A75" s="11"/>
+      <c r="B75" s="39" t="s">
         <v>228</v>
       </c>
-      <c r="C75" s="31"/>
-      <c r="D75" s="31"/>
-      <c r="E75" s="31">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C75" s="11"/>
+      <c r="D75" s="11"/>
+      <c r="E75" s="11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A76" s="11"/>
       <c r="B76" s="12"/>
       <c r="C76" s="22" t="s">
@@ -9212,7 +9191,7 @@
       </c>
       <c r="E76" s="12"/>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
       <c r="D77">
         <f>-SUM(D72:D76)</f>
         <v>0</v>
@@ -9222,7 +9201,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A79" s="7" t="s">
         <v>57</v>
       </c>
@@ -9235,7 +9214,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A80" s="7"/>
       <c r="B80" s="8" t="s">
         <v>60</v>
@@ -9246,7 +9225,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A81" s="7"/>
       <c r="B81" s="8" t="s">
         <v>59</v>
@@ -9257,7 +9236,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A82" s="7"/>
       <c r="B82" s="8" t="s">
         <v>56</v>
@@ -9268,7 +9247,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A83" s="7"/>
       <c r="B83" s="8" t="s">
         <v>231</v>
@@ -9279,7 +9258,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A84" s="7"/>
       <c r="B84" s="8" t="s">
         <v>61</v>
@@ -9292,7 +9271,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A85" s="7"/>
       <c r="B85" s="8"/>
       <c r="C85" s="8" t="s">
@@ -9303,7 +9282,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A86" s="7"/>
       <c r="B86" s="8"/>
       <c r="C86" s="8" t="s">
@@ -9314,7 +9293,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A87" s="7"/>
       <c r="B87" s="8"/>
       <c r="C87" s="8" t="s">
@@ -9325,7 +9304,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A88" s="7"/>
       <c r="B88" s="8"/>
       <c r="C88" s="8" t="s">
@@ -9336,7 +9315,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A89" s="7"/>
       <c r="B89" s="8"/>
       <c r="C89" s="22" t="s">
@@ -9348,7 +9327,7 @@
       </c>
       <c r="E89" s="8"/>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
       <c r="D90">
         <f>-SUM(D79:D89)</f>
         <v>0</v>
@@ -9358,7 +9337,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A91" s="11" t="s">
         <v>168</v>
       </c>
@@ -9371,7 +9350,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A92" s="11"/>
       <c r="B92" s="12" t="s">
         <v>77</v>
@@ -9382,7 +9361,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A93" s="11"/>
       <c r="B93" s="12" t="s">
         <v>170</v>
@@ -9393,7 +9372,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A94" s="11"/>
       <c r="B94" s="12"/>
       <c r="C94" s="22" t="s">
@@ -9405,7 +9384,7 @@
       </c>
       <c r="E94" s="12"/>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
       <c r="D95">
         <f>-SUM(D91:D94)</f>
         <v>0</v>
@@ -9415,392 +9394,427 @@
         <v>20</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A96" s="1" t="s">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A96" s="40" t="s">
         <v>62</v>
       </c>
-      <c r="B96" s="31" t="s">
+      <c r="B96" s="41" t="s">
         <v>63</v>
       </c>
-      <c r="C96" s="31" t="s">
+      <c r="C96" s="42" t="s">
         <v>64</v>
       </c>
-      <c r="D96" s="31"/>
-      <c r="E96" s="31">
+      <c r="D96" s="42"/>
+      <c r="E96" s="42">
         <v>5</v>
       </c>
       <c r="H96" s="1"/>
     </row>
-    <row r="97" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B97" s="31"/>
-      <c r="C97" s="31" t="s">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A97" s="40"/>
+      <c r="B97" s="42"/>
+      <c r="C97" s="42" t="s">
         <v>65</v>
       </c>
-      <c r="D97" s="31"/>
-      <c r="E97" s="31">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="98" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B98" s="31"/>
-      <c r="C98" s="31" t="s">
+      <c r="D97" s="42"/>
+      <c r="E97" s="42">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A98" s="40"/>
+      <c r="B98" s="42"/>
+      <c r="C98" s="42" t="s">
         <v>53</v>
       </c>
-      <c r="D98" s="31"/>
-      <c r="E98" s="31">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="99" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B99" s="31"/>
-      <c r="C99" s="31" t="s">
+      <c r="D98" s="42"/>
+      <c r="E98" s="42">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A99" s="40"/>
+      <c r="B99" s="42"/>
+      <c r="C99" s="42" t="s">
         <v>249</v>
       </c>
-      <c r="D99" s="31"/>
-      <c r="E99" s="31">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="100" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B100" s="31"/>
-      <c r="C100" s="31" t="s">
+      <c r="D99" s="42"/>
+      <c r="E99" s="42">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A100" s="40"/>
+      <c r="B100" s="42"/>
+      <c r="C100" s="42" t="s">
         <v>248</v>
       </c>
-      <c r="D100" s="31"/>
-      <c r="E100" s="31">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="101" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B101" s="31"/>
-      <c r="C101" s="31" t="s">
+      <c r="D100" s="42"/>
+      <c r="E100" s="42">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A101" s="40"/>
+      <c r="B101" s="42"/>
+      <c r="C101" s="42" t="s">
         <v>67</v>
       </c>
-      <c r="D101" s="31"/>
-      <c r="E101" s="31">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="102" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B102" s="31"/>
-      <c r="C102" s="31" t="s">
+      <c r="D101" s="42"/>
+      <c r="E101" s="42">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A102" s="40"/>
+      <c r="B102" s="42"/>
+      <c r="C102" s="42" t="s">
         <v>68</v>
       </c>
-      <c r="D102" s="31"/>
-      <c r="E102" s="31">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="103" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B103" s="31"/>
-      <c r="C103" s="31" t="s">
+      <c r="D102" s="42"/>
+      <c r="E102" s="42">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A103" s="40"/>
+      <c r="B103" s="42"/>
+      <c r="C103" s="42" t="s">
         <v>97</v>
       </c>
-      <c r="D103" s="31"/>
-      <c r="E103" s="31">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="104" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B104" s="12"/>
-      <c r="C104" s="22" t="s">
+      <c r="D103" s="42"/>
+      <c r="E103" s="42">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A104" s="40"/>
+      <c r="B104" s="42"/>
+      <c r="C104" s="43" t="s">
         <v>236</v>
       </c>
-      <c r="D104" s="22">
+      <c r="D104" s="43">
         <f>-SUM(D96:D103)</f>
         <v>0</v>
       </c>
-      <c r="E104" s="12"/>
-    </row>
-    <row r="105" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="D105">
+      <c r="E104" s="42"/>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A105" s="40"/>
+      <c r="B105" s="44"/>
+      <c r="C105" s="44"/>
+      <c r="D105" s="44">
         <f>-SUM(D96:D104)</f>
         <v>0</v>
       </c>
-      <c r="E105">
+      <c r="E105" s="44">
         <f>SUM(E96:E103)</f>
         <v>40</v>
       </c>
     </row>
-    <row r="106" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B106" s="25" t="s">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A106" s="40"/>
+      <c r="B106" s="45" t="s">
         <v>63</v>
       </c>
-      <c r="C106" s="25" t="s">
+      <c r="C106" s="46" t="s">
         <v>64</v>
       </c>
-      <c r="D106" s="25"/>
-      <c r="E106" s="25">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="107" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B107" s="25"/>
-      <c r="C107" s="25" t="s">
+      <c r="D106" s="46"/>
+      <c r="E106" s="46">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A107" s="40"/>
+      <c r="B107" s="46"/>
+      <c r="C107" s="46" t="s">
         <v>65</v>
       </c>
-      <c r="D107" s="25"/>
-      <c r="E107" s="25">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="108" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B108" s="25"/>
-      <c r="C108" s="25" t="s">
+      <c r="D107" s="46"/>
+      <c r="E107" s="46">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A108" s="40"/>
+      <c r="B108" s="46"/>
+      <c r="C108" s="46" t="s">
         <v>53</v>
       </c>
-      <c r="D108" s="25"/>
-      <c r="E108" s="25">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="109" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B109" s="25"/>
-      <c r="C109" s="25" t="s">
+      <c r="D108" s="46"/>
+      <c r="E108" s="46">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A109" s="40"/>
+      <c r="B109" s="46"/>
+      <c r="C109" s="46" t="s">
         <v>66</v>
       </c>
-      <c r="D109" s="25"/>
-      <c r="E109" s="25">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="110" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B110" s="25"/>
-      <c r="C110" s="25" t="s">
+      <c r="D109" s="46"/>
+      <c r="E109" s="46">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A110" s="40"/>
+      <c r="B110" s="46"/>
+      <c r="C110" s="46" t="s">
         <v>52</v>
       </c>
-      <c r="D110" s="25"/>
-      <c r="E110" s="25">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="111" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B111" s="25"/>
-      <c r="C111" s="25" t="s">
+      <c r="D110" s="46"/>
+      <c r="E110" s="46">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A111" s="40"/>
+      <c r="B111" s="46"/>
+      <c r="C111" s="46" t="s">
         <v>67</v>
       </c>
-      <c r="D111" s="25"/>
-      <c r="E111" s="25">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="112" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B112" s="25"/>
-      <c r="C112" s="25" t="s">
+      <c r="D111" s="46"/>
+      <c r="E111" s="46">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A112" s="40"/>
+      <c r="B112" s="46"/>
+      <c r="C112" s="46" t="s">
         <v>68</v>
       </c>
-      <c r="D112" s="25"/>
-      <c r="E112" s="25">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B113" s="25"/>
-      <c r="C113" s="25" t="s">
+      <c r="D112" s="46"/>
+      <c r="E112" s="46">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A113" s="40"/>
+      <c r="B113" s="46"/>
+      <c r="C113" s="46" t="s">
         <v>97</v>
       </c>
-      <c r="D113" s="25"/>
-      <c r="E113" s="25">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B114" s="13"/>
-      <c r="C114" s="22" t="s">
+      <c r="D113" s="46"/>
+      <c r="E113" s="46">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A114" s="40"/>
+      <c r="B114" s="46"/>
+      <c r="C114" s="43" t="s">
         <v>236</v>
       </c>
-      <c r="D114" s="22">
+      <c r="D114" s="43">
         <f>-SUM(D106:D113)</f>
         <v>0</v>
       </c>
-      <c r="E114" s="13"/>
-    </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="D115">
+      <c r="E114" s="46"/>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A115" s="40"/>
+      <c r="B115" s="44"/>
+      <c r="C115" s="44"/>
+      <c r="D115" s="44">
         <f>-SUM(D106:D114)</f>
         <v>0</v>
       </c>
-      <c r="E115">
+      <c r="E115" s="44">
         <f>SUM(E106:E113)</f>
         <v>40</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B116" s="24" t="s">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A116" s="40"/>
+      <c r="B116" s="47" t="s">
         <v>63</v>
       </c>
-      <c r="C116" s="24" t="s">
+      <c r="C116" s="48" t="s">
         <v>64</v>
       </c>
-      <c r="D116" s="24"/>
-      <c r="E116" s="24">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B117" s="24"/>
-      <c r="C117" s="24" t="s">
+      <c r="D116" s="48"/>
+      <c r="E116" s="48">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A117" s="40"/>
+      <c r="B117" s="48"/>
+      <c r="C117" s="48" t="s">
         <v>65</v>
       </c>
-      <c r="D117" s="24"/>
-      <c r="E117" s="24">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B118" s="24"/>
-      <c r="C118" s="24" t="s">
+      <c r="D117" s="48"/>
+      <c r="E117" s="48">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A118" s="40"/>
+      <c r="B118" s="48"/>
+      <c r="C118" s="48" t="s">
         <v>53</v>
       </c>
-      <c r="D118" s="24"/>
-      <c r="E118" s="24">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B119" s="24"/>
-      <c r="C119" s="24" t="s">
+      <c r="D118" s="48"/>
+      <c r="E118" s="48">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A119" s="40"/>
+      <c r="B119" s="48"/>
+      <c r="C119" s="48" t="s">
         <v>66</v>
       </c>
-      <c r="D119" s="24"/>
-      <c r="E119" s="24">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B120" s="24"/>
-      <c r="C120" s="24" t="s">
+      <c r="D119" s="48"/>
+      <c r="E119" s="48">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A120" s="40"/>
+      <c r="B120" s="48"/>
+      <c r="C120" s="48" t="s">
         <v>52</v>
       </c>
-      <c r="D120" s="24"/>
-      <c r="E120" s="24">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B121" s="24"/>
-      <c r="C121" s="24" t="s">
+      <c r="D120" s="48"/>
+      <c r="E120" s="48">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A121" s="40"/>
+      <c r="B121" s="48"/>
+      <c r="C121" s="48" t="s">
         <v>67</v>
       </c>
-      <c r="D121" s="24"/>
-      <c r="E121" s="24">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B122" s="24"/>
-      <c r="C122" s="24" t="s">
+      <c r="D121" s="48"/>
+      <c r="E121" s="48">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A122" s="40"/>
+      <c r="B122" s="48"/>
+      <c r="C122" s="48" t="s">
         <v>68</v>
       </c>
-      <c r="D122" s="24"/>
-      <c r="E122" s="24">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B123" s="24"/>
-      <c r="C123" s="24" t="s">
+      <c r="D122" s="48"/>
+      <c r="E122" s="48">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A123" s="40"/>
+      <c r="B123" s="48"/>
+      <c r="C123" s="48" t="s">
         <v>97</v>
       </c>
-      <c r="D123" s="24"/>
-      <c r="E123" s="24">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B124" s="14"/>
-      <c r="C124" s="22" t="s">
+      <c r="D123" s="48"/>
+      <c r="E123" s="48">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A124" s="40"/>
+      <c r="B124" s="48"/>
+      <c r="C124" s="43" t="s">
         <v>236</v>
       </c>
-      <c r="D124" s="22">
+      <c r="D124" s="43">
         <f>-SUM(D116:D123)</f>
         <v>0</v>
       </c>
-      <c r="E124" s="14"/>
-    </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="D125">
+      <c r="E124" s="48"/>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A125" s="40"/>
+      <c r="B125" s="44"/>
+      <c r="C125" s="44"/>
+      <c r="D125" s="44">
         <f>-SUM(D116:D124)</f>
         <v>0</v>
       </c>
-      <c r="E125">
+      <c r="E125" s="44">
         <f>SUM(E116:E123)</f>
         <v>40</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A127" s="31" t="s">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A127" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="B127" s="31" t="s">
+      <c r="B127" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="C127" s="31" t="s">
+      <c r="C127" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="D127" s="31"/>
-      <c r="E127" s="31">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A128" s="31"/>
-      <c r="B128" s="31"/>
-      <c r="C128" s="31" t="s">
+      <c r="D127" s="12"/>
+      <c r="E127" s="12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A128" s="12"/>
+      <c r="B128" s="12"/>
+      <c r="C128" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="D128" s="31" t="s">
+      <c r="D128" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="E128" s="31">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A129" s="31"/>
-      <c r="B129" s="31"/>
-      <c r="C129" s="31"/>
-      <c r="D129" s="31" t="s">
+      <c r="E128" s="12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A129" s="12"/>
+      <c r="B129" s="12"/>
+      <c r="C129" s="12"/>
+      <c r="D129" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="E129" s="31">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A130" s="31"/>
-      <c r="B130" s="31"/>
-      <c r="C130" s="31" t="s">
+      <c r="E129" s="12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A130" s="12"/>
+      <c r="B130" s="12"/>
+      <c r="C130" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="D130" s="31"/>
-      <c r="E130" s="31">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A131" s="31"/>
-      <c r="B131" s="31"/>
-      <c r="C131" s="31" t="s">
+      <c r="D130" s="12"/>
+      <c r="E130" s="12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A131" s="12"/>
+      <c r="B131" s="12"/>
+      <c r="C131" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="D131" s="31"/>
-      <c r="E131" s="31">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A132" s="31"/>
-      <c r="B132" s="31"/>
-      <c r="C132" s="31" t="s">
+      <c r="D131" s="12"/>
+      <c r="E131" s="12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A132" s="12"/>
+      <c r="B132" s="12"/>
+      <c r="C132" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="D132" s="31"/>
-      <c r="E132" s="31">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D132" s="12"/>
+      <c r="E132" s="12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A133" s="12"/>
       <c r="B133" s="12"/>
       <c r="C133" s="22" t="s">
@@ -9812,7 +9826,7 @@
       </c>
       <c r="E133" s="12"/>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A134"/>
       <c r="D134">
         <f>-SUM(D127:D133)</f>
@@ -9823,90 +9837,90 @@
         <v>30</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A135" s="31" t="s">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A135" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="B135" s="31" t="s">
+      <c r="B135" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="C135" s="31" t="s">
+      <c r="C135" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="D135" s="31"/>
-      <c r="E135" s="31">
+      <c r="D135" s="12"/>
+      <c r="E135" s="12">
         <v>10</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A136" s="31"/>
-      <c r="B136" s="31"/>
-      <c r="C136" s="31" t="s">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A136" s="12"/>
+      <c r="B136" s="12"/>
+      <c r="C136" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="D136" s="31"/>
-      <c r="E136" s="31">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A137" s="31"/>
-      <c r="B137" s="31"/>
-      <c r="C137" s="31" t="s">
+      <c r="D136" s="12"/>
+      <c r="E136" s="12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A137" s="12"/>
+      <c r="B137" s="12"/>
+      <c r="C137" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="D137" s="31"/>
-      <c r="E137" s="31">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A138" s="31"/>
-      <c r="B138" s="31"/>
-      <c r="C138" s="31" t="s">
+      <c r="D137" s="12"/>
+      <c r="E137" s="12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A138" s="12"/>
+      <c r="B138" s="12"/>
+      <c r="C138" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="D138" s="31" t="s">
+      <c r="D138" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="E138" s="31">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A139" s="31"/>
-      <c r="B139" s="31"/>
-      <c r="C139" s="31"/>
-      <c r="D139" s="31" t="s">
+      <c r="E138" s="12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A139" s="12"/>
+      <c r="B139" s="12"/>
+      <c r="C139" s="12"/>
+      <c r="D139" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="E139" s="31">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A140" s="30"/>
-      <c r="B140" s="31"/>
-      <c r="C140" s="31"/>
-      <c r="D140" s="31" t="s">
+      <c r="E139" s="12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A140" s="12"/>
+      <c r="B140" s="12"/>
+      <c r="C140" s="12"/>
+      <c r="D140" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="E140" s="31">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A141" s="30"/>
-      <c r="B141" s="31"/>
-      <c r="C141" s="31"/>
-      <c r="D141" s="31" t="s">
+      <c r="E140" s="12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A141" s="12"/>
+      <c r="B141" s="12"/>
+      <c r="C141" s="12"/>
+      <c r="D141" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="E141" s="31">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E141" s="12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A142" s="11"/>
       <c r="B142" s="12"/>
       <c r="C142" s="22" t="s">
@@ -9918,7 +9932,7 @@
       </c>
       <c r="E142" s="12"/>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.2">
       <c r="D143">
         <f>-SUM(D135:D142)</f>
         <v>0</v>
@@ -9928,66 +9942,66 @@
         <v>40</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A144" s="26" t="s">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A144" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="B144" s="27" t="s">
+      <c r="B144" s="37" t="s">
         <v>114</v>
       </c>
-      <c r="C144" s="27" t="s">
+      <c r="C144" s="37" t="s">
         <v>54</v>
       </c>
-      <c r="D144" s="27"/>
-      <c r="E144" s="27">
+      <c r="D144" s="37"/>
+      <c r="E144" s="37">
         <v>10</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A145" s="26"/>
-      <c r="B145" s="27"/>
-      <c r="C145" s="27" t="s">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A145" s="15"/>
+      <c r="B145" s="37"/>
+      <c r="C145" s="37" t="s">
         <v>126</v>
       </c>
-      <c r="D145" s="27"/>
-      <c r="E145" s="27">
+      <c r="D145" s="37"/>
+      <c r="E145" s="37">
         <v>10</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A146" s="26"/>
-      <c r="B146" s="27"/>
-      <c r="C146" s="27" t="s">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A146" s="15"/>
+      <c r="B146" s="37"/>
+      <c r="C146" s="37" t="s">
         <v>127</v>
       </c>
-      <c r="D146" s="27"/>
-      <c r="E146" s="27">
+      <c r="D146" s="37"/>
+      <c r="E146" s="37">
         <v>10</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A147" s="26"/>
-      <c r="B147" s="27"/>
-      <c r="C147" s="27" t="s">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A147" s="15"/>
+      <c r="B147" s="37"/>
+      <c r="C147" s="37" t="s">
         <v>124</v>
       </c>
-      <c r="D147" s="27"/>
-      <c r="E147" s="27">
+      <c r="D147" s="37"/>
+      <c r="E147" s="37">
         <v>10</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A148" s="26"/>
-      <c r="B148" s="27"/>
-      <c r="C148" s="27" t="s">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A148" s="15"/>
+      <c r="B148" s="37"/>
+      <c r="C148" s="37" t="s">
         <v>128</v>
       </c>
-      <c r="D148" s="27"/>
-      <c r="E148" s="27">
+      <c r="D148" s="37"/>
+      <c r="E148" s="37">
         <v>10</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A149" s="15"/>
       <c r="B149" s="13"/>
       <c r="C149" s="22" t="s">
@@ -9999,7 +10013,7 @@
       </c>
       <c r="E149" s="13"/>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.2">
       <c r="D150">
         <f>-SUM(D144:D149)</f>
         <v>0</v>
@@ -10009,44 +10023,44 @@
         <v>50</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A151" s="23" t="s">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A151" s="16" t="s">
         <v>125</v>
       </c>
-      <c r="B151" s="24" t="s">
+      <c r="B151" s="38" t="s">
         <v>129</v>
       </c>
-      <c r="C151" s="24" t="s">
+      <c r="C151" s="38" t="s">
         <v>54</v>
       </c>
-      <c r="D151" s="24"/>
-      <c r="E151" s="24">
+      <c r="D151" s="16"/>
+      <c r="E151" s="16">
         <v>20</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A152" s="23"/>
-      <c r="B152" s="24"/>
-      <c r="C152" s="24" t="s">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A152" s="16"/>
+      <c r="B152" s="38"/>
+      <c r="C152" s="38" t="s">
         <v>127</v>
       </c>
-      <c r="D152" s="24"/>
-      <c r="E152" s="24">
+      <c r="D152" s="16"/>
+      <c r="E152" s="16">
         <v>20</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A153" s="23"/>
-      <c r="B153" s="24"/>
-      <c r="C153" s="24" t="s">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A153" s="16"/>
+      <c r="B153" s="38"/>
+      <c r="C153" s="38" t="s">
         <v>124</v>
       </c>
-      <c r="D153" s="24"/>
-      <c r="E153" s="24">
+      <c r="D153" s="16"/>
+      <c r="E153" s="16">
         <v>20</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A154" s="16"/>
       <c r="B154" s="14"/>
       <c r="C154" s="22" t="s">
@@ -10058,7 +10072,7 @@
       </c>
       <c r="E154" s="14"/>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.2">
       <c r="D155">
         <f>-SUM(D151:D154)</f>
         <v>0</v>
@@ -10068,7 +10082,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A157" s="16" t="s">
         <v>119</v>
       </c>
@@ -10081,7 +10095,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A158" s="16"/>
       <c r="B158" s="14" t="s">
         <v>121</v>
@@ -10092,7 +10106,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A159" s="16"/>
       <c r="B159" s="14" t="s">
         <v>224</v>
@@ -10103,7 +10117,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A160" s="16"/>
       <c r="B160" s="14" t="s">
         <v>232</v>
@@ -10114,7 +10128,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A161" s="16"/>
       <c r="B161" s="14" t="s">
         <v>225</v>
@@ -10125,7 +10139,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A162" s="16"/>
       <c r="B162" s="14"/>
       <c r="C162" s="22" t="s">
@@ -10137,7 +10151,7 @@
       </c>
       <c r="E162" s="14"/>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.2">
       <c r="D163">
         <f>-SUM(D157:D162)</f>
         <v>0</v>
@@ -10147,75 +10161,75 @@
         <v>30</v>
       </c>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A164" s="30" t="s">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A164" s="11" t="s">
         <v>206</v>
       </c>
-      <c r="B164" s="31" t="s">
+      <c r="B164" s="39" t="s">
         <v>205</v>
       </c>
-      <c r="C164" s="31"/>
-      <c r="D164" s="31"/>
-      <c r="E164" s="31">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A165" s="30"/>
-      <c r="B165" s="31" t="s">
+      <c r="C164" s="11"/>
+      <c r="D164" s="11"/>
+      <c r="E164" s="11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A165" s="11"/>
+      <c r="B165" s="39" t="s">
         <v>65</v>
       </c>
-      <c r="C165" s="31"/>
-      <c r="D165" s="31"/>
-      <c r="E165" s="31">
+      <c r="C165" s="11"/>
+      <c r="D165" s="11"/>
+      <c r="E165" s="11">
         <v>10</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A166" s="30"/>
-      <c r="B166" s="31" t="s">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A166" s="11"/>
+      <c r="B166" s="39" t="s">
         <v>50</v>
       </c>
-      <c r="C166" s="31"/>
-      <c r="D166" s="31"/>
-      <c r="E166" s="31">
+      <c r="C166" s="11"/>
+      <c r="D166" s="11"/>
+      <c r="E166" s="11">
         <v>10</v>
       </c>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A167" s="30"/>
-      <c r="B167" s="31" t="s">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A167" s="11"/>
+      <c r="B167" s="39" t="s">
         <v>207</v>
       </c>
-      <c r="C167" s="31"/>
-      <c r="D167" s="31"/>
-      <c r="E167" s="31">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A168" s="30"/>
-      <c r="B168" s="31" t="s">
+      <c r="C167" s="11"/>
+      <c r="D167" s="11"/>
+      <c r="E167" s="11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A168" s="11"/>
+      <c r="B168" s="39" t="s">
         <v>51</v>
       </c>
-      <c r="C168" s="31"/>
-      <c r="D168" s="31"/>
-      <c r="E168" s="31">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A169" s="30"/>
-      <c r="B169" s="31" t="s">
+      <c r="C168" s="11"/>
+      <c r="D168" s="11"/>
+      <c r="E168" s="11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A169" s="11"/>
+      <c r="B169" s="39" t="s">
         <v>234</v>
       </c>
-      <c r="C169" s="31"/>
-      <c r="D169" s="31"/>
-      <c r="E169" s="31">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C169" s="11"/>
+      <c r="D169" s="11"/>
+      <c r="E169" s="11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A170" s="11"/>
       <c r="B170" s="12"/>
       <c r="C170" s="22" t="s">
@@ -10227,7 +10241,7 @@
       </c>
       <c r="E170" s="12"/>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.2">
       <c r="D171">
         <f>-SUM(D164:D170)</f>
         <v>0</v>
@@ -10237,75 +10251,75 @@
         <v>40</v>
       </c>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A172" s="26" t="s">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A172" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="B172" s="27" t="s">
+      <c r="B172" s="37" t="s">
         <v>131</v>
       </c>
-      <c r="C172" s="27"/>
-      <c r="D172" s="27"/>
-      <c r="E172" s="27">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A173" s="26"/>
-      <c r="B173" s="27" t="s">
+      <c r="C172" s="37"/>
+      <c r="D172" s="37"/>
+      <c r="E172" s="37">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A173" s="15"/>
+      <c r="B173" s="37" t="s">
         <v>235</v>
       </c>
-      <c r="C173" s="27"/>
-      <c r="D173" s="27"/>
-      <c r="E173" s="27">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A174" s="26"/>
-      <c r="B174" s="27" t="s">
+      <c r="C173" s="37"/>
+      <c r="D173" s="37"/>
+      <c r="E173" s="37">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A174" s="15"/>
+      <c r="B174" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="C174" s="27"/>
-      <c r="D174" s="27"/>
-      <c r="E174" s="27">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A175" s="26"/>
-      <c r="B175" s="27" t="s">
+      <c r="C174" s="37"/>
+      <c r="D174" s="37"/>
+      <c r="E174" s="37">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A175" s="15"/>
+      <c r="B175" s="37" t="s">
         <v>132</v>
       </c>
-      <c r="C175" s="27"/>
-      <c r="D175" s="27"/>
-      <c r="E175" s="27">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A176" s="26"/>
-      <c r="B176" s="27" t="s">
+      <c r="C175" s="37"/>
+      <c r="D175" s="37"/>
+      <c r="E175" s="37">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A176" s="15"/>
+      <c r="B176" s="37" t="s">
         <v>133</v>
       </c>
-      <c r="C176" s="27"/>
-      <c r="D176" s="27"/>
-      <c r="E176" s="27">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A177" s="26"/>
-      <c r="B177" s="27" t="s">
+      <c r="C176" s="37"/>
+      <c r="D176" s="37"/>
+      <c r="E176" s="37">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A177" s="15"/>
+      <c r="B177" s="37" t="s">
         <v>134</v>
       </c>
-      <c r="C177" s="27"/>
-      <c r="D177" s="27"/>
-      <c r="E177" s="27">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C177" s="37"/>
+      <c r="D177" s="37"/>
+      <c r="E177" s="37">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A178" s="15"/>
       <c r="B178" s="13"/>
       <c r="C178" s="22" t="s">
@@ -10317,7 +10331,7 @@
       </c>
       <c r="E178" s="13"/>
     </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.2">
       <c r="D179">
         <f>-SUM(D172:D178)</f>
         <v>0</v>
@@ -10327,119 +10341,119 @@
         <v>30</v>
       </c>
     </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A180" s="23" t="s">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A180" s="16" t="s">
         <v>135</v>
       </c>
-      <c r="B180" s="24" t="s">
+      <c r="B180" s="38" t="s">
         <v>50</v>
       </c>
-      <c r="C180" s="24"/>
-      <c r="D180" s="24"/>
-      <c r="E180" s="24">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A181" s="23"/>
-      <c r="B181" s="24" t="s">
+      <c r="C180" s="16"/>
+      <c r="D180" s="16"/>
+      <c r="E180" s="16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A181" s="16"/>
+      <c r="B181" s="38" t="s">
         <v>233</v>
       </c>
-      <c r="C181" s="24"/>
-      <c r="D181" s="24"/>
-      <c r="E181" s="24">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A182" s="23"/>
-      <c r="B182" s="24" t="s">
+      <c r="C181" s="16"/>
+      <c r="D181" s="16"/>
+      <c r="E181" s="16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A182" s="16"/>
+      <c r="B182" s="38" t="s">
         <v>136</v>
       </c>
-      <c r="C182" s="24"/>
-      <c r="D182" s="24"/>
-      <c r="E182" s="24">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A183" s="23"/>
-      <c r="B183" s="24" t="s">
+      <c r="C182" s="16"/>
+      <c r="D182" s="16"/>
+      <c r="E182" s="16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A183" s="16"/>
+      <c r="B183" s="38" t="s">
         <v>137</v>
       </c>
-      <c r="C183" s="24"/>
-      <c r="D183" s="24"/>
-      <c r="E183" s="24">
+      <c r="C183" s="16"/>
+      <c r="D183" s="16"/>
+      <c r="E183" s="16">
         <v>10</v>
       </c>
     </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A184" s="23"/>
-      <c r="B184" s="24" t="s">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A184" s="16"/>
+      <c r="B184" s="38" t="s">
         <v>55</v>
       </c>
-      <c r="C184" s="24"/>
-      <c r="D184" s="24"/>
-      <c r="E184" s="24">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A185" s="23"/>
-      <c r="B185" s="24" t="s">
+      <c r="C184" s="16"/>
+      <c r="D184" s="16"/>
+      <c r="E184" s="16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A185" s="16"/>
+      <c r="B185" s="38" t="s">
         <v>54</v>
       </c>
-      <c r="C185" s="24"/>
-      <c r="D185" s="24"/>
-      <c r="E185" s="24">
+      <c r="C185" s="16"/>
+      <c r="D185" s="16"/>
+      <c r="E185" s="16">
         <v>10</v>
       </c>
     </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A186" s="23"/>
-      <c r="B186" s="24" t="s">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A186" s="16"/>
+      <c r="B186" s="38" t="s">
         <v>138</v>
       </c>
-      <c r="C186" s="24"/>
-      <c r="D186" s="24"/>
-      <c r="E186" s="24">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A187" s="23"/>
-      <c r="B187" s="24" t="s">
+      <c r="C186" s="16"/>
+      <c r="D186" s="16"/>
+      <c r="E186" s="16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A187" s="16"/>
+      <c r="B187" s="38" t="s">
         <v>139</v>
       </c>
-      <c r="C187" s="24"/>
-      <c r="D187" s="24"/>
-      <c r="E187" s="24">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A188" s="23"/>
-      <c r="B188" s="24" t="s">
+      <c r="C187" s="16"/>
+      <c r="D187" s="16"/>
+      <c r="E187" s="16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A188" s="16"/>
+      <c r="B188" s="38" t="s">
         <v>140</v>
       </c>
-      <c r="C188" s="24"/>
-      <c r="D188" s="24"/>
-      <c r="E188" s="24">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A189" s="23"/>
-      <c r="B189" s="24" t="s">
+      <c r="C188" s="16"/>
+      <c r="D188" s="16"/>
+      <c r="E188" s="16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A189" s="16"/>
+      <c r="B189" s="38" t="s">
         <v>141</v>
       </c>
-      <c r="C189" s="24"/>
-      <c r="D189" s="24"/>
-      <c r="E189" s="24">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C189" s="16"/>
+      <c r="D189" s="16"/>
+      <c r="E189" s="16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A190" s="16"/>
       <c r="B190" s="14"/>
       <c r="C190" s="22" t="s">
@@ -10451,7 +10465,7 @@
       </c>
       <c r="E190" s="14"/>
     </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.2">
       <c r="D191">
         <f>-SUM(D180:D190)</f>
         <v>0</v>
@@ -10461,7 +10475,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A194" s="7" t="s">
         <v>171</v>
       </c>
@@ -10476,7 +10490,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A195" s="7"/>
       <c r="B195" s="8"/>
       <c r="C195" s="8" t="s">
@@ -10487,7 +10501,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A196" s="7"/>
       <c r="B196" s="8"/>
       <c r="C196" s="8" t="s">
@@ -10498,7 +10512,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A197" s="7"/>
       <c r="B197" s="8" t="s">
         <v>176</v>
@@ -10511,7 +10525,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A198" s="7"/>
       <c r="B198" s="8"/>
       <c r="C198" s="8" t="s">
@@ -10522,7 +10536,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A199" s="7"/>
       <c r="B199" s="8"/>
       <c r="C199" s="8" t="s">
@@ -10533,7 +10547,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A200" s="7"/>
       <c r="B200" s="8"/>
       <c r="C200" s="8" t="s">
@@ -10544,7 +10558,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A201" s="7"/>
       <c r="B201" s="8"/>
       <c r="C201" s="8" t="s">
@@ -10555,7 +10569,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A202" s="7"/>
       <c r="B202" s="8" t="s">
         <v>182</v>
@@ -10566,7 +10580,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A203" s="7"/>
       <c r="B203" s="8" t="s">
         <v>204</v>
@@ -10579,7 +10593,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A204" s="7"/>
       <c r="B204" s="8"/>
       <c r="C204" s="8" t="s">
@@ -10590,7 +10604,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A205" s="7"/>
       <c r="B205" s="8"/>
       <c r="C205" s="8" t="s">
@@ -10601,7 +10615,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A206" s="7"/>
       <c r="B206" s="8"/>
       <c r="C206" s="8" t="s">
@@ -10612,7 +10626,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A207" s="7"/>
       <c r="B207" s="8" t="str">
         <f>Report!B408</f>
@@ -10627,7 +10641,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A208" s="7"/>
       <c r="B208" s="8"/>
       <c r="C208" s="8" t="str">
@@ -10639,7 +10653,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A209" s="7"/>
       <c r="B209" s="8"/>
       <c r="C209" s="8" t="str">
@@ -10651,7 +10665,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A210" s="7"/>
       <c r="B210" s="8"/>
       <c r="C210" s="8" t="str">
@@ -10663,7 +10677,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A211" s="7"/>
       <c r="B211" s="8"/>
       <c r="C211" s="8" t="str">
@@ -10675,7 +10689,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A212" s="7"/>
       <c r="B212" s="8"/>
       <c r="C212" s="22" t="s">
@@ -10687,7 +10701,7 @@
       </c>
       <c r="E212" s="8"/>
     </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:7" x14ac:dyDescent="0.2">
       <c r="D213">
         <f>-SUM(D194:D212)</f>
         <v>0</v>
@@ -10697,7 +10711,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A218" s="7"/>
       <c r="B218" t="s">
         <v>213</v>
@@ -10715,9 +10729,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A219" s="11" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B219" t="s">
         <v>214</v>
@@ -10735,9 +10749,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A220" s="15" t="s">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="B220" t="s">
         <v>215</v>
@@ -10755,9 +10769,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A221" s="16" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B221" t="s">
         <v>216</v>
@@ -10775,7 +10789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="226" spans="4:7" x14ac:dyDescent="0.2">
       <c r="F226" t="s">
         <v>260</v>
       </c>
@@ -10783,7 +10797,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="227" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="227" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D227" t="s">
         <v>262</v>
       </c>
@@ -10791,7 +10805,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="228" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="228" spans="4:7" x14ac:dyDescent="0.2">
       <c r="F228">
         <v>45</v>
       </c>
@@ -10799,7 +10813,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="229" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="229" spans="4:7" x14ac:dyDescent="0.2">
       <c r="F229">
         <f>F228+(F237-F228)/9</f>
         <v>50</v>
@@ -10808,7 +10822,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="230" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="230" spans="4:7" x14ac:dyDescent="0.2">
       <c r="F230">
         <f>F229+(F237-F228)/9</f>
         <v>55</v>
@@ -10817,7 +10831,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="231" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="231" spans="4:7" x14ac:dyDescent="0.2">
       <c r="F231">
         <f>F230+(F237-F228)/9</f>
         <v>60</v>
@@ -10826,7 +10840,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="232" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="232" spans="4:7" x14ac:dyDescent="0.2">
       <c r="F232">
         <f>F231+(F237-F228)/9</f>
         <v>65</v>
@@ -10835,7 +10849,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="233" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="233" spans="4:7" x14ac:dyDescent="0.2">
       <c r="F233">
         <f>F232+(F237-F228)/9</f>
         <v>70</v>
@@ -10844,7 +10858,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="234" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="234" spans="4:7" x14ac:dyDescent="0.2">
       <c r="F234">
         <f>F233+(F237-F228)/9</f>
         <v>75</v>
@@ -10853,7 +10867,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="235" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="235" spans="4:7" x14ac:dyDescent="0.2">
       <c r="F235">
         <f>F234+(F237-F228)/9</f>
         <v>80</v>
@@ -10862,7 +10876,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="236" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="236" spans="4:7" x14ac:dyDescent="0.2">
       <c r="F236">
         <f>F235+(F237-F228)/9</f>
         <v>85</v>
@@ -10871,7 +10885,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="237" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="237" spans="4:7" x14ac:dyDescent="0.2">
       <c r="F237">
         <v>90</v>
       </c>
@@ -10879,16 +10893,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="238" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="238" spans="4:7" x14ac:dyDescent="0.2">
       <c r="E238" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="1047724" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="1047724" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E1047724" s="8"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
+    <mergeCell ref="A96:A125"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A5:C5"/>
   </mergeCells>
@@ -10907,25 +10922,25 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D37"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="35.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.44140625" style="20"/>
+    <col min="2" max="2" width="35.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5" style="20"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A1" s="44" t="s">
+    <row r="1" spans="1:4" ht="26" x14ac:dyDescent="0.3">
+      <c r="A1" s="36" t="s">
         <v>253</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="1"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
         <v>237</v>
       </c>
@@ -10933,7 +10948,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
         <v>42</v>
       </c>
@@ -10941,7 +10956,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
         <v>239</v>
       </c>
@@ -10949,7 +10964,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
         <v>240</v>
       </c>
@@ -10957,7 +10972,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B8" t="s">
         <v>241</v>
       </c>
@@ -10965,7 +10980,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
         <v>242</v>
       </c>
@@ -10973,7 +10988,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
         <v>204</v>
       </c>
@@ -10981,7 +10996,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B11" t="s">
         <v>238</v>
       </c>
@@ -10989,7 +11004,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B12" t="s">
         <v>244</v>
       </c>
@@ -10997,7 +11012,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
         <v>243</v>
       </c>
@@ -11005,7 +11020,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B14" t="s">
         <v>245</v>
       </c>
@@ -11013,7 +11028,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B15" t="s">
         <v>246</v>
       </c>
@@ -11021,7 +11036,7 @@
         <v>-0.3</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
         <v>252</v>
       </c>
@@ -11029,7 +11044,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B17" t="s">
         <v>254</v>
       </c>
@@ -11037,7 +11052,7 @@
         <v>-0.2</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B18" t="s">
         <v>255</v>
       </c>
@@ -11045,7 +11060,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>42</v>
       </c>
@@ -11059,7 +11074,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="C23" t="s">
         <v>174</v>
       </c>
@@ -11067,7 +11082,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="C24" t="s">
         <v>175</v>
       </c>
@@ -11075,7 +11090,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B25" t="s">
         <v>176</v>
       </c>
@@ -11086,7 +11101,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="C26" t="s">
         <v>178</v>
       </c>
@@ -11094,7 +11109,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="C27" t="s">
         <v>179</v>
       </c>
@@ -11102,7 +11117,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="C28" t="s">
         <v>180</v>
       </c>
@@ -11110,12 +11125,12 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B30" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B31" t="s">
         <v>192</v>
       </c>
@@ -11126,7 +11141,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="C32" t="s">
         <v>196</v>
       </c>
@@ -11134,7 +11149,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:4" x14ac:dyDescent="0.2">
       <c r="C33" t="s">
         <v>179</v>
       </c>
@@ -11142,7 +11157,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B34" t="s">
         <v>250</v>
       </c>
@@ -11150,7 +11165,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B35" t="s">
         <v>197</v>
       </c>
@@ -11161,7 +11176,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:4" x14ac:dyDescent="0.2">
       <c r="C36" t="s">
         <v>199</v>
       </c>
@@ -11169,7 +11184,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:4" x14ac:dyDescent="0.2">
       <c r="C37" t="s">
         <v>200</v>
       </c>

--- a/ProjectManagement/EvaluationHWAndProject.xlsx
+++ b/ProjectManagement/EvaluationHWAndProject.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11122"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sid/Documents/GitHub/ML26-03-Car-Licence-Plate-Identification-with-a-Jetson-Nano/ProjectManagement/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\ML26-03-Car-Licence-Plate-Identification-with-a-Jetson-Nano\ProjectManagement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EB73112-5C7D-D247-8157-E9C03D750F7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07C1DF9F-AF02-47B7-8AAF-B207F8925BAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="800" windowWidth="36000" windowHeight="22580" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Report" sheetId="2" r:id="rId1"/>
@@ -274,7 +274,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="886" uniqueCount="404">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="896" uniqueCount="414">
   <si>
     <t>Literature</t>
   </si>
@@ -1486,6 +1486,36 @@
   </si>
   <si>
     <t>Shubhankar Dhumka</t>
+  </si>
+  <si>
+    <t>The "Self-Healing" Watchdog</t>
+  </si>
+  <si>
+    <t>system automatically detects a crash and reboots itself in 3.5 seconds.</t>
+  </si>
+  <si>
+    <t>"Crash-Proof" Database</t>
+  </si>
+  <si>
+    <t>configured SQLite with PRAGMA journal_mode=WAL (Write-Ahead Logging).</t>
+  </si>
+  <si>
+    <t>TensorRT Acceleration</t>
+  </si>
+  <si>
+    <t>used the .engine format for YOLOv8 instead of the standard .pt</t>
+  </si>
+  <si>
+    <t>Input Sanitization Engine (Regex Filters)</t>
+  </si>
+  <si>
+    <t>added a Regular Expression (Regex) layer that strictly enforces the license plate format</t>
+  </si>
+  <si>
+    <t>Filesystem Integrity Protection (Soft Shutdown)</t>
+  </si>
+  <si>
+    <t>added a physical/GUI "Safe Shutdown" button.</t>
   </si>
 </sst>
 </file>
@@ -1700,7 +1730,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1763,23 +1793,12 @@
     <xf numFmtId="0" fontId="20" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="255"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2061,45 +2080,45 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:M575"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.46484375" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.46484375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.1328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.53125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:6" ht="34" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:6" ht="33.4" x14ac:dyDescent="1">
       <c r="A2" s="29" t="s">
         <v>392</v>
       </c>
       <c r="B2" s="29"/>
       <c r="C2" s="29"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" s="30" t="s">
         <v>393</v>
       </c>
       <c r="B6" s="30"/>
       <c r="C6" s="30"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" ht="28.5" x14ac:dyDescent="0.85">
       <c r="A9" s="2" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A10" s="1" t="s">
         <v>84</v>
       </c>
@@ -2116,7 +2135,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>397</v>
       </c>
@@ -2130,10 +2149,10 @@
         <v>400</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
       <c r="C12" s="3"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A14" s="1" t="s">
         <v>88</v>
       </c>
@@ -2141,7 +2160,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A16" s="1" t="s">
         <v>89</v>
       </c>
@@ -2149,7 +2168,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A18" s="1" t="s">
         <v>90</v>
       </c>
@@ -2157,7 +2176,7 @@
         <v>45924</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A19" s="1" t="s">
         <v>91</v>
       </c>
@@ -2165,7 +2184,7 @@
         <v>46051</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A21" s="1" t="s">
         <v>92</v>
       </c>
@@ -2173,7 +2192,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A22" s="1" t="s">
         <v>93</v>
       </c>
@@ -2181,12 +2200,12 @@
         <v>218</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="24" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" ht="23.25" x14ac:dyDescent="0.7">
       <c r="A25" s="6" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="19" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="5" t="s">
         <v>95</v>
       </c>
@@ -2194,7 +2213,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A28" s="13"/>
       <c r="B28" s="13" t="s">
         <v>166</v>
@@ -2211,7 +2230,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A29" s="14"/>
       <c r="B29" s="14" t="s">
         <v>166</v>
@@ -2228,7 +2247,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A30" s="12"/>
       <c r="B30" s="12" t="s">
         <v>166</v>
@@ -2245,7 +2264,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A31" s="12"/>
       <c r="B31" s="12" t="s">
         <v>167</v>
@@ -2262,7 +2281,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A32" s="14"/>
       <c r="B32" s="14" t="s">
         <v>167</v>
@@ -2279,7 +2298,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A33" s="13"/>
       <c r="B33" s="13" t="s">
         <v>167</v>
@@ -2296,12 +2315,12 @@
         <v>391</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" ht="21" x14ac:dyDescent="0.65">
       <c r="A35" s="23" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A36" s="15" t="s">
         <v>0</v>
       </c>
@@ -2311,7 +2330,7 @@
       <c r="E36" s="13"/>
       <c r="F36" s="13"/>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A37" s="15"/>
       <c r="B37" s="13" t="s">
         <v>3</v>
@@ -2323,7 +2342,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A38" s="13"/>
       <c r="B38" s="13" t="s">
         <v>28</v>
@@ -2335,7 +2354,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A39" s="13"/>
       <c r="B39" s="13" t="s">
         <v>4</v>
@@ -2347,7 +2366,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A40" s="13"/>
       <c r="B40" s="13" t="s">
         <v>5</v>
@@ -2359,7 +2378,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A41" s="13"/>
       <c r="B41" s="13" t="s">
         <v>6</v>
@@ -2371,7 +2390,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A42" s="13"/>
       <c r="B42" s="13" t="s">
         <v>1</v>
@@ -2383,7 +2402,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A43" s="15"/>
       <c r="B43" s="13"/>
       <c r="C43" s="13"/>
@@ -2391,7 +2410,7 @@
       <c r="E43" s="13"/>
       <c r="F43" s="13"/>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A44" s="15"/>
       <c r="B44" s="13" t="s">
         <v>2</v>
@@ -2405,7 +2424,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A45" s="13"/>
       <c r="B45" s="13"/>
       <c r="C45" s="13" t="s">
@@ -2417,7 +2436,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A46" s="13"/>
       <c r="B46" s="13"/>
       <c r="C46" s="13" t="s">
@@ -2429,7 +2448,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A47" s="13"/>
       <c r="B47" s="13"/>
       <c r="C47" s="13" t="s">
@@ -2441,7 +2460,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A48" s="13"/>
       <c r="B48" s="13"/>
       <c r="C48" s="13" t="s">
@@ -2453,7 +2472,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A49" s="13"/>
       <c r="B49" s="13"/>
       <c r="C49" s="13" t="s">
@@ -2465,7 +2484,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A50" s="13"/>
       <c r="B50" s="13"/>
       <c r="C50" s="13" t="s">
@@ -2477,7 +2496,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A51" s="13"/>
       <c r="B51" s="13"/>
       <c r="C51" s="13"/>
@@ -2489,7 +2508,7 @@
       </c>
       <c r="F51" s="13"/>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.45">
       <c r="E52">
         <f>SUM(E36:E50)*E51</f>
         <v>0</v>
@@ -2499,12 +2518,12 @@
         <v>100</v>
       </c>
     </row>
-    <row r="54" spans="1:7" s="5" customFormat="1" ht="21" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" s="5" customFormat="1" ht="21" x14ac:dyDescent="0.65">
       <c r="A54" s="23" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A55" s="16" t="s">
         <v>135</v>
       </c>
@@ -2521,7 +2540,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A56" s="16"/>
       <c r="B56" s="14" t="s">
         <v>50</v>
@@ -2534,7 +2553,7 @@
       </c>
       <c r="G56" s="31"/>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A57" s="16"/>
       <c r="B57" s="14" t="s">
         <v>233</v>
@@ -2547,7 +2566,7 @@
       </c>
       <c r="G57" s="31"/>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A58" s="16"/>
       <c r="B58" s="14" t="s">
         <v>136</v>
@@ -2560,7 +2579,7 @@
       </c>
       <c r="G58" s="31"/>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A59" s="16"/>
       <c r="B59" s="14" t="s">
         <v>137</v>
@@ -2573,7 +2592,7 @@
       </c>
       <c r="G59" s="31"/>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A60" s="16"/>
       <c r="B60" s="14" t="s">
         <v>55</v>
@@ -2586,7 +2605,7 @@
       </c>
       <c r="G60" s="31"/>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A61" s="16"/>
       <c r="B61" s="14" t="s">
         <v>54</v>
@@ -2599,7 +2618,7 @@
       </c>
       <c r="G61" s="31"/>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A62" s="16"/>
       <c r="B62" s="14" t="s">
         <v>138</v>
@@ -2612,7 +2631,7 @@
       </c>
       <c r="G62" s="31"/>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A63" s="16"/>
       <c r="B63" s="14" t="s">
         <v>139</v>
@@ -2625,7 +2644,7 @@
       </c>
       <c r="G63" s="31"/>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A64" s="16"/>
       <c r="B64" s="14" t="s">
         <v>140</v>
@@ -2638,7 +2657,7 @@
       </c>
       <c r="G64" s="31"/>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A65" s="16"/>
       <c r="B65" s="14" t="s">
         <v>323</v>
@@ -2651,7 +2670,7 @@
       </c>
       <c r="G65" s="31"/>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A66" s="16"/>
       <c r="B66" s="14" t="s">
         <v>324</v>
@@ -2664,7 +2683,7 @@
       </c>
       <c r="G66" s="31"/>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A67" s="16"/>
       <c r="B67" s="14" t="s">
         <v>141</v>
@@ -2677,7 +2696,7 @@
       </c>
       <c r="G67" s="31"/>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A68" s="16"/>
       <c r="B68" s="14"/>
       <c r="C68" s="14"/>
@@ -2690,7 +2709,7 @@
       <c r="F68" s="14"/>
       <c r="G68" s="31"/>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A69" s="1"/>
       <c r="E69">
         <f>-SUM(E55:E67)*E68</f>
@@ -2701,12 +2720,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="70" spans="1:7" s="5" customFormat="1" ht="19" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" s="5" customFormat="1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" s="5" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A71" s="16" t="s">
         <v>135</v>
       </c>
@@ -2723,7 +2742,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A72" s="16"/>
       <c r="B72" s="14" t="s">
         <v>46</v>
@@ -2736,7 +2755,7 @@
       </c>
       <c r="G72" s="34"/>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A73" s="16"/>
       <c r="B73" s="14" t="s">
         <v>344</v>
@@ -2749,7 +2768,7 @@
       </c>
       <c r="G73" s="34"/>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A74" s="16"/>
       <c r="B74" s="14" t="s">
         <v>70</v>
@@ -2762,7 +2781,7 @@
       </c>
       <c r="G74" s="34"/>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A75" s="16"/>
       <c r="B75" s="14" t="s">
         <v>345</v>
@@ -2775,7 +2794,7 @@
       </c>
       <c r="G75" s="34"/>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A76" s="16"/>
       <c r="B76" s="14" t="s">
         <v>346</v>
@@ -2788,7 +2807,7 @@
       </c>
       <c r="G76" s="34"/>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A77" s="16"/>
       <c r="B77" s="14"/>
       <c r="C77" s="14"/>
@@ -2801,7 +2820,7 @@
       <c r="F77" s="14"/>
       <c r="G77" s="34"/>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A78" s="1"/>
       <c r="E78">
         <f>-SUM(E71:E76)*E77</f>
@@ -2812,15 +2831,15 @@
         <v>40</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A79" s="1"/>
     </row>
-    <row r="80" spans="1:7" ht="19" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" s="5" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A81" s="7" t="s">
         <v>380</v>
       </c>
@@ -2839,7 +2858,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A82" s="7"/>
       <c r="B82" s="7" t="s">
         <v>382</v>
@@ -2854,7 +2873,7 @@
       </c>
       <c r="G82" s="35"/>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A83" s="7"/>
       <c r="B83" s="7"/>
       <c r="C83" s="8" t="s">
@@ -2867,7 +2886,7 @@
       </c>
       <c r="G83" s="35"/>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A84" s="7"/>
       <c r="B84" s="7"/>
       <c r="C84" s="8" t="s">
@@ -2880,7 +2899,7 @@
       </c>
       <c r="G84" s="35"/>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A85" s="7"/>
       <c r="B85" s="7"/>
       <c r="C85" s="7"/>
@@ -2893,7 +2912,7 @@
       <c r="F85" s="7"/>
       <c r="G85" s="35"/>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="E86">
@@ -2905,15 +2924,15 @@
         <v>50</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A87" s="1"/>
     </row>
-    <row r="88" spans="1:7" ht="21" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:7" ht="21" x14ac:dyDescent="0.65">
       <c r="A88" s="23" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A89" s="15" t="s">
         <v>317</v>
       </c>
@@ -2927,7 +2946,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A90" s="15"/>
       <c r="B90" s="13" t="s">
         <v>131</v>
@@ -2939,7 +2958,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A91" s="15"/>
       <c r="B91" s="13" t="s">
         <v>235</v>
@@ -2951,7 +2970,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A92" s="15"/>
       <c r="B92" s="13" t="s">
         <v>8</v>
@@ -2963,7 +2982,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A93" s="15"/>
       <c r="B93" s="13" t="s">
         <v>132</v>
@@ -2975,7 +2994,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A94" s="15"/>
       <c r="B94" s="13" t="s">
         <v>133</v>
@@ -2987,7 +3006,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A95" s="15"/>
       <c r="B95" s="13" t="s">
         <v>134</v>
@@ -2999,7 +3018,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A96" s="15"/>
       <c r="B96" s="13"/>
       <c r="C96" s="13"/>
@@ -3011,7 +3030,7 @@
       </c>
       <c r="F96" s="13"/>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A97" s="1"/>
       <c r="E97">
         <f>SUM(E89:E95)*E96</f>
@@ -3022,18 +3041,18 @@
         <v>40</v>
       </c>
     </row>
-    <row r="98" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="99" spans="1:6" ht="21" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="99" spans="1:6" ht="21" x14ac:dyDescent="0.65">
       <c r="A99" s="23" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="100" spans="1:6" ht="19" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A100" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A101" s="15" t="s">
         <v>7</v>
       </c>
@@ -3047,7 +3066,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A102" s="13"/>
       <c r="B102" s="13" t="s">
         <v>9</v>
@@ -3059,7 +3078,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A103" s="13"/>
       <c r="B103" s="13" t="s">
         <v>10</v>
@@ -3071,7 +3090,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A104" s="13"/>
       <c r="B104" s="13" t="s">
         <v>11</v>
@@ -3083,7 +3102,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A105" s="13"/>
       <c r="B105" s="13" t="s">
         <v>12</v>
@@ -3095,7 +3114,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A106" s="13"/>
       <c r="B106" s="13" t="s">
         <v>100</v>
@@ -3107,7 +3126,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A107" s="13"/>
       <c r="B107" s="13"/>
       <c r="C107" s="13"/>
@@ -3119,7 +3138,7 @@
       </c>
       <c r="F107" s="13"/>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.45">
       <c r="E108">
         <f>SUM(E101:E106)*E107</f>
         <v>0</v>
@@ -3129,12 +3148,12 @@
         <v>35</v>
       </c>
     </row>
-    <row r="110" spans="1:6" ht="19" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A110" s="5" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A111" s="16" t="s">
         <v>275</v>
       </c>
@@ -3148,7 +3167,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A112" s="16"/>
       <c r="B112" s="14" t="s">
         <v>14</v>
@@ -3160,7 +3179,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A113" s="14"/>
       <c r="B113" s="14" t="s">
         <v>15</v>
@@ -3172,7 +3191,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A114" s="14"/>
       <c r="B114" s="14" t="s">
         <v>16</v>
@@ -3184,7 +3203,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A115" s="14"/>
       <c r="B115" s="14" t="s">
         <v>17</v>
@@ -3196,7 +3215,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A116" s="14"/>
       <c r="B116" s="14" t="s">
         <v>18</v>
@@ -3208,7 +3227,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A117" s="14"/>
       <c r="B117" s="14" t="s">
         <v>20</v>
@@ -3220,7 +3239,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="118" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A118" s="14"/>
       <c r="B118" s="24" t="s">
         <v>19</v>
@@ -3232,7 +3251,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A119" s="14"/>
       <c r="B119" s="24"/>
       <c r="C119" s="14"/>
@@ -3244,7 +3263,7 @@
       </c>
       <c r="F119" s="14"/>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.45">
       <c r="E120">
         <f>SUM(E111:E118)*E119</f>
         <v>0</v>
@@ -3254,12 +3273,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="123" spans="1:7" ht="19" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:7" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A123" s="5" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A124" s="11" t="s">
         <v>335</v>
       </c>
@@ -3280,7 +3299,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A125" s="11" t="s">
         <v>330</v>
       </c>
@@ -3299,7 +3318,7 @@
       </c>
       <c r="G125" s="32"/>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A126" s="12"/>
       <c r="B126" s="12"/>
       <c r="C126" s="12"/>
@@ -3314,7 +3333,7 @@
       </c>
       <c r="G126" s="32"/>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A127" s="12"/>
       <c r="B127" s="12"/>
       <c r="C127" s="12" t="s">
@@ -3329,7 +3348,7 @@
       </c>
       <c r="G127" s="32"/>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A128" s="12"/>
       <c r="B128" s="12"/>
       <c r="C128" s="12" t="s">
@@ -3344,7 +3363,7 @@
       </c>
       <c r="G128" s="32"/>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A129" s="12"/>
       <c r="B129" s="12"/>
       <c r="C129" s="12" t="s">
@@ -3359,7 +3378,7 @@
       </c>
       <c r="G129" s="32"/>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A130" s="12"/>
       <c r="B130" s="12"/>
       <c r="C130" s="12"/>
@@ -3372,7 +3391,7 @@
       <c r="F130" s="12"/>
       <c r="G130" s="32"/>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.45">
       <c r="E131">
         <f>SUM(E124:E129)*E130</f>
         <v>0</v>
@@ -3383,7 +3402,7 @@
       </c>
       <c r="G131" s="32"/>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A132" s="11" t="s">
         <v>276</v>
       </c>
@@ -3402,7 +3421,7 @@
       </c>
       <c r="G132" s="32"/>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A133" s="12"/>
       <c r="B133" s="12"/>
       <c r="C133" s="12" t="s">
@@ -3419,7 +3438,7 @@
       </c>
       <c r="G133" s="32"/>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A134" s="12"/>
       <c r="B134" s="12"/>
       <c r="C134" s="12"/>
@@ -3434,7 +3453,7 @@
       </c>
       <c r="G134" s="32"/>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A135" s="11"/>
       <c r="B135" s="12"/>
       <c r="C135" s="12"/>
@@ -3449,7 +3468,7 @@
       </c>
       <c r="G135" s="32"/>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A136" s="11"/>
       <c r="B136" s="12"/>
       <c r="C136" s="12"/>
@@ -3464,7 +3483,7 @@
       </c>
       <c r="G136" s="32"/>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A137" s="11"/>
       <c r="B137" s="12"/>
       <c r="C137" s="12" t="s">
@@ -3479,7 +3498,7 @@
       </c>
       <c r="G137" s="32"/>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A138" s="12"/>
       <c r="B138" s="12"/>
       <c r="C138" s="12" t="s">
@@ -3494,7 +3513,7 @@
       </c>
       <c r="G138" s="32"/>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A139" s="12"/>
       <c r="B139" s="12"/>
       <c r="C139" s="12" t="s">
@@ -3509,7 +3528,7 @@
       </c>
       <c r="G139" s="32"/>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A140" s="12"/>
       <c r="B140" s="12"/>
       <c r="C140" s="12"/>
@@ -3522,7 +3541,7 @@
       <c r="F140" s="12"/>
       <c r="G140" s="32"/>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.45">
       <c r="E141">
         <f>SUM(E132:E139)*E140</f>
         <v>0</v>
@@ -3533,7 +3552,7 @@
       </c>
       <c r="G141" s="32"/>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A142" s="11" t="s">
         <v>333</v>
       </c>
@@ -3552,7 +3571,7 @@
       </c>
       <c r="G142" s="32"/>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A143" s="11" t="s">
         <v>334</v>
       </c>
@@ -3567,7 +3586,7 @@
       </c>
       <c r="G143" s="32"/>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A144" s="11"/>
       <c r="B144" s="12"/>
       <c r="C144" s="12" t="s">
@@ -3580,7 +3599,7 @@
       </c>
       <c r="G144" s="32"/>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A145" s="11"/>
       <c r="B145" s="12"/>
       <c r="C145" s="12" t="s">
@@ -3597,7 +3616,7 @@
       </c>
       <c r="G145" s="32"/>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A146" s="12"/>
       <c r="B146" s="12"/>
       <c r="C146" s="12"/>
@@ -3612,7 +3631,7 @@
       </c>
       <c r="G146" s="32"/>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A147" s="12"/>
       <c r="B147" s="12"/>
       <c r="C147" s="12" t="s">
@@ -3627,7 +3646,7 @@
       </c>
       <c r="G147" s="32"/>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A148" s="12"/>
       <c r="B148" s="12"/>
       <c r="C148" s="12" t="s">
@@ -3642,7 +3661,7 @@
       </c>
       <c r="G148" s="32"/>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A149" s="12"/>
       <c r="B149" s="12"/>
       <c r="C149" s="12" t="s">
@@ -3657,7 +3676,7 @@
       </c>
       <c r="G149" s="32"/>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A150" s="12"/>
       <c r="B150" s="12"/>
       <c r="C150" s="12"/>
@@ -3670,7 +3689,7 @@
       <c r="F150" s="12"/>
       <c r="G150" s="32"/>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.45">
       <c r="E151">
         <f>SUM(E142:E149)*E150</f>
         <v>0</v>
@@ -3681,7 +3700,7 @@
       </c>
       <c r="G151" s="32"/>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A152" s="11" t="s">
         <v>338</v>
       </c>
@@ -3700,7 +3719,7 @@
       </c>
       <c r="G152" s="32"/>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A153" s="12"/>
       <c r="B153" s="12"/>
       <c r="C153" s="12" t="s">
@@ -3717,7 +3736,7 @@
       </c>
       <c r="G153" s="32"/>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A154" s="12"/>
       <c r="B154" s="12"/>
       <c r="C154" s="12"/>
@@ -3732,7 +3751,7 @@
       </c>
       <c r="G154" s="32"/>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A155" s="11"/>
       <c r="B155" s="12"/>
       <c r="C155" s="12"/>
@@ -3747,7 +3766,7 @@
       </c>
       <c r="G155" s="32"/>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A156" s="11"/>
       <c r="B156" s="12"/>
       <c r="C156" s="12"/>
@@ -3762,7 +3781,7 @@
       </c>
       <c r="G156" s="32"/>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A157" s="11"/>
       <c r="B157" s="12"/>
       <c r="C157" s="12" t="s">
@@ -3775,7 +3794,7 @@
       </c>
       <c r="G157" s="32"/>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A158" s="11"/>
       <c r="B158" s="12"/>
       <c r="C158" s="12" t="s">
@@ -3790,7 +3809,7 @@
       </c>
       <c r="G158" s="32"/>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A159" s="12"/>
       <c r="B159" s="12"/>
       <c r="C159" s="12" t="s">
@@ -3805,7 +3824,7 @@
       </c>
       <c r="G159" s="32"/>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A160" s="12"/>
       <c r="B160" s="12"/>
       <c r="C160" s="12" t="s">
@@ -3820,7 +3839,7 @@
       </c>
       <c r="G160" s="32"/>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A161" s="12"/>
       <c r="B161" s="12"/>
       <c r="C161" s="12"/>
@@ -3833,7 +3852,7 @@
       <c r="F161" s="12"/>
       <c r="G161" s="32"/>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.45">
       <c r="E162">
         <f>SUM(E152:E160)*E161</f>
         <v>0</v>
@@ -3844,10 +3863,10 @@
       </c>
       <c r="G162" s="32"/>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.45">
       <c r="G163" s="27"/>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A164" s="16" t="s">
         <v>125</v>
       </c>
@@ -3863,7 +3882,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A165" s="16"/>
       <c r="B165" s="14"/>
       <c r="C165" s="14" t="s">
@@ -3875,7 +3894,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A166" s="16"/>
       <c r="B166" s="14"/>
       <c r="C166" s="14" t="s">
@@ -3887,7 +3906,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A167" s="16"/>
       <c r="B167" s="14"/>
       <c r="C167" s="14"/>
@@ -3899,7 +3918,7 @@
       </c>
       <c r="F167" s="14"/>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A168" s="1"/>
       <c r="E168">
         <f>-SUM(E164:E166)*E167</f>
@@ -3910,7 +3929,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A169" s="16" t="s">
         <v>125</v>
       </c>
@@ -3926,7 +3945,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A170" s="16"/>
       <c r="B170" s="14"/>
       <c r="C170" s="14" t="s">
@@ -3938,7 +3957,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A171" s="16"/>
       <c r="B171" s="14"/>
       <c r="C171" s="14" t="s">
@@ -3950,7 +3969,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A172" s="16"/>
       <c r="B172" s="14"/>
       <c r="C172" s="14" t="s">
@@ -3962,7 +3981,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A173" s="16"/>
       <c r="B173" s="14"/>
       <c r="C173" s="14" t="s">
@@ -3974,7 +3993,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A174" s="16"/>
       <c r="B174" s="14"/>
       <c r="C174" s="14"/>
@@ -3986,7 +4005,7 @@
       </c>
       <c r="F174" s="14"/>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A175" s="1"/>
       <c r="E175">
         <f>-SUM(E169:E173)*E174</f>
@@ -3997,7 +4016,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A176" s="16" t="s">
         <v>339</v>
       </c>
@@ -4015,7 +4034,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A177" s="16" t="s">
         <v>340</v>
       </c>
@@ -4029,7 +4048,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A178" s="16"/>
       <c r="B178" s="14"/>
       <c r="C178" s="14" t="s">
@@ -4041,7 +4060,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A179" s="16"/>
       <c r="B179" s="14"/>
       <c r="C179" s="14" t="s">
@@ -4053,7 +4072,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A180" s="16"/>
       <c r="B180" s="14"/>
       <c r="C180" s="14" t="s">
@@ -4065,7 +4084,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A181" s="16"/>
       <c r="B181" s="14"/>
       <c r="C181" s="14" t="s">
@@ -4081,7 +4100,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A182" s="14"/>
       <c r="B182" s="14"/>
       <c r="C182" s="14"/>
@@ -4095,7 +4114,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A183" s="14"/>
       <c r="B183" s="14"/>
       <c r="C183" s="14" t="s">
@@ -4109,7 +4128,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A184" s="14"/>
       <c r="B184" s="14"/>
       <c r="C184" s="14" t="s">
@@ -4123,7 +4142,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A185" s="14"/>
       <c r="B185" s="14"/>
       <c r="C185" s="14" t="s">
@@ -4137,7 +4156,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A186" s="14"/>
       <c r="B186" s="14"/>
       <c r="C186" s="14"/>
@@ -4149,7 +4168,7 @@
       </c>
       <c r="F186" s="14"/>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.45">
       <c r="E187">
         <f>SUM(E176:E185)*E186</f>
         <v>0</v>
@@ -4159,7 +4178,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A188" s="16" t="s">
         <v>339</v>
       </c>
@@ -4177,7 +4196,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A189" s="14" t="s">
         <v>340</v>
       </c>
@@ -4191,7 +4210,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A190" s="16"/>
       <c r="B190" s="14"/>
       <c r="C190" s="14" t="s">
@@ -4203,7 +4222,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A191" s="14"/>
       <c r="B191" s="14"/>
       <c r="C191" s="14" t="s">
@@ -4219,7 +4238,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A192" s="14"/>
       <c r="B192" s="14"/>
       <c r="C192" s="14"/>
@@ -4233,7 +4252,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A193" s="16"/>
       <c r="B193" s="14"/>
       <c r="C193" s="14"/>
@@ -4247,7 +4266,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A194" s="16"/>
       <c r="B194" s="14"/>
       <c r="C194" s="14"/>
@@ -4261,7 +4280,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A195" s="14"/>
       <c r="B195" s="14"/>
       <c r="C195" s="14" t="s">
@@ -4275,7 +4294,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A196" s="14"/>
       <c r="B196" s="14"/>
       <c r="C196" s="14" t="s">
@@ -4289,7 +4308,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A197" s="14"/>
       <c r="B197" s="14"/>
       <c r="C197" s="14"/>
@@ -4301,7 +4320,7 @@
       </c>
       <c r="F197" s="14"/>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.45">
       <c r="E198">
         <f>SUM(E188:E196)*E197</f>
         <v>0</v>
@@ -4311,7 +4330,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A199" s="16" t="s">
         <v>342</v>
       </c>
@@ -4325,7 +4344,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A200" s="16"/>
       <c r="B200" s="14" t="s">
         <v>127</v>
@@ -4337,7 +4356,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A201" s="16"/>
       <c r="B201" s="14" t="s">
         <v>124</v>
@@ -4349,7 +4368,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A202" s="16"/>
       <c r="B202" s="14"/>
       <c r="C202" s="14"/>
@@ -4361,7 +4380,7 @@
       </c>
       <c r="F202" s="14"/>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A203" s="1"/>
       <c r="E203">
         <f>SUM(E199:E201)*E202</f>
@@ -4372,15 +4391,15 @@
         <v>60</v>
       </c>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A204" s="1"/>
     </row>
-    <row r="205" spans="1:9" s="5" customFormat="1" ht="19" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:9" s="5" customFormat="1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A205" s="5" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A206" s="1" t="s">
         <v>62</v>
       </c>
@@ -4397,7 +4416,7 @@
       </c>
       <c r="I206" s="1"/>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A207" s="1"/>
       <c r="B207" s="12"/>
       <c r="C207" s="12" t="s">
@@ -4409,7 +4428,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A208" s="1"/>
       <c r="B208" s="12"/>
       <c r="C208" s="12" t="s">
@@ -4421,7 +4440,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A209" s="1"/>
       <c r="B209" s="12"/>
       <c r="C209" s="12" t="s">
@@ -4433,7 +4452,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A210" s="1"/>
       <c r="B210" s="12"/>
       <c r="C210" s="12" t="s">
@@ -4445,7 +4464,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A211" s="1"/>
       <c r="B211" s="12"/>
       <c r="C211" s="12" t="s">
@@ -4457,7 +4476,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A212" s="1"/>
       <c r="B212" s="12"/>
       <c r="C212" s="12" t="s">
@@ -4469,7 +4488,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A213" s="1"/>
       <c r="B213" s="12"/>
       <c r="C213" s="12" t="s">
@@ -4481,7 +4500,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A214" s="1"/>
       <c r="B214" s="12"/>
       <c r="C214" s="12"/>
@@ -4493,7 +4512,7 @@
       </c>
       <c r="F214" s="12"/>
     </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A215" s="1"/>
       <c r="E215">
         <f>-SUM(E206:E213)*E214</f>
@@ -4504,7 +4523,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A216" s="1"/>
       <c r="B216" s="13" t="s">
         <v>63</v>
@@ -4518,7 +4537,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A217" s="1"/>
       <c r="B217" s="13"/>
       <c r="C217" s="13" t="s">
@@ -4530,7 +4549,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A218" s="1"/>
       <c r="B218" s="13"/>
       <c r="C218" s="13" t="s">
@@ -4542,7 +4561,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A219" s="1"/>
       <c r="B219" s="13"/>
       <c r="C219" s="13" t="s">
@@ -4554,7 +4573,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A220" s="1"/>
       <c r="B220" s="13"/>
       <c r="C220" s="13" t="s">
@@ -4566,7 +4585,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A221" s="1"/>
       <c r="B221" s="13"/>
       <c r="C221" s="13" t="s">
@@ -4578,7 +4597,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A222" s="1"/>
       <c r="B222" s="13"/>
       <c r="C222" s="13" t="s">
@@ -4590,7 +4609,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A223" s="1"/>
       <c r="B223" s="13"/>
       <c r="C223" s="13" t="s">
@@ -4602,7 +4621,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A224" s="1"/>
       <c r="B224" s="13"/>
       <c r="C224" s="13"/>
@@ -4614,7 +4633,7 @@
       </c>
       <c r="F224" s="13"/>
     </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A225" s="1"/>
       <c r="E225">
         <f>-SUM(E216:E223)*E224</f>
@@ -4625,7 +4644,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A226" s="1"/>
       <c r="B226" s="14" t="s">
         <v>63</v>
@@ -4639,7 +4658,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A227" s="1"/>
       <c r="B227" s="14"/>
       <c r="C227" s="14" t="s">
@@ -4651,7 +4670,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A228" s="1"/>
       <c r="B228" s="14"/>
       <c r="C228" s="14" t="s">
@@ -4663,7 +4682,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A229" s="1"/>
       <c r="B229" s="14"/>
       <c r="C229" s="14" t="s">
@@ -4675,7 +4694,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A230" s="1"/>
       <c r="B230" s="14"/>
       <c r="C230" s="14" t="s">
@@ -4687,7 +4706,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A231" s="1"/>
       <c r="B231" s="14"/>
       <c r="C231" s="14" t="s">
@@ -4699,7 +4718,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A232" s="1"/>
       <c r="B232" s="14"/>
       <c r="C232" s="14" t="s">
@@ -4711,7 +4730,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A233" s="1"/>
       <c r="B233" s="14"/>
       <c r="C233" s="14" t="s">
@@ -4723,7 +4742,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A234" s="1"/>
       <c r="B234" s="14"/>
       <c r="C234" s="14"/>
@@ -4735,7 +4754,7 @@
       </c>
       <c r="F234" s="14"/>
     </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A235" s="1"/>
       <c r="E235">
         <f>-SUM(E226:E233)*E234</f>
@@ -4746,7 +4765,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A236" s="15" t="s">
         <v>277</v>
       </c>
@@ -4762,7 +4781,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A237" s="13"/>
       <c r="B237" s="13"/>
       <c r="C237" s="13" t="s">
@@ -4774,7 +4793,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A238" s="13"/>
       <c r="B238" s="13"/>
       <c r="C238" s="13" t="s">
@@ -4786,7 +4805,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A239" s="13"/>
       <c r="B239" s="13"/>
       <c r="C239" s="13" t="s">
@@ -4798,7 +4817,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A240" s="13"/>
       <c r="B240" s="13"/>
       <c r="C240" s="13" t="s">
@@ -4810,7 +4829,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A241" s="13"/>
       <c r="B241" s="13"/>
       <c r="C241" s="13" t="s">
@@ -4822,7 +4841,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A242" s="13"/>
       <c r="B242" s="13"/>
       <c r="C242" s="13" t="s">
@@ -4834,7 +4853,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A243" s="13"/>
       <c r="B243" s="13"/>
       <c r="C243" s="13" t="s">
@@ -4846,7 +4865,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A244" s="15"/>
       <c r="B244" s="13"/>
       <c r="C244" s="13" t="s">
@@ -4858,7 +4877,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A245" s="13"/>
       <c r="B245" s="13"/>
       <c r="C245" s="13"/>
@@ -4870,7 +4889,7 @@
       </c>
       <c r="F245" s="13"/>
     </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A246" s="25"/>
       <c r="B246" s="25"/>
       <c r="C246" s="25"/>
@@ -4884,7 +4903,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A247" s="25"/>
       <c r="B247" s="25"/>
       <c r="C247" s="25"/>
@@ -4892,12 +4911,12 @@
       <c r="E247" s="25"/>
       <c r="F247" s="25"/>
     </row>
-    <row r="248" spans="1:6" ht="19" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:6" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A248" s="5" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A249" s="11" t="s">
         <v>206</v>
       </c>
@@ -4911,7 +4930,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A250" s="11" t="s">
         <v>325</v>
       </c>
@@ -4925,7 +4944,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A251" s="11"/>
       <c r="B251" s="12" t="s">
         <v>50</v>
@@ -4937,7 +4956,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A252" s="11"/>
       <c r="B252" s="12" t="s">
         <v>207</v>
@@ -4949,7 +4968,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A253" s="11"/>
       <c r="B253" s="12" t="s">
         <v>51</v>
@@ -4961,7 +4980,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A254" s="11"/>
       <c r="B254" s="12" t="s">
         <v>234</v>
@@ -4973,7 +4992,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A255" s="11"/>
       <c r="B255" s="12"/>
       <c r="C255" s="12"/>
@@ -4985,7 +5004,7 @@
       </c>
       <c r="F255" s="12"/>
     </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A256" s="1"/>
       <c r="E256">
         <f>SUM(E249:E254)*E255</f>
@@ -4996,7 +5015,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A257" s="11" t="s">
         <v>386</v>
       </c>
@@ -5013,7 +5032,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A258" s="11" t="s">
         <v>327</v>
       </c>
@@ -5028,7 +5047,7 @@
       </c>
       <c r="G258" s="33"/>
     </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A259" s="11" t="s">
         <v>326</v>
       </c>
@@ -5043,7 +5062,7 @@
       </c>
       <c r="G259" s="33"/>
     </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A260" s="11"/>
       <c r="B260" s="12"/>
       <c r="C260" s="12" t="s">
@@ -5056,7 +5075,7 @@
       </c>
       <c r="G260" s="33"/>
     </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A261" s="11"/>
       <c r="B261" s="12"/>
       <c r="C261" s="12" t="s">
@@ -5069,7 +5088,7 @@
       </c>
       <c r="G261" s="33"/>
     </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A262" s="11"/>
       <c r="B262" s="12"/>
       <c r="C262" s="12" t="s">
@@ -5082,7 +5101,7 @@
       </c>
       <c r="G262" s="33"/>
     </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A263" s="11"/>
       <c r="B263" s="12"/>
       <c r="C263" s="12"/>
@@ -5095,7 +5114,7 @@
       <c r="F263" s="12"/>
       <c r="G263" s="33"/>
     </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A264" s="1"/>
       <c r="E264">
         <f>SUM(E257:E262)*E263</f>
@@ -5106,12 +5125,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="265" spans="1:7" ht="19" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:7" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A265" s="5" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A266" s="7" t="s">
         <v>29</v>
       </c>
@@ -5123,7 +5142,7 @@
       <c r="E266" s="8"/>
       <c r="F266" s="8"/>
     </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A267" s="8"/>
       <c r="B267" s="8"/>
       <c r="C267" s="8" t="s">
@@ -5135,7 +5154,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="268" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A268" s="8"/>
       <c r="B268" s="8"/>
       <c r="C268" s="8" t="s">
@@ -5145,7 +5164,7 @@
       <c r="E268" s="8"/>
       <c r="F268" s="8"/>
     </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A269" s="8"/>
       <c r="B269" s="8"/>
       <c r="C269" s="8" t="s">
@@ -5155,7 +5174,7 @@
       <c r="E269" s="8"/>
       <c r="F269" s="8"/>
     </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A270" s="8"/>
       <c r="B270" s="8"/>
       <c r="C270" s="8" t="s">
@@ -5167,12 +5186,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="272" spans="1:7" ht="19" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:7" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A272" s="5" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A273" s="12" t="s">
         <v>75</v>
       </c>
@@ -5190,7 +5209,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A274" s="12"/>
       <c r="B274" s="12"/>
       <c r="C274" s="12"/>
@@ -5202,7 +5221,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A275" s="12"/>
       <c r="B275" s="12"/>
       <c r="C275" s="12"/>
@@ -5214,7 +5233,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A276" s="12"/>
       <c r="B276" s="12"/>
       <c r="C276" s="12"/>
@@ -5226,7 +5245,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A277" s="12"/>
       <c r="B277" s="12"/>
       <c r="C277" s="12"/>
@@ -5238,7 +5257,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A278" s="12"/>
       <c r="B278" s="12"/>
       <c r="C278" s="12"/>
@@ -5250,7 +5269,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A279" s="12"/>
       <c r="B279" s="12"/>
       <c r="C279" s="12" t="s">
@@ -5264,7 +5283,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A280" s="12"/>
       <c r="B280" s="12"/>
       <c r="C280" s="12"/>
@@ -5276,7 +5295,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A281" s="12"/>
       <c r="B281" s="12"/>
       <c r="C281" s="12"/>
@@ -5288,7 +5307,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A282" s="12"/>
       <c r="B282" s="12"/>
       <c r="C282" s="12"/>
@@ -5300,7 +5319,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="283" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A283" s="12"/>
       <c r="B283" s="12"/>
       <c r="C283" s="12"/>
@@ -5312,7 +5331,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="284" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A284" s="12"/>
       <c r="B284" s="12"/>
       <c r="C284" s="12"/>
@@ -5324,7 +5343,7 @@
       </c>
       <c r="F284" s="12"/>
     </row>
-    <row r="285" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:6" x14ac:dyDescent="0.45">
       <c r="E285">
         <f>SUM(E273:E283)*E284</f>
         <v>0</v>
@@ -5334,7 +5353,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="286" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A286" s="7" t="s">
         <v>293</v>
       </c>
@@ -5348,7 +5367,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="287" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A287" s="8"/>
       <c r="B287" s="8" t="s">
         <v>21</v>
@@ -5362,7 +5381,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="288" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A288" s="8"/>
       <c r="B288" s="8"/>
       <c r="C288" s="8" t="s">
@@ -5374,7 +5393,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="289" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A289" s="8"/>
       <c r="B289" s="8"/>
       <c r="C289" s="8" t="s">
@@ -5386,7 +5405,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="290" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A290" s="8"/>
       <c r="B290" s="8"/>
       <c r="C290" s="8" t="s">
@@ -5398,7 +5417,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="291" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A291" s="8"/>
       <c r="B291" s="8"/>
       <c r="C291" s="8" t="s">
@@ -5410,7 +5429,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="292" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A292" s="8"/>
       <c r="B292" s="8"/>
       <c r="C292" s="8" t="s">
@@ -5422,7 +5441,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="293" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A293" s="8"/>
       <c r="B293" s="8"/>
       <c r="C293" s="8"/>
@@ -5434,7 +5453,7 @@
       </c>
       <c r="F293" s="8"/>
     </row>
-    <row r="294" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:6" x14ac:dyDescent="0.45">
       <c r="E294">
         <f>SUM(E286:E292)*E293</f>
         <v>0</v>
@@ -5444,7 +5463,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="296" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A296" s="7" t="s">
         <v>299</v>
       </c>
@@ -5458,7 +5477,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="297" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A297" s="7" t="s">
         <v>301</v>
       </c>
@@ -5472,7 +5491,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="298" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A298" s="8"/>
       <c r="B298" s="8" t="s">
         <v>303</v>
@@ -5484,7 +5503,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="299" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A299" s="8"/>
       <c r="B299" s="8" t="s">
         <v>304</v>
@@ -5496,7 +5515,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="300" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A300" s="8"/>
       <c r="B300" s="8"/>
       <c r="C300" s="8"/>
@@ -5508,7 +5527,7 @@
       </c>
       <c r="F300" s="8"/>
     </row>
-    <row r="301" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:6" x14ac:dyDescent="0.45">
       <c r="E301">
         <f>SUM(E296:E299)*E300</f>
         <v>0</v>
@@ -5518,7 +5537,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="303" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A303" s="16" t="s">
         <v>305</v>
       </c>
@@ -5532,7 +5551,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="304" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A304" s="14"/>
       <c r="B304" s="14" t="s">
         <v>307</v>
@@ -5544,7 +5563,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="305" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A305" s="14"/>
       <c r="B305" s="14" t="s">
         <v>134</v>
@@ -5556,7 +5575,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="306" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A306" s="16" t="s">
         <v>308</v>
       </c>
@@ -5570,7 +5589,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="307" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A307" s="14"/>
       <c r="B307" s="14" t="s">
         <v>310</v>
@@ -5582,7 +5601,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="308" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A308" s="16" t="s">
         <v>359</v>
       </c>
@@ -5598,7 +5617,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="309" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A309" s="14"/>
       <c r="B309" s="14"/>
       <c r="C309" s="14" t="s">
@@ -5610,7 +5629,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="310" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A310" s="14"/>
       <c r="B310" s="14"/>
       <c r="C310" s="14" t="s">
@@ -5622,7 +5641,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="311" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A311" s="14"/>
       <c r="B311" s="14"/>
       <c r="C311" s="14"/>
@@ -5634,7 +5653,7 @@
       </c>
       <c r="F311" s="14"/>
     </row>
-    <row r="312" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:6" x14ac:dyDescent="0.45">
       <c r="E312">
         <f>SUM(E303:E310)*E311</f>
         <v>0</v>
@@ -5644,7 +5663,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="313" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A313" s="11" t="s">
         <v>35</v>
       </c>
@@ -5658,7 +5677,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="314" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A314" s="12"/>
       <c r="B314" s="12" t="s">
         <v>251</v>
@@ -5670,7 +5689,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="315" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A315" s="11"/>
       <c r="B315" s="12" t="s">
         <v>320</v>
@@ -5684,7 +5703,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="316" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A316" s="12"/>
       <c r="B316" s="12" t="s">
         <v>312</v>
@@ -5698,7 +5717,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="317" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A317" s="11"/>
       <c r="B317" s="12" t="s">
         <v>230</v>
@@ -5712,7 +5731,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="318" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A318" s="11"/>
       <c r="B318" s="12" t="s">
         <v>321</v>
@@ -5726,7 +5745,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="319" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A319" s="11"/>
       <c r="B319" s="12" t="s">
         <v>322</v>
@@ -5738,7 +5757,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="320" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A320" s="12"/>
       <c r="B320" s="12" t="s">
         <v>313</v>
@@ -5750,7 +5769,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="321" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A321" s="12"/>
       <c r="B321" s="12" t="s">
         <v>314</v>
@@ -5762,7 +5781,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="322" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A322" s="12"/>
       <c r="B322" s="12" t="s">
         <v>40</v>
@@ -5774,7 +5793,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="323" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A323" s="12"/>
       <c r="B323" s="12"/>
       <c r="C323" s="12"/>
@@ -5786,7 +5805,7 @@
       </c>
       <c r="F323" s="12"/>
     </row>
-    <row r="324" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:6" x14ac:dyDescent="0.45">
       <c r="E324">
         <f>SUM(E313:E322)*E323</f>
         <v>0</v>
@@ -5796,7 +5815,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="326" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A326" s="7" t="s">
         <v>347</v>
       </c>
@@ -5810,7 +5829,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="327" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A327" s="7"/>
       <c r="B327" s="8" t="s">
         <v>191</v>
@@ -5822,7 +5841,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="328" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A328" s="7"/>
       <c r="B328" s="8" t="s">
         <v>192</v>
@@ -5836,7 +5855,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="329" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A329" s="7"/>
       <c r="B329" s="8"/>
       <c r="C329" s="8" t="s">
@@ -5848,7 +5867,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="330" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A330" s="7"/>
       <c r="B330" s="8"/>
       <c r="C330" s="8" t="s">
@@ -5860,7 +5879,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="331" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A331" s="7"/>
       <c r="B331" s="8"/>
       <c r="C331" s="8" t="s">
@@ -5872,7 +5891,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="332" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A332" s="7"/>
       <c r="B332" s="8"/>
       <c r="C332" s="8" t="s">
@@ -5884,7 +5903,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="333" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A333" s="7"/>
       <c r="B333" s="8"/>
       <c r="C333" s="8"/>
@@ -5896,7 +5915,7 @@
       </c>
       <c r="F333" s="8"/>
     </row>
-    <row r="334" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A334" s="1"/>
       <c r="E334">
         <f>SUM(E326:E332)*E333</f>
@@ -5907,7 +5926,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="335" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A335" s="7" t="s">
         <v>78</v>
       </c>
@@ -5921,7 +5940,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="336" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A336" s="7"/>
       <c r="B336" s="8" t="s">
         <v>46</v>
@@ -5933,7 +5952,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="337" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A337" s="7"/>
       <c r="B337" s="8" t="s">
         <v>358</v>
@@ -5945,7 +5964,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="338" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A338" s="7"/>
       <c r="B338" s="8" t="s">
         <v>169</v>
@@ -5957,7 +5976,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="339" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A339" s="7"/>
       <c r="B339" s="8" t="s">
         <v>77</v>
@@ -5969,7 +5988,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="340" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A340" s="7"/>
       <c r="B340" s="8" t="s">
         <v>79</v>
@@ -5981,7 +6000,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="341" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A341" s="7"/>
       <c r="B341" s="7" t="s">
         <v>57</v>
@@ -5995,7 +6014,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="342" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A342" s="7"/>
       <c r="B342" s="7"/>
       <c r="C342" s="8" t="s">
@@ -6007,7 +6026,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="343" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A343" s="7"/>
       <c r="B343" s="7"/>
       <c r="C343" s="8" t="s">
@@ -6019,7 +6038,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="344" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A344" s="7"/>
       <c r="B344" s="7"/>
       <c r="C344" s="8" t="s">
@@ -6031,7 +6050,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="345" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A345" s="7"/>
       <c r="B345" s="7"/>
       <c r="C345" s="8" t="s">
@@ -6043,7 +6062,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="346" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A346" s="7"/>
       <c r="B346" s="7"/>
       <c r="C346" s="8" t="s">
@@ -6057,7 +6076,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="347" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A347" s="7"/>
       <c r="B347" s="7"/>
       <c r="C347" s="8"/>
@@ -6069,7 +6088,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="348" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A348" s="7"/>
       <c r="B348" s="7"/>
       <c r="C348" s="8"/>
@@ -6081,7 +6100,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="349" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A349" s="7"/>
       <c r="B349" s="7"/>
       <c r="C349" s="8"/>
@@ -6093,7 +6112,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="350" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A350" s="7"/>
       <c r="B350" s="7"/>
       <c r="C350" s="8"/>
@@ -6105,7 +6124,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="351" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A351" s="7"/>
       <c r="B351" s="7"/>
       <c r="C351" s="8"/>
@@ -6117,7 +6136,7 @@
       </c>
       <c r="F351" s="8"/>
     </row>
-    <row r="352" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:6" x14ac:dyDescent="0.45">
       <c r="E352">
         <f>SUM(E335:E350)*E351</f>
         <v>0</v>
@@ -6127,12 +6146,12 @@
         <v>160</v>
       </c>
     </row>
-    <row r="353" spans="1:6" ht="19" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:6" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A353" s="5" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="354" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A354" s="13" t="s">
         <v>220</v>
       </c>
@@ -6146,7 +6165,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="355" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A355" s="13"/>
       <c r="B355" s="13" t="s">
         <v>387</v>
@@ -6160,7 +6179,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="356" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A356" s="13"/>
       <c r="B356" s="13"/>
       <c r="C356" s="13" t="s">
@@ -6172,7 +6191,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="357" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A357" s="13"/>
       <c r="B357" s="13"/>
       <c r="C357" s="13" t="s">
@@ -6184,7 +6203,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="358" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A358" s="13"/>
       <c r="B358" s="13" t="s">
         <v>388</v>
@@ -6198,7 +6217,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="359" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A359" s="13"/>
       <c r="B359" s="13"/>
       <c r="C359" s="13" t="s">
@@ -6210,7 +6229,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="360" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A360" s="13"/>
       <c r="B360" s="13"/>
       <c r="C360" s="13" t="s">
@@ -6222,7 +6241,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="361" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A361" s="13"/>
       <c r="B361" s="13"/>
       <c r="C361" s="13"/>
@@ -6234,7 +6253,7 @@
       </c>
       <c r="F361" s="13"/>
     </row>
-    <row r="362" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:6" x14ac:dyDescent="0.45">
       <c r="E362">
         <f>SUM(E354:E360)*E361</f>
         <v>0</v>
@@ -6244,12 +6263,12 @@
         <v>190</v>
       </c>
     </row>
-    <row r="363" spans="1:6" s="18" customFormat="1" ht="19" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:6" s="18" customFormat="1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A363" s="5" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="364" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A364" s="15" t="s">
         <v>361</v>
       </c>
@@ -6265,7 +6284,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="365" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A365" s="13"/>
       <c r="B365" s="13"/>
       <c r="C365" s="13" t="s">
@@ -6279,7 +6298,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="366" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A366" s="13"/>
       <c r="B366" s="13"/>
       <c r="C366" s="13" t="s">
@@ -6293,7 +6312,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="367" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A367" s="13"/>
       <c r="B367" s="13"/>
       <c r="C367" s="13" t="s">
@@ -6307,7 +6326,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="368" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A368" s="13"/>
       <c r="B368" s="13"/>
       <c r="C368" s="13" t="s">
@@ -6321,7 +6340,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="369" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A369" s="13"/>
       <c r="B369" s="13"/>
       <c r="C369" s="13" t="s">
@@ -6335,7 +6354,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="370" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A370" s="13"/>
       <c r="B370" s="13"/>
       <c r="C370" s="13"/>
@@ -6347,7 +6366,7 @@
       </c>
       <c r="F370" s="13"/>
     </row>
-    <row r="371" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:6" x14ac:dyDescent="0.45">
       <c r="E371">
         <f>SUM(E364:E369)*E370</f>
         <v>0</v>
@@ -6357,7 +6376,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="372" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A372" s="15" t="s">
         <v>44</v>
       </c>
@@ -6371,7 +6390,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="373" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A373" s="15"/>
       <c r="B373" s="17" t="s">
         <v>77</v>
@@ -6383,7 +6402,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="374" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A374" s="15"/>
       <c r="B374" s="17" t="s">
         <v>124</v>
@@ -6395,7 +6414,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="375" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A375" s="15"/>
       <c r="B375" s="13"/>
       <c r="C375" s="13"/>
@@ -6403,7 +6422,7 @@
       <c r="E375" s="13"/>
       <c r="F375" s="13"/>
     </row>
-    <row r="376" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A376" s="15" t="s">
         <v>122</v>
       </c>
@@ -6417,7 +6436,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="377" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A377" s="15"/>
       <c r="B377" s="13" t="s">
         <v>123</v>
@@ -6429,7 +6448,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="378" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A378" s="15"/>
       <c r="B378" s="13" t="s">
         <v>124</v>
@@ -6441,7 +6460,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="379" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A379" s="15"/>
       <c r="B379" s="13"/>
       <c r="C379" s="13"/>
@@ -6449,7 +6468,7 @@
       <c r="E379" s="13"/>
       <c r="F379" s="13"/>
     </row>
-    <row r="380" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A380" s="15" t="s">
         <v>227</v>
       </c>
@@ -6463,7 +6482,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="381" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A381" s="15"/>
       <c r="B381" s="13" t="s">
         <v>123</v>
@@ -6475,7 +6494,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="382" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A382" s="15"/>
       <c r="B382" s="13" t="s">
         <v>124</v>
@@ -6487,7 +6506,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="383" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A383" s="15"/>
       <c r="B383" s="13"/>
       <c r="C383" s="13"/>
@@ -6499,7 +6518,7 @@
       </c>
       <c r="F383" s="13"/>
     </row>
-    <row r="384" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A384" s="1"/>
       <c r="E384">
         <f>SUM(E372:E382)*E383</f>
@@ -6510,7 +6529,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="385" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A385" s="16" t="s">
         <v>45</v>
       </c>
@@ -6525,7 +6544,7 @@
       </c>
       <c r="M385" s="20"/>
     </row>
-    <row r="386" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A386" s="16" t="s">
         <v>357</v>
       </c>
@@ -6540,7 +6559,7 @@
       </c>
       <c r="M386" s="20"/>
     </row>
-    <row r="387" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A387" s="16"/>
       <c r="B387" s="14"/>
       <c r="C387" s="14"/>
@@ -6553,7 +6572,7 @@
       <c r="F387" s="14"/>
       <c r="M387" s="20"/>
     </row>
-    <row r="388" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A388" s="1"/>
       <c r="E388">
         <f>SUM(E385:E386)*E387</f>
@@ -6565,12 +6584,12 @@
       </c>
       <c r="M388" s="20"/>
     </row>
-    <row r="391" spans="1:13" ht="19" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:13" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A391" s="5" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="392" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A392" s="11" t="s">
         <v>104</v>
       </c>
@@ -6584,7 +6603,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="393" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A393" s="12"/>
       <c r="B393" s="12" t="s">
         <v>106</v>
@@ -6596,7 +6615,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="394" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A394" s="12"/>
       <c r="B394" s="12" t="s">
         <v>107</v>
@@ -6608,7 +6627,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="395" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A395" s="12"/>
       <c r="B395" s="12" t="s">
         <v>108</v>
@@ -6620,7 +6639,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="396" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A396" s="11" t="s">
         <v>120</v>
       </c>
@@ -6630,7 +6649,7 @@
       <c r="E396" s="12"/>
       <c r="F396" s="12"/>
     </row>
-    <row r="397" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A397" s="11"/>
       <c r="B397" s="12" t="s">
         <v>142</v>
@@ -6642,7 +6661,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="398" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A398" s="12"/>
       <c r="B398" s="12" t="s">
         <v>143</v>
@@ -6654,7 +6673,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="399" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A399" s="12"/>
       <c r="B399" s="12" t="s">
         <v>144</v>
@@ -6666,7 +6685,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="400" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A400" s="12"/>
       <c r="B400" s="12" t="s">
         <v>145</v>
@@ -6678,7 +6697,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="401" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A401" s="12"/>
       <c r="B401" s="12"/>
       <c r="C401" s="12"/>
@@ -6686,7 +6705,7 @@
       <c r="E401" s="12"/>
       <c r="F401" s="12"/>
     </row>
-    <row r="402" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A402" s="12" t="s">
         <v>146</v>
       </c>
@@ -6700,7 +6719,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="403" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A403" s="12"/>
       <c r="B403" s="12" t="s">
         <v>148</v>
@@ -6712,7 +6731,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="404" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A404" s="12"/>
       <c r="B404" s="12" t="s">
         <v>149</v>
@@ -6724,7 +6743,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="405" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A405" s="12"/>
       <c r="B405" s="12"/>
       <c r="C405" s="12"/>
@@ -6736,7 +6755,7 @@
       </c>
       <c r="F405" s="12"/>
     </row>
-    <row r="406" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:6" x14ac:dyDescent="0.45">
       <c r="E406">
         <f>SUM(E392:E404)*E405</f>
         <v>0</v>
@@ -6746,12 +6765,12 @@
         <v>120</v>
       </c>
     </row>
-    <row r="407" spans="1:6" ht="19" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:6" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A407" s="5" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="408" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A408" s="7" t="s">
         <v>40</v>
       </c>
@@ -6767,7 +6786,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="409" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A409" s="7"/>
       <c r="B409" s="8"/>
       <c r="C409" s="8" t="s">
@@ -6779,7 +6798,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="410" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A410" s="7"/>
       <c r="B410" s="8"/>
       <c r="C410" s="8" t="s">
@@ -6791,7 +6810,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="411" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A411" s="7"/>
       <c r="B411" s="8"/>
       <c r="C411" s="8" t="s">
@@ -6803,7 +6822,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="412" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A412" s="7"/>
       <c r="B412" s="8"/>
       <c r="C412" s="8" t="s">
@@ -6815,7 +6834,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="413" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A413" s="8"/>
       <c r="B413" s="8" t="s">
         <v>13</v>
@@ -6827,7 +6846,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="414" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A414" s="8"/>
       <c r="B414" s="8" t="s">
         <v>43</v>
@@ -6839,7 +6858,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="415" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A415" s="8"/>
       <c r="B415" s="8" t="s">
         <v>80</v>
@@ -6851,7 +6870,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="416" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A416" s="8"/>
       <c r="B416" s="8" t="s">
         <v>99</v>
@@ -6863,7 +6882,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="417" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A417" s="8"/>
       <c r="B417" s="8"/>
       <c r="C417" s="8"/>
@@ -6875,7 +6894,7 @@
       </c>
       <c r="F417" s="8"/>
     </row>
-    <row r="418" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:6" x14ac:dyDescent="0.45">
       <c r="E418">
         <f>SUM(E408:E416)*E417</f>
         <v>0</v>
@@ -6885,7 +6904,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="419" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A419" s="14" t="s">
         <v>150</v>
       </c>
@@ -6899,7 +6918,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="420" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A420" s="14"/>
       <c r="B420" s="14" t="s">
         <v>152</v>
@@ -6911,7 +6930,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="421" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A421" s="14"/>
       <c r="B421" s="14" t="s">
         <v>153</v>
@@ -6923,7 +6942,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="422" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A422" s="14"/>
       <c r="B422" s="14" t="s">
         <v>154</v>
@@ -6935,7 +6954,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="423" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A423" s="14"/>
       <c r="B423" s="14" t="s">
         <v>155</v>
@@ -6947,7 +6966,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="424" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A424" s="14"/>
       <c r="B424" s="14" t="s">
         <v>258</v>
@@ -6959,7 +6978,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="425" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A425" s="14"/>
       <c r="B425" s="14" t="s">
         <v>156</v>
@@ -6971,7 +6990,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="426" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A426" s="14"/>
       <c r="B426" s="14" t="s">
         <v>259</v>
@@ -6983,7 +7002,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="427" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A427" s="14"/>
       <c r="B427" s="14" t="s">
         <v>157</v>
@@ -6995,7 +7014,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="428" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A428" s="14"/>
       <c r="B428" s="14"/>
       <c r="C428" s="14"/>
@@ -7007,7 +7026,7 @@
       </c>
       <c r="F428" s="14"/>
     </row>
-    <row r="429" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:6" x14ac:dyDescent="0.45">
       <c r="E429">
         <f>SUM(E419:E427)*E428</f>
         <v>0</v>
@@ -7017,7 +7036,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="430" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A430" s="8" t="s">
         <v>158</v>
       </c>
@@ -7031,7 +7050,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="431" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A431" s="8"/>
       <c r="B431" s="8" t="s">
         <v>160</v>
@@ -7043,7 +7062,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="432" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A432" s="8"/>
       <c r="B432" s="8" t="s">
         <v>8</v>
@@ -7055,7 +7074,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="433" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A433" s="8"/>
       <c r="B433" s="8" t="s">
         <v>161</v>
@@ -7067,7 +7086,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="434" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A434" s="8"/>
       <c r="B434" s="8" t="s">
         <v>162</v>
@@ -7079,7 +7098,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="435" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A435" s="8"/>
       <c r="B435" s="8" t="s">
         <v>163</v>
@@ -7091,7 +7110,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="436" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A436" s="8"/>
       <c r="B436" s="8" t="s">
         <v>164</v>
@@ -7103,7 +7122,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="437" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A437" s="8"/>
       <c r="B437" s="8"/>
       <c r="C437" s="8"/>
@@ -7115,7 +7134,7 @@
       </c>
       <c r="F437" s="8"/>
     </row>
-    <row r="438" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:6" x14ac:dyDescent="0.45">
       <c r="E438">
         <f>SUM(E430:E436)*E437</f>
         <v>0</v>
@@ -7125,7 +7144,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="439" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A439" s="7" t="s">
         <v>362</v>
       </c>
@@ -7141,7 +7160,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="440" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A440" s="7"/>
       <c r="B440" s="7"/>
       <c r="C440" s="8"/>
@@ -7153,7 +7172,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="441" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A441" s="7"/>
       <c r="B441" s="7"/>
       <c r="C441" s="8"/>
@@ -7165,7 +7184,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="442" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A442" s="7"/>
       <c r="B442" s="7"/>
       <c r="C442" s="8" t="s">
@@ -7179,7 +7198,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="443" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A443" s="7"/>
       <c r="B443" s="7"/>
       <c r="C443" s="8"/>
@@ -7191,7 +7210,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="444" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A444" s="7"/>
       <c r="B444" s="7"/>
       <c r="C444" s="8"/>
@@ -7203,7 +7222,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="445" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A445" s="7"/>
       <c r="B445" s="7"/>
       <c r="C445" s="8"/>
@@ -7215,7 +7234,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="446" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A446" s="7"/>
       <c r="B446" s="7"/>
       <c r="C446" s="8"/>
@@ -7227,7 +7246,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="447" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:6" x14ac:dyDescent="0.45">
       <c r="E447">
         <f>SUM(E439:E446)</f>
         <v>0</v>
@@ -7237,12 +7256,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="448" spans="1:6" ht="19" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:6" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A448" s="5" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="449" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A449" s="7" t="s">
         <v>265</v>
       </c>
@@ -7258,7 +7277,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="450" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A450" s="7"/>
       <c r="B450" s="8"/>
       <c r="C450" s="8" t="s">
@@ -7270,7 +7289,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="451" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A451" s="8"/>
       <c r="B451" s="7" t="s">
         <v>266</v>
@@ -7282,7 +7301,7 @@
       <c r="E451" s="8"/>
       <c r="F451" s="8"/>
     </row>
-    <row r="452" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A452" s="8"/>
       <c r="B452" s="8"/>
       <c r="C452" s="8" t="s">
@@ -7294,7 +7313,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="453" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A453" s="8"/>
       <c r="B453" s="8"/>
       <c r="C453" s="8" t="s">
@@ -7306,7 +7325,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="454" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A454" s="8"/>
       <c r="B454" s="8"/>
       <c r="C454" s="8" t="s">
@@ -7318,7 +7337,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="455" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A455" s="8"/>
       <c r="B455" s="8"/>
       <c r="C455" s="8" t="s">
@@ -7330,7 +7349,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="456" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A456" s="8"/>
       <c r="B456" s="8"/>
       <c r="C456" s="8"/>
@@ -7341,7 +7360,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="457" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:6" x14ac:dyDescent="0.45">
       <c r="E457">
         <f>SUM(E449:E455)*E456</f>
         <v>0</v>
@@ -7351,12 +7370,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="458" spans="1:6" ht="21" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:6" ht="21" x14ac:dyDescent="0.65">
       <c r="A458" s="23" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="459" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A459" s="11" t="s">
         <v>369</v>
       </c>
@@ -7370,7 +7389,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="460" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A460" s="11" t="s">
         <v>371</v>
       </c>
@@ -7386,7 +7405,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="461" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A461" s="11"/>
       <c r="B461" s="12"/>
       <c r="C461" s="12" t="s">
@@ -7398,7 +7417,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="462" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A462" s="11"/>
       <c r="B462" s="12"/>
       <c r="C462" s="12"/>
@@ -7410,7 +7429,7 @@
       </c>
       <c r="F462" s="12"/>
     </row>
-    <row r="463" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A463" s="1"/>
       <c r="E463">
         <f>SUM(E459:E461)*E462</f>
@@ -7421,15 +7440,15 @@
         <v>50</v>
       </c>
     </row>
-    <row r="464" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A464" s="1"/>
     </row>
-    <row r="465" spans="1:6" ht="19" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:6" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A465" s="5" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="466" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A466" s="15" t="s">
         <v>348</v>
       </c>
@@ -7445,7 +7464,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="467" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A467" s="13" t="s">
         <v>355</v>
       </c>
@@ -7459,7 +7478,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="468" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A468" s="13" t="s">
         <v>0</v>
       </c>
@@ -7473,7 +7492,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="469" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A469" s="13"/>
       <c r="B469" s="13" t="s">
         <v>350</v>
@@ -7485,7 +7504,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="470" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A470" s="13"/>
       <c r="B470" s="13"/>
       <c r="C470" s="13"/>
@@ -7497,7 +7516,7 @@
       </c>
       <c r="F470" s="13"/>
     </row>
-    <row r="471" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:6" x14ac:dyDescent="0.45">
       <c r="E471">
         <f>SUM(E466:E469)*E470</f>
         <v>0</v>
@@ -7507,7 +7526,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="473" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A473" s="16" t="s">
         <v>348</v>
       </c>
@@ -7523,7 +7542,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="474" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A474" s="14" t="s">
         <v>135</v>
       </c>
@@ -7537,7 +7556,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="475" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A475" s="14"/>
       <c r="B475" s="14" t="s">
         <v>228</v>
@@ -7549,7 +7568,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="476" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A476" s="14"/>
       <c r="B476" s="14"/>
       <c r="C476" s="14"/>
@@ -7561,7 +7580,7 @@
       </c>
       <c r="F476" s="14"/>
     </row>
-    <row r="477" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:6" x14ac:dyDescent="0.45">
       <c r="E477">
         <f>SUM(E473:E475)*E476</f>
         <v>0</v>
@@ -7571,7 +7590,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="478" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A478" s="11" t="s">
         <v>348</v>
       </c>
@@ -7587,7 +7606,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="479" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A479" s="12" t="s">
         <v>353</v>
       </c>
@@ -7601,7 +7620,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="480" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A480" s="12"/>
       <c r="B480" s="12" t="s">
         <v>354</v>
@@ -7613,7 +7632,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="481" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A481" s="12"/>
       <c r="B481" s="12"/>
       <c r="C481" s="12"/>
@@ -7625,7 +7644,7 @@
       </c>
       <c r="F481" s="12"/>
     </row>
-    <row r="482" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:6" x14ac:dyDescent="0.45">
       <c r="E482">
         <f>SUM(E478:E480)*E481</f>
         <v>0</v>
@@ -7635,12 +7654,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="487" spans="1:6" ht="19" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:6" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A487" s="5" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="488" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A488" s="14" t="s">
         <v>265</v>
       </c>
@@ -7654,7 +7673,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="489" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A489" s="14" t="s">
         <v>270</v>
       </c>
@@ -7668,7 +7687,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="490" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A490" s="14"/>
       <c r="B490" s="14" t="s">
         <v>268</v>
@@ -7680,7 +7699,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="491" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A491" s="14"/>
       <c r="B491" s="14" t="s">
         <v>267</v>
@@ -7692,7 +7711,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="492" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A492" s="14"/>
       <c r="B492" s="14" t="s">
         <v>269</v>
@@ -7704,7 +7723,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="493" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A493" s="14"/>
       <c r="B493" s="14" t="s">
         <v>271</v>
@@ -7716,7 +7735,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="494" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A494" s="14"/>
       <c r="B494" s="14" t="s">
         <v>272</v>
@@ -7728,7 +7747,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="495" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A495" s="14"/>
       <c r="B495" s="14" t="s">
         <v>26</v>
@@ -7740,7 +7759,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="496" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A496" s="14"/>
       <c r="B496" s="14" t="s">
         <v>27</v>
@@ -7752,7 +7771,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="497" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A497" s="14"/>
       <c r="B497" s="14" t="s">
         <v>273</v>
@@ -7764,7 +7783,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="498" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A498" s="14"/>
       <c r="B498" s="14" t="s">
         <v>274</v>
@@ -7776,7 +7795,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="499" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A499" s="14"/>
       <c r="B499" s="14"/>
       <c r="C499" s="14"/>
@@ -7788,7 +7807,7 @@
       </c>
       <c r="F499" s="14"/>
     </row>
-    <row r="500" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:6" x14ac:dyDescent="0.45">
       <c r="E500">
         <f>SUM(E488:E498)*E499</f>
         <v>0</v>
@@ -7798,7 +7817,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="502" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A502" s="12" t="s">
         <v>265</v>
       </c>
@@ -7812,7 +7831,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="503" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A503" s="12" t="s">
         <v>270</v>
       </c>
@@ -7826,7 +7845,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="504" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A504" s="12"/>
       <c r="B504" s="12" t="s">
         <v>268</v>
@@ -7838,7 +7857,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="505" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A505" s="12"/>
       <c r="B505" s="12" t="s">
         <v>267</v>
@@ -7850,7 +7869,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="506" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A506" s="12"/>
       <c r="B506" s="12" t="s">
         <v>269</v>
@@ -7862,7 +7881,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="507" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A507" s="12"/>
       <c r="B507" s="12" t="s">
         <v>271</v>
@@ -7874,7 +7893,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="508" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A508" s="12"/>
       <c r="B508" s="12" t="s">
         <v>272</v>
@@ -7886,7 +7905,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="509" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A509" s="12"/>
       <c r="B509" s="12" t="s">
         <v>26</v>
@@ -7898,7 +7917,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="510" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A510" s="12"/>
       <c r="B510" s="12" t="s">
         <v>27</v>
@@ -7910,7 +7929,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="511" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A511" s="12"/>
       <c r="B511" s="12" t="s">
         <v>273</v>
@@ -7922,7 +7941,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="512" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A512" s="12"/>
       <c r="B512" s="12" t="s">
         <v>274</v>
@@ -7934,7 +7953,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="513" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A513" s="12"/>
       <c r="B513" s="12"/>
       <c r="C513" s="12"/>
@@ -7946,7 +7965,7 @@
       </c>
       <c r="F513" s="12"/>
     </row>
-    <row r="514" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:6" x14ac:dyDescent="0.45">
       <c r="E514">
         <f>SUM(E502:E512)*E513</f>
         <v>0</v>
@@ -7956,7 +7975,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="516" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A516" s="13" t="s">
         <v>265</v>
       </c>
@@ -7970,7 +7989,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="517" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="517" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A517" s="13" t="s">
         <v>270</v>
       </c>
@@ -7984,7 +8003,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="518" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="518" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A518" s="13"/>
       <c r="B518" s="13" t="s">
         <v>268</v>
@@ -7996,7 +8015,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="519" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="519" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A519" s="13"/>
       <c r="B519" s="13" t="s">
         <v>267</v>
@@ -8008,7 +8027,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="520" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="520" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A520" s="13"/>
       <c r="B520" s="13" t="s">
         <v>269</v>
@@ -8020,7 +8039,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="521" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="521" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A521" s="13"/>
       <c r="B521" s="13" t="s">
         <v>271</v>
@@ -8032,7 +8051,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="522" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="522" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A522" s="13"/>
       <c r="B522" s="13" t="s">
         <v>272</v>
@@ -8044,7 +8063,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="523" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A523" s="13"/>
       <c r="B523" s="13" t="s">
         <v>26</v>
@@ -8056,7 +8075,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="524" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="524" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A524" s="13"/>
       <c r="B524" s="13" t="s">
         <v>27</v>
@@ -8068,7 +8087,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="525" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="525" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A525" s="13"/>
       <c r="B525" s="13" t="s">
         <v>273</v>
@@ -8080,7 +8099,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="526" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="526" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A526" s="13"/>
       <c r="B526" s="13" t="s">
         <v>274</v>
@@ -8092,7 +8111,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="527" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="527" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A527" s="13"/>
       <c r="B527" s="13"/>
       <c r="C527" s="13"/>
@@ -8104,7 +8123,7 @@
       </c>
       <c r="F527" s="13"/>
     </row>
-    <row r="528" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="528" spans="1:6" x14ac:dyDescent="0.45">
       <c r="E528">
         <f>SUM(E516:E526)*E527</f>
         <v>0</v>
@@ -8114,64 +8133,84 @@
         <v>60</v>
       </c>
     </row>
-    <row r="530" spans="1:6" ht="21" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:6" ht="21" x14ac:dyDescent="0.65">
       <c r="A530" s="23" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="531" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A531" s="16" t="s">
         <v>375</v>
       </c>
-      <c r="B531" s="14"/>
+      <c r="B531" s="14" t="s">
+        <v>404</v>
+      </c>
       <c r="C531" s="14"/>
-      <c r="D531" s="14"/>
+      <c r="D531" s="14" t="s">
+        <v>405</v>
+      </c>
       <c r="E531" s="14"/>
       <c r="F531" s="14">
         <v>30</v>
       </c>
     </row>
-    <row r="532" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A532" s="14"/>
-      <c r="B532" s="14"/>
+      <c r="B532" s="14" t="s">
+        <v>406</v>
+      </c>
       <c r="C532" s="14"/>
-      <c r="D532" s="14"/>
+      <c r="D532" s="14" t="s">
+        <v>407</v>
+      </c>
       <c r="E532" s="14"/>
       <c r="F532" s="14">
         <v>30</v>
       </c>
     </row>
-    <row r="533" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A533" s="14"/>
-      <c r="B533" s="14"/>
+      <c r="B533" s="14" t="s">
+        <v>408</v>
+      </c>
       <c r="C533" s="14"/>
-      <c r="D533" s="14"/>
+      <c r="D533" s="14" t="s">
+        <v>409</v>
+      </c>
       <c r="E533" s="14"/>
       <c r="F533" s="14">
         <v>30</v>
       </c>
     </row>
-    <row r="534" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A534" s="14"/>
-      <c r="B534" s="14"/>
+      <c r="B534" s="14" t="s">
+        <v>410</v>
+      </c>
       <c r="C534" s="14"/>
-      <c r="D534" s="14"/>
+      <c r="D534" s="14" t="s">
+        <v>411</v>
+      </c>
       <c r="E534" s="14"/>
       <c r="F534" s="14">
         <v>30</v>
       </c>
     </row>
-    <row r="535" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:6" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A535" s="14"/>
-      <c r="B535" s="14"/>
+      <c r="B535" s="14" t="s">
+        <v>412</v>
+      </c>
       <c r="C535" s="14"/>
-      <c r="D535" s="14"/>
+      <c r="D535" s="24" t="s">
+        <v>413</v>
+      </c>
       <c r="E535" s="14"/>
       <c r="F535" s="14">
         <v>30</v>
       </c>
     </row>
-    <row r="536" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A536" s="14"/>
       <c r="B536" s="14"/>
       <c r="C536" s="14"/>
@@ -8183,7 +8222,7 @@
       </c>
       <c r="F536" s="14"/>
     </row>
-    <row r="537" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="537" spans="1:6" x14ac:dyDescent="0.45">
       <c r="E537">
         <f>SUM(E531:E535)*E536</f>
         <v>0</v>
@@ -8193,7 +8232,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="539" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="539" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A539" s="11" t="s">
         <v>375</v>
       </c>
@@ -8205,7 +8244,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="540" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="540" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A540" s="12"/>
       <c r="B540" s="12"/>
       <c r="C540" s="12"/>
@@ -8215,7 +8254,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="541" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="541" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A541" s="12"/>
       <c r="B541" s="12"/>
       <c r="C541" s="12"/>
@@ -8225,7 +8264,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="542" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="542" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A542" s="12"/>
       <c r="B542" s="12"/>
       <c r="C542" s="12"/>
@@ -8235,7 +8274,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="543" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="543" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A543" s="12"/>
       <c r="B543" s="12"/>
       <c r="C543" s="12"/>
@@ -8245,7 +8284,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="544" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="544" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A544" s="12"/>
       <c r="B544" s="12"/>
       <c r="C544" s="12"/>
@@ -8257,7 +8296,7 @@
       </c>
       <c r="F544" s="12"/>
     </row>
-    <row r="545" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="545" spans="1:8" x14ac:dyDescent="0.45">
       <c r="E545">
         <f>SUM(E539:E543)*E544</f>
         <v>0</v>
@@ -8267,7 +8306,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="547" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="547" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A547" s="15" t="s">
         <v>375</v>
       </c>
@@ -8279,7 +8318,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="548" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="548" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A548" s="13"/>
       <c r="B548" s="13"/>
       <c r="C548" s="13"/>
@@ -8289,7 +8328,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="549" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="549" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A549" s="13"/>
       <c r="B549" s="13"/>
       <c r="C549" s="13"/>
@@ -8299,7 +8338,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="550" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="550" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A550" s="13"/>
       <c r="B550" s="13"/>
       <c r="C550" s="13"/>
@@ -8309,7 +8348,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="551" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="551" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A551" s="13"/>
       <c r="B551" s="13"/>
       <c r="C551" s="13"/>
@@ -8319,7 +8358,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="552" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="552" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A552" s="13"/>
       <c r="B552" s="13"/>
       <c r="C552" s="13"/>
@@ -8331,7 +8370,7 @@
       </c>
       <c r="F552" s="13"/>
     </row>
-    <row r="553" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="553" spans="1:8" x14ac:dyDescent="0.45">
       <c r="E553">
         <f>SUM(E547:E551)*E552</f>
         <v>0</v>
@@ -8341,7 +8380,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="556" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="556" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A556" s="7"/>
       <c r="B556" t="s">
         <v>213</v>
@@ -8359,7 +8398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="557" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="557" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A557" s="11" t="s">
         <v>395</v>
       </c>
@@ -8379,7 +8418,7 @@
         <v>-3.5137034434293744E-2</v>
       </c>
     </row>
-    <row r="558" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="558" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A558" s="15" t="s">
         <v>402</v>
       </c>
@@ -8399,7 +8438,7 @@
         <v>-3.5971223021582732E-2</v>
       </c>
     </row>
-    <row r="559" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="559" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A559" s="16" t="s">
         <v>396</v>
       </c>
@@ -8419,7 +8458,7 @@
         <v>-3.5739814152966405E-2</v>
       </c>
     </row>
-    <row r="563" spans="4:7" x14ac:dyDescent="0.2">
+    <row r="563" spans="4:7" x14ac:dyDescent="0.45">
       <c r="F563" t="s">
         <v>260</v>
       </c>
@@ -8427,7 +8466,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="564" spans="4:7" x14ac:dyDescent="0.2">
+    <row r="564" spans="4:7" x14ac:dyDescent="0.45">
       <c r="D564" t="s">
         <v>262</v>
       </c>
@@ -8435,7 +8474,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="565" spans="4:7" x14ac:dyDescent="0.2">
+    <row r="565" spans="4:7" x14ac:dyDescent="0.45">
       <c r="F565">
         <v>45</v>
       </c>
@@ -8443,7 +8482,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="566" spans="4:7" x14ac:dyDescent="0.2">
+    <row r="566" spans="4:7" x14ac:dyDescent="0.45">
       <c r="F566">
         <f>F565+(F574-F565)/9</f>
         <v>50</v>
@@ -8452,7 +8491,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="567" spans="4:7" x14ac:dyDescent="0.2">
+    <row r="567" spans="4:7" x14ac:dyDescent="0.45">
       <c r="F567">
         <f>F566+(F574-F565)/9</f>
         <v>55</v>
@@ -8461,7 +8500,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="568" spans="4:7" x14ac:dyDescent="0.2">
+    <row r="568" spans="4:7" x14ac:dyDescent="0.45">
       <c r="F568">
         <f>F567+(F574-F565)/9</f>
         <v>60</v>
@@ -8470,7 +8509,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="569" spans="4:7" x14ac:dyDescent="0.2">
+    <row r="569" spans="4:7" x14ac:dyDescent="0.45">
       <c r="F569">
         <f>F568+(F574-F565)/9</f>
         <v>65</v>
@@ -8479,7 +8518,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="570" spans="4:7" x14ac:dyDescent="0.2">
+    <row r="570" spans="4:7" x14ac:dyDescent="0.45">
       <c r="F570">
         <f>F569+(F574-F565)/9</f>
         <v>70</v>
@@ -8488,7 +8527,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="571" spans="4:7" x14ac:dyDescent="0.2">
+    <row r="571" spans="4:7" x14ac:dyDescent="0.45">
       <c r="F571">
         <f>F570+(F574-F565)/9</f>
         <v>75</v>
@@ -8497,7 +8536,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="572" spans="4:7" x14ac:dyDescent="0.2">
+    <row r="572" spans="4:7" x14ac:dyDescent="0.45">
       <c r="F572">
         <f>F571+(F574-F565)/9</f>
         <v>80</v>
@@ -8506,7 +8545,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="573" spans="4:7" x14ac:dyDescent="0.2">
+    <row r="573" spans="4:7" x14ac:dyDescent="0.45">
       <c r="F573">
         <f>F572+(F574-F565)/9</f>
         <v>85</v>
@@ -8515,7 +8554,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="574" spans="4:7" x14ac:dyDescent="0.2">
+    <row r="574" spans="4:7" x14ac:dyDescent="0.45">
       <c r="F574">
         <v>90</v>
       </c>
@@ -8523,7 +8562,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="575" spans="4:7" x14ac:dyDescent="0.2">
+    <row r="575" spans="4:7" x14ac:dyDescent="0.45">
       <c r="E575" t="s">
         <v>264</v>
       </c>
@@ -8553,45 +8592,45 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:L1047724"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.46484375" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="31.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="27.5" customWidth="1"/>
-    <col min="5" max="5" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="31.1328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.46484375" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="27.46484375" customWidth="1"/>
+    <col min="5" max="5" width="14.46484375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="34" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" ht="33.4" x14ac:dyDescent="1">
       <c r="A1" s="29" t="s">
         <v>392</v>
       </c>
       <c r="B1" s="29"/>
       <c r="C1" s="29"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="30" t="s">
         <v>393</v>
       </c>
       <c r="B5" s="30"/>
       <c r="C5" s="30"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" ht="28.5" x14ac:dyDescent="0.85">
       <c r="A8" s="2" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
         <v>84</v>
       </c>
@@ -8605,7 +8644,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A10" s="1" t="s">
         <v>397</v>
       </c>
@@ -8619,15 +8658,15 @@
         <v>400</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
       <c r="C11" s="3"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A13" s="1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A15" s="1" t="s">
         <v>89</v>
       </c>
@@ -8635,7 +8674,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A17" s="1" t="s">
         <v>90</v>
       </c>
@@ -8643,7 +8682,7 @@
         <v>45924</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A18" s="1" t="s">
         <v>91</v>
       </c>
@@ -8651,12 +8690,12 @@
         <v>46051</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A20" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A21" s="1" t="s">
         <v>93</v>
       </c>
@@ -8664,13 +8703,13 @@
         <v>401</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="24" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" ht="23.25" x14ac:dyDescent="0.7">
       <c r="A23" s="6" t="s">
         <v>94</v>
       </c>
       <c r="H23" s="21"/>
     </row>
-    <row r="25" spans="1:8" ht="19" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="5" t="s">
         <v>95</v>
       </c>
@@ -8681,7 +8720,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A27" s="15" t="s">
         <v>36</v>
       </c>
@@ -8694,7 +8733,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A28" s="15"/>
       <c r="B28" s="13" t="s">
         <v>37</v>
@@ -8705,7 +8744,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A29" s="15"/>
       <c r="B29" s="13" t="s">
         <v>38</v>
@@ -8716,7 +8755,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A30" s="15"/>
       <c r="B30" s="13" t="s">
         <v>19</v>
@@ -8727,7 +8766,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A31" s="15"/>
       <c r="B31" s="13" t="s">
         <v>39</v>
@@ -8738,7 +8777,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A32" s="15"/>
       <c r="B32" s="13"/>
       <c r="C32" s="22" t="s">
@@ -8750,7 +8789,7 @@
       </c>
       <c r="E32" s="13"/>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.45">
       <c r="D33">
         <f>-SUM(D27:D32)</f>
         <v>0</v>
@@ -8761,11 +8800,11 @@
       </c>
       <c r="L33" s="20"/>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A34" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="B34" s="38" t="s">
+      <c r="B34" s="14" t="s">
         <v>226</v>
       </c>
       <c r="C34" s="16"/>
@@ -8775,9 +8814,9 @@
       </c>
       <c r="L34" s="20"/>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A35" s="16"/>
-      <c r="B35" s="38" t="s">
+      <c r="B35" s="14" t="s">
         <v>50</v>
       </c>
       <c r="C35" s="16"/>
@@ -8787,7 +8826,7 @@
       </c>
       <c r="L35" s="20"/>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A36" s="16"/>
       <c r="B36" s="14"/>
       <c r="C36" s="22" t="s">
@@ -8800,7 +8839,7 @@
       <c r="E36" s="14"/>
       <c r="L36" s="20"/>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.45">
       <c r="D37">
         <f>-SUM(D34:D36)</f>
         <v>0</v>
@@ -8811,10 +8850,10 @@
       </c>
       <c r="L37" s="20"/>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.45">
       <c r="L38" s="20"/>
     </row>
-    <row r="39" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A39" s="7" t="s">
         <v>98</v>
       </c>
@@ -8828,7 +8867,7 @@
       </c>
       <c r="L39" s="20"/>
     </row>
-    <row r="40" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A40" s="7"/>
       <c r="B40" s="10" t="s">
         <v>47</v>
@@ -8840,7 +8879,7 @@
       </c>
       <c r="L40" s="20"/>
     </row>
-    <row r="41" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A41" s="7"/>
       <c r="B41" s="9" t="s">
         <v>48</v>
@@ -8852,7 +8891,7 @@
       </c>
       <c r="L41" s="20"/>
     </row>
-    <row r="42" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A42" s="7"/>
       <c r="B42" s="9" t="s">
         <v>49</v>
@@ -8864,7 +8903,7 @@
       </c>
       <c r="L42" s="20"/>
     </row>
-    <row r="43" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A43" s="7"/>
       <c r="B43" s="9" t="s">
         <v>50</v>
@@ -8876,7 +8915,7 @@
       </c>
       <c r="L43" s="20"/>
     </row>
-    <row r="44" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A44" s="7"/>
       <c r="B44" s="9" t="s">
         <v>51</v>
@@ -8888,7 +8927,7 @@
       </c>
       <c r="L44" s="20"/>
     </row>
-    <row r="45" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A45" s="7"/>
       <c r="B45" s="9" t="s">
         <v>52</v>
@@ -8900,7 +8939,7 @@
       </c>
       <c r="L45" s="20"/>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A46" s="7"/>
       <c r="B46" s="9"/>
       <c r="C46" s="22" t="s">
@@ -8913,7 +8952,7 @@
       <c r="E46" s="8"/>
       <c r="L46" s="20"/>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.45">
       <c r="D47">
         <f>-SUM(D39:D46)</f>
         <v>0</v>
@@ -8924,11 +8963,11 @@
       </c>
       <c r="L47" s="20"/>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A49" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="B49" s="37" t="s">
+      <c r="B49" s="13" t="s">
         <v>76</v>
       </c>
       <c r="C49" s="15"/>
@@ -8937,9 +8976,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A50" s="15"/>
-      <c r="B50" s="37" t="s">
+      <c r="B50" s="13" t="s">
         <v>77</v>
       </c>
       <c r="C50" s="15"/>
@@ -8948,9 +8987,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A51" s="15"/>
-      <c r="B51" s="37" t="s">
+      <c r="B51" s="13" t="s">
         <v>124</v>
       </c>
       <c r="C51" s="15"/>
@@ -8959,18 +8998,18 @@
         <v>5</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A52" s="15"/>
-      <c r="B52" s="37"/>
+      <c r="B52" s="13"/>
       <c r="C52" s="15"/>
       <c r="D52" s="15"/>
       <c r="E52" s="15"/>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A53" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="B53" s="37" t="s">
+      <c r="B53" s="13" t="s">
         <v>77</v>
       </c>
       <c r="C53" s="15"/>
@@ -8979,9 +9018,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A54" s="15"/>
-      <c r="B54" s="37" t="s">
+      <c r="B54" s="13" t="s">
         <v>123</v>
       </c>
       <c r="C54" s="15"/>
@@ -8990,9 +9029,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A55" s="15"/>
-      <c r="B55" s="37" t="s">
+      <c r="B55" s="13" t="s">
         <v>124</v>
       </c>
       <c r="C55" s="15"/>
@@ -9001,18 +9040,18 @@
         <v>5</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A56" s="15"/>
-      <c r="B56" s="37"/>
+      <c r="B56" s="13"/>
       <c r="C56" s="15"/>
       <c r="D56" s="15"/>
       <c r="E56" s="15"/>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A57" s="15" t="s">
         <v>227</v>
       </c>
-      <c r="B57" s="37" t="s">
+      <c r="B57" s="13" t="s">
         <v>77</v>
       </c>
       <c r="C57" s="15"/>
@@ -9021,9 +9060,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A58" s="15"/>
-      <c r="B58" s="37" t="s">
+      <c r="B58" s="13" t="s">
         <v>123</v>
       </c>
       <c r="C58" s="15"/>
@@ -9032,9 +9071,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A59" s="15"/>
-      <c r="B59" s="37" t="s">
+      <c r="B59" s="13" t="s">
         <v>124</v>
       </c>
       <c r="C59" s="15"/>
@@ -9043,7 +9082,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A60" s="15"/>
       <c r="B60" s="13"/>
       <c r="C60" s="22" t="s">
@@ -9055,7 +9094,7 @@
       </c>
       <c r="E60" s="13"/>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.45">
       <c r="D61">
         <f>-SUM(D49:D60)</f>
         <v>0</v>
@@ -9065,7 +9104,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A63" s="15" t="s">
         <v>78</v>
       </c>
@@ -9078,7 +9117,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A64" s="15"/>
       <c r="B64" s="13" t="s">
         <v>46</v>
@@ -9089,7 +9128,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A65" s="15"/>
       <c r="B65" s="13" t="s">
         <v>247</v>
@@ -9100,7 +9139,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A66" s="15"/>
       <c r="B66" s="13" t="s">
         <v>79</v>
@@ -9111,7 +9150,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A67" s="15"/>
       <c r="B67" s="13"/>
       <c r="C67" s="22" t="s">
@@ -9123,7 +9162,7 @@
       </c>
       <c r="E67" s="13"/>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.45">
       <c r="D68">
         <f>-SUM(D63:D67)</f>
         <v>0</v>
@@ -9133,11 +9172,11 @@
         <v>40</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A72" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="B72" s="39" t="s">
+      <c r="B72" s="12" t="s">
         <v>251</v>
       </c>
       <c r="C72" s="11"/>
@@ -9146,9 +9185,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A73" s="11"/>
-      <c r="B73" s="39" t="s">
+      <c r="B73" s="12" t="s">
         <v>229</v>
       </c>
       <c r="C73" s="11"/>
@@ -9157,9 +9196,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A74" s="11"/>
-      <c r="B74" s="39" t="s">
+      <c r="B74" s="12" t="s">
         <v>230</v>
       </c>
       <c r="C74" s="11"/>
@@ -9168,9 +9207,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A75" s="11"/>
-      <c r="B75" s="39" t="s">
+      <c r="B75" s="12" t="s">
         <v>228</v>
       </c>
       <c r="C75" s="11"/>
@@ -9179,7 +9218,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A76" s="11"/>
       <c r="B76" s="12"/>
       <c r="C76" s="22" t="s">
@@ -9191,7 +9230,7 @@
       </c>
       <c r="E76" s="12"/>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.45">
       <c r="D77">
         <f>-SUM(D72:D76)</f>
         <v>0</v>
@@ -9201,7 +9240,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A79" s="7" t="s">
         <v>57</v>
       </c>
@@ -9214,7 +9253,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A80" s="7"/>
       <c r="B80" s="8" t="s">
         <v>60</v>
@@ -9225,7 +9264,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A81" s="7"/>
       <c r="B81" s="8" t="s">
         <v>59</v>
@@ -9236,7 +9275,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A82" s="7"/>
       <c r="B82" s="8" t="s">
         <v>56</v>
@@ -9247,7 +9286,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A83" s="7"/>
       <c r="B83" s="8" t="s">
         <v>231</v>
@@ -9258,7 +9297,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A84" s="7"/>
       <c r="B84" s="8" t="s">
         <v>61</v>
@@ -9271,7 +9310,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A85" s="7"/>
       <c r="B85" s="8"/>
       <c r="C85" s="8" t="s">
@@ -9282,7 +9321,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A86" s="7"/>
       <c r="B86" s="8"/>
       <c r="C86" s="8" t="s">
@@ -9293,7 +9332,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A87" s="7"/>
       <c r="B87" s="8"/>
       <c r="C87" s="8" t="s">
@@ -9304,7 +9343,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A88" s="7"/>
       <c r="B88" s="8"/>
       <c r="C88" s="8" t="s">
@@ -9315,7 +9354,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A89" s="7"/>
       <c r="B89" s="8"/>
       <c r="C89" s="22" t="s">
@@ -9327,7 +9366,7 @@
       </c>
       <c r="E89" s="8"/>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.45">
       <c r="D90">
         <f>-SUM(D79:D89)</f>
         <v>0</v>
@@ -9337,7 +9376,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A91" s="11" t="s">
         <v>168</v>
       </c>
@@ -9350,7 +9389,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A92" s="11"/>
       <c r="B92" s="12" t="s">
         <v>77</v>
@@ -9361,7 +9400,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A93" s="11"/>
       <c r="B93" s="12" t="s">
         <v>170</v>
@@ -9372,7 +9411,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A94" s="11"/>
       <c r="B94" s="12"/>
       <c r="C94" s="22" t="s">
@@ -9384,7 +9423,7 @@
       </c>
       <c r="E94" s="12"/>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.45">
       <c r="D95">
         <f>-SUM(D91:D94)</f>
         <v>0</v>
@@ -9394,355 +9433,349 @@
         <v>20</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A96" s="40" t="s">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A96" s="36" t="s">
         <v>62</v>
       </c>
-      <c r="B96" s="41" t="s">
+      <c r="B96" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="C96" s="42" t="s">
+      <c r="C96" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="D96" s="42"/>
-      <c r="E96" s="42">
+      <c r="D96" s="12"/>
+      <c r="E96" s="12">
         <v>5</v>
       </c>
       <c r="H96" s="1"/>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A97" s="40"/>
-      <c r="B97" s="42"/>
-      <c r="C97" s="42" t="s">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A97" s="36"/>
+      <c r="B97" s="12"/>
+      <c r="C97" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="D97" s="42"/>
-      <c r="E97" s="42">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A98" s="40"/>
-      <c r="B98" s="42"/>
-      <c r="C98" s="42" t="s">
+      <c r="D97" s="12"/>
+      <c r="E97" s="12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A98" s="36"/>
+      <c r="B98" s="12"/>
+      <c r="C98" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="D98" s="42"/>
-      <c r="E98" s="42">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A99" s="40"/>
-      <c r="B99" s="42"/>
-      <c r="C99" s="42" t="s">
+      <c r="D98" s="12"/>
+      <c r="E98" s="12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A99" s="36"/>
+      <c r="B99" s="12"/>
+      <c r="C99" s="12" t="s">
         <v>249</v>
       </c>
-      <c r="D99" s="42"/>
-      <c r="E99" s="42">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A100" s="40"/>
-      <c r="B100" s="42"/>
-      <c r="C100" s="42" t="s">
+      <c r="D99" s="12"/>
+      <c r="E99" s="12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A100" s="36"/>
+      <c r="B100" s="12"/>
+      <c r="C100" s="12" t="s">
         <v>248</v>
       </c>
-      <c r="D100" s="42"/>
-      <c r="E100" s="42">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A101" s="40"/>
-      <c r="B101" s="42"/>
-      <c r="C101" s="42" t="s">
+      <c r="D100" s="12"/>
+      <c r="E100" s="12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A101" s="36"/>
+      <c r="B101" s="12"/>
+      <c r="C101" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="D101" s="42"/>
-      <c r="E101" s="42">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A102" s="40"/>
-      <c r="B102" s="42"/>
-      <c r="C102" s="42" t="s">
+      <c r="D101" s="12"/>
+      <c r="E101" s="12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A102" s="36"/>
+      <c r="B102" s="12"/>
+      <c r="C102" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="D102" s="42"/>
-      <c r="E102" s="42">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A103" s="40"/>
-      <c r="B103" s="42"/>
-      <c r="C103" s="42" t="s">
+      <c r="D102" s="12"/>
+      <c r="E102" s="12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A103" s="36"/>
+      <c r="B103" s="12"/>
+      <c r="C103" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="D103" s="42"/>
-      <c r="E103" s="42">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A104" s="40"/>
-      <c r="B104" s="42"/>
-      <c r="C104" s="43" t="s">
+      <c r="D103" s="12"/>
+      <c r="E103" s="12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A104" s="36"/>
+      <c r="B104" s="12"/>
+      <c r="C104" s="22" t="s">
         <v>236</v>
       </c>
-      <c r="D104" s="43">
+      <c r="D104" s="22">
         <f>-SUM(D96:D103)</f>
         <v>0</v>
       </c>
-      <c r="E104" s="42"/>
-    </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A105" s="40"/>
-      <c r="B105" s="44"/>
-      <c r="C105" s="44"/>
-      <c r="D105" s="44">
+      <c r="E104" s="12"/>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A105" s="36"/>
+      <c r="D105">
         <f>-SUM(D96:D104)</f>
         <v>0</v>
       </c>
-      <c r="E105" s="44">
+      <c r="E105">
         <f>SUM(E96:E103)</f>
         <v>40</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A106" s="40"/>
-      <c r="B106" s="45" t="s">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A106" s="36"/>
+      <c r="B106" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="C106" s="46" t="s">
+      <c r="C106" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="D106" s="46"/>
-      <c r="E106" s="46">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A107" s="40"/>
-      <c r="B107" s="46"/>
-      <c r="C107" s="46" t="s">
+      <c r="D106" s="13"/>
+      <c r="E106" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A107" s="36"/>
+      <c r="B107" s="13"/>
+      <c r="C107" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="D107" s="46"/>
-      <c r="E107" s="46">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A108" s="40"/>
-      <c r="B108" s="46"/>
-      <c r="C108" s="46" t="s">
+      <c r="D107" s="13"/>
+      <c r="E107" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A108" s="36"/>
+      <c r="B108" s="13"/>
+      <c r="C108" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="D108" s="46"/>
-      <c r="E108" s="46">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A109" s="40"/>
-      <c r="B109" s="46"/>
-      <c r="C109" s="46" t="s">
+      <c r="D108" s="13"/>
+      <c r="E108" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A109" s="36"/>
+      <c r="B109" s="13"/>
+      <c r="C109" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="D109" s="46"/>
-      <c r="E109" s="46">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A110" s="40"/>
-      <c r="B110" s="46"/>
-      <c r="C110" s="46" t="s">
+      <c r="D109" s="13"/>
+      <c r="E109" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A110" s="36"/>
+      <c r="B110" s="13"/>
+      <c r="C110" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="D110" s="46"/>
-      <c r="E110" s="46">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A111" s="40"/>
-      <c r="B111" s="46"/>
-      <c r="C111" s="46" t="s">
+      <c r="D110" s="13"/>
+      <c r="E110" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A111" s="36"/>
+      <c r="B111" s="13"/>
+      <c r="C111" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="D111" s="46"/>
-      <c r="E111" s="46">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A112" s="40"/>
-      <c r="B112" s="46"/>
-      <c r="C112" s="46" t="s">
+      <c r="D111" s="13"/>
+      <c r="E111" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A112" s="36"/>
+      <c r="B112" s="13"/>
+      <c r="C112" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="D112" s="46"/>
-      <c r="E112" s="46">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A113" s="40"/>
-      <c r="B113" s="46"/>
-      <c r="C113" s="46" t="s">
+      <c r="D112" s="13"/>
+      <c r="E112" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A113" s="36"/>
+      <c r="B113" s="13"/>
+      <c r="C113" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="D113" s="46"/>
-      <c r="E113" s="46">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A114" s="40"/>
-      <c r="B114" s="46"/>
-      <c r="C114" s="43" t="s">
+      <c r="D113" s="13"/>
+      <c r="E113" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A114" s="36"/>
+      <c r="B114" s="13"/>
+      <c r="C114" s="22" t="s">
         <v>236</v>
       </c>
-      <c r="D114" s="43">
+      <c r="D114" s="22">
         <f>-SUM(D106:D113)</f>
         <v>0</v>
       </c>
-      <c r="E114" s="46"/>
-    </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A115" s="40"/>
-      <c r="B115" s="44"/>
-      <c r="C115" s="44"/>
-      <c r="D115" s="44">
+      <c r="E114" s="13"/>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A115" s="36"/>
+      <c r="D115">
         <f>-SUM(D106:D114)</f>
         <v>0</v>
       </c>
-      <c r="E115" s="44">
+      <c r="E115">
         <f>SUM(E106:E113)</f>
         <v>40</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A116" s="40"/>
-      <c r="B116" s="47" t="s">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A116" s="36"/>
+      <c r="B116" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="C116" s="48" t="s">
+      <c r="C116" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="D116" s="48"/>
-      <c r="E116" s="48">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A117" s="40"/>
-      <c r="B117" s="48"/>
-      <c r="C117" s="48" t="s">
+      <c r="D116" s="14"/>
+      <c r="E116" s="14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A117" s="36"/>
+      <c r="B117" s="14"/>
+      <c r="C117" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="D117" s="48"/>
-      <c r="E117" s="48">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A118" s="40"/>
-      <c r="B118" s="48"/>
-      <c r="C118" s="48" t="s">
+      <c r="D117" s="14"/>
+      <c r="E117" s="14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A118" s="36"/>
+      <c r="B118" s="14"/>
+      <c r="C118" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="D118" s="48"/>
-      <c r="E118" s="48">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A119" s="40"/>
-      <c r="B119" s="48"/>
-      <c r="C119" s="48" t="s">
+      <c r="D118" s="14"/>
+      <c r="E118" s="14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A119" s="36"/>
+      <c r="B119" s="14"/>
+      <c r="C119" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="D119" s="48"/>
-      <c r="E119" s="48">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A120" s="40"/>
-      <c r="B120" s="48"/>
-      <c r="C120" s="48" t="s">
+      <c r="D119" s="14"/>
+      <c r="E119" s="14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A120" s="36"/>
+      <c r="B120" s="14"/>
+      <c r="C120" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="D120" s="48"/>
-      <c r="E120" s="48">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A121" s="40"/>
-      <c r="B121" s="48"/>
-      <c r="C121" s="48" t="s">
+      <c r="D120" s="14"/>
+      <c r="E120" s="14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A121" s="36"/>
+      <c r="B121" s="14"/>
+      <c r="C121" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="D121" s="48"/>
-      <c r="E121" s="48">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A122" s="40"/>
-      <c r="B122" s="48"/>
-      <c r="C122" s="48" t="s">
+      <c r="D121" s="14"/>
+      <c r="E121" s="14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A122" s="36"/>
+      <c r="B122" s="14"/>
+      <c r="C122" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="D122" s="48"/>
-      <c r="E122" s="48">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A123" s="40"/>
-      <c r="B123" s="48"/>
-      <c r="C123" s="48" t="s">
+      <c r="D122" s="14"/>
+      <c r="E122" s="14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A123" s="36"/>
+      <c r="B123" s="14"/>
+      <c r="C123" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="D123" s="48"/>
-      <c r="E123" s="48">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A124" s="40"/>
-      <c r="B124" s="48"/>
-      <c r="C124" s="43" t="s">
+      <c r="D123" s="14"/>
+      <c r="E123" s="14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A124" s="36"/>
+      <c r="B124" s="14"/>
+      <c r="C124" s="22" t="s">
         <v>236</v>
       </c>
-      <c r="D124" s="43">
+      <c r="D124" s="22">
         <f>-SUM(D116:D123)</f>
         <v>0</v>
       </c>
-      <c r="E124" s="48"/>
-    </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A125" s="40"/>
-      <c r="B125" s="44"/>
-      <c r="C125" s="44"/>
-      <c r="D125" s="44">
+      <c r="E124" s="14"/>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A125" s="36"/>
+      <c r="D125">
         <f>-SUM(D116:D124)</f>
         <v>0</v>
       </c>
-      <c r="E125" s="44">
+      <c r="E125">
         <f>SUM(E116:E123)</f>
         <v>40</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A127" s="11" t="s">
         <v>109</v>
       </c>
@@ -9757,7 +9790,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A128" s="12"/>
       <c r="B128" s="12"/>
       <c r="C128" s="12" t="s">
@@ -9770,7 +9803,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A129" s="12"/>
       <c r="B129" s="12"/>
       <c r="C129" s="12"/>
@@ -9781,7 +9814,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A130" s="12"/>
       <c r="B130" s="12"/>
       <c r="C130" s="12" t="s">
@@ -9792,7 +9825,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A131" s="12"/>
       <c r="B131" s="12"/>
       <c r="C131" s="12" t="s">
@@ -9803,7 +9836,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A132" s="12"/>
       <c r="B132" s="12"/>
       <c r="C132" s="12" t="s">
@@ -9814,7 +9847,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A133" s="12"/>
       <c r="B133" s="12"/>
       <c r="C133" s="22" t="s">
@@ -9826,7 +9859,7 @@
       </c>
       <c r="E133" s="12"/>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A134"/>
       <c r="D134">
         <f>-SUM(D127:D133)</f>
@@ -9837,7 +9870,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A135" s="11" t="s">
         <v>109</v>
       </c>
@@ -9852,7 +9885,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A136" s="12"/>
       <c r="B136" s="12"/>
       <c r="C136" s="12" t="s">
@@ -9863,7 +9896,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A137" s="12"/>
       <c r="B137" s="12"/>
       <c r="C137" s="12" t="s">
@@ -9874,7 +9907,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A138" s="12"/>
       <c r="B138" s="12"/>
       <c r="C138" s="12" t="s">
@@ -9887,7 +9920,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A139" s="12"/>
       <c r="B139" s="12"/>
       <c r="C139" s="12"/>
@@ -9898,7 +9931,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A140" s="12"/>
       <c r="B140" s="12"/>
       <c r="C140" s="12"/>
@@ -9909,7 +9942,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A141" s="12"/>
       <c r="B141" s="12"/>
       <c r="C141" s="12"/>
@@ -9920,7 +9953,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A142" s="11"/>
       <c r="B142" s="12"/>
       <c r="C142" s="22" t="s">
@@ -9932,7 +9965,7 @@
       </c>
       <c r="E142" s="12"/>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.45">
       <c r="D143">
         <f>-SUM(D135:D142)</f>
         <v>0</v>
@@ -9942,66 +9975,66 @@
         <v>40</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A144" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="B144" s="37" t="s">
+      <c r="B144" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="C144" s="37" t="s">
+      <c r="C144" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="D144" s="37"/>
-      <c r="E144" s="37">
+      <c r="D144" s="13"/>
+      <c r="E144" s="13">
         <v>10</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A145" s="15"/>
-      <c r="B145" s="37"/>
-      <c r="C145" s="37" t="s">
+      <c r="B145" s="13"/>
+      <c r="C145" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="D145" s="37"/>
-      <c r="E145" s="37">
+      <c r="D145" s="13"/>
+      <c r="E145" s="13">
         <v>10</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A146" s="15"/>
-      <c r="B146" s="37"/>
-      <c r="C146" s="37" t="s">
+      <c r="B146" s="13"/>
+      <c r="C146" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="D146" s="37"/>
-      <c r="E146" s="37">
+      <c r="D146" s="13"/>
+      <c r="E146" s="13">
         <v>10</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A147" s="15"/>
-      <c r="B147" s="37"/>
-      <c r="C147" s="37" t="s">
+      <c r="B147" s="13"/>
+      <c r="C147" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="D147" s="37"/>
-      <c r="E147" s="37">
+      <c r="D147" s="13"/>
+      <c r="E147" s="13">
         <v>10</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A148" s="15"/>
-      <c r="B148" s="37"/>
-      <c r="C148" s="37" t="s">
+      <c r="B148" s="13"/>
+      <c r="C148" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="D148" s="37"/>
-      <c r="E148" s="37">
+      <c r="D148" s="13"/>
+      <c r="E148" s="13">
         <v>10</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A149" s="15"/>
       <c r="B149" s="13"/>
       <c r="C149" s="22" t="s">
@@ -10013,7 +10046,7 @@
       </c>
       <c r="E149" s="13"/>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.45">
       <c r="D150">
         <f>-SUM(D144:D149)</f>
         <v>0</v>
@@ -10023,14 +10056,14 @@
         <v>50</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A151" s="16" t="s">
         <v>125</v>
       </c>
-      <c r="B151" s="38" t="s">
+      <c r="B151" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="C151" s="38" t="s">
+      <c r="C151" s="14" t="s">
         <v>54</v>
       </c>
       <c r="D151" s="16"/>
@@ -10038,10 +10071,10 @@
         <v>20</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A152" s="16"/>
-      <c r="B152" s="38"/>
-      <c r="C152" s="38" t="s">
+      <c r="B152" s="14"/>
+      <c r="C152" s="14" t="s">
         <v>127</v>
       </c>
       <c r="D152" s="16"/>
@@ -10049,10 +10082,10 @@
         <v>20</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A153" s="16"/>
-      <c r="B153" s="38"/>
-      <c r="C153" s="38" t="s">
+      <c r="B153" s="14"/>
+      <c r="C153" s="14" t="s">
         <v>124</v>
       </c>
       <c r="D153" s="16"/>
@@ -10060,7 +10093,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A154" s="16"/>
       <c r="B154" s="14"/>
       <c r="C154" s="22" t="s">
@@ -10072,7 +10105,7 @@
       </c>
       <c r="E154" s="14"/>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.45">
       <c r="D155">
         <f>-SUM(D151:D154)</f>
         <v>0</v>
@@ -10082,7 +10115,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A157" s="16" t="s">
         <v>119</v>
       </c>
@@ -10095,7 +10128,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A158" s="16"/>
       <c r="B158" s="14" t="s">
         <v>121</v>
@@ -10106,7 +10139,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A159" s="16"/>
       <c r="B159" s="14" t="s">
         <v>224</v>
@@ -10117,7 +10150,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A160" s="16"/>
       <c r="B160" s="14" t="s">
         <v>232</v>
@@ -10128,7 +10161,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A161" s="16"/>
       <c r="B161" s="14" t="s">
         <v>225</v>
@@ -10139,7 +10172,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A162" s="16"/>
       <c r="B162" s="14"/>
       <c r="C162" s="22" t="s">
@@ -10151,7 +10184,7 @@
       </c>
       <c r="E162" s="14"/>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.45">
       <c r="D163">
         <f>-SUM(D157:D162)</f>
         <v>0</v>
@@ -10161,11 +10194,11 @@
         <v>30</v>
       </c>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A164" s="11" t="s">
         <v>206</v>
       </c>
-      <c r="B164" s="39" t="s">
+      <c r="B164" s="12" t="s">
         <v>205</v>
       </c>
       <c r="C164" s="11"/>
@@ -10174,9 +10207,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A165" s="11"/>
-      <c r="B165" s="39" t="s">
+      <c r="B165" s="12" t="s">
         <v>65</v>
       </c>
       <c r="C165" s="11"/>
@@ -10185,9 +10218,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A166" s="11"/>
-      <c r="B166" s="39" t="s">
+      <c r="B166" s="12" t="s">
         <v>50</v>
       </c>
       <c r="C166" s="11"/>
@@ -10196,9 +10229,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A167" s="11"/>
-      <c r="B167" s="39" t="s">
+      <c r="B167" s="12" t="s">
         <v>207</v>
       </c>
       <c r="C167" s="11"/>
@@ -10207,9 +10240,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A168" s="11"/>
-      <c r="B168" s="39" t="s">
+      <c r="B168" s="12" t="s">
         <v>51</v>
       </c>
       <c r="C168" s="11"/>
@@ -10218,9 +10251,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A169" s="11"/>
-      <c r="B169" s="39" t="s">
+      <c r="B169" s="12" t="s">
         <v>234</v>
       </c>
       <c r="C169" s="11"/>
@@ -10229,7 +10262,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A170" s="11"/>
       <c r="B170" s="12"/>
       <c r="C170" s="22" t="s">
@@ -10241,7 +10274,7 @@
       </c>
       <c r="E170" s="12"/>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.45">
       <c r="D171">
         <f>-SUM(D164:D170)</f>
         <v>0</v>
@@ -10251,75 +10284,75 @@
         <v>40</v>
       </c>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A172" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="B172" s="37" t="s">
+      <c r="B172" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="C172" s="37"/>
-      <c r="D172" s="37"/>
-      <c r="E172" s="37">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="C172" s="13"/>
+      <c r="D172" s="13"/>
+      <c r="E172" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A173" s="15"/>
-      <c r="B173" s="37" t="s">
+      <c r="B173" s="13" t="s">
         <v>235</v>
       </c>
-      <c r="C173" s="37"/>
-      <c r="D173" s="37"/>
-      <c r="E173" s="37">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="C173" s="13"/>
+      <c r="D173" s="13"/>
+      <c r="E173" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A174" s="15"/>
-      <c r="B174" s="37" t="s">
+      <c r="B174" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="C174" s="37"/>
-      <c r="D174" s="37"/>
-      <c r="E174" s="37">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="C174" s="13"/>
+      <c r="D174" s="13"/>
+      <c r="E174" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A175" s="15"/>
-      <c r="B175" s="37" t="s">
+      <c r="B175" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="C175" s="37"/>
-      <c r="D175" s="37"/>
-      <c r="E175" s="37">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="C175" s="13"/>
+      <c r="D175" s="13"/>
+      <c r="E175" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A176" s="15"/>
-      <c r="B176" s="37" t="s">
+      <c r="B176" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="C176" s="37"/>
-      <c r="D176" s="37"/>
-      <c r="E176" s="37">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="C176" s="13"/>
+      <c r="D176" s="13"/>
+      <c r="E176" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A177" s="15"/>
-      <c r="B177" s="37" t="s">
+      <c r="B177" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="C177" s="37"/>
-      <c r="D177" s="37"/>
-      <c r="E177" s="37">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="C177" s="13"/>
+      <c r="D177" s="13"/>
+      <c r="E177" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A178" s="15"/>
       <c r="B178" s="13"/>
       <c r="C178" s="22" t="s">
@@ -10331,7 +10364,7 @@
       </c>
       <c r="E178" s="13"/>
     </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.45">
       <c r="D179">
         <f>-SUM(D172:D178)</f>
         <v>0</v>
@@ -10341,11 +10374,11 @@
         <v>30</v>
       </c>
     </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A180" s="16" t="s">
         <v>135</v>
       </c>
-      <c r="B180" s="38" t="s">
+      <c r="B180" s="14" t="s">
         <v>50</v>
       </c>
       <c r="C180" s="16"/>
@@ -10354,9 +10387,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A181" s="16"/>
-      <c r="B181" s="38" t="s">
+      <c r="B181" s="14" t="s">
         <v>233</v>
       </c>
       <c r="C181" s="16"/>
@@ -10365,9 +10398,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A182" s="16"/>
-      <c r="B182" s="38" t="s">
+      <c r="B182" s="14" t="s">
         <v>136</v>
       </c>
       <c r="C182" s="16"/>
@@ -10376,9 +10409,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A183" s="16"/>
-      <c r="B183" s="38" t="s">
+      <c r="B183" s="14" t="s">
         <v>137</v>
       </c>
       <c r="C183" s="16"/>
@@ -10387,9 +10420,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A184" s="16"/>
-      <c r="B184" s="38" t="s">
+      <c r="B184" s="14" t="s">
         <v>55</v>
       </c>
       <c r="C184" s="16"/>
@@ -10398,9 +10431,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A185" s="16"/>
-      <c r="B185" s="38" t="s">
+      <c r="B185" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C185" s="16"/>
@@ -10409,9 +10442,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A186" s="16"/>
-      <c r="B186" s="38" t="s">
+      <c r="B186" s="14" t="s">
         <v>138</v>
       </c>
       <c r="C186" s="16"/>
@@ -10420,9 +10453,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A187" s="16"/>
-      <c r="B187" s="38" t="s">
+      <c r="B187" s="14" t="s">
         <v>139</v>
       </c>
       <c r="C187" s="16"/>
@@ -10431,9 +10464,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A188" s="16"/>
-      <c r="B188" s="38" t="s">
+      <c r="B188" s="14" t="s">
         <v>140</v>
       </c>
       <c r="C188" s="16"/>
@@ -10442,9 +10475,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A189" s="16"/>
-      <c r="B189" s="38" t="s">
+      <c r="B189" s="14" t="s">
         <v>141</v>
       </c>
       <c r="C189" s="16"/>
@@ -10453,7 +10486,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A190" s="16"/>
       <c r="B190" s="14"/>
       <c r="C190" s="22" t="s">
@@ -10465,7 +10498,7 @@
       </c>
       <c r="E190" s="14"/>
     </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.45">
       <c r="D191">
         <f>-SUM(D180:D190)</f>
         <v>0</v>
@@ -10475,7 +10508,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A194" s="7" t="s">
         <v>171</v>
       </c>
@@ -10490,7 +10523,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A195" s="7"/>
       <c r="B195" s="8"/>
       <c r="C195" s="8" t="s">
@@ -10501,7 +10534,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A196" s="7"/>
       <c r="B196" s="8"/>
       <c r="C196" s="8" t="s">
@@ -10512,7 +10545,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A197" s="7"/>
       <c r="B197" s="8" t="s">
         <v>176</v>
@@ -10525,7 +10558,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A198" s="7"/>
       <c r="B198" s="8"/>
       <c r="C198" s="8" t="s">
@@ -10536,7 +10569,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A199" s="7"/>
       <c r="B199" s="8"/>
       <c r="C199" s="8" t="s">
@@ -10547,7 +10580,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A200" s="7"/>
       <c r="B200" s="8"/>
       <c r="C200" s="8" t="s">
@@ -10558,7 +10591,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A201" s="7"/>
       <c r="B201" s="8"/>
       <c r="C201" s="8" t="s">
@@ -10569,7 +10602,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A202" s="7"/>
       <c r="B202" s="8" t="s">
         <v>182</v>
@@ -10580,7 +10613,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A203" s="7"/>
       <c r="B203" s="8" t="s">
         <v>204</v>
@@ -10593,7 +10626,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A204" s="7"/>
       <c r="B204" s="8"/>
       <c r="C204" s="8" t="s">
@@ -10604,7 +10637,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A205" s="7"/>
       <c r="B205" s="8"/>
       <c r="C205" s="8" t="s">
@@ -10615,7 +10648,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A206" s="7"/>
       <c r="B206" s="8"/>
       <c r="C206" s="8" t="s">
@@ -10626,7 +10659,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A207" s="7"/>
       <c r="B207" s="8" t="str">
         <f>Report!B408</f>
@@ -10641,7 +10674,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A208" s="7"/>
       <c r="B208" s="8"/>
       <c r="C208" s="8" t="str">
@@ -10653,7 +10686,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A209" s="7"/>
       <c r="B209" s="8"/>
       <c r="C209" s="8" t="str">
@@ -10665,7 +10698,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A210" s="7"/>
       <c r="B210" s="8"/>
       <c r="C210" s="8" t="str">
@@ -10677,7 +10710,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A211" s="7"/>
       <c r="B211" s="8"/>
       <c r="C211" s="8" t="str">
@@ -10689,7 +10722,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A212" s="7"/>
       <c r="B212" s="8"/>
       <c r="C212" s="22" t="s">
@@ -10701,7 +10734,7 @@
       </c>
       <c r="E212" s="8"/>
     </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:7" x14ac:dyDescent="0.45">
       <c r="D213">
         <f>-SUM(D194:D212)</f>
         <v>0</v>
@@ -10711,7 +10744,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A218" s="7"/>
       <c r="B218" t="s">
         <v>213</v>
@@ -10729,7 +10762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A219" s="11" t="s">
         <v>395</v>
       </c>
@@ -10749,7 +10782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A220" s="15" t="s">
         <v>403</v>
       </c>
@@ -10769,7 +10802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A221" s="16" t="s">
         <v>396</v>
       </c>
@@ -10789,7 +10822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="4:7" x14ac:dyDescent="0.2">
+    <row r="226" spans="4:7" x14ac:dyDescent="0.45">
       <c r="F226" t="s">
         <v>260</v>
       </c>
@@ -10797,7 +10830,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="227" spans="4:7" x14ac:dyDescent="0.2">
+    <row r="227" spans="4:7" x14ac:dyDescent="0.45">
       <c r="D227" t="s">
         <v>262</v>
       </c>
@@ -10805,7 +10838,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="228" spans="4:7" x14ac:dyDescent="0.2">
+    <row r="228" spans="4:7" x14ac:dyDescent="0.45">
       <c r="F228">
         <v>45</v>
       </c>
@@ -10813,7 +10846,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="229" spans="4:7" x14ac:dyDescent="0.2">
+    <row r="229" spans="4:7" x14ac:dyDescent="0.45">
       <c r="F229">
         <f>F228+(F237-F228)/9</f>
         <v>50</v>
@@ -10822,7 +10855,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="230" spans="4:7" x14ac:dyDescent="0.2">
+    <row r="230" spans="4:7" x14ac:dyDescent="0.45">
       <c r="F230">
         <f>F229+(F237-F228)/9</f>
         <v>55</v>
@@ -10831,7 +10864,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="231" spans="4:7" x14ac:dyDescent="0.2">
+    <row r="231" spans="4:7" x14ac:dyDescent="0.45">
       <c r="F231">
         <f>F230+(F237-F228)/9</f>
         <v>60</v>
@@ -10840,7 +10873,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="232" spans="4:7" x14ac:dyDescent="0.2">
+    <row r="232" spans="4:7" x14ac:dyDescent="0.45">
       <c r="F232">
         <f>F231+(F237-F228)/9</f>
         <v>65</v>
@@ -10849,7 +10882,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="233" spans="4:7" x14ac:dyDescent="0.2">
+    <row r="233" spans="4:7" x14ac:dyDescent="0.45">
       <c r="F233">
         <f>F232+(F237-F228)/9</f>
         <v>70</v>
@@ -10858,7 +10891,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="234" spans="4:7" x14ac:dyDescent="0.2">
+    <row r="234" spans="4:7" x14ac:dyDescent="0.45">
       <c r="F234">
         <f>F233+(F237-F228)/9</f>
         <v>75</v>
@@ -10867,7 +10900,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="235" spans="4:7" x14ac:dyDescent="0.2">
+    <row r="235" spans="4:7" x14ac:dyDescent="0.45">
       <c r="F235">
         <f>F234+(F237-F228)/9</f>
         <v>80</v>
@@ -10876,7 +10909,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="236" spans="4:7" x14ac:dyDescent="0.2">
+    <row r="236" spans="4:7" x14ac:dyDescent="0.45">
       <c r="F236">
         <f>F235+(F237-F228)/9</f>
         <v>85</v>
@@ -10885,7 +10918,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="237" spans="4:7" x14ac:dyDescent="0.2">
+    <row r="237" spans="4:7" x14ac:dyDescent="0.45">
       <c r="F237">
         <v>90</v>
       </c>
@@ -10893,12 +10926,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="238" spans="4:7" x14ac:dyDescent="0.2">
+    <row r="238" spans="4:7" x14ac:dyDescent="0.45">
       <c r="E238" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="1047724" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="1047724" spans="5:5" x14ac:dyDescent="0.45">
       <c r="E1047724" s="8"/>
     </row>
   </sheetData>
@@ -10922,25 +10955,25 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D37"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.46484375" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="35.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5" style="20"/>
+    <col min="2" max="2" width="35.796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.46484375" style="20"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="36" t="s">
+    <row r="1" spans="1:4" ht="25.5" x14ac:dyDescent="0.75">
+      <c r="A1" s="37" t="s">
         <v>253</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A2" s="1"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B4" t="s">
         <v>237</v>
       </c>
@@ -10948,7 +10981,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
         <v>42</v>
       </c>
@@ -10956,7 +10989,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B6" t="s">
         <v>239</v>
       </c>
@@ -10964,7 +10997,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B7" t="s">
         <v>240</v>
       </c>
@@ -10972,7 +11005,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B8" t="s">
         <v>241</v>
       </c>
@@ -10980,7 +11013,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
         <v>242</v>
       </c>
@@ -10988,7 +11021,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
         <v>204</v>
       </c>
@@ -10996,7 +11029,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
         <v>238</v>
       </c>
@@ -11004,7 +11037,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
         <v>244</v>
       </c>
@@ -11012,7 +11045,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
         <v>243</v>
       </c>
@@ -11020,7 +11053,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
         <v>245</v>
       </c>
@@ -11028,7 +11061,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
         <v>246</v>
       </c>
@@ -11036,7 +11069,7 @@
         <v>-0.3</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
         <v>252</v>
       </c>
@@ -11044,7 +11077,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B17" t="s">
         <v>254</v>
       </c>
@@ -11052,7 +11085,7 @@
         <v>-0.2</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B18" t="s">
         <v>255</v>
       </c>
@@ -11060,7 +11093,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>42</v>
       </c>
@@ -11074,7 +11107,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
       <c r="C23" t="s">
         <v>174</v>
       </c>
@@ -11082,7 +11115,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
       <c r="C24" t="s">
         <v>175</v>
       </c>
@@ -11090,7 +11123,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B25" t="s">
         <v>176</v>
       </c>
@@ -11101,7 +11134,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
       <c r="C26" t="s">
         <v>178</v>
       </c>
@@ -11109,7 +11142,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
       <c r="C27" t="s">
         <v>179</v>
       </c>
@@ -11117,7 +11150,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
       <c r="C28" t="s">
         <v>180</v>
       </c>
@@ -11125,12 +11158,12 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B30" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B31" t="s">
         <v>192</v>
       </c>
@@ -11141,7 +11174,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
       <c r="C32" t="s">
         <v>196</v>
       </c>
@@ -11149,7 +11182,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:4" x14ac:dyDescent="0.45">
       <c r="C33" t="s">
         <v>179</v>
       </c>
@@ -11157,7 +11190,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B34" t="s">
         <v>250</v>
       </c>
@@ -11165,7 +11198,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B35" t="s">
         <v>197</v>
       </c>
@@ -11176,7 +11209,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:4" x14ac:dyDescent="0.45">
       <c r="C36" t="s">
         <v>199</v>
       </c>
@@ -11184,7 +11217,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:4" x14ac:dyDescent="0.45">
       <c r="C37" t="s">
         <v>200</v>
       </c>

--- a/ProjectManagement/EvaluationHWAndProject.xlsx
+++ b/ProjectManagement/EvaluationHWAndProject.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\ML26-03-Car-Licence-Plate-Identification-with-a-Jetson-Nano\ProjectManagement\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\gthub\ML26-03-Car-Licence-Plate-Identification-with-a-Jetson-Nano\ProjectManagement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07C1DF9F-AF02-47B7-8AAF-B207F8925BAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39945EBF-606D-4BF5-A2DB-67107DFF197C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Report" sheetId="2" r:id="rId1"/>
@@ -274,7 +274,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="896" uniqueCount="414">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="906" uniqueCount="424">
   <si>
     <t>Literature</t>
   </si>
@@ -1516,6 +1516,36 @@
   </si>
   <si>
     <t>added a physical/GUI "Safe Shutdown" button.</t>
+  </si>
+  <si>
+    <t>Contents Section matches Evaluation Sheet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Report sections were always created and formatted in such a way that they map to the evaluation sheet directly. The contents section and the evaluation sheet are coherent. </t>
+  </si>
+  <si>
+    <t>Timely Project Management and Follow up</t>
+  </si>
+  <si>
+    <t>Ensured timelines and delivarables aren’t missed and processes are checked and documented thoroughly</t>
+  </si>
+  <si>
+    <t>Ensured all documents are high quality, adhereing to structural suggestions and following guidelines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clean templating, structuring of presentations, reports, files. </t>
+  </si>
+  <si>
+    <t>Ensured clarity with respect to processes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I was able to contribute to a very positive enviroment within the team, this made our thought processes clear. </t>
+  </si>
+  <si>
+    <t>Ensured tikz diagrams are heavily used in the report</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Encouraged colleagues to create meaningful tikz diagrams outlining key processes. </t>
   </si>
 </sst>
 </file>
@@ -1730,7 +1760,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1798,6 +1828,33 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2080,45 +2137,45 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:M575"/>
-  <sheetFormatPr defaultColWidth="11.46484375" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.46484375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.1328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.53125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="39.21875" customWidth="1"/>
+    <col min="3" max="3" width="28.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="39.21875" style="38" customWidth="1"/>
+    <col min="5" max="5" width="13.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:6" ht="33.4" x14ac:dyDescent="1">
+    <row r="2" spans="1:6" ht="33.6" x14ac:dyDescent="0.65">
       <c r="A2" s="29" t="s">
         <v>392</v>
       </c>
       <c r="B2" s="29"/>
       <c r="C2" s="29"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="30" t="s">
         <v>393</v>
       </c>
       <c r="B6" s="30"/>
       <c r="C6" s="30"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="28.5" x14ac:dyDescent="0.85">
+    <row r="9" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="2" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>84</v>
       </c>
@@ -2128,14 +2185,14 @@
       <c r="C10" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="39" t="s">
         <v>87</v>
       </c>
       <c r="F10" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>397</v>
       </c>
@@ -2145,14 +2202,14 @@
       <c r="C11" s="3">
         <v>7026787</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="38" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="C12" s="3"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>88</v>
       </c>
@@ -2160,7 +2217,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>89</v>
       </c>
@@ -2168,7 +2225,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>90</v>
       </c>
@@ -2176,7 +2233,7 @@
         <v>45924</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>91</v>
       </c>
@@ -2184,7 +2241,7 @@
         <v>46051</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>92</v>
       </c>
@@ -2192,7 +2249,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>93</v>
       </c>
@@ -2200,12 +2257,12 @@
         <v>218</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="23.25" x14ac:dyDescent="0.7">
+    <row r="25" spans="1:8" ht="23.4" x14ac:dyDescent="0.45">
       <c r="A25" s="6" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:8" ht="18" x14ac:dyDescent="0.35">
       <c r="A27" s="5" t="s">
         <v>95</v>
       </c>
@@ -2213,13 +2270,13 @@
         <v>96</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="13"/>
       <c r="B28" s="13" t="s">
         <v>166</v>
       </c>
       <c r="C28" s="13"/>
-      <c r="D28" s="13"/>
+      <c r="D28" s="40"/>
       <c r="E28" s="13">
         <v>-25</v>
       </c>
@@ -2230,13 +2287,13 @@
         <v>390</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="14"/>
       <c r="B29" s="14" t="s">
         <v>166</v>
       </c>
       <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
+      <c r="D29" s="24"/>
       <c r="E29" s="14">
         <v>-25</v>
       </c>
@@ -2247,13 +2304,13 @@
         <v>390</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="12"/>
       <c r="B30" s="12" t="s">
         <v>166</v>
       </c>
       <c r="C30" s="12"/>
-      <c r="D30" s="12"/>
+      <c r="D30" s="41"/>
       <c r="E30" s="12">
         <v>-25</v>
       </c>
@@ -2264,13 +2321,13 @@
         <v>390</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="12"/>
       <c r="B31" s="12" t="s">
         <v>167</v>
       </c>
       <c r="C31" s="12"/>
-      <c r="D31" s="12"/>
+      <c r="D31" s="41"/>
       <c r="E31" s="12">
         <v>-25</v>
       </c>
@@ -2281,13 +2338,13 @@
         <v>391</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="14"/>
       <c r="B32" s="14" t="s">
         <v>167</v>
       </c>
       <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
+      <c r="D32" s="24"/>
       <c r="E32" s="14">
         <v>-25</v>
       </c>
@@ -2298,13 +2355,13 @@
         <v>391</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="13"/>
       <c r="B33" s="13" t="s">
         <v>167</v>
       </c>
       <c r="C33" s="13"/>
-      <c r="D33" s="13"/>
+      <c r="D33" s="40"/>
       <c r="E33" s="13">
         <v>-25</v>
       </c>
@@ -2315,102 +2372,102 @@
         <v>391</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="21" x14ac:dyDescent="0.65">
+    <row r="35" spans="1:8" ht="21" x14ac:dyDescent="0.4">
       <c r="A35" s="23" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="15" t="s">
         <v>0</v>
       </c>
       <c r="B36" s="13"/>
       <c r="C36" s="13"/>
-      <c r="D36" s="13"/>
+      <c r="D36" s="40"/>
       <c r="E36" s="13"/>
       <c r="F36" s="13"/>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="15"/>
       <c r="B37" s="13" t="s">
         <v>3</v>
       </c>
       <c r="C37" s="13"/>
-      <c r="D37" s="13"/>
+      <c r="D37" s="40"/>
       <c r="E37" s="13"/>
       <c r="F37" s="13">
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="13"/>
       <c r="B38" s="13" t="s">
         <v>28</v>
       </c>
       <c r="C38" s="13"/>
-      <c r="D38" s="13"/>
+      <c r="D38" s="40"/>
       <c r="E38" s="13"/>
       <c r="F38" s="13">
         <v>10</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="13"/>
       <c r="B39" s="13" t="s">
         <v>4</v>
       </c>
       <c r="C39" s="13"/>
-      <c r="D39" s="13"/>
+      <c r="D39" s="40"/>
       <c r="E39" s="13"/>
       <c r="F39" s="13">
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="13"/>
       <c r="B40" s="13" t="s">
         <v>5</v>
       </c>
       <c r="C40" s="13"/>
-      <c r="D40" s="13"/>
+      <c r="D40" s="40"/>
       <c r="E40" s="13"/>
       <c r="F40" s="13">
         <v>10</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="13"/>
       <c r="B41" s="13" t="s">
         <v>6</v>
       </c>
       <c r="C41" s="13"/>
-      <c r="D41" s="13"/>
+      <c r="D41" s="40"/>
       <c r="E41" s="13"/>
       <c r="F41" s="13">
         <v>10</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="13"/>
       <c r="B42" s="13" t="s">
         <v>1</v>
       </c>
       <c r="C42" s="13"/>
-      <c r="D42" s="13"/>
+      <c r="D42" s="40"/>
       <c r="E42" s="13"/>
       <c r="F42" s="13">
         <v>10</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="15"/>
       <c r="B43" s="13"/>
       <c r="C43" s="13"/>
-      <c r="D43" s="13"/>
+      <c r="D43" s="40"/>
       <c r="E43" s="13"/>
       <c r="F43" s="13"/>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="15"/>
       <c r="B44" s="13" t="s">
         <v>2</v>
@@ -2418,89 +2475,89 @@
       <c r="C44" s="13" t="s">
         <v>257</v>
       </c>
-      <c r="D44" s="13"/>
+      <c r="D44" s="40"/>
       <c r="E44" s="13"/>
       <c r="F44" s="13">
         <v>4</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="13"/>
       <c r="B45" s="13"/>
       <c r="C45" s="13" t="s">
         <v>201</v>
       </c>
-      <c r="D45" s="13"/>
+      <c r="D45" s="40"/>
       <c r="E45" s="13"/>
       <c r="F45" s="13">
         <v>6</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="13"/>
       <c r="B46" s="13"/>
       <c r="C46" s="13" t="s">
         <v>202</v>
       </c>
-      <c r="D46" s="13"/>
+      <c r="D46" s="40"/>
       <c r="E46" s="13"/>
       <c r="F46" s="13">
         <v>10</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="13"/>
       <c r="B47" s="13"/>
       <c r="C47" s="13" t="s">
         <v>203</v>
       </c>
-      <c r="D47" s="13"/>
+      <c r="D47" s="40"/>
       <c r="E47" s="13"/>
       <c r="F47" s="13">
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="13"/>
       <c r="B48" s="13"/>
       <c r="C48" s="13" t="s">
         <v>256</v>
       </c>
-      <c r="D48" s="13"/>
+      <c r="D48" s="40"/>
       <c r="E48" s="13"/>
       <c r="F48" s="13">
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" s="13"/>
       <c r="B49" s="13"/>
       <c r="C49" s="13" t="s">
         <v>198</v>
       </c>
-      <c r="D49" s="13"/>
+      <c r="D49" s="40"/>
       <c r="E49" s="13"/>
       <c r="F49" s="13">
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="13"/>
       <c r="B50" s="13"/>
       <c r="C50" s="13" t="s">
         <v>199</v>
       </c>
-      <c r="D50" s="13"/>
+      <c r="D50" s="40"/>
       <c r="E50" s="13"/>
       <c r="F50" s="13">
         <v>5</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" s="13"/>
       <c r="B51" s="13"/>
       <c r="C51" s="13"/>
-      <c r="D51" s="22" t="s">
+      <c r="D51" s="42" t="s">
         <v>389</v>
       </c>
       <c r="E51" s="28">
@@ -2508,7 +2565,7 @@
       </c>
       <c r="F51" s="13"/>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="E52">
         <f>SUM(E36:E50)*E51</f>
         <v>0</v>
@@ -2518,12 +2575,13 @@
         <v>100</v>
       </c>
     </row>
-    <row r="54" spans="1:7" s="5" customFormat="1" ht="21" x14ac:dyDescent="0.65">
+    <row r="54" spans="1:7" s="5" customFormat="1" ht="21" x14ac:dyDescent="0.4">
       <c r="A54" s="23" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="D54" s="43"/>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" s="16" t="s">
         <v>135</v>
       </c>
@@ -2531,7 +2589,7 @@
         <v>316</v>
       </c>
       <c r="C55" s="14"/>
-      <c r="D55" s="14"/>
+      <c r="D55" s="24"/>
       <c r="E55" s="14"/>
       <c r="F55" s="14">
         <v>10</v>
@@ -2540,167 +2598,167 @@
         <v>109</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" s="16"/>
       <c r="B56" s="14" t="s">
         <v>50</v>
       </c>
       <c r="C56" s="14"/>
-      <c r="D56" s="14"/>
+      <c r="D56" s="24"/>
       <c r="E56" s="14"/>
       <c r="F56" s="14">
         <v>5</v>
       </c>
       <c r="G56" s="31"/>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" s="16"/>
       <c r="B57" s="14" t="s">
         <v>233</v>
       </c>
       <c r="C57" s="14"/>
-      <c r="D57" s="14"/>
+      <c r="D57" s="24"/>
       <c r="E57" s="14"/>
       <c r="F57" s="14">
         <v>5</v>
       </c>
       <c r="G57" s="31"/>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" s="16"/>
       <c r="B58" s="14" t="s">
         <v>136</v>
       </c>
       <c r="C58" s="14"/>
-      <c r="D58" s="14"/>
+      <c r="D58" s="24"/>
       <c r="E58" s="14"/>
       <c r="F58" s="14">
         <v>5</v>
       </c>
       <c r="G58" s="31"/>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" s="16"/>
       <c r="B59" s="14" t="s">
         <v>137</v>
       </c>
       <c r="C59" s="14"/>
-      <c r="D59" s="14"/>
+      <c r="D59" s="24"/>
       <c r="E59" s="14"/>
       <c r="F59" s="14">
         <v>10</v>
       </c>
       <c r="G59" s="31"/>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" s="16"/>
       <c r="B60" s="14" t="s">
         <v>55</v>
       </c>
       <c r="C60" s="14"/>
-      <c r="D60" s="14"/>
+      <c r="D60" s="24"/>
       <c r="E60" s="14"/>
       <c r="F60" s="14">
         <v>5</v>
       </c>
       <c r="G60" s="31"/>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" s="16"/>
       <c r="B61" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C61" s="14"/>
-      <c r="D61" s="14"/>
+      <c r="D61" s="24"/>
       <c r="E61" s="14"/>
       <c r="F61" s="14">
         <v>10</v>
       </c>
       <c r="G61" s="31"/>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" s="16"/>
       <c r="B62" s="14" t="s">
         <v>138</v>
       </c>
       <c r="C62" s="14"/>
-      <c r="D62" s="14"/>
+      <c r="D62" s="24"/>
       <c r="E62" s="14"/>
       <c r="F62" s="14">
         <v>5</v>
       </c>
       <c r="G62" s="31"/>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" s="16"/>
       <c r="B63" s="14" t="s">
         <v>139</v>
       </c>
       <c r="C63" s="14"/>
-      <c r="D63" s="14"/>
+      <c r="D63" s="24"/>
       <c r="E63" s="14"/>
       <c r="F63" s="14">
         <v>5</v>
       </c>
       <c r="G63" s="31"/>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" s="16"/>
       <c r="B64" s="14" t="s">
         <v>140</v>
       </c>
       <c r="C64" s="14"/>
-      <c r="D64" s="14"/>
+      <c r="D64" s="24"/>
       <c r="E64" s="14"/>
       <c r="F64" s="14">
         <v>5</v>
       </c>
       <c r="G64" s="31"/>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" s="16"/>
       <c r="B65" s="14" t="s">
         <v>323</v>
       </c>
       <c r="C65" s="14"/>
-      <c r="D65" s="14"/>
+      <c r="D65" s="24"/>
       <c r="E65" s="14"/>
       <c r="F65" s="14">
         <v>5</v>
       </c>
       <c r="G65" s="31"/>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" s="16"/>
       <c r="B66" s="14" t="s">
         <v>324</v>
       </c>
       <c r="C66" s="14"/>
-      <c r="D66" s="14"/>
+      <c r="D66" s="24"/>
       <c r="E66" s="14"/>
       <c r="F66" s="14">
         <v>5</v>
       </c>
       <c r="G66" s="31"/>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" s="16"/>
       <c r="B67" s="14" t="s">
         <v>141</v>
       </c>
       <c r="C67" s="14"/>
-      <c r="D67" s="14"/>
+      <c r="D67" s="24"/>
       <c r="E67" s="14"/>
       <c r="F67" s="14">
         <v>5</v>
       </c>
       <c r="G67" s="31"/>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" s="16"/>
       <c r="B68" s="14"/>
       <c r="C68" s="14"/>
-      <c r="D68" s="22" t="s">
+      <c r="D68" s="42" t="s">
         <v>389</v>
       </c>
       <c r="E68" s="28">
@@ -2709,7 +2767,7 @@
       <c r="F68" s="14"/>
       <c r="G68" s="31"/>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" s="1"/>
       <c r="E69">
         <f>-SUM(E55:E67)*E68</f>
@@ -2720,12 +2778,13 @@
         <v>80</v>
       </c>
     </row>
-    <row r="70" spans="1:7" s="5" customFormat="1" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:7" s="5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A70" s="5" t="s">
         <v>343</v>
       </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="D70" s="43"/>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" s="16" t="s">
         <v>135</v>
       </c>
@@ -2733,7 +2792,7 @@
         <v>316</v>
       </c>
       <c r="C71" s="14"/>
-      <c r="D71" s="14"/>
+      <c r="D71" s="24"/>
       <c r="E71" s="14"/>
       <c r="F71" s="14">
         <v>10</v>
@@ -2742,76 +2801,76 @@
         <v>109</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" s="16"/>
       <c r="B72" s="14" t="s">
         <v>46</v>
       </c>
       <c r="C72" s="14"/>
-      <c r="D72" s="14"/>
+      <c r="D72" s="24"/>
       <c r="E72" s="14"/>
       <c r="F72" s="14">
         <v>5</v>
       </c>
       <c r="G72" s="34"/>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" s="16"/>
       <c r="B73" s="14" t="s">
         <v>344</v>
       </c>
       <c r="C73" s="14"/>
-      <c r="D73" s="14"/>
+      <c r="D73" s="24"/>
       <c r="E73" s="14"/>
       <c r="F73" s="14">
         <v>5</v>
       </c>
       <c r="G73" s="34"/>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" s="16"/>
       <c r="B74" s="14" t="s">
         <v>70</v>
       </c>
       <c r="C74" s="14"/>
-      <c r="D74" s="14"/>
+      <c r="D74" s="24"/>
       <c r="E74" s="14"/>
       <c r="F74" s="14">
         <v>5</v>
       </c>
       <c r="G74" s="34"/>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" s="16"/>
       <c r="B75" s="14" t="s">
         <v>345</v>
       </c>
       <c r="C75" s="14"/>
-      <c r="D75" s="14"/>
+      <c r="D75" s="24"/>
       <c r="E75" s="14"/>
       <c r="F75" s="14">
         <v>10</v>
       </c>
       <c r="G75" s="34"/>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" s="16"/>
       <c r="B76" s="14" t="s">
         <v>346</v>
       </c>
       <c r="C76" s="14"/>
-      <c r="D76" s="14"/>
+      <c r="D76" s="24"/>
       <c r="E76" s="14"/>
       <c r="F76" s="14">
         <v>5</v>
       </c>
       <c r="G76" s="34"/>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" s="16"/>
       <c r="B77" s="14"/>
       <c r="C77" s="14"/>
-      <c r="D77" s="22" t="s">
+      <c r="D77" s="42" t="s">
         <v>389</v>
       </c>
       <c r="E77" s="28">
@@ -2820,7 +2879,7 @@
       <c r="F77" s="14"/>
       <c r="G77" s="34"/>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" s="1"/>
       <c r="E78">
         <f>-SUM(E71:E76)*E77</f>
@@ -2831,15 +2890,15 @@
         <v>40</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" s="1"/>
     </row>
-    <row r="80" spans="1:7" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A80" s="5" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" s="7" t="s">
         <v>380</v>
       </c>
@@ -2849,7 +2908,7 @@
       <c r="C81" s="8" t="s">
         <v>316</v>
       </c>
-      <c r="D81" s="8"/>
+      <c r="D81" s="44"/>
       <c r="E81" s="8"/>
       <c r="F81" s="8">
         <v>0</v>
@@ -2858,7 +2917,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" s="7"/>
       <c r="B82" s="7" t="s">
         <v>382</v>
@@ -2866,44 +2925,44 @@
       <c r="C82" s="8" t="s">
         <v>383</v>
       </c>
-      <c r="D82" s="8"/>
+      <c r="D82" s="44"/>
       <c r="E82" s="8"/>
       <c r="F82" s="8">
         <v>30</v>
       </c>
       <c r="G82" s="35"/>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" s="7"/>
       <c r="B83" s="7"/>
       <c r="C83" s="8" t="s">
         <v>384</v>
       </c>
-      <c r="D83" s="8"/>
+      <c r="D83" s="44"/>
       <c r="E83" s="8"/>
       <c r="F83" s="8">
         <v>10</v>
       </c>
       <c r="G83" s="35"/>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" s="7"/>
       <c r="B84" s="7"/>
       <c r="C84" s="8" t="s">
         <v>385</v>
       </c>
-      <c r="D84" s="8"/>
+      <c r="D84" s="44"/>
       <c r="E84" s="8"/>
       <c r="F84" s="8">
         <v>10</v>
       </c>
       <c r="G84" s="35"/>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" s="7"/>
       <c r="B85" s="7"/>
       <c r="C85" s="7"/>
-      <c r="D85" s="22" t="s">
+      <c r="D85" s="42" t="s">
         <v>389</v>
       </c>
       <c r="E85" s="28">
@@ -2912,7 +2971,7 @@
       <c r="F85" s="7"/>
       <c r="G85" s="35"/>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="E86">
@@ -2924,15 +2983,15 @@
         <v>50</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" s="1"/>
     </row>
-    <row r="88" spans="1:7" ht="21" x14ac:dyDescent="0.65">
+    <row r="88" spans="1:7" ht="21" x14ac:dyDescent="0.4">
       <c r="A88" s="23" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" s="15" t="s">
         <v>317</v>
       </c>
@@ -2940,89 +2999,89 @@
         <v>316</v>
       </c>
       <c r="C89" s="13"/>
-      <c r="D89" s="13"/>
+      <c r="D89" s="40"/>
       <c r="E89" s="13"/>
       <c r="F89" s="13">
         <v>10</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" s="15"/>
       <c r="B90" s="13" t="s">
         <v>131</v>
       </c>
       <c r="C90" s="13"/>
-      <c r="D90" s="13"/>
+      <c r="D90" s="40"/>
       <c r="E90" s="13"/>
       <c r="F90" s="13">
         <v>5</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" s="15"/>
       <c r="B91" s="13" t="s">
         <v>235</v>
       </c>
       <c r="C91" s="13"/>
-      <c r="D91" s="13"/>
+      <c r="D91" s="40"/>
       <c r="E91" s="13"/>
       <c r="F91" s="13">
         <v>5</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" s="15"/>
       <c r="B92" s="13" t="s">
         <v>8</v>
       </c>
       <c r="C92" s="13"/>
-      <c r="D92" s="13"/>
+      <c r="D92" s="40"/>
       <c r="E92" s="13"/>
       <c r="F92" s="13">
         <v>5</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" s="15"/>
       <c r="B93" s="13" t="s">
         <v>132</v>
       </c>
       <c r="C93" s="13"/>
-      <c r="D93" s="13"/>
+      <c r="D93" s="40"/>
       <c r="E93" s="13"/>
       <c r="F93" s="13">
         <v>5</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" s="15"/>
       <c r="B94" s="13" t="s">
         <v>133</v>
       </c>
       <c r="C94" s="13"/>
-      <c r="D94" s="13"/>
+      <c r="D94" s="40"/>
       <c r="E94" s="13"/>
       <c r="F94" s="13">
         <v>5</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" s="15"/>
       <c r="B95" s="13" t="s">
         <v>134</v>
       </c>
       <c r="C95" s="13"/>
-      <c r="D95" s="13"/>
+      <c r="D95" s="40"/>
       <c r="E95" s="13"/>
       <c r="F95" s="13">
         <v>5</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" s="15"/>
       <c r="B96" s="13"/>
       <c r="C96" s="13"/>
-      <c r="D96" s="22" t="s">
+      <c r="D96" s="42" t="s">
         <v>389</v>
       </c>
       <c r="E96" s="28">
@@ -3030,7 +3089,7 @@
       </c>
       <c r="F96" s="13"/>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97" s="1"/>
       <c r="E97">
         <f>SUM(E89:E95)*E96</f>
@@ -3041,18 +3100,18 @@
         <v>40</v>
       </c>
     </row>
-    <row r="98" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="99" spans="1:6" ht="21" x14ac:dyDescent="0.65">
+    <row r="98" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="99" spans="1:6" ht="21" x14ac:dyDescent="0.4">
       <c r="A99" s="23" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="100" spans="1:6" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="100" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A100" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A101" s="15" t="s">
         <v>7</v>
       </c>
@@ -3060,77 +3119,77 @@
         <v>8</v>
       </c>
       <c r="C101" s="13"/>
-      <c r="D101" s="13"/>
+      <c r="D101" s="40"/>
       <c r="E101" s="13"/>
       <c r="F101" s="13">
         <v>5</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A102" s="13"/>
       <c r="B102" s="13" t="s">
         <v>9</v>
       </c>
       <c r="C102" s="13"/>
-      <c r="D102" s="13"/>
+      <c r="D102" s="40"/>
       <c r="E102" s="13"/>
       <c r="F102" s="13">
         <v>5</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103" s="13"/>
       <c r="B103" s="13" t="s">
         <v>10</v>
       </c>
       <c r="C103" s="13"/>
-      <c r="D103" s="13"/>
+      <c r="D103" s="40"/>
       <c r="E103" s="13"/>
       <c r="F103" s="13">
         <v>5</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A104" s="13"/>
       <c r="B104" s="13" t="s">
         <v>11</v>
       </c>
       <c r="C104" s="13"/>
-      <c r="D104" s="13"/>
+      <c r="D104" s="40"/>
       <c r="E104" s="13"/>
       <c r="F104" s="13">
         <v>10</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105" s="13"/>
       <c r="B105" s="13" t="s">
         <v>12</v>
       </c>
       <c r="C105" s="13"/>
-      <c r="D105" s="13"/>
+      <c r="D105" s="40"/>
       <c r="E105" s="13"/>
       <c r="F105" s="13">
         <v>5</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106" s="13"/>
       <c r="B106" s="13" t="s">
         <v>100</v>
       </c>
       <c r="C106" s="13"/>
-      <c r="D106" s="13"/>
+      <c r="D106" s="40"/>
       <c r="E106" s="13"/>
       <c r="F106" s="13">
         <v>5</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107" s="13"/>
       <c r="B107" s="13"/>
       <c r="C107" s="13"/>
-      <c r="D107" s="22" t="s">
+      <c r="D107" s="42" t="s">
         <v>389</v>
       </c>
       <c r="E107" s="28">
@@ -3138,7 +3197,7 @@
       </c>
       <c r="F107" s="13"/>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E108">
         <f>SUM(E101:E106)*E107</f>
         <v>0</v>
@@ -3148,12 +3207,12 @@
         <v>35</v>
       </c>
     </row>
-    <row r="110" spans="1:6" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="110" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A110" s="5" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A111" s="16" t="s">
         <v>275</v>
       </c>
@@ -3161,101 +3220,101 @@
         <v>307</v>
       </c>
       <c r="C111" s="14"/>
-      <c r="D111" s="14"/>
+      <c r="D111" s="24"/>
       <c r="E111" s="14"/>
       <c r="F111" s="14">
         <v>5</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A112" s="16"/>
       <c r="B112" s="14" t="s">
         <v>14</v>
       </c>
       <c r="C112" s="14"/>
-      <c r="D112" s="14"/>
+      <c r="D112" s="24"/>
       <c r="E112" s="14"/>
       <c r="F112" s="14">
         <v>5</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" s="14"/>
       <c r="B113" s="14" t="s">
         <v>15</v>
       </c>
       <c r="C113" s="14"/>
-      <c r="D113" s="14"/>
+      <c r="D113" s="24"/>
       <c r="E113" s="14"/>
       <c r="F113" s="14">
         <v>5</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114" s="14"/>
       <c r="B114" s="14" t="s">
         <v>16</v>
       </c>
       <c r="C114" s="14"/>
-      <c r="D114" s="14"/>
+      <c r="D114" s="24"/>
       <c r="E114" s="14"/>
       <c r="F114" s="14">
         <v>5</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A115" s="14"/>
       <c r="B115" s="14" t="s">
         <v>17</v>
       </c>
       <c r="C115" s="14"/>
-      <c r="D115" s="14"/>
+      <c r="D115" s="24"/>
       <c r="E115" s="14"/>
       <c r="F115" s="14">
         <v>5</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116" s="14"/>
       <c r="B116" s="14" t="s">
         <v>18</v>
       </c>
       <c r="C116" s="14"/>
-      <c r="D116" s="14"/>
+      <c r="D116" s="24"/>
       <c r="E116" s="14"/>
       <c r="F116" s="14">
         <v>5</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A117" s="14"/>
       <c r="B117" s="14" t="s">
         <v>20</v>
       </c>
       <c r="C117" s="14"/>
-      <c r="D117" s="14"/>
+      <c r="D117" s="24"/>
       <c r="E117" s="14"/>
       <c r="F117" s="14">
         <v>5</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A118" s="14"/>
       <c r="B118" s="24" t="s">
         <v>19</v>
       </c>
       <c r="C118" s="14"/>
-      <c r="D118" s="14"/>
+      <c r="D118" s="24"/>
       <c r="E118" s="14"/>
       <c r="F118" s="14">
         <v>5</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A119" s="14"/>
       <c r="B119" s="24"/>
       <c r="C119" s="14"/>
-      <c r="D119" s="22" t="s">
+      <c r="D119" s="42" t="s">
         <v>389</v>
       </c>
       <c r="E119" s="28">
@@ -3263,7 +3322,7 @@
       </c>
       <c r="F119" s="14"/>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="E120">
         <f>SUM(E111:E118)*E119</f>
         <v>0</v>
@@ -3273,12 +3332,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="123" spans="1:7" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="123" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A123" s="5" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A124" s="11" t="s">
         <v>335</v>
       </c>
@@ -3288,7 +3347,7 @@
       <c r="C124" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="D124" s="12"/>
+      <c r="D124" s="41"/>
       <c r="E124" s="12" t="s">
         <v>319</v>
       </c>
@@ -3299,7 +3358,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A125" s="11" t="s">
         <v>330</v>
       </c>
@@ -3307,7 +3366,7 @@
       <c r="C125" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="D125" s="12" t="s">
+      <c r="D125" s="41" t="s">
         <v>331</v>
       </c>
       <c r="E125" s="12" t="s">
@@ -3318,11 +3377,11 @@
       </c>
       <c r="G125" s="32"/>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A126" s="12"/>
       <c r="B126" s="12"/>
       <c r="C126" s="12"/>
-      <c r="D126" s="12" t="s">
+      <c r="D126" s="41" t="s">
         <v>102</v>
       </c>
       <c r="E126" s="12" t="s">
@@ -3333,13 +3392,13 @@
       </c>
       <c r="G126" s="32"/>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A127" s="12"/>
       <c r="B127" s="12"/>
       <c r="C127" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="D127" s="12"/>
+      <c r="D127" s="41"/>
       <c r="E127" s="12" t="s">
         <v>319</v>
       </c>
@@ -3348,13 +3407,13 @@
       </c>
       <c r="G127" s="32"/>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A128" s="12"/>
       <c r="B128" s="12"/>
       <c r="C128" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="D128" s="12"/>
+      <c r="D128" s="41"/>
       <c r="E128" s="12" t="s">
         <v>319</v>
       </c>
@@ -3363,13 +3422,13 @@
       </c>
       <c r="G128" s="32"/>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A129" s="12"/>
       <c r="B129" s="12"/>
       <c r="C129" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="D129" s="12"/>
+      <c r="D129" s="41"/>
       <c r="E129" s="12" t="s">
         <v>319</v>
       </c>
@@ -3378,11 +3437,11 @@
       </c>
       <c r="G129" s="32"/>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A130" s="12"/>
       <c r="B130" s="12"/>
       <c r="C130" s="12"/>
-      <c r="D130" s="22" t="s">
+      <c r="D130" s="42" t="s">
         <v>389</v>
       </c>
       <c r="E130" s="28">
@@ -3391,7 +3450,7 @@
       <c r="F130" s="12"/>
       <c r="G130" s="32"/>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
       <c r="E131">
         <f>SUM(E124:E129)*E130</f>
         <v>0</v>
@@ -3402,7 +3461,7 @@
       </c>
       <c r="G131" s="32"/>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A132" s="11" t="s">
         <v>276</v>
       </c>
@@ -3412,7 +3471,7 @@
       <c r="C132" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="D132" s="12"/>
+      <c r="D132" s="41"/>
       <c r="E132" s="12" t="s">
         <v>319</v>
       </c>
@@ -3421,13 +3480,13 @@
       </c>
       <c r="G132" s="32"/>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A133" s="12"/>
       <c r="B133" s="12"/>
       <c r="C133" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="D133" s="12" t="s">
+      <c r="D133" s="41" t="s">
         <v>117</v>
       </c>
       <c r="E133" s="12" t="s">
@@ -3438,11 +3497,11 @@
       </c>
       <c r="G133" s="32"/>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A134" s="12"/>
       <c r="B134" s="12"/>
       <c r="C134" s="12"/>
-      <c r="D134" s="12" t="s">
+      <c r="D134" s="41" t="s">
         <v>118</v>
       </c>
       <c r="E134" s="12" t="s">
@@ -3453,11 +3512,11 @@
       </c>
       <c r="G134" s="32"/>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A135" s="11"/>
       <c r="B135" s="12"/>
       <c r="C135" s="12"/>
-      <c r="D135" s="12" t="s">
+      <c r="D135" s="41" t="s">
         <v>103</v>
       </c>
       <c r="E135" s="12" t="s">
@@ -3468,11 +3527,11 @@
       </c>
       <c r="G135" s="32"/>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A136" s="11"/>
       <c r="B136" s="12"/>
       <c r="C136" s="12"/>
-      <c r="D136" s="12" t="s">
+      <c r="D136" s="41" t="s">
         <v>13</v>
       </c>
       <c r="E136" s="12" t="s">
@@ -3483,13 +3542,13 @@
       </c>
       <c r="G136" s="32"/>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A137" s="11"/>
       <c r="B137" s="12"/>
       <c r="C137" s="12" t="s">
         <v>332</v>
       </c>
-      <c r="D137" s="12"/>
+      <c r="D137" s="41"/>
       <c r="E137" s="12" t="s">
         <v>319</v>
       </c>
@@ -3498,13 +3557,13 @@
       </c>
       <c r="G137" s="32"/>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A138" s="12"/>
       <c r="B138" s="12"/>
       <c r="C138" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="D138" s="12"/>
+      <c r="D138" s="41"/>
       <c r="E138" s="12" t="s">
         <v>319</v>
       </c>
@@ -3513,13 +3572,13 @@
       </c>
       <c r="G138" s="32"/>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A139" s="12"/>
       <c r="B139" s="12"/>
       <c r="C139" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="D139" s="12"/>
+      <c r="D139" s="41"/>
       <c r="E139" s="12" t="s">
         <v>319</v>
       </c>
@@ -3528,11 +3587,11 @@
       </c>
       <c r="G139" s="32"/>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A140" s="12"/>
       <c r="B140" s="12"/>
       <c r="C140" s="12"/>
-      <c r="D140" s="22" t="s">
+      <c r="D140" s="42" t="s">
         <v>389</v>
       </c>
       <c r="E140" s="28">
@@ -3541,7 +3600,7 @@
       <c r="F140" s="12"/>
       <c r="G140" s="32"/>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
       <c r="E141">
         <f>SUM(E132:E139)*E140</f>
         <v>0</v>
@@ -3552,7 +3611,7 @@
       </c>
       <c r="G141" s="32"/>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A142" s="11" t="s">
         <v>333</v>
       </c>
@@ -3562,7 +3621,7 @@
       <c r="C142" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="D142" s="12"/>
+      <c r="D142" s="41"/>
       <c r="E142" s="12" t="s">
         <v>319</v>
       </c>
@@ -3571,7 +3630,7 @@
       </c>
       <c r="G142" s="32"/>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A143" s="11" t="s">
         <v>334</v>
       </c>
@@ -3579,33 +3638,33 @@
       <c r="C143" s="12" t="s">
         <v>336</v>
       </c>
-      <c r="D143" s="12"/>
+      <c r="D143" s="41"/>
       <c r="E143" s="12"/>
       <c r="F143" s="12">
         <v>6</v>
       </c>
       <c r="G143" s="32"/>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A144" s="11"/>
       <c r="B144" s="12"/>
       <c r="C144" s="12" t="s">
         <v>337</v>
       </c>
-      <c r="D144" s="12"/>
+      <c r="D144" s="41"/>
       <c r="E144" s="12"/>
       <c r="F144" s="12">
         <v>10</v>
       </c>
       <c r="G144" s="32"/>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A145" s="11"/>
       <c r="B145" s="12"/>
       <c r="C145" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="D145" s="12" t="s">
+      <c r="D145" s="41" t="s">
         <v>331</v>
       </c>
       <c r="E145" s="12" t="s">
@@ -3616,11 +3675,11 @@
       </c>
       <c r="G145" s="32"/>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A146" s="12"/>
       <c r="B146" s="12"/>
       <c r="C146" s="12"/>
-      <c r="D146" s="12" t="s">
+      <c r="D146" s="41" t="s">
         <v>102</v>
       </c>
       <c r="E146" s="12" t="s">
@@ -3631,13 +3690,13 @@
       </c>
       <c r="G146" s="32"/>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A147" s="12"/>
       <c r="B147" s="12"/>
       <c r="C147" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="D147" s="12"/>
+      <c r="D147" s="41"/>
       <c r="E147" s="12" t="s">
         <v>319</v>
       </c>
@@ -3646,13 +3705,13 @@
       </c>
       <c r="G147" s="32"/>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A148" s="12"/>
       <c r="B148" s="12"/>
       <c r="C148" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="D148" s="12"/>
+      <c r="D148" s="41"/>
       <c r="E148" s="12" t="s">
         <v>319</v>
       </c>
@@ -3661,13 +3720,13 @@
       </c>
       <c r="G148" s="32"/>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A149" s="12"/>
       <c r="B149" s="12"/>
       <c r="C149" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="D149" s="12"/>
+      <c r="D149" s="41"/>
       <c r="E149" s="12" t="s">
         <v>319</v>
       </c>
@@ -3676,11 +3735,11 @@
       </c>
       <c r="G149" s="32"/>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A150" s="12"/>
       <c r="B150" s="12"/>
       <c r="C150" s="12"/>
-      <c r="D150" s="22" t="s">
+      <c r="D150" s="42" t="s">
         <v>389</v>
       </c>
       <c r="E150" s="28">
@@ -3689,7 +3748,7 @@
       <c r="F150" s="12"/>
       <c r="G150" s="32"/>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
       <c r="E151">
         <f>SUM(E142:E149)*E150</f>
         <v>0</v>
@@ -3700,7 +3759,7 @@
       </c>
       <c r="G151" s="32"/>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A152" s="11" t="s">
         <v>338</v>
       </c>
@@ -3710,7 +3769,7 @@
       <c r="C152" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="D152" s="12"/>
+      <c r="D152" s="41"/>
       <c r="E152" s="12" t="s">
         <v>319</v>
       </c>
@@ -3719,13 +3778,13 @@
       </c>
       <c r="G152" s="32"/>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A153" s="12"/>
       <c r="B153" s="12"/>
       <c r="C153" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="D153" s="12" t="s">
+      <c r="D153" s="41" t="s">
         <v>117</v>
       </c>
       <c r="E153" s="12" t="s">
@@ -3736,11 +3795,11 @@
       </c>
       <c r="G153" s="32"/>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A154" s="12"/>
       <c r="B154" s="12"/>
       <c r="C154" s="12"/>
-      <c r="D154" s="12" t="s">
+      <c r="D154" s="41" t="s">
         <v>118</v>
       </c>
       <c r="E154" s="12" t="s">
@@ -3751,11 +3810,11 @@
       </c>
       <c r="G154" s="32"/>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A155" s="11"/>
       <c r="B155" s="12"/>
       <c r="C155" s="12"/>
-      <c r="D155" s="12" t="s">
+      <c r="D155" s="41" t="s">
         <v>103</v>
       </c>
       <c r="E155" s="12" t="s">
@@ -3766,11 +3825,11 @@
       </c>
       <c r="G155" s="32"/>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A156" s="11"/>
       <c r="B156" s="12"/>
       <c r="C156" s="12"/>
-      <c r="D156" s="12" t="s">
+      <c r="D156" s="41" t="s">
         <v>13</v>
       </c>
       <c r="E156" s="12" t="s">
@@ -3781,26 +3840,26 @@
       </c>
       <c r="G156" s="32"/>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A157" s="11"/>
       <c r="B157" s="12"/>
       <c r="C157" s="12" t="s">
         <v>337</v>
       </c>
-      <c r="D157" s="12"/>
+      <c r="D157" s="41"/>
       <c r="E157" s="12"/>
       <c r="F157" s="12">
         <v>10</v>
       </c>
       <c r="G157" s="32"/>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A158" s="11"/>
       <c r="B158" s="12"/>
       <c r="C158" s="12" t="s">
         <v>332</v>
       </c>
-      <c r="D158" s="12"/>
+      <c r="D158" s="41"/>
       <c r="E158" s="12" t="s">
         <v>319</v>
       </c>
@@ -3809,13 +3868,13 @@
       </c>
       <c r="G158" s="32"/>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A159" s="12"/>
       <c r="B159" s="12"/>
       <c r="C159" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="D159" s="12"/>
+      <c r="D159" s="41"/>
       <c r="E159" s="12" t="s">
         <v>319</v>
       </c>
@@ -3824,13 +3883,13 @@
       </c>
       <c r="G159" s="32"/>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A160" s="12"/>
       <c r="B160" s="12"/>
       <c r="C160" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="D160" s="12"/>
+      <c r="D160" s="41"/>
       <c r="E160" s="12" t="s">
         <v>319</v>
       </c>
@@ -3839,11 +3898,11 @@
       </c>
       <c r="G160" s="32"/>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A161" s="12"/>
       <c r="B161" s="12"/>
       <c r="C161" s="12"/>
-      <c r="D161" s="22" t="s">
+      <c r="D161" s="42" t="s">
         <v>389</v>
       </c>
       <c r="E161" s="28">
@@ -3852,7 +3911,7 @@
       <c r="F161" s="12"/>
       <c r="G161" s="32"/>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.3">
       <c r="E162">
         <f>SUM(E152:E160)*E161</f>
         <v>0</v>
@@ -3863,10 +3922,10 @@
       </c>
       <c r="G162" s="32"/>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.3">
       <c r="G163" s="27"/>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A164" s="16" t="s">
         <v>125</v>
       </c>
@@ -3876,41 +3935,41 @@
       <c r="C164" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="D164" s="14"/>
+      <c r="D164" s="24"/>
       <c r="E164" s="14"/>
       <c r="F164" s="14">
         <v>20</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A165" s="16"/>
       <c r="B165" s="14"/>
       <c r="C165" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="D165" s="14"/>
+      <c r="D165" s="24"/>
       <c r="E165" s="14"/>
       <c r="F165" s="14">
         <v>20</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A166" s="16"/>
       <c r="B166" s="14"/>
       <c r="C166" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="D166" s="14"/>
+      <c r="D166" s="24"/>
       <c r="E166" s="14"/>
       <c r="F166" s="14">
         <v>20</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A167" s="16"/>
       <c r="B167" s="14"/>
       <c r="C167" s="14"/>
-      <c r="D167" s="22" t="s">
+      <c r="D167" s="42" t="s">
         <v>389</v>
       </c>
       <c r="E167" s="28">
@@ -3918,7 +3977,7 @@
       </c>
       <c r="F167" s="14"/>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A168" s="1"/>
       <c r="E168">
         <f>-SUM(E164:E166)*E167</f>
@@ -3929,7 +3988,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A169" s="16" t="s">
         <v>125</v>
       </c>
@@ -3939,65 +3998,65 @@
       <c r="C169" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="D169" s="14"/>
+      <c r="D169" s="24"/>
       <c r="E169" s="14"/>
       <c r="F169" s="14">
         <v>10</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A170" s="16"/>
       <c r="B170" s="14"/>
       <c r="C170" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="D170" s="14"/>
+      <c r="D170" s="24"/>
       <c r="E170" s="14"/>
       <c r="F170" s="14">
         <v>10</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A171" s="16"/>
       <c r="B171" s="14"/>
       <c r="C171" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="D171" s="14"/>
+      <c r="D171" s="24"/>
       <c r="E171" s="14"/>
       <c r="F171" s="14">
         <v>10</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A172" s="16"/>
       <c r="B172" s="14"/>
       <c r="C172" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="D172" s="14"/>
+      <c r="D172" s="24"/>
       <c r="E172" s="14"/>
       <c r="F172" s="14">
         <v>10</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A173" s="16"/>
       <c r="B173" s="14"/>
       <c r="C173" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="D173" s="14"/>
+      <c r="D173" s="24"/>
       <c r="E173" s="14"/>
       <c r="F173" s="14">
         <v>15</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A174" s="16"/>
       <c r="B174" s="14"/>
       <c r="C174" s="14"/>
-      <c r="D174" s="22" t="s">
+      <c r="D174" s="42" t="s">
         <v>389</v>
       </c>
       <c r="E174" s="28">
@@ -4005,7 +4064,7 @@
       </c>
       <c r="F174" s="14"/>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A175" s="1"/>
       <c r="E175">
         <f>-SUM(E169:E173)*E174</f>
@@ -4016,7 +4075,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A176" s="16" t="s">
         <v>339</v>
       </c>
@@ -4026,7 +4085,7 @@
       <c r="C176" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="D176" s="14"/>
+      <c r="D176" s="24"/>
       <c r="E176" s="14" t="s">
         <v>319</v>
       </c>
@@ -4034,7 +4093,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A177" s="16" t="s">
         <v>340</v>
       </c>
@@ -4042,55 +4101,55 @@
       <c r="C177" s="14" t="s">
         <v>341</v>
       </c>
-      <c r="D177" s="14"/>
+      <c r="D177" s="24"/>
       <c r="E177" s="14"/>
       <c r="F177" s="14">
         <v>6</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="178" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A178" s="16"/>
       <c r="B178" s="14"/>
       <c r="C178" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="D178" s="14"/>
+      <c r="D178" s="24"/>
       <c r="E178" s="14"/>
       <c r="F178" s="14">
         <v>6</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A179" s="16"/>
       <c r="B179" s="14"/>
       <c r="C179" s="14" t="s">
         <v>336</v>
       </c>
-      <c r="D179" s="14"/>
+      <c r="D179" s="24"/>
       <c r="E179" s="14"/>
       <c r="F179" s="14">
         <v>6</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="180" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A180" s="16"/>
       <c r="B180" s="14"/>
       <c r="C180" s="14" t="s">
         <v>337</v>
       </c>
-      <c r="D180" s="14"/>
+      <c r="D180" s="24"/>
       <c r="E180" s="14"/>
       <c r="F180" s="14">
         <v>20</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="181" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A181" s="16"/>
       <c r="B181" s="14"/>
       <c r="C181" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="D181" s="14" t="s">
+      <c r="D181" s="24" t="s">
         <v>331</v>
       </c>
       <c r="E181" s="14" t="s">
@@ -4100,11 +4159,11 @@
         <v>6</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A182" s="14"/>
       <c r="B182" s="14"/>
       <c r="C182" s="14"/>
-      <c r="D182" s="14" t="s">
+      <c r="D182" s="24" t="s">
         <v>102</v>
       </c>
       <c r="E182" s="14" t="s">
@@ -4114,13 +4173,13 @@
         <v>6</v>
       </c>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A183" s="14"/>
       <c r="B183" s="14"/>
       <c r="C183" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="D183" s="14"/>
+      <c r="D183" s="24"/>
       <c r="E183" s="14" t="s">
         <v>319</v>
       </c>
@@ -4128,13 +4187,13 @@
         <v>6</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A184" s="14"/>
       <c r="B184" s="14"/>
       <c r="C184" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="D184" s="14"/>
+      <c r="D184" s="24"/>
       <c r="E184" s="14" t="s">
         <v>319</v>
       </c>
@@ -4142,13 +4201,13 @@
         <v>6</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A185" s="14"/>
       <c r="B185" s="14"/>
       <c r="C185" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="D185" s="14"/>
+      <c r="D185" s="24"/>
       <c r="E185" s="14" t="s">
         <v>319</v>
       </c>
@@ -4156,11 +4215,11 @@
         <v>6</v>
       </c>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="186" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A186" s="14"/>
       <c r="B186" s="14"/>
       <c r="C186" s="14"/>
-      <c r="D186" s="22" t="s">
+      <c r="D186" s="42" t="s">
         <v>389</v>
       </c>
       <c r="E186" s="28">
@@ -4168,7 +4227,7 @@
       </c>
       <c r="F186" s="14"/>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E187">
         <f>SUM(E176:E185)*E186</f>
         <v>0</v>
@@ -4178,7 +4237,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="188" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A188" s="16" t="s">
         <v>339</v>
       </c>
@@ -4188,7 +4247,7 @@
       <c r="C188" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="D188" s="14"/>
+      <c r="D188" s="24"/>
       <c r="E188" s="14" t="s">
         <v>319</v>
       </c>
@@ -4196,7 +4255,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="189" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A189" s="14" t="s">
         <v>340</v>
       </c>
@@ -4204,31 +4263,31 @@
       <c r="C189" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="D189" s="14"/>
+      <c r="D189" s="24"/>
       <c r="E189" s="14"/>
       <c r="F189" s="14">
         <v>5</v>
       </c>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="190" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A190" s="16"/>
       <c r="B190" s="14"/>
       <c r="C190" s="14" t="s">
         <v>272</v>
       </c>
-      <c r="D190" s="14"/>
+      <c r="D190" s="24"/>
       <c r="E190" s="14"/>
       <c r="F190" s="14">
         <v>5</v>
       </c>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="191" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A191" s="14"/>
       <c r="B191" s="14"/>
       <c r="C191" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="D191" s="14" t="s">
+      <c r="D191" s="24" t="s">
         <v>117</v>
       </c>
       <c r="E191" s="14" t="s">
@@ -4238,11 +4297,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="192" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A192" s="14"/>
       <c r="B192" s="14"/>
       <c r="C192" s="14"/>
-      <c r="D192" s="14" t="s">
+      <c r="D192" s="24" t="s">
         <v>118</v>
       </c>
       <c r="E192" s="14" t="s">
@@ -4252,11 +4311,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A193" s="16"/>
       <c r="B193" s="14"/>
       <c r="C193" s="14"/>
-      <c r="D193" s="14" t="s">
+      <c r="D193" s="24" t="s">
         <v>103</v>
       </c>
       <c r="E193" s="14" t="s">
@@ -4266,11 +4325,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A194" s="16"/>
       <c r="B194" s="14"/>
       <c r="C194" s="14"/>
-      <c r="D194" s="14" t="s">
+      <c r="D194" s="24" t="s">
         <v>13</v>
       </c>
       <c r="E194" s="14" t="s">
@@ -4280,13 +4339,13 @@
         <v>5</v>
       </c>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A195" s="14"/>
       <c r="B195" s="14"/>
       <c r="C195" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="D195" s="14"/>
+      <c r="D195" s="24"/>
       <c r="E195" s="14" t="s">
         <v>319</v>
       </c>
@@ -4294,13 +4353,13 @@
         <v>5</v>
       </c>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A196" s="14"/>
       <c r="B196" s="14"/>
       <c r="C196" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="D196" s="14"/>
+      <c r="D196" s="24"/>
       <c r="E196" s="14" t="s">
         <v>319</v>
       </c>
@@ -4308,11 +4367,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A197" s="14"/>
       <c r="B197" s="14"/>
       <c r="C197" s="14"/>
-      <c r="D197" s="22" t="s">
+      <c r="D197" s="42" t="s">
         <v>389</v>
       </c>
       <c r="E197" s="28">
@@ -4320,7 +4379,7 @@
       </c>
       <c r="F197" s="14"/>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E198">
         <f>SUM(E188:E196)*E197</f>
         <v>0</v>
@@ -4330,7 +4389,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A199" s="16" t="s">
         <v>342</v>
       </c>
@@ -4338,41 +4397,41 @@
         <v>54</v>
       </c>
       <c r="C199" s="14"/>
-      <c r="D199" s="14"/>
+      <c r="D199" s="24"/>
       <c r="E199" s="14"/>
       <c r="F199" s="14">
         <v>20</v>
       </c>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A200" s="16"/>
       <c r="B200" s="14" t="s">
         <v>127</v>
       </c>
       <c r="C200" s="14"/>
-      <c r="D200" s="14"/>
+      <c r="D200" s="24"/>
       <c r="E200" s="14"/>
       <c r="F200" s="14">
         <v>20</v>
       </c>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A201" s="16"/>
       <c r="B201" s="14" t="s">
         <v>124</v>
       </c>
       <c r="C201" s="14"/>
-      <c r="D201" s="14"/>
+      <c r="D201" s="24"/>
       <c r="E201" s="14"/>
       <c r="F201" s="14">
         <v>20</v>
       </c>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A202" s="16"/>
       <c r="B202" s="14"/>
       <c r="C202" s="14"/>
-      <c r="D202" s="22" t="s">
+      <c r="D202" s="42" t="s">
         <v>389</v>
       </c>
       <c r="E202" s="28">
@@ -4380,7 +4439,7 @@
       </c>
       <c r="F202" s="14"/>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A203" s="1"/>
       <c r="E203">
         <f>SUM(E199:E201)*E202</f>
@@ -4391,15 +4450,16 @@
         <v>60</v>
       </c>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A204" s="1"/>
     </row>
-    <row r="205" spans="1:9" s="5" customFormat="1" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="205" spans="1:9" s="5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A205" s="5" t="s">
         <v>378</v>
       </c>
-    </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="D205" s="43"/>
+    </row>
+    <row r="206" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A206" s="1" t="s">
         <v>62</v>
       </c>
@@ -4409,102 +4469,102 @@
       <c r="C206" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="D206" s="12"/>
+      <c r="D206" s="41"/>
       <c r="E206" s="12"/>
       <c r="F206" s="12">
         <v>5</v>
       </c>
       <c r="I206" s="1"/>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A207" s="1"/>
       <c r="B207" s="12"/>
       <c r="C207" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="D207" s="12"/>
+      <c r="D207" s="41"/>
       <c r="E207" s="12"/>
       <c r="F207" s="12">
         <v>5</v>
       </c>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A208" s="1"/>
       <c r="B208" s="12"/>
       <c r="C208" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="D208" s="12"/>
+      <c r="D208" s="41"/>
       <c r="E208" s="12"/>
       <c r="F208" s="12">
         <v>5</v>
       </c>
     </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="209" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A209" s="1"/>
       <c r="B209" s="12"/>
       <c r="C209" s="12" t="s">
         <v>249</v>
       </c>
-      <c r="D209" s="12"/>
+      <c r="D209" s="41"/>
       <c r="E209" s="12"/>
       <c r="F209" s="12">
         <v>5</v>
       </c>
     </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="210" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A210" s="1"/>
       <c r="B210" s="12"/>
       <c r="C210" s="12" t="s">
         <v>248</v>
       </c>
-      <c r="D210" s="12"/>
+      <c r="D210" s="41"/>
       <c r="E210" s="12"/>
       <c r="F210" s="12">
         <v>5</v>
       </c>
     </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="211" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A211" s="1"/>
       <c r="B211" s="12"/>
       <c r="C211" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="D211" s="12"/>
+      <c r="D211" s="41"/>
       <c r="E211" s="12"/>
       <c r="F211" s="12">
         <v>5</v>
       </c>
     </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="212" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A212" s="1"/>
       <c r="B212" s="12"/>
       <c r="C212" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="D212" s="12"/>
+      <c r="D212" s="41"/>
       <c r="E212" s="12"/>
       <c r="F212" s="12">
         <v>5</v>
       </c>
     </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="213" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A213" s="1"/>
       <c r="B213" s="12"/>
       <c r="C213" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="D213" s="12"/>
+      <c r="D213" s="41"/>
       <c r="E213" s="12"/>
       <c r="F213" s="12">
         <v>5</v>
       </c>
     </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="214" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A214" s="1"/>
       <c r="B214" s="12"/>
       <c r="C214" s="12"/>
-      <c r="D214" s="22" t="s">
+      <c r="D214" s="42" t="s">
         <v>389</v>
       </c>
       <c r="E214" s="28">
@@ -4512,7 +4572,7 @@
       </c>
       <c r="F214" s="12"/>
     </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="215" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A215" s="1"/>
       <c r="E215">
         <f>-SUM(E206:E213)*E214</f>
@@ -4523,7 +4583,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="216" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A216" s="1"/>
       <c r="B216" s="13" t="s">
         <v>63</v>
@@ -4531,101 +4591,101 @@
       <c r="C216" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="D216" s="13"/>
+      <c r="D216" s="40"/>
       <c r="E216" s="13"/>
       <c r="F216" s="13">
         <v>5</v>
       </c>
     </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="217" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A217" s="1"/>
       <c r="B217" s="13"/>
       <c r="C217" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="D217" s="13"/>
+      <c r="D217" s="40"/>
       <c r="E217" s="13"/>
       <c r="F217" s="13">
         <v>5</v>
       </c>
     </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="218" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A218" s="1"/>
       <c r="B218" s="13"/>
       <c r="C218" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="D218" s="13"/>
+      <c r="D218" s="40"/>
       <c r="E218" s="13"/>
       <c r="F218" s="13">
         <v>5</v>
       </c>
     </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="219" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A219" s="1"/>
       <c r="B219" s="13"/>
       <c r="C219" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="D219" s="13"/>
+      <c r="D219" s="40"/>
       <c r="E219" s="13"/>
       <c r="F219" s="13">
         <v>5</v>
       </c>
     </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="220" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A220" s="1"/>
       <c r="B220" s="13"/>
       <c r="C220" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="D220" s="13"/>
+      <c r="D220" s="40"/>
       <c r="E220" s="13"/>
       <c r="F220" s="13">
         <v>5</v>
       </c>
     </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="221" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A221" s="1"/>
       <c r="B221" s="13"/>
       <c r="C221" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="D221" s="13"/>
+      <c r="D221" s="40"/>
       <c r="E221" s="13"/>
       <c r="F221" s="13">
         <v>5</v>
       </c>
     </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="222" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A222" s="1"/>
       <c r="B222" s="13"/>
       <c r="C222" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="D222" s="13"/>
+      <c r="D222" s="40"/>
       <c r="E222" s="13"/>
       <c r="F222" s="13">
         <v>5</v>
       </c>
     </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="223" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A223" s="1"/>
       <c r="B223" s="13"/>
       <c r="C223" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="D223" s="13"/>
+      <c r="D223" s="40"/>
       <c r="E223" s="13"/>
       <c r="F223" s="13">
         <v>5</v>
       </c>
     </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="224" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A224" s="1"/>
       <c r="B224" s="13"/>
       <c r="C224" s="13"/>
-      <c r="D224" s="22" t="s">
+      <c r="D224" s="42" t="s">
         <v>389</v>
       </c>
       <c r="E224" s="28">
@@ -4633,7 +4693,7 @@
       </c>
       <c r="F224" s="13"/>
     </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="225" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A225" s="1"/>
       <c r="E225">
         <f>-SUM(E216:E223)*E224</f>
@@ -4644,7 +4704,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="226" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A226" s="1"/>
       <c r="B226" s="14" t="s">
         <v>63</v>
@@ -4652,101 +4712,101 @@
       <c r="C226" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="D226" s="14"/>
+      <c r="D226" s="24"/>
       <c r="E226" s="14"/>
       <c r="F226" s="14">
         <v>5</v>
       </c>
     </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="227" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A227" s="1"/>
       <c r="B227" s="14"/>
       <c r="C227" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="D227" s="14"/>
+      <c r="D227" s="24"/>
       <c r="E227" s="14"/>
       <c r="F227" s="14">
         <v>5</v>
       </c>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="228" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A228" s="1"/>
       <c r="B228" s="14"/>
       <c r="C228" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="D228" s="14"/>
+      <c r="D228" s="24"/>
       <c r="E228" s="14"/>
       <c r="F228" s="14">
         <v>5</v>
       </c>
     </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="229" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A229" s="1"/>
       <c r="B229" s="14"/>
       <c r="C229" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="D229" s="14"/>
+      <c r="D229" s="24"/>
       <c r="E229" s="14"/>
       <c r="F229" s="14">
         <v>5</v>
       </c>
     </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="230" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A230" s="1"/>
       <c r="B230" s="14"/>
       <c r="C230" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="D230" s="14"/>
+      <c r="D230" s="24"/>
       <c r="E230" s="14"/>
       <c r="F230" s="14">
         <v>5</v>
       </c>
     </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="231" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A231" s="1"/>
       <c r="B231" s="14"/>
       <c r="C231" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="D231" s="14"/>
+      <c r="D231" s="24"/>
       <c r="E231" s="14"/>
       <c r="F231" s="14">
         <v>5</v>
       </c>
     </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="232" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A232" s="1"/>
       <c r="B232" s="14"/>
       <c r="C232" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="D232" s="14"/>
+      <c r="D232" s="24"/>
       <c r="E232" s="14"/>
       <c r="F232" s="14">
         <v>5</v>
       </c>
     </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="233" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A233" s="1"/>
       <c r="B233" s="14"/>
       <c r="C233" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="D233" s="14"/>
+      <c r="D233" s="24"/>
       <c r="E233" s="14"/>
       <c r="F233" s="14">
         <v>5</v>
       </c>
     </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="234" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A234" s="1"/>
       <c r="B234" s="14"/>
       <c r="C234" s="14"/>
-      <c r="D234" s="22" t="s">
+      <c r="D234" s="42" t="s">
         <v>389</v>
       </c>
       <c r="E234" s="28">
@@ -4754,7 +4814,7 @@
       </c>
       <c r="F234" s="14"/>
     </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="235" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A235" s="1"/>
       <c r="E235">
         <f>-SUM(E226:E233)*E234</f>
@@ -4765,7 +4825,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="236" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A236" s="15" t="s">
         <v>277</v>
       </c>
@@ -4775,113 +4835,113 @@
       <c r="C236" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="D236" s="13"/>
+      <c r="D236" s="40"/>
       <c r="E236" s="13"/>
       <c r="F236" s="13">
         <v>10</v>
       </c>
     </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="237" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A237" s="13"/>
       <c r="B237" s="13"/>
       <c r="C237" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="D237" s="13"/>
+      <c r="D237" s="40"/>
       <c r="E237" s="13"/>
       <c r="F237" s="13">
         <v>10</v>
       </c>
     </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="238" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A238" s="13"/>
       <c r="B238" s="13"/>
       <c r="C238" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="D238" s="13"/>
+      <c r="D238" s="40"/>
       <c r="E238" s="13"/>
       <c r="F238" s="13">
         <v>10</v>
       </c>
     </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="239" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A239" s="13"/>
       <c r="B239" s="13"/>
       <c r="C239" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="D239" s="13"/>
+      <c r="D239" s="40"/>
       <c r="E239" s="13"/>
       <c r="F239" s="13">
         <v>10</v>
       </c>
     </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="240" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A240" s="13"/>
       <c r="B240" s="13"/>
       <c r="C240" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D240" s="13"/>
+      <c r="D240" s="40"/>
       <c r="E240" s="13"/>
       <c r="F240" s="13">
         <v>20</v>
       </c>
     </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="241" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A241" s="13"/>
       <c r="B241" s="13"/>
       <c r="C241" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="D241" s="13"/>
+      <c r="D241" s="40"/>
       <c r="E241" s="13"/>
       <c r="F241" s="13">
         <v>10</v>
       </c>
     </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="242" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A242" s="13"/>
       <c r="B242" s="13"/>
       <c r="C242" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="D242" s="13"/>
+      <c r="D242" s="40"/>
       <c r="E242" s="13"/>
       <c r="F242" s="13">
         <v>10</v>
       </c>
     </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="243" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A243" s="13"/>
       <c r="B243" s="13"/>
       <c r="C243" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D243" s="13"/>
+      <c r="D243" s="40"/>
       <c r="E243" s="13"/>
       <c r="F243" s="13">
         <v>30</v>
       </c>
     </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="244" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A244" s="15"/>
       <c r="B244" s="13"/>
       <c r="C244" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="D244" s="13"/>
+      <c r="D244" s="40"/>
       <c r="E244" s="13"/>
       <c r="F244" s="13">
         <v>10</v>
       </c>
     </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="245" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A245" s="13"/>
       <c r="B245" s="13"/>
       <c r="C245" s="13"/>
-      <c r="D245" s="22" t="s">
+      <c r="D245" s="42" t="s">
         <v>389</v>
       </c>
       <c r="E245" s="28">
@@ -4889,11 +4949,11 @@
       </c>
       <c r="F245" s="13"/>
     </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="246" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A246" s="25"/>
       <c r="B246" s="25"/>
       <c r="C246" s="25"/>
-      <c r="D246" s="25"/>
+      <c r="D246" s="45"/>
       <c r="E246" s="26">
         <f>SUM(E236:E244)*E245</f>
         <v>0</v>
@@ -4903,20 +4963,20 @@
         <v>120</v>
       </c>
     </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="247" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A247" s="25"/>
       <c r="B247" s="25"/>
       <c r="C247" s="25"/>
-      <c r="D247" s="25"/>
+      <c r="D247" s="45"/>
       <c r="E247" s="25"/>
       <c r="F247" s="25"/>
     </row>
-    <row r="248" spans="1:6" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="248" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A248" s="5" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="249" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A249" s="11" t="s">
         <v>206</v>
       </c>
@@ -4924,13 +4984,13 @@
         <v>205</v>
       </c>
       <c r="C249" s="12"/>
-      <c r="D249" s="12"/>
+      <c r="D249" s="41"/>
       <c r="E249" s="12"/>
       <c r="F249" s="12">
         <v>5</v>
       </c>
     </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="250" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A250" s="11" t="s">
         <v>325</v>
       </c>
@@ -4938,65 +4998,65 @@
         <v>65</v>
       </c>
       <c r="C250" s="12"/>
-      <c r="D250" s="12"/>
+      <c r="D250" s="41"/>
       <c r="E250" s="12"/>
       <c r="F250" s="12">
         <v>10</v>
       </c>
     </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="251" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A251" s="11"/>
       <c r="B251" s="12" t="s">
         <v>50</v>
       </c>
       <c r="C251" s="12"/>
-      <c r="D251" s="12"/>
+      <c r="D251" s="41"/>
       <c r="E251" s="12"/>
       <c r="F251" s="12">
         <v>10</v>
       </c>
     </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="252" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A252" s="11"/>
       <c r="B252" s="12" t="s">
         <v>207</v>
       </c>
       <c r="C252" s="12"/>
-      <c r="D252" s="12"/>
+      <c r="D252" s="41"/>
       <c r="E252" s="12"/>
       <c r="F252" s="12">
         <v>5</v>
       </c>
     </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="253" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A253" s="11"/>
       <c r="B253" s="12" t="s">
         <v>51</v>
       </c>
       <c r="C253" s="12"/>
-      <c r="D253" s="12"/>
+      <c r="D253" s="41"/>
       <c r="E253" s="12"/>
       <c r="F253" s="12">
         <v>5</v>
       </c>
     </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="254" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A254" s="11"/>
       <c r="B254" s="12" t="s">
         <v>234</v>
       </c>
       <c r="C254" s="12"/>
-      <c r="D254" s="12"/>
+      <c r="D254" s="41"/>
       <c r="E254" s="12"/>
       <c r="F254" s="12">
         <v>5</v>
       </c>
     </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="255" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A255" s="11"/>
       <c r="B255" s="12"/>
       <c r="C255" s="12"/>
-      <c r="D255" s="22" t="s">
+      <c r="D255" s="42" t="s">
         <v>389</v>
       </c>
       <c r="E255" s="28">
@@ -5004,7 +5064,7 @@
       </c>
       <c r="F255" s="12"/>
     </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="256" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A256" s="1"/>
       <c r="E256">
         <f>SUM(E249:E254)*E255</f>
@@ -5015,7 +5075,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="257" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A257" s="11" t="s">
         <v>386</v>
       </c>
@@ -5023,7 +5083,7 @@
       <c r="C257" s="12" t="s">
         <v>205</v>
       </c>
-      <c r="D257" s="12"/>
+      <c r="D257" s="41"/>
       <c r="E257" s="12"/>
       <c r="F257" s="12">
         <v>5</v>
@@ -5032,7 +5092,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="258" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A258" s="11" t="s">
         <v>327</v>
       </c>
@@ -5040,14 +5100,14 @@
       <c r="C258" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="D258" s="12"/>
+      <c r="D258" s="41"/>
       <c r="E258" s="12"/>
       <c r="F258" s="12">
         <v>10</v>
       </c>
       <c r="G258" s="33"/>
     </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="259" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A259" s="11" t="s">
         <v>326</v>
       </c>
@@ -5055,57 +5115,57 @@
       <c r="C259" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="D259" s="12"/>
+      <c r="D259" s="41"/>
       <c r="E259" s="12"/>
       <c r="F259" s="12">
         <v>10</v>
       </c>
       <c r="G259" s="33"/>
     </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="260" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A260" s="11"/>
       <c r="B260" s="12"/>
       <c r="C260" s="12" t="s">
         <v>207</v>
       </c>
-      <c r="D260" s="12"/>
+      <c r="D260" s="41"/>
       <c r="E260" s="12"/>
       <c r="F260" s="12">
         <v>5</v>
       </c>
       <c r="G260" s="33"/>
     </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="261" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A261" s="11"/>
       <c r="B261" s="12"/>
       <c r="C261" s="12" t="s">
         <v>329</v>
       </c>
-      <c r="D261" s="12"/>
+      <c r="D261" s="41"/>
       <c r="E261" s="12"/>
       <c r="F261" s="12">
         <v>5</v>
       </c>
       <c r="G261" s="33"/>
     </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="262" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A262" s="11"/>
       <c r="B262" s="12"/>
       <c r="C262" s="12" t="s">
         <v>328</v>
       </c>
-      <c r="D262" s="12"/>
+      <c r="D262" s="41"/>
       <c r="E262" s="12"/>
       <c r="F262" s="12">
         <v>5</v>
       </c>
       <c r="G262" s="33"/>
     </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="263" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A263" s="11"/>
       <c r="B263" s="12"/>
       <c r="C263" s="12"/>
-      <c r="D263" s="22" t="s">
+      <c r="D263" s="42" t="s">
         <v>389</v>
       </c>
       <c r="E263" s="28">
@@ -5114,7 +5174,7 @@
       <c r="F263" s="12"/>
       <c r="G263" s="33"/>
     </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="264" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A264" s="1"/>
       <c r="E264">
         <f>SUM(E257:E262)*E263</f>
@@ -5125,12 +5185,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="265" spans="1:7" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="265" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A265" s="5" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="266" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A266" s="7" t="s">
         <v>29</v>
       </c>
@@ -5138,60 +5198,60 @@
       <c r="C266" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="D266" s="8"/>
+      <c r="D266" s="44"/>
       <c r="E266" s="8"/>
       <c r="F266" s="8"/>
     </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="267" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A267" s="8"/>
       <c r="B267" s="8"/>
       <c r="C267" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="D267" s="8"/>
+      <c r="D267" s="44"/>
       <c r="E267" s="8"/>
       <c r="F267" s="8">
         <v>5</v>
       </c>
     </row>
-    <row r="268" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="268" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A268" s="8"/>
       <c r="B268" s="8"/>
       <c r="C268" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="D268" s="8"/>
+      <c r="D268" s="44"/>
       <c r="E268" s="8"/>
       <c r="F268" s="8"/>
     </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="269" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A269" s="8"/>
       <c r="B269" s="8"/>
       <c r="C269" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="D269" s="8"/>
+      <c r="D269" s="44"/>
       <c r="E269" s="8"/>
       <c r="F269" s="8"/>
     </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="270" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A270" s="8"/>
       <c r="B270" s="8"/>
       <c r="C270" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="D270" s="8"/>
+      <c r="D270" s="44"/>
       <c r="E270" s="8"/>
       <c r="F270" s="8">
         <v>2</v>
       </c>
     </row>
-    <row r="272" spans="1:7" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="272" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A272" s="5" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="273" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A273" s="12" t="s">
         <v>75</v>
       </c>
@@ -5201,7 +5261,7 @@
       <c r="C273" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="D273" s="12" t="s">
+      <c r="D273" s="41" t="s">
         <v>39</v>
       </c>
       <c r="E273" s="12"/>
@@ -5209,11 +5269,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="274" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A274" s="12"/>
       <c r="B274" s="12"/>
       <c r="C274" s="12"/>
-      <c r="D274" s="12" t="s">
+      <c r="D274" s="41" t="s">
         <v>101</v>
       </c>
       <c r="E274" s="12"/>
@@ -5221,11 +5281,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="275" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A275" s="12"/>
       <c r="B275" s="12"/>
       <c r="C275" s="12"/>
-      <c r="D275" s="12" t="s">
+      <c r="D275" s="41" t="s">
         <v>286</v>
       </c>
       <c r="E275" s="12"/>
@@ -5233,11 +5293,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="276" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A276" s="12"/>
       <c r="B276" s="12"/>
       <c r="C276" s="12"/>
-      <c r="D276" s="12" t="s">
+      <c r="D276" s="41" t="s">
         <v>102</v>
       </c>
       <c r="E276" s="12"/>
@@ -5245,11 +5305,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="277" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A277" s="12"/>
       <c r="B277" s="12"/>
       <c r="C277" s="12"/>
-      <c r="D277" s="12" t="s">
+      <c r="D277" s="41" t="s">
         <v>288</v>
       </c>
       <c r="E277" s="12"/>
@@ -5257,11 +5317,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="278" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A278" s="12"/>
       <c r="B278" s="12"/>
       <c r="C278" s="12"/>
-      <c r="D278" s="12" t="s">
+      <c r="D278" s="41" t="s">
         <v>287</v>
       </c>
       <c r="E278" s="12"/>
@@ -5269,13 +5329,13 @@
         <v>5</v>
       </c>
     </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="279" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A279" s="12"/>
       <c r="B279" s="12"/>
       <c r="C279" s="12" t="s">
         <v>289</v>
       </c>
-      <c r="D279" s="12" t="s">
+      <c r="D279" s="41" t="s">
         <v>290</v>
       </c>
       <c r="E279" s="12"/>
@@ -5283,11 +5343,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="280" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A280" s="12"/>
       <c r="B280" s="12"/>
       <c r="C280" s="12"/>
-      <c r="D280" s="12" t="s">
+      <c r="D280" s="41" t="s">
         <v>291</v>
       </c>
       <c r="E280" s="12"/>
@@ -5295,11 +5355,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="281" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A281" s="12"/>
       <c r="B281" s="12"/>
       <c r="C281" s="12"/>
-      <c r="D281" s="12" t="s">
+      <c r="D281" s="41" t="s">
         <v>20</v>
       </c>
       <c r="E281" s="12"/>
@@ -5307,11 +5367,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="282" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A282" s="12"/>
       <c r="B282" s="12"/>
       <c r="C282" s="12"/>
-      <c r="D282" s="12" t="s">
+      <c r="D282" s="41" t="s">
         <v>19</v>
       </c>
       <c r="E282" s="12"/>
@@ -5319,11 +5379,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="283" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="283" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A283" s="12"/>
       <c r="B283" s="12"/>
       <c r="C283" s="12"/>
-      <c r="D283" s="12" t="s">
+      <c r="D283" s="41" t="s">
         <v>292</v>
       </c>
       <c r="E283" s="12"/>
@@ -5331,11 +5391,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="284" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="284" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A284" s="12"/>
       <c r="B284" s="12"/>
       <c r="C284" s="12"/>
-      <c r="D284" s="22" t="s">
+      <c r="D284" s="42" t="s">
         <v>389</v>
       </c>
       <c r="E284" s="28">
@@ -5343,7 +5403,7 @@
       </c>
       <c r="F284" s="12"/>
     </row>
-    <row r="285" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="285" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E285">
         <f>SUM(E273:E283)*E284</f>
         <v>0</v>
@@ -5353,7 +5413,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="286" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="286" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A286" s="7" t="s">
         <v>293</v>
       </c>
@@ -5361,13 +5421,13 @@
         <v>74</v>
       </c>
       <c r="C286" s="8"/>
-      <c r="D286" s="8"/>
+      <c r="D286" s="44"/>
       <c r="E286" s="8"/>
       <c r="F286" s="8">
         <v>5</v>
       </c>
     </row>
-    <row r="287" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="287" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A287" s="8"/>
       <c r="B287" s="8" t="s">
         <v>21</v>
@@ -5375,77 +5435,77 @@
       <c r="C287" s="8" t="s">
         <v>294</v>
       </c>
-      <c r="D287" s="8"/>
+      <c r="D287" s="44"/>
       <c r="E287" s="8"/>
       <c r="F287" s="8">
         <v>5</v>
       </c>
     </row>
-    <row r="288" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="288" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A288" s="8"/>
       <c r="B288" s="8"/>
       <c r="C288" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D288" s="8"/>
+      <c r="D288" s="44"/>
       <c r="E288" s="8"/>
       <c r="F288" s="8">
         <v>5</v>
       </c>
     </row>
-    <row r="289" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="289" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A289" s="8"/>
       <c r="B289" s="8"/>
       <c r="C289" s="8" t="s">
         <v>295</v>
       </c>
-      <c r="D289" s="8"/>
+      <c r="D289" s="44"/>
       <c r="E289" s="8"/>
       <c r="F289" s="8">
         <v>5</v>
       </c>
     </row>
-    <row r="290" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="290" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A290" s="8"/>
       <c r="B290" s="8"/>
       <c r="C290" s="8" t="s">
         <v>296</v>
       </c>
-      <c r="D290" s="8"/>
+      <c r="D290" s="44"/>
       <c r="E290" s="8"/>
       <c r="F290" s="8">
         <v>5</v>
       </c>
     </row>
-    <row r="291" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="291" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A291" s="8"/>
       <c r="B291" s="8"/>
       <c r="C291" s="8" t="s">
         <v>297</v>
       </c>
-      <c r="D291" s="8"/>
+      <c r="D291" s="44"/>
       <c r="E291" s="8"/>
       <c r="F291" s="8">
         <v>5</v>
       </c>
     </row>
-    <row r="292" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="292" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A292" s="8"/>
       <c r="B292" s="8"/>
       <c r="C292" s="8" t="s">
         <v>298</v>
       </c>
-      <c r="D292" s="8"/>
+      <c r="D292" s="44"/>
       <c r="E292" s="8"/>
       <c r="F292" s="8">
         <v>5</v>
       </c>
     </row>
-    <row r="293" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="293" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A293" s="8"/>
       <c r="B293" s="8"/>
       <c r="C293" s="8"/>
-      <c r="D293" s="22" t="s">
+      <c r="D293" s="42" t="s">
         <v>389</v>
       </c>
       <c r="E293" s="28">
@@ -5453,7 +5513,7 @@
       </c>
       <c r="F293" s="8"/>
     </row>
-    <row r="294" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="294" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E294">
         <f>SUM(E286:E292)*E293</f>
         <v>0</v>
@@ -5463,7 +5523,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="296" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="296" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A296" s="7" t="s">
         <v>299</v>
       </c>
@@ -5471,13 +5531,13 @@
         <v>300</v>
       </c>
       <c r="C296" s="8"/>
-      <c r="D296" s="8"/>
+      <c r="D296" s="44"/>
       <c r="E296" s="8"/>
       <c r="F296" s="8">
         <v>5</v>
       </c>
     </row>
-    <row r="297" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="297" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A297" s="7" t="s">
         <v>301</v>
       </c>
@@ -5485,41 +5545,41 @@
         <v>302</v>
       </c>
       <c r="C297" s="8"/>
-      <c r="D297" s="8"/>
+      <c r="D297" s="44"/>
       <c r="E297" s="8"/>
       <c r="F297" s="8">
         <v>5</v>
       </c>
     </row>
-    <row r="298" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="298" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A298" s="8"/>
       <c r="B298" s="8" t="s">
         <v>303</v>
       </c>
       <c r="C298" s="8"/>
-      <c r="D298" s="8"/>
+      <c r="D298" s="44"/>
       <c r="E298" s="8"/>
       <c r="F298" s="8">
         <v>5</v>
       </c>
     </row>
-    <row r="299" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="299" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A299" s="8"/>
       <c r="B299" s="8" t="s">
         <v>304</v>
       </c>
       <c r="C299" s="8"/>
-      <c r="D299" s="8"/>
+      <c r="D299" s="44"/>
       <c r="E299" s="8"/>
       <c r="F299" s="8">
         <v>5</v>
       </c>
     </row>
-    <row r="300" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="300" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A300" s="8"/>
       <c r="B300" s="8"/>
       <c r="C300" s="8"/>
-      <c r="D300" s="22" t="s">
+      <c r="D300" s="42" t="s">
         <v>389</v>
       </c>
       <c r="E300" s="28">
@@ -5527,7 +5587,7 @@
       </c>
       <c r="F300" s="8"/>
     </row>
-    <row r="301" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="301" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E301">
         <f>SUM(E296:E299)*E300</f>
         <v>0</v>
@@ -5537,7 +5597,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="303" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="303" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A303" s="16" t="s">
         <v>305</v>
       </c>
@@ -5545,37 +5605,37 @@
         <v>306</v>
       </c>
       <c r="C303" s="14"/>
-      <c r="D303" s="14"/>
+      <c r="D303" s="24"/>
       <c r="E303" s="14"/>
       <c r="F303" s="14">
         <v>5</v>
       </c>
     </row>
-    <row r="304" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="304" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A304" s="14"/>
       <c r="B304" s="14" t="s">
         <v>307</v>
       </c>
       <c r="C304" s="14"/>
-      <c r="D304" s="14"/>
+      <c r="D304" s="24"/>
       <c r="E304" s="14"/>
       <c r="F304" s="14">
         <v>10</v>
       </c>
     </row>
-    <row r="305" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="305" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A305" s="14"/>
       <c r="B305" s="14" t="s">
         <v>134</v>
       </c>
       <c r="C305" s="14"/>
-      <c r="D305" s="14"/>
+      <c r="D305" s="24"/>
       <c r="E305" s="14"/>
       <c r="F305" s="14">
         <v>10</v>
       </c>
     </row>
-    <row r="306" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="306" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A306" s="16" t="s">
         <v>308</v>
       </c>
@@ -5583,25 +5643,25 @@
         <v>309</v>
       </c>
       <c r="C306" s="14"/>
-      <c r="D306" s="14"/>
+      <c r="D306" s="24"/>
       <c r="E306" s="14"/>
       <c r="F306" s="14">
         <v>5</v>
       </c>
     </row>
-    <row r="307" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="307" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A307" s="14"/>
       <c r="B307" s="14" t="s">
         <v>310</v>
       </c>
       <c r="C307" s="14"/>
-      <c r="D307" s="14"/>
+      <c r="D307" s="24"/>
       <c r="E307" s="14"/>
       <c r="F307" s="14">
         <v>15</v>
       </c>
     </row>
-    <row r="308" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="308" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A308" s="16" t="s">
         <v>359</v>
       </c>
@@ -5609,7 +5669,7 @@
       <c r="C308" s="14" t="s">
         <v>224</v>
       </c>
-      <c r="D308" s="14" t="s">
+      <c r="D308" s="24" t="s">
         <v>360</v>
       </c>
       <c r="E308" s="14"/>
@@ -5617,35 +5677,35 @@
         <v>15</v>
       </c>
     </row>
-    <row r="309" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="309" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A309" s="14"/>
       <c r="B309" s="14"/>
       <c r="C309" s="14" t="s">
         <v>232</v>
       </c>
-      <c r="D309" s="14"/>
+      <c r="D309" s="24"/>
       <c r="E309" s="14"/>
       <c r="F309" s="14">
         <v>5</v>
       </c>
     </row>
-    <row r="310" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="310" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A310" s="14"/>
       <c r="B310" s="14"/>
       <c r="C310" s="14" t="s">
         <v>225</v>
       </c>
-      <c r="D310" s="14"/>
+      <c r="D310" s="24"/>
       <c r="E310" s="14"/>
       <c r="F310" s="14">
         <v>5</v>
       </c>
     </row>
-    <row r="311" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="311" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A311" s="14"/>
       <c r="B311" s="14"/>
       <c r="C311" s="14"/>
-      <c r="D311" s="22" t="s">
+      <c r="D311" s="42" t="s">
         <v>389</v>
       </c>
       <c r="E311" s="28">
@@ -5653,7 +5713,7 @@
       </c>
       <c r="F311" s="14"/>
     </row>
-    <row r="312" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="312" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E312">
         <f>SUM(E303:E310)*E311</f>
         <v>0</v>
@@ -5663,7 +5723,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="313" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="313" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A313" s="11" t="s">
         <v>35</v>
       </c>
@@ -5671,31 +5731,31 @@
         <v>311</v>
       </c>
       <c r="C313" s="12"/>
-      <c r="D313" s="12"/>
+      <c r="D313" s="41"/>
       <c r="E313" s="12"/>
       <c r="F313" s="12">
         <v>5</v>
       </c>
     </row>
-    <row r="314" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="314" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A314" s="12"/>
       <c r="B314" s="12" t="s">
         <v>251</v>
       </c>
       <c r="C314" s="12"/>
-      <c r="D314" s="12"/>
+      <c r="D314" s="41"/>
       <c r="E314" s="12"/>
       <c r="F314" s="12">
         <v>10</v>
       </c>
     </row>
-    <row r="315" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="315" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A315" s="11"/>
       <c r="B315" s="12" t="s">
         <v>320</v>
       </c>
       <c r="C315" s="12"/>
-      <c r="D315" s="12"/>
+      <c r="D315" s="41"/>
       <c r="E315" s="12" t="s">
         <v>319</v>
       </c>
@@ -5703,13 +5763,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="316" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="316" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A316" s="12"/>
       <c r="B316" s="12" t="s">
         <v>312</v>
       </c>
       <c r="C316" s="12"/>
-      <c r="D316" s="12"/>
+      <c r="D316" s="41"/>
       <c r="E316" s="12" t="s">
         <v>319</v>
       </c>
@@ -5717,13 +5777,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="317" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="317" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A317" s="11"/>
       <c r="B317" s="12" t="s">
         <v>230</v>
       </c>
       <c r="C317" s="12"/>
-      <c r="D317" s="12"/>
+      <c r="D317" s="41"/>
       <c r="E317" s="12" t="s">
         <v>319</v>
       </c>
@@ -5731,13 +5791,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="318" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="318" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A318" s="11"/>
       <c r="B318" s="12" t="s">
         <v>321</v>
       </c>
       <c r="C318" s="12"/>
-      <c r="D318" s="12"/>
+      <c r="D318" s="41"/>
       <c r="E318" s="12" t="s">
         <v>319</v>
       </c>
@@ -5745,59 +5805,59 @@
         <v>5</v>
       </c>
     </row>
-    <row r="319" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="319" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A319" s="11"/>
       <c r="B319" s="12" t="s">
         <v>322</v>
       </c>
       <c r="C319" s="12"/>
-      <c r="D319" s="12"/>
+      <c r="D319" s="41"/>
       <c r="E319" s="12"/>
       <c r="F319" s="12">
         <v>5</v>
       </c>
     </row>
-    <row r="320" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="320" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A320" s="12"/>
       <c r="B320" s="12" t="s">
         <v>313</v>
       </c>
       <c r="C320" s="12"/>
-      <c r="D320" s="12"/>
+      <c r="D320" s="41"/>
       <c r="E320" s="12"/>
       <c r="F320" s="12">
         <v>5</v>
       </c>
     </row>
-    <row r="321" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="321" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A321" s="12"/>
       <c r="B321" s="12" t="s">
         <v>314</v>
       </c>
       <c r="C321" s="12"/>
-      <c r="D321" s="12"/>
+      <c r="D321" s="41"/>
       <c r="E321" s="12"/>
       <c r="F321" s="12">
         <v>5</v>
       </c>
     </row>
-    <row r="322" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="322" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A322" s="12"/>
       <c r="B322" s="12" t="s">
         <v>40</v>
       </c>
       <c r="C322" s="12"/>
-      <c r="D322" s="12"/>
+      <c r="D322" s="41"/>
       <c r="E322" s="12"/>
       <c r="F322" s="12">
         <v>10</v>
       </c>
     </row>
-    <row r="323" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="323" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A323" s="12"/>
       <c r="B323" s="12"/>
       <c r="C323" s="12"/>
-      <c r="D323" s="22" t="s">
+      <c r="D323" s="42" t="s">
         <v>389</v>
       </c>
       <c r="E323" s="28">
@@ -5805,7 +5865,7 @@
       </c>
       <c r="F323" s="12"/>
     </row>
-    <row r="324" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="324" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E324">
         <f>SUM(E313:E322)*E323</f>
         <v>0</v>
@@ -5815,7 +5875,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="326" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="326" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A326" s="7" t="s">
         <v>347</v>
       </c>
@@ -5823,25 +5883,25 @@
         <v>190</v>
       </c>
       <c r="C326" s="8"/>
-      <c r="D326" s="8"/>
+      <c r="D326" s="44"/>
       <c r="E326" s="8"/>
       <c r="F326" s="8">
         <v>25</v>
       </c>
     </row>
-    <row r="327" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="327" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A327" s="7"/>
       <c r="B327" s="8" t="s">
         <v>191</v>
       </c>
       <c r="C327" s="8"/>
-      <c r="D327" s="8"/>
+      <c r="D327" s="44"/>
       <c r="E327" s="8"/>
       <c r="F327" s="8">
         <v>25</v>
       </c>
     </row>
-    <row r="328" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="328" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A328" s="7"/>
       <c r="B328" s="8" t="s">
         <v>192</v>
@@ -5849,65 +5909,65 @@
       <c r="C328" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="D328" s="8"/>
+      <c r="D328" s="44"/>
       <c r="E328" s="8"/>
       <c r="F328" s="8">
         <v>10</v>
       </c>
     </row>
-    <row r="329" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="329" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A329" s="7"/>
       <c r="B329" s="8"/>
       <c r="C329" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="D329" s="8"/>
+      <c r="D329" s="44"/>
       <c r="E329" s="8"/>
       <c r="F329" s="8">
         <v>10</v>
       </c>
     </row>
-    <row r="330" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="330" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A330" s="7"/>
       <c r="B330" s="8"/>
       <c r="C330" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="D330" s="8"/>
+      <c r="D330" s="44"/>
       <c r="E330" s="8"/>
       <c r="F330" s="8">
         <v>10</v>
       </c>
     </row>
-    <row r="331" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="331" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A331" s="7"/>
       <c r="B331" s="8"/>
       <c r="C331" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="D331" s="8"/>
+      <c r="D331" s="44"/>
       <c r="E331" s="8"/>
       <c r="F331" s="8">
         <v>10</v>
       </c>
     </row>
-    <row r="332" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="332" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A332" s="7"/>
       <c r="B332" s="8"/>
       <c r="C332" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D332" s="8"/>
+      <c r="D332" s="44"/>
       <c r="E332" s="8"/>
       <c r="F332" s="8">
         <v>10</v>
       </c>
     </row>
-    <row r="333" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="333" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A333" s="7"/>
       <c r="B333" s="8"/>
       <c r="C333" s="8"/>
-      <c r="D333" s="22" t="s">
+      <c r="D333" s="42" t="s">
         <v>389</v>
       </c>
       <c r="E333" s="28">
@@ -5915,7 +5975,7 @@
       </c>
       <c r="F333" s="8"/>
     </row>
-    <row r="334" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="334" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A334" s="1"/>
       <c r="E334">
         <f>SUM(E326:E332)*E333</f>
@@ -5926,7 +5986,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="335" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="335" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A335" s="7" t="s">
         <v>78</v>
       </c>
@@ -5934,73 +5994,73 @@
         <v>13</v>
       </c>
       <c r="C335" s="8"/>
-      <c r="D335" s="8"/>
+      <c r="D335" s="44"/>
       <c r="E335" s="8"/>
       <c r="F335" s="8">
         <v>10</v>
       </c>
     </row>
-    <row r="336" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="336" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A336" s="7"/>
       <c r="B336" s="8" t="s">
         <v>46</v>
       </c>
       <c r="C336" s="8"/>
-      <c r="D336" s="8"/>
+      <c r="D336" s="44"/>
       <c r="E336" s="8"/>
       <c r="F336" s="8">
         <v>5</v>
       </c>
     </row>
-    <row r="337" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="337" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A337" s="7"/>
       <c r="B337" s="8" t="s">
         <v>358</v>
       </c>
       <c r="C337" s="8"/>
-      <c r="D337" s="8"/>
+      <c r="D337" s="44"/>
       <c r="E337" s="8"/>
       <c r="F337" s="8">
         <v>15</v>
       </c>
     </row>
-    <row r="338" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="338" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A338" s="7"/>
       <c r="B338" s="8" t="s">
         <v>169</v>
       </c>
       <c r="C338" s="8"/>
-      <c r="D338" s="8"/>
+      <c r="D338" s="44"/>
       <c r="E338" s="8"/>
       <c r="F338" s="8">
         <v>5</v>
       </c>
     </row>
-    <row r="339" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="339" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A339" s="7"/>
       <c r="B339" s="8" t="s">
         <v>77</v>
       </c>
       <c r="C339" s="8"/>
-      <c r="D339" s="8"/>
+      <c r="D339" s="44"/>
       <c r="E339" s="8"/>
       <c r="F339" s="8">
         <v>5</v>
       </c>
     </row>
-    <row r="340" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="340" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A340" s="7"/>
       <c r="B340" s="8" t="s">
         <v>79</v>
       </c>
       <c r="C340" s="8"/>
-      <c r="D340" s="8"/>
+      <c r="D340" s="44"/>
       <c r="E340" s="8"/>
       <c r="F340" s="8">
         <v>25</v>
       </c>
     </row>
-    <row r="341" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="341" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A341" s="7"/>
       <c r="B341" s="7" t="s">
         <v>57</v>
@@ -6008,67 +6068,67 @@
       <c r="C341" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="D341" s="8"/>
+      <c r="D341" s="44"/>
       <c r="E341" s="8"/>
       <c r="F341" s="8">
         <v>5</v>
       </c>
     </row>
-    <row r="342" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="342" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A342" s="7"/>
       <c r="B342" s="7"/>
       <c r="C342" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="D342" s="8"/>
+      <c r="D342" s="44"/>
       <c r="E342" s="8"/>
       <c r="F342" s="8">
         <v>10</v>
       </c>
     </row>
-    <row r="343" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="343" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A343" s="7"/>
       <c r="B343" s="7"/>
       <c r="C343" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="D343" s="8"/>
+      <c r="D343" s="44"/>
       <c r="E343" s="8"/>
       <c r="F343" s="8">
         <v>25</v>
       </c>
     </row>
-    <row r="344" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="344" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A344" s="7"/>
       <c r="B344" s="7"/>
       <c r="C344" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D344" s="8"/>
+      <c r="D344" s="44"/>
       <c r="E344" s="8"/>
       <c r="F344" s="8">
         <v>20</v>
       </c>
     </row>
-    <row r="345" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="345" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A345" s="7"/>
       <c r="B345" s="7"/>
       <c r="C345" s="8" t="s">
         <v>231</v>
       </c>
-      <c r="D345" s="8"/>
+      <c r="D345" s="44"/>
       <c r="E345" s="8"/>
       <c r="F345" s="8">
         <v>20</v>
       </c>
     </row>
-    <row r="346" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="346" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A346" s="7"/>
       <c r="B346" s="7"/>
       <c r="C346" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="D346" s="8" t="s">
+      <c r="D346" s="44" t="s">
         <v>69</v>
       </c>
       <c r="E346" s="8"/>
@@ -6076,11 +6136,11 @@
         <v>3</v>
       </c>
     </row>
-    <row r="347" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="347" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A347" s="7"/>
       <c r="B347" s="7"/>
       <c r="C347" s="8"/>
-      <c r="D347" s="8" t="s">
+      <c r="D347" s="44" t="s">
         <v>70</v>
       </c>
       <c r="E347" s="8"/>
@@ -6088,11 +6148,11 @@
         <v>3</v>
       </c>
     </row>
-    <row r="348" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="348" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A348" s="7"/>
       <c r="B348" s="7"/>
       <c r="C348" s="8"/>
-      <c r="D348" s="8" t="s">
+      <c r="D348" s="44" t="s">
         <v>71</v>
       </c>
       <c r="E348" s="8"/>
@@ -6100,11 +6160,11 @@
         <v>3</v>
       </c>
     </row>
-    <row r="349" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="349" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A349" s="7"/>
       <c r="B349" s="7"/>
       <c r="C349" s="8"/>
-      <c r="D349" s="8" t="s">
+      <c r="D349" s="44" t="s">
         <v>54</v>
       </c>
       <c r="E349" s="8"/>
@@ -6112,11 +6172,11 @@
         <v>3</v>
       </c>
     </row>
-    <row r="350" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="350" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A350" s="7"/>
       <c r="B350" s="7"/>
       <c r="C350" s="8"/>
-      <c r="D350" s="8" t="s">
+      <c r="D350" s="44" t="s">
         <v>72</v>
       </c>
       <c r="E350" s="8"/>
@@ -6124,11 +6184,11 @@
         <v>3</v>
       </c>
     </row>
-    <row r="351" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="351" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A351" s="7"/>
       <c r="B351" s="7"/>
       <c r="C351" s="8"/>
-      <c r="D351" s="22" t="s">
+      <c r="D351" s="42" t="s">
         <v>389</v>
       </c>
       <c r="E351" s="28">
@@ -6136,7 +6196,7 @@
       </c>
       <c r="F351" s="8"/>
     </row>
-    <row r="352" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="352" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E352">
         <f>SUM(E335:E350)*E351</f>
         <v>0</v>
@@ -6146,12 +6206,12 @@
         <v>160</v>
       </c>
     </row>
-    <row r="353" spans="1:6" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="353" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A353" s="5" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="354" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="354" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A354" s="13" t="s">
         <v>220</v>
       </c>
@@ -6159,13 +6219,13 @@
         <v>221</v>
       </c>
       <c r="C354" s="13"/>
-      <c r="D354" s="13"/>
+      <c r="D354" s="40"/>
       <c r="E354" s="13"/>
       <c r="F354" s="13">
         <v>10</v>
       </c>
     </row>
-    <row r="355" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="355" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A355" s="13"/>
       <c r="B355" s="13" t="s">
         <v>387</v>
@@ -6173,37 +6233,37 @@
       <c r="C355" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="D355" s="13"/>
+      <c r="D355" s="40"/>
       <c r="E355" s="13"/>
       <c r="F355" s="13">
         <v>30</v>
       </c>
     </row>
-    <row r="356" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="356" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A356" s="13"/>
       <c r="B356" s="13"/>
       <c r="C356" s="13" t="s">
         <v>222</v>
       </c>
-      <c r="D356" s="13"/>
+      <c r="D356" s="40"/>
       <c r="E356" s="13"/>
       <c r="F356" s="13">
         <v>30</v>
       </c>
     </row>
-    <row r="357" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="357" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A357" s="13"/>
       <c r="B357" s="13"/>
       <c r="C357" s="13" t="s">
         <v>223</v>
       </c>
-      <c r="D357" s="13"/>
+      <c r="D357" s="40"/>
       <c r="E357" s="13"/>
       <c r="F357" s="13">
         <v>30</v>
       </c>
     </row>
-    <row r="358" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="358" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A358" s="13"/>
       <c r="B358" s="13" t="s">
         <v>388</v>
@@ -6211,41 +6271,41 @@
       <c r="C358" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="D358" s="13"/>
+      <c r="D358" s="40"/>
       <c r="E358" s="13"/>
       <c r="F358" s="13">
         <v>30</v>
       </c>
     </row>
-    <row r="359" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="359" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A359" s="13"/>
       <c r="B359" s="13"/>
       <c r="C359" s="13" t="s">
         <v>222</v>
       </c>
-      <c r="D359" s="13"/>
+      <c r="D359" s="40"/>
       <c r="E359" s="13"/>
       <c r="F359" s="13">
         <v>30</v>
       </c>
     </row>
-    <row r="360" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="360" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A360" s="13"/>
       <c r="B360" s="13"/>
       <c r="C360" s="13" t="s">
         <v>223</v>
       </c>
-      <c r="D360" s="13"/>
+      <c r="D360" s="40"/>
       <c r="E360" s="13"/>
       <c r="F360" s="13">
         <v>30</v>
       </c>
     </row>
-    <row r="361" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="361" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A361" s="13"/>
       <c r="B361" s="13"/>
       <c r="C361" s="13"/>
-      <c r="D361" s="22" t="s">
+      <c r="D361" s="42" t="s">
         <v>389</v>
       </c>
       <c r="E361" s="28">
@@ -6253,7 +6313,7 @@
       </c>
       <c r="F361" s="13"/>
     </row>
-    <row r="362" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="362" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E362">
         <f>SUM(E354:E360)*E361</f>
         <v>0</v>
@@ -6263,12 +6323,13 @@
         <v>190</v>
       </c>
     </row>
-    <row r="363" spans="1:6" s="18" customFormat="1" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="363" spans="1:6" s="18" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A363" s="5" t="s">
         <v>283</v>
       </c>
-    </row>
-    <row r="364" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="D363" s="46"/>
+    </row>
+    <row r="364" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A364" s="15" t="s">
         <v>361</v>
       </c>
@@ -6276,7 +6337,7 @@
       <c r="C364" s="13" t="s">
         <v>183</v>
       </c>
-      <c r="D364" s="13"/>
+      <c r="D364" s="40"/>
       <c r="E364" s="13">
         <v>0</v>
       </c>
@@ -6284,13 +6345,13 @@
         <v>5</v>
       </c>
     </row>
-    <row r="365" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="365" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A365" s="13"/>
       <c r="B365" s="13"/>
       <c r="C365" s="13" t="s">
         <v>187</v>
       </c>
-      <c r="D365" s="13"/>
+      <c r="D365" s="40"/>
       <c r="E365" s="13">
         <v>0</v>
       </c>
@@ -6298,13 +6359,13 @@
         <v>5</v>
       </c>
     </row>
-    <row r="366" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="366" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A366" s="13"/>
       <c r="B366" s="13"/>
       <c r="C366" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="D366" s="13"/>
+      <c r="D366" s="40"/>
       <c r="E366" s="13">
         <v>0</v>
       </c>
@@ -6312,13 +6373,13 @@
         <v>5</v>
       </c>
     </row>
-    <row r="367" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="367" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A367" s="13"/>
       <c r="B367" s="13"/>
       <c r="C367" s="13" t="s">
         <v>188</v>
       </c>
-      <c r="D367" s="13"/>
+      <c r="D367" s="40"/>
       <c r="E367" s="13">
         <v>0</v>
       </c>
@@ -6326,13 +6387,13 @@
         <v>5</v>
       </c>
     </row>
-    <row r="368" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="368" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A368" s="13"/>
       <c r="B368" s="13"/>
       <c r="C368" s="13" t="s">
         <v>189</v>
       </c>
-      <c r="D368" s="13"/>
+      <c r="D368" s="40"/>
       <c r="E368" s="13">
         <v>0</v>
       </c>
@@ -6340,13 +6401,13 @@
         <v>5</v>
       </c>
     </row>
-    <row r="369" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="369" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A369" s="13"/>
       <c r="B369" s="13"/>
       <c r="C369" s="13" t="s">
         <v>190</v>
       </c>
-      <c r="D369" s="13"/>
+      <c r="D369" s="40"/>
       <c r="E369" s="13">
         <v>0</v>
       </c>
@@ -6354,11 +6415,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="370" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="370" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A370" s="13"/>
       <c r="B370" s="13"/>
       <c r="C370" s="13"/>
-      <c r="D370" s="22" t="s">
+      <c r="D370" s="42" t="s">
         <v>389</v>
       </c>
       <c r="E370" s="28">
@@ -6366,7 +6427,7 @@
       </c>
       <c r="F370" s="13"/>
     </row>
-    <row r="371" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="371" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E371">
         <f>SUM(E364:E369)*E370</f>
         <v>0</v>
@@ -6376,7 +6437,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="372" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="372" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A372" s="15" t="s">
         <v>44</v>
       </c>
@@ -6384,45 +6445,45 @@
         <v>356</v>
       </c>
       <c r="C372" s="17"/>
-      <c r="D372" s="13"/>
+      <c r="D372" s="40"/>
       <c r="E372" s="13"/>
       <c r="F372" s="13">
         <v>10</v>
       </c>
     </row>
-    <row r="373" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="373" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A373" s="15"/>
       <c r="B373" s="17" t="s">
         <v>77</v>
       </c>
       <c r="C373" s="17"/>
-      <c r="D373" s="13"/>
+      <c r="D373" s="40"/>
       <c r="E373" s="13"/>
       <c r="F373" s="13">
         <v>5</v>
       </c>
     </row>
-    <row r="374" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="374" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A374" s="15"/>
       <c r="B374" s="17" t="s">
         <v>124</v>
       </c>
       <c r="C374" s="17"/>
-      <c r="D374" s="13"/>
+      <c r="D374" s="40"/>
       <c r="E374" s="13"/>
       <c r="F374" s="13">
         <v>5</v>
       </c>
     </row>
-    <row r="375" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="375" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A375" s="15"/>
       <c r="B375" s="13"/>
       <c r="C375" s="13"/>
-      <c r="D375" s="13"/>
+      <c r="D375" s="40"/>
       <c r="E375" s="13"/>
       <c r="F375" s="13"/>
     </row>
-    <row r="376" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="376" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A376" s="15" t="s">
         <v>122</v>
       </c>
@@ -6430,45 +6491,45 @@
         <v>77</v>
       </c>
       <c r="C376" s="13"/>
-      <c r="D376" s="13"/>
+      <c r="D376" s="40"/>
       <c r="E376" s="13"/>
       <c r="F376" s="13">
         <v>5</v>
       </c>
     </row>
-    <row r="377" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="377" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A377" s="15"/>
       <c r="B377" s="13" t="s">
         <v>123</v>
       </c>
       <c r="C377" s="13"/>
-      <c r="D377" s="13"/>
+      <c r="D377" s="40"/>
       <c r="E377" s="13"/>
       <c r="F377" s="13">
         <v>5</v>
       </c>
     </row>
-    <row r="378" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="378" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A378" s="15"/>
       <c r="B378" s="13" t="s">
         <v>124</v>
       </c>
       <c r="C378" s="13"/>
-      <c r="D378" s="13"/>
+      <c r="D378" s="40"/>
       <c r="E378" s="13"/>
       <c r="F378" s="13">
         <v>5</v>
       </c>
     </row>
-    <row r="379" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="379" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A379" s="15"/>
       <c r="B379" s="13"/>
       <c r="C379" s="13"/>
-      <c r="D379" s="13"/>
+      <c r="D379" s="40"/>
       <c r="E379" s="13"/>
       <c r="F379" s="13"/>
     </row>
-    <row r="380" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="380" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A380" s="15" t="s">
         <v>227</v>
       </c>
@@ -6476,41 +6537,41 @@
         <v>77</v>
       </c>
       <c r="C380" s="13"/>
-      <c r="D380" s="13"/>
+      <c r="D380" s="40"/>
       <c r="E380" s="13"/>
       <c r="F380" s="13">
         <v>5</v>
       </c>
     </row>
-    <row r="381" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="381" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A381" s="15"/>
       <c r="B381" s="13" t="s">
         <v>123</v>
       </c>
       <c r="C381" s="13"/>
-      <c r="D381" s="13"/>
+      <c r="D381" s="40"/>
       <c r="E381" s="13"/>
       <c r="F381" s="13">
         <v>5</v>
       </c>
     </row>
-    <row r="382" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="382" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A382" s="15"/>
       <c r="B382" s="13" t="s">
         <v>124</v>
       </c>
       <c r="C382" s="13"/>
-      <c r="D382" s="13"/>
+      <c r="D382" s="40"/>
       <c r="E382" s="13"/>
       <c r="F382" s="13">
         <v>5</v>
       </c>
     </row>
-    <row r="383" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="383" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A383" s="15"/>
       <c r="B383" s="13"/>
       <c r="C383" s="13"/>
-      <c r="D383" s="22" t="s">
+      <c r="D383" s="42" t="s">
         <v>389</v>
       </c>
       <c r="E383" s="28">
@@ -6518,7 +6579,7 @@
       </c>
       <c r="F383" s="13"/>
     </row>
-    <row r="384" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="384" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A384" s="1"/>
       <c r="E384">
         <f>SUM(E372:E382)*E383</f>
@@ -6529,7 +6590,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="385" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="385" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A385" s="16" t="s">
         <v>45</v>
       </c>
@@ -6537,14 +6598,14 @@
         <v>226</v>
       </c>
       <c r="C385" s="14"/>
-      <c r="D385" s="14"/>
+      <c r="D385" s="24"/>
       <c r="E385" s="14"/>
       <c r="F385" s="14">
         <v>5</v>
       </c>
       <c r="M385" s="20"/>
     </row>
-    <row r="386" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="386" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A386" s="16" t="s">
         <v>357</v>
       </c>
@@ -6552,18 +6613,18 @@
         <v>50</v>
       </c>
       <c r="C386" s="14"/>
-      <c r="D386" s="14"/>
+      <c r="D386" s="24"/>
       <c r="E386" s="14"/>
       <c r="F386" s="14">
         <v>5</v>
       </c>
       <c r="M386" s="20"/>
     </row>
-    <row r="387" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="387" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A387" s="16"/>
       <c r="B387" s="14"/>
       <c r="C387" s="14"/>
-      <c r="D387" s="22" t="s">
+      <c r="D387" s="42" t="s">
         <v>389</v>
       </c>
       <c r="E387" s="28">
@@ -6572,7 +6633,7 @@
       <c r="F387" s="14"/>
       <c r="M387" s="20"/>
     </row>
-    <row r="388" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="388" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A388" s="1"/>
       <c r="E388">
         <f>SUM(E385:E386)*E387</f>
@@ -6584,12 +6645,12 @@
       </c>
       <c r="M388" s="20"/>
     </row>
-    <row r="391" spans="1:13" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="391" spans="1:13" ht="18" x14ac:dyDescent="0.35">
       <c r="A391" s="5" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="392" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="392" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A392" s="11" t="s">
         <v>104</v>
       </c>
@@ -6597,115 +6658,115 @@
         <v>105</v>
       </c>
       <c r="C392" s="12"/>
-      <c r="D392" s="12"/>
+      <c r="D392" s="41"/>
       <c r="E392" s="12"/>
       <c r="F392" s="12">
         <v>10</v>
       </c>
     </row>
-    <row r="393" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="393" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A393" s="12"/>
       <c r="B393" s="12" t="s">
         <v>106</v>
       </c>
       <c r="C393" s="12"/>
-      <c r="D393" s="12"/>
+      <c r="D393" s="41"/>
       <c r="E393" s="12"/>
       <c r="F393" s="12">
         <v>10</v>
       </c>
     </row>
-    <row r="394" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="394" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A394" s="12"/>
       <c r="B394" s="12" t="s">
         <v>107</v>
       </c>
       <c r="C394" s="12"/>
-      <c r="D394" s="12"/>
+      <c r="D394" s="41"/>
       <c r="E394" s="12"/>
       <c r="F394" s="12">
         <v>10</v>
       </c>
     </row>
-    <row r="395" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="395" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A395" s="12"/>
       <c r="B395" s="12" t="s">
         <v>108</v>
       </c>
       <c r="C395" s="12"/>
-      <c r="D395" s="12"/>
+      <c r="D395" s="41"/>
       <c r="E395" s="12"/>
       <c r="F395" s="12">
         <v>10</v>
       </c>
     </row>
-    <row r="396" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="396" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A396" s="11" t="s">
         <v>120</v>
       </c>
       <c r="B396" s="12"/>
       <c r="C396" s="12"/>
-      <c r="D396" s="12"/>
+      <c r="D396" s="41"/>
       <c r="E396" s="12"/>
       <c r="F396" s="12"/>
     </row>
-    <row r="397" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="397" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A397" s="11"/>
       <c r="B397" s="12" t="s">
         <v>142</v>
       </c>
       <c r="C397" s="12"/>
-      <c r="D397" s="12"/>
+      <c r="D397" s="41"/>
       <c r="E397" s="12"/>
       <c r="F397" s="12">
         <v>5</v>
       </c>
     </row>
-    <row r="398" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="398" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A398" s="12"/>
       <c r="B398" s="12" t="s">
         <v>143</v>
       </c>
       <c r="C398" s="12"/>
-      <c r="D398" s="12"/>
+      <c r="D398" s="41"/>
       <c r="E398" s="12"/>
       <c r="F398" s="12">
         <v>15</v>
       </c>
     </row>
-    <row r="399" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="399" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A399" s="12"/>
       <c r="B399" s="12" t="s">
         <v>144</v>
       </c>
       <c r="C399" s="12"/>
-      <c r="D399" s="12"/>
+      <c r="D399" s="41"/>
       <c r="E399" s="12"/>
       <c r="F399" s="12">
         <v>20</v>
       </c>
     </row>
-    <row r="400" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="400" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A400" s="12"/>
       <c r="B400" s="12" t="s">
         <v>145</v>
       </c>
       <c r="C400" s="12"/>
-      <c r="D400" s="12"/>
+      <c r="D400" s="41"/>
       <c r="E400" s="12"/>
       <c r="F400" s="12">
         <v>5</v>
       </c>
     </row>
-    <row r="401" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="401" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A401" s="12"/>
       <c r="B401" s="12"/>
       <c r="C401" s="12"/>
-      <c r="D401" s="12"/>
+      <c r="D401" s="41"/>
       <c r="E401" s="12"/>
       <c r="F401" s="12"/>
     </row>
-    <row r="402" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="402" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A402" s="12" t="s">
         <v>146</v>
       </c>
@@ -6713,41 +6774,41 @@
         <v>147</v>
       </c>
       <c r="C402" s="12"/>
-      <c r="D402" s="12"/>
+      <c r="D402" s="41"/>
       <c r="E402" s="12"/>
       <c r="F402" s="12">
         <v>5</v>
       </c>
     </row>
-    <row r="403" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="403" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A403" s="12"/>
       <c r="B403" s="12" t="s">
         <v>148</v>
       </c>
       <c r="C403" s="12"/>
-      <c r="D403" s="12"/>
+      <c r="D403" s="41"/>
       <c r="E403" s="12"/>
       <c r="F403" s="12">
         <v>15</v>
       </c>
     </row>
-    <row r="404" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="404" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A404" s="12"/>
       <c r="B404" s="12" t="s">
         <v>149</v>
       </c>
       <c r="C404" s="12"/>
-      <c r="D404" s="12"/>
+      <c r="D404" s="41"/>
       <c r="E404" s="12"/>
       <c r="F404" s="12">
         <v>15</v>
       </c>
     </row>
-    <row r="405" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="405" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A405" s="12"/>
       <c r="B405" s="12"/>
       <c r="C405" s="12"/>
-      <c r="D405" s="22" t="s">
+      <c r="D405" s="42" t="s">
         <v>389</v>
       </c>
       <c r="E405" s="28">
@@ -6755,7 +6816,7 @@
       </c>
       <c r="F405" s="12"/>
     </row>
-    <row r="406" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="406" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E406">
         <f>SUM(E392:E404)*E405</f>
         <v>0</v>
@@ -6765,12 +6826,12 @@
         <v>120</v>
       </c>
     </row>
-    <row r="407" spans="1:6" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="407" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A407" s="5" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="408" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="408" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A408" s="7" t="s">
         <v>40</v>
       </c>
@@ -6780,113 +6841,113 @@
       <c r="C408" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="D408" s="8"/>
+      <c r="D408" s="44"/>
       <c r="E408" s="8"/>
       <c r="F408" s="8">
         <v>2</v>
       </c>
     </row>
-    <row r="409" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="409" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A409" s="7"/>
       <c r="B409" s="8"/>
       <c r="C409" s="8" t="s">
         <v>209</v>
       </c>
-      <c r="D409" s="8"/>
+      <c r="D409" s="44"/>
       <c r="E409" s="8"/>
       <c r="F409" s="8">
         <v>2</v>
       </c>
     </row>
-    <row r="410" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="410" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A410" s="7"/>
       <c r="B410" s="8"/>
       <c r="C410" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="D410" s="8"/>
+      <c r="D410" s="44"/>
       <c r="E410" s="8"/>
       <c r="F410" s="8">
         <v>2</v>
       </c>
     </row>
-    <row r="411" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="411" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A411" s="7"/>
       <c r="B411" s="8"/>
       <c r="C411" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="D411" s="8"/>
+      <c r="D411" s="44"/>
       <c r="E411" s="8"/>
       <c r="F411" s="8">
         <v>2</v>
       </c>
     </row>
-    <row r="412" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="412" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A412" s="7"/>
       <c r="B412" s="8"/>
       <c r="C412" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="D412" s="8"/>
+      <c r="D412" s="44"/>
       <c r="E412" s="8"/>
       <c r="F412" s="8">
         <v>2</v>
       </c>
     </row>
-    <row r="413" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="413" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A413" s="8"/>
       <c r="B413" s="8" t="s">
         <v>13</v>
       </c>
       <c r="C413" s="8"/>
-      <c r="D413" s="8"/>
+      <c r="D413" s="44"/>
       <c r="E413" s="8"/>
       <c r="F413" s="8">
         <v>5</v>
       </c>
     </row>
-    <row r="414" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="414" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A414" s="8"/>
       <c r="B414" s="8" t="s">
         <v>43</v>
       </c>
       <c r="C414" s="8"/>
-      <c r="D414" s="8"/>
+      <c r="D414" s="44"/>
       <c r="E414" s="8"/>
       <c r="F414" s="8">
         <v>5</v>
       </c>
     </row>
-    <row r="415" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="415" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A415" s="8"/>
       <c r="B415" s="8" t="s">
         <v>80</v>
       </c>
       <c r="C415" s="8"/>
-      <c r="D415" s="8"/>
+      <c r="D415" s="44"/>
       <c r="E415" s="8"/>
       <c r="F415" s="8">
         <v>5</v>
       </c>
     </row>
-    <row r="416" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="416" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A416" s="8"/>
       <c r="B416" s="8" t="s">
         <v>99</v>
       </c>
       <c r="C416" s="8"/>
-      <c r="D416" s="8"/>
+      <c r="D416" s="44"/>
       <c r="E416" s="8"/>
       <c r="F416" s="8">
         <v>5</v>
       </c>
     </row>
-    <row r="417" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="417" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A417" s="8"/>
       <c r="B417" s="8"/>
       <c r="C417" s="8"/>
-      <c r="D417" s="22" t="s">
+      <c r="D417" s="42" t="s">
         <v>389</v>
       </c>
       <c r="E417" s="28">
@@ -6894,7 +6955,7 @@
       </c>
       <c r="F417" s="8"/>
     </row>
-    <row r="418" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="418" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E418">
         <f>SUM(E408:E416)*E417</f>
         <v>0</v>
@@ -6904,7 +6965,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="419" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="419" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A419" s="14" t="s">
         <v>150</v>
       </c>
@@ -6912,113 +6973,113 @@
         <v>151</v>
       </c>
       <c r="C419" s="14"/>
-      <c r="D419" s="14"/>
+      <c r="D419" s="24"/>
       <c r="E419" s="14"/>
       <c r="F419" s="14">
         <v>3</v>
       </c>
     </row>
-    <row r="420" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="420" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A420" s="14"/>
       <c r="B420" s="14" t="s">
         <v>152</v>
       </c>
       <c r="C420" s="14"/>
-      <c r="D420" s="14"/>
+      <c r="D420" s="24"/>
       <c r="E420" s="14"/>
       <c r="F420" s="14">
         <v>4</v>
       </c>
     </row>
-    <row r="421" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="421" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A421" s="14"/>
       <c r="B421" s="14" t="s">
         <v>153</v>
       </c>
       <c r="C421" s="14"/>
-      <c r="D421" s="14"/>
+      <c r="D421" s="24"/>
       <c r="E421" s="14"/>
       <c r="F421" s="14">
         <v>4</v>
       </c>
     </row>
-    <row r="422" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="422" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A422" s="14"/>
       <c r="B422" s="14" t="s">
         <v>154</v>
       </c>
       <c r="C422" s="14"/>
-      <c r="D422" s="14"/>
+      <c r="D422" s="24"/>
       <c r="E422" s="14"/>
       <c r="F422" s="14">
         <v>4</v>
       </c>
     </row>
-    <row r="423" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="423" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A423" s="14"/>
       <c r="B423" s="14" t="s">
         <v>155</v>
       </c>
       <c r="C423" s="14"/>
-      <c r="D423" s="14"/>
+      <c r="D423" s="24"/>
       <c r="E423" s="14"/>
       <c r="F423" s="14">
         <v>4</v>
       </c>
     </row>
-    <row r="424" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="424" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A424" s="14"/>
       <c r="B424" s="14" t="s">
         <v>258</v>
       </c>
       <c r="C424" s="14"/>
-      <c r="D424" s="14"/>
+      <c r="D424" s="24"/>
       <c r="E424" s="14"/>
       <c r="F424" s="14">
         <v>4</v>
       </c>
     </row>
-    <row r="425" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="425" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A425" s="14"/>
       <c r="B425" s="14" t="s">
         <v>156</v>
       </c>
       <c r="C425" s="14"/>
-      <c r="D425" s="14"/>
+      <c r="D425" s="24"/>
       <c r="E425" s="14"/>
       <c r="F425" s="14">
         <v>4</v>
       </c>
     </row>
-    <row r="426" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="426" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A426" s="14"/>
       <c r="B426" s="14" t="s">
         <v>259</v>
       </c>
       <c r="C426" s="14"/>
-      <c r="D426" s="14"/>
+      <c r="D426" s="24"/>
       <c r="E426" s="14"/>
       <c r="F426" s="14">
         <v>4</v>
       </c>
     </row>
-    <row r="427" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="427" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A427" s="14"/>
       <c r="B427" s="14" t="s">
         <v>157</v>
       </c>
       <c r="C427" s="14"/>
-      <c r="D427" s="14"/>
+      <c r="D427" s="24"/>
       <c r="E427" s="14"/>
       <c r="F427" s="14">
         <v>4</v>
       </c>
     </row>
-    <row r="428" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="428" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A428" s="14"/>
       <c r="B428" s="14"/>
       <c r="C428" s="14"/>
-      <c r="D428" s="22" t="s">
+      <c r="D428" s="42" t="s">
         <v>389</v>
       </c>
       <c r="E428" s="28">
@@ -7026,7 +7087,7 @@
       </c>
       <c r="F428" s="14"/>
     </row>
-    <row r="429" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="429" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E429">
         <f>SUM(E419:E427)*E428</f>
         <v>0</v>
@@ -7036,7 +7097,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="430" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="430" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A430" s="8" t="s">
         <v>158</v>
       </c>
@@ -7044,89 +7105,89 @@
         <v>159</v>
       </c>
       <c r="C430" s="8"/>
-      <c r="D430" s="8"/>
+      <c r="D430" s="44"/>
       <c r="E430" s="8"/>
       <c r="F430" s="8">
         <v>3</v>
       </c>
     </row>
-    <row r="431" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="431" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A431" s="8"/>
       <c r="B431" s="8" t="s">
         <v>160</v>
       </c>
       <c r="C431" s="8"/>
-      <c r="D431" s="8"/>
+      <c r="D431" s="44"/>
       <c r="E431" s="8"/>
       <c r="F431" s="8">
         <v>5</v>
       </c>
     </row>
-    <row r="432" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="432" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A432" s="8"/>
       <c r="B432" s="8" t="s">
         <v>8</v>
       </c>
       <c r="C432" s="8"/>
-      <c r="D432" s="8"/>
+      <c r="D432" s="44"/>
       <c r="E432" s="8"/>
       <c r="F432" s="8">
         <v>3</v>
       </c>
     </row>
-    <row r="433" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="433" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A433" s="8"/>
       <c r="B433" s="8" t="s">
         <v>161</v>
       </c>
       <c r="C433" s="8"/>
-      <c r="D433" s="8"/>
+      <c r="D433" s="44"/>
       <c r="E433" s="8"/>
       <c r="F433" s="8">
         <v>3</v>
       </c>
     </row>
-    <row r="434" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="434" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A434" s="8"/>
       <c r="B434" s="8" t="s">
         <v>162</v>
       </c>
       <c r="C434" s="8"/>
-      <c r="D434" s="8"/>
+      <c r="D434" s="44"/>
       <c r="E434" s="8"/>
       <c r="F434" s="8">
         <v>3</v>
       </c>
     </row>
-    <row r="435" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="435" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A435" s="8"/>
       <c r="B435" s="8" t="s">
         <v>163</v>
       </c>
       <c r="C435" s="8"/>
-      <c r="D435" s="8"/>
+      <c r="D435" s="44"/>
       <c r="E435" s="8"/>
       <c r="F435" s="8">
         <v>3</v>
       </c>
     </row>
-    <row r="436" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="436" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A436" s="8"/>
       <c r="B436" s="8" t="s">
         <v>164</v>
       </c>
       <c r="C436" s="8"/>
-      <c r="D436" s="8"/>
+      <c r="D436" s="44"/>
       <c r="E436" s="8"/>
       <c r="F436" s="8">
         <v>3</v>
       </c>
     </row>
-    <row r="437" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="437" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A437" s="8"/>
       <c r="B437" s="8"/>
       <c r="C437" s="8"/>
-      <c r="D437" s="22" t="s">
+      <c r="D437" s="42" t="s">
         <v>389</v>
       </c>
       <c r="E437" s="28">
@@ -7134,7 +7195,7 @@
       </c>
       <c r="F437" s="8"/>
     </row>
-    <row r="438" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="438" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E438">
         <f>SUM(E430:E436)*E437</f>
         <v>0</v>
@@ -7144,7 +7205,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="439" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="439" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A439" s="7" t="s">
         <v>362</v>
       </c>
@@ -7152,7 +7213,7 @@
       <c r="C439" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="D439" s="8" t="s">
+      <c r="D439" s="44" t="s">
         <v>173</v>
       </c>
       <c r="E439" s="8"/>
@@ -7160,11 +7221,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="440" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="440" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A440" s="7"/>
       <c r="B440" s="7"/>
       <c r="C440" s="8"/>
-      <c r="D440" s="8" t="s">
+      <c r="D440" s="44" t="s">
         <v>174</v>
       </c>
       <c r="E440" s="8"/>
@@ -7172,11 +7233,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="441" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="441" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A441" s="7"/>
       <c r="B441" s="7"/>
       <c r="C441" s="8"/>
-      <c r="D441" s="8" t="s">
+      <c r="D441" s="44" t="s">
         <v>175</v>
       </c>
       <c r="E441" s="8"/>
@@ -7184,13 +7245,13 @@
         <v>5</v>
       </c>
     </row>
-    <row r="442" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="442" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A442" s="7"/>
       <c r="B442" s="7"/>
       <c r="C442" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="D442" s="8" t="s">
+      <c r="D442" s="44" t="s">
         <v>177</v>
       </c>
       <c r="E442" s="8"/>
@@ -7198,11 +7259,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="443" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="443" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A443" s="7"/>
       <c r="B443" s="7"/>
       <c r="C443" s="8"/>
-      <c r="D443" s="8" t="s">
+      <c r="D443" s="44" t="s">
         <v>178</v>
       </c>
       <c r="E443" s="8"/>
@@ -7210,11 +7271,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="444" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="444" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A444" s="7"/>
       <c r="B444" s="7"/>
       <c r="C444" s="8"/>
-      <c r="D444" s="8" t="s">
+      <c r="D444" s="44" t="s">
         <v>179</v>
       </c>
       <c r="E444" s="8"/>
@@ -7222,11 +7283,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="445" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="445" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A445" s="7"/>
       <c r="B445" s="7"/>
       <c r="C445" s="8"/>
-      <c r="D445" s="8" t="s">
+      <c r="D445" s="44" t="s">
         <v>180</v>
       </c>
       <c r="E445" s="8"/>
@@ -7234,11 +7295,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="446" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="446" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A446" s="7"/>
       <c r="B446" s="7"/>
       <c r="C446" s="8"/>
-      <c r="D446" s="8" t="s">
+      <c r="D446" s="44" t="s">
         <v>181</v>
       </c>
       <c r="E446" s="8"/>
@@ -7246,7 +7307,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="447" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="447" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E447">
         <f>SUM(E439:E446)</f>
         <v>0</v>
@@ -7256,12 +7317,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="448" spans="1:6" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="448" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A448" s="5" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="449" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="449" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A449" s="7" t="s">
         <v>265</v>
       </c>
@@ -7271,25 +7332,25 @@
       <c r="C449" s="8" t="s">
         <v>316</v>
       </c>
-      <c r="D449" s="8"/>
+      <c r="D449" s="44"/>
       <c r="E449" s="8"/>
       <c r="F449" s="8">
         <v>10</v>
       </c>
     </row>
-    <row r="450" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="450" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A450" s="7"/>
       <c r="B450" s="8"/>
       <c r="C450" s="8" t="s">
         <v>364</v>
       </c>
-      <c r="D450" s="8"/>
+      <c r="D450" s="44"/>
       <c r="E450" s="8"/>
       <c r="F450" s="8">
         <v>10</v>
       </c>
     </row>
-    <row r="451" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="451" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A451" s="8"/>
       <c r="B451" s="7" t="s">
         <v>266</v>
@@ -7297,70 +7358,70 @@
       <c r="C451" s="8" t="s">
         <v>319</v>
       </c>
-      <c r="D451" s="8"/>
+      <c r="D451" s="44"/>
       <c r="E451" s="8"/>
       <c r="F451" s="8"/>
     </row>
-    <row r="452" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="452" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A452" s="8"/>
       <c r="B452" s="8"/>
       <c r="C452" s="8" t="s">
         <v>365</v>
       </c>
-      <c r="D452" s="8"/>
+      <c r="D452" s="44"/>
       <c r="E452" s="8"/>
       <c r="F452" s="8">
         <v>10</v>
       </c>
     </row>
-    <row r="453" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="453" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A453" s="8"/>
       <c r="B453" s="8"/>
       <c r="C453" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="D453" s="8"/>
+      <c r="D453" s="44"/>
       <c r="E453" s="8"/>
       <c r="F453" s="8">
         <v>10</v>
       </c>
     </row>
-    <row r="454" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="454" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A454" s="8"/>
       <c r="B454" s="8"/>
       <c r="C454" s="8" t="s">
         <v>366</v>
       </c>
-      <c r="D454" s="8"/>
+      <c r="D454" s="44"/>
       <c r="E454" s="8"/>
       <c r="F454" s="8">
         <v>10</v>
       </c>
     </row>
-    <row r="455" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="455" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A455" s="8"/>
       <c r="B455" s="8"/>
       <c r="C455" s="8" t="s">
         <v>367</v>
       </c>
-      <c r="D455" s="8"/>
+      <c r="D455" s="44"/>
       <c r="E455" s="8"/>
       <c r="F455" s="8">
         <v>10</v>
       </c>
     </row>
-    <row r="456" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="456" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A456" s="8"/>
       <c r="B456" s="8"/>
       <c r="C456" s="8"/>
-      <c r="D456" s="22" t="s">
+      <c r="D456" s="42" t="s">
         <v>389</v>
       </c>
       <c r="E456" s="28">
         <v>1</v>
       </c>
     </row>
-    <row r="457" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="457" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E457">
         <f>SUM(E449:E455)*E456</f>
         <v>0</v>
@@ -7370,12 +7431,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="458" spans="1:6" ht="21" x14ac:dyDescent="0.65">
+    <row r="458" spans="1:6" ht="21" x14ac:dyDescent="0.4">
       <c r="A458" s="23" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="459" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="459" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A459" s="11" t="s">
         <v>369</v>
       </c>
@@ -7383,13 +7444,13 @@
         <v>370</v>
       </c>
       <c r="C459" s="12"/>
-      <c r="D459" s="12"/>
+      <c r="D459" s="41"/>
       <c r="E459" s="12"/>
       <c r="F459" s="12">
         <v>10</v>
       </c>
     </row>
-    <row r="460" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="460" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A460" s="11" t="s">
         <v>371</v>
       </c>
@@ -7399,29 +7460,29 @@
       <c r="C460" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="D460" s="12"/>
+      <c r="D460" s="41"/>
       <c r="E460" s="12"/>
       <c r="F460" s="12">
         <v>20</v>
       </c>
     </row>
-    <row r="461" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="461" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A461" s="11"/>
       <c r="B461" s="12"/>
       <c r="C461" s="12" t="s">
         <v>373</v>
       </c>
-      <c r="D461" s="12"/>
+      <c r="D461" s="41"/>
       <c r="E461" s="12"/>
       <c r="F461" s="12">
         <v>20</v>
       </c>
     </row>
-    <row r="462" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="462" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A462" s="11"/>
       <c r="B462" s="12"/>
       <c r="C462" s="12"/>
-      <c r="D462" s="22" t="s">
+      <c r="D462" s="42" t="s">
         <v>389</v>
       </c>
       <c r="E462" s="28">
@@ -7429,7 +7490,7 @@
       </c>
       <c r="F462" s="12"/>
     </row>
-    <row r="463" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="463" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A463" s="1"/>
       <c r="E463">
         <f>SUM(E459:E461)*E462</f>
@@ -7440,15 +7501,15 @@
         <v>50</v>
       </c>
     </row>
-    <row r="464" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="464" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A464" s="1"/>
     </row>
-    <row r="465" spans="1:6" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="465" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A465" s="5" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="466" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="466" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A466" s="15" t="s">
         <v>348</v>
       </c>
@@ -7458,13 +7519,13 @@
       <c r="C466" s="13" t="s">
         <v>351</v>
       </c>
-      <c r="D466" s="13"/>
+      <c r="D466" s="40"/>
       <c r="E466" s="13"/>
       <c r="F466" s="13">
         <v>10</v>
       </c>
     </row>
-    <row r="467" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="467" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A467" s="13" t="s">
         <v>355</v>
       </c>
@@ -7472,13 +7533,13 @@
         <v>7</v>
       </c>
       <c r="C467" s="13"/>
-      <c r="D467" s="13"/>
+      <c r="D467" s="40"/>
       <c r="E467" s="13"/>
       <c r="F467" s="13">
         <v>10</v>
       </c>
     </row>
-    <row r="468" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="468" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A468" s="13" t="s">
         <v>0</v>
       </c>
@@ -7486,29 +7547,29 @@
         <v>349</v>
       </c>
       <c r="C468" s="13"/>
-      <c r="D468" s="13"/>
+      <c r="D468" s="40"/>
       <c r="E468" s="13"/>
       <c r="F468" s="13">
         <v>20</v>
       </c>
     </row>
-    <row r="469" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="469" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A469" s="13"/>
       <c r="B469" s="13" t="s">
         <v>350</v>
       </c>
       <c r="C469" s="13"/>
-      <c r="D469" s="13"/>
+      <c r="D469" s="40"/>
       <c r="E469" s="13"/>
       <c r="F469" s="13">
         <v>10</v>
       </c>
     </row>
-    <row r="470" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="470" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A470" s="13"/>
       <c r="B470" s="13"/>
       <c r="C470" s="13"/>
-      <c r="D470" s="22" t="s">
+      <c r="D470" s="42" t="s">
         <v>389</v>
       </c>
       <c r="E470" s="28">
@@ -7516,7 +7577,7 @@
       </c>
       <c r="F470" s="13"/>
     </row>
-    <row r="471" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="471" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E471">
         <f>SUM(E466:E469)*E470</f>
         <v>0</v>
@@ -7526,7 +7587,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="473" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="473" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A473" s="16" t="s">
         <v>348</v>
       </c>
@@ -7536,13 +7597,13 @@
       <c r="C473" s="14" t="s">
         <v>351</v>
       </c>
-      <c r="D473" s="14"/>
+      <c r="D473" s="24"/>
       <c r="E473" s="14"/>
       <c r="F473" s="14">
         <v>10</v>
       </c>
     </row>
-    <row r="474" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="474" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A474" s="14" t="s">
         <v>135</v>
       </c>
@@ -7550,29 +7611,29 @@
         <v>352</v>
       </c>
       <c r="C474" s="14"/>
-      <c r="D474" s="14"/>
+      <c r="D474" s="24"/>
       <c r="E474" s="14"/>
       <c r="F474" s="14">
         <v>20</v>
       </c>
     </row>
-    <row r="475" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="475" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A475" s="14"/>
       <c r="B475" s="14" t="s">
         <v>228</v>
       </c>
       <c r="C475" s="14"/>
-      <c r="D475" s="14"/>
+      <c r="D475" s="24"/>
       <c r="E475" s="14"/>
       <c r="F475" s="14">
         <v>20</v>
       </c>
     </row>
-    <row r="476" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="476" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A476" s="14"/>
       <c r="B476" s="14"/>
       <c r="C476" s="14"/>
-      <c r="D476" s="22" t="s">
+      <c r="D476" s="42" t="s">
         <v>389</v>
       </c>
       <c r="E476" s="28">
@@ -7580,7 +7641,7 @@
       </c>
       <c r="F476" s="14"/>
     </row>
-    <row r="477" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="477" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E477">
         <f>SUM(E473:E475)*E476</f>
         <v>0</v>
@@ -7590,7 +7651,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="478" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="478" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A478" s="11" t="s">
         <v>348</v>
       </c>
@@ -7600,13 +7661,13 @@
       <c r="C478" s="12" t="s">
         <v>351</v>
       </c>
-      <c r="D478" s="12"/>
+      <c r="D478" s="41"/>
       <c r="E478" s="12"/>
       <c r="F478" s="12">
         <v>10</v>
       </c>
     </row>
-    <row r="479" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="479" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A479" s="12" t="s">
         <v>353</v>
       </c>
@@ -7614,29 +7675,29 @@
         <v>352</v>
       </c>
       <c r="C479" s="12"/>
-      <c r="D479" s="12"/>
+      <c r="D479" s="41"/>
       <c r="E479" s="12"/>
       <c r="F479" s="12">
         <v>20</v>
       </c>
     </row>
-    <row r="480" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="480" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A480" s="12"/>
       <c r="B480" s="12" t="s">
         <v>354</v>
       </c>
       <c r="C480" s="12"/>
-      <c r="D480" s="12"/>
+      <c r="D480" s="41"/>
       <c r="E480" s="12"/>
       <c r="F480" s="12">
         <v>40</v>
       </c>
     </row>
-    <row r="481" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="481" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A481" s="12"/>
       <c r="B481" s="12"/>
       <c r="C481" s="12"/>
-      <c r="D481" s="22" t="s">
+      <c r="D481" s="42" t="s">
         <v>389</v>
       </c>
       <c r="E481" s="28">
@@ -7644,7 +7705,7 @@
       </c>
       <c r="F481" s="12"/>
     </row>
-    <row r="482" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="482" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E482">
         <f>SUM(E478:E480)*E481</f>
         <v>0</v>
@@ -7654,12 +7715,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="487" spans="1:6" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="487" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A487" s="5" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="488" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="488" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A488" s="14" t="s">
         <v>265</v>
       </c>
@@ -7667,13 +7728,13 @@
         <v>266</v>
       </c>
       <c r="C488" s="14"/>
-      <c r="D488" s="14"/>
+      <c r="D488" s="24"/>
       <c r="E488" s="14"/>
       <c r="F488" s="14">
         <v>10</v>
       </c>
     </row>
-    <row r="489" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="489" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A489" s="14" t="s">
         <v>270</v>
       </c>
@@ -7681,125 +7742,125 @@
         <v>120</v>
       </c>
       <c r="C489" s="14"/>
-      <c r="D489" s="14"/>
+      <c r="D489" s="24"/>
       <c r="E489" s="14"/>
       <c r="F489" s="14">
         <v>5</v>
       </c>
     </row>
-    <row r="490" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="490" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A490" s="14"/>
       <c r="B490" s="14" t="s">
         <v>268</v>
       </c>
       <c r="C490" s="14"/>
-      <c r="D490" s="14"/>
+      <c r="D490" s="24"/>
       <c r="E490" s="14"/>
       <c r="F490" s="14">
         <v>5</v>
       </c>
     </row>
-    <row r="491" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="491" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A491" s="14"/>
       <c r="B491" s="14" t="s">
         <v>267</v>
       </c>
       <c r="C491" s="14"/>
-      <c r="D491" s="14"/>
+      <c r="D491" s="24"/>
       <c r="E491" s="14"/>
       <c r="F491" s="14">
         <v>5</v>
       </c>
     </row>
-    <row r="492" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="492" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A492" s="14"/>
       <c r="B492" s="14" t="s">
         <v>269</v>
       </c>
       <c r="C492" s="14"/>
-      <c r="D492" s="14"/>
+      <c r="D492" s="24"/>
       <c r="E492" s="14"/>
       <c r="F492" s="14">
         <v>5</v>
       </c>
     </row>
-    <row r="493" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="493" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A493" s="14"/>
       <c r="B493" s="14" t="s">
         <v>271</v>
       </c>
       <c r="C493" s="14"/>
-      <c r="D493" s="14"/>
+      <c r="D493" s="24"/>
       <c r="E493" s="14"/>
       <c r="F493" s="14">
         <v>5</v>
       </c>
     </row>
-    <row r="494" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="494" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A494" s="14"/>
       <c r="B494" s="14" t="s">
         <v>272</v>
       </c>
       <c r="C494" s="14"/>
-      <c r="D494" s="14"/>
+      <c r="D494" s="24"/>
       <c r="E494" s="14"/>
       <c r="F494" s="14">
         <v>5</v>
       </c>
     </row>
-    <row r="495" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="495" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A495" s="14"/>
       <c r="B495" s="14" t="s">
         <v>26</v>
       </c>
       <c r="C495" s="14"/>
-      <c r="D495" s="14"/>
+      <c r="D495" s="24"/>
       <c r="E495" s="14"/>
       <c r="F495" s="14">
         <v>5</v>
       </c>
     </row>
-    <row r="496" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="496" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A496" s="14"/>
       <c r="B496" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C496" s="14"/>
-      <c r="D496" s="14"/>
+      <c r="D496" s="24"/>
       <c r="E496" s="14"/>
       <c r="F496" s="14">
         <v>5</v>
       </c>
     </row>
-    <row r="497" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="497" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A497" s="14"/>
       <c r="B497" s="14" t="s">
         <v>273</v>
       </c>
       <c r="C497" s="14"/>
-      <c r="D497" s="14"/>
+      <c r="D497" s="24"/>
       <c r="E497" s="14"/>
       <c r="F497" s="14">
         <v>5</v>
       </c>
     </row>
-    <row r="498" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="498" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A498" s="14"/>
       <c r="B498" s="14" t="s">
         <v>274</v>
       </c>
       <c r="C498" s="14"/>
-      <c r="D498" s="14"/>
+      <c r="D498" s="24"/>
       <c r="E498" s="14"/>
       <c r="F498" s="14">
         <v>5</v>
       </c>
     </row>
-    <row r="499" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="499" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A499" s="14"/>
       <c r="B499" s="14"/>
       <c r="C499" s="14"/>
-      <c r="D499" s="22" t="s">
+      <c r="D499" s="42" t="s">
         <v>389</v>
       </c>
       <c r="E499" s="28">
@@ -7807,7 +7868,7 @@
       </c>
       <c r="F499" s="14"/>
     </row>
-    <row r="500" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="500" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E500">
         <f>SUM(E488:E498)*E499</f>
         <v>0</v>
@@ -7817,7 +7878,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="502" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="502" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A502" s="12" t="s">
         <v>265</v>
       </c>
@@ -7825,13 +7886,13 @@
         <v>266</v>
       </c>
       <c r="C502" s="12"/>
-      <c r="D502" s="12"/>
+      <c r="D502" s="41"/>
       <c r="E502" s="12"/>
       <c r="F502" s="12">
         <v>10</v>
       </c>
     </row>
-    <row r="503" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="503" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A503" s="12" t="s">
         <v>270</v>
       </c>
@@ -7839,125 +7900,125 @@
         <v>120</v>
       </c>
       <c r="C503" s="12"/>
-      <c r="D503" s="12"/>
+      <c r="D503" s="41"/>
       <c r="E503" s="12"/>
       <c r="F503" s="12">
         <v>5</v>
       </c>
     </row>
-    <row r="504" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="504" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A504" s="12"/>
       <c r="B504" s="12" t="s">
         <v>268</v>
       </c>
       <c r="C504" s="12"/>
-      <c r="D504" s="12"/>
+      <c r="D504" s="41"/>
       <c r="E504" s="12"/>
       <c r="F504" s="12">
         <v>5</v>
       </c>
     </row>
-    <row r="505" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="505" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A505" s="12"/>
       <c r="B505" s="12" t="s">
         <v>267</v>
       </c>
       <c r="C505" s="12"/>
-      <c r="D505" s="12"/>
+      <c r="D505" s="41"/>
       <c r="E505" s="12"/>
       <c r="F505" s="12">
         <v>5</v>
       </c>
     </row>
-    <row r="506" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="506" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A506" s="12"/>
       <c r="B506" s="12" t="s">
         <v>269</v>
       </c>
       <c r="C506" s="12"/>
-      <c r="D506" s="12"/>
+      <c r="D506" s="41"/>
       <c r="E506" s="12"/>
       <c r="F506" s="12">
         <v>5</v>
       </c>
     </row>
-    <row r="507" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="507" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A507" s="12"/>
       <c r="B507" s="12" t="s">
         <v>271</v>
       </c>
       <c r="C507" s="12"/>
-      <c r="D507" s="12"/>
+      <c r="D507" s="41"/>
       <c r="E507" s="12"/>
       <c r="F507" s="12">
         <v>5</v>
       </c>
     </row>
-    <row r="508" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="508" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A508" s="12"/>
       <c r="B508" s="12" t="s">
         <v>272</v>
       </c>
       <c r="C508" s="12"/>
-      <c r="D508" s="12"/>
+      <c r="D508" s="41"/>
       <c r="E508" s="12"/>
       <c r="F508" s="12">
         <v>5</v>
       </c>
     </row>
-    <row r="509" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="509" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A509" s="12"/>
       <c r="B509" s="12" t="s">
         <v>26</v>
       </c>
       <c r="C509" s="12"/>
-      <c r="D509" s="12"/>
+      <c r="D509" s="41"/>
       <c r="E509" s="12"/>
       <c r="F509" s="12">
         <v>5</v>
       </c>
     </row>
-    <row r="510" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="510" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A510" s="12"/>
       <c r="B510" s="12" t="s">
         <v>27</v>
       </c>
       <c r="C510" s="12"/>
-      <c r="D510" s="12"/>
+      <c r="D510" s="41"/>
       <c r="E510" s="12"/>
       <c r="F510" s="12">
         <v>5</v>
       </c>
     </row>
-    <row r="511" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="511" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A511" s="12"/>
       <c r="B511" s="12" t="s">
         <v>273</v>
       </c>
       <c r="C511" s="12"/>
-      <c r="D511" s="12"/>
+      <c r="D511" s="41"/>
       <c r="E511" s="12"/>
       <c r="F511" s="12">
         <v>5</v>
       </c>
     </row>
-    <row r="512" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="512" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A512" s="12"/>
       <c r="B512" s="12" t="s">
         <v>274</v>
       </c>
       <c r="C512" s="12"/>
-      <c r="D512" s="12"/>
+      <c r="D512" s="41"/>
       <c r="E512" s="12"/>
       <c r="F512" s="12">
         <v>5</v>
       </c>
     </row>
-    <row r="513" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="513" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A513" s="12"/>
       <c r="B513" s="12"/>
       <c r="C513" s="12"/>
-      <c r="D513" s="22" t="s">
+      <c r="D513" s="42" t="s">
         <v>389</v>
       </c>
       <c r="E513" s="28">
@@ -7965,7 +8026,7 @@
       </c>
       <c r="F513" s="12"/>
     </row>
-    <row r="514" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="514" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E514">
         <f>SUM(E502:E512)*E513</f>
         <v>0</v>
@@ -7975,7 +8036,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="516" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="516" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A516" s="13" t="s">
         <v>265</v>
       </c>
@@ -7983,13 +8044,13 @@
         <v>266</v>
       </c>
       <c r="C516" s="13"/>
-      <c r="D516" s="13"/>
+      <c r="D516" s="40"/>
       <c r="E516" s="13"/>
       <c r="F516" s="13">
         <v>10</v>
       </c>
     </row>
-    <row r="517" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="517" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A517" s="13" t="s">
         <v>270</v>
       </c>
@@ -7997,125 +8058,125 @@
         <v>120</v>
       </c>
       <c r="C517" s="13"/>
-      <c r="D517" s="13"/>
+      <c r="D517" s="40"/>
       <c r="E517" s="13"/>
       <c r="F517" s="13">
         <v>5</v>
       </c>
     </row>
-    <row r="518" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="518" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A518" s="13"/>
       <c r="B518" s="13" t="s">
         <v>268</v>
       </c>
       <c r="C518" s="13"/>
-      <c r="D518" s="13"/>
+      <c r="D518" s="40"/>
       <c r="E518" s="13"/>
       <c r="F518" s="13">
         <v>5</v>
       </c>
     </row>
-    <row r="519" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="519" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A519" s="13"/>
       <c r="B519" s="13" t="s">
         <v>267</v>
       </c>
       <c r="C519" s="13"/>
-      <c r="D519" s="13"/>
+      <c r="D519" s="40"/>
       <c r="E519" s="13"/>
       <c r="F519" s="13">
         <v>5</v>
       </c>
     </row>
-    <row r="520" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="520" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A520" s="13"/>
       <c r="B520" s="13" t="s">
         <v>269</v>
       </c>
       <c r="C520" s="13"/>
-      <c r="D520" s="13"/>
+      <c r="D520" s="40"/>
       <c r="E520" s="13"/>
       <c r="F520" s="13">
         <v>5</v>
       </c>
     </row>
-    <row r="521" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="521" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A521" s="13"/>
       <c r="B521" s="13" t="s">
         <v>271</v>
       </c>
       <c r="C521" s="13"/>
-      <c r="D521" s="13"/>
+      <c r="D521" s="40"/>
       <c r="E521" s="13"/>
       <c r="F521" s="13">
         <v>5</v>
       </c>
     </row>
-    <row r="522" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="522" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A522" s="13"/>
       <c r="B522" s="13" t="s">
         <v>272</v>
       </c>
       <c r="C522" s="13"/>
-      <c r="D522" s="13"/>
+      <c r="D522" s="40"/>
       <c r="E522" s="13"/>
       <c r="F522" s="13">
         <v>5</v>
       </c>
     </row>
-    <row r="523" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="523" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A523" s="13"/>
       <c r="B523" s="13" t="s">
         <v>26</v>
       </c>
       <c r="C523" s="13"/>
-      <c r="D523" s="13"/>
+      <c r="D523" s="40"/>
       <c r="E523" s="13"/>
       <c r="F523" s="13">
         <v>5</v>
       </c>
     </row>
-    <row r="524" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="524" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A524" s="13"/>
       <c r="B524" s="13" t="s">
         <v>27</v>
       </c>
       <c r="C524" s="13"/>
-      <c r="D524" s="13"/>
+      <c r="D524" s="40"/>
       <c r="E524" s="13"/>
       <c r="F524" s="13">
         <v>5</v>
       </c>
     </row>
-    <row r="525" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="525" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A525" s="13"/>
       <c r="B525" s="13" t="s">
         <v>273</v>
       </c>
       <c r="C525" s="13"/>
-      <c r="D525" s="13"/>
+      <c r="D525" s="40"/>
       <c r="E525" s="13"/>
       <c r="F525" s="13">
         <v>5</v>
       </c>
     </row>
-    <row r="526" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="526" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A526" s="13"/>
       <c r="B526" s="13" t="s">
         <v>274</v>
       </c>
       <c r="C526" s="13"/>
-      <c r="D526" s="13"/>
+      <c r="D526" s="40"/>
       <c r="E526" s="13"/>
       <c r="F526" s="13">
         <v>5</v>
       </c>
     </row>
-    <row r="527" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="527" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A527" s="13"/>
       <c r="B527" s="13"/>
       <c r="C527" s="13"/>
-      <c r="D527" s="22" t="s">
+      <c r="D527" s="42" t="s">
         <v>389</v>
       </c>
       <c r="E527" s="28">
@@ -8123,7 +8184,7 @@
       </c>
       <c r="F527" s="13"/>
     </row>
-    <row r="528" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="528" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E528">
         <f>SUM(E516:E526)*E527</f>
         <v>0</v>
@@ -8133,12 +8194,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="530" spans="1:6" ht="21" x14ac:dyDescent="0.65">
+    <row r="530" spans="1:6" ht="21" x14ac:dyDescent="0.4">
       <c r="A530" s="23" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="531" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="531" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A531" s="16" t="s">
         <v>375</v>
       </c>
@@ -8146,7 +8207,7 @@
         <v>404</v>
       </c>
       <c r="C531" s="14"/>
-      <c r="D531" s="14" t="s">
+      <c r="D531" s="24" t="s">
         <v>405</v>
       </c>
       <c r="E531" s="14"/>
@@ -8154,13 +8215,13 @@
         <v>30</v>
       </c>
     </row>
-    <row r="532" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="532" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A532" s="14"/>
       <c r="B532" s="14" t="s">
         <v>406</v>
       </c>
       <c r="C532" s="14"/>
-      <c r="D532" s="14" t="s">
+      <c r="D532" s="24" t="s">
         <v>407</v>
       </c>
       <c r="E532" s="14"/>
@@ -8168,13 +8229,13 @@
         <v>30</v>
       </c>
     </row>
-    <row r="533" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="533" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A533" s="14"/>
       <c r="B533" s="14" t="s">
         <v>408</v>
       </c>
       <c r="C533" s="14"/>
-      <c r="D533" s="14" t="s">
+      <c r="D533" s="24" t="s">
         <v>409</v>
       </c>
       <c r="E533" s="14"/>
@@ -8182,13 +8243,13 @@
         <v>30</v>
       </c>
     </row>
-    <row r="534" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="534" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A534" s="14"/>
       <c r="B534" s="14" t="s">
         <v>410</v>
       </c>
       <c r="C534" s="14"/>
-      <c r="D534" s="14" t="s">
+      <c r="D534" s="24" t="s">
         <v>411</v>
       </c>
       <c r="E534" s="14"/>
@@ -8196,7 +8257,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="535" spans="1:6" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="535" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A535" s="14"/>
       <c r="B535" s="14" t="s">
         <v>412</v>
@@ -8210,11 +8271,11 @@
         <v>30</v>
       </c>
     </row>
-    <row r="536" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="536" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A536" s="14"/>
       <c r="B536" s="14"/>
       <c r="C536" s="14"/>
-      <c r="D536" s="22" t="s">
+      <c r="D536" s="42" t="s">
         <v>389</v>
       </c>
       <c r="E536" s="28">
@@ -8222,7 +8283,7 @@
       </c>
       <c r="F536" s="14"/>
     </row>
-    <row r="537" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="537" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E537">
         <f>SUM(E531:E535)*E536</f>
         <v>0</v>
@@ -8232,63 +8293,63 @@
         <v>150</v>
       </c>
     </row>
-    <row r="539" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="539" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A539" s="11" t="s">
         <v>375</v>
       </c>
       <c r="B539" s="12"/>
       <c r="C539" s="12"/>
-      <c r="D539" s="12"/>
+      <c r="D539" s="41"/>
       <c r="E539" s="12"/>
       <c r="F539" s="12">
         <v>30</v>
       </c>
     </row>
-    <row r="540" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="540" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A540" s="12"/>
       <c r="B540" s="12"/>
       <c r="C540" s="12"/>
-      <c r="D540" s="12"/>
+      <c r="D540" s="41"/>
       <c r="E540" s="12"/>
       <c r="F540" s="12">
         <v>30</v>
       </c>
     </row>
-    <row r="541" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="541" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A541" s="12"/>
       <c r="B541" s="12"/>
       <c r="C541" s="12"/>
-      <c r="D541" s="12"/>
+      <c r="D541" s="41"/>
       <c r="E541" s="12"/>
       <c r="F541" s="12">
         <v>30</v>
       </c>
     </row>
-    <row r="542" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="542" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A542" s="12"/>
       <c r="B542" s="12"/>
       <c r="C542" s="12"/>
-      <c r="D542" s="12"/>
+      <c r="D542" s="41"/>
       <c r="E542" s="12"/>
       <c r="F542" s="12">
         <v>30</v>
       </c>
     </row>
-    <row r="543" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="543" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A543" s="12"/>
       <c r="B543" s="12"/>
       <c r="C543" s="12"/>
-      <c r="D543" s="12"/>
+      <c r="D543" s="41"/>
       <c r="E543" s="12"/>
       <c r="F543" s="12">
         <v>30</v>
       </c>
     </row>
-    <row r="544" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="544" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A544" s="12"/>
       <c r="B544" s="12"/>
       <c r="C544" s="12"/>
-      <c r="D544" s="22" t="s">
+      <c r="D544" s="42" t="s">
         <v>389</v>
       </c>
       <c r="E544" s="28">
@@ -8296,7 +8357,7 @@
       </c>
       <c r="F544" s="12"/>
     </row>
-    <row r="545" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="545" spans="1:8" x14ac:dyDescent="0.3">
       <c r="E545">
         <f>SUM(E539:E543)*E544</f>
         <v>0</v>
@@ -8306,63 +8367,83 @@
         <v>150</v>
       </c>
     </row>
-    <row r="547" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="547" spans="1:8" ht="72" x14ac:dyDescent="0.3">
       <c r="A547" s="15" t="s">
         <v>375</v>
       </c>
-      <c r="B547" s="13"/>
+      <c r="B547" s="13" t="s">
+        <v>414</v>
+      </c>
       <c r="C547" s="13"/>
-      <c r="D547" s="13"/>
+      <c r="D547" s="40" t="s">
+        <v>415</v>
+      </c>
       <c r="E547" s="13"/>
       <c r="F547" s="13">
         <v>30</v>
       </c>
     </row>
-    <row r="548" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="548" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A548" s="13"/>
-      <c r="B548" s="13"/>
+      <c r="B548" s="13" t="s">
+        <v>416</v>
+      </c>
       <c r="C548" s="13"/>
-      <c r="D548" s="13"/>
+      <c r="D548" s="40" t="s">
+        <v>417</v>
+      </c>
       <c r="E548" s="13"/>
       <c r="F548" s="13">
         <v>30</v>
       </c>
     </row>
-    <row r="549" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="549" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A549" s="13"/>
-      <c r="B549" s="13"/>
+      <c r="B549" s="13" t="s">
+        <v>419</v>
+      </c>
       <c r="C549" s="13"/>
-      <c r="D549" s="13"/>
+      <c r="D549" s="40" t="s">
+        <v>418</v>
+      </c>
       <c r="E549" s="13"/>
       <c r="F549" s="13">
         <v>30</v>
       </c>
     </row>
-    <row r="550" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="550" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A550" s="13"/>
-      <c r="B550" s="13"/>
+      <c r="B550" s="13" t="s">
+        <v>420</v>
+      </c>
       <c r="C550" s="13"/>
-      <c r="D550" s="13"/>
+      <c r="D550" s="40" t="s">
+        <v>421</v>
+      </c>
       <c r="E550" s="13"/>
       <c r="F550" s="13">
         <v>30</v>
       </c>
     </row>
-    <row r="551" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="551" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A551" s="13"/>
-      <c r="B551" s="13"/>
+      <c r="B551" s="13" t="s">
+        <v>422</v>
+      </c>
       <c r="C551" s="13"/>
-      <c r="D551" s="13"/>
+      <c r="D551" s="40" t="s">
+        <v>423</v>
+      </c>
       <c r="E551" s="13"/>
       <c r="F551" s="13">
         <v>30</v>
       </c>
     </row>
-    <row r="552" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="552" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A552" s="13"/>
       <c r="B552" s="13"/>
       <c r="C552" s="13"/>
-      <c r="D552" s="22" t="s">
+      <c r="D552" s="42" t="s">
         <v>389</v>
       </c>
       <c r="E552" s="28">
@@ -8370,7 +8451,7 @@
       </c>
       <c r="F552" s="13"/>
     </row>
-    <row r="553" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="553" spans="1:8" x14ac:dyDescent="0.3">
       <c r="E553">
         <f>SUM(E547:E551)*E552</f>
         <v>0</v>
@@ -8380,7 +8461,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="556" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="556" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A556" s="7"/>
       <c r="B556" t="s">
         <v>213</v>
@@ -8398,7 +8479,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="557" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="557" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A557" s="11" t="s">
         <v>395</v>
       </c>
@@ -8418,7 +8499,7 @@
         <v>-3.5137034434293744E-2</v>
       </c>
     </row>
-    <row r="558" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="558" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A558" s="15" t="s">
         <v>402</v>
       </c>
@@ -8438,7 +8519,7 @@
         <v>-3.5971223021582732E-2</v>
       </c>
     </row>
-    <row r="559" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="559" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A559" s="16" t="s">
         <v>396</v>
       </c>
@@ -8458,7 +8539,7 @@
         <v>-3.5739814152966405E-2</v>
       </c>
     </row>
-    <row r="563" spans="4:7" x14ac:dyDescent="0.45">
+    <row r="563" spans="4:7" x14ac:dyDescent="0.3">
       <c r="F563" t="s">
         <v>260</v>
       </c>
@@ -8466,15 +8547,15 @@
         <v>261</v>
       </c>
     </row>
-    <row r="564" spans="4:7" x14ac:dyDescent="0.45">
-      <c r="D564" t="s">
+    <row r="564" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D564" s="38" t="s">
         <v>262</v>
       </c>
       <c r="G564" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="565" spans="4:7" x14ac:dyDescent="0.45">
+    <row r="565" spans="4:7" x14ac:dyDescent="0.3">
       <c r="F565">
         <v>45</v>
       </c>
@@ -8482,7 +8563,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="566" spans="4:7" x14ac:dyDescent="0.45">
+    <row r="566" spans="4:7" x14ac:dyDescent="0.3">
       <c r="F566">
         <f>F565+(F574-F565)/9</f>
         <v>50</v>
@@ -8491,7 +8572,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="567" spans="4:7" x14ac:dyDescent="0.45">
+    <row r="567" spans="4:7" x14ac:dyDescent="0.3">
       <c r="F567">
         <f>F566+(F574-F565)/9</f>
         <v>55</v>
@@ -8500,7 +8581,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="568" spans="4:7" x14ac:dyDescent="0.45">
+    <row r="568" spans="4:7" x14ac:dyDescent="0.3">
       <c r="F568">
         <f>F567+(F574-F565)/9</f>
         <v>60</v>
@@ -8509,7 +8590,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="569" spans="4:7" x14ac:dyDescent="0.45">
+    <row r="569" spans="4:7" x14ac:dyDescent="0.3">
       <c r="F569">
         <f>F568+(F574-F565)/9</f>
         <v>65</v>
@@ -8518,7 +8599,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="570" spans="4:7" x14ac:dyDescent="0.45">
+    <row r="570" spans="4:7" x14ac:dyDescent="0.3">
       <c r="F570">
         <f>F569+(F574-F565)/9</f>
         <v>70</v>
@@ -8527,7 +8608,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="571" spans="4:7" x14ac:dyDescent="0.45">
+    <row r="571" spans="4:7" x14ac:dyDescent="0.3">
       <c r="F571">
         <f>F570+(F574-F565)/9</f>
         <v>75</v>
@@ -8536,7 +8617,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="572" spans="4:7" x14ac:dyDescent="0.45">
+    <row r="572" spans="4:7" x14ac:dyDescent="0.3">
       <c r="F572">
         <f>F571+(F574-F565)/9</f>
         <v>80</v>
@@ -8545,7 +8626,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="573" spans="4:7" x14ac:dyDescent="0.45">
+    <row r="573" spans="4:7" x14ac:dyDescent="0.3">
       <c r="F573">
         <f>F572+(F574-F565)/9</f>
         <v>85</v>
@@ -8554,7 +8635,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="574" spans="4:7" x14ac:dyDescent="0.45">
+    <row r="574" spans="4:7" x14ac:dyDescent="0.3">
       <c r="F574">
         <v>90</v>
       </c>
@@ -8562,7 +8643,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="575" spans="4:7" x14ac:dyDescent="0.45">
+    <row r="575" spans="4:7" x14ac:dyDescent="0.3">
       <c r="E575" t="s">
         <v>264</v>
       </c>
@@ -8592,45 +8673,45 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:L1047724"/>
-  <sheetFormatPr defaultColWidth="11.46484375" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="31.1328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.46484375" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="27.46484375" customWidth="1"/>
-    <col min="5" max="5" width="14.46484375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="31.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="27.44140625" customWidth="1"/>
+    <col min="5" max="5" width="14.44140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="33.4" x14ac:dyDescent="1">
+    <row r="1" spans="1:4" ht="33.6" x14ac:dyDescent="0.65">
       <c r="A1" s="29" t="s">
         <v>392</v>
       </c>
       <c r="B1" s="29"/>
       <c r="C1" s="29"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="30" t="s">
         <v>393</v>
       </c>
       <c r="B5" s="30"/>
       <c r="C5" s="30"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="28.5" x14ac:dyDescent="0.85">
+    <row r="8" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="2" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>84</v>
       </c>
@@ -8644,7 +8725,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>397</v>
       </c>
@@ -8658,15 +8739,15 @@
         <v>400</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C11" s="3"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>89</v>
       </c>
@@ -8674,7 +8755,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>90</v>
       </c>
@@ -8682,7 +8763,7 @@
         <v>45924</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>91</v>
       </c>
@@ -8690,12 +8771,12 @@
         <v>46051</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>93</v>
       </c>
@@ -8703,13 +8784,13 @@
         <v>401</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="23.25" x14ac:dyDescent="0.7">
+    <row r="23" spans="1:8" ht="23.4" x14ac:dyDescent="0.45">
       <c r="A23" s="6" t="s">
         <v>94</v>
       </c>
       <c r="H23" s="21"/>
     </row>
-    <row r="25" spans="1:8" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:8" ht="18" x14ac:dyDescent="0.35">
       <c r="A25" s="5" t="s">
         <v>95</v>
       </c>
@@ -8720,7 +8801,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="15" t="s">
         <v>36</v>
       </c>
@@ -8733,7 +8814,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="15"/>
       <c r="B28" s="13" t="s">
         <v>37</v>
@@ -8744,7 +8825,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="15"/>
       <c r="B29" s="13" t="s">
         <v>38</v>
@@ -8755,7 +8836,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="15"/>
       <c r="B30" s="13" t="s">
         <v>19</v>
@@ -8766,7 +8847,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="15"/>
       <c r="B31" s="13" t="s">
         <v>39</v>
@@ -8777,7 +8858,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="15"/>
       <c r="B32" s="13"/>
       <c r="C32" s="22" t="s">
@@ -8789,7 +8870,7 @@
       </c>
       <c r="E32" s="13"/>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D33">
         <f>-SUM(D27:D32)</f>
         <v>0</v>
@@ -8800,7 +8881,7 @@
       </c>
       <c r="L33" s="20"/>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" s="16" t="s">
         <v>45</v>
       </c>
@@ -8814,7 +8895,7 @@
       </c>
       <c r="L34" s="20"/>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" s="16"/>
       <c r="B35" s="14" t="s">
         <v>50</v>
@@ -8826,7 +8907,7 @@
       </c>
       <c r="L35" s="20"/>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" s="16"/>
       <c r="B36" s="14"/>
       <c r="C36" s="22" t="s">
@@ -8839,7 +8920,7 @@
       <c r="E36" s="14"/>
       <c r="L36" s="20"/>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D37">
         <f>-SUM(D34:D36)</f>
         <v>0</v>
@@ -8850,10 +8931,10 @@
       </c>
       <c r="L37" s="20"/>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="L38" s="20"/>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" s="7" t="s">
         <v>98</v>
       </c>
@@ -8867,7 +8948,7 @@
       </c>
       <c r="L39" s="20"/>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" s="7"/>
       <c r="B40" s="10" t="s">
         <v>47</v>
@@ -8879,7 +8960,7 @@
       </c>
       <c r="L40" s="20"/>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" s="7"/>
       <c r="B41" s="9" t="s">
         <v>48</v>
@@ -8891,7 +8972,7 @@
       </c>
       <c r="L41" s="20"/>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" s="7"/>
       <c r="B42" s="9" t="s">
         <v>49</v>
@@ -8903,7 +8984,7 @@
       </c>
       <c r="L42" s="20"/>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" s="7"/>
       <c r="B43" s="9" t="s">
         <v>50</v>
@@ -8915,7 +8996,7 @@
       </c>
       <c r="L43" s="20"/>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" s="7"/>
       <c r="B44" s="9" t="s">
         <v>51</v>
@@ -8927,7 +9008,7 @@
       </c>
       <c r="L44" s="20"/>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" s="7"/>
       <c r="B45" s="9" t="s">
         <v>52</v>
@@ -8939,7 +9020,7 @@
       </c>
       <c r="L45" s="20"/>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" s="7"/>
       <c r="B46" s="9"/>
       <c r="C46" s="22" t="s">
@@ -8952,7 +9033,7 @@
       <c r="E46" s="8"/>
       <c r="L46" s="20"/>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D47">
         <f>-SUM(D39:D46)</f>
         <v>0</v>
@@ -8963,7 +9044,7 @@
       </c>
       <c r="L47" s="20"/>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" s="15" t="s">
         <v>44</v>
       </c>
@@ -8976,7 +9057,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" s="15"/>
       <c r="B50" s="13" t="s">
         <v>77</v>
@@ -8987,7 +9068,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" s="15"/>
       <c r="B51" s="13" t="s">
         <v>124</v>
@@ -8998,14 +9079,14 @@
         <v>5</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" s="15"/>
       <c r="B52" s="13"/>
       <c r="C52" s="15"/>
       <c r="D52" s="15"/>
       <c r="E52" s="15"/>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" s="15" t="s">
         <v>122</v>
       </c>
@@ -9018,7 +9099,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" s="15"/>
       <c r="B54" s="13" t="s">
         <v>123</v>
@@ -9029,7 +9110,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" s="15"/>
       <c r="B55" s="13" t="s">
         <v>124</v>
@@ -9040,14 +9121,14 @@
         <v>5</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" s="15"/>
       <c r="B56" s="13"/>
       <c r="C56" s="15"/>
       <c r="D56" s="15"/>
       <c r="E56" s="15"/>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" s="15" t="s">
         <v>227</v>
       </c>
@@ -9060,7 +9141,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" s="15"/>
       <c r="B58" s="13" t="s">
         <v>123</v>
@@ -9071,7 +9152,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" s="15"/>
       <c r="B59" s="13" t="s">
         <v>124</v>
@@ -9082,7 +9163,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" s="15"/>
       <c r="B60" s="13"/>
       <c r="C60" s="22" t="s">
@@ -9094,7 +9175,7 @@
       </c>
       <c r="E60" s="13"/>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D61">
         <f>-SUM(D49:D60)</f>
         <v>0</v>
@@ -9104,7 +9185,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" s="15" t="s">
         <v>78</v>
       </c>
@@ -9117,7 +9198,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" s="15"/>
       <c r="B64" s="13" t="s">
         <v>46</v>
@@ -9128,7 +9209,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" s="15"/>
       <c r="B65" s="13" t="s">
         <v>247</v>
@@ -9139,7 +9220,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" s="15"/>
       <c r="B66" s="13" t="s">
         <v>79</v>
@@ -9150,7 +9231,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" s="15"/>
       <c r="B67" s="13"/>
       <c r="C67" s="22" t="s">
@@ -9162,7 +9243,7 @@
       </c>
       <c r="E67" s="13"/>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D68">
         <f>-SUM(D63:D67)</f>
         <v>0</v>
@@ -9172,7 +9253,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" s="11" t="s">
         <v>35</v>
       </c>
@@ -9185,7 +9266,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" s="11"/>
       <c r="B73" s="12" t="s">
         <v>229</v>
@@ -9196,7 +9277,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" s="11"/>
       <c r="B74" s="12" t="s">
         <v>230</v>
@@ -9207,7 +9288,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" s="11"/>
       <c r="B75" s="12" t="s">
         <v>228</v>
@@ -9218,7 +9299,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" s="11"/>
       <c r="B76" s="12"/>
       <c r="C76" s="22" t="s">
@@ -9230,7 +9311,7 @@
       </c>
       <c r="E76" s="12"/>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D77">
         <f>-SUM(D72:D76)</f>
         <v>0</v>
@@ -9240,7 +9321,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" s="7" t="s">
         <v>57</v>
       </c>
@@ -9253,7 +9334,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" s="7"/>
       <c r="B80" s="8" t="s">
         <v>60</v>
@@ -9264,7 +9345,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" s="7"/>
       <c r="B81" s="8" t="s">
         <v>59</v>
@@ -9275,7 +9356,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" s="7"/>
       <c r="B82" s="8" t="s">
         <v>56</v>
@@ -9286,7 +9367,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" s="7"/>
       <c r="B83" s="8" t="s">
         <v>231</v>
@@ -9297,7 +9378,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" s="7"/>
       <c r="B84" s="8" t="s">
         <v>61</v>
@@ -9310,7 +9391,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" s="7"/>
       <c r="B85" s="8"/>
       <c r="C85" s="8" t="s">
@@ -9321,7 +9402,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" s="7"/>
       <c r="B86" s="8"/>
       <c r="C86" s="8" t="s">
@@ -9332,7 +9413,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" s="7"/>
       <c r="B87" s="8"/>
       <c r="C87" s="8" t="s">
@@ -9343,7 +9424,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" s="7"/>
       <c r="B88" s="8"/>
       <c r="C88" s="8" t="s">
@@ -9354,7 +9435,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" s="7"/>
       <c r="B89" s="8"/>
       <c r="C89" s="22" t="s">
@@ -9366,7 +9447,7 @@
       </c>
       <c r="E89" s="8"/>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="D90">
         <f>-SUM(D79:D89)</f>
         <v>0</v>
@@ -9376,7 +9457,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" s="11" t="s">
         <v>168</v>
       </c>
@@ -9389,7 +9470,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" s="11"/>
       <c r="B92" s="12" t="s">
         <v>77</v>
@@ -9400,7 +9481,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" s="11"/>
       <c r="B93" s="12" t="s">
         <v>170</v>
@@ -9411,7 +9492,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" s="11"/>
       <c r="B94" s="12"/>
       <c r="C94" s="22" t="s">
@@ -9423,7 +9504,7 @@
       </c>
       <c r="E94" s="12"/>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="D95">
         <f>-SUM(D91:D94)</f>
         <v>0</v>
@@ -9433,7 +9514,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" s="36" t="s">
         <v>62</v>
       </c>
@@ -9449,7 +9530,7 @@
       </c>
       <c r="H96" s="1"/>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97" s="36"/>
       <c r="B97" s="12"/>
       <c r="C97" s="12" t="s">
@@ -9460,7 +9541,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98" s="36"/>
       <c r="B98" s="12"/>
       <c r="C98" s="12" t="s">
@@ -9471,7 +9552,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99" s="36"/>
       <c r="B99" s="12"/>
       <c r="C99" s="12" t="s">
@@ -9482,7 +9563,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100" s="36"/>
       <c r="B100" s="12"/>
       <c r="C100" s="12" t="s">
@@ -9493,7 +9574,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101" s="36"/>
       <c r="B101" s="12"/>
       <c r="C101" s="12" t="s">
@@ -9504,7 +9585,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102" s="36"/>
       <c r="B102" s="12"/>
       <c r="C102" s="12" t="s">
@@ -9515,7 +9596,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103" s="36"/>
       <c r="B103" s="12"/>
       <c r="C103" s="12" t="s">
@@ -9526,7 +9607,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104" s="36"/>
       <c r="B104" s="12"/>
       <c r="C104" s="22" t="s">
@@ -9538,7 +9619,7 @@
       </c>
       <c r="E104" s="12"/>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A105" s="36"/>
       <c r="D105">
         <f>-SUM(D96:D104)</f>
@@ -9549,7 +9630,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106" s="36"/>
       <c r="B106" s="15" t="s">
         <v>63</v>
@@ -9562,7 +9643,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A107" s="36"/>
       <c r="B107" s="13"/>
       <c r="C107" s="13" t="s">
@@ -9573,7 +9654,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108" s="36"/>
       <c r="B108" s="13"/>
       <c r="C108" s="13" t="s">
@@ -9584,7 +9665,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A109" s="36"/>
       <c r="B109" s="13"/>
       <c r="C109" s="13" t="s">
@@ -9595,7 +9676,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A110" s="36"/>
       <c r="B110" s="13"/>
       <c r="C110" s="13" t="s">
@@ -9606,7 +9687,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A111" s="36"/>
       <c r="B111" s="13"/>
       <c r="C111" s="13" t="s">
@@ -9617,7 +9698,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112" s="36"/>
       <c r="B112" s="13"/>
       <c r="C112" s="13" t="s">
@@ -9628,7 +9709,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113" s="36"/>
       <c r="B113" s="13"/>
       <c r="C113" s="13" t="s">
@@ -9639,7 +9720,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114" s="36"/>
       <c r="B114" s="13"/>
       <c r="C114" s="22" t="s">
@@ -9651,7 +9732,7 @@
       </c>
       <c r="E114" s="13"/>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115" s="36"/>
       <c r="D115">
         <f>-SUM(D106:D114)</f>
@@ -9662,7 +9743,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116" s="36"/>
       <c r="B116" s="16" t="s">
         <v>63</v>
@@ -9675,7 +9756,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117" s="36"/>
       <c r="B117" s="14"/>
       <c r="C117" s="14" t="s">
@@ -9686,7 +9767,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A118" s="36"/>
       <c r="B118" s="14"/>
       <c r="C118" s="14" t="s">
@@ -9697,7 +9778,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A119" s="36"/>
       <c r="B119" s="14"/>
       <c r="C119" s="14" t="s">
@@ -9708,7 +9789,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A120" s="36"/>
       <c r="B120" s="14"/>
       <c r="C120" s="14" t="s">
@@ -9719,7 +9800,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A121" s="36"/>
       <c r="B121" s="14"/>
       <c r="C121" s="14" t="s">
@@ -9730,7 +9811,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A122" s="36"/>
       <c r="B122" s="14"/>
       <c r="C122" s="14" t="s">
@@ -9741,7 +9822,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A123" s="36"/>
       <c r="B123" s="14"/>
       <c r="C123" s="14" t="s">
@@ -9752,7 +9833,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A124" s="36"/>
       <c r="B124" s="14"/>
       <c r="C124" s="22" t="s">
@@ -9764,7 +9845,7 @@
       </c>
       <c r="E124" s="14"/>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A125" s="36"/>
       <c r="D125">
         <f>-SUM(D116:D124)</f>
@@ -9775,7 +9856,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A127" s="11" t="s">
         <v>109</v>
       </c>
@@ -9790,7 +9871,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A128" s="12"/>
       <c r="B128" s="12"/>
       <c r="C128" s="12" t="s">
@@ -9803,7 +9884,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A129" s="12"/>
       <c r="B129" s="12"/>
       <c r="C129" s="12"/>
@@ -9814,7 +9895,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A130" s="12"/>
       <c r="B130" s="12"/>
       <c r="C130" s="12" t="s">
@@ -9825,7 +9906,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A131" s="12"/>
       <c r="B131" s="12"/>
       <c r="C131" s="12" t="s">
@@ -9836,7 +9917,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A132" s="12"/>
       <c r="B132" s="12"/>
       <c r="C132" s="12" t="s">
@@ -9847,7 +9928,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A133" s="12"/>
       <c r="B133" s="12"/>
       <c r="C133" s="22" t="s">
@@ -9859,7 +9940,7 @@
       </c>
       <c r="E133" s="12"/>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A134"/>
       <c r="D134">
         <f>-SUM(D127:D133)</f>
@@ -9870,7 +9951,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A135" s="11" t="s">
         <v>109</v>
       </c>
@@ -9885,7 +9966,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A136" s="12"/>
       <c r="B136" s="12"/>
       <c r="C136" s="12" t="s">
@@ -9896,7 +9977,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A137" s="12"/>
       <c r="B137" s="12"/>
       <c r="C137" s="12" t="s">
@@ -9907,7 +9988,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A138" s="12"/>
       <c r="B138" s="12"/>
       <c r="C138" s="12" t="s">
@@ -9920,7 +10001,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A139" s="12"/>
       <c r="B139" s="12"/>
       <c r="C139" s="12"/>
@@ -9931,7 +10012,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A140" s="12"/>
       <c r="B140" s="12"/>
       <c r="C140" s="12"/>
@@ -9942,7 +10023,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A141" s="12"/>
       <c r="B141" s="12"/>
       <c r="C141" s="12"/>
@@ -9953,7 +10034,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A142" s="11"/>
       <c r="B142" s="12"/>
       <c r="C142" s="22" t="s">
@@ -9965,7 +10046,7 @@
       </c>
       <c r="E142" s="12"/>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D143">
         <f>-SUM(D135:D142)</f>
         <v>0</v>
@@ -9975,7 +10056,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A144" s="15" t="s">
         <v>125</v>
       </c>
@@ -9990,7 +10071,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A145" s="15"/>
       <c r="B145" s="13"/>
       <c r="C145" s="13" t="s">
@@ -10001,7 +10082,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A146" s="15"/>
       <c r="B146" s="13"/>
       <c r="C146" s="13" t="s">
@@ -10012,7 +10093,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A147" s="15"/>
       <c r="B147" s="13"/>
       <c r="C147" s="13" t="s">
@@ -10023,7 +10104,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A148" s="15"/>
       <c r="B148" s="13"/>
       <c r="C148" s="13" t="s">
@@ -10034,7 +10115,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A149" s="15"/>
       <c r="B149" s="13"/>
       <c r="C149" s="22" t="s">
@@ -10046,7 +10127,7 @@
       </c>
       <c r="E149" s="13"/>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D150">
         <f>-SUM(D144:D149)</f>
         <v>0</v>
@@ -10056,7 +10137,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A151" s="16" t="s">
         <v>125</v>
       </c>
@@ -10071,7 +10152,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A152" s="16"/>
       <c r="B152" s="14"/>
       <c r="C152" s="14" t="s">
@@ -10082,7 +10163,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A153" s="16"/>
       <c r="B153" s="14"/>
       <c r="C153" s="14" t="s">
@@ -10093,7 +10174,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A154" s="16"/>
       <c r="B154" s="14"/>
       <c r="C154" s="22" t="s">
@@ -10105,7 +10186,7 @@
       </c>
       <c r="E154" s="14"/>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D155">
         <f>-SUM(D151:D154)</f>
         <v>0</v>
@@ -10115,7 +10196,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A157" s="16" t="s">
         <v>119</v>
       </c>
@@ -10128,7 +10209,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A158" s="16"/>
       <c r="B158" s="14" t="s">
         <v>121</v>
@@ -10139,7 +10220,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A159" s="16"/>
       <c r="B159" s="14" t="s">
         <v>224</v>
@@ -10150,7 +10231,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A160" s="16"/>
       <c r="B160" s="14" t="s">
         <v>232</v>
@@ -10161,7 +10242,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A161" s="16"/>
       <c r="B161" s="14" t="s">
         <v>225</v>
@@ -10172,7 +10253,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A162" s="16"/>
       <c r="B162" s="14"/>
       <c r="C162" s="22" t="s">
@@ -10184,7 +10265,7 @@
       </c>
       <c r="E162" s="14"/>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D163">
         <f>-SUM(D157:D162)</f>
         <v>0</v>
@@ -10194,7 +10275,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A164" s="11" t="s">
         <v>206</v>
       </c>
@@ -10207,7 +10288,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A165" s="11"/>
       <c r="B165" s="12" t="s">
         <v>65</v>
@@ -10218,7 +10299,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A166" s="11"/>
       <c r="B166" s="12" t="s">
         <v>50</v>
@@ -10229,7 +10310,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A167" s="11"/>
       <c r="B167" s="12" t="s">
         <v>207</v>
@@ -10240,7 +10321,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A168" s="11"/>
       <c r="B168" s="12" t="s">
         <v>51</v>
@@ -10251,7 +10332,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A169" s="11"/>
       <c r="B169" s="12" t="s">
         <v>234</v>
@@ -10262,7 +10343,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A170" s="11"/>
       <c r="B170" s="12"/>
       <c r="C170" s="22" t="s">
@@ -10274,7 +10355,7 @@
       </c>
       <c r="E170" s="12"/>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D171">
         <f>-SUM(D164:D170)</f>
         <v>0</v>
@@ -10284,7 +10365,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A172" s="15" t="s">
         <v>130</v>
       </c>
@@ -10297,7 +10378,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A173" s="15"/>
       <c r="B173" s="13" t="s">
         <v>235</v>
@@ -10308,7 +10389,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A174" s="15"/>
       <c r="B174" s="13" t="s">
         <v>8</v>
@@ -10319,7 +10400,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A175" s="15"/>
       <c r="B175" s="13" t="s">
         <v>132</v>
@@ -10330,7 +10411,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A176" s="15"/>
       <c r="B176" s="13" t="s">
         <v>133</v>
@@ -10341,7 +10422,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A177" s="15"/>
       <c r="B177" s="13" t="s">
         <v>134</v>
@@ -10352,7 +10433,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A178" s="15"/>
       <c r="B178" s="13"/>
       <c r="C178" s="22" t="s">
@@ -10364,7 +10445,7 @@
       </c>
       <c r="E178" s="13"/>
     </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D179">
         <f>-SUM(D172:D178)</f>
         <v>0</v>
@@ -10374,7 +10455,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A180" s="16" t="s">
         <v>135</v>
       </c>
@@ -10387,7 +10468,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A181" s="16"/>
       <c r="B181" s="14" t="s">
         <v>233</v>
@@ -10398,7 +10479,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="182" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A182" s="16"/>
       <c r="B182" s="14" t="s">
         <v>136</v>
@@ -10409,7 +10490,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A183" s="16"/>
       <c r="B183" s="14" t="s">
         <v>137</v>
@@ -10420,7 +10501,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A184" s="16"/>
       <c r="B184" s="14" t="s">
         <v>55</v>
@@ -10431,7 +10512,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A185" s="16"/>
       <c r="B185" s="14" t="s">
         <v>54</v>
@@ -10442,7 +10523,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A186" s="16"/>
       <c r="B186" s="14" t="s">
         <v>138</v>
@@ -10453,7 +10534,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="187" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A187" s="16"/>
       <c r="B187" s="14" t="s">
         <v>139</v>
@@ -10464,7 +10545,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="188" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A188" s="16"/>
       <c r="B188" s="14" t="s">
         <v>140</v>
@@ -10475,7 +10556,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A189" s="16"/>
       <c r="B189" s="14" t="s">
         <v>141</v>
@@ -10486,7 +10567,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A190" s="16"/>
       <c r="B190" s="14"/>
       <c r="C190" s="22" t="s">
@@ -10498,7 +10579,7 @@
       </c>
       <c r="E190" s="14"/>
     </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D191">
         <f>-SUM(D180:D190)</f>
         <v>0</v>
@@ -10508,7 +10589,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A194" s="7" t="s">
         <v>171</v>
       </c>
@@ -10523,7 +10604,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A195" s="7"/>
       <c r="B195" s="8"/>
       <c r="C195" s="8" t="s">
@@ -10534,7 +10615,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A196" s="7"/>
       <c r="B196" s="8"/>
       <c r="C196" s="8" t="s">
@@ -10545,7 +10626,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A197" s="7"/>
       <c r="B197" s="8" t="s">
         <v>176</v>
@@ -10558,7 +10639,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A198" s="7"/>
       <c r="B198" s="8"/>
       <c r="C198" s="8" t="s">
@@ -10569,7 +10650,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="199" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A199" s="7"/>
       <c r="B199" s="8"/>
       <c r="C199" s="8" t="s">
@@ -10580,7 +10661,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="200" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A200" s="7"/>
       <c r="B200" s="8"/>
       <c r="C200" s="8" t="s">
@@ -10591,7 +10672,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="201" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A201" s="7"/>
       <c r="B201" s="8"/>
       <c r="C201" s="8" t="s">
@@ -10602,7 +10683,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="202" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A202" s="7"/>
       <c r="B202" s="8" t="s">
         <v>182</v>
@@ -10613,7 +10694,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="203" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A203" s="7"/>
       <c r="B203" s="8" t="s">
         <v>204</v>
@@ -10626,7 +10707,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="204" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A204" s="7"/>
       <c r="B204" s="8"/>
       <c r="C204" s="8" t="s">
@@ -10637,7 +10718,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="205" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A205" s="7"/>
       <c r="B205" s="8"/>
       <c r="C205" s="8" t="s">
@@ -10648,7 +10729,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="206" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A206" s="7"/>
       <c r="B206" s="8"/>
       <c r="C206" s="8" t="s">
@@ -10659,7 +10740,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="207" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A207" s="7"/>
       <c r="B207" s="8" t="str">
         <f>Report!B408</f>
@@ -10674,7 +10755,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="208" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A208" s="7"/>
       <c r="B208" s="8"/>
       <c r="C208" s="8" t="str">
@@ -10686,7 +10767,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="209" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A209" s="7"/>
       <c r="B209" s="8"/>
       <c r="C209" s="8" t="str">
@@ -10698,7 +10779,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="210" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A210" s="7"/>
       <c r="B210" s="8"/>
       <c r="C210" s="8" t="str">
@@ -10710,7 +10791,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="211" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A211" s="7"/>
       <c r="B211" s="8"/>
       <c r="C211" s="8" t="str">
@@ -10722,7 +10803,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="212" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A212" s="7"/>
       <c r="B212" s="8"/>
       <c r="C212" s="22" t="s">
@@ -10734,7 +10815,7 @@
       </c>
       <c r="E212" s="8"/>
     </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="213" spans="1:7" x14ac:dyDescent="0.3">
       <c r="D213">
         <f>-SUM(D194:D212)</f>
         <v>0</v>
@@ -10744,7 +10825,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="218" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A218" s="7"/>
       <c r="B218" t="s">
         <v>213</v>
@@ -10762,7 +10843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="219" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A219" s="11" t="s">
         <v>395</v>
       </c>
@@ -10782,7 +10863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="220" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A220" s="15" t="s">
         <v>403</v>
       </c>
@@ -10802,7 +10883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="221" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A221" s="16" t="s">
         <v>396</v>
       </c>
@@ -10822,7 +10903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="4:7" x14ac:dyDescent="0.45">
+    <row r="226" spans="4:7" x14ac:dyDescent="0.3">
       <c r="F226" t="s">
         <v>260</v>
       </c>
@@ -10830,7 +10911,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="227" spans="4:7" x14ac:dyDescent="0.45">
+    <row r="227" spans="4:7" x14ac:dyDescent="0.3">
       <c r="D227" t="s">
         <v>262</v>
       </c>
@@ -10838,7 +10919,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="228" spans="4:7" x14ac:dyDescent="0.45">
+    <row r="228" spans="4:7" x14ac:dyDescent="0.3">
       <c r="F228">
         <v>45</v>
       </c>
@@ -10846,7 +10927,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="229" spans="4:7" x14ac:dyDescent="0.45">
+    <row r="229" spans="4:7" x14ac:dyDescent="0.3">
       <c r="F229">
         <f>F228+(F237-F228)/9</f>
         <v>50</v>
@@ -10855,7 +10936,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="230" spans="4:7" x14ac:dyDescent="0.45">
+    <row r="230" spans="4:7" x14ac:dyDescent="0.3">
       <c r="F230">
         <f>F229+(F237-F228)/9</f>
         <v>55</v>
@@ -10864,7 +10945,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="231" spans="4:7" x14ac:dyDescent="0.45">
+    <row r="231" spans="4:7" x14ac:dyDescent="0.3">
       <c r="F231">
         <f>F230+(F237-F228)/9</f>
         <v>60</v>
@@ -10873,7 +10954,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="232" spans="4:7" x14ac:dyDescent="0.45">
+    <row r="232" spans="4:7" x14ac:dyDescent="0.3">
       <c r="F232">
         <f>F231+(F237-F228)/9</f>
         <v>65</v>
@@ -10882,7 +10963,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="233" spans="4:7" x14ac:dyDescent="0.45">
+    <row r="233" spans="4:7" x14ac:dyDescent="0.3">
       <c r="F233">
         <f>F232+(F237-F228)/9</f>
         <v>70</v>
@@ -10891,7 +10972,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="234" spans="4:7" x14ac:dyDescent="0.45">
+    <row r="234" spans="4:7" x14ac:dyDescent="0.3">
       <c r="F234">
         <f>F233+(F237-F228)/9</f>
         <v>75</v>
@@ -10900,7 +10981,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="235" spans="4:7" x14ac:dyDescent="0.45">
+    <row r="235" spans="4:7" x14ac:dyDescent="0.3">
       <c r="F235">
         <f>F234+(F237-F228)/9</f>
         <v>80</v>
@@ -10909,7 +10990,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="236" spans="4:7" x14ac:dyDescent="0.45">
+    <row r="236" spans="4:7" x14ac:dyDescent="0.3">
       <c r="F236">
         <f>F235+(F237-F228)/9</f>
         <v>85</v>
@@ -10918,7 +10999,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="237" spans="4:7" x14ac:dyDescent="0.45">
+    <row r="237" spans="4:7" x14ac:dyDescent="0.3">
       <c r="F237">
         <v>90</v>
       </c>
@@ -10926,12 +11007,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="238" spans="4:7" x14ac:dyDescent="0.45">
+    <row r="238" spans="4:7" x14ac:dyDescent="0.3">
       <c r="E238" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="1047724" spans="5:5" x14ac:dyDescent="0.45">
+    <row r="1047724" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E1047724" s="8"/>
     </row>
   </sheetData>
@@ -10955,14 +11036,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D37"/>
-  <sheetFormatPr defaultColWidth="11.46484375" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="35.796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.46484375" style="20"/>
+    <col min="2" max="2" width="35.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.44140625" style="20"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="25.5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:4" ht="25.8" x14ac:dyDescent="0.5">
       <c r="A1" s="37" t="s">
         <v>253</v>
       </c>
@@ -10970,10 +11051,10 @@
       <c r="C1" s="37"/>
       <c r="D1" s="37"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>237</v>
       </c>
@@ -10981,7 +11062,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>42</v>
       </c>
@@ -10989,7 +11070,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>239</v>
       </c>
@@ -10997,7 +11078,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>240</v>
       </c>
@@ -11005,7 +11086,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>241</v>
       </c>
@@ -11013,7 +11094,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>242</v>
       </c>
@@ -11021,7 +11102,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>204</v>
       </c>
@@ -11029,7 +11110,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>238</v>
       </c>
@@ -11037,7 +11118,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>244</v>
       </c>
@@ -11045,7 +11126,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>243</v>
       </c>
@@ -11053,7 +11134,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>245</v>
       </c>
@@ -11061,7 +11142,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>246</v>
       </c>
@@ -11069,7 +11150,7 @@
         <v>-0.3</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>252</v>
       </c>
@@ -11077,7 +11158,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>254</v>
       </c>
@@ -11085,7 +11166,7 @@
         <v>-0.2</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>255</v>
       </c>
@@ -11093,7 +11174,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>42</v>
       </c>
@@ -11107,7 +11188,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C23" t="s">
         <v>174</v>
       </c>
@@ -11115,7 +11196,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C24" t="s">
         <v>175</v>
       </c>
@@ -11123,7 +11204,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
         <v>176</v>
       </c>
@@ -11134,7 +11215,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C26" t="s">
         <v>178</v>
       </c>
@@ -11142,7 +11223,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C27" t="s">
         <v>179</v>
       </c>
@@ -11150,7 +11231,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C28" t="s">
         <v>180</v>
       </c>
@@ -11158,12 +11239,12 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
         <v>192</v>
       </c>
@@ -11174,7 +11255,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C32" t="s">
         <v>196</v>
       </c>
@@ -11182,7 +11263,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="33" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C33" t="s">
         <v>179</v>
       </c>
@@ -11190,7 +11271,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B34" t="s">
         <v>250</v>
       </c>
@@ -11198,7 +11279,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="35" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B35" t="s">
         <v>197</v>
       </c>
@@ -11209,7 +11290,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="36" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C36" t="s">
         <v>199</v>
       </c>
@@ -11217,7 +11298,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="37" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C37" t="s">
         <v>200</v>
       </c>

--- a/ProjectManagement/EvaluationHWAndProject.xlsx
+++ b/ProjectManagement/EvaluationHWAndProject.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\gthub\ML26-03-Car-Licence-Plate-Identification-with-a-Jetson-Nano\ProjectManagement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39945EBF-606D-4BF5-A2DB-67107DFF197C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A84961D-D91D-4C59-A025-85C8B66A1D18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1802,6 +1802,33 @@
       <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1828,33 +1855,6 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2142,16 +2142,16 @@
     <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="39.21875" customWidth="1"/>
     <col min="3" max="3" width="28.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="39.21875" style="38" customWidth="1"/>
+    <col min="4" max="4" width="39.21875" style="29" customWidth="1"/>
     <col min="5" max="5" width="13.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:6" ht="33.6" x14ac:dyDescent="0.65">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="38" t="s">
         <v>392</v>
       </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
@@ -2159,11 +2159,11 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="30" t="s">
+      <c r="A6" s="39" t="s">
         <v>393</v>
       </c>
-      <c r="B6" s="30"/>
-      <c r="C6" s="30"/>
+      <c r="B6" s="39"/>
+      <c r="C6" s="39"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
@@ -2185,7 +2185,7 @@
       <c r="C10" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="D10" s="39" t="s">
+      <c r="D10" s="30" t="s">
         <v>87</v>
       </c>
       <c r="F10" t="s">
@@ -2202,7 +2202,7 @@
       <c r="C11" s="3">
         <v>7026787</v>
       </c>
-      <c r="D11" s="38" t="s">
+      <c r="D11" s="29" t="s">
         <v>400</v>
       </c>
     </row>
@@ -2276,7 +2276,7 @@
         <v>166</v>
       </c>
       <c r="C28" s="13"/>
-      <c r="D28" s="40"/>
+      <c r="D28" s="31"/>
       <c r="E28" s="13">
         <v>-25</v>
       </c>
@@ -2310,7 +2310,7 @@
         <v>166</v>
       </c>
       <c r="C30" s="12"/>
-      <c r="D30" s="41"/>
+      <c r="D30" s="32"/>
       <c r="E30" s="12">
         <v>-25</v>
       </c>
@@ -2327,7 +2327,7 @@
         <v>167</v>
       </c>
       <c r="C31" s="12"/>
-      <c r="D31" s="41"/>
+      <c r="D31" s="32"/>
       <c r="E31" s="12">
         <v>-25</v>
       </c>
@@ -2361,7 +2361,7 @@
         <v>167</v>
       </c>
       <c r="C33" s="13"/>
-      <c r="D33" s="40"/>
+      <c r="D33" s="31"/>
       <c r="E33" s="13">
         <v>-25</v>
       </c>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="B36" s="13"/>
       <c r="C36" s="13"/>
-      <c r="D36" s="40"/>
+      <c r="D36" s="31"/>
       <c r="E36" s="13"/>
       <c r="F36" s="13"/>
     </row>
@@ -2393,7 +2393,7 @@
         <v>3</v>
       </c>
       <c r="C37" s="13"/>
-      <c r="D37" s="40"/>
+      <c r="D37" s="31"/>
       <c r="E37" s="13"/>
       <c r="F37" s="13">
         <v>10</v>
@@ -2405,7 +2405,7 @@
         <v>28</v>
       </c>
       <c r="C38" s="13"/>
-      <c r="D38" s="40"/>
+      <c r="D38" s="31"/>
       <c r="E38" s="13"/>
       <c r="F38" s="13">
         <v>10</v>
@@ -2417,7 +2417,7 @@
         <v>4</v>
       </c>
       <c r="C39" s="13"/>
-      <c r="D39" s="40"/>
+      <c r="D39" s="31"/>
       <c r="E39" s="13"/>
       <c r="F39" s="13">
         <v>10</v>
@@ -2429,7 +2429,7 @@
         <v>5</v>
       </c>
       <c r="C40" s="13"/>
-      <c r="D40" s="40"/>
+      <c r="D40" s="31"/>
       <c r="E40" s="13"/>
       <c r="F40" s="13">
         <v>10</v>
@@ -2441,7 +2441,7 @@
         <v>6</v>
       </c>
       <c r="C41" s="13"/>
-      <c r="D41" s="40"/>
+      <c r="D41" s="31"/>
       <c r="E41" s="13"/>
       <c r="F41" s="13">
         <v>10</v>
@@ -2453,7 +2453,7 @@
         <v>1</v>
       </c>
       <c r="C42" s="13"/>
-      <c r="D42" s="40"/>
+      <c r="D42" s="31"/>
       <c r="E42" s="13"/>
       <c r="F42" s="13">
         <v>10</v>
@@ -2463,7 +2463,7 @@
       <c r="A43" s="15"/>
       <c r="B43" s="13"/>
       <c r="C43" s="13"/>
-      <c r="D43" s="40"/>
+      <c r="D43" s="31"/>
       <c r="E43" s="13"/>
       <c r="F43" s="13"/>
     </row>
@@ -2475,7 +2475,7 @@
       <c r="C44" s="13" t="s">
         <v>257</v>
       </c>
-      <c r="D44" s="40"/>
+      <c r="D44" s="31"/>
       <c r="E44" s="13"/>
       <c r="F44" s="13">
         <v>4</v>
@@ -2487,7 +2487,7 @@
       <c r="C45" s="13" t="s">
         <v>201</v>
       </c>
-      <c r="D45" s="40"/>
+      <c r="D45" s="31"/>
       <c r="E45" s="13"/>
       <c r="F45" s="13">
         <v>6</v>
@@ -2499,7 +2499,7 @@
       <c r="C46" s="13" t="s">
         <v>202</v>
       </c>
-      <c r="D46" s="40"/>
+      <c r="D46" s="31"/>
       <c r="E46" s="13"/>
       <c r="F46" s="13">
         <v>10</v>
@@ -2511,7 +2511,7 @@
       <c r="C47" s="13" t="s">
         <v>203</v>
       </c>
-      <c r="D47" s="40"/>
+      <c r="D47" s="31"/>
       <c r="E47" s="13"/>
       <c r="F47" s="13">
         <v>5</v>
@@ -2523,7 +2523,7 @@
       <c r="C48" s="13" t="s">
         <v>256</v>
       </c>
-      <c r="D48" s="40"/>
+      <c r="D48" s="31"/>
       <c r="E48" s="13"/>
       <c r="F48" s="13">
         <v>5</v>
@@ -2535,7 +2535,7 @@
       <c r="C49" s="13" t="s">
         <v>198</v>
       </c>
-      <c r="D49" s="40"/>
+      <c r="D49" s="31"/>
       <c r="E49" s="13"/>
       <c r="F49" s="13">
         <v>5</v>
@@ -2547,7 +2547,7 @@
       <c r="C50" s="13" t="s">
         <v>199</v>
       </c>
-      <c r="D50" s="40"/>
+      <c r="D50" s="31"/>
       <c r="E50" s="13"/>
       <c r="F50" s="13">
         <v>5</v>
@@ -2557,7 +2557,7 @@
       <c r="A51" s="13"/>
       <c r="B51" s="13"/>
       <c r="C51" s="13"/>
-      <c r="D51" s="42" t="s">
+      <c r="D51" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E51" s="28">
@@ -2579,7 +2579,7 @@
       <c r="A54" s="23" t="s">
         <v>135</v>
       </c>
-      <c r="D54" s="43"/>
+      <c r="D54" s="34"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" s="16" t="s">
@@ -2594,7 +2594,7 @@
       <c r="F55" s="14">
         <v>10</v>
       </c>
-      <c r="G55" s="31" t="s">
+      <c r="G55" s="40" t="s">
         <v>109</v>
       </c>
     </row>
@@ -2609,7 +2609,7 @@
       <c r="F56" s="14">
         <v>5</v>
       </c>
-      <c r="G56" s="31"/>
+      <c r="G56" s="40"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" s="16"/>
@@ -2622,7 +2622,7 @@
       <c r="F57" s="14">
         <v>5</v>
       </c>
-      <c r="G57" s="31"/>
+      <c r="G57" s="40"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" s="16"/>
@@ -2635,7 +2635,7 @@
       <c r="F58" s="14">
         <v>5</v>
       </c>
-      <c r="G58" s="31"/>
+      <c r="G58" s="40"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" s="16"/>
@@ -2648,7 +2648,7 @@
       <c r="F59" s="14">
         <v>10</v>
       </c>
-      <c r="G59" s="31"/>
+      <c r="G59" s="40"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" s="16"/>
@@ -2661,7 +2661,7 @@
       <c r="F60" s="14">
         <v>5</v>
       </c>
-      <c r="G60" s="31"/>
+      <c r="G60" s="40"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" s="16"/>
@@ -2674,7 +2674,7 @@
       <c r="F61" s="14">
         <v>10</v>
       </c>
-      <c r="G61" s="31"/>
+      <c r="G61" s="40"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" s="16"/>
@@ -2687,7 +2687,7 @@
       <c r="F62" s="14">
         <v>5</v>
       </c>
-      <c r="G62" s="31"/>
+      <c r="G62" s="40"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" s="16"/>
@@ -2700,7 +2700,7 @@
       <c r="F63" s="14">
         <v>5</v>
       </c>
-      <c r="G63" s="31"/>
+      <c r="G63" s="40"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" s="16"/>
@@ -2713,7 +2713,7 @@
       <c r="F64" s="14">
         <v>5</v>
       </c>
-      <c r="G64" s="31"/>
+      <c r="G64" s="40"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" s="16"/>
@@ -2726,7 +2726,7 @@
       <c r="F65" s="14">
         <v>5</v>
       </c>
-      <c r="G65" s="31"/>
+      <c r="G65" s="40"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" s="16"/>
@@ -2739,7 +2739,7 @@
       <c r="F66" s="14">
         <v>5</v>
       </c>
-      <c r="G66" s="31"/>
+      <c r="G66" s="40"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" s="16"/>
@@ -2752,20 +2752,20 @@
       <c r="F67" s="14">
         <v>5</v>
       </c>
-      <c r="G67" s="31"/>
+      <c r="G67" s="40"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" s="16"/>
       <c r="B68" s="14"/>
       <c r="C68" s="14"/>
-      <c r="D68" s="42" t="s">
+      <c r="D68" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E68" s="28">
         <v>1</v>
       </c>
       <c r="F68" s="14"/>
-      <c r="G68" s="31"/>
+      <c r="G68" s="40"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" s="1"/>
@@ -2782,7 +2782,7 @@
       <c r="A70" s="5" t="s">
         <v>343</v>
       </c>
-      <c r="D70" s="43"/>
+      <c r="D70" s="34"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" s="16" t="s">
@@ -2797,7 +2797,7 @@
       <c r="F71" s="14">
         <v>10</v>
       </c>
-      <c r="G71" s="34" t="s">
+      <c r="G71" s="43" t="s">
         <v>109</v>
       </c>
     </row>
@@ -2812,7 +2812,7 @@
       <c r="F72" s="14">
         <v>5</v>
       </c>
-      <c r="G72" s="34"/>
+      <c r="G72" s="43"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" s="16"/>
@@ -2825,7 +2825,7 @@
       <c r="F73" s="14">
         <v>5</v>
       </c>
-      <c r="G73" s="34"/>
+      <c r="G73" s="43"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" s="16"/>
@@ -2838,7 +2838,7 @@
       <c r="F74" s="14">
         <v>5</v>
       </c>
-      <c r="G74" s="34"/>
+      <c r="G74" s="43"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" s="16"/>
@@ -2851,7 +2851,7 @@
       <c r="F75" s="14">
         <v>10</v>
       </c>
-      <c r="G75" s="34"/>
+      <c r="G75" s="43"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" s="16"/>
@@ -2864,20 +2864,20 @@
       <c r="F76" s="14">
         <v>5</v>
       </c>
-      <c r="G76" s="34"/>
+      <c r="G76" s="43"/>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" s="16"/>
       <c r="B77" s="14"/>
       <c r="C77" s="14"/>
-      <c r="D77" s="42" t="s">
+      <c r="D77" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E77" s="28">
         <v>1</v>
       </c>
       <c r="F77" s="14"/>
-      <c r="G77" s="34"/>
+      <c r="G77" s="43"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" s="1"/>
@@ -2908,12 +2908,12 @@
       <c r="C81" s="8" t="s">
         <v>316</v>
       </c>
-      <c r="D81" s="44"/>
+      <c r="D81" s="35"/>
       <c r="E81" s="8"/>
       <c r="F81" s="8">
         <v>0</v>
       </c>
-      <c r="G81" s="35" t="s">
+      <c r="G81" s="44" t="s">
         <v>109</v>
       </c>
     </row>
@@ -2925,12 +2925,12 @@
       <c r="C82" s="8" t="s">
         <v>383</v>
       </c>
-      <c r="D82" s="44"/>
+      <c r="D82" s="35"/>
       <c r="E82" s="8"/>
       <c r="F82" s="8">
         <v>30</v>
       </c>
-      <c r="G82" s="35"/>
+      <c r="G82" s="44"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" s="7"/>
@@ -2938,12 +2938,12 @@
       <c r="C83" s="8" t="s">
         <v>384</v>
       </c>
-      <c r="D83" s="44"/>
+      <c r="D83" s="35"/>
       <c r="E83" s="8"/>
       <c r="F83" s="8">
         <v>10</v>
       </c>
-      <c r="G83" s="35"/>
+      <c r="G83" s="44"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" s="7"/>
@@ -2951,25 +2951,25 @@
       <c r="C84" s="8" t="s">
         <v>385</v>
       </c>
-      <c r="D84" s="44"/>
+      <c r="D84" s="35"/>
       <c r="E84" s="8"/>
       <c r="F84" s="8">
         <v>10</v>
       </c>
-      <c r="G84" s="35"/>
+      <c r="G84" s="44"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" s="7"/>
       <c r="B85" s="7"/>
       <c r="C85" s="7"/>
-      <c r="D85" s="42" t="s">
+      <c r="D85" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E85" s="28">
         <v>1</v>
       </c>
       <c r="F85" s="7"/>
-      <c r="G85" s="35"/>
+      <c r="G85" s="44"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" s="1"/>
@@ -2999,7 +2999,7 @@
         <v>316</v>
       </c>
       <c r="C89" s="13"/>
-      <c r="D89" s="40"/>
+      <c r="D89" s="31"/>
       <c r="E89" s="13"/>
       <c r="F89" s="13">
         <v>10</v>
@@ -3011,7 +3011,7 @@
         <v>131</v>
       </c>
       <c r="C90" s="13"/>
-      <c r="D90" s="40"/>
+      <c r="D90" s="31"/>
       <c r="E90" s="13"/>
       <c r="F90" s="13">
         <v>5</v>
@@ -3023,7 +3023,7 @@
         <v>235</v>
       </c>
       <c r="C91" s="13"/>
-      <c r="D91" s="40"/>
+      <c r="D91" s="31"/>
       <c r="E91" s="13"/>
       <c r="F91" s="13">
         <v>5</v>
@@ -3035,7 +3035,7 @@
         <v>8</v>
       </c>
       <c r="C92" s="13"/>
-      <c r="D92" s="40"/>
+      <c r="D92" s="31"/>
       <c r="E92" s="13"/>
       <c r="F92" s="13">
         <v>5</v>
@@ -3047,7 +3047,7 @@
         <v>132</v>
       </c>
       <c r="C93" s="13"/>
-      <c r="D93" s="40"/>
+      <c r="D93" s="31"/>
       <c r="E93" s="13"/>
       <c r="F93" s="13">
         <v>5</v>
@@ -3059,7 +3059,7 @@
         <v>133</v>
       </c>
       <c r="C94" s="13"/>
-      <c r="D94" s="40"/>
+      <c r="D94" s="31"/>
       <c r="E94" s="13"/>
       <c r="F94" s="13">
         <v>5</v>
@@ -3071,7 +3071,7 @@
         <v>134</v>
       </c>
       <c r="C95" s="13"/>
-      <c r="D95" s="40"/>
+      <c r="D95" s="31"/>
       <c r="E95" s="13"/>
       <c r="F95" s="13">
         <v>5</v>
@@ -3081,7 +3081,7 @@
       <c r="A96" s="15"/>
       <c r="B96" s="13"/>
       <c r="C96" s="13"/>
-      <c r="D96" s="42" t="s">
+      <c r="D96" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E96" s="28">
@@ -3119,7 +3119,7 @@
         <v>8</v>
       </c>
       <c r="C101" s="13"/>
-      <c r="D101" s="40"/>
+      <c r="D101" s="31"/>
       <c r="E101" s="13"/>
       <c r="F101" s="13">
         <v>5</v>
@@ -3131,7 +3131,7 @@
         <v>9</v>
       </c>
       <c r="C102" s="13"/>
-      <c r="D102" s="40"/>
+      <c r="D102" s="31"/>
       <c r="E102" s="13"/>
       <c r="F102" s="13">
         <v>5</v>
@@ -3143,7 +3143,7 @@
         <v>10</v>
       </c>
       <c r="C103" s="13"/>
-      <c r="D103" s="40"/>
+      <c r="D103" s="31"/>
       <c r="E103" s="13"/>
       <c r="F103" s="13">
         <v>5</v>
@@ -3155,7 +3155,7 @@
         <v>11</v>
       </c>
       <c r="C104" s="13"/>
-      <c r="D104" s="40"/>
+      <c r="D104" s="31"/>
       <c r="E104" s="13"/>
       <c r="F104" s="13">
         <v>10</v>
@@ -3167,7 +3167,7 @@
         <v>12</v>
       </c>
       <c r="C105" s="13"/>
-      <c r="D105" s="40"/>
+      <c r="D105" s="31"/>
       <c r="E105" s="13"/>
       <c r="F105" s="13">
         <v>5</v>
@@ -3179,7 +3179,7 @@
         <v>100</v>
       </c>
       <c r="C106" s="13"/>
-      <c r="D106" s="40"/>
+      <c r="D106" s="31"/>
       <c r="E106" s="13"/>
       <c r="F106" s="13">
         <v>5</v>
@@ -3189,7 +3189,7 @@
       <c r="A107" s="13"/>
       <c r="B107" s="13"/>
       <c r="C107" s="13"/>
-      <c r="D107" s="42" t="s">
+      <c r="D107" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E107" s="28">
@@ -3314,7 +3314,7 @@
       <c r="A119" s="14"/>
       <c r="B119" s="24"/>
       <c r="C119" s="14"/>
-      <c r="D119" s="42" t="s">
+      <c r="D119" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E119" s="28">
@@ -3347,14 +3347,14 @@
       <c r="C124" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="D124" s="41"/>
+      <c r="D124" s="32"/>
       <c r="E124" s="12" t="s">
         <v>319</v>
       </c>
       <c r="F124" s="12">
         <v>6</v>
       </c>
-      <c r="G124" s="32" t="s">
+      <c r="G124" s="41" t="s">
         <v>109</v>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       <c r="C125" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="D125" s="41" t="s">
+      <c r="D125" s="32" t="s">
         <v>331</v>
       </c>
       <c r="E125" s="12" t="s">
@@ -3375,13 +3375,13 @@
       <c r="F125" s="12">
         <v>6</v>
       </c>
-      <c r="G125" s="32"/>
+      <c r="G125" s="41"/>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A126" s="12"/>
       <c r="B126" s="12"/>
       <c r="C126" s="12"/>
-      <c r="D126" s="41" t="s">
+      <c r="D126" s="32" t="s">
         <v>102</v>
       </c>
       <c r="E126" s="12" t="s">
@@ -3390,7 +3390,7 @@
       <c r="F126" s="12">
         <v>6</v>
       </c>
-      <c r="G126" s="32"/>
+      <c r="G126" s="41"/>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A127" s="12"/>
@@ -3398,14 +3398,14 @@
       <c r="C127" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="D127" s="41"/>
+      <c r="D127" s="32"/>
       <c r="E127" s="12" t="s">
         <v>319</v>
       </c>
       <c r="F127" s="12">
         <v>6</v>
       </c>
-      <c r="G127" s="32"/>
+      <c r="G127" s="41"/>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A128" s="12"/>
@@ -3413,14 +3413,14 @@
       <c r="C128" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="D128" s="41"/>
+      <c r="D128" s="32"/>
       <c r="E128" s="12" t="s">
         <v>319</v>
       </c>
       <c r="F128" s="12">
         <v>6</v>
       </c>
-      <c r="G128" s="32"/>
+      <c r="G128" s="41"/>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A129" s="12"/>
@@ -3428,27 +3428,27 @@
       <c r="C129" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="D129" s="41"/>
+      <c r="D129" s="32"/>
       <c r="E129" s="12" t="s">
         <v>319</v>
       </c>
       <c r="F129" s="12">
         <v>6</v>
       </c>
-      <c r="G129" s="32"/>
+      <c r="G129" s="41"/>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A130" s="12"/>
       <c r="B130" s="12"/>
       <c r="C130" s="12"/>
-      <c r="D130" s="42" t="s">
+      <c r="D130" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E130" s="28">
         <v>1</v>
       </c>
       <c r="F130" s="12"/>
-      <c r="G130" s="32"/>
+      <c r="G130" s="41"/>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.3">
       <c r="E131">
@@ -3459,7 +3459,7 @@
         <f>SUM(F124:F129)</f>
         <v>36</v>
       </c>
-      <c r="G131" s="32"/>
+      <c r="G131" s="41"/>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A132" s="11" t="s">
@@ -3471,14 +3471,14 @@
       <c r="C132" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="D132" s="41"/>
+      <c r="D132" s="32"/>
       <c r="E132" s="12" t="s">
         <v>319</v>
       </c>
       <c r="F132" s="12">
         <v>10</v>
       </c>
-      <c r="G132" s="32"/>
+      <c r="G132" s="41"/>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A133" s="12"/>
@@ -3486,7 +3486,7 @@
       <c r="C133" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="D133" s="41" t="s">
+      <c r="D133" s="32" t="s">
         <v>117</v>
       </c>
       <c r="E133" s="12" t="s">
@@ -3495,13 +3495,13 @@
       <c r="F133" s="12">
         <v>5</v>
       </c>
-      <c r="G133" s="32"/>
+      <c r="G133" s="41"/>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A134" s="12"/>
       <c r="B134" s="12"/>
       <c r="C134" s="12"/>
-      <c r="D134" s="41" t="s">
+      <c r="D134" s="32" t="s">
         <v>118</v>
       </c>
       <c r="E134" s="12" t="s">
@@ -3510,13 +3510,13 @@
       <c r="F134" s="12">
         <v>5</v>
       </c>
-      <c r="G134" s="32"/>
+      <c r="G134" s="41"/>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A135" s="11"/>
       <c r="B135" s="12"/>
       <c r="C135" s="12"/>
-      <c r="D135" s="41" t="s">
+      <c r="D135" s="32" t="s">
         <v>103</v>
       </c>
       <c r="E135" s="12" t="s">
@@ -3525,13 +3525,13 @@
       <c r="F135" s="12">
         <v>5</v>
       </c>
-      <c r="G135" s="32"/>
+      <c r="G135" s="41"/>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A136" s="11"/>
       <c r="B136" s="12"/>
       <c r="C136" s="12"/>
-      <c r="D136" s="41" t="s">
+      <c r="D136" s="32" t="s">
         <v>13</v>
       </c>
       <c r="E136" s="12" t="s">
@@ -3540,7 +3540,7 @@
       <c r="F136" s="12">
         <v>5</v>
       </c>
-      <c r="G136" s="32"/>
+      <c r="G136" s="41"/>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A137" s="11"/>
@@ -3548,14 +3548,14 @@
       <c r="C137" s="12" t="s">
         <v>332</v>
       </c>
-      <c r="D137" s="41"/>
+      <c r="D137" s="32"/>
       <c r="E137" s="12" t="s">
         <v>319</v>
       </c>
       <c r="F137" s="12">
         <v>10</v>
       </c>
-      <c r="G137" s="32"/>
+      <c r="G137" s="41"/>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A138" s="12"/>
@@ -3563,14 +3563,14 @@
       <c r="C138" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="D138" s="41"/>
+      <c r="D138" s="32"/>
       <c r="E138" s="12" t="s">
         <v>319</v>
       </c>
       <c r="F138" s="12">
         <v>5</v>
       </c>
-      <c r="G138" s="32"/>
+      <c r="G138" s="41"/>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A139" s="12"/>
@@ -3578,27 +3578,27 @@
       <c r="C139" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="D139" s="41"/>
+      <c r="D139" s="32"/>
       <c r="E139" s="12" t="s">
         <v>319</v>
       </c>
       <c r="F139" s="12">
         <v>5</v>
       </c>
-      <c r="G139" s="32"/>
+      <c r="G139" s="41"/>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A140" s="12"/>
       <c r="B140" s="12"/>
       <c r="C140" s="12"/>
-      <c r="D140" s="42" t="s">
+      <c r="D140" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E140" s="28">
         <v>1</v>
       </c>
       <c r="F140" s="12"/>
-      <c r="G140" s="32"/>
+      <c r="G140" s="41"/>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.3">
       <c r="E141">
@@ -3609,7 +3609,7 @@
         <f>SUM(F132:F139)</f>
         <v>50</v>
       </c>
-      <c r="G141" s="32"/>
+      <c r="G141" s="41"/>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A142" s="11" t="s">
@@ -3621,14 +3621,14 @@
       <c r="C142" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="D142" s="41"/>
+      <c r="D142" s="32"/>
       <c r="E142" s="12" t="s">
         <v>319</v>
       </c>
       <c r="F142" s="12">
         <v>6</v>
       </c>
-      <c r="G142" s="32"/>
+      <c r="G142" s="41"/>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A143" s="11" t="s">
@@ -3638,12 +3638,12 @@
       <c r="C143" s="12" t="s">
         <v>336</v>
       </c>
-      <c r="D143" s="41"/>
+      <c r="D143" s="32"/>
       <c r="E143" s="12"/>
       <c r="F143" s="12">
         <v>6</v>
       </c>
-      <c r="G143" s="32"/>
+      <c r="G143" s="41"/>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A144" s="11"/>
@@ -3651,12 +3651,12 @@
       <c r="C144" s="12" t="s">
         <v>337</v>
       </c>
-      <c r="D144" s="41"/>
+      <c r="D144" s="32"/>
       <c r="E144" s="12"/>
       <c r="F144" s="12">
         <v>10</v>
       </c>
-      <c r="G144" s="32"/>
+      <c r="G144" s="41"/>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A145" s="11"/>
@@ -3664,7 +3664,7 @@
       <c r="C145" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="D145" s="41" t="s">
+      <c r="D145" s="32" t="s">
         <v>331</v>
       </c>
       <c r="E145" s="12" t="s">
@@ -3673,13 +3673,13 @@
       <c r="F145" s="12">
         <v>6</v>
       </c>
-      <c r="G145" s="32"/>
+      <c r="G145" s="41"/>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A146" s="12"/>
       <c r="B146" s="12"/>
       <c r="C146" s="12"/>
-      <c r="D146" s="41" t="s">
+      <c r="D146" s="32" t="s">
         <v>102</v>
       </c>
       <c r="E146" s="12" t="s">
@@ -3688,7 +3688,7 @@
       <c r="F146" s="12">
         <v>6</v>
       </c>
-      <c r="G146" s="32"/>
+      <c r="G146" s="41"/>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A147" s="12"/>
@@ -3696,14 +3696,14 @@
       <c r="C147" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="D147" s="41"/>
+      <c r="D147" s="32"/>
       <c r="E147" s="12" t="s">
         <v>319</v>
       </c>
       <c r="F147" s="12">
         <v>6</v>
       </c>
-      <c r="G147" s="32"/>
+      <c r="G147" s="41"/>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A148" s="12"/>
@@ -3711,14 +3711,14 @@
       <c r="C148" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="D148" s="41"/>
+      <c r="D148" s="32"/>
       <c r="E148" s="12" t="s">
         <v>319</v>
       </c>
       <c r="F148" s="12">
         <v>6</v>
       </c>
-      <c r="G148" s="32"/>
+      <c r="G148" s="41"/>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A149" s="12"/>
@@ -3726,27 +3726,27 @@
       <c r="C149" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="D149" s="41"/>
+      <c r="D149" s="32"/>
       <c r="E149" s="12" t="s">
         <v>319</v>
       </c>
       <c r="F149" s="12">
         <v>6</v>
       </c>
-      <c r="G149" s="32"/>
+      <c r="G149" s="41"/>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A150" s="12"/>
       <c r="B150" s="12"/>
       <c r="C150" s="12"/>
-      <c r="D150" s="42" t="s">
+      <c r="D150" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E150" s="28">
         <v>1</v>
       </c>
       <c r="F150" s="12"/>
-      <c r="G150" s="32"/>
+      <c r="G150" s="41"/>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.3">
       <c r="E151">
@@ -3757,7 +3757,7 @@
         <f>SUM(F142:F149)</f>
         <v>52</v>
       </c>
-      <c r="G151" s="32"/>
+      <c r="G151" s="41"/>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A152" s="11" t="s">
@@ -3769,14 +3769,14 @@
       <c r="C152" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="D152" s="41"/>
+      <c r="D152" s="32"/>
       <c r="E152" s="12" t="s">
         <v>319</v>
       </c>
       <c r="F152" s="12">
         <v>10</v>
       </c>
-      <c r="G152" s="32"/>
+      <c r="G152" s="41"/>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A153" s="12"/>
@@ -3784,7 +3784,7 @@
       <c r="C153" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="D153" s="41" t="s">
+      <c r="D153" s="32" t="s">
         <v>117</v>
       </c>
       <c r="E153" s="12" t="s">
@@ -3793,13 +3793,13 @@
       <c r="F153" s="12">
         <v>5</v>
       </c>
-      <c r="G153" s="32"/>
+      <c r="G153" s="41"/>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A154" s="12"/>
       <c r="B154" s="12"/>
       <c r="C154" s="12"/>
-      <c r="D154" s="41" t="s">
+      <c r="D154" s="32" t="s">
         <v>118</v>
       </c>
       <c r="E154" s="12" t="s">
@@ -3808,13 +3808,13 @@
       <c r="F154" s="12">
         <v>5</v>
       </c>
-      <c r="G154" s="32"/>
+      <c r="G154" s="41"/>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A155" s="11"/>
       <c r="B155" s="12"/>
       <c r="C155" s="12"/>
-      <c r="D155" s="41" t="s">
+      <c r="D155" s="32" t="s">
         <v>103</v>
       </c>
       <c r="E155" s="12" t="s">
@@ -3823,13 +3823,13 @@
       <c r="F155" s="12">
         <v>5</v>
       </c>
-      <c r="G155" s="32"/>
+      <c r="G155" s="41"/>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A156" s="11"/>
       <c r="B156" s="12"/>
       <c r="C156" s="12"/>
-      <c r="D156" s="41" t="s">
+      <c r="D156" s="32" t="s">
         <v>13</v>
       </c>
       <c r="E156" s="12" t="s">
@@ -3838,7 +3838,7 @@
       <c r="F156" s="12">
         <v>5</v>
       </c>
-      <c r="G156" s="32"/>
+      <c r="G156" s="41"/>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A157" s="11"/>
@@ -3846,12 +3846,12 @@
       <c r="C157" s="12" t="s">
         <v>337</v>
       </c>
-      <c r="D157" s="41"/>
+      <c r="D157" s="32"/>
       <c r="E157" s="12"/>
       <c r="F157" s="12">
         <v>10</v>
       </c>
-      <c r="G157" s="32"/>
+      <c r="G157" s="41"/>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A158" s="11"/>
@@ -3859,14 +3859,14 @@
       <c r="C158" s="12" t="s">
         <v>332</v>
       </c>
-      <c r="D158" s="41"/>
+      <c r="D158" s="32"/>
       <c r="E158" s="12" t="s">
         <v>319</v>
       </c>
       <c r="F158" s="12">
         <v>10</v>
       </c>
-      <c r="G158" s="32"/>
+      <c r="G158" s="41"/>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A159" s="12"/>
@@ -3874,14 +3874,14 @@
       <c r="C159" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="D159" s="41"/>
+      <c r="D159" s="32"/>
       <c r="E159" s="12" t="s">
         <v>319</v>
       </c>
       <c r="F159" s="12">
         <v>5</v>
       </c>
-      <c r="G159" s="32"/>
+      <c r="G159" s="41"/>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A160" s="12"/>
@@ -3889,27 +3889,27 @@
       <c r="C160" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="D160" s="41"/>
+      <c r="D160" s="32"/>
       <c r="E160" s="12" t="s">
         <v>319</v>
       </c>
       <c r="F160" s="12">
         <v>5</v>
       </c>
-      <c r="G160" s="32"/>
+      <c r="G160" s="41"/>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A161" s="12"/>
       <c r="B161" s="12"/>
       <c r="C161" s="12"/>
-      <c r="D161" s="42" t="s">
+      <c r="D161" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E161" s="28">
         <v>1</v>
       </c>
       <c r="F161" s="12"/>
-      <c r="G161" s="32"/>
+      <c r="G161" s="41"/>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.3">
       <c r="E162">
@@ -3920,7 +3920,7 @@
         <f>SUM(F152:F160)</f>
         <v>60</v>
       </c>
-      <c r="G162" s="32"/>
+      <c r="G162" s="41"/>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.3">
       <c r="G163" s="27"/>
@@ -3969,7 +3969,7 @@
       <c r="A167" s="16"/>
       <c r="B167" s="14"/>
       <c r="C167" s="14"/>
-      <c r="D167" s="42" t="s">
+      <c r="D167" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E167" s="28">
@@ -4056,7 +4056,7 @@
       <c r="A174" s="16"/>
       <c r="B174" s="14"/>
       <c r="C174" s="14"/>
-      <c r="D174" s="42" t="s">
+      <c r="D174" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E174" s="28">
@@ -4219,7 +4219,7 @@
       <c r="A186" s="14"/>
       <c r="B186" s="14"/>
       <c r="C186" s="14"/>
-      <c r="D186" s="42" t="s">
+      <c r="D186" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E186" s="28">
@@ -4371,7 +4371,7 @@
       <c r="A197" s="14"/>
       <c r="B197" s="14"/>
       <c r="C197" s="14"/>
-      <c r="D197" s="42" t="s">
+      <c r="D197" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E197" s="28">
@@ -4431,7 +4431,7 @@
       <c r="A202" s="16"/>
       <c r="B202" s="14"/>
       <c r="C202" s="14"/>
-      <c r="D202" s="42" t="s">
+      <c r="D202" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E202" s="28">
@@ -4457,7 +4457,7 @@
       <c r="A205" s="5" t="s">
         <v>378</v>
       </c>
-      <c r="D205" s="43"/>
+      <c r="D205" s="34"/>
     </row>
     <row r="206" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A206" s="1" t="s">
@@ -4469,7 +4469,7 @@
       <c r="C206" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="D206" s="41"/>
+      <c r="D206" s="32"/>
       <c r="E206" s="12"/>
       <c r="F206" s="12">
         <v>5</v>
@@ -4482,7 +4482,7 @@
       <c r="C207" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="D207" s="41"/>
+      <c r="D207" s="32"/>
       <c r="E207" s="12"/>
       <c r="F207" s="12">
         <v>5</v>
@@ -4494,7 +4494,7 @@
       <c r="C208" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="D208" s="41"/>
+      <c r="D208" s="32"/>
       <c r="E208" s="12"/>
       <c r="F208" s="12">
         <v>5</v>
@@ -4506,7 +4506,7 @@
       <c r="C209" s="12" t="s">
         <v>249</v>
       </c>
-      <c r="D209" s="41"/>
+      <c r="D209" s="32"/>
       <c r="E209" s="12"/>
       <c r="F209" s="12">
         <v>5</v>
@@ -4518,7 +4518,7 @@
       <c r="C210" s="12" t="s">
         <v>248</v>
       </c>
-      <c r="D210" s="41"/>
+      <c r="D210" s="32"/>
       <c r="E210" s="12"/>
       <c r="F210" s="12">
         <v>5</v>
@@ -4530,7 +4530,7 @@
       <c r="C211" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="D211" s="41"/>
+      <c r="D211" s="32"/>
       <c r="E211" s="12"/>
       <c r="F211" s="12">
         <v>5</v>
@@ -4542,7 +4542,7 @@
       <c r="C212" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="D212" s="41"/>
+      <c r="D212" s="32"/>
       <c r="E212" s="12"/>
       <c r="F212" s="12">
         <v>5</v>
@@ -4554,7 +4554,7 @@
       <c r="C213" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="D213" s="41"/>
+      <c r="D213" s="32"/>
       <c r="E213" s="12"/>
       <c r="F213" s="12">
         <v>5</v>
@@ -4564,7 +4564,7 @@
       <c r="A214" s="1"/>
       <c r="B214" s="12"/>
       <c r="C214" s="12"/>
-      <c r="D214" s="42" t="s">
+      <c r="D214" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E214" s="28">
@@ -4591,7 +4591,7 @@
       <c r="C216" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="D216" s="40"/>
+      <c r="D216" s="31"/>
       <c r="E216" s="13"/>
       <c r="F216" s="13">
         <v>5</v>
@@ -4603,7 +4603,7 @@
       <c r="C217" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="D217" s="40"/>
+      <c r="D217" s="31"/>
       <c r="E217" s="13"/>
       <c r="F217" s="13">
         <v>5</v>
@@ -4615,7 +4615,7 @@
       <c r="C218" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="D218" s="40"/>
+      <c r="D218" s="31"/>
       <c r="E218" s="13"/>
       <c r="F218" s="13">
         <v>5</v>
@@ -4627,7 +4627,7 @@
       <c r="C219" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="D219" s="40"/>
+      <c r="D219" s="31"/>
       <c r="E219" s="13"/>
       <c r="F219" s="13">
         <v>5</v>
@@ -4639,7 +4639,7 @@
       <c r="C220" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="D220" s="40"/>
+      <c r="D220" s="31"/>
       <c r="E220" s="13"/>
       <c r="F220" s="13">
         <v>5</v>
@@ -4651,7 +4651,7 @@
       <c r="C221" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="D221" s="40"/>
+      <c r="D221" s="31"/>
       <c r="E221" s="13"/>
       <c r="F221" s="13">
         <v>5</v>
@@ -4663,7 +4663,7 @@
       <c r="C222" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="D222" s="40"/>
+      <c r="D222" s="31"/>
       <c r="E222" s="13"/>
       <c r="F222" s="13">
         <v>5</v>
@@ -4675,7 +4675,7 @@
       <c r="C223" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="D223" s="40"/>
+      <c r="D223" s="31"/>
       <c r="E223" s="13"/>
       <c r="F223" s="13">
         <v>5</v>
@@ -4685,7 +4685,7 @@
       <c r="A224" s="1"/>
       <c r="B224" s="13"/>
       <c r="C224" s="13"/>
-      <c r="D224" s="42" t="s">
+      <c r="D224" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E224" s="28">
@@ -4806,7 +4806,7 @@
       <c r="A234" s="1"/>
       <c r="B234" s="14"/>
       <c r="C234" s="14"/>
-      <c r="D234" s="42" t="s">
+      <c r="D234" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E234" s="28">
@@ -4835,7 +4835,7 @@
       <c r="C236" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="D236" s="40"/>
+      <c r="D236" s="31"/>
       <c r="E236" s="13"/>
       <c r="F236" s="13">
         <v>10</v>
@@ -4847,7 +4847,7 @@
       <c r="C237" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="D237" s="40"/>
+      <c r="D237" s="31"/>
       <c r="E237" s="13"/>
       <c r="F237" s="13">
         <v>10</v>
@@ -4859,7 +4859,7 @@
       <c r="C238" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="D238" s="40"/>
+      <c r="D238" s="31"/>
       <c r="E238" s="13"/>
       <c r="F238" s="13">
         <v>10</v>
@@ -4871,7 +4871,7 @@
       <c r="C239" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="D239" s="40"/>
+      <c r="D239" s="31"/>
       <c r="E239" s="13"/>
       <c r="F239" s="13">
         <v>10</v>
@@ -4883,7 +4883,7 @@
       <c r="C240" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D240" s="40"/>
+      <c r="D240" s="31"/>
       <c r="E240" s="13"/>
       <c r="F240" s="13">
         <v>20</v>
@@ -4895,7 +4895,7 @@
       <c r="C241" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="D241" s="40"/>
+      <c r="D241" s="31"/>
       <c r="E241" s="13"/>
       <c r="F241" s="13">
         <v>10</v>
@@ -4907,7 +4907,7 @@
       <c r="C242" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="D242" s="40"/>
+      <c r="D242" s="31"/>
       <c r="E242" s="13"/>
       <c r="F242" s="13">
         <v>10</v>
@@ -4919,7 +4919,7 @@
       <c r="C243" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D243" s="40"/>
+      <c r="D243" s="31"/>
       <c r="E243" s="13"/>
       <c r="F243" s="13">
         <v>30</v>
@@ -4931,7 +4931,7 @@
       <c r="C244" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="D244" s="40"/>
+      <c r="D244" s="31"/>
       <c r="E244" s="13"/>
       <c r="F244" s="13">
         <v>10</v>
@@ -4941,7 +4941,7 @@
       <c r="A245" s="13"/>
       <c r="B245" s="13"/>
       <c r="C245" s="13"/>
-      <c r="D245" s="42" t="s">
+      <c r="D245" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E245" s="28">
@@ -4953,7 +4953,7 @@
       <c r="A246" s="25"/>
       <c r="B246" s="25"/>
       <c r="C246" s="25"/>
-      <c r="D246" s="45"/>
+      <c r="D246" s="36"/>
       <c r="E246" s="26">
         <f>SUM(E236:E244)*E245</f>
         <v>0</v>
@@ -4967,7 +4967,7 @@
       <c r="A247" s="25"/>
       <c r="B247" s="25"/>
       <c r="C247" s="25"/>
-      <c r="D247" s="45"/>
+      <c r="D247" s="36"/>
       <c r="E247" s="25"/>
       <c r="F247" s="25"/>
     </row>
@@ -4984,7 +4984,7 @@
         <v>205</v>
       </c>
       <c r="C249" s="12"/>
-      <c r="D249" s="41"/>
+      <c r="D249" s="32"/>
       <c r="E249" s="12"/>
       <c r="F249" s="12">
         <v>5</v>
@@ -4998,7 +4998,7 @@
         <v>65</v>
       </c>
       <c r="C250" s="12"/>
-      <c r="D250" s="41"/>
+      <c r="D250" s="32"/>
       <c r="E250" s="12"/>
       <c r="F250" s="12">
         <v>10</v>
@@ -5010,7 +5010,7 @@
         <v>50</v>
       </c>
       <c r="C251" s="12"/>
-      <c r="D251" s="41"/>
+      <c r="D251" s="32"/>
       <c r="E251" s="12"/>
       <c r="F251" s="12">
         <v>10</v>
@@ -5022,7 +5022,7 @@
         <v>207</v>
       </c>
       <c r="C252" s="12"/>
-      <c r="D252" s="41"/>
+      <c r="D252" s="32"/>
       <c r="E252" s="12"/>
       <c r="F252" s="12">
         <v>5</v>
@@ -5034,7 +5034,7 @@
         <v>51</v>
       </c>
       <c r="C253" s="12"/>
-      <c r="D253" s="41"/>
+      <c r="D253" s="32"/>
       <c r="E253" s="12"/>
       <c r="F253" s="12">
         <v>5</v>
@@ -5046,7 +5046,7 @@
         <v>234</v>
       </c>
       <c r="C254" s="12"/>
-      <c r="D254" s="41"/>
+      <c r="D254" s="32"/>
       <c r="E254" s="12"/>
       <c r="F254" s="12">
         <v>5</v>
@@ -5056,7 +5056,7 @@
       <c r="A255" s="11"/>
       <c r="B255" s="12"/>
       <c r="C255" s="12"/>
-      <c r="D255" s="42" t="s">
+      <c r="D255" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E255" s="28">
@@ -5083,12 +5083,12 @@
       <c r="C257" s="12" t="s">
         <v>205</v>
       </c>
-      <c r="D257" s="41"/>
+      <c r="D257" s="32"/>
       <c r="E257" s="12"/>
       <c r="F257" s="12">
         <v>5</v>
       </c>
-      <c r="G257" s="33" t="s">
+      <c r="G257" s="42" t="s">
         <v>109</v>
       </c>
     </row>
@@ -5100,12 +5100,12 @@
       <c r="C258" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="D258" s="41"/>
+      <c r="D258" s="32"/>
       <c r="E258" s="12"/>
       <c r="F258" s="12">
         <v>10</v>
       </c>
-      <c r="G258" s="33"/>
+      <c r="G258" s="42"/>
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A259" s="11" t="s">
@@ -5115,12 +5115,12 @@
       <c r="C259" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="D259" s="41"/>
+      <c r="D259" s="32"/>
       <c r="E259" s="12"/>
       <c r="F259" s="12">
         <v>10</v>
       </c>
-      <c r="G259" s="33"/>
+      <c r="G259" s="42"/>
     </row>
     <row r="260" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A260" s="11"/>
@@ -5128,12 +5128,12 @@
       <c r="C260" s="12" t="s">
         <v>207</v>
       </c>
-      <c r="D260" s="41"/>
+      <c r="D260" s="32"/>
       <c r="E260" s="12"/>
       <c r="F260" s="12">
         <v>5</v>
       </c>
-      <c r="G260" s="33"/>
+      <c r="G260" s="42"/>
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A261" s="11"/>
@@ -5141,12 +5141,12 @@
       <c r="C261" s="12" t="s">
         <v>329</v>
       </c>
-      <c r="D261" s="41"/>
+      <c r="D261" s="32"/>
       <c r="E261" s="12"/>
       <c r="F261" s="12">
         <v>5</v>
       </c>
-      <c r="G261" s="33"/>
+      <c r="G261" s="42"/>
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A262" s="11"/>
@@ -5154,25 +5154,25 @@
       <c r="C262" s="12" t="s">
         <v>328</v>
       </c>
-      <c r="D262" s="41"/>
+      <c r="D262" s="32"/>
       <c r="E262" s="12"/>
       <c r="F262" s="12">
         <v>5</v>
       </c>
-      <c r="G262" s="33"/>
+      <c r="G262" s="42"/>
     </row>
     <row r="263" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A263" s="11"/>
       <c r="B263" s="12"/>
       <c r="C263" s="12"/>
-      <c r="D263" s="42" t="s">
+      <c r="D263" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E263" s="28">
         <v>1</v>
       </c>
       <c r="F263" s="12"/>
-      <c r="G263" s="33"/>
+      <c r="G263" s="42"/>
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A264" s="1"/>
@@ -5198,7 +5198,7 @@
       <c r="C266" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="D266" s="44"/>
+      <c r="D266" s="35"/>
       <c r="E266" s="8"/>
       <c r="F266" s="8"/>
     </row>
@@ -5208,7 +5208,7 @@
       <c r="C267" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="D267" s="44"/>
+      <c r="D267" s="35"/>
       <c r="E267" s="8"/>
       <c r="F267" s="8">
         <v>5</v>
@@ -5220,7 +5220,7 @@
       <c r="C268" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="D268" s="44"/>
+      <c r="D268" s="35"/>
       <c r="E268" s="8"/>
       <c r="F268" s="8"/>
     </row>
@@ -5230,7 +5230,7 @@
       <c r="C269" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="D269" s="44"/>
+      <c r="D269" s="35"/>
       <c r="E269" s="8"/>
       <c r="F269" s="8"/>
     </row>
@@ -5240,7 +5240,7 @@
       <c r="C270" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="D270" s="44"/>
+      <c r="D270" s="35"/>
       <c r="E270" s="8"/>
       <c r="F270" s="8">
         <v>2</v>
@@ -5261,7 +5261,7 @@
       <c r="C273" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="D273" s="41" t="s">
+      <c r="D273" s="32" t="s">
         <v>39</v>
       </c>
       <c r="E273" s="12"/>
@@ -5273,7 +5273,7 @@
       <c r="A274" s="12"/>
       <c r="B274" s="12"/>
       <c r="C274" s="12"/>
-      <c r="D274" s="41" t="s">
+      <c r="D274" s="32" t="s">
         <v>101</v>
       </c>
       <c r="E274" s="12"/>
@@ -5285,7 +5285,7 @@
       <c r="A275" s="12"/>
       <c r="B275" s="12"/>
       <c r="C275" s="12"/>
-      <c r="D275" s="41" t="s">
+      <c r="D275" s="32" t="s">
         <v>286</v>
       </c>
       <c r="E275" s="12"/>
@@ -5297,7 +5297,7 @@
       <c r="A276" s="12"/>
       <c r="B276" s="12"/>
       <c r="C276" s="12"/>
-      <c r="D276" s="41" t="s">
+      <c r="D276" s="32" t="s">
         <v>102</v>
       </c>
       <c r="E276" s="12"/>
@@ -5309,7 +5309,7 @@
       <c r="A277" s="12"/>
       <c r="B277" s="12"/>
       <c r="C277" s="12"/>
-      <c r="D277" s="41" t="s">
+      <c r="D277" s="32" t="s">
         <v>288</v>
       </c>
       <c r="E277" s="12"/>
@@ -5321,7 +5321,7 @@
       <c r="A278" s="12"/>
       <c r="B278" s="12"/>
       <c r="C278" s="12"/>
-      <c r="D278" s="41" t="s">
+      <c r="D278" s="32" t="s">
         <v>287</v>
       </c>
       <c r="E278" s="12"/>
@@ -5335,7 +5335,7 @@
       <c r="C279" s="12" t="s">
         <v>289</v>
       </c>
-      <c r="D279" s="41" t="s">
+      <c r="D279" s="32" t="s">
         <v>290</v>
       </c>
       <c r="E279" s="12"/>
@@ -5347,7 +5347,7 @@
       <c r="A280" s="12"/>
       <c r="B280" s="12"/>
       <c r="C280" s="12"/>
-      <c r="D280" s="41" t="s">
+      <c r="D280" s="32" t="s">
         <v>291</v>
       </c>
       <c r="E280" s="12"/>
@@ -5359,7 +5359,7 @@
       <c r="A281" s="12"/>
       <c r="B281" s="12"/>
       <c r="C281" s="12"/>
-      <c r="D281" s="41" t="s">
+      <c r="D281" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E281" s="12"/>
@@ -5371,7 +5371,7 @@
       <c r="A282" s="12"/>
       <c r="B282" s="12"/>
       <c r="C282" s="12"/>
-      <c r="D282" s="41" t="s">
+      <c r="D282" s="32" t="s">
         <v>19</v>
       </c>
       <c r="E282" s="12"/>
@@ -5383,7 +5383,7 @@
       <c r="A283" s="12"/>
       <c r="B283" s="12"/>
       <c r="C283" s="12"/>
-      <c r="D283" s="41" t="s">
+      <c r="D283" s="32" t="s">
         <v>292</v>
       </c>
       <c r="E283" s="12"/>
@@ -5395,7 +5395,7 @@
       <c r="A284" s="12"/>
       <c r="B284" s="12"/>
       <c r="C284" s="12"/>
-      <c r="D284" s="42" t="s">
+      <c r="D284" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E284" s="28">
@@ -5421,7 +5421,7 @@
         <v>74</v>
       </c>
       <c r="C286" s="8"/>
-      <c r="D286" s="44"/>
+      <c r="D286" s="35"/>
       <c r="E286" s="8"/>
       <c r="F286" s="8">
         <v>5</v>
@@ -5435,7 +5435,7 @@
       <c r="C287" s="8" t="s">
         <v>294</v>
       </c>
-      <c r="D287" s="44"/>
+      <c r="D287" s="35"/>
       <c r="E287" s="8"/>
       <c r="F287" s="8">
         <v>5</v>
@@ -5447,7 +5447,7 @@
       <c r="C288" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D288" s="44"/>
+      <c r="D288" s="35"/>
       <c r="E288" s="8"/>
       <c r="F288" s="8">
         <v>5</v>
@@ -5459,7 +5459,7 @@
       <c r="C289" s="8" t="s">
         <v>295</v>
       </c>
-      <c r="D289" s="44"/>
+      <c r="D289" s="35"/>
       <c r="E289" s="8"/>
       <c r="F289" s="8">
         <v>5</v>
@@ -5471,7 +5471,7 @@
       <c r="C290" s="8" t="s">
         <v>296</v>
       </c>
-      <c r="D290" s="44"/>
+      <c r="D290" s="35"/>
       <c r="E290" s="8"/>
       <c r="F290" s="8">
         <v>5</v>
@@ -5483,7 +5483,7 @@
       <c r="C291" s="8" t="s">
         <v>297</v>
       </c>
-      <c r="D291" s="44"/>
+      <c r="D291" s="35"/>
       <c r="E291" s="8"/>
       <c r="F291" s="8">
         <v>5</v>
@@ -5495,7 +5495,7 @@
       <c r="C292" s="8" t="s">
         <v>298</v>
       </c>
-      <c r="D292" s="44"/>
+      <c r="D292" s="35"/>
       <c r="E292" s="8"/>
       <c r="F292" s="8">
         <v>5</v>
@@ -5505,7 +5505,7 @@
       <c r="A293" s="8"/>
       <c r="B293" s="8"/>
       <c r="C293" s="8"/>
-      <c r="D293" s="42" t="s">
+      <c r="D293" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E293" s="28">
@@ -5531,7 +5531,7 @@
         <v>300</v>
       </c>
       <c r="C296" s="8"/>
-      <c r="D296" s="44"/>
+      <c r="D296" s="35"/>
       <c r="E296" s="8"/>
       <c r="F296" s="8">
         <v>5</v>
@@ -5545,7 +5545,7 @@
         <v>302</v>
       </c>
       <c r="C297" s="8"/>
-      <c r="D297" s="44"/>
+      <c r="D297" s="35"/>
       <c r="E297" s="8"/>
       <c r="F297" s="8">
         <v>5</v>
@@ -5557,7 +5557,7 @@
         <v>303</v>
       </c>
       <c r="C298" s="8"/>
-      <c r="D298" s="44"/>
+      <c r="D298" s="35"/>
       <c r="E298" s="8"/>
       <c r="F298" s="8">
         <v>5</v>
@@ -5569,7 +5569,7 @@
         <v>304</v>
       </c>
       <c r="C299" s="8"/>
-      <c r="D299" s="44"/>
+      <c r="D299" s="35"/>
       <c r="E299" s="8"/>
       <c r="F299" s="8">
         <v>5</v>
@@ -5579,7 +5579,7 @@
       <c r="A300" s="8"/>
       <c r="B300" s="8"/>
       <c r="C300" s="8"/>
-      <c r="D300" s="42" t="s">
+      <c r="D300" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E300" s="28">
@@ -5705,7 +5705,7 @@
       <c r="A311" s="14"/>
       <c r="B311" s="14"/>
       <c r="C311" s="14"/>
-      <c r="D311" s="42" t="s">
+      <c r="D311" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E311" s="28">
@@ -5731,7 +5731,7 @@
         <v>311</v>
       </c>
       <c r="C313" s="12"/>
-      <c r="D313" s="41"/>
+      <c r="D313" s="32"/>
       <c r="E313" s="12"/>
       <c r="F313" s="12">
         <v>5</v>
@@ -5743,7 +5743,7 @@
         <v>251</v>
       </c>
       <c r="C314" s="12"/>
-      <c r="D314" s="41"/>
+      <c r="D314" s="32"/>
       <c r="E314" s="12"/>
       <c r="F314" s="12">
         <v>10</v>
@@ -5755,7 +5755,7 @@
         <v>320</v>
       </c>
       <c r="C315" s="12"/>
-      <c r="D315" s="41"/>
+      <c r="D315" s="32"/>
       <c r="E315" s="12" t="s">
         <v>319</v>
       </c>
@@ -5769,7 +5769,7 @@
         <v>312</v>
       </c>
       <c r="C316" s="12"/>
-      <c r="D316" s="41"/>
+      <c r="D316" s="32"/>
       <c r="E316" s="12" t="s">
         <v>319</v>
       </c>
@@ -5783,7 +5783,7 @@
         <v>230</v>
       </c>
       <c r="C317" s="12"/>
-      <c r="D317" s="41"/>
+      <c r="D317" s="32"/>
       <c r="E317" s="12" t="s">
         <v>319</v>
       </c>
@@ -5797,7 +5797,7 @@
         <v>321</v>
       </c>
       <c r="C318" s="12"/>
-      <c r="D318" s="41"/>
+      <c r="D318" s="32"/>
       <c r="E318" s="12" t="s">
         <v>319</v>
       </c>
@@ -5811,7 +5811,7 @@
         <v>322</v>
       </c>
       <c r="C319" s="12"/>
-      <c r="D319" s="41"/>
+      <c r="D319" s="32"/>
       <c r="E319" s="12"/>
       <c r="F319" s="12">
         <v>5</v>
@@ -5823,7 +5823,7 @@
         <v>313</v>
       </c>
       <c r="C320" s="12"/>
-      <c r="D320" s="41"/>
+      <c r="D320" s="32"/>
       <c r="E320" s="12"/>
       <c r="F320" s="12">
         <v>5</v>
@@ -5835,7 +5835,7 @@
         <v>314</v>
       </c>
       <c r="C321" s="12"/>
-      <c r="D321" s="41"/>
+      <c r="D321" s="32"/>
       <c r="E321" s="12"/>
       <c r="F321" s="12">
         <v>5</v>
@@ -5847,7 +5847,7 @@
         <v>40</v>
       </c>
       <c r="C322" s="12"/>
-      <c r="D322" s="41"/>
+      <c r="D322" s="32"/>
       <c r="E322" s="12"/>
       <c r="F322" s="12">
         <v>10</v>
@@ -5857,7 +5857,7 @@
       <c r="A323" s="12"/>
       <c r="B323" s="12"/>
       <c r="C323" s="12"/>
-      <c r="D323" s="42" t="s">
+      <c r="D323" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E323" s="28">
@@ -5883,7 +5883,7 @@
         <v>190</v>
       </c>
       <c r="C326" s="8"/>
-      <c r="D326" s="44"/>
+      <c r="D326" s="35"/>
       <c r="E326" s="8"/>
       <c r="F326" s="8">
         <v>25</v>
@@ -5895,7 +5895,7 @@
         <v>191</v>
       </c>
       <c r="C327" s="8"/>
-      <c r="D327" s="44"/>
+      <c r="D327" s="35"/>
       <c r="E327" s="8"/>
       <c r="F327" s="8">
         <v>25</v>
@@ -5909,7 +5909,7 @@
       <c r="C328" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="D328" s="44"/>
+      <c r="D328" s="35"/>
       <c r="E328" s="8"/>
       <c r="F328" s="8">
         <v>10</v>
@@ -5921,7 +5921,7 @@
       <c r="C329" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="D329" s="44"/>
+      <c r="D329" s="35"/>
       <c r="E329" s="8"/>
       <c r="F329" s="8">
         <v>10</v>
@@ -5933,7 +5933,7 @@
       <c r="C330" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="D330" s="44"/>
+      <c r="D330" s="35"/>
       <c r="E330" s="8"/>
       <c r="F330" s="8">
         <v>10</v>
@@ -5945,7 +5945,7 @@
       <c r="C331" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="D331" s="44"/>
+      <c r="D331" s="35"/>
       <c r="E331" s="8"/>
       <c r="F331" s="8">
         <v>10</v>
@@ -5957,7 +5957,7 @@
       <c r="C332" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D332" s="44"/>
+      <c r="D332" s="35"/>
       <c r="E332" s="8"/>
       <c r="F332" s="8">
         <v>10</v>
@@ -5967,7 +5967,7 @@
       <c r="A333" s="7"/>
       <c r="B333" s="8"/>
       <c r="C333" s="8"/>
-      <c r="D333" s="42" t="s">
+      <c r="D333" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E333" s="28">
@@ -5994,7 +5994,7 @@
         <v>13</v>
       </c>
       <c r="C335" s="8"/>
-      <c r="D335" s="44"/>
+      <c r="D335" s="35"/>
       <c r="E335" s="8"/>
       <c r="F335" s="8">
         <v>10</v>
@@ -6006,7 +6006,7 @@
         <v>46</v>
       </c>
       <c r="C336" s="8"/>
-      <c r="D336" s="44"/>
+      <c r="D336" s="35"/>
       <c r="E336" s="8"/>
       <c r="F336" s="8">
         <v>5</v>
@@ -6018,7 +6018,7 @@
         <v>358</v>
       </c>
       <c r="C337" s="8"/>
-      <c r="D337" s="44"/>
+      <c r="D337" s="35"/>
       <c r="E337" s="8"/>
       <c r="F337" s="8">
         <v>15</v>
@@ -6030,7 +6030,7 @@
         <v>169</v>
       </c>
       <c r="C338" s="8"/>
-      <c r="D338" s="44"/>
+      <c r="D338" s="35"/>
       <c r="E338" s="8"/>
       <c r="F338" s="8">
         <v>5</v>
@@ -6042,7 +6042,7 @@
         <v>77</v>
       </c>
       <c r="C339" s="8"/>
-      <c r="D339" s="44"/>
+      <c r="D339" s="35"/>
       <c r="E339" s="8"/>
       <c r="F339" s="8">
         <v>5</v>
@@ -6054,7 +6054,7 @@
         <v>79</v>
       </c>
       <c r="C340" s="8"/>
-      <c r="D340" s="44"/>
+      <c r="D340" s="35"/>
       <c r="E340" s="8"/>
       <c r="F340" s="8">
         <v>25</v>
@@ -6068,7 +6068,7 @@
       <c r="C341" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="D341" s="44"/>
+      <c r="D341" s="35"/>
       <c r="E341" s="8"/>
       <c r="F341" s="8">
         <v>5</v>
@@ -6080,7 +6080,7 @@
       <c r="C342" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="D342" s="44"/>
+      <c r="D342" s="35"/>
       <c r="E342" s="8"/>
       <c r="F342" s="8">
         <v>10</v>
@@ -6092,7 +6092,7 @@
       <c r="C343" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="D343" s="44"/>
+      <c r="D343" s="35"/>
       <c r="E343" s="8"/>
       <c r="F343" s="8">
         <v>25</v>
@@ -6104,7 +6104,7 @@
       <c r="C344" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D344" s="44"/>
+      <c r="D344" s="35"/>
       <c r="E344" s="8"/>
       <c r="F344" s="8">
         <v>20</v>
@@ -6116,7 +6116,7 @@
       <c r="C345" s="8" t="s">
         <v>231</v>
       </c>
-      <c r="D345" s="44"/>
+      <c r="D345" s="35"/>
       <c r="E345" s="8"/>
       <c r="F345" s="8">
         <v>20</v>
@@ -6128,7 +6128,7 @@
       <c r="C346" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="D346" s="44" t="s">
+      <c r="D346" s="35" t="s">
         <v>69</v>
       </c>
       <c r="E346" s="8"/>
@@ -6140,7 +6140,7 @@
       <c r="A347" s="7"/>
       <c r="B347" s="7"/>
       <c r="C347" s="8"/>
-      <c r="D347" s="44" t="s">
+      <c r="D347" s="35" t="s">
         <v>70</v>
       </c>
       <c r="E347" s="8"/>
@@ -6152,7 +6152,7 @@
       <c r="A348" s="7"/>
       <c r="B348" s="7"/>
       <c r="C348" s="8"/>
-      <c r="D348" s="44" t="s">
+      <c r="D348" s="35" t="s">
         <v>71</v>
       </c>
       <c r="E348" s="8"/>
@@ -6164,7 +6164,7 @@
       <c r="A349" s="7"/>
       <c r="B349" s="7"/>
       <c r="C349" s="8"/>
-      <c r="D349" s="44" t="s">
+      <c r="D349" s="35" t="s">
         <v>54</v>
       </c>
       <c r="E349" s="8"/>
@@ -6176,7 +6176,7 @@
       <c r="A350" s="7"/>
       <c r="B350" s="7"/>
       <c r="C350" s="8"/>
-      <c r="D350" s="44" t="s">
+      <c r="D350" s="35" t="s">
         <v>72</v>
       </c>
       <c r="E350" s="8"/>
@@ -6188,7 +6188,7 @@
       <c r="A351" s="7"/>
       <c r="B351" s="7"/>
       <c r="C351" s="8"/>
-      <c r="D351" s="42" t="s">
+      <c r="D351" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E351" s="28">
@@ -6219,7 +6219,7 @@
         <v>221</v>
       </c>
       <c r="C354" s="13"/>
-      <c r="D354" s="40"/>
+      <c r="D354" s="31"/>
       <c r="E354" s="13"/>
       <c r="F354" s="13">
         <v>10</v>
@@ -6233,7 +6233,7 @@
       <c r="C355" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="D355" s="40"/>
+      <c r="D355" s="31"/>
       <c r="E355" s="13"/>
       <c r="F355" s="13">
         <v>30</v>
@@ -6245,7 +6245,7 @@
       <c r="C356" s="13" t="s">
         <v>222</v>
       </c>
-      <c r="D356" s="40"/>
+      <c r="D356" s="31"/>
       <c r="E356" s="13"/>
       <c r="F356" s="13">
         <v>30</v>
@@ -6257,7 +6257,7 @@
       <c r="C357" s="13" t="s">
         <v>223</v>
       </c>
-      <c r="D357" s="40"/>
+      <c r="D357" s="31"/>
       <c r="E357" s="13"/>
       <c r="F357" s="13">
         <v>30</v>
@@ -6271,7 +6271,7 @@
       <c r="C358" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="D358" s="40"/>
+      <c r="D358" s="31"/>
       <c r="E358" s="13"/>
       <c r="F358" s="13">
         <v>30</v>
@@ -6283,7 +6283,7 @@
       <c r="C359" s="13" t="s">
         <v>222</v>
       </c>
-      <c r="D359" s="40"/>
+      <c r="D359" s="31"/>
       <c r="E359" s="13"/>
       <c r="F359" s="13">
         <v>30</v>
@@ -6295,7 +6295,7 @@
       <c r="C360" s="13" t="s">
         <v>223</v>
       </c>
-      <c r="D360" s="40"/>
+      <c r="D360" s="31"/>
       <c r="E360" s="13"/>
       <c r="F360" s="13">
         <v>30</v>
@@ -6305,7 +6305,7 @@
       <c r="A361" s="13"/>
       <c r="B361" s="13"/>
       <c r="C361" s="13"/>
-      <c r="D361" s="42" t="s">
+      <c r="D361" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E361" s="28">
@@ -6327,7 +6327,7 @@
       <c r="A363" s="5" t="s">
         <v>283</v>
       </c>
-      <c r="D363" s="46"/>
+      <c r="D363" s="37"/>
     </row>
     <row r="364" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A364" s="15" t="s">
@@ -6337,7 +6337,7 @@
       <c r="C364" s="13" t="s">
         <v>183</v>
       </c>
-      <c r="D364" s="40"/>
+      <c r="D364" s="31"/>
       <c r="E364" s="13">
         <v>0</v>
       </c>
@@ -6351,7 +6351,7 @@
       <c r="C365" s="13" t="s">
         <v>187</v>
       </c>
-      <c r="D365" s="40"/>
+      <c r="D365" s="31"/>
       <c r="E365" s="13">
         <v>0</v>
       </c>
@@ -6365,7 +6365,7 @@
       <c r="C366" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="D366" s="40"/>
+      <c r="D366" s="31"/>
       <c r="E366" s="13">
         <v>0</v>
       </c>
@@ -6379,7 +6379,7 @@
       <c r="C367" s="13" t="s">
         <v>188</v>
       </c>
-      <c r="D367" s="40"/>
+      <c r="D367" s="31"/>
       <c r="E367" s="13">
         <v>0</v>
       </c>
@@ -6393,7 +6393,7 @@
       <c r="C368" s="13" t="s">
         <v>189</v>
       </c>
-      <c r="D368" s="40"/>
+      <c r="D368" s="31"/>
       <c r="E368" s="13">
         <v>0</v>
       </c>
@@ -6407,7 +6407,7 @@
       <c r="C369" s="13" t="s">
         <v>190</v>
       </c>
-      <c r="D369" s="40"/>
+      <c r="D369" s="31"/>
       <c r="E369" s="13">
         <v>0</v>
       </c>
@@ -6419,7 +6419,7 @@
       <c r="A370" s="13"/>
       <c r="B370" s="13"/>
       <c r="C370" s="13"/>
-      <c r="D370" s="42" t="s">
+      <c r="D370" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E370" s="28">
@@ -6445,7 +6445,7 @@
         <v>356</v>
       </c>
       <c r="C372" s="17"/>
-      <c r="D372" s="40"/>
+      <c r="D372" s="31"/>
       <c r="E372" s="13"/>
       <c r="F372" s="13">
         <v>10</v>
@@ -6457,7 +6457,7 @@
         <v>77</v>
       </c>
       <c r="C373" s="17"/>
-      <c r="D373" s="40"/>
+      <c r="D373" s="31"/>
       <c r="E373" s="13"/>
       <c r="F373" s="13">
         <v>5</v>
@@ -6469,7 +6469,7 @@
         <v>124</v>
       </c>
       <c r="C374" s="17"/>
-      <c r="D374" s="40"/>
+      <c r="D374" s="31"/>
       <c r="E374" s="13"/>
       <c r="F374" s="13">
         <v>5</v>
@@ -6479,7 +6479,7 @@
       <c r="A375" s="15"/>
       <c r="B375" s="13"/>
       <c r="C375" s="13"/>
-      <c r="D375" s="40"/>
+      <c r="D375" s="31"/>
       <c r="E375" s="13"/>
       <c r="F375" s="13"/>
     </row>
@@ -6491,7 +6491,7 @@
         <v>77</v>
       </c>
       <c r="C376" s="13"/>
-      <c r="D376" s="40"/>
+      <c r="D376" s="31"/>
       <c r="E376" s="13"/>
       <c r="F376" s="13">
         <v>5</v>
@@ -6503,7 +6503,7 @@
         <v>123</v>
       </c>
       <c r="C377" s="13"/>
-      <c r="D377" s="40"/>
+      <c r="D377" s="31"/>
       <c r="E377" s="13"/>
       <c r="F377" s="13">
         <v>5</v>
@@ -6515,7 +6515,7 @@
         <v>124</v>
       </c>
       <c r="C378" s="13"/>
-      <c r="D378" s="40"/>
+      <c r="D378" s="31"/>
       <c r="E378" s="13"/>
       <c r="F378" s="13">
         <v>5</v>
@@ -6525,7 +6525,7 @@
       <c r="A379" s="15"/>
       <c r="B379" s="13"/>
       <c r="C379" s="13"/>
-      <c r="D379" s="40"/>
+      <c r="D379" s="31"/>
       <c r="E379" s="13"/>
       <c r="F379" s="13"/>
     </row>
@@ -6537,7 +6537,7 @@
         <v>77</v>
       </c>
       <c r="C380" s="13"/>
-      <c r="D380" s="40"/>
+      <c r="D380" s="31"/>
       <c r="E380" s="13"/>
       <c r="F380" s="13">
         <v>5</v>
@@ -6549,7 +6549,7 @@
         <v>123</v>
       </c>
       <c r="C381" s="13"/>
-      <c r="D381" s="40"/>
+      <c r="D381" s="31"/>
       <c r="E381" s="13"/>
       <c r="F381" s="13">
         <v>5</v>
@@ -6561,7 +6561,7 @@
         <v>124</v>
       </c>
       <c r="C382" s="13"/>
-      <c r="D382" s="40"/>
+      <c r="D382" s="31"/>
       <c r="E382" s="13"/>
       <c r="F382" s="13">
         <v>5</v>
@@ -6571,7 +6571,7 @@
       <c r="A383" s="15"/>
       <c r="B383" s="13"/>
       <c r="C383" s="13"/>
-      <c r="D383" s="42" t="s">
+      <c r="D383" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E383" s="28">
@@ -6624,7 +6624,7 @@
       <c r="A387" s="16"/>
       <c r="B387" s="14"/>
       <c r="C387" s="14"/>
-      <c r="D387" s="42" t="s">
+      <c r="D387" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E387" s="28">
@@ -6658,7 +6658,7 @@
         <v>105</v>
       </c>
       <c r="C392" s="12"/>
-      <c r="D392" s="41"/>
+      <c r="D392" s="32"/>
       <c r="E392" s="12"/>
       <c r="F392" s="12">
         <v>10</v>
@@ -6670,7 +6670,7 @@
         <v>106</v>
       </c>
       <c r="C393" s="12"/>
-      <c r="D393" s="41"/>
+      <c r="D393" s="32"/>
       <c r="E393" s="12"/>
       <c r="F393" s="12">
         <v>10</v>
@@ -6682,7 +6682,7 @@
         <v>107</v>
       </c>
       <c r="C394" s="12"/>
-      <c r="D394" s="41"/>
+      <c r="D394" s="32"/>
       <c r="E394" s="12"/>
       <c r="F394" s="12">
         <v>10</v>
@@ -6694,7 +6694,7 @@
         <v>108</v>
       </c>
       <c r="C395" s="12"/>
-      <c r="D395" s="41"/>
+      <c r="D395" s="32"/>
       <c r="E395" s="12"/>
       <c r="F395" s="12">
         <v>10</v>
@@ -6706,7 +6706,7 @@
       </c>
       <c r="B396" s="12"/>
       <c r="C396" s="12"/>
-      <c r="D396" s="41"/>
+      <c r="D396" s="32"/>
       <c r="E396" s="12"/>
       <c r="F396" s="12"/>
     </row>
@@ -6716,7 +6716,7 @@
         <v>142</v>
       </c>
       <c r="C397" s="12"/>
-      <c r="D397" s="41"/>
+      <c r="D397" s="32"/>
       <c r="E397" s="12"/>
       <c r="F397" s="12">
         <v>5</v>
@@ -6728,7 +6728,7 @@
         <v>143</v>
       </c>
       <c r="C398" s="12"/>
-      <c r="D398" s="41"/>
+      <c r="D398" s="32"/>
       <c r="E398" s="12"/>
       <c r="F398" s="12">
         <v>15</v>
@@ -6740,7 +6740,7 @@
         <v>144</v>
       </c>
       <c r="C399" s="12"/>
-      <c r="D399" s="41"/>
+      <c r="D399" s="32"/>
       <c r="E399" s="12"/>
       <c r="F399" s="12">
         <v>20</v>
@@ -6752,7 +6752,7 @@
         <v>145</v>
       </c>
       <c r="C400" s="12"/>
-      <c r="D400" s="41"/>
+      <c r="D400" s="32"/>
       <c r="E400" s="12"/>
       <c r="F400" s="12">
         <v>5</v>
@@ -6762,7 +6762,7 @@
       <c r="A401" s="12"/>
       <c r="B401" s="12"/>
       <c r="C401" s="12"/>
-      <c r="D401" s="41"/>
+      <c r="D401" s="32"/>
       <c r="E401" s="12"/>
       <c r="F401" s="12"/>
     </row>
@@ -6774,7 +6774,7 @@
         <v>147</v>
       </c>
       <c r="C402" s="12"/>
-      <c r="D402" s="41"/>
+      <c r="D402" s="32"/>
       <c r="E402" s="12"/>
       <c r="F402" s="12">
         <v>5</v>
@@ -6786,7 +6786,7 @@
         <v>148</v>
       </c>
       <c r="C403" s="12"/>
-      <c r="D403" s="41"/>
+      <c r="D403" s="32"/>
       <c r="E403" s="12"/>
       <c r="F403" s="12">
         <v>15</v>
@@ -6798,7 +6798,7 @@
         <v>149</v>
       </c>
       <c r="C404" s="12"/>
-      <c r="D404" s="41"/>
+      <c r="D404" s="32"/>
       <c r="E404" s="12"/>
       <c r="F404" s="12">
         <v>15</v>
@@ -6808,7 +6808,7 @@
       <c r="A405" s="12"/>
       <c r="B405" s="12"/>
       <c r="C405" s="12"/>
-      <c r="D405" s="42" t="s">
+      <c r="D405" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E405" s="28">
@@ -6841,7 +6841,7 @@
       <c r="C408" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="D408" s="44"/>
+      <c r="D408" s="35"/>
       <c r="E408" s="8"/>
       <c r="F408" s="8">
         <v>2</v>
@@ -6853,7 +6853,7 @@
       <c r="C409" s="8" t="s">
         <v>209</v>
       </c>
-      <c r="D409" s="44"/>
+      <c r="D409" s="35"/>
       <c r="E409" s="8"/>
       <c r="F409" s="8">
         <v>2</v>
@@ -6865,7 +6865,7 @@
       <c r="C410" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="D410" s="44"/>
+      <c r="D410" s="35"/>
       <c r="E410" s="8"/>
       <c r="F410" s="8">
         <v>2</v>
@@ -6877,7 +6877,7 @@
       <c r="C411" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="D411" s="44"/>
+      <c r="D411" s="35"/>
       <c r="E411" s="8"/>
       <c r="F411" s="8">
         <v>2</v>
@@ -6889,7 +6889,7 @@
       <c r="C412" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="D412" s="44"/>
+      <c r="D412" s="35"/>
       <c r="E412" s="8"/>
       <c r="F412" s="8">
         <v>2</v>
@@ -6901,7 +6901,7 @@
         <v>13</v>
       </c>
       <c r="C413" s="8"/>
-      <c r="D413" s="44"/>
+      <c r="D413" s="35"/>
       <c r="E413" s="8"/>
       <c r="F413" s="8">
         <v>5</v>
@@ -6913,7 +6913,7 @@
         <v>43</v>
       </c>
       <c r="C414" s="8"/>
-      <c r="D414" s="44"/>
+      <c r="D414" s="35"/>
       <c r="E414" s="8"/>
       <c r="F414" s="8">
         <v>5</v>
@@ -6925,7 +6925,7 @@
         <v>80</v>
       </c>
       <c r="C415" s="8"/>
-      <c r="D415" s="44"/>
+      <c r="D415" s="35"/>
       <c r="E415" s="8"/>
       <c r="F415" s="8">
         <v>5</v>
@@ -6937,7 +6937,7 @@
         <v>99</v>
       </c>
       <c r="C416" s="8"/>
-      <c r="D416" s="44"/>
+      <c r="D416" s="35"/>
       <c r="E416" s="8"/>
       <c r="F416" s="8">
         <v>5</v>
@@ -6947,7 +6947,7 @@
       <c r="A417" s="8"/>
       <c r="B417" s="8"/>
       <c r="C417" s="8"/>
-      <c r="D417" s="42" t="s">
+      <c r="D417" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E417" s="28">
@@ -7079,7 +7079,7 @@
       <c r="A428" s="14"/>
       <c r="B428" s="14"/>
       <c r="C428" s="14"/>
-      <c r="D428" s="42" t="s">
+      <c r="D428" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E428" s="28">
@@ -7105,7 +7105,7 @@
         <v>159</v>
       </c>
       <c r="C430" s="8"/>
-      <c r="D430" s="44"/>
+      <c r="D430" s="35"/>
       <c r="E430" s="8"/>
       <c r="F430" s="8">
         <v>3</v>
@@ -7117,7 +7117,7 @@
         <v>160</v>
       </c>
       <c r="C431" s="8"/>
-      <c r="D431" s="44"/>
+      <c r="D431" s="35"/>
       <c r="E431" s="8"/>
       <c r="F431" s="8">
         <v>5</v>
@@ -7129,7 +7129,7 @@
         <v>8</v>
       </c>
       <c r="C432" s="8"/>
-      <c r="D432" s="44"/>
+      <c r="D432" s="35"/>
       <c r="E432" s="8"/>
       <c r="F432" s="8">
         <v>3</v>
@@ -7141,7 +7141,7 @@
         <v>161</v>
       </c>
       <c r="C433" s="8"/>
-      <c r="D433" s="44"/>
+      <c r="D433" s="35"/>
       <c r="E433" s="8"/>
       <c r="F433" s="8">
         <v>3</v>
@@ -7153,7 +7153,7 @@
         <v>162</v>
       </c>
       <c r="C434" s="8"/>
-      <c r="D434" s="44"/>
+      <c r="D434" s="35"/>
       <c r="E434" s="8"/>
       <c r="F434" s="8">
         <v>3</v>
@@ -7165,7 +7165,7 @@
         <v>163</v>
       </c>
       <c r="C435" s="8"/>
-      <c r="D435" s="44"/>
+      <c r="D435" s="35"/>
       <c r="E435" s="8"/>
       <c r="F435" s="8">
         <v>3</v>
@@ -7177,7 +7177,7 @@
         <v>164</v>
       </c>
       <c r="C436" s="8"/>
-      <c r="D436" s="44"/>
+      <c r="D436" s="35"/>
       <c r="E436" s="8"/>
       <c r="F436" s="8">
         <v>3</v>
@@ -7187,7 +7187,7 @@
       <c r="A437" s="8"/>
       <c r="B437" s="8"/>
       <c r="C437" s="8"/>
-      <c r="D437" s="42" t="s">
+      <c r="D437" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E437" s="28">
@@ -7213,7 +7213,7 @@
       <c r="C439" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="D439" s="44" t="s">
+      <c r="D439" s="35" t="s">
         <v>173</v>
       </c>
       <c r="E439" s="8"/>
@@ -7221,11 +7221,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="440" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A440" s="7"/>
       <c r="B440" s="7"/>
       <c r="C440" s="8"/>
-      <c r="D440" s="44" t="s">
+      <c r="D440" s="35" t="s">
         <v>174</v>
       </c>
       <c r="E440" s="8"/>
@@ -7233,11 +7233,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="441" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A441" s="7"/>
       <c r="B441" s="7"/>
       <c r="C441" s="8"/>
-      <c r="D441" s="44" t="s">
+      <c r="D441" s="35" t="s">
         <v>175</v>
       </c>
       <c r="E441" s="8"/>
@@ -7251,7 +7251,7 @@
       <c r="C442" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="D442" s="44" t="s">
+      <c r="D442" s="35" t="s">
         <v>177</v>
       </c>
       <c r="E442" s="8"/>
@@ -7263,7 +7263,7 @@
       <c r="A443" s="7"/>
       <c r="B443" s="7"/>
       <c r="C443" s="8"/>
-      <c r="D443" s="44" t="s">
+      <c r="D443" s="35" t="s">
         <v>178</v>
       </c>
       <c r="E443" s="8"/>
@@ -7275,7 +7275,7 @@
       <c r="A444" s="7"/>
       <c r="B444" s="7"/>
       <c r="C444" s="8"/>
-      <c r="D444" s="44" t="s">
+      <c r="D444" s="35" t="s">
         <v>179</v>
       </c>
       <c r="E444" s="8"/>
@@ -7287,7 +7287,7 @@
       <c r="A445" s="7"/>
       <c r="B445" s="7"/>
       <c r="C445" s="8"/>
-      <c r="D445" s="44" t="s">
+      <c r="D445" s="35" t="s">
         <v>180</v>
       </c>
       <c r="E445" s="8"/>
@@ -7299,7 +7299,7 @@
       <c r="A446" s="7"/>
       <c r="B446" s="7"/>
       <c r="C446" s="8"/>
-      <c r="D446" s="44" t="s">
+      <c r="D446" s="35" t="s">
         <v>181</v>
       </c>
       <c r="E446" s="8"/>
@@ -7332,7 +7332,7 @@
       <c r="C449" s="8" t="s">
         <v>316</v>
       </c>
-      <c r="D449" s="44"/>
+      <c r="D449" s="35"/>
       <c r="E449" s="8"/>
       <c r="F449" s="8">
         <v>10</v>
@@ -7344,7 +7344,7 @@
       <c r="C450" s="8" t="s">
         <v>364</v>
       </c>
-      <c r="D450" s="44"/>
+      <c r="D450" s="35"/>
       <c r="E450" s="8"/>
       <c r="F450" s="8">
         <v>10</v>
@@ -7358,7 +7358,7 @@
       <c r="C451" s="8" t="s">
         <v>319</v>
       </c>
-      <c r="D451" s="44"/>
+      <c r="D451" s="35"/>
       <c r="E451" s="8"/>
       <c r="F451" s="8"/>
     </row>
@@ -7368,7 +7368,7 @@
       <c r="C452" s="8" t="s">
         <v>365</v>
       </c>
-      <c r="D452" s="44"/>
+      <c r="D452" s="35"/>
       <c r="E452" s="8"/>
       <c r="F452" s="8">
         <v>10</v>
@@ -7380,7 +7380,7 @@
       <c r="C453" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="D453" s="44"/>
+      <c r="D453" s="35"/>
       <c r="E453" s="8"/>
       <c r="F453" s="8">
         <v>10</v>
@@ -7392,7 +7392,7 @@
       <c r="C454" s="8" t="s">
         <v>366</v>
       </c>
-      <c r="D454" s="44"/>
+      <c r="D454" s="35"/>
       <c r="E454" s="8"/>
       <c r="F454" s="8">
         <v>10</v>
@@ -7404,7 +7404,7 @@
       <c r="C455" s="8" t="s">
         <v>367</v>
       </c>
-      <c r="D455" s="44"/>
+      <c r="D455" s="35"/>
       <c r="E455" s="8"/>
       <c r="F455" s="8">
         <v>10</v>
@@ -7414,7 +7414,7 @@
       <c r="A456" s="8"/>
       <c r="B456" s="8"/>
       <c r="C456" s="8"/>
-      <c r="D456" s="42" t="s">
+      <c r="D456" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E456" s="28">
@@ -7444,7 +7444,7 @@
         <v>370</v>
       </c>
       <c r="C459" s="12"/>
-      <c r="D459" s="41"/>
+      <c r="D459" s="32"/>
       <c r="E459" s="12"/>
       <c r="F459" s="12">
         <v>10</v>
@@ -7460,7 +7460,7 @@
       <c r="C460" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="D460" s="41"/>
+      <c r="D460" s="32"/>
       <c r="E460" s="12"/>
       <c r="F460" s="12">
         <v>20</v>
@@ -7472,7 +7472,7 @@
       <c r="C461" s="12" t="s">
         <v>373</v>
       </c>
-      <c r="D461" s="41"/>
+      <c r="D461" s="32"/>
       <c r="E461" s="12"/>
       <c r="F461" s="12">
         <v>20</v>
@@ -7482,7 +7482,7 @@
       <c r="A462" s="11"/>
       <c r="B462" s="12"/>
       <c r="C462" s="12"/>
-      <c r="D462" s="42" t="s">
+      <c r="D462" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E462" s="28">
@@ -7519,7 +7519,7 @@
       <c r="C466" s="13" t="s">
         <v>351</v>
       </c>
-      <c r="D466" s="40"/>
+      <c r="D466" s="31"/>
       <c r="E466" s="13"/>
       <c r="F466" s="13">
         <v>10</v>
@@ -7533,7 +7533,7 @@
         <v>7</v>
       </c>
       <c r="C467" s="13"/>
-      <c r="D467" s="40"/>
+      <c r="D467" s="31"/>
       <c r="E467" s="13"/>
       <c r="F467" s="13">
         <v>10</v>
@@ -7547,7 +7547,7 @@
         <v>349</v>
       </c>
       <c r="C468" s="13"/>
-      <c r="D468" s="40"/>
+      <c r="D468" s="31"/>
       <c r="E468" s="13"/>
       <c r="F468" s="13">
         <v>20</v>
@@ -7559,7 +7559,7 @@
         <v>350</v>
       </c>
       <c r="C469" s="13"/>
-      <c r="D469" s="40"/>
+      <c r="D469" s="31"/>
       <c r="E469" s="13"/>
       <c r="F469" s="13">
         <v>10</v>
@@ -7569,7 +7569,7 @@
       <c r="A470" s="13"/>
       <c r="B470" s="13"/>
       <c r="C470" s="13"/>
-      <c r="D470" s="42" t="s">
+      <c r="D470" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E470" s="28">
@@ -7633,7 +7633,7 @@
       <c r="A476" s="14"/>
       <c r="B476" s="14"/>
       <c r="C476" s="14"/>
-      <c r="D476" s="42" t="s">
+      <c r="D476" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E476" s="28">
@@ -7661,7 +7661,7 @@
       <c r="C478" s="12" t="s">
         <v>351</v>
       </c>
-      <c r="D478" s="41"/>
+      <c r="D478" s="32"/>
       <c r="E478" s="12"/>
       <c r="F478" s="12">
         <v>10</v>
@@ -7675,7 +7675,7 @@
         <v>352</v>
       </c>
       <c r="C479" s="12"/>
-      <c r="D479" s="41"/>
+      <c r="D479" s="32"/>
       <c r="E479" s="12"/>
       <c r="F479" s="12">
         <v>20</v>
@@ -7687,7 +7687,7 @@
         <v>354</v>
       </c>
       <c r="C480" s="12"/>
-      <c r="D480" s="41"/>
+      <c r="D480" s="32"/>
       <c r="E480" s="12"/>
       <c r="F480" s="12">
         <v>40</v>
@@ -7697,7 +7697,7 @@
       <c r="A481" s="12"/>
       <c r="B481" s="12"/>
       <c r="C481" s="12"/>
-      <c r="D481" s="42" t="s">
+      <c r="D481" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E481" s="28">
@@ -7860,7 +7860,7 @@
       <c r="A499" s="14"/>
       <c r="B499" s="14"/>
       <c r="C499" s="14"/>
-      <c r="D499" s="42" t="s">
+      <c r="D499" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E499" s="28">
@@ -7886,7 +7886,7 @@
         <v>266</v>
       </c>
       <c r="C502" s="12"/>
-      <c r="D502" s="41"/>
+      <c r="D502" s="32"/>
       <c r="E502" s="12"/>
       <c r="F502" s="12">
         <v>10</v>
@@ -7900,7 +7900,7 @@
         <v>120</v>
       </c>
       <c r="C503" s="12"/>
-      <c r="D503" s="41"/>
+      <c r="D503" s="32"/>
       <c r="E503" s="12"/>
       <c r="F503" s="12">
         <v>5</v>
@@ -7912,7 +7912,7 @@
         <v>268</v>
       </c>
       <c r="C504" s="12"/>
-      <c r="D504" s="41"/>
+      <c r="D504" s="32"/>
       <c r="E504" s="12"/>
       <c r="F504" s="12">
         <v>5</v>
@@ -7924,7 +7924,7 @@
         <v>267</v>
       </c>
       <c r="C505" s="12"/>
-      <c r="D505" s="41"/>
+      <c r="D505" s="32"/>
       <c r="E505" s="12"/>
       <c r="F505" s="12">
         <v>5</v>
@@ -7936,7 +7936,7 @@
         <v>269</v>
       </c>
       <c r="C506" s="12"/>
-      <c r="D506" s="41"/>
+      <c r="D506" s="32"/>
       <c r="E506" s="12"/>
       <c r="F506" s="12">
         <v>5</v>
@@ -7948,7 +7948,7 @@
         <v>271</v>
       </c>
       <c r="C507" s="12"/>
-      <c r="D507" s="41"/>
+      <c r="D507" s="32"/>
       <c r="E507" s="12"/>
       <c r="F507" s="12">
         <v>5</v>
@@ -7960,7 +7960,7 @@
         <v>272</v>
       </c>
       <c r="C508" s="12"/>
-      <c r="D508" s="41"/>
+      <c r="D508" s="32"/>
       <c r="E508" s="12"/>
       <c r="F508" s="12">
         <v>5</v>
@@ -7972,7 +7972,7 @@
         <v>26</v>
       </c>
       <c r="C509" s="12"/>
-      <c r="D509" s="41"/>
+      <c r="D509" s="32"/>
       <c r="E509" s="12"/>
       <c r="F509" s="12">
         <v>5</v>
@@ -7984,7 +7984,7 @@
         <v>27</v>
       </c>
       <c r="C510" s="12"/>
-      <c r="D510" s="41"/>
+      <c r="D510" s="32"/>
       <c r="E510" s="12"/>
       <c r="F510" s="12">
         <v>5</v>
@@ -7996,7 +7996,7 @@
         <v>273</v>
       </c>
       <c r="C511" s="12"/>
-      <c r="D511" s="41"/>
+      <c r="D511" s="32"/>
       <c r="E511" s="12"/>
       <c r="F511" s="12">
         <v>5</v>
@@ -8008,7 +8008,7 @@
         <v>274</v>
       </c>
       <c r="C512" s="12"/>
-      <c r="D512" s="41"/>
+      <c r="D512" s="32"/>
       <c r="E512" s="12"/>
       <c r="F512" s="12">
         <v>5</v>
@@ -8018,7 +8018,7 @@
       <c r="A513" s="12"/>
       <c r="B513" s="12"/>
       <c r="C513" s="12"/>
-      <c r="D513" s="42" t="s">
+      <c r="D513" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E513" s="28">
@@ -8044,7 +8044,7 @@
         <v>266</v>
       </c>
       <c r="C516" s="13"/>
-      <c r="D516" s="40"/>
+      <c r="D516" s="31"/>
       <c r="E516" s="13"/>
       <c r="F516" s="13">
         <v>10</v>
@@ -8058,7 +8058,7 @@
         <v>120</v>
       </c>
       <c r="C517" s="13"/>
-      <c r="D517" s="40"/>
+      <c r="D517" s="31"/>
       <c r="E517" s="13"/>
       <c r="F517" s="13">
         <v>5</v>
@@ -8070,7 +8070,7 @@
         <v>268</v>
       </c>
       <c r="C518" s="13"/>
-      <c r="D518" s="40"/>
+      <c r="D518" s="31"/>
       <c r="E518" s="13"/>
       <c r="F518" s="13">
         <v>5</v>
@@ -8082,7 +8082,7 @@
         <v>267</v>
       </c>
       <c r="C519" s="13"/>
-      <c r="D519" s="40"/>
+      <c r="D519" s="31"/>
       <c r="E519" s="13"/>
       <c r="F519" s="13">
         <v>5</v>
@@ -8094,7 +8094,7 @@
         <v>269</v>
       </c>
       <c r="C520" s="13"/>
-      <c r="D520" s="40"/>
+      <c r="D520" s="31"/>
       <c r="E520" s="13"/>
       <c r="F520" s="13">
         <v>5</v>
@@ -8106,7 +8106,7 @@
         <v>271</v>
       </c>
       <c r="C521" s="13"/>
-      <c r="D521" s="40"/>
+      <c r="D521" s="31"/>
       <c r="E521" s="13"/>
       <c r="F521" s="13">
         <v>5</v>
@@ -8118,7 +8118,7 @@
         <v>272</v>
       </c>
       <c r="C522" s="13"/>
-      <c r="D522" s="40"/>
+      <c r="D522" s="31"/>
       <c r="E522" s="13"/>
       <c r="F522" s="13">
         <v>5</v>
@@ -8130,7 +8130,7 @@
         <v>26</v>
       </c>
       <c r="C523" s="13"/>
-      <c r="D523" s="40"/>
+      <c r="D523" s="31"/>
       <c r="E523" s="13"/>
       <c r="F523" s="13">
         <v>5</v>
@@ -8142,7 +8142,7 @@
         <v>27</v>
       </c>
       <c r="C524" s="13"/>
-      <c r="D524" s="40"/>
+      <c r="D524" s="31"/>
       <c r="E524" s="13"/>
       <c r="F524" s="13">
         <v>5</v>
@@ -8154,7 +8154,7 @@
         <v>273</v>
       </c>
       <c r="C525" s="13"/>
-      <c r="D525" s="40"/>
+      <c r="D525" s="31"/>
       <c r="E525" s="13"/>
       <c r="F525" s="13">
         <v>5</v>
@@ -8166,7 +8166,7 @@
         <v>274</v>
       </c>
       <c r="C526" s="13"/>
-      <c r="D526" s="40"/>
+      <c r="D526" s="31"/>
       <c r="E526" s="13"/>
       <c r="F526" s="13">
         <v>5</v>
@@ -8176,7 +8176,7 @@
       <c r="A527" s="13"/>
       <c r="B527" s="13"/>
       <c r="C527" s="13"/>
-      <c r="D527" s="42" t="s">
+      <c r="D527" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E527" s="28">
@@ -8275,7 +8275,7 @@
       <c r="A536" s="14"/>
       <c r="B536" s="14"/>
       <c r="C536" s="14"/>
-      <c r="D536" s="42" t="s">
+      <c r="D536" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E536" s="28">
@@ -8299,7 +8299,7 @@
       </c>
       <c r="B539" s="12"/>
       <c r="C539" s="12"/>
-      <c r="D539" s="41"/>
+      <c r="D539" s="32"/>
       <c r="E539" s="12"/>
       <c r="F539" s="12">
         <v>30</v>
@@ -8309,7 +8309,7 @@
       <c r="A540" s="12"/>
       <c r="B540" s="12"/>
       <c r="C540" s="12"/>
-      <c r="D540" s="41"/>
+      <c r="D540" s="32"/>
       <c r="E540" s="12"/>
       <c r="F540" s="12">
         <v>30</v>
@@ -8319,7 +8319,7 @@
       <c r="A541" s="12"/>
       <c r="B541" s="12"/>
       <c r="C541" s="12"/>
-      <c r="D541" s="41"/>
+      <c r="D541" s="32"/>
       <c r="E541" s="12"/>
       <c r="F541" s="12">
         <v>30</v>
@@ -8329,7 +8329,7 @@
       <c r="A542" s="12"/>
       <c r="B542" s="12"/>
       <c r="C542" s="12"/>
-      <c r="D542" s="41"/>
+      <c r="D542" s="32"/>
       <c r="E542" s="12"/>
       <c r="F542" s="12">
         <v>30</v>
@@ -8339,7 +8339,7 @@
       <c r="A543" s="12"/>
       <c r="B543" s="12"/>
       <c r="C543" s="12"/>
-      <c r="D543" s="41"/>
+      <c r="D543" s="32"/>
       <c r="E543" s="12"/>
       <c r="F543" s="12">
         <v>30</v>
@@ -8349,7 +8349,7 @@
       <c r="A544" s="12"/>
       <c r="B544" s="12"/>
       <c r="C544" s="12"/>
-      <c r="D544" s="42" t="s">
+      <c r="D544" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E544" s="28">
@@ -8375,7 +8375,7 @@
         <v>414</v>
       </c>
       <c r="C547" s="13"/>
-      <c r="D547" s="40" t="s">
+      <c r="D547" s="31" t="s">
         <v>415</v>
       </c>
       <c r="E547" s="13"/>
@@ -8389,7 +8389,7 @@
         <v>416</v>
       </c>
       <c r="C548" s="13"/>
-      <c r="D548" s="40" t="s">
+      <c r="D548" s="31" t="s">
         <v>417</v>
       </c>
       <c r="E548" s="13"/>
@@ -8403,7 +8403,7 @@
         <v>419</v>
       </c>
       <c r="C549" s="13"/>
-      <c r="D549" s="40" t="s">
+      <c r="D549" s="31" t="s">
         <v>418</v>
       </c>
       <c r="E549" s="13"/>
@@ -8417,7 +8417,7 @@
         <v>420</v>
       </c>
       <c r="C550" s="13"/>
-      <c r="D550" s="40" t="s">
+      <c r="D550" s="31" t="s">
         <v>421</v>
       </c>
       <c r="E550" s="13"/>
@@ -8431,7 +8431,7 @@
         <v>422</v>
       </c>
       <c r="C551" s="13"/>
-      <c r="D551" s="40" t="s">
+      <c r="D551" s="31" t="s">
         <v>423</v>
       </c>
       <c r="E551" s="13"/>
@@ -8443,7 +8443,7 @@
       <c r="A552" s="13"/>
       <c r="B552" s="13"/>
       <c r="C552" s="13"/>
-      <c r="D552" s="42" t="s">
+      <c r="D552" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E552" s="28">
@@ -8548,7 +8548,7 @@
       </c>
     </row>
     <row r="564" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D564" s="38" t="s">
+      <c r="D564" s="29" t="s">
         <v>262</v>
       </c>
       <c r="G564" t="s">
@@ -8683,11 +8683,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="33.6" x14ac:dyDescent="0.65">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="38" t="s">
         <v>392</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -8695,11 +8695,11 @@
       </c>
     </row>
     <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="30" t="s">
+      <c r="A5" s="39" t="s">
         <v>393</v>
       </c>
-      <c r="B5" s="30"/>
-      <c r="C5" s="30"/>
+      <c r="B5" s="39"/>
+      <c r="C5" s="39"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
@@ -9515,7 +9515,7 @@
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A96" s="36" t="s">
+      <c r="A96" s="45" t="s">
         <v>62</v>
       </c>
       <c r="B96" s="11" t="s">
@@ -9531,7 +9531,7 @@
       <c r="H96" s="1"/>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A97" s="36"/>
+      <c r="A97" s="45"/>
       <c r="B97" s="12"/>
       <c r="C97" s="12" t="s">
         <v>65</v>
@@ -9542,7 +9542,7 @@
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A98" s="36"/>
+      <c r="A98" s="45"/>
       <c r="B98" s="12"/>
       <c r="C98" s="12" t="s">
         <v>53</v>
@@ -9553,7 +9553,7 @@
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A99" s="36"/>
+      <c r="A99" s="45"/>
       <c r="B99" s="12"/>
       <c r="C99" s="12" t="s">
         <v>249</v>
@@ -9564,7 +9564,7 @@
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A100" s="36"/>
+      <c r="A100" s="45"/>
       <c r="B100" s="12"/>
       <c r="C100" s="12" t="s">
         <v>248</v>
@@ -9575,7 +9575,7 @@
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A101" s="36"/>
+      <c r="A101" s="45"/>
       <c r="B101" s="12"/>
       <c r="C101" s="12" t="s">
         <v>67</v>
@@ -9586,7 +9586,7 @@
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A102" s="36"/>
+      <c r="A102" s="45"/>
       <c r="B102" s="12"/>
       <c r="C102" s="12" t="s">
         <v>68</v>
@@ -9597,7 +9597,7 @@
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A103" s="36"/>
+      <c r="A103" s="45"/>
       <c r="B103" s="12"/>
       <c r="C103" s="12" t="s">
         <v>97</v>
@@ -9608,7 +9608,7 @@
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A104" s="36"/>
+      <c r="A104" s="45"/>
       <c r="B104" s="12"/>
       <c r="C104" s="22" t="s">
         <v>236</v>
@@ -9620,7 +9620,7 @@
       <c r="E104" s="12"/>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A105" s="36"/>
+      <c r="A105" s="45"/>
       <c r="D105">
         <f>-SUM(D96:D104)</f>
         <v>0</v>
@@ -9631,7 +9631,7 @@
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A106" s="36"/>
+      <c r="A106" s="45"/>
       <c r="B106" s="15" t="s">
         <v>63</v>
       </c>
@@ -9644,7 +9644,7 @@
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A107" s="36"/>
+      <c r="A107" s="45"/>
       <c r="B107" s="13"/>
       <c r="C107" s="13" t="s">
         <v>65</v>
@@ -9655,7 +9655,7 @@
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A108" s="36"/>
+      <c r="A108" s="45"/>
       <c r="B108" s="13"/>
       <c r="C108" s="13" t="s">
         <v>53</v>
@@ -9666,7 +9666,7 @@
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A109" s="36"/>
+      <c r="A109" s="45"/>
       <c r="B109" s="13"/>
       <c r="C109" s="13" t="s">
         <v>66</v>
@@ -9677,7 +9677,7 @@
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A110" s="36"/>
+      <c r="A110" s="45"/>
       <c r="B110" s="13"/>
       <c r="C110" s="13" t="s">
         <v>52</v>
@@ -9688,7 +9688,7 @@
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A111" s="36"/>
+      <c r="A111" s="45"/>
       <c r="B111" s="13"/>
       <c r="C111" s="13" t="s">
         <v>67</v>
@@ -9699,7 +9699,7 @@
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A112" s="36"/>
+      <c r="A112" s="45"/>
       <c r="B112" s="13"/>
       <c r="C112" s="13" t="s">
         <v>68</v>
@@ -9710,7 +9710,7 @@
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A113" s="36"/>
+      <c r="A113" s="45"/>
       <c r="B113" s="13"/>
       <c r="C113" s="13" t="s">
         <v>97</v>
@@ -9721,7 +9721,7 @@
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A114" s="36"/>
+      <c r="A114" s="45"/>
       <c r="B114" s="13"/>
       <c r="C114" s="22" t="s">
         <v>236</v>
@@ -9733,7 +9733,7 @@
       <c r="E114" s="13"/>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A115" s="36"/>
+      <c r="A115" s="45"/>
       <c r="D115">
         <f>-SUM(D106:D114)</f>
         <v>0</v>
@@ -9744,7 +9744,7 @@
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A116" s="36"/>
+      <c r="A116" s="45"/>
       <c r="B116" s="16" t="s">
         <v>63</v>
       </c>
@@ -9757,7 +9757,7 @@
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A117" s="36"/>
+      <c r="A117" s="45"/>
       <c r="B117" s="14"/>
       <c r="C117" s="14" t="s">
         <v>65</v>
@@ -9768,7 +9768,7 @@
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A118" s="36"/>
+      <c r="A118" s="45"/>
       <c r="B118" s="14"/>
       <c r="C118" s="14" t="s">
         <v>53</v>
@@ -9779,7 +9779,7 @@
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A119" s="36"/>
+      <c r="A119" s="45"/>
       <c r="B119" s="14"/>
       <c r="C119" s="14" t="s">
         <v>66</v>
@@ -9790,7 +9790,7 @@
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A120" s="36"/>
+      <c r="A120" s="45"/>
       <c r="B120" s="14"/>
       <c r="C120" s="14" t="s">
         <v>52</v>
@@ -9801,7 +9801,7 @@
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A121" s="36"/>
+      <c r="A121" s="45"/>
       <c r="B121" s="14"/>
       <c r="C121" s="14" t="s">
         <v>67</v>
@@ -9812,7 +9812,7 @@
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A122" s="36"/>
+      <c r="A122" s="45"/>
       <c r="B122" s="14"/>
       <c r="C122" s="14" t="s">
         <v>68</v>
@@ -9823,7 +9823,7 @@
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A123" s="36"/>
+      <c r="A123" s="45"/>
       <c r="B123" s="14"/>
       <c r="C123" s="14" t="s">
         <v>97</v>
@@ -9834,7 +9834,7 @@
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A124" s="36"/>
+      <c r="A124" s="45"/>
       <c r="B124" s="14"/>
       <c r="C124" s="22" t="s">
         <v>236</v>
@@ -9846,7 +9846,7 @@
       <c r="E124" s="14"/>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A125" s="36"/>
+      <c r="A125" s="45"/>
       <c r="D125">
         <f>-SUM(D116:D124)</f>
         <v>0</v>
@@ -11044,12 +11044,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="46" t="s">
         <v>253</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>

--- a/ProjectManagement/EvaluationHWAndProject.xlsx
+++ b/ProjectManagement/EvaluationHWAndProject.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10125"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\gthub\ML26-03-Car-Licence-Plate-Identification-with-a-Jetson-Nano\ProjectManagement\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sid/Documents/GitHub/ML26-03-Car-Licence-Plate-Identification-with-a-Jetson-Nano/ProjectManagement/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39945EBF-606D-4BF5-A2DB-67107DFF197C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEC02876-4F2A-B74C-9F3B-C449DF6DD26A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="22600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Report" sheetId="2" r:id="rId1"/>
@@ -274,7 +274,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="906" uniqueCount="424">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="916" uniqueCount="434">
   <si>
     <t>Literature</t>
   </si>
@@ -1546,6 +1546,36 @@
   </si>
   <si>
     <t xml:space="preserve">Encouraged colleagues to create meaningful tikz diagrams outlining key processes. </t>
+  </si>
+  <si>
+    <t>Edge Impulse vs. Jetson Nano comparison</t>
+  </si>
+  <si>
+    <t>End-to-end workflow comparison (data, training, deployment, profiling, integration) with trade-offs and architecture sketch. (EdgeImpulseVSJetsonNano.tex)</t>
+  </si>
+  <si>
+    <t>TikZ hardware diagrams (Jetson Nano J1010)</t>
+  </si>
+  <si>
+    <t>Structured TikZ repository</t>
+  </si>
+  <si>
+    <t>Scalable and reusable folder structure for all TikZ diagrams, organized by domain and used consistently across the project. (report/tikz/**)</t>
+  </si>
+  <si>
+    <t>Monitoring &amp; ops playbook</t>
+  </si>
+  <si>
+    <t>Practical guide for edge monitoring covering metrics, runtime checks, hard-case logging, privacy, and robustness. (Monitoring.tex)</t>
+  </si>
+  <si>
+    <t>Reproducible Jetson dev setup</t>
+  </si>
+  <si>
+    <t>Documented JetPack/L4T + CUDA/TensorRT environment with constraints and sanity-check scripts for OS, Python, and camera. (DevEnvHardwareOsSystemTools.tex; DevEnvPython.tex; scripts)</t>
+  </si>
+  <si>
+    <t>Created TikZ diagrams of the Jetson Nano / J1010 board with clear layouts, connectors, and pin labeling. (JetsonNanoLabeledLayout.tikz; JetsonNanoOversight.tikz)</t>
   </si>
 </sst>
 </file>
@@ -1802,6 +1832,33 @@
       <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1828,33 +1885,6 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2137,45 +2167,45 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:M575"/>
-  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="39.21875" customWidth="1"/>
-    <col min="3" max="3" width="28.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="39.21875" style="38" customWidth="1"/>
-    <col min="5" max="5" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="39.1640625" customWidth="1"/>
+    <col min="3" max="3" width="28.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="50.6640625" style="29" customWidth="1"/>
+    <col min="5" max="5" width="13.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:6" ht="33.6" x14ac:dyDescent="0.65">
-      <c r="A2" s="29" t="s">
+    <row r="2" spans="1:6" ht="34" x14ac:dyDescent="0.4">
+      <c r="A2" s="38" t="s">
         <v>392</v>
       </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="30" t="s">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" s="39" t="s">
         <v>393</v>
       </c>
-      <c r="B6" s="30"/>
-      <c r="C6" s="30"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B6" s="39"/>
+      <c r="C6" s="39"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>84</v>
       </c>
@@ -2185,14 +2215,14 @@
       <c r="C10" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="D10" s="39" t="s">
+      <c r="D10" s="30" t="s">
         <v>87</v>
       </c>
       <c r="F10" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>397</v>
       </c>
@@ -2202,14 +2232,14 @@
       <c r="C11" s="3">
         <v>7026787</v>
       </c>
-      <c r="D11" s="38" t="s">
+      <c r="D11" s="29" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C12" s="3"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>88</v>
       </c>
@@ -2217,7 +2247,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>89</v>
       </c>
@@ -2225,7 +2255,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>90</v>
       </c>
@@ -2233,7 +2263,7 @@
         <v>45924</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>91</v>
       </c>
@@ -2241,7 +2271,7 @@
         <v>46051</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>92</v>
       </c>
@@ -2249,7 +2279,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>93</v>
       </c>
@@ -2257,12 +2287,12 @@
         <v>218</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="23.4" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:8" ht="24" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="18" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:8" ht="19" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
         <v>95</v>
       </c>
@@ -2270,13 +2300,13 @@
         <v>96</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="13"/>
       <c r="B28" s="13" t="s">
         <v>166</v>
       </c>
       <c r="C28" s="13"/>
-      <c r="D28" s="40"/>
+      <c r="D28" s="31"/>
       <c r="E28" s="13">
         <v>-25</v>
       </c>
@@ -2287,7 +2317,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="14"/>
       <c r="B29" s="14" t="s">
         <v>166</v>
@@ -2304,13 +2334,13 @@
         <v>390</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="12"/>
       <c r="B30" s="12" t="s">
         <v>166</v>
       </c>
       <c r="C30" s="12"/>
-      <c r="D30" s="41"/>
+      <c r="D30" s="32"/>
       <c r="E30" s="12">
         <v>-25</v>
       </c>
@@ -2321,13 +2351,13 @@
         <v>390</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="12"/>
       <c r="B31" s="12" t="s">
         <v>167</v>
       </c>
       <c r="C31" s="12"/>
-      <c r="D31" s="41"/>
+      <c r="D31" s="32"/>
       <c r="E31" s="12">
         <v>-25</v>
       </c>
@@ -2338,7 +2368,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="14"/>
       <c r="B32" s="14" t="s">
         <v>167</v>
@@ -2355,13 +2385,13 @@
         <v>391</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" s="13"/>
       <c r="B33" s="13" t="s">
         <v>167</v>
       </c>
       <c r="C33" s="13"/>
-      <c r="D33" s="40"/>
+      <c r="D33" s="31"/>
       <c r="E33" s="13">
         <v>-25</v>
       </c>
@@ -2372,102 +2402,102 @@
         <v>391</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="21" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:8" ht="21" x14ac:dyDescent="0.25">
       <c r="A35" s="23" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" s="15" t="s">
         <v>0</v>
       </c>
       <c r="B36" s="13"/>
       <c r="C36" s="13"/>
-      <c r="D36" s="40"/>
+      <c r="D36" s="31"/>
       <c r="E36" s="13"/>
       <c r="F36" s="13"/>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" s="15"/>
       <c r="B37" s="13" t="s">
         <v>3</v>
       </c>
       <c r="C37" s="13"/>
-      <c r="D37" s="40"/>
+      <c r="D37" s="31"/>
       <c r="E37" s="13"/>
       <c r="F37" s="13">
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" s="13"/>
       <c r="B38" s="13" t="s">
         <v>28</v>
       </c>
       <c r="C38" s="13"/>
-      <c r="D38" s="40"/>
+      <c r="D38" s="31"/>
       <c r="E38" s="13"/>
       <c r="F38" s="13">
         <v>10</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" s="13"/>
       <c r="B39" s="13" t="s">
         <v>4</v>
       </c>
       <c r="C39" s="13"/>
-      <c r="D39" s="40"/>
+      <c r="D39" s="31"/>
       <c r="E39" s="13"/>
       <c r="F39" s="13">
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" s="13"/>
       <c r="B40" s="13" t="s">
         <v>5</v>
       </c>
       <c r="C40" s="13"/>
-      <c r="D40" s="40"/>
+      <c r="D40" s="31"/>
       <c r="E40" s="13"/>
       <c r="F40" s="13">
         <v>10</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" s="13"/>
       <c r="B41" s="13" t="s">
         <v>6</v>
       </c>
       <c r="C41" s="13"/>
-      <c r="D41" s="40"/>
+      <c r="D41" s="31"/>
       <c r="E41" s="13"/>
       <c r="F41" s="13">
         <v>10</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" s="13"/>
       <c r="B42" s="13" t="s">
         <v>1</v>
       </c>
       <c r="C42" s="13"/>
-      <c r="D42" s="40"/>
+      <c r="D42" s="31"/>
       <c r="E42" s="13"/>
       <c r="F42" s="13">
         <v>10</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" s="15"/>
       <c r="B43" s="13"/>
       <c r="C43" s="13"/>
-      <c r="D43" s="40"/>
+      <c r="D43" s="31"/>
       <c r="E43" s="13"/>
       <c r="F43" s="13"/>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" s="15"/>
       <c r="B44" s="13" t="s">
         <v>2</v>
@@ -2475,89 +2505,89 @@
       <c r="C44" s="13" t="s">
         <v>257</v>
       </c>
-      <c r="D44" s="40"/>
+      <c r="D44" s="31"/>
       <c r="E44" s="13"/>
       <c r="F44" s="13">
         <v>4</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" s="13"/>
       <c r="B45" s="13"/>
       <c r="C45" s="13" t="s">
         <v>201</v>
       </c>
-      <c r="D45" s="40"/>
+      <c r="D45" s="31"/>
       <c r="E45" s="13"/>
       <c r="F45" s="13">
         <v>6</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" s="13"/>
       <c r="B46" s="13"/>
       <c r="C46" s="13" t="s">
         <v>202</v>
       </c>
-      <c r="D46" s="40"/>
+      <c r="D46" s="31"/>
       <c r="E46" s="13"/>
       <c r="F46" s="13">
         <v>10</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" s="13"/>
       <c r="B47" s="13"/>
       <c r="C47" s="13" t="s">
         <v>203</v>
       </c>
-      <c r="D47" s="40"/>
+      <c r="D47" s="31"/>
       <c r="E47" s="13"/>
       <c r="F47" s="13">
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" s="13"/>
       <c r="B48" s="13"/>
       <c r="C48" s="13" t="s">
         <v>256</v>
       </c>
-      <c r="D48" s="40"/>
+      <c r="D48" s="31"/>
       <c r="E48" s="13"/>
       <c r="F48" s="13">
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="13"/>
       <c r="B49" s="13"/>
       <c r="C49" s="13" t="s">
         <v>198</v>
       </c>
-      <c r="D49" s="40"/>
+      <c r="D49" s="31"/>
       <c r="E49" s="13"/>
       <c r="F49" s="13">
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="13"/>
       <c r="B50" s="13"/>
       <c r="C50" s="13" t="s">
         <v>199</v>
       </c>
-      <c r="D50" s="40"/>
+      <c r="D50" s="31"/>
       <c r="E50" s="13"/>
       <c r="F50" s="13">
         <v>5</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A51" s="13"/>
       <c r="B51" s="13"/>
       <c r="C51" s="13"/>
-      <c r="D51" s="42" t="s">
+      <c r="D51" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E51" s="28">
@@ -2565,7 +2595,7 @@
       </c>
       <c r="F51" s="13"/>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="E52">
         <f>SUM(E36:E50)*E51</f>
         <v>0</v>
@@ -2575,13 +2605,13 @@
         <v>100</v>
       </c>
     </row>
-    <row r="54" spans="1:7" s="5" customFormat="1" ht="21" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:7" s="5" customFormat="1" ht="21" x14ac:dyDescent="0.25">
       <c r="A54" s="23" t="s">
         <v>135</v>
       </c>
-      <c r="D54" s="43"/>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D54" s="34"/>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A55" s="16" t="s">
         <v>135</v>
       </c>
@@ -2594,11 +2624,11 @@
       <c r="F55" s="14">
         <v>10</v>
       </c>
-      <c r="G55" s="31" t="s">
+      <c r="G55" s="40" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A56" s="16"/>
       <c r="B56" s="14" t="s">
         <v>50</v>
@@ -2609,9 +2639,9 @@
       <c r="F56" s="14">
         <v>5</v>
       </c>
-      <c r="G56" s="31"/>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G56" s="40"/>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A57" s="16"/>
       <c r="B57" s="14" t="s">
         <v>233</v>
@@ -2622,9 +2652,9 @@
       <c r="F57" s="14">
         <v>5</v>
       </c>
-      <c r="G57" s="31"/>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G57" s="40"/>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A58" s="16"/>
       <c r="B58" s="14" t="s">
         <v>136</v>
@@ -2635,9 +2665,9 @@
       <c r="F58" s="14">
         <v>5</v>
       </c>
-      <c r="G58" s="31"/>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G58" s="40"/>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A59" s="16"/>
       <c r="B59" s="14" t="s">
         <v>137</v>
@@ -2648,9 +2678,9 @@
       <c r="F59" s="14">
         <v>10</v>
       </c>
-      <c r="G59" s="31"/>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G59" s="40"/>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A60" s="16"/>
       <c r="B60" s="14" t="s">
         <v>55</v>
@@ -2661,9 +2691,9 @@
       <c r="F60" s="14">
         <v>5</v>
       </c>
-      <c r="G60" s="31"/>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G60" s="40"/>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A61" s="16"/>
       <c r="B61" s="14" t="s">
         <v>54</v>
@@ -2674,9 +2704,9 @@
       <c r="F61" s="14">
         <v>10</v>
       </c>
-      <c r="G61" s="31"/>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G61" s="40"/>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A62" s="16"/>
       <c r="B62" s="14" t="s">
         <v>138</v>
@@ -2687,9 +2717,9 @@
       <c r="F62" s="14">
         <v>5</v>
       </c>
-      <c r="G62" s="31"/>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G62" s="40"/>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A63" s="16"/>
       <c r="B63" s="14" t="s">
         <v>139</v>
@@ -2700,9 +2730,9 @@
       <c r="F63" s="14">
         <v>5</v>
       </c>
-      <c r="G63" s="31"/>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G63" s="40"/>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A64" s="16"/>
       <c r="B64" s="14" t="s">
         <v>140</v>
@@ -2713,9 +2743,9 @@
       <c r="F64" s="14">
         <v>5</v>
       </c>
-      <c r="G64" s="31"/>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G64" s="40"/>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A65" s="16"/>
       <c r="B65" s="14" t="s">
         <v>323</v>
@@ -2726,9 +2756,9 @@
       <c r="F65" s="14">
         <v>5</v>
       </c>
-      <c r="G65" s="31"/>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G65" s="40"/>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A66" s="16"/>
       <c r="B66" s="14" t="s">
         <v>324</v>
@@ -2739,9 +2769,9 @@
       <c r="F66" s="14">
         <v>5</v>
       </c>
-      <c r="G66" s="31"/>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G66" s="40"/>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A67" s="16"/>
       <c r="B67" s="14" t="s">
         <v>141</v>
@@ -2752,22 +2782,22 @@
       <c r="F67" s="14">
         <v>5</v>
       </c>
-      <c r="G67" s="31"/>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G67" s="40"/>
+    </row>
+    <row r="68" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A68" s="16"/>
       <c r="B68" s="14"/>
       <c r="C68" s="14"/>
-      <c r="D68" s="42" t="s">
+      <c r="D68" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E68" s="28">
         <v>1</v>
       </c>
       <c r="F68" s="14"/>
-      <c r="G68" s="31"/>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G68" s="40"/>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A69" s="1"/>
       <c r="E69">
         <f>-SUM(E55:E67)*E68</f>
@@ -2778,13 +2808,13 @@
         <v>80</v>
       </c>
     </row>
-    <row r="70" spans="1:7" s="5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:7" s="5" customFormat="1" ht="19" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="s">
         <v>343</v>
       </c>
-      <c r="D70" s="43"/>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D70" s="34"/>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A71" s="16" t="s">
         <v>135</v>
       </c>
@@ -2797,11 +2827,11 @@
       <c r="F71" s="14">
         <v>10</v>
       </c>
-      <c r="G71" s="34" t="s">
+      <c r="G71" s="43" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A72" s="16"/>
       <c r="B72" s="14" t="s">
         <v>46</v>
@@ -2812,9 +2842,9 @@
       <c r="F72" s="14">
         <v>5</v>
       </c>
-      <c r="G72" s="34"/>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G72" s="43"/>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A73" s="16"/>
       <c r="B73" s="14" t="s">
         <v>344</v>
@@ -2825,9 +2855,9 @@
       <c r="F73" s="14">
         <v>5</v>
       </c>
-      <c r="G73" s="34"/>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G73" s="43"/>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A74" s="16"/>
       <c r="B74" s="14" t="s">
         <v>70</v>
@@ -2838,9 +2868,9 @@
       <c r="F74" s="14">
         <v>5</v>
       </c>
-      <c r="G74" s="34"/>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G74" s="43"/>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A75" s="16"/>
       <c r="B75" s="14" t="s">
         <v>345</v>
@@ -2851,9 +2881,9 @@
       <c r="F75" s="14">
         <v>10</v>
       </c>
-      <c r="G75" s="34"/>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G75" s="43"/>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A76" s="16"/>
       <c r="B76" s="14" t="s">
         <v>346</v>
@@ -2864,22 +2894,22 @@
       <c r="F76" s="14">
         <v>5</v>
       </c>
-      <c r="G76" s="34"/>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G76" s="43"/>
+    </row>
+    <row r="77" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A77" s="16"/>
       <c r="B77" s="14"/>
       <c r="C77" s="14"/>
-      <c r="D77" s="42" t="s">
+      <c r="D77" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E77" s="28">
         <v>1</v>
       </c>
       <c r="F77" s="14"/>
-      <c r="G77" s="34"/>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G77" s="43"/>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A78" s="1"/>
       <c r="E78">
         <f>-SUM(E71:E76)*E77</f>
@@ -2890,15 +2920,15 @@
         <v>40</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A79" s="1"/>
     </row>
-    <row r="80" spans="1:7" ht="18" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:7" ht="19" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A81" s="7" t="s">
         <v>380</v>
       </c>
@@ -2908,16 +2938,16 @@
       <c r="C81" s="8" t="s">
         <v>316</v>
       </c>
-      <c r="D81" s="44"/>
+      <c r="D81" s="35"/>
       <c r="E81" s="8"/>
       <c r="F81" s="8">
         <v>0</v>
       </c>
-      <c r="G81" s="35" t="s">
+      <c r="G81" s="44" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A82" s="7"/>
       <c r="B82" s="7" t="s">
         <v>382</v>
@@ -2925,53 +2955,53 @@
       <c r="C82" s="8" t="s">
         <v>383</v>
       </c>
-      <c r="D82" s="44"/>
+      <c r="D82" s="35"/>
       <c r="E82" s="8"/>
       <c r="F82" s="8">
         <v>30</v>
       </c>
-      <c r="G82" s="35"/>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G82" s="44"/>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A83" s="7"/>
       <c r="B83" s="7"/>
       <c r="C83" s="8" t="s">
         <v>384</v>
       </c>
-      <c r="D83" s="44"/>
+      <c r="D83" s="35"/>
       <c r="E83" s="8"/>
       <c r="F83" s="8">
         <v>10</v>
       </c>
-      <c r="G83" s="35"/>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G83" s="44"/>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A84" s="7"/>
       <c r="B84" s="7"/>
       <c r="C84" s="8" t="s">
         <v>385</v>
       </c>
-      <c r="D84" s="44"/>
+      <c r="D84" s="35"/>
       <c r="E84" s="8"/>
       <c r="F84" s="8">
         <v>10</v>
       </c>
-      <c r="G84" s="35"/>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G84" s="44"/>
+    </row>
+    <row r="85" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A85" s="7"/>
       <c r="B85" s="7"/>
       <c r="C85" s="7"/>
-      <c r="D85" s="42" t="s">
+      <c r="D85" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E85" s="28">
         <v>1</v>
       </c>
       <c r="F85" s="7"/>
-      <c r="G85" s="35"/>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G85" s="44"/>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="E86">
@@ -2983,15 +3013,15 @@
         <v>50</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A87" s="1"/>
     </row>
-    <row r="88" spans="1:7" ht="21" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:7" ht="21" x14ac:dyDescent="0.25">
       <c r="A88" s="23" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A89" s="15" t="s">
         <v>317</v>
       </c>
@@ -2999,89 +3029,89 @@
         <v>316</v>
       </c>
       <c r="C89" s="13"/>
-      <c r="D89" s="40"/>
+      <c r="D89" s="31"/>
       <c r="E89" s="13"/>
       <c r="F89" s="13">
         <v>10</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A90" s="15"/>
       <c r="B90" s="13" t="s">
         <v>131</v>
       </c>
       <c r="C90" s="13"/>
-      <c r="D90" s="40"/>
+      <c r="D90" s="31"/>
       <c r="E90" s="13"/>
       <c r="F90" s="13">
         <v>5</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A91" s="15"/>
       <c r="B91" s="13" t="s">
         <v>235</v>
       </c>
       <c r="C91" s="13"/>
-      <c r="D91" s="40"/>
+      <c r="D91" s="31"/>
       <c r="E91" s="13"/>
       <c r="F91" s="13">
         <v>5</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A92" s="15"/>
       <c r="B92" s="13" t="s">
         <v>8</v>
       </c>
       <c r="C92" s="13"/>
-      <c r="D92" s="40"/>
+      <c r="D92" s="31"/>
       <c r="E92" s="13"/>
       <c r="F92" s="13">
         <v>5</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A93" s="15"/>
       <c r="B93" s="13" t="s">
         <v>132</v>
       </c>
       <c r="C93" s="13"/>
-      <c r="D93" s="40"/>
+      <c r="D93" s="31"/>
       <c r="E93" s="13"/>
       <c r="F93" s="13">
         <v>5</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A94" s="15"/>
       <c r="B94" s="13" t="s">
         <v>133</v>
       </c>
       <c r="C94" s="13"/>
-      <c r="D94" s="40"/>
+      <c r="D94" s="31"/>
       <c r="E94" s="13"/>
       <c r="F94" s="13">
         <v>5</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A95" s="15"/>
       <c r="B95" s="13" t="s">
         <v>134</v>
       </c>
       <c r="C95" s="13"/>
-      <c r="D95" s="40"/>
+      <c r="D95" s="31"/>
       <c r="E95" s="13"/>
       <c r="F95" s="13">
         <v>5</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A96" s="15"/>
       <c r="B96" s="13"/>
       <c r="C96" s="13"/>
-      <c r="D96" s="42" t="s">
+      <c r="D96" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E96" s="28">
@@ -3089,7 +3119,7 @@
       </c>
       <c r="F96" s="13"/>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A97" s="1"/>
       <c r="E97">
         <f>SUM(E89:E95)*E96</f>
@@ -3100,18 +3130,18 @@
         <v>40</v>
       </c>
     </row>
-    <row r="98" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="99" spans="1:6" ht="21" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="99" spans="1:6" ht="21" x14ac:dyDescent="0.25">
       <c r="A99" s="23" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="100" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:6" ht="19" x14ac:dyDescent="0.25">
       <c r="A100" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A101" s="15" t="s">
         <v>7</v>
       </c>
@@ -3119,77 +3149,77 @@
         <v>8</v>
       </c>
       <c r="C101" s="13"/>
-      <c r="D101" s="40"/>
+      <c r="D101" s="31"/>
       <c r="E101" s="13"/>
       <c r="F101" s="13">
         <v>5</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A102" s="13"/>
       <c r="B102" s="13" t="s">
         <v>9</v>
       </c>
       <c r="C102" s="13"/>
-      <c r="D102" s="40"/>
+      <c r="D102" s="31"/>
       <c r="E102" s="13"/>
       <c r="F102" s="13">
         <v>5</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A103" s="13"/>
       <c r="B103" s="13" t="s">
         <v>10</v>
       </c>
       <c r="C103" s="13"/>
-      <c r="D103" s="40"/>
+      <c r="D103" s="31"/>
       <c r="E103" s="13"/>
       <c r="F103" s="13">
         <v>5</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A104" s="13"/>
       <c r="B104" s="13" t="s">
         <v>11</v>
       </c>
       <c r="C104" s="13"/>
-      <c r="D104" s="40"/>
+      <c r="D104" s="31"/>
       <c r="E104" s="13"/>
       <c r="F104" s="13">
         <v>10</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A105" s="13"/>
       <c r="B105" s="13" t="s">
         <v>12</v>
       </c>
       <c r="C105" s="13"/>
-      <c r="D105" s="40"/>
+      <c r="D105" s="31"/>
       <c r="E105" s="13"/>
       <c r="F105" s="13">
         <v>5</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A106" s="13"/>
       <c r="B106" s="13" t="s">
         <v>100</v>
       </c>
       <c r="C106" s="13"/>
-      <c r="D106" s="40"/>
+      <c r="D106" s="31"/>
       <c r="E106" s="13"/>
       <c r="F106" s="13">
         <v>5</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A107" s="13"/>
       <c r="B107" s="13"/>
       <c r="C107" s="13"/>
-      <c r="D107" s="42" t="s">
+      <c r="D107" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E107" s="28">
@@ -3197,7 +3227,7 @@
       </c>
       <c r="F107" s="13"/>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
       <c r="E108">
         <f>SUM(E101:E106)*E107</f>
         <v>0</v>
@@ -3207,12 +3237,12 @@
         <v>35</v>
       </c>
     </row>
-    <row r="110" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:6" ht="19" x14ac:dyDescent="0.25">
       <c r="A110" s="5" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A111" s="16" t="s">
         <v>275</v>
       </c>
@@ -3226,7 +3256,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A112" s="16"/>
       <c r="B112" s="14" t="s">
         <v>14</v>
@@ -3238,7 +3268,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A113" s="14"/>
       <c r="B113" s="14" t="s">
         <v>15</v>
@@ -3250,7 +3280,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A114" s="14"/>
       <c r="B114" s="14" t="s">
         <v>16</v>
@@ -3262,7 +3292,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A115" s="14"/>
       <c r="B115" s="14" t="s">
         <v>17</v>
@@ -3274,7 +3304,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A116" s="14"/>
       <c r="B116" s="14" t="s">
         <v>18</v>
@@ -3286,7 +3316,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A117" s="14"/>
       <c r="B117" s="14" t="s">
         <v>20</v>
@@ -3298,7 +3328,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A118" s="14"/>
       <c r="B118" s="24" t="s">
         <v>19</v>
@@ -3310,11 +3340,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A119" s="14"/>
       <c r="B119" s="24"/>
       <c r="C119" s="14"/>
-      <c r="D119" s="42" t="s">
+      <c r="D119" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E119" s="28">
@@ -3322,7 +3352,7 @@
       </c>
       <c r="F119" s="14"/>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.2">
       <c r="E120">
         <f>SUM(E111:E118)*E119</f>
         <v>0</v>
@@ -3332,12 +3362,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="123" spans="1:7" ht="18" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:7" ht="19" x14ac:dyDescent="0.25">
       <c r="A123" s="5" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A124" s="11" t="s">
         <v>335</v>
       </c>
@@ -3347,18 +3377,18 @@
       <c r="C124" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="D124" s="41"/>
+      <c r="D124" s="32"/>
       <c r="E124" s="12" t="s">
         <v>319</v>
       </c>
       <c r="F124" s="12">
         <v>6</v>
       </c>
-      <c r="G124" s="32" t="s">
+      <c r="G124" s="41" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A125" s="11" t="s">
         <v>330</v>
       </c>
@@ -3366,7 +3396,7 @@
       <c r="C125" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="D125" s="41" t="s">
+      <c r="D125" s="32" t="s">
         <v>331</v>
       </c>
       <c r="E125" s="12" t="s">
@@ -3375,13 +3405,13 @@
       <c r="F125" s="12">
         <v>6</v>
       </c>
-      <c r="G125" s="32"/>
-    </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G125" s="41"/>
+    </row>
+    <row r="126" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A126" s="12"/>
       <c r="B126" s="12"/>
       <c r="C126" s="12"/>
-      <c r="D126" s="41" t="s">
+      <c r="D126" s="32" t="s">
         <v>102</v>
       </c>
       <c r="E126" s="12" t="s">
@@ -3390,67 +3420,67 @@
       <c r="F126" s="12">
         <v>6</v>
       </c>
-      <c r="G126" s="32"/>
-    </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G126" s="41"/>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A127" s="12"/>
       <c r="B127" s="12"/>
       <c r="C127" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="D127" s="41"/>
+      <c r="D127" s="32"/>
       <c r="E127" s="12" t="s">
         <v>319</v>
       </c>
       <c r="F127" s="12">
         <v>6</v>
       </c>
-      <c r="G127" s="32"/>
-    </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G127" s="41"/>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A128" s="12"/>
       <c r="B128" s="12"/>
       <c r="C128" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="D128" s="41"/>
+      <c r="D128" s="32"/>
       <c r="E128" s="12" t="s">
         <v>319</v>
       </c>
       <c r="F128" s="12">
         <v>6</v>
       </c>
-      <c r="G128" s="32"/>
-    </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G128" s="41"/>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A129" s="12"/>
       <c r="B129" s="12"/>
       <c r="C129" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="D129" s="41"/>
+      <c r="D129" s="32"/>
       <c r="E129" s="12" t="s">
         <v>319</v>
       </c>
       <c r="F129" s="12">
         <v>6</v>
       </c>
-      <c r="G129" s="32"/>
-    </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G129" s="41"/>
+    </row>
+    <row r="130" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A130" s="12"/>
       <c r="B130" s="12"/>
       <c r="C130" s="12"/>
-      <c r="D130" s="42" t="s">
+      <c r="D130" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E130" s="28">
         <v>1</v>
       </c>
       <c r="F130" s="12"/>
-      <c r="G130" s="32"/>
-    </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G130" s="41"/>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
       <c r="E131">
         <f>SUM(E124:E129)*E130</f>
         <v>0</v>
@@ -3459,9 +3489,9 @@
         <f>SUM(F124:F129)</f>
         <v>36</v>
       </c>
-      <c r="G131" s="32"/>
-    </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G131" s="41"/>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A132" s="11" t="s">
         <v>276</v>
       </c>
@@ -3471,22 +3501,22 @@
       <c r="C132" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="D132" s="41"/>
+      <c r="D132" s="32"/>
       <c r="E132" s="12" t="s">
         <v>319</v>
       </c>
       <c r="F132" s="12">
         <v>10</v>
       </c>
-      <c r="G132" s="32"/>
-    </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G132" s="41"/>
+    </row>
+    <row r="133" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A133" s="12"/>
       <c r="B133" s="12"/>
       <c r="C133" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="D133" s="41" t="s">
+      <c r="D133" s="32" t="s">
         <v>117</v>
       </c>
       <c r="E133" s="12" t="s">
@@ -3495,13 +3525,13 @@
       <c r="F133" s="12">
         <v>5</v>
       </c>
-      <c r="G133" s="32"/>
-    </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G133" s="41"/>
+    </row>
+    <row r="134" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A134" s="12"/>
       <c r="B134" s="12"/>
       <c r="C134" s="12"/>
-      <c r="D134" s="41" t="s">
+      <c r="D134" s="32" t="s">
         <v>118</v>
       </c>
       <c r="E134" s="12" t="s">
@@ -3510,13 +3540,13 @@
       <c r="F134" s="12">
         <v>5</v>
       </c>
-      <c r="G134" s="32"/>
-    </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G134" s="41"/>
+    </row>
+    <row r="135" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A135" s="11"/>
       <c r="B135" s="12"/>
       <c r="C135" s="12"/>
-      <c r="D135" s="41" t="s">
+      <c r="D135" s="32" t="s">
         <v>103</v>
       </c>
       <c r="E135" s="12" t="s">
@@ -3525,13 +3555,13 @@
       <c r="F135" s="12">
         <v>5</v>
       </c>
-      <c r="G135" s="32"/>
-    </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G135" s="41"/>
+    </row>
+    <row r="136" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A136" s="11"/>
       <c r="B136" s="12"/>
       <c r="C136" s="12"/>
-      <c r="D136" s="41" t="s">
+      <c r="D136" s="32" t="s">
         <v>13</v>
       </c>
       <c r="E136" s="12" t="s">
@@ -3540,67 +3570,67 @@
       <c r="F136" s="12">
         <v>5</v>
       </c>
-      <c r="G136" s="32"/>
-    </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G136" s="41"/>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A137" s="11"/>
       <c r="B137" s="12"/>
       <c r="C137" s="12" t="s">
         <v>332</v>
       </c>
-      <c r="D137" s="41"/>
+      <c r="D137" s="32"/>
       <c r="E137" s="12" t="s">
         <v>319</v>
       </c>
       <c r="F137" s="12">
         <v>10</v>
       </c>
-      <c r="G137" s="32"/>
-    </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G137" s="41"/>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A138" s="12"/>
       <c r="B138" s="12"/>
       <c r="C138" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="D138" s="41"/>
+      <c r="D138" s="32"/>
       <c r="E138" s="12" t="s">
         <v>319</v>
       </c>
       <c r="F138" s="12">
         <v>5</v>
       </c>
-      <c r="G138" s="32"/>
-    </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G138" s="41"/>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A139" s="12"/>
       <c r="B139" s="12"/>
       <c r="C139" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="D139" s="41"/>
+      <c r="D139" s="32"/>
       <c r="E139" s="12" t="s">
         <v>319</v>
       </c>
       <c r="F139" s="12">
         <v>5</v>
       </c>
-      <c r="G139" s="32"/>
-    </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G139" s="41"/>
+    </row>
+    <row r="140" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A140" s="12"/>
       <c r="B140" s="12"/>
       <c r="C140" s="12"/>
-      <c r="D140" s="42" t="s">
+      <c r="D140" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E140" s="28">
         <v>1</v>
       </c>
       <c r="F140" s="12"/>
-      <c r="G140" s="32"/>
-    </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G140" s="41"/>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
       <c r="E141">
         <f>SUM(E132:E139)*E140</f>
         <v>0</v>
@@ -3609,9 +3639,9 @@
         <f>SUM(F132:F139)</f>
         <v>50</v>
       </c>
-      <c r="G141" s="32"/>
-    </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G141" s="41"/>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A142" s="11" t="s">
         <v>333</v>
       </c>
@@ -3621,16 +3651,16 @@
       <c r="C142" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="D142" s="41"/>
+      <c r="D142" s="32"/>
       <c r="E142" s="12" t="s">
         <v>319</v>
       </c>
       <c r="F142" s="12">
         <v>6</v>
       </c>
-      <c r="G142" s="32"/>
-    </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G142" s="41"/>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A143" s="11" t="s">
         <v>334</v>
       </c>
@@ -3638,33 +3668,33 @@
       <c r="C143" s="12" t="s">
         <v>336</v>
       </c>
-      <c r="D143" s="41"/>
+      <c r="D143" s="32"/>
       <c r="E143" s="12"/>
       <c r="F143" s="12">
         <v>6</v>
       </c>
-      <c r="G143" s="32"/>
-    </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G143" s="41"/>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A144" s="11"/>
       <c r="B144" s="12"/>
       <c r="C144" s="12" t="s">
         <v>337</v>
       </c>
-      <c r="D144" s="41"/>
+      <c r="D144" s="32"/>
       <c r="E144" s="12"/>
       <c r="F144" s="12">
         <v>10</v>
       </c>
-      <c r="G144" s="32"/>
-    </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G144" s="41"/>
+    </row>
+    <row r="145" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A145" s="11"/>
       <c r="B145" s="12"/>
       <c r="C145" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="D145" s="41" t="s">
+      <c r="D145" s="32" t="s">
         <v>331</v>
       </c>
       <c r="E145" s="12" t="s">
@@ -3673,13 +3703,13 @@
       <c r="F145" s="12">
         <v>6</v>
       </c>
-      <c r="G145" s="32"/>
-    </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G145" s="41"/>
+    </row>
+    <row r="146" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A146" s="12"/>
       <c r="B146" s="12"/>
       <c r="C146" s="12"/>
-      <c r="D146" s="41" t="s">
+      <c r="D146" s="32" t="s">
         <v>102</v>
       </c>
       <c r="E146" s="12" t="s">
@@ -3688,67 +3718,67 @@
       <c r="F146" s="12">
         <v>6</v>
       </c>
-      <c r="G146" s="32"/>
-    </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G146" s="41"/>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A147" s="12"/>
       <c r="B147" s="12"/>
       <c r="C147" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="D147" s="41"/>
+      <c r="D147" s="32"/>
       <c r="E147" s="12" t="s">
         <v>319</v>
       </c>
       <c r="F147" s="12">
         <v>6</v>
       </c>
-      <c r="G147" s="32"/>
-    </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G147" s="41"/>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A148" s="12"/>
       <c r="B148" s="12"/>
       <c r="C148" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="D148" s="41"/>
+      <c r="D148" s="32"/>
       <c r="E148" s="12" t="s">
         <v>319</v>
       </c>
       <c r="F148" s="12">
         <v>6</v>
       </c>
-      <c r="G148" s="32"/>
-    </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G148" s="41"/>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A149" s="12"/>
       <c r="B149" s="12"/>
       <c r="C149" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="D149" s="41"/>
+      <c r="D149" s="32"/>
       <c r="E149" s="12" t="s">
         <v>319</v>
       </c>
       <c r="F149" s="12">
         <v>6</v>
       </c>
-      <c r="G149" s="32"/>
-    </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G149" s="41"/>
+    </row>
+    <row r="150" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A150" s="12"/>
       <c r="B150" s="12"/>
       <c r="C150" s="12"/>
-      <c r="D150" s="42" t="s">
+      <c r="D150" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E150" s="28">
         <v>1</v>
       </c>
       <c r="F150" s="12"/>
-      <c r="G150" s="32"/>
-    </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G150" s="41"/>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.2">
       <c r="E151">
         <f>SUM(E142:E149)*E150</f>
         <v>0</v>
@@ -3757,9 +3787,9 @@
         <f>SUM(F142:F149)</f>
         <v>52</v>
       </c>
-      <c r="G151" s="32"/>
-    </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G151" s="41"/>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A152" s="11" t="s">
         <v>338</v>
       </c>
@@ -3769,22 +3799,22 @@
       <c r="C152" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="D152" s="41"/>
+      <c r="D152" s="32"/>
       <c r="E152" s="12" t="s">
         <v>319</v>
       </c>
       <c r="F152" s="12">
         <v>10</v>
       </c>
-      <c r="G152" s="32"/>
-    </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G152" s="41"/>
+    </row>
+    <row r="153" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A153" s="12"/>
       <c r="B153" s="12"/>
       <c r="C153" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="D153" s="41" t="s">
+      <c r="D153" s="32" t="s">
         <v>117</v>
       </c>
       <c r="E153" s="12" t="s">
@@ -3793,13 +3823,13 @@
       <c r="F153" s="12">
         <v>5</v>
       </c>
-      <c r="G153" s="32"/>
-    </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G153" s="41"/>
+    </row>
+    <row r="154" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A154" s="12"/>
       <c r="B154" s="12"/>
       <c r="C154" s="12"/>
-      <c r="D154" s="41" t="s">
+      <c r="D154" s="32" t="s">
         <v>118</v>
       </c>
       <c r="E154" s="12" t="s">
@@ -3808,13 +3838,13 @@
       <c r="F154" s="12">
         <v>5</v>
       </c>
-      <c r="G154" s="32"/>
-    </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G154" s="41"/>
+    </row>
+    <row r="155" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A155" s="11"/>
       <c r="B155" s="12"/>
       <c r="C155" s="12"/>
-      <c r="D155" s="41" t="s">
+      <c r="D155" s="32" t="s">
         <v>103</v>
       </c>
       <c r="E155" s="12" t="s">
@@ -3823,13 +3853,13 @@
       <c r="F155" s="12">
         <v>5</v>
       </c>
-      <c r="G155" s="32"/>
-    </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G155" s="41"/>
+    </row>
+    <row r="156" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A156" s="11"/>
       <c r="B156" s="12"/>
       <c r="C156" s="12"/>
-      <c r="D156" s="41" t="s">
+      <c r="D156" s="32" t="s">
         <v>13</v>
       </c>
       <c r="E156" s="12" t="s">
@@ -3838,80 +3868,80 @@
       <c r="F156" s="12">
         <v>5</v>
       </c>
-      <c r="G156" s="32"/>
-    </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G156" s="41"/>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A157" s="11"/>
       <c r="B157" s="12"/>
       <c r="C157" s="12" t="s">
         <v>337</v>
       </c>
-      <c r="D157" s="41"/>
+      <c r="D157" s="32"/>
       <c r="E157" s="12"/>
       <c r="F157" s="12">
         <v>10</v>
       </c>
-      <c r="G157" s="32"/>
-    </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G157" s="41"/>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A158" s="11"/>
       <c r="B158" s="12"/>
       <c r="C158" s="12" t="s">
         <v>332</v>
       </c>
-      <c r="D158" s="41"/>
+      <c r="D158" s="32"/>
       <c r="E158" s="12" t="s">
         <v>319</v>
       </c>
       <c r="F158" s="12">
         <v>10</v>
       </c>
-      <c r="G158" s="32"/>
-    </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G158" s="41"/>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A159" s="12"/>
       <c r="B159" s="12"/>
       <c r="C159" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="D159" s="41"/>
+      <c r="D159" s="32"/>
       <c r="E159" s="12" t="s">
         <v>319</v>
       </c>
       <c r="F159" s="12">
         <v>5</v>
       </c>
-      <c r="G159" s="32"/>
-    </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G159" s="41"/>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A160" s="12"/>
       <c r="B160" s="12"/>
       <c r="C160" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="D160" s="41"/>
+      <c r="D160" s="32"/>
       <c r="E160" s="12" t="s">
         <v>319</v>
       </c>
       <c r="F160" s="12">
         <v>5</v>
       </c>
-      <c r="G160" s="32"/>
-    </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G160" s="41"/>
+    </row>
+    <row r="161" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A161" s="12"/>
       <c r="B161" s="12"/>
       <c r="C161" s="12"/>
-      <c r="D161" s="42" t="s">
+      <c r="D161" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E161" s="28">
         <v>1</v>
       </c>
       <c r="F161" s="12"/>
-      <c r="G161" s="32"/>
-    </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G161" s="41"/>
+    </row>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.2">
       <c r="E162">
         <f>SUM(E152:E160)*E161</f>
         <v>0</v>
@@ -3920,12 +3950,12 @@
         <f>SUM(F152:F160)</f>
         <v>60</v>
       </c>
-      <c r="G162" s="32"/>
-    </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G162" s="41"/>
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.2">
       <c r="G163" s="27"/>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A164" s="16" t="s">
         <v>125</v>
       </c>
@@ -3941,7 +3971,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A165" s="16"/>
       <c r="B165" s="14"/>
       <c r="C165" s="14" t="s">
@@ -3953,7 +3983,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A166" s="16"/>
       <c r="B166" s="14"/>
       <c r="C166" s="14" t="s">
@@ -3965,11 +3995,11 @@
         <v>20</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A167" s="16"/>
       <c r="B167" s="14"/>
       <c r="C167" s="14"/>
-      <c r="D167" s="42" t="s">
+      <c r="D167" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E167" s="28">
@@ -3977,7 +4007,7 @@
       </c>
       <c r="F167" s="14"/>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A168" s="1"/>
       <c r="E168">
         <f>-SUM(E164:E166)*E167</f>
@@ -3988,7 +4018,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A169" s="16" t="s">
         <v>125</v>
       </c>
@@ -4004,7 +4034,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A170" s="16"/>
       <c r="B170" s="14"/>
       <c r="C170" s="14" t="s">
@@ -4016,7 +4046,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A171" s="16"/>
       <c r="B171" s="14"/>
       <c r="C171" s="14" t="s">
@@ -4028,7 +4058,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A172" s="16"/>
       <c r="B172" s="14"/>
       <c r="C172" s="14" t="s">
@@ -4040,7 +4070,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A173" s="16"/>
       <c r="B173" s="14"/>
       <c r="C173" s="14" t="s">
@@ -4052,11 +4082,11 @@
         <v>15</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A174" s="16"/>
       <c r="B174" s="14"/>
       <c r="C174" s="14"/>
-      <c r="D174" s="42" t="s">
+      <c r="D174" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E174" s="28">
@@ -4064,7 +4094,7 @@
       </c>
       <c r="F174" s="14"/>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A175" s="1"/>
       <c r="E175">
         <f>-SUM(E169:E173)*E174</f>
@@ -4075,7 +4105,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A176" s="16" t="s">
         <v>339</v>
       </c>
@@ -4093,7 +4123,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A177" s="16" t="s">
         <v>340</v>
       </c>
@@ -4107,7 +4137,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A178" s="16"/>
       <c r="B178" s="14"/>
       <c r="C178" s="14" t="s">
@@ -4119,7 +4149,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A179" s="16"/>
       <c r="B179" s="14"/>
       <c r="C179" s="14" t="s">
@@ -4131,7 +4161,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A180" s="16"/>
       <c r="B180" s="14"/>
       <c r="C180" s="14" t="s">
@@ -4143,7 +4173,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A181" s="16"/>
       <c r="B181" s="14"/>
       <c r="C181" s="14" t="s">
@@ -4159,7 +4189,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A182" s="14"/>
       <c r="B182" s="14"/>
       <c r="C182" s="14"/>
@@ -4173,7 +4203,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A183" s="14"/>
       <c r="B183" s="14"/>
       <c r="C183" s="14" t="s">
@@ -4187,7 +4217,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A184" s="14"/>
       <c r="B184" s="14"/>
       <c r="C184" s="14" t="s">
@@ -4201,7 +4231,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A185" s="14"/>
       <c r="B185" s="14"/>
       <c r="C185" s="14" t="s">
@@ -4215,11 +4245,11 @@
         <v>6</v>
       </c>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A186" s="14"/>
       <c r="B186" s="14"/>
       <c r="C186" s="14"/>
-      <c r="D186" s="42" t="s">
+      <c r="D186" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E186" s="28">
@@ -4227,7 +4257,7 @@
       </c>
       <c r="F186" s="14"/>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.2">
       <c r="E187">
         <f>SUM(E176:E185)*E186</f>
         <v>0</v>
@@ -4237,7 +4267,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A188" s="16" t="s">
         <v>339</v>
       </c>
@@ -4255,7 +4285,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A189" s="14" t="s">
         <v>340</v>
       </c>
@@ -4269,7 +4299,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A190" s="16"/>
       <c r="B190" s="14"/>
       <c r="C190" s="14" t="s">
@@ -4281,7 +4311,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A191" s="14"/>
       <c r="B191" s="14"/>
       <c r="C191" s="14" t="s">
@@ -4297,7 +4327,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A192" s="14"/>
       <c r="B192" s="14"/>
       <c r="C192" s="14"/>
@@ -4311,7 +4341,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A193" s="16"/>
       <c r="B193" s="14"/>
       <c r="C193" s="14"/>
@@ -4325,7 +4355,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A194" s="16"/>
       <c r="B194" s="14"/>
       <c r="C194" s="14"/>
@@ -4339,7 +4369,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A195" s="14"/>
       <c r="B195" s="14"/>
       <c r="C195" s="14" t="s">
@@ -4353,7 +4383,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A196" s="14"/>
       <c r="B196" s="14"/>
       <c r="C196" s="14" t="s">
@@ -4367,11 +4397,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A197" s="14"/>
       <c r="B197" s="14"/>
       <c r="C197" s="14"/>
-      <c r="D197" s="42" t="s">
+      <c r="D197" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E197" s="28">
@@ -4379,7 +4409,7 @@
       </c>
       <c r="F197" s="14"/>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.2">
       <c r="E198">
         <f>SUM(E188:E196)*E197</f>
         <v>0</v>
@@ -4389,7 +4419,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A199" s="16" t="s">
         <v>342</v>
       </c>
@@ -4403,7 +4433,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A200" s="16"/>
       <c r="B200" s="14" t="s">
         <v>127</v>
@@ -4415,7 +4445,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A201" s="16"/>
       <c r="B201" s="14" t="s">
         <v>124</v>
@@ -4427,11 +4457,11 @@
         <v>20</v>
       </c>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A202" s="16"/>
       <c r="B202" s="14"/>
       <c r="C202" s="14"/>
-      <c r="D202" s="42" t="s">
+      <c r="D202" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E202" s="28">
@@ -4439,7 +4469,7 @@
       </c>
       <c r="F202" s="14"/>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A203" s="1"/>
       <c r="E203">
         <f>SUM(E199:E201)*E202</f>
@@ -4450,16 +4480,16 @@
         <v>60</v>
       </c>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A204" s="1"/>
     </row>
-    <row r="205" spans="1:9" s="5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:9" s="5" customFormat="1" ht="19" x14ac:dyDescent="0.25">
       <c r="A205" s="5" t="s">
         <v>378</v>
       </c>
-      <c r="D205" s="43"/>
-    </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D205" s="34"/>
+    </row>
+    <row r="206" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A206" s="1" t="s">
         <v>62</v>
       </c>
@@ -4469,102 +4499,102 @@
       <c r="C206" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="D206" s="41"/>
+      <c r="D206" s="32"/>
       <c r="E206" s="12"/>
       <c r="F206" s="12">
         <v>5</v>
       </c>
       <c r="I206" s="1"/>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A207" s="1"/>
       <c r="B207" s="12"/>
       <c r="C207" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="D207" s="41"/>
+      <c r="D207" s="32"/>
       <c r="E207" s="12"/>
       <c r="F207" s="12">
         <v>5</v>
       </c>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A208" s="1"/>
       <c r="B208" s="12"/>
       <c r="C208" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="D208" s="41"/>
+      <c r="D208" s="32"/>
       <c r="E208" s="12"/>
       <c r="F208" s="12">
         <v>5</v>
       </c>
     </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A209" s="1"/>
       <c r="B209" s="12"/>
       <c r="C209" s="12" t="s">
         <v>249</v>
       </c>
-      <c r="D209" s="41"/>
+      <c r="D209" s="32"/>
       <c r="E209" s="12"/>
       <c r="F209" s="12">
         <v>5</v>
       </c>
     </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A210" s="1"/>
       <c r="B210" s="12"/>
       <c r="C210" s="12" t="s">
         <v>248</v>
       </c>
-      <c r="D210" s="41"/>
+      <c r="D210" s="32"/>
       <c r="E210" s="12"/>
       <c r="F210" s="12">
         <v>5</v>
       </c>
     </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A211" s="1"/>
       <c r="B211" s="12"/>
       <c r="C211" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="D211" s="41"/>
+      <c r="D211" s="32"/>
       <c r="E211" s="12"/>
       <c r="F211" s="12">
         <v>5</v>
       </c>
     </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A212" s="1"/>
       <c r="B212" s="12"/>
       <c r="C212" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="D212" s="41"/>
+      <c r="D212" s="32"/>
       <c r="E212" s="12"/>
       <c r="F212" s="12">
         <v>5</v>
       </c>
     </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A213" s="1"/>
       <c r="B213" s="12"/>
       <c r="C213" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="D213" s="41"/>
+      <c r="D213" s="32"/>
       <c r="E213" s="12"/>
       <c r="F213" s="12">
         <v>5</v>
       </c>
     </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A214" s="1"/>
       <c r="B214" s="12"/>
       <c r="C214" s="12"/>
-      <c r="D214" s="42" t="s">
+      <c r="D214" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E214" s="28">
@@ -4572,7 +4602,7 @@
       </c>
       <c r="F214" s="12"/>
     </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A215" s="1"/>
       <c r="E215">
         <f>-SUM(E206:E213)*E214</f>
@@ -4583,7 +4613,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A216" s="1"/>
       <c r="B216" s="13" t="s">
         <v>63</v>
@@ -4591,101 +4621,101 @@
       <c r="C216" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="D216" s="40"/>
+      <c r="D216" s="31"/>
       <c r="E216" s="13"/>
       <c r="F216" s="13">
         <v>5</v>
       </c>
     </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A217" s="1"/>
       <c r="B217" s="13"/>
       <c r="C217" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="D217" s="40"/>
+      <c r="D217" s="31"/>
       <c r="E217" s="13"/>
       <c r="F217" s="13">
         <v>5</v>
       </c>
     </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A218" s="1"/>
       <c r="B218" s="13"/>
       <c r="C218" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="D218" s="40"/>
+      <c r="D218" s="31"/>
       <c r="E218" s="13"/>
       <c r="F218" s="13">
         <v>5</v>
       </c>
     </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A219" s="1"/>
       <c r="B219" s="13"/>
       <c r="C219" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="D219" s="40"/>
+      <c r="D219" s="31"/>
       <c r="E219" s="13"/>
       <c r="F219" s="13">
         <v>5</v>
       </c>
     </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A220" s="1"/>
       <c r="B220" s="13"/>
       <c r="C220" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="D220" s="40"/>
+      <c r="D220" s="31"/>
       <c r="E220" s="13"/>
       <c r="F220" s="13">
         <v>5</v>
       </c>
     </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A221" s="1"/>
       <c r="B221" s="13"/>
       <c r="C221" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="D221" s="40"/>
+      <c r="D221" s="31"/>
       <c r="E221" s="13"/>
       <c r="F221" s="13">
         <v>5</v>
       </c>
     </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A222" s="1"/>
       <c r="B222" s="13"/>
       <c r="C222" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="D222" s="40"/>
+      <c r="D222" s="31"/>
       <c r="E222" s="13"/>
       <c r="F222" s="13">
         <v>5</v>
       </c>
     </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A223" s="1"/>
       <c r="B223" s="13"/>
       <c r="C223" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="D223" s="40"/>
+      <c r="D223" s="31"/>
       <c r="E223" s="13"/>
       <c r="F223" s="13">
         <v>5</v>
       </c>
     </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A224" s="1"/>
       <c r="B224" s="13"/>
       <c r="C224" s="13"/>
-      <c r="D224" s="42" t="s">
+      <c r="D224" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E224" s="28">
@@ -4693,7 +4723,7 @@
       </c>
       <c r="F224" s="13"/>
     </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A225" s="1"/>
       <c r="E225">
         <f>-SUM(E216:E223)*E224</f>
@@ -4704,7 +4734,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A226" s="1"/>
       <c r="B226" s="14" t="s">
         <v>63</v>
@@ -4718,7 +4748,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A227" s="1"/>
       <c r="B227" s="14"/>
       <c r="C227" s="14" t="s">
@@ -4730,7 +4760,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A228" s="1"/>
       <c r="B228" s="14"/>
       <c r="C228" s="14" t="s">
@@ -4742,7 +4772,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A229" s="1"/>
       <c r="B229" s="14"/>
       <c r="C229" s="14" t="s">
@@ -4754,7 +4784,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A230" s="1"/>
       <c r="B230" s="14"/>
       <c r="C230" s="14" t="s">
@@ -4766,7 +4796,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A231" s="1"/>
       <c r="B231" s="14"/>
       <c r="C231" s="14" t="s">
@@ -4778,7 +4808,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A232" s="1"/>
       <c r="B232" s="14"/>
       <c r="C232" s="14" t="s">
@@ -4790,7 +4820,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A233" s="1"/>
       <c r="B233" s="14"/>
       <c r="C233" s="14" t="s">
@@ -4802,11 +4832,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A234" s="1"/>
       <c r="B234" s="14"/>
       <c r="C234" s="14"/>
-      <c r="D234" s="42" t="s">
+      <c r="D234" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E234" s="28">
@@ -4814,7 +4844,7 @@
       </c>
       <c r="F234" s="14"/>
     </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A235" s="1"/>
       <c r="E235">
         <f>-SUM(E226:E233)*E234</f>
@@ -4825,7 +4855,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A236" s="15" t="s">
         <v>277</v>
       </c>
@@ -4835,113 +4865,113 @@
       <c r="C236" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="D236" s="40"/>
+      <c r="D236" s="31"/>
       <c r="E236" s="13"/>
       <c r="F236" s="13">
         <v>10</v>
       </c>
     </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A237" s="13"/>
       <c r="B237" s="13"/>
       <c r="C237" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="D237" s="40"/>
+      <c r="D237" s="31"/>
       <c r="E237" s="13"/>
       <c r="F237" s="13">
         <v>10</v>
       </c>
     </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A238" s="13"/>
       <c r="B238" s="13"/>
       <c r="C238" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="D238" s="40"/>
+      <c r="D238" s="31"/>
       <c r="E238" s="13"/>
       <c r="F238" s="13">
         <v>10</v>
       </c>
     </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A239" s="13"/>
       <c r="B239" s="13"/>
       <c r="C239" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="D239" s="40"/>
+      <c r="D239" s="31"/>
       <c r="E239" s="13"/>
       <c r="F239" s="13">
         <v>10</v>
       </c>
     </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A240" s="13"/>
       <c r="B240" s="13"/>
       <c r="C240" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D240" s="40"/>
+      <c r="D240" s="31"/>
       <c r="E240" s="13"/>
       <c r="F240" s="13">
         <v>20</v>
       </c>
     </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A241" s="13"/>
       <c r="B241" s="13"/>
       <c r="C241" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="D241" s="40"/>
+      <c r="D241" s="31"/>
       <c r="E241" s="13"/>
       <c r="F241" s="13">
         <v>10</v>
       </c>
     </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A242" s="13"/>
       <c r="B242" s="13"/>
       <c r="C242" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="D242" s="40"/>
+      <c r="D242" s="31"/>
       <c r="E242" s="13"/>
       <c r="F242" s="13">
         <v>10</v>
       </c>
     </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A243" s="13"/>
       <c r="B243" s="13"/>
       <c r="C243" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D243" s="40"/>
+      <c r="D243" s="31"/>
       <c r="E243" s="13"/>
       <c r="F243" s="13">
         <v>30</v>
       </c>
     </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A244" s="15"/>
       <c r="B244" s="13"/>
       <c r="C244" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="D244" s="40"/>
+      <c r="D244" s="31"/>
       <c r="E244" s="13"/>
       <c r="F244" s="13">
         <v>10</v>
       </c>
     </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A245" s="13"/>
       <c r="B245" s="13"/>
       <c r="C245" s="13"/>
-      <c r="D245" s="42" t="s">
+      <c r="D245" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E245" s="28">
@@ -4949,11 +4979,11 @@
       </c>
       <c r="F245" s="13"/>
     </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A246" s="25"/>
       <c r="B246" s="25"/>
       <c r="C246" s="25"/>
-      <c r="D246" s="45"/>
+      <c r="D246" s="36"/>
       <c r="E246" s="26">
         <f>SUM(E236:E244)*E245</f>
         <v>0</v>
@@ -4963,20 +4993,20 @@
         <v>120</v>
       </c>
     </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A247" s="25"/>
       <c r="B247" s="25"/>
       <c r="C247" s="25"/>
-      <c r="D247" s="45"/>
+      <c r="D247" s="36"/>
       <c r="E247" s="25"/>
       <c r="F247" s="25"/>
     </row>
-    <row r="248" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:6" ht="19" x14ac:dyDescent="0.25">
       <c r="A248" s="5" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A249" s="11" t="s">
         <v>206</v>
       </c>
@@ -4984,13 +5014,13 @@
         <v>205</v>
       </c>
       <c r="C249" s="12"/>
-      <c r="D249" s="41"/>
+      <c r="D249" s="32"/>
       <c r="E249" s="12"/>
       <c r="F249" s="12">
         <v>5</v>
       </c>
     </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A250" s="11" t="s">
         <v>325</v>
       </c>
@@ -4998,65 +5028,65 @@
         <v>65</v>
       </c>
       <c r="C250" s="12"/>
-      <c r="D250" s="41"/>
+      <c r="D250" s="32"/>
       <c r="E250" s="12"/>
       <c r="F250" s="12">
         <v>10</v>
       </c>
     </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A251" s="11"/>
       <c r="B251" s="12" t="s">
         <v>50</v>
       </c>
       <c r="C251" s="12"/>
-      <c r="D251" s="41"/>
+      <c r="D251" s="32"/>
       <c r="E251" s="12"/>
       <c r="F251" s="12">
         <v>10</v>
       </c>
     </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A252" s="11"/>
       <c r="B252" s="12" t="s">
         <v>207</v>
       </c>
       <c r="C252" s="12"/>
-      <c r="D252" s="41"/>
+      <c r="D252" s="32"/>
       <c r="E252" s="12"/>
       <c r="F252" s="12">
         <v>5</v>
       </c>
     </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A253" s="11"/>
       <c r="B253" s="12" t="s">
         <v>51</v>
       </c>
       <c r="C253" s="12"/>
-      <c r="D253" s="41"/>
+      <c r="D253" s="32"/>
       <c r="E253" s="12"/>
       <c r="F253" s="12">
         <v>5</v>
       </c>
     </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A254" s="11"/>
       <c r="B254" s="12" t="s">
         <v>234</v>
       </c>
       <c r="C254" s="12"/>
-      <c r="D254" s="41"/>
+      <c r="D254" s="32"/>
       <c r="E254" s="12"/>
       <c r="F254" s="12">
         <v>5</v>
       </c>
     </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A255" s="11"/>
       <c r="B255" s="12"/>
       <c r="C255" s="12"/>
-      <c r="D255" s="42" t="s">
+      <c r="D255" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E255" s="28">
@@ -5064,7 +5094,7 @@
       </c>
       <c r="F255" s="12"/>
     </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A256" s="1"/>
       <c r="E256">
         <f>SUM(E249:E254)*E255</f>
@@ -5075,7 +5105,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A257" s="11" t="s">
         <v>386</v>
       </c>
@@ -5083,16 +5113,16 @@
       <c r="C257" s="12" t="s">
         <v>205</v>
       </c>
-      <c r="D257" s="41"/>
+      <c r="D257" s="32"/>
       <c r="E257" s="12"/>
       <c r="F257" s="12">
         <v>5</v>
       </c>
-      <c r="G257" s="33" t="s">
+      <c r="G257" s="42" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A258" s="11" t="s">
         <v>327</v>
       </c>
@@ -5100,14 +5130,14 @@
       <c r="C258" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="D258" s="41"/>
+      <c r="D258" s="32"/>
       <c r="E258" s="12"/>
       <c r="F258" s="12">
         <v>10</v>
       </c>
-      <c r="G258" s="33"/>
-    </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G258" s="42"/>
+    </row>
+    <row r="259" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A259" s="11" t="s">
         <v>326</v>
       </c>
@@ -5115,66 +5145,66 @@
       <c r="C259" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="D259" s="41"/>
+      <c r="D259" s="32"/>
       <c r="E259" s="12"/>
       <c r="F259" s="12">
         <v>10</v>
       </c>
-      <c r="G259" s="33"/>
-    </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G259" s="42"/>
+    </row>
+    <row r="260" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A260" s="11"/>
       <c r="B260" s="12"/>
       <c r="C260" s="12" t="s">
         <v>207</v>
       </c>
-      <c r="D260" s="41"/>
+      <c r="D260" s="32"/>
       <c r="E260" s="12"/>
       <c r="F260" s="12">
         <v>5</v>
       </c>
-      <c r="G260" s="33"/>
-    </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G260" s="42"/>
+    </row>
+    <row r="261" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A261" s="11"/>
       <c r="B261" s="12"/>
       <c r="C261" s="12" t="s">
         <v>329</v>
       </c>
-      <c r="D261" s="41"/>
+      <c r="D261" s="32"/>
       <c r="E261" s="12"/>
       <c r="F261" s="12">
         <v>5</v>
       </c>
-      <c r="G261" s="33"/>
-    </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G261" s="42"/>
+    </row>
+    <row r="262" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A262" s="11"/>
       <c r="B262" s="12"/>
       <c r="C262" s="12" t="s">
         <v>328</v>
       </c>
-      <c r="D262" s="41"/>
+      <c r="D262" s="32"/>
       <c r="E262" s="12"/>
       <c r="F262" s="12">
         <v>5</v>
       </c>
-      <c r="G262" s="33"/>
-    </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G262" s="42"/>
+    </row>
+    <row r="263" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A263" s="11"/>
       <c r="B263" s="12"/>
       <c r="C263" s="12"/>
-      <c r="D263" s="42" t="s">
+      <c r="D263" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E263" s="28">
         <v>1</v>
       </c>
       <c r="F263" s="12"/>
-      <c r="G263" s="33"/>
-    </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G263" s="42"/>
+    </row>
+    <row r="264" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A264" s="1"/>
       <c r="E264">
         <f>SUM(E257:E262)*E263</f>
@@ -5185,12 +5215,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="265" spans="1:7" ht="18" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:7" ht="19" x14ac:dyDescent="0.25">
       <c r="A265" s="5" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A266" s="7" t="s">
         <v>29</v>
       </c>
@@ -5198,60 +5228,60 @@
       <c r="C266" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="D266" s="44"/>
+      <c r="D266" s="35"/>
       <c r="E266" s="8"/>
       <c r="F266" s="8"/>
     </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A267" s="8"/>
       <c r="B267" s="8"/>
       <c r="C267" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="D267" s="44"/>
+      <c r="D267" s="35"/>
       <c r="E267" s="8"/>
       <c r="F267" s="8">
         <v>5</v>
       </c>
     </row>
-    <row r="268" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A268" s="8"/>
       <c r="B268" s="8"/>
       <c r="C268" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="D268" s="44"/>
+      <c r="D268" s="35"/>
       <c r="E268" s="8"/>
       <c r="F268" s="8"/>
     </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A269" s="8"/>
       <c r="B269" s="8"/>
       <c r="C269" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="D269" s="44"/>
+      <c r="D269" s="35"/>
       <c r="E269" s="8"/>
       <c r="F269" s="8"/>
     </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A270" s="8"/>
       <c r="B270" s="8"/>
       <c r="C270" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="D270" s="44"/>
+      <c r="D270" s="35"/>
       <c r="E270" s="8"/>
       <c r="F270" s="8">
         <v>2</v>
       </c>
     </row>
-    <row r="272" spans="1:7" ht="18" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:7" ht="19" x14ac:dyDescent="0.25">
       <c r="A272" s="5" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A273" s="12" t="s">
         <v>75</v>
       </c>
@@ -5261,7 +5291,7 @@
       <c r="C273" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="D273" s="41" t="s">
+      <c r="D273" s="32" t="s">
         <v>39</v>
       </c>
       <c r="E273" s="12"/>
@@ -5269,11 +5299,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A274" s="12"/>
       <c r="B274" s="12"/>
       <c r="C274" s="12"/>
-      <c r="D274" s="41" t="s">
+      <c r="D274" s="32" t="s">
         <v>101</v>
       </c>
       <c r="E274" s="12"/>
@@ -5281,11 +5311,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A275" s="12"/>
       <c r="B275" s="12"/>
       <c r="C275" s="12"/>
-      <c r="D275" s="41" t="s">
+      <c r="D275" s="32" t="s">
         <v>286</v>
       </c>
       <c r="E275" s="12"/>
@@ -5293,11 +5323,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A276" s="12"/>
       <c r="B276" s="12"/>
       <c r="C276" s="12"/>
-      <c r="D276" s="41" t="s">
+      <c r="D276" s="32" t="s">
         <v>102</v>
       </c>
       <c r="E276" s="12"/>
@@ -5305,11 +5335,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A277" s="12"/>
       <c r="B277" s="12"/>
       <c r="C277" s="12"/>
-      <c r="D277" s="41" t="s">
+      <c r="D277" s="32" t="s">
         <v>288</v>
       </c>
       <c r="E277" s="12"/>
@@ -5317,11 +5347,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A278" s="12"/>
       <c r="B278" s="12"/>
       <c r="C278" s="12"/>
-      <c r="D278" s="41" t="s">
+      <c r="D278" s="32" t="s">
         <v>287</v>
       </c>
       <c r="E278" s="12"/>
@@ -5329,13 +5359,13 @@
         <v>5</v>
       </c>
     </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A279" s="12"/>
       <c r="B279" s="12"/>
       <c r="C279" s="12" t="s">
         <v>289</v>
       </c>
-      <c r="D279" s="41" t="s">
+      <c r="D279" s="32" t="s">
         <v>290</v>
       </c>
       <c r="E279" s="12"/>
@@ -5343,11 +5373,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A280" s="12"/>
       <c r="B280" s="12"/>
       <c r="C280" s="12"/>
-      <c r="D280" s="41" t="s">
+      <c r="D280" s="32" t="s">
         <v>291</v>
       </c>
       <c r="E280" s="12"/>
@@ -5355,11 +5385,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A281" s="12"/>
       <c r="B281" s="12"/>
       <c r="C281" s="12"/>
-      <c r="D281" s="41" t="s">
+      <c r="D281" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E281" s="12"/>
@@ -5367,11 +5397,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A282" s="12"/>
       <c r="B282" s="12"/>
       <c r="C282" s="12"/>
-      <c r="D282" s="41" t="s">
+      <c r="D282" s="32" t="s">
         <v>19</v>
       </c>
       <c r="E282" s="12"/>
@@ -5379,11 +5409,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="283" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A283" s="12"/>
       <c r="B283" s="12"/>
       <c r="C283" s="12"/>
-      <c r="D283" s="41" t="s">
+      <c r="D283" s="32" t="s">
         <v>292</v>
       </c>
       <c r="E283" s="12"/>
@@ -5391,11 +5421,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="284" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A284" s="12"/>
       <c r="B284" s="12"/>
       <c r="C284" s="12"/>
-      <c r="D284" s="42" t="s">
+      <c r="D284" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E284" s="28">
@@ -5403,7 +5433,7 @@
       </c>
       <c r="F284" s="12"/>
     </row>
-    <row r="285" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:6" x14ac:dyDescent="0.2">
       <c r="E285">
         <f>SUM(E273:E283)*E284</f>
         <v>0</v>
@@ -5413,7 +5443,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="286" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A286" s="7" t="s">
         <v>293</v>
       </c>
@@ -5421,13 +5451,13 @@
         <v>74</v>
       </c>
       <c r="C286" s="8"/>
-      <c r="D286" s="44"/>
+      <c r="D286" s="35"/>
       <c r="E286" s="8"/>
       <c r="F286" s="8">
         <v>5</v>
       </c>
     </row>
-    <row r="287" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A287" s="8"/>
       <c r="B287" s="8" t="s">
         <v>21</v>
@@ -5435,77 +5465,77 @@
       <c r="C287" s="8" t="s">
         <v>294</v>
       </c>
-      <c r="D287" s="44"/>
+      <c r="D287" s="35"/>
       <c r="E287" s="8"/>
       <c r="F287" s="8">
         <v>5</v>
       </c>
     </row>
-    <row r="288" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A288" s="8"/>
       <c r="B288" s="8"/>
       <c r="C288" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D288" s="44"/>
+      <c r="D288" s="35"/>
       <c r="E288" s="8"/>
       <c r="F288" s="8">
         <v>5</v>
       </c>
     </row>
-    <row r="289" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A289" s="8"/>
       <c r="B289" s="8"/>
       <c r="C289" s="8" t="s">
         <v>295</v>
       </c>
-      <c r="D289" s="44"/>
+      <c r="D289" s="35"/>
       <c r="E289" s="8"/>
       <c r="F289" s="8">
         <v>5</v>
       </c>
     </row>
-    <row r="290" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A290" s="8"/>
       <c r="B290" s="8"/>
       <c r="C290" s="8" t="s">
         <v>296</v>
       </c>
-      <c r="D290" s="44"/>
+      <c r="D290" s="35"/>
       <c r="E290" s="8"/>
       <c r="F290" s="8">
         <v>5</v>
       </c>
     </row>
-    <row r="291" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A291" s="8"/>
       <c r="B291" s="8"/>
       <c r="C291" s="8" t="s">
         <v>297</v>
       </c>
-      <c r="D291" s="44"/>
+      <c r="D291" s="35"/>
       <c r="E291" s="8"/>
       <c r="F291" s="8">
         <v>5</v>
       </c>
     </row>
-    <row r="292" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A292" s="8"/>
       <c r="B292" s="8"/>
       <c r="C292" s="8" t="s">
         <v>298</v>
       </c>
-      <c r="D292" s="44"/>
+      <c r="D292" s="35"/>
       <c r="E292" s="8"/>
       <c r="F292" s="8">
         <v>5</v>
       </c>
     </row>
-    <row r="293" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A293" s="8"/>
       <c r="B293" s="8"/>
       <c r="C293" s="8"/>
-      <c r="D293" s="42" t="s">
+      <c r="D293" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E293" s="28">
@@ -5513,7 +5543,7 @@
       </c>
       <c r="F293" s="8"/>
     </row>
-    <row r="294" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:6" x14ac:dyDescent="0.2">
       <c r="E294">
         <f>SUM(E286:E292)*E293</f>
         <v>0</v>
@@ -5523,7 +5553,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="296" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A296" s="7" t="s">
         <v>299</v>
       </c>
@@ -5531,13 +5561,13 @@
         <v>300</v>
       </c>
       <c r="C296" s="8"/>
-      <c r="D296" s="44"/>
+      <c r="D296" s="35"/>
       <c r="E296" s="8"/>
       <c r="F296" s="8">
         <v>5</v>
       </c>
     </row>
-    <row r="297" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A297" s="7" t="s">
         <v>301</v>
       </c>
@@ -5545,41 +5575,41 @@
         <v>302</v>
       </c>
       <c r="C297" s="8"/>
-      <c r="D297" s="44"/>
+      <c r="D297" s="35"/>
       <c r="E297" s="8"/>
       <c r="F297" s="8">
         <v>5</v>
       </c>
     </row>
-    <row r="298" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A298" s="8"/>
       <c r="B298" s="8" t="s">
         <v>303</v>
       </c>
       <c r="C298" s="8"/>
-      <c r="D298" s="44"/>
+      <c r="D298" s="35"/>
       <c r="E298" s="8"/>
       <c r="F298" s="8">
         <v>5</v>
       </c>
     </row>
-    <row r="299" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A299" s="8"/>
       <c r="B299" s="8" t="s">
         <v>304</v>
       </c>
       <c r="C299" s="8"/>
-      <c r="D299" s="44"/>
+      <c r="D299" s="35"/>
       <c r="E299" s="8"/>
       <c r="F299" s="8">
         <v>5</v>
       </c>
     </row>
-    <row r="300" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A300" s="8"/>
       <c r="B300" s="8"/>
       <c r="C300" s="8"/>
-      <c r="D300" s="42" t="s">
+      <c r="D300" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E300" s="28">
@@ -5587,7 +5617,7 @@
       </c>
       <c r="F300" s="8"/>
     </row>
-    <row r="301" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:6" x14ac:dyDescent="0.2">
       <c r="E301">
         <f>SUM(E296:E299)*E300</f>
         <v>0</v>
@@ -5597,7 +5627,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="303" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A303" s="16" t="s">
         <v>305</v>
       </c>
@@ -5611,7 +5641,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="304" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A304" s="14"/>
       <c r="B304" s="14" t="s">
         <v>307</v>
@@ -5623,7 +5653,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="305" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A305" s="14"/>
       <c r="B305" s="14" t="s">
         <v>134</v>
@@ -5635,7 +5665,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="306" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A306" s="16" t="s">
         <v>308</v>
       </c>
@@ -5649,7 +5679,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="307" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A307" s="14"/>
       <c r="B307" s="14" t="s">
         <v>310</v>
@@ -5661,7 +5691,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="308" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A308" s="16" t="s">
         <v>359</v>
       </c>
@@ -5677,7 +5707,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="309" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A309" s="14"/>
       <c r="B309" s="14"/>
       <c r="C309" s="14" t="s">
@@ -5689,7 +5719,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="310" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A310" s="14"/>
       <c r="B310" s="14"/>
       <c r="C310" s="14" t="s">
@@ -5701,11 +5731,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="311" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A311" s="14"/>
       <c r="B311" s="14"/>
       <c r="C311" s="14"/>
-      <c r="D311" s="42" t="s">
+      <c r="D311" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E311" s="28">
@@ -5713,7 +5743,7 @@
       </c>
       <c r="F311" s="14"/>
     </row>
-    <row r="312" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:6" x14ac:dyDescent="0.2">
       <c r="E312">
         <f>SUM(E303:E310)*E311</f>
         <v>0</v>
@@ -5723,7 +5753,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="313" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A313" s="11" t="s">
         <v>35</v>
       </c>
@@ -5731,31 +5761,31 @@
         <v>311</v>
       </c>
       <c r="C313" s="12"/>
-      <c r="D313" s="41"/>
+      <c r="D313" s="32"/>
       <c r="E313" s="12"/>
       <c r="F313" s="12">
         <v>5</v>
       </c>
     </row>
-    <row r="314" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A314" s="12"/>
       <c r="B314" s="12" t="s">
         <v>251</v>
       </c>
       <c r="C314" s="12"/>
-      <c r="D314" s="41"/>
+      <c r="D314" s="32"/>
       <c r="E314" s="12"/>
       <c r="F314" s="12">
         <v>10</v>
       </c>
     </row>
-    <row r="315" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A315" s="11"/>
       <c r="B315" s="12" t="s">
         <v>320</v>
       </c>
       <c r="C315" s="12"/>
-      <c r="D315" s="41"/>
+      <c r="D315" s="32"/>
       <c r="E315" s="12" t="s">
         <v>319</v>
       </c>
@@ -5763,13 +5793,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="316" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A316" s="12"/>
       <c r="B316" s="12" t="s">
         <v>312</v>
       </c>
       <c r="C316" s="12"/>
-      <c r="D316" s="41"/>
+      <c r="D316" s="32"/>
       <c r="E316" s="12" t="s">
         <v>319</v>
       </c>
@@ -5777,13 +5807,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="317" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A317" s="11"/>
       <c r="B317" s="12" t="s">
         <v>230</v>
       </c>
       <c r="C317" s="12"/>
-      <c r="D317" s="41"/>
+      <c r="D317" s="32"/>
       <c r="E317" s="12" t="s">
         <v>319</v>
       </c>
@@ -5791,13 +5821,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="318" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A318" s="11"/>
       <c r="B318" s="12" t="s">
         <v>321</v>
       </c>
       <c r="C318" s="12"/>
-      <c r="D318" s="41"/>
+      <c r="D318" s="32"/>
       <c r="E318" s="12" t="s">
         <v>319</v>
       </c>
@@ -5805,59 +5835,59 @@
         <v>5</v>
       </c>
     </row>
-    <row r="319" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A319" s="11"/>
       <c r="B319" s="12" t="s">
         <v>322</v>
       </c>
       <c r="C319" s="12"/>
-      <c r="D319" s="41"/>
+      <c r="D319" s="32"/>
       <c r="E319" s="12"/>
       <c r="F319" s="12">
         <v>5</v>
       </c>
     </row>
-    <row r="320" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A320" s="12"/>
       <c r="B320" s="12" t="s">
         <v>313</v>
       </c>
       <c r="C320" s="12"/>
-      <c r="D320" s="41"/>
+      <c r="D320" s="32"/>
       <c r="E320" s="12"/>
       <c r="F320" s="12">
         <v>5</v>
       </c>
     </row>
-    <row r="321" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A321" s="12"/>
       <c r="B321" s="12" t="s">
         <v>314</v>
       </c>
       <c r="C321" s="12"/>
-      <c r="D321" s="41"/>
+      <c r="D321" s="32"/>
       <c r="E321" s="12"/>
       <c r="F321" s="12">
         <v>5</v>
       </c>
     </row>
-    <row r="322" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A322" s="12"/>
       <c r="B322" s="12" t="s">
         <v>40</v>
       </c>
       <c r="C322" s="12"/>
-      <c r="D322" s="41"/>
+      <c r="D322" s="32"/>
       <c r="E322" s="12"/>
       <c r="F322" s="12">
         <v>10</v>
       </c>
     </row>
-    <row r="323" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A323" s="12"/>
       <c r="B323" s="12"/>
       <c r="C323" s="12"/>
-      <c r="D323" s="42" t="s">
+      <c r="D323" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E323" s="28">
@@ -5865,7 +5895,7 @@
       </c>
       <c r="F323" s="12"/>
     </row>
-    <row r="324" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:6" x14ac:dyDescent="0.2">
       <c r="E324">
         <f>SUM(E313:E322)*E323</f>
         <v>0</v>
@@ -5875,7 +5905,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="326" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A326" s="7" t="s">
         <v>347</v>
       </c>
@@ -5883,25 +5913,25 @@
         <v>190</v>
       </c>
       <c r="C326" s="8"/>
-      <c r="D326" s="44"/>
+      <c r="D326" s="35"/>
       <c r="E326" s="8"/>
       <c r="F326" s="8">
         <v>25</v>
       </c>
     </row>
-    <row r="327" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A327" s="7"/>
       <c r="B327" s="8" t="s">
         <v>191</v>
       </c>
       <c r="C327" s="8"/>
-      <c r="D327" s="44"/>
+      <c r="D327" s="35"/>
       <c r="E327" s="8"/>
       <c r="F327" s="8">
         <v>25</v>
       </c>
     </row>
-    <row r="328" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A328" s="7"/>
       <c r="B328" s="8" t="s">
         <v>192</v>
@@ -5909,65 +5939,65 @@
       <c r="C328" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="D328" s="44"/>
+      <c r="D328" s="35"/>
       <c r="E328" s="8"/>
       <c r="F328" s="8">
         <v>10</v>
       </c>
     </row>
-    <row r="329" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A329" s="7"/>
       <c r="B329" s="8"/>
       <c r="C329" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="D329" s="44"/>
+      <c r="D329" s="35"/>
       <c r="E329" s="8"/>
       <c r="F329" s="8">
         <v>10</v>
       </c>
     </row>
-    <row r="330" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A330" s="7"/>
       <c r="B330" s="8"/>
       <c r="C330" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="D330" s="44"/>
+      <c r="D330" s="35"/>
       <c r="E330" s="8"/>
       <c r="F330" s="8">
         <v>10</v>
       </c>
     </row>
-    <row r="331" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A331" s="7"/>
       <c r="B331" s="8"/>
       <c r="C331" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="D331" s="44"/>
+      <c r="D331" s="35"/>
       <c r="E331" s="8"/>
       <c r="F331" s="8">
         <v>10</v>
       </c>
     </row>
-    <row r="332" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A332" s="7"/>
       <c r="B332" s="8"/>
       <c r="C332" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D332" s="44"/>
+      <c r="D332" s="35"/>
       <c r="E332" s="8"/>
       <c r="F332" s="8">
         <v>10</v>
       </c>
     </row>
-    <row r="333" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A333" s="7"/>
       <c r="B333" s="8"/>
       <c r="C333" s="8"/>
-      <c r="D333" s="42" t="s">
+      <c r="D333" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E333" s="28">
@@ -5975,7 +6005,7 @@
       </c>
       <c r="F333" s="8"/>
     </row>
-    <row r="334" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A334" s="1"/>
       <c r="E334">
         <f>SUM(E326:E332)*E333</f>
@@ -5986,7 +6016,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="335" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A335" s="7" t="s">
         <v>78</v>
       </c>
@@ -5994,73 +6024,73 @@
         <v>13</v>
       </c>
       <c r="C335" s="8"/>
-      <c r="D335" s="44"/>
+      <c r="D335" s="35"/>
       <c r="E335" s="8"/>
       <c r="F335" s="8">
         <v>10</v>
       </c>
     </row>
-    <row r="336" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A336" s="7"/>
       <c r="B336" s="8" t="s">
         <v>46</v>
       </c>
       <c r="C336" s="8"/>
-      <c r="D336" s="44"/>
+      <c r="D336" s="35"/>
       <c r="E336" s="8"/>
       <c r="F336" s="8">
         <v>5</v>
       </c>
     </row>
-    <row r="337" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A337" s="7"/>
       <c r="B337" s="8" t="s">
         <v>358</v>
       </c>
       <c r="C337" s="8"/>
-      <c r="D337" s="44"/>
+      <c r="D337" s="35"/>
       <c r="E337" s="8"/>
       <c r="F337" s="8">
         <v>15</v>
       </c>
     </row>
-    <row r="338" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A338" s="7"/>
       <c r="B338" s="8" t="s">
         <v>169</v>
       </c>
       <c r="C338" s="8"/>
-      <c r="D338" s="44"/>
+      <c r="D338" s="35"/>
       <c r="E338" s="8"/>
       <c r="F338" s="8">
         <v>5</v>
       </c>
     </row>
-    <row r="339" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A339" s="7"/>
       <c r="B339" s="8" t="s">
         <v>77</v>
       </c>
       <c r="C339" s="8"/>
-      <c r="D339" s="44"/>
+      <c r="D339" s="35"/>
       <c r="E339" s="8"/>
       <c r="F339" s="8">
         <v>5</v>
       </c>
     </row>
-    <row r="340" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A340" s="7"/>
       <c r="B340" s="8" t="s">
         <v>79</v>
       </c>
       <c r="C340" s="8"/>
-      <c r="D340" s="44"/>
+      <c r="D340" s="35"/>
       <c r="E340" s="8"/>
       <c r="F340" s="8">
         <v>25</v>
       </c>
     </row>
-    <row r="341" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A341" s="7"/>
       <c r="B341" s="7" t="s">
         <v>57</v>
@@ -6068,67 +6098,67 @@
       <c r="C341" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="D341" s="44"/>
+      <c r="D341" s="35"/>
       <c r="E341" s="8"/>
       <c r="F341" s="8">
         <v>5</v>
       </c>
     </row>
-    <row r="342" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A342" s="7"/>
       <c r="B342" s="7"/>
       <c r="C342" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="D342" s="44"/>
+      <c r="D342" s="35"/>
       <c r="E342" s="8"/>
       <c r="F342" s="8">
         <v>10</v>
       </c>
     </row>
-    <row r="343" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A343" s="7"/>
       <c r="B343" s="7"/>
       <c r="C343" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="D343" s="44"/>
+      <c r="D343" s="35"/>
       <c r="E343" s="8"/>
       <c r="F343" s="8">
         <v>25</v>
       </c>
     </row>
-    <row r="344" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A344" s="7"/>
       <c r="B344" s="7"/>
       <c r="C344" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D344" s="44"/>
+      <c r="D344" s="35"/>
       <c r="E344" s="8"/>
       <c r="F344" s="8">
         <v>20</v>
       </c>
     </row>
-    <row r="345" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A345" s="7"/>
       <c r="B345" s="7"/>
       <c r="C345" s="8" t="s">
         <v>231</v>
       </c>
-      <c r="D345" s="44"/>
+      <c r="D345" s="35"/>
       <c r="E345" s="8"/>
       <c r="F345" s="8">
         <v>20</v>
       </c>
     </row>
-    <row r="346" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A346" s="7"/>
       <c r="B346" s="7"/>
       <c r="C346" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="D346" s="44" t="s">
+      <c r="D346" s="35" t="s">
         <v>69</v>
       </c>
       <c r="E346" s="8"/>
@@ -6136,11 +6166,11 @@
         <v>3</v>
       </c>
     </row>
-    <row r="347" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A347" s="7"/>
       <c r="B347" s="7"/>
       <c r="C347" s="8"/>
-      <c r="D347" s="44" t="s">
+      <c r="D347" s="35" t="s">
         <v>70</v>
       </c>
       <c r="E347" s="8"/>
@@ -6148,11 +6178,11 @@
         <v>3</v>
       </c>
     </row>
-    <row r="348" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A348" s="7"/>
       <c r="B348" s="7"/>
       <c r="C348" s="8"/>
-      <c r="D348" s="44" t="s">
+      <c r="D348" s="35" t="s">
         <v>71</v>
       </c>
       <c r="E348" s="8"/>
@@ -6160,11 +6190,11 @@
         <v>3</v>
       </c>
     </row>
-    <row r="349" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A349" s="7"/>
       <c r="B349" s="7"/>
       <c r="C349" s="8"/>
-      <c r="D349" s="44" t="s">
+      <c r="D349" s="35" t="s">
         <v>54</v>
       </c>
       <c r="E349" s="8"/>
@@ -6172,11 +6202,11 @@
         <v>3</v>
       </c>
     </row>
-    <row r="350" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A350" s="7"/>
       <c r="B350" s="7"/>
       <c r="C350" s="8"/>
-      <c r="D350" s="44" t="s">
+      <c r="D350" s="35" t="s">
         <v>72</v>
       </c>
       <c r="E350" s="8"/>
@@ -6184,11 +6214,11 @@
         <v>3</v>
       </c>
     </row>
-    <row r="351" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A351" s="7"/>
       <c r="B351" s="7"/>
       <c r="C351" s="8"/>
-      <c r="D351" s="42" t="s">
+      <c r="D351" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E351" s="28">
@@ -6196,7 +6226,7 @@
       </c>
       <c r="F351" s="8"/>
     </row>
-    <row r="352" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:6" x14ac:dyDescent="0.2">
       <c r="E352">
         <f>SUM(E335:E350)*E351</f>
         <v>0</v>
@@ -6206,12 +6236,12 @@
         <v>160</v>
       </c>
     </row>
-    <row r="353" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:6" ht="19" x14ac:dyDescent="0.25">
       <c r="A353" s="5" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="354" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A354" s="13" t="s">
         <v>220</v>
       </c>
@@ -6219,13 +6249,13 @@
         <v>221</v>
       </c>
       <c r="C354" s="13"/>
-      <c r="D354" s="40"/>
+      <c r="D354" s="31"/>
       <c r="E354" s="13"/>
       <c r="F354" s="13">
         <v>10</v>
       </c>
     </row>
-    <row r="355" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A355" s="13"/>
       <c r="B355" s="13" t="s">
         <v>387</v>
@@ -6233,37 +6263,37 @@
       <c r="C355" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="D355" s="40"/>
+      <c r="D355" s="31"/>
       <c r="E355" s="13"/>
       <c r="F355" s="13">
         <v>30</v>
       </c>
     </row>
-    <row r="356" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A356" s="13"/>
       <c r="B356" s="13"/>
       <c r="C356" s="13" t="s">
         <v>222</v>
       </c>
-      <c r="D356" s="40"/>
+      <c r="D356" s="31"/>
       <c r="E356" s="13"/>
       <c r="F356" s="13">
         <v>30</v>
       </c>
     </row>
-    <row r="357" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A357" s="13"/>
       <c r="B357" s="13"/>
       <c r="C357" s="13" t="s">
         <v>223</v>
       </c>
-      <c r="D357" s="40"/>
+      <c r="D357" s="31"/>
       <c r="E357" s="13"/>
       <c r="F357" s="13">
         <v>30</v>
       </c>
     </row>
-    <row r="358" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A358" s="13"/>
       <c r="B358" s="13" t="s">
         <v>388</v>
@@ -6271,41 +6301,41 @@
       <c r="C358" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="D358" s="40"/>
+      <c r="D358" s="31"/>
       <c r="E358" s="13"/>
       <c r="F358" s="13">
         <v>30</v>
       </c>
     </row>
-    <row r="359" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A359" s="13"/>
       <c r="B359" s="13"/>
       <c r="C359" s="13" t="s">
         <v>222</v>
       </c>
-      <c r="D359" s="40"/>
+      <c r="D359" s="31"/>
       <c r="E359" s="13"/>
       <c r="F359" s="13">
         <v>30</v>
       </c>
     </row>
-    <row r="360" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A360" s="13"/>
       <c r="B360" s="13"/>
       <c r="C360" s="13" t="s">
         <v>223</v>
       </c>
-      <c r="D360" s="40"/>
+      <c r="D360" s="31"/>
       <c r="E360" s="13"/>
       <c r="F360" s="13">
         <v>30</v>
       </c>
     </row>
-    <row r="361" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A361" s="13"/>
       <c r="B361" s="13"/>
       <c r="C361" s="13"/>
-      <c r="D361" s="42" t="s">
+      <c r="D361" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E361" s="28">
@@ -6313,7 +6343,7 @@
       </c>
       <c r="F361" s="13"/>
     </row>
-    <row r="362" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:6" x14ac:dyDescent="0.2">
       <c r="E362">
         <f>SUM(E354:E360)*E361</f>
         <v>0</v>
@@ -6323,13 +6353,13 @@
         <v>190</v>
       </c>
     </row>
-    <row r="363" spans="1:6" s="18" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:6" s="18" customFormat="1" ht="19" x14ac:dyDescent="0.25">
       <c r="A363" s="5" t="s">
         <v>283</v>
       </c>
-      <c r="D363" s="46"/>
-    </row>
-    <row r="364" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D363" s="37"/>
+    </row>
+    <row r="364" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A364" s="15" t="s">
         <v>361</v>
       </c>
@@ -6337,7 +6367,7 @@
       <c r="C364" s="13" t="s">
         <v>183</v>
       </c>
-      <c r="D364" s="40"/>
+      <c r="D364" s="31"/>
       <c r="E364" s="13">
         <v>0</v>
       </c>
@@ -6345,13 +6375,13 @@
         <v>5</v>
       </c>
     </row>
-    <row r="365" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A365" s="13"/>
       <c r="B365" s="13"/>
       <c r="C365" s="13" t="s">
         <v>187</v>
       </c>
-      <c r="D365" s="40"/>
+      <c r="D365" s="31"/>
       <c r="E365" s="13">
         <v>0</v>
       </c>
@@ -6359,13 +6389,13 @@
         <v>5</v>
       </c>
     </row>
-    <row r="366" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A366" s="13"/>
       <c r="B366" s="13"/>
       <c r="C366" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="D366" s="40"/>
+      <c r="D366" s="31"/>
       <c r="E366" s="13">
         <v>0</v>
       </c>
@@ -6373,13 +6403,13 @@
         <v>5</v>
       </c>
     </row>
-    <row r="367" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A367" s="13"/>
       <c r="B367" s="13"/>
       <c r="C367" s="13" t="s">
         <v>188</v>
       </c>
-      <c r="D367" s="40"/>
+      <c r="D367" s="31"/>
       <c r="E367" s="13">
         <v>0</v>
       </c>
@@ -6387,13 +6417,13 @@
         <v>5</v>
       </c>
     </row>
-    <row r="368" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A368" s="13"/>
       <c r="B368" s="13"/>
       <c r="C368" s="13" t="s">
         <v>189</v>
       </c>
-      <c r="D368" s="40"/>
+      <c r="D368" s="31"/>
       <c r="E368" s="13">
         <v>0</v>
       </c>
@@ -6401,13 +6431,13 @@
         <v>5</v>
       </c>
     </row>
-    <row r="369" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A369" s="13"/>
       <c r="B369" s="13"/>
       <c r="C369" s="13" t="s">
         <v>190</v>
       </c>
-      <c r="D369" s="40"/>
+      <c r="D369" s="31"/>
       <c r="E369" s="13">
         <v>0</v>
       </c>
@@ -6415,11 +6445,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="370" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A370" s="13"/>
       <c r="B370" s="13"/>
       <c r="C370" s="13"/>
-      <c r="D370" s="42" t="s">
+      <c r="D370" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E370" s="28">
@@ -6427,7 +6457,7 @@
       </c>
       <c r="F370" s="13"/>
     </row>
-    <row r="371" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:6" x14ac:dyDescent="0.2">
       <c r="E371">
         <f>SUM(E364:E369)*E370</f>
         <v>0</v>
@@ -6437,7 +6467,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="372" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A372" s="15" t="s">
         <v>44</v>
       </c>
@@ -6445,45 +6475,45 @@
         <v>356</v>
       </c>
       <c r="C372" s="17"/>
-      <c r="D372" s="40"/>
+      <c r="D372" s="31"/>
       <c r="E372" s="13"/>
       <c r="F372" s="13">
         <v>10</v>
       </c>
     </row>
-    <row r="373" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A373" s="15"/>
       <c r="B373" s="17" t="s">
         <v>77</v>
       </c>
       <c r="C373" s="17"/>
-      <c r="D373" s="40"/>
+      <c r="D373" s="31"/>
       <c r="E373" s="13"/>
       <c r="F373" s="13">
         <v>5</v>
       </c>
     </row>
-    <row r="374" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A374" s="15"/>
       <c r="B374" s="17" t="s">
         <v>124</v>
       </c>
       <c r="C374" s="17"/>
-      <c r="D374" s="40"/>
+      <c r="D374" s="31"/>
       <c r="E374" s="13"/>
       <c r="F374" s="13">
         <v>5</v>
       </c>
     </row>
-    <row r="375" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A375" s="15"/>
       <c r="B375" s="13"/>
       <c r="C375" s="13"/>
-      <c r="D375" s="40"/>
+      <c r="D375" s="31"/>
       <c r="E375" s="13"/>
       <c r="F375" s="13"/>
     </row>
-    <row r="376" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A376" s="15" t="s">
         <v>122</v>
       </c>
@@ -6491,45 +6521,45 @@
         <v>77</v>
       </c>
       <c r="C376" s="13"/>
-      <c r="D376" s="40"/>
+      <c r="D376" s="31"/>
       <c r="E376" s="13"/>
       <c r="F376" s="13">
         <v>5</v>
       </c>
     </row>
-    <row r="377" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A377" s="15"/>
       <c r="B377" s="13" t="s">
         <v>123</v>
       </c>
       <c r="C377" s="13"/>
-      <c r="D377" s="40"/>
+      <c r="D377" s="31"/>
       <c r="E377" s="13"/>
       <c r="F377" s="13">
         <v>5</v>
       </c>
     </row>
-    <row r="378" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A378" s="15"/>
       <c r="B378" s="13" t="s">
         <v>124</v>
       </c>
       <c r="C378" s="13"/>
-      <c r="D378" s="40"/>
+      <c r="D378" s="31"/>
       <c r="E378" s="13"/>
       <c r="F378" s="13">
         <v>5</v>
       </c>
     </row>
-    <row r="379" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A379" s="15"/>
       <c r="B379" s="13"/>
       <c r="C379" s="13"/>
-      <c r="D379" s="40"/>
+      <c r="D379" s="31"/>
       <c r="E379" s="13"/>
       <c r="F379" s="13"/>
     </row>
-    <row r="380" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A380" s="15" t="s">
         <v>227</v>
       </c>
@@ -6537,41 +6567,41 @@
         <v>77</v>
       </c>
       <c r="C380" s="13"/>
-      <c r="D380" s="40"/>
+      <c r="D380" s="31"/>
       <c r="E380" s="13"/>
       <c r="F380" s="13">
         <v>5</v>
       </c>
     </row>
-    <row r="381" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A381" s="15"/>
       <c r="B381" s="13" t="s">
         <v>123</v>
       </c>
       <c r="C381" s="13"/>
-      <c r="D381" s="40"/>
+      <c r="D381" s="31"/>
       <c r="E381" s="13"/>
       <c r="F381" s="13">
         <v>5</v>
       </c>
     </row>
-    <row r="382" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A382" s="15"/>
       <c r="B382" s="13" t="s">
         <v>124</v>
       </c>
       <c r="C382" s="13"/>
-      <c r="D382" s="40"/>
+      <c r="D382" s="31"/>
       <c r="E382" s="13"/>
       <c r="F382" s="13">
         <v>5</v>
       </c>
     </row>
-    <row r="383" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A383" s="15"/>
       <c r="B383" s="13"/>
       <c r="C383" s="13"/>
-      <c r="D383" s="42" t="s">
+      <c r="D383" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E383" s="28">
@@ -6579,7 +6609,7 @@
       </c>
       <c r="F383" s="13"/>
     </row>
-    <row r="384" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A384" s="1"/>
       <c r="E384">
         <f>SUM(E372:E382)*E383</f>
@@ -6590,7 +6620,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="385" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A385" s="16" t="s">
         <v>45</v>
       </c>
@@ -6605,7 +6635,7 @@
       </c>
       <c r="M385" s="20"/>
     </row>
-    <row r="386" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A386" s="16" t="s">
         <v>357</v>
       </c>
@@ -6620,11 +6650,11 @@
       </c>
       <c r="M386" s="20"/>
     </row>
-    <row r="387" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A387" s="16"/>
       <c r="B387" s="14"/>
       <c r="C387" s="14"/>
-      <c r="D387" s="42" t="s">
+      <c r="D387" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E387" s="28">
@@ -6633,7 +6663,7 @@
       <c r="F387" s="14"/>
       <c r="M387" s="20"/>
     </row>
-    <row r="388" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A388" s="1"/>
       <c r="E388">
         <f>SUM(E385:E386)*E387</f>
@@ -6645,12 +6675,12 @@
       </c>
       <c r="M388" s="20"/>
     </row>
-    <row r="391" spans="1:13" ht="18" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:13" ht="19" x14ac:dyDescent="0.25">
       <c r="A391" s="5" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="392" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A392" s="11" t="s">
         <v>104</v>
       </c>
@@ -6658,115 +6688,115 @@
         <v>105</v>
       </c>
       <c r="C392" s="12"/>
-      <c r="D392" s="41"/>
+      <c r="D392" s="32"/>
       <c r="E392" s="12"/>
       <c r="F392" s="12">
         <v>10</v>
       </c>
     </row>
-    <row r="393" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A393" s="12"/>
       <c r="B393" s="12" t="s">
         <v>106</v>
       </c>
       <c r="C393" s="12"/>
-      <c r="D393" s="41"/>
+      <c r="D393" s="32"/>
       <c r="E393" s="12"/>
       <c r="F393" s="12">
         <v>10</v>
       </c>
     </row>
-    <row r="394" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A394" s="12"/>
       <c r="B394" s="12" t="s">
         <v>107</v>
       </c>
       <c r="C394" s="12"/>
-      <c r="D394" s="41"/>
+      <c r="D394" s="32"/>
       <c r="E394" s="12"/>
       <c r="F394" s="12">
         <v>10</v>
       </c>
     </row>
-    <row r="395" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A395" s="12"/>
       <c r="B395" s="12" t="s">
         <v>108</v>
       </c>
       <c r="C395" s="12"/>
-      <c r="D395" s="41"/>
+      <c r="D395" s="32"/>
       <c r="E395" s="12"/>
       <c r="F395" s="12">
         <v>10</v>
       </c>
     </row>
-    <row r="396" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A396" s="11" t="s">
         <v>120</v>
       </c>
       <c r="B396" s="12"/>
       <c r="C396" s="12"/>
-      <c r="D396" s="41"/>
+      <c r="D396" s="32"/>
       <c r="E396" s="12"/>
       <c r="F396" s="12"/>
     </row>
-    <row r="397" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A397" s="11"/>
       <c r="B397" s="12" t="s">
         <v>142</v>
       </c>
       <c r="C397" s="12"/>
-      <c r="D397" s="41"/>
+      <c r="D397" s="32"/>
       <c r="E397" s="12"/>
       <c r="F397" s="12">
         <v>5</v>
       </c>
     </row>
-    <row r="398" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A398" s="12"/>
       <c r="B398" s="12" t="s">
         <v>143</v>
       </c>
       <c r="C398" s="12"/>
-      <c r="D398" s="41"/>
+      <c r="D398" s="32"/>
       <c r="E398" s="12"/>
       <c r="F398" s="12">
         <v>15</v>
       </c>
     </row>
-    <row r="399" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A399" s="12"/>
       <c r="B399" s="12" t="s">
         <v>144</v>
       </c>
       <c r="C399" s="12"/>
-      <c r="D399" s="41"/>
+      <c r="D399" s="32"/>
       <c r="E399" s="12"/>
       <c r="F399" s="12">
         <v>20</v>
       </c>
     </row>
-    <row r="400" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A400" s="12"/>
       <c r="B400" s="12" t="s">
         <v>145</v>
       </c>
       <c r="C400" s="12"/>
-      <c r="D400" s="41"/>
+      <c r="D400" s="32"/>
       <c r="E400" s="12"/>
       <c r="F400" s="12">
         <v>5</v>
       </c>
     </row>
-    <row r="401" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A401" s="12"/>
       <c r="B401" s="12"/>
       <c r="C401" s="12"/>
-      <c r="D401" s="41"/>
+      <c r="D401" s="32"/>
       <c r="E401" s="12"/>
       <c r="F401" s="12"/>
     </row>
-    <row r="402" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A402" s="12" t="s">
         <v>146</v>
       </c>
@@ -6774,41 +6804,41 @@
         <v>147</v>
       </c>
       <c r="C402" s="12"/>
-      <c r="D402" s="41"/>
+      <c r="D402" s="32"/>
       <c r="E402" s="12"/>
       <c r="F402" s="12">
         <v>5</v>
       </c>
     </row>
-    <row r="403" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A403" s="12"/>
       <c r="B403" s="12" t="s">
         <v>148</v>
       </c>
       <c r="C403" s="12"/>
-      <c r="D403" s="41"/>
+      <c r="D403" s="32"/>
       <c r="E403" s="12"/>
       <c r="F403" s="12">
         <v>15</v>
       </c>
     </row>
-    <row r="404" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A404" s="12"/>
       <c r="B404" s="12" t="s">
         <v>149</v>
       </c>
       <c r="C404" s="12"/>
-      <c r="D404" s="41"/>
+      <c r="D404" s="32"/>
       <c r="E404" s="12"/>
       <c r="F404" s="12">
         <v>15</v>
       </c>
     </row>
-    <row r="405" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A405" s="12"/>
       <c r="B405" s="12"/>
       <c r="C405" s="12"/>
-      <c r="D405" s="42" t="s">
+      <c r="D405" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E405" s="28">
@@ -6816,7 +6846,7 @@
       </c>
       <c r="F405" s="12"/>
     </row>
-    <row r="406" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:6" x14ac:dyDescent="0.2">
       <c r="E406">
         <f>SUM(E392:E404)*E405</f>
         <v>0</v>
@@ -6826,12 +6856,12 @@
         <v>120</v>
       </c>
     </row>
-    <row r="407" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:6" ht="19" x14ac:dyDescent="0.25">
       <c r="A407" s="5" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="408" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A408" s="7" t="s">
         <v>40</v>
       </c>
@@ -6841,113 +6871,113 @@
       <c r="C408" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="D408" s="44"/>
+      <c r="D408" s="35"/>
       <c r="E408" s="8"/>
       <c r="F408" s="8">
         <v>2</v>
       </c>
     </row>
-    <row r="409" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A409" s="7"/>
       <c r="B409" s="8"/>
       <c r="C409" s="8" t="s">
         <v>209</v>
       </c>
-      <c r="D409" s="44"/>
+      <c r="D409" s="35"/>
       <c r="E409" s="8"/>
       <c r="F409" s="8">
         <v>2</v>
       </c>
     </row>
-    <row r="410" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A410" s="7"/>
       <c r="B410" s="8"/>
       <c r="C410" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="D410" s="44"/>
+      <c r="D410" s="35"/>
       <c r="E410" s="8"/>
       <c r="F410" s="8">
         <v>2</v>
       </c>
     </row>
-    <row r="411" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A411" s="7"/>
       <c r="B411" s="8"/>
       <c r="C411" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="D411" s="44"/>
+      <c r="D411" s="35"/>
       <c r="E411" s="8"/>
       <c r="F411" s="8">
         <v>2</v>
       </c>
     </row>
-    <row r="412" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A412" s="7"/>
       <c r="B412" s="8"/>
       <c r="C412" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="D412" s="44"/>
+      <c r="D412" s="35"/>
       <c r="E412" s="8"/>
       <c r="F412" s="8">
         <v>2</v>
       </c>
     </row>
-    <row r="413" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A413" s="8"/>
       <c r="B413" s="8" t="s">
         <v>13</v>
       </c>
       <c r="C413" s="8"/>
-      <c r="D413" s="44"/>
+      <c r="D413" s="35"/>
       <c r="E413" s="8"/>
       <c r="F413" s="8">
         <v>5</v>
       </c>
     </row>
-    <row r="414" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A414" s="8"/>
       <c r="B414" s="8" t="s">
         <v>43</v>
       </c>
       <c r="C414" s="8"/>
-      <c r="D414" s="44"/>
+      <c r="D414" s="35"/>
       <c r="E414" s="8"/>
       <c r="F414" s="8">
         <v>5</v>
       </c>
     </row>
-    <row r="415" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A415" s="8"/>
       <c r="B415" s="8" t="s">
         <v>80</v>
       </c>
       <c r="C415" s="8"/>
-      <c r="D415" s="44"/>
+      <c r="D415" s="35"/>
       <c r="E415" s="8"/>
       <c r="F415" s="8">
         <v>5</v>
       </c>
     </row>
-    <row r="416" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A416" s="8"/>
       <c r="B416" s="8" t="s">
         <v>99</v>
       </c>
       <c r="C416" s="8"/>
-      <c r="D416" s="44"/>
+      <c r="D416" s="35"/>
       <c r="E416" s="8"/>
       <c r="F416" s="8">
         <v>5</v>
       </c>
     </row>
-    <row r="417" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A417" s="8"/>
       <c r="B417" s="8"/>
       <c r="C417" s="8"/>
-      <c r="D417" s="42" t="s">
+      <c r="D417" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E417" s="28">
@@ -6955,7 +6985,7 @@
       </c>
       <c r="F417" s="8"/>
     </row>
-    <row r="418" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:6" x14ac:dyDescent="0.2">
       <c r="E418">
         <f>SUM(E408:E416)*E417</f>
         <v>0</v>
@@ -6965,7 +6995,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="419" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A419" s="14" t="s">
         <v>150</v>
       </c>
@@ -6979,7 +7009,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="420" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A420" s="14"/>
       <c r="B420" s="14" t="s">
         <v>152</v>
@@ -6991,7 +7021,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="421" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A421" s="14"/>
       <c r="B421" s="14" t="s">
         <v>153</v>
@@ -7003,7 +7033,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="422" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A422" s="14"/>
       <c r="B422" s="14" t="s">
         <v>154</v>
@@ -7015,7 +7045,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="423" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A423" s="14"/>
       <c r="B423" s="14" t="s">
         <v>155</v>
@@ -7027,7 +7057,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="424" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A424" s="14"/>
       <c r="B424" s="14" t="s">
         <v>258</v>
@@ -7039,7 +7069,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="425" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A425" s="14"/>
       <c r="B425" s="14" t="s">
         <v>156</v>
@@ -7051,7 +7081,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="426" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A426" s="14"/>
       <c r="B426" s="14" t="s">
         <v>259</v>
@@ -7063,7 +7093,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="427" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A427" s="14"/>
       <c r="B427" s="14" t="s">
         <v>157</v>
@@ -7075,11 +7105,11 @@
         <v>4</v>
       </c>
     </row>
-    <row r="428" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A428" s="14"/>
       <c r="B428" s="14"/>
       <c r="C428" s="14"/>
-      <c r="D428" s="42" t="s">
+      <c r="D428" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E428" s="28">
@@ -7087,7 +7117,7 @@
       </c>
       <c r="F428" s="14"/>
     </row>
-    <row r="429" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:6" x14ac:dyDescent="0.2">
       <c r="E429">
         <f>SUM(E419:E427)*E428</f>
         <v>0</v>
@@ -7097,7 +7127,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="430" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A430" s="8" t="s">
         <v>158</v>
       </c>
@@ -7105,89 +7135,89 @@
         <v>159</v>
       </c>
       <c r="C430" s="8"/>
-      <c r="D430" s="44"/>
+      <c r="D430" s="35"/>
       <c r="E430" s="8"/>
       <c r="F430" s="8">
         <v>3</v>
       </c>
     </row>
-    <row r="431" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A431" s="8"/>
       <c r="B431" s="8" t="s">
         <v>160</v>
       </c>
       <c r="C431" s="8"/>
-      <c r="D431" s="44"/>
+      <c r="D431" s="35"/>
       <c r="E431" s="8"/>
       <c r="F431" s="8">
         <v>5</v>
       </c>
     </row>
-    <row r="432" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A432" s="8"/>
       <c r="B432" s="8" t="s">
         <v>8</v>
       </c>
       <c r="C432" s="8"/>
-      <c r="D432" s="44"/>
+      <c r="D432" s="35"/>
       <c r="E432" s="8"/>
       <c r="F432" s="8">
         <v>3</v>
       </c>
     </row>
-    <row r="433" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A433" s="8"/>
       <c r="B433" s="8" t="s">
         <v>161</v>
       </c>
       <c r="C433" s="8"/>
-      <c r="D433" s="44"/>
+      <c r="D433" s="35"/>
       <c r="E433" s="8"/>
       <c r="F433" s="8">
         <v>3</v>
       </c>
     </row>
-    <row r="434" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A434" s="8"/>
       <c r="B434" s="8" t="s">
         <v>162</v>
       </c>
       <c r="C434" s="8"/>
-      <c r="D434" s="44"/>
+      <c r="D434" s="35"/>
       <c r="E434" s="8"/>
       <c r="F434" s="8">
         <v>3</v>
       </c>
     </row>
-    <row r="435" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A435" s="8"/>
       <c r="B435" s="8" t="s">
         <v>163</v>
       </c>
       <c r="C435" s="8"/>
-      <c r="D435" s="44"/>
+      <c r="D435" s="35"/>
       <c r="E435" s="8"/>
       <c r="F435" s="8">
         <v>3</v>
       </c>
     </row>
-    <row r="436" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A436" s="8"/>
       <c r="B436" s="8" t="s">
         <v>164</v>
       </c>
       <c r="C436" s="8"/>
-      <c r="D436" s="44"/>
+      <c r="D436" s="35"/>
       <c r="E436" s="8"/>
       <c r="F436" s="8">
         <v>3</v>
       </c>
     </row>
-    <row r="437" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A437" s="8"/>
       <c r="B437" s="8"/>
       <c r="C437" s="8"/>
-      <c r="D437" s="42" t="s">
+      <c r="D437" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E437" s="28">
@@ -7195,7 +7225,7 @@
       </c>
       <c r="F437" s="8"/>
     </row>
-    <row r="438" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:6" x14ac:dyDescent="0.2">
       <c r="E438">
         <f>SUM(E430:E436)*E437</f>
         <v>0</v>
@@ -7205,7 +7235,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="439" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A439" s="7" t="s">
         <v>362</v>
       </c>
@@ -7213,7 +7243,7 @@
       <c r="C439" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="D439" s="44" t="s">
+      <c r="D439" s="35" t="s">
         <v>173</v>
       </c>
       <c r="E439" s="8"/>
@@ -7221,11 +7251,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="440" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A440" s="7"/>
       <c r="B440" s="7"/>
       <c r="C440" s="8"/>
-      <c r="D440" s="44" t="s">
+      <c r="D440" s="35" t="s">
         <v>174</v>
       </c>
       <c r="E440" s="8"/>
@@ -7233,11 +7263,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="441" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A441" s="7"/>
       <c r="B441" s="7"/>
       <c r="C441" s="8"/>
-      <c r="D441" s="44" t="s">
+      <c r="D441" s="35" t="s">
         <v>175</v>
       </c>
       <c r="E441" s="8"/>
@@ -7245,13 +7275,13 @@
         <v>5</v>
       </c>
     </row>
-    <row r="442" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A442" s="7"/>
       <c r="B442" s="7"/>
       <c r="C442" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="D442" s="44" t="s">
+      <c r="D442" s="35" t="s">
         <v>177</v>
       </c>
       <c r="E442" s="8"/>
@@ -7259,11 +7289,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="443" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A443" s="7"/>
       <c r="B443" s="7"/>
       <c r="C443" s="8"/>
-      <c r="D443" s="44" t="s">
+      <c r="D443" s="35" t="s">
         <v>178</v>
       </c>
       <c r="E443" s="8"/>
@@ -7271,11 +7301,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="444" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A444" s="7"/>
       <c r="B444" s="7"/>
       <c r="C444" s="8"/>
-      <c r="D444" s="44" t="s">
+      <c r="D444" s="35" t="s">
         <v>179</v>
       </c>
       <c r="E444" s="8"/>
@@ -7283,11 +7313,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="445" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A445" s="7"/>
       <c r="B445" s="7"/>
       <c r="C445" s="8"/>
-      <c r="D445" s="44" t="s">
+      <c r="D445" s="35" t="s">
         <v>180</v>
       </c>
       <c r="E445" s="8"/>
@@ -7295,11 +7325,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="446" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A446" s="7"/>
       <c r="B446" s="7"/>
       <c r="C446" s="8"/>
-      <c r="D446" s="44" t="s">
+      <c r="D446" s="35" t="s">
         <v>181</v>
       </c>
       <c r="E446" s="8"/>
@@ -7307,7 +7337,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="447" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:6" x14ac:dyDescent="0.2">
       <c r="E447">
         <f>SUM(E439:E446)</f>
         <v>0</v>
@@ -7317,12 +7347,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="448" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:6" ht="19" x14ac:dyDescent="0.25">
       <c r="A448" s="5" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="449" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A449" s="7" t="s">
         <v>265</v>
       </c>
@@ -7332,25 +7362,25 @@
       <c r="C449" s="8" t="s">
         <v>316</v>
       </c>
-      <c r="D449" s="44"/>
+      <c r="D449" s="35"/>
       <c r="E449" s="8"/>
       <c r="F449" s="8">
         <v>10</v>
       </c>
     </row>
-    <row r="450" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A450" s="7"/>
       <c r="B450" s="8"/>
       <c r="C450" s="8" t="s">
         <v>364</v>
       </c>
-      <c r="D450" s="44"/>
+      <c r="D450" s="35"/>
       <c r="E450" s="8"/>
       <c r="F450" s="8">
         <v>10</v>
       </c>
     </row>
-    <row r="451" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A451" s="8"/>
       <c r="B451" s="7" t="s">
         <v>266</v>
@@ -7358,70 +7388,70 @@
       <c r="C451" s="8" t="s">
         <v>319</v>
       </c>
-      <c r="D451" s="44"/>
+      <c r="D451" s="35"/>
       <c r="E451" s="8"/>
       <c r="F451" s="8"/>
     </row>
-    <row r="452" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A452" s="8"/>
       <c r="B452" s="8"/>
       <c r="C452" s="8" t="s">
         <v>365</v>
       </c>
-      <c r="D452" s="44"/>
+      <c r="D452" s="35"/>
       <c r="E452" s="8"/>
       <c r="F452" s="8">
         <v>10</v>
       </c>
     </row>
-    <row r="453" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A453" s="8"/>
       <c r="B453" s="8"/>
       <c r="C453" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="D453" s="44"/>
+      <c r="D453" s="35"/>
       <c r="E453" s="8"/>
       <c r="F453" s="8">
         <v>10</v>
       </c>
     </row>
-    <row r="454" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A454" s="8"/>
       <c r="B454" s="8"/>
       <c r="C454" s="8" t="s">
         <v>366</v>
       </c>
-      <c r="D454" s="44"/>
+      <c r="D454" s="35"/>
       <c r="E454" s="8"/>
       <c r="F454" s="8">
         <v>10</v>
       </c>
     </row>
-    <row r="455" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A455" s="8"/>
       <c r="B455" s="8"/>
       <c r="C455" s="8" t="s">
         <v>367</v>
       </c>
-      <c r="D455" s="44"/>
+      <c r="D455" s="35"/>
       <c r="E455" s="8"/>
       <c r="F455" s="8">
         <v>10</v>
       </c>
     </row>
-    <row r="456" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A456" s="8"/>
       <c r="B456" s="8"/>
       <c r="C456" s="8"/>
-      <c r="D456" s="42" t="s">
+      <c r="D456" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E456" s="28">
         <v>1</v>
       </c>
     </row>
-    <row r="457" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:6" x14ac:dyDescent="0.2">
       <c r="E457">
         <f>SUM(E449:E455)*E456</f>
         <v>0</v>
@@ -7431,12 +7461,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="458" spans="1:6" ht="21" x14ac:dyDescent="0.4">
+    <row r="458" spans="1:6" ht="21" x14ac:dyDescent="0.25">
       <c r="A458" s="23" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="459" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A459" s="11" t="s">
         <v>369</v>
       </c>
@@ -7444,13 +7474,13 @@
         <v>370</v>
       </c>
       <c r="C459" s="12"/>
-      <c r="D459" s="41"/>
+      <c r="D459" s="32"/>
       <c r="E459" s="12"/>
       <c r="F459" s="12">
         <v>10</v>
       </c>
     </row>
-    <row r="460" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A460" s="11" t="s">
         <v>371</v>
       </c>
@@ -7460,29 +7490,29 @@
       <c r="C460" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="D460" s="41"/>
+      <c r="D460" s="32"/>
       <c r="E460" s="12"/>
       <c r="F460" s="12">
         <v>20</v>
       </c>
     </row>
-    <row r="461" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A461" s="11"/>
       <c r="B461" s="12"/>
       <c r="C461" s="12" t="s">
         <v>373</v>
       </c>
-      <c r="D461" s="41"/>
+      <c r="D461" s="32"/>
       <c r="E461" s="12"/>
       <c r="F461" s="12">
         <v>20</v>
       </c>
     </row>
-    <row r="462" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A462" s="11"/>
       <c r="B462" s="12"/>
       <c r="C462" s="12"/>
-      <c r="D462" s="42" t="s">
+      <c r="D462" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E462" s="28">
@@ -7490,7 +7520,7 @@
       </c>
       <c r="F462" s="12"/>
     </row>
-    <row r="463" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A463" s="1"/>
       <c r="E463">
         <f>SUM(E459:E461)*E462</f>
@@ -7501,15 +7531,15 @@
         <v>50</v>
       </c>
     </row>
-    <row r="464" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A464" s="1"/>
     </row>
-    <row r="465" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:6" ht="19" x14ac:dyDescent="0.25">
       <c r="A465" s="5" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="466" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A466" s="15" t="s">
         <v>348</v>
       </c>
@@ -7519,13 +7549,13 @@
       <c r="C466" s="13" t="s">
         <v>351</v>
       </c>
-      <c r="D466" s="40"/>
+      <c r="D466" s="31"/>
       <c r="E466" s="13"/>
       <c r="F466" s="13">
         <v>10</v>
       </c>
     </row>
-    <row r="467" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A467" s="13" t="s">
         <v>355</v>
       </c>
@@ -7533,13 +7563,13 @@
         <v>7</v>
       </c>
       <c r="C467" s="13"/>
-      <c r="D467" s="40"/>
+      <c r="D467" s="31"/>
       <c r="E467" s="13"/>
       <c r="F467" s="13">
         <v>10</v>
       </c>
     </row>
-    <row r="468" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A468" s="13" t="s">
         <v>0</v>
       </c>
@@ -7547,29 +7577,29 @@
         <v>349</v>
       </c>
       <c r="C468" s="13"/>
-      <c r="D468" s="40"/>
+      <c r="D468" s="31"/>
       <c r="E468" s="13"/>
       <c r="F468" s="13">
         <v>20</v>
       </c>
     </row>
-    <row r="469" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A469" s="13"/>
       <c r="B469" s="13" t="s">
         <v>350</v>
       </c>
       <c r="C469" s="13"/>
-      <c r="D469" s="40"/>
+      <c r="D469" s="31"/>
       <c r="E469" s="13"/>
       <c r="F469" s="13">
         <v>10</v>
       </c>
     </row>
-    <row r="470" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A470" s="13"/>
       <c r="B470" s="13"/>
       <c r="C470" s="13"/>
-      <c r="D470" s="42" t="s">
+      <c r="D470" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E470" s="28">
@@ -7577,7 +7607,7 @@
       </c>
       <c r="F470" s="13"/>
     </row>
-    <row r="471" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:6" x14ac:dyDescent="0.2">
       <c r="E471">
         <f>SUM(E466:E469)*E470</f>
         <v>0</v>
@@ -7587,7 +7617,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="473" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A473" s="16" t="s">
         <v>348</v>
       </c>
@@ -7603,7 +7633,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="474" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A474" s="14" t="s">
         <v>135</v>
       </c>
@@ -7617,7 +7647,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="475" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A475" s="14"/>
       <c r="B475" s="14" t="s">
         <v>228</v>
@@ -7629,11 +7659,11 @@
         <v>20</v>
       </c>
     </row>
-    <row r="476" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A476" s="14"/>
       <c r="B476" s="14"/>
       <c r="C476" s="14"/>
-      <c r="D476" s="42" t="s">
+      <c r="D476" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E476" s="28">
@@ -7641,7 +7671,7 @@
       </c>
       <c r="F476" s="14"/>
     </row>
-    <row r="477" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:6" x14ac:dyDescent="0.2">
       <c r="E477">
         <f>SUM(E473:E475)*E476</f>
         <v>0</v>
@@ -7651,7 +7681,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="478" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A478" s="11" t="s">
         <v>348</v>
       </c>
@@ -7661,13 +7691,13 @@
       <c r="C478" s="12" t="s">
         <v>351</v>
       </c>
-      <c r="D478" s="41"/>
+      <c r="D478" s="32"/>
       <c r="E478" s="12"/>
       <c r="F478" s="12">
         <v>10</v>
       </c>
     </row>
-    <row r="479" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A479" s="12" t="s">
         <v>353</v>
       </c>
@@ -7675,29 +7705,29 @@
         <v>352</v>
       </c>
       <c r="C479" s="12"/>
-      <c r="D479" s="41"/>
+      <c r="D479" s="32"/>
       <c r="E479" s="12"/>
       <c r="F479" s="12">
         <v>20</v>
       </c>
     </row>
-    <row r="480" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A480" s="12"/>
       <c r="B480" s="12" t="s">
         <v>354</v>
       </c>
       <c r="C480" s="12"/>
-      <c r="D480" s="41"/>
+      <c r="D480" s="32"/>
       <c r="E480" s="12"/>
       <c r="F480" s="12">
         <v>40</v>
       </c>
     </row>
-    <row r="481" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A481" s="12"/>
       <c r="B481" s="12"/>
       <c r="C481" s="12"/>
-      <c r="D481" s="42" t="s">
+      <c r="D481" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E481" s="28">
@@ -7705,7 +7735,7 @@
       </c>
       <c r="F481" s="12"/>
     </row>
-    <row r="482" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:6" x14ac:dyDescent="0.2">
       <c r="E482">
         <f>SUM(E478:E480)*E481</f>
         <v>0</v>
@@ -7715,12 +7745,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="487" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:6" ht="19" x14ac:dyDescent="0.25">
       <c r="A487" s="5" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="488" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A488" s="14" t="s">
         <v>265</v>
       </c>
@@ -7734,7 +7764,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="489" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A489" s="14" t="s">
         <v>270</v>
       </c>
@@ -7748,7 +7778,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="490" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A490" s="14"/>
       <c r="B490" s="14" t="s">
         <v>268</v>
@@ -7760,7 +7790,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="491" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A491" s="14"/>
       <c r="B491" s="14" t="s">
         <v>267</v>
@@ -7772,7 +7802,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="492" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A492" s="14"/>
       <c r="B492" s="14" t="s">
         <v>269</v>
@@ -7784,7 +7814,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="493" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A493" s="14"/>
       <c r="B493" s="14" t="s">
         <v>271</v>
@@ -7796,7 +7826,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="494" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A494" s="14"/>
       <c r="B494" s="14" t="s">
         <v>272</v>
@@ -7808,7 +7838,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="495" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A495" s="14"/>
       <c r="B495" s="14" t="s">
         <v>26</v>
@@ -7820,7 +7850,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="496" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A496" s="14"/>
       <c r="B496" s="14" t="s">
         <v>27</v>
@@ -7832,7 +7862,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="497" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A497" s="14"/>
       <c r="B497" s="14" t="s">
         <v>273</v>
@@ -7844,7 +7874,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="498" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A498" s="14"/>
       <c r="B498" s="14" t="s">
         <v>274</v>
@@ -7856,11 +7886,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="499" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A499" s="14"/>
       <c r="B499" s="14"/>
       <c r="C499" s="14"/>
-      <c r="D499" s="42" t="s">
+      <c r="D499" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E499" s="28">
@@ -7868,7 +7898,7 @@
       </c>
       <c r="F499" s="14"/>
     </row>
-    <row r="500" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:6" x14ac:dyDescent="0.2">
       <c r="E500">
         <f>SUM(E488:E498)*E499</f>
         <v>0</v>
@@ -7878,7 +7908,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="502" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A502" s="12" t="s">
         <v>265</v>
       </c>
@@ -7886,13 +7916,13 @@
         <v>266</v>
       </c>
       <c r="C502" s="12"/>
-      <c r="D502" s="41"/>
+      <c r="D502" s="32"/>
       <c r="E502" s="12"/>
       <c r="F502" s="12">
         <v>10</v>
       </c>
     </row>
-    <row r="503" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A503" s="12" t="s">
         <v>270</v>
       </c>
@@ -7900,125 +7930,125 @@
         <v>120</v>
       </c>
       <c r="C503" s="12"/>
-      <c r="D503" s="41"/>
+      <c r="D503" s="32"/>
       <c r="E503" s="12"/>
       <c r="F503" s="12">
         <v>5</v>
       </c>
     </row>
-    <row r="504" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A504" s="12"/>
       <c r="B504" s="12" t="s">
         <v>268</v>
       </c>
       <c r="C504" s="12"/>
-      <c r="D504" s="41"/>
+      <c r="D504" s="32"/>
       <c r="E504" s="12"/>
       <c r="F504" s="12">
         <v>5</v>
       </c>
     </row>
-    <row r="505" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A505" s="12"/>
       <c r="B505" s="12" t="s">
         <v>267</v>
       </c>
       <c r="C505" s="12"/>
-      <c r="D505" s="41"/>
+      <c r="D505" s="32"/>
       <c r="E505" s="12"/>
       <c r="F505" s="12">
         <v>5</v>
       </c>
     </row>
-    <row r="506" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A506" s="12"/>
       <c r="B506" s="12" t="s">
         <v>269</v>
       </c>
       <c r="C506" s="12"/>
-      <c r="D506" s="41"/>
+      <c r="D506" s="32"/>
       <c r="E506" s="12"/>
       <c r="F506" s="12">
         <v>5</v>
       </c>
     </row>
-    <row r="507" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A507" s="12"/>
       <c r="B507" s="12" t="s">
         <v>271</v>
       </c>
       <c r="C507" s="12"/>
-      <c r="D507" s="41"/>
+      <c r="D507" s="32"/>
       <c r="E507" s="12"/>
       <c r="F507" s="12">
         <v>5</v>
       </c>
     </row>
-    <row r="508" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A508" s="12"/>
       <c r="B508" s="12" t="s">
         <v>272</v>
       </c>
       <c r="C508" s="12"/>
-      <c r="D508" s="41"/>
+      <c r="D508" s="32"/>
       <c r="E508" s="12"/>
       <c r="F508" s="12">
         <v>5</v>
       </c>
     </row>
-    <row r="509" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A509" s="12"/>
       <c r="B509" s="12" t="s">
         <v>26</v>
       </c>
       <c r="C509" s="12"/>
-      <c r="D509" s="41"/>
+      <c r="D509" s="32"/>
       <c r="E509" s="12"/>
       <c r="F509" s="12">
         <v>5</v>
       </c>
     </row>
-    <row r="510" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A510" s="12"/>
       <c r="B510" s="12" t="s">
         <v>27</v>
       </c>
       <c r="C510" s="12"/>
-      <c r="D510" s="41"/>
+      <c r="D510" s="32"/>
       <c r="E510" s="12"/>
       <c r="F510" s="12">
         <v>5</v>
       </c>
     </row>
-    <row r="511" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A511" s="12"/>
       <c r="B511" s="12" t="s">
         <v>273</v>
       </c>
       <c r="C511" s="12"/>
-      <c r="D511" s="41"/>
+      <c r="D511" s="32"/>
       <c r="E511" s="12"/>
       <c r="F511" s="12">
         <v>5</v>
       </c>
     </row>
-    <row r="512" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A512" s="12"/>
       <c r="B512" s="12" t="s">
         <v>274</v>
       </c>
       <c r="C512" s="12"/>
-      <c r="D512" s="41"/>
+      <c r="D512" s="32"/>
       <c r="E512" s="12"/>
       <c r="F512" s="12">
         <v>5</v>
       </c>
     </row>
-    <row r="513" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A513" s="12"/>
       <c r="B513" s="12"/>
       <c r="C513" s="12"/>
-      <c r="D513" s="42" t="s">
+      <c r="D513" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E513" s="28">
@@ -8026,7 +8056,7 @@
       </c>
       <c r="F513" s="12"/>
     </row>
-    <row r="514" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:6" x14ac:dyDescent="0.2">
       <c r="E514">
         <f>SUM(E502:E512)*E513</f>
         <v>0</v>
@@ -8036,7 +8066,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="516" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A516" s="13" t="s">
         <v>265</v>
       </c>
@@ -8044,13 +8074,13 @@
         <v>266</v>
       </c>
       <c r="C516" s="13"/>
-      <c r="D516" s="40"/>
+      <c r="D516" s="31"/>
       <c r="E516" s="13"/>
       <c r="F516" s="13">
         <v>10</v>
       </c>
     </row>
-    <row r="517" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A517" s="13" t="s">
         <v>270</v>
       </c>
@@ -8058,125 +8088,125 @@
         <v>120</v>
       </c>
       <c r="C517" s="13"/>
-      <c r="D517" s="40"/>
+      <c r="D517" s="31"/>
       <c r="E517" s="13"/>
       <c r="F517" s="13">
         <v>5</v>
       </c>
     </row>
-    <row r="518" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A518" s="13"/>
       <c r="B518" s="13" t="s">
         <v>268</v>
       </c>
       <c r="C518" s="13"/>
-      <c r="D518" s="40"/>
+      <c r="D518" s="31"/>
       <c r="E518" s="13"/>
       <c r="F518" s="13">
         <v>5</v>
       </c>
     </row>
-    <row r="519" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A519" s="13"/>
       <c r="B519" s="13" t="s">
         <v>267</v>
       </c>
       <c r="C519" s="13"/>
-      <c r="D519" s="40"/>
+      <c r="D519" s="31"/>
       <c r="E519" s="13"/>
       <c r="F519" s="13">
         <v>5</v>
       </c>
     </row>
-    <row r="520" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A520" s="13"/>
       <c r="B520" s="13" t="s">
         <v>269</v>
       </c>
       <c r="C520" s="13"/>
-      <c r="D520" s="40"/>
+      <c r="D520" s="31"/>
       <c r="E520" s="13"/>
       <c r="F520" s="13">
         <v>5</v>
       </c>
     </row>
-    <row r="521" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A521" s="13"/>
       <c r="B521" s="13" t="s">
         <v>271</v>
       </c>
       <c r="C521" s="13"/>
-      <c r="D521" s="40"/>
+      <c r="D521" s="31"/>
       <c r="E521" s="13"/>
       <c r="F521" s="13">
         <v>5</v>
       </c>
     </row>
-    <row r="522" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A522" s="13"/>
       <c r="B522" s="13" t="s">
         <v>272</v>
       </c>
       <c r="C522" s="13"/>
-      <c r="D522" s="40"/>
+      <c r="D522" s="31"/>
       <c r="E522" s="13"/>
       <c r="F522" s="13">
         <v>5</v>
       </c>
     </row>
-    <row r="523" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A523" s="13"/>
       <c r="B523" s="13" t="s">
         <v>26</v>
       </c>
       <c r="C523" s="13"/>
-      <c r="D523" s="40"/>
+      <c r="D523" s="31"/>
       <c r="E523" s="13"/>
       <c r="F523" s="13">
         <v>5</v>
       </c>
     </row>
-    <row r="524" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A524" s="13"/>
       <c r="B524" s="13" t="s">
         <v>27</v>
       </c>
       <c r="C524" s="13"/>
-      <c r="D524" s="40"/>
+      <c r="D524" s="31"/>
       <c r="E524" s="13"/>
       <c r="F524" s="13">
         <v>5</v>
       </c>
     </row>
-    <row r="525" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A525" s="13"/>
       <c r="B525" s="13" t="s">
         <v>273</v>
       </c>
       <c r="C525" s="13"/>
-      <c r="D525" s="40"/>
+      <c r="D525" s="31"/>
       <c r="E525" s="13"/>
       <c r="F525" s="13">
         <v>5</v>
       </c>
     </row>
-    <row r="526" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A526" s="13"/>
       <c r="B526" s="13" t="s">
         <v>274</v>
       </c>
       <c r="C526" s="13"/>
-      <c r="D526" s="40"/>
+      <c r="D526" s="31"/>
       <c r="E526" s="13"/>
       <c r="F526" s="13">
         <v>5</v>
       </c>
     </row>
-    <row r="527" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A527" s="13"/>
       <c r="B527" s="13"/>
       <c r="C527" s="13"/>
-      <c r="D527" s="42" t="s">
+      <c r="D527" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E527" s="28">
@@ -8184,7 +8214,7 @@
       </c>
       <c r="F527" s="13"/>
     </row>
-    <row r="528" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:6" x14ac:dyDescent="0.2">
       <c r="E528">
         <f>SUM(E516:E526)*E527</f>
         <v>0</v>
@@ -8194,12 +8224,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="530" spans="1:6" ht="21" x14ac:dyDescent="0.4">
+    <row r="530" spans="1:6" ht="21" x14ac:dyDescent="0.25">
       <c r="A530" s="23" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="531" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:6" ht="32" x14ac:dyDescent="0.2">
       <c r="A531" s="16" t="s">
         <v>375</v>
       </c>
@@ -8215,7 +8245,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="532" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:6" ht="32" x14ac:dyDescent="0.2">
       <c r="A532" s="14"/>
       <c r="B532" s="14" t="s">
         <v>406</v>
@@ -8229,7 +8259,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="533" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:6" ht="32" x14ac:dyDescent="0.2">
       <c r="A533" s="14"/>
       <c r="B533" s="14" t="s">
         <v>408</v>
@@ -8243,7 +8273,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="534" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:6" ht="32" x14ac:dyDescent="0.2">
       <c r="A534" s="14"/>
       <c r="B534" s="14" t="s">
         <v>410</v>
@@ -8257,7 +8287,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="535" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A535" s="14"/>
       <c r="B535" s="14" t="s">
         <v>412</v>
@@ -8271,11 +8301,11 @@
         <v>30</v>
       </c>
     </row>
-    <row r="536" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A536" s="14"/>
       <c r="B536" s="14"/>
       <c r="C536" s="14"/>
-      <c r="D536" s="42" t="s">
+      <c r="D536" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E536" s="28">
@@ -8283,7 +8313,7 @@
       </c>
       <c r="F536" s="14"/>
     </row>
-    <row r="537" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:6" x14ac:dyDescent="0.2">
       <c r="E537">
         <f>SUM(E531:E535)*E536</f>
         <v>0</v>
@@ -8293,63 +8323,83 @@
         <v>150</v>
       </c>
     </row>
-    <row r="539" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:6" ht="48" x14ac:dyDescent="0.2">
       <c r="A539" s="11" t="s">
         <v>375</v>
       </c>
-      <c r="B539" s="12"/>
+      <c r="B539" s="12" t="s">
+        <v>424</v>
+      </c>
       <c r="C539" s="12"/>
-      <c r="D539" s="41"/>
+      <c r="D539" s="32" t="s">
+        <v>425</v>
+      </c>
       <c r="E539" s="12"/>
       <c r="F539" s="12">
         <v>30</v>
       </c>
     </row>
-    <row r="540" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:6" ht="48" x14ac:dyDescent="0.2">
       <c r="A540" s="12"/>
-      <c r="B540" s="12"/>
+      <c r="B540" s="12" t="s">
+        <v>426</v>
+      </c>
       <c r="C540" s="12"/>
-      <c r="D540" s="41"/>
+      <c r="D540" s="32" t="s">
+        <v>433</v>
+      </c>
       <c r="E540" s="12"/>
       <c r="F540" s="12">
         <v>30</v>
       </c>
     </row>
-    <row r="541" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:6" ht="48" x14ac:dyDescent="0.2">
       <c r="A541" s="12"/>
-      <c r="B541" s="12"/>
+      <c r="B541" s="12" t="s">
+        <v>427</v>
+      </c>
       <c r="C541" s="12"/>
-      <c r="D541" s="41"/>
+      <c r="D541" s="32" t="s">
+        <v>428</v>
+      </c>
       <c r="E541" s="12"/>
       <c r="F541" s="12">
         <v>30</v>
       </c>
     </row>
-    <row r="542" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:6" ht="48" x14ac:dyDescent="0.2">
       <c r="A542" s="12"/>
-      <c r="B542" s="12"/>
+      <c r="B542" s="12" t="s">
+        <v>429</v>
+      </c>
       <c r="C542" s="12"/>
-      <c r="D542" s="41"/>
+      <c r="D542" s="32" t="s">
+        <v>430</v>
+      </c>
       <c r="E542" s="12"/>
       <c r="F542" s="12">
         <v>30</v>
       </c>
     </row>
-    <row r="543" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:6" ht="48" x14ac:dyDescent="0.2">
       <c r="A543" s="12"/>
-      <c r="B543" s="12"/>
+      <c r="B543" s="12" t="s">
+        <v>431</v>
+      </c>
       <c r="C543" s="12"/>
-      <c r="D543" s="41"/>
+      <c r="D543" s="32" t="s">
+        <v>432</v>
+      </c>
       <c r="E543" s="12"/>
       <c r="F543" s="12">
         <v>30</v>
       </c>
     </row>
-    <row r="544" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A544" s="12"/>
       <c r="B544" s="12"/>
       <c r="C544" s="12"/>
-      <c r="D544" s="42" t="s">
+      <c r="D544" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E544" s="28">
@@ -8357,7 +8407,7 @@
       </c>
       <c r="F544" s="12"/>
     </row>
-    <row r="545" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:8" x14ac:dyDescent="0.2">
       <c r="E545">
         <f>SUM(E539:E543)*E544</f>
         <v>0</v>
@@ -8367,7 +8417,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="547" spans="1:8" ht="72" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:8" ht="64" x14ac:dyDescent="0.2">
       <c r="A547" s="15" t="s">
         <v>375</v>
       </c>
@@ -8375,7 +8425,7 @@
         <v>414</v>
       </c>
       <c r="C547" s="13"/>
-      <c r="D547" s="40" t="s">
+      <c r="D547" s="31" t="s">
         <v>415</v>
       </c>
       <c r="E547" s="13"/>
@@ -8383,13 +8433,13 @@
         <v>30</v>
       </c>
     </row>
-    <row r="548" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A548" s="13"/>
       <c r="B548" s="13" t="s">
         <v>416</v>
       </c>
       <c r="C548" s="13"/>
-      <c r="D548" s="40" t="s">
+      <c r="D548" s="31" t="s">
         <v>417</v>
       </c>
       <c r="E548" s="13"/>
@@ -8397,13 +8447,13 @@
         <v>30</v>
       </c>
     </row>
-    <row r="549" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A549" s="13"/>
       <c r="B549" s="13" t="s">
         <v>419</v>
       </c>
       <c r="C549" s="13"/>
-      <c r="D549" s="40" t="s">
+      <c r="D549" s="31" t="s">
         <v>418</v>
       </c>
       <c r="E549" s="13"/>
@@ -8411,13 +8461,13 @@
         <v>30</v>
       </c>
     </row>
-    <row r="550" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A550" s="13"/>
       <c r="B550" s="13" t="s">
         <v>420</v>
       </c>
       <c r="C550" s="13"/>
-      <c r="D550" s="40" t="s">
+      <c r="D550" s="31" t="s">
         <v>421</v>
       </c>
       <c r="E550" s="13"/>
@@ -8425,13 +8475,13 @@
         <v>30</v>
       </c>
     </row>
-    <row r="551" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A551" s="13"/>
       <c r="B551" s="13" t="s">
         <v>422</v>
       </c>
       <c r="C551" s="13"/>
-      <c r="D551" s="40" t="s">
+      <c r="D551" s="31" t="s">
         <v>423</v>
       </c>
       <c r="E551" s="13"/>
@@ -8439,11 +8489,11 @@
         <v>30</v>
       </c>
     </row>
-    <row r="552" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A552" s="13"/>
       <c r="B552" s="13"/>
       <c r="C552" s="13"/>
-      <c r="D552" s="42" t="s">
+      <c r="D552" s="33" t="s">
         <v>389</v>
       </c>
       <c r="E552" s="28">
@@ -8451,7 +8501,7 @@
       </c>
       <c r="F552" s="13"/>
     </row>
-    <row r="553" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:8" x14ac:dyDescent="0.2">
       <c r="E553">
         <f>SUM(E547:E551)*E552</f>
         <v>0</v>
@@ -8461,7 +8511,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="556" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A556" s="7"/>
       <c r="B556" t="s">
         <v>213</v>
@@ -8479,7 +8529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="557" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A557" s="11" t="s">
         <v>395</v>
       </c>
@@ -8499,7 +8549,7 @@
         <v>-3.5137034434293744E-2</v>
       </c>
     </row>
-    <row r="558" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A558" s="15" t="s">
         <v>402</v>
       </c>
@@ -8519,7 +8569,7 @@
         <v>-3.5971223021582732E-2</v>
       </c>
     </row>
-    <row r="559" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A559" s="16" t="s">
         <v>396</v>
       </c>
@@ -8539,7 +8589,7 @@
         <v>-3.5739814152966405E-2</v>
       </c>
     </row>
-    <row r="563" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="563" spans="4:7" x14ac:dyDescent="0.2">
       <c r="F563" t="s">
         <v>260</v>
       </c>
@@ -8547,15 +8597,15 @@
         <v>261</v>
       </c>
     </row>
-    <row r="564" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D564" s="38" t="s">
+    <row r="564" spans="4:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="D564" s="29" t="s">
         <v>262</v>
       </c>
       <c r="G564" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="565" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="565" spans="4:7" x14ac:dyDescent="0.2">
       <c r="F565">
         <v>45</v>
       </c>
@@ -8563,7 +8613,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="566" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="566" spans="4:7" x14ac:dyDescent="0.2">
       <c r="F566">
         <f>F565+(F574-F565)/9</f>
         <v>50</v>
@@ -8572,7 +8622,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="567" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="567" spans="4:7" x14ac:dyDescent="0.2">
       <c r="F567">
         <f>F566+(F574-F565)/9</f>
         <v>55</v>
@@ -8581,7 +8631,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="568" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="568" spans="4:7" x14ac:dyDescent="0.2">
       <c r="F568">
         <f>F567+(F574-F565)/9</f>
         <v>60</v>
@@ -8590,7 +8640,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="569" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="569" spans="4:7" x14ac:dyDescent="0.2">
       <c r="F569">
         <f>F568+(F574-F565)/9</f>
         <v>65</v>
@@ -8599,7 +8649,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="570" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="570" spans="4:7" x14ac:dyDescent="0.2">
       <c r="F570">
         <f>F569+(F574-F565)/9</f>
         <v>70</v>
@@ -8608,7 +8658,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="571" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="571" spans="4:7" x14ac:dyDescent="0.2">
       <c r="F571">
         <f>F570+(F574-F565)/9</f>
         <v>75</v>
@@ -8617,7 +8667,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="572" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="572" spans="4:7" x14ac:dyDescent="0.2">
       <c r="F572">
         <f>F571+(F574-F565)/9</f>
         <v>80</v>
@@ -8626,7 +8676,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="573" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="573" spans="4:7" x14ac:dyDescent="0.2">
       <c r="F573">
         <f>F572+(F574-F565)/9</f>
         <v>85</v>
@@ -8635,7 +8685,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="574" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="574" spans="4:7" x14ac:dyDescent="0.2">
       <c r="F574">
         <v>90</v>
       </c>
@@ -8643,7 +8693,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="575" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="575" spans="4:7" x14ac:dyDescent="0.2">
       <c r="E575" t="s">
         <v>264</v>
       </c>
@@ -8673,45 +8723,45 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:L1047724"/>
-  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="31.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="27.44140625" customWidth="1"/>
-    <col min="5" max="5" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="31.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="27.5" customWidth="1"/>
+    <col min="5" max="5" width="14.5" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="33.6" x14ac:dyDescent="0.65">
-      <c r="A1" s="29" t="s">
+    <row r="1" spans="1:4" ht="34" x14ac:dyDescent="0.4">
+      <c r="A1" s="38" t="s">
         <v>392</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="30" t="s">
+    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="39" t="s">
         <v>393</v>
       </c>
-      <c r="B5" s="30"/>
-      <c r="C5" s="30"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B5" s="39"/>
+      <c r="C5" s="39"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>84</v>
       </c>
@@ -8725,7 +8775,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>397</v>
       </c>
@@ -8739,15 +8789,15 @@
         <v>400</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="C11" s="3"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>89</v>
       </c>
@@ -8755,7 +8805,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>90</v>
       </c>
@@ -8763,7 +8813,7 @@
         <v>45924</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>91</v>
       </c>
@@ -8771,12 +8821,12 @@
         <v>46051</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>93</v>
       </c>
@@ -8784,13 +8834,13 @@
         <v>401</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="23.4" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:8" ht="24" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
         <v>94</v>
       </c>
       <c r="H23" s="21"/>
     </row>
-    <row r="25" spans="1:8" ht="18" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8" ht="19" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>95</v>
       </c>
@@ -8801,7 +8851,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" s="15" t="s">
         <v>36</v>
       </c>
@@ -8814,7 +8864,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="15"/>
       <c r="B28" s="13" t="s">
         <v>37</v>
@@ -8825,7 +8875,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="15"/>
       <c r="B29" s="13" t="s">
         <v>38</v>
@@ -8836,7 +8886,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="15"/>
       <c r="B30" s="13" t="s">
         <v>19</v>
@@ -8847,7 +8897,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="15"/>
       <c r="B31" s="13" t="s">
         <v>39</v>
@@ -8858,7 +8908,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="15"/>
       <c r="B32" s="13"/>
       <c r="C32" s="22" t="s">
@@ -8870,7 +8920,7 @@
       </c>
       <c r="E32" s="13"/>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D33">
         <f>-SUM(D27:D32)</f>
         <v>0</v>
@@ -8881,7 +8931,7 @@
       </c>
       <c r="L33" s="20"/>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A34" s="16" t="s">
         <v>45</v>
       </c>
@@ -8895,7 +8945,7 @@
       </c>
       <c r="L34" s="20"/>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A35" s="16"/>
       <c r="B35" s="14" t="s">
         <v>50</v>
@@ -8907,7 +8957,7 @@
       </c>
       <c r="L35" s="20"/>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A36" s="16"/>
       <c r="B36" s="14"/>
       <c r="C36" s="22" t="s">
@@ -8920,7 +8970,7 @@
       <c r="E36" s="14"/>
       <c r="L36" s="20"/>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D37">
         <f>-SUM(D34:D36)</f>
         <v>0</v>
@@ -8931,10 +8981,10 @@
       </c>
       <c r="L37" s="20"/>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
       <c r="L38" s="20"/>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A39" s="7" t="s">
         <v>98</v>
       </c>
@@ -8948,7 +8998,7 @@
       </c>
       <c r="L39" s="20"/>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A40" s="7"/>
       <c r="B40" s="10" t="s">
         <v>47</v>
@@ -8960,7 +9010,7 @@
       </c>
       <c r="L40" s="20"/>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A41" s="7"/>
       <c r="B41" s="9" t="s">
         <v>48</v>
@@ -8972,7 +9022,7 @@
       </c>
       <c r="L41" s="20"/>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A42" s="7"/>
       <c r="B42" s="9" t="s">
         <v>49</v>
@@ -8984,7 +9034,7 @@
       </c>
       <c r="L42" s="20"/>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A43" s="7"/>
       <c r="B43" s="9" t="s">
         <v>50</v>
@@ -8996,7 +9046,7 @@
       </c>
       <c r="L43" s="20"/>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A44" s="7"/>
       <c r="B44" s="9" t="s">
         <v>51</v>
@@ -9008,7 +9058,7 @@
       </c>
       <c r="L44" s="20"/>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A45" s="7"/>
       <c r="B45" s="9" t="s">
         <v>52</v>
@@ -9020,7 +9070,7 @@
       </c>
       <c r="L45" s="20"/>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A46" s="7"/>
       <c r="B46" s="9"/>
       <c r="C46" s="22" t="s">
@@ -9033,7 +9083,7 @@
       <c r="E46" s="8"/>
       <c r="L46" s="20"/>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D47">
         <f>-SUM(D39:D46)</f>
         <v>0</v>
@@ -9044,7 +9094,7 @@
       </c>
       <c r="L47" s="20"/>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A49" s="15" t="s">
         <v>44</v>
       </c>
@@ -9057,7 +9107,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A50" s="15"/>
       <c r="B50" s="13" t="s">
         <v>77</v>
@@ -9068,7 +9118,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A51" s="15"/>
       <c r="B51" s="13" t="s">
         <v>124</v>
@@ -9079,14 +9129,14 @@
         <v>5</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A52" s="15"/>
       <c r="B52" s="13"/>
       <c r="C52" s="15"/>
       <c r="D52" s="15"/>
       <c r="E52" s="15"/>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A53" s="15" t="s">
         <v>122</v>
       </c>
@@ -9099,7 +9149,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A54" s="15"/>
       <c r="B54" s="13" t="s">
         <v>123</v>
@@ -9110,7 +9160,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A55" s="15"/>
       <c r="B55" s="13" t="s">
         <v>124</v>
@@ -9121,14 +9171,14 @@
         <v>5</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A56" s="15"/>
       <c r="B56" s="13"/>
       <c r="C56" s="15"/>
       <c r="D56" s="15"/>
       <c r="E56" s="15"/>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A57" s="15" t="s">
         <v>227</v>
       </c>
@@ -9141,7 +9191,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A58" s="15"/>
       <c r="B58" s="13" t="s">
         <v>123</v>
@@ -9152,7 +9202,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A59" s="15"/>
       <c r="B59" s="13" t="s">
         <v>124</v>
@@ -9163,7 +9213,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A60" s="15"/>
       <c r="B60" s="13"/>
       <c r="C60" s="22" t="s">
@@ -9175,7 +9225,7 @@
       </c>
       <c r="E60" s="13"/>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
       <c r="D61">
         <f>-SUM(D49:D60)</f>
         <v>0</v>
@@ -9185,7 +9235,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A63" s="15" t="s">
         <v>78</v>
       </c>
@@ -9198,7 +9248,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A64" s="15"/>
       <c r="B64" s="13" t="s">
         <v>46</v>
@@ -9209,7 +9259,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A65" s="15"/>
       <c r="B65" s="13" t="s">
         <v>247</v>
@@ -9220,7 +9270,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A66" s="15"/>
       <c r="B66" s="13" t="s">
         <v>79</v>
@@ -9231,7 +9281,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A67" s="15"/>
       <c r="B67" s="13"/>
       <c r="C67" s="22" t="s">
@@ -9243,7 +9293,7 @@
       </c>
       <c r="E67" s="13"/>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
       <c r="D68">
         <f>-SUM(D63:D67)</f>
         <v>0</v>
@@ -9253,7 +9303,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A72" s="11" t="s">
         <v>35</v>
       </c>
@@ -9266,7 +9316,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A73" s="11"/>
       <c r="B73" s="12" t="s">
         <v>229</v>
@@ -9277,7 +9327,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A74" s="11"/>
       <c r="B74" s="12" t="s">
         <v>230</v>
@@ -9288,7 +9338,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A75" s="11"/>
       <c r="B75" s="12" t="s">
         <v>228</v>
@@ -9299,7 +9349,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A76" s="11"/>
       <c r="B76" s="12"/>
       <c r="C76" s="22" t="s">
@@ -9311,7 +9361,7 @@
       </c>
       <c r="E76" s="12"/>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
       <c r="D77">
         <f>-SUM(D72:D76)</f>
         <v>0</v>
@@ -9321,7 +9371,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A79" s="7" t="s">
         <v>57</v>
       </c>
@@ -9334,7 +9384,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A80" s="7"/>
       <c r="B80" s="8" t="s">
         <v>60</v>
@@ -9345,7 +9395,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A81" s="7"/>
       <c r="B81" s="8" t="s">
         <v>59</v>
@@ -9356,7 +9406,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A82" s="7"/>
       <c r="B82" s="8" t="s">
         <v>56</v>
@@ -9367,7 +9417,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A83" s="7"/>
       <c r="B83" s="8" t="s">
         <v>231</v>
@@ -9378,7 +9428,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A84" s="7"/>
       <c r="B84" s="8" t="s">
         <v>61</v>
@@ -9391,7 +9441,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A85" s="7"/>
       <c r="B85" s="8"/>
       <c r="C85" s="8" t="s">
@@ -9402,7 +9452,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A86" s="7"/>
       <c r="B86" s="8"/>
       <c r="C86" s="8" t="s">
@@ -9413,7 +9463,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A87" s="7"/>
       <c r="B87" s="8"/>
       <c r="C87" s="8" t="s">
@@ -9424,7 +9474,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A88" s="7"/>
       <c r="B88" s="8"/>
       <c r="C88" s="8" t="s">
@@ -9435,7 +9485,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A89" s="7"/>
       <c r="B89" s="8"/>
       <c r="C89" s="22" t="s">
@@ -9447,7 +9497,7 @@
       </c>
       <c r="E89" s="8"/>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
       <c r="D90">
         <f>-SUM(D79:D89)</f>
         <v>0</v>
@@ -9457,7 +9507,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A91" s="11" t="s">
         <v>168</v>
       </c>
@@ -9470,7 +9520,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A92" s="11"/>
       <c r="B92" s="12" t="s">
         <v>77</v>
@@ -9481,7 +9531,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A93" s="11"/>
       <c r="B93" s="12" t="s">
         <v>170</v>
@@ -9492,7 +9542,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A94" s="11"/>
       <c r="B94" s="12"/>
       <c r="C94" s="22" t="s">
@@ -9504,7 +9554,7 @@
       </c>
       <c r="E94" s="12"/>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
       <c r="D95">
         <f>-SUM(D91:D94)</f>
         <v>0</v>
@@ -9514,8 +9564,8 @@
         <v>20</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A96" s="36" t="s">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A96" s="45" t="s">
         <v>62</v>
       </c>
       <c r="B96" s="11" t="s">
@@ -9530,8 +9580,8 @@
       </c>
       <c r="H96" s="1"/>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A97" s="36"/>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A97" s="45"/>
       <c r="B97" s="12"/>
       <c r="C97" s="12" t="s">
         <v>65</v>
@@ -9541,8 +9591,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A98" s="36"/>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A98" s="45"/>
       <c r="B98" s="12"/>
       <c r="C98" s="12" t="s">
         <v>53</v>
@@ -9552,8 +9602,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A99" s="36"/>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A99" s="45"/>
       <c r="B99" s="12"/>
       <c r="C99" s="12" t="s">
         <v>249</v>
@@ -9563,8 +9613,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A100" s="36"/>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A100" s="45"/>
       <c r="B100" s="12"/>
       <c r="C100" s="12" t="s">
         <v>248</v>
@@ -9574,8 +9624,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A101" s="36"/>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A101" s="45"/>
       <c r="B101" s="12"/>
       <c r="C101" s="12" t="s">
         <v>67</v>
@@ -9585,8 +9635,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A102" s="36"/>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A102" s="45"/>
       <c r="B102" s="12"/>
       <c r="C102" s="12" t="s">
         <v>68</v>
@@ -9596,8 +9646,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A103" s="36"/>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A103" s="45"/>
       <c r="B103" s="12"/>
       <c r="C103" s="12" t="s">
         <v>97</v>
@@ -9607,8 +9657,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A104" s="36"/>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A104" s="45"/>
       <c r="B104" s="12"/>
       <c r="C104" s="22" t="s">
         <v>236</v>
@@ -9619,8 +9669,8 @@
       </c>
       <c r="E104" s="12"/>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A105" s="36"/>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A105" s="45"/>
       <c r="D105">
         <f>-SUM(D96:D104)</f>
         <v>0</v>
@@ -9630,8 +9680,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A106" s="36"/>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A106" s="45"/>
       <c r="B106" s="15" t="s">
         <v>63</v>
       </c>
@@ -9643,8 +9693,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A107" s="36"/>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A107" s="45"/>
       <c r="B107" s="13"/>
       <c r="C107" s="13" t="s">
         <v>65</v>
@@ -9654,8 +9704,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A108" s="36"/>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A108" s="45"/>
       <c r="B108" s="13"/>
       <c r="C108" s="13" t="s">
         <v>53</v>
@@ -9665,8 +9715,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A109" s="36"/>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A109" s="45"/>
       <c r="B109" s="13"/>
       <c r="C109" s="13" t="s">
         <v>66</v>
@@ -9676,8 +9726,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A110" s="36"/>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A110" s="45"/>
       <c r="B110" s="13"/>
       <c r="C110" s="13" t="s">
         <v>52</v>
@@ -9687,8 +9737,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A111" s="36"/>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A111" s="45"/>
       <c r="B111" s="13"/>
       <c r="C111" s="13" t="s">
         <v>67</v>
@@ -9698,8 +9748,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A112" s="36"/>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A112" s="45"/>
       <c r="B112" s="13"/>
       <c r="C112" s="13" t="s">
         <v>68</v>
@@ -9709,8 +9759,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A113" s="36"/>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A113" s="45"/>
       <c r="B113" s="13"/>
       <c r="C113" s="13" t="s">
         <v>97</v>
@@ -9720,8 +9770,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A114" s="36"/>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A114" s="45"/>
       <c r="B114" s="13"/>
       <c r="C114" s="22" t="s">
         <v>236</v>
@@ -9732,8 +9782,8 @@
       </c>
       <c r="E114" s="13"/>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A115" s="36"/>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A115" s="45"/>
       <c r="D115">
         <f>-SUM(D106:D114)</f>
         <v>0</v>
@@ -9743,8 +9793,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A116" s="36"/>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A116" s="45"/>
       <c r="B116" s="16" t="s">
         <v>63</v>
       </c>
@@ -9756,8 +9806,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A117" s="36"/>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A117" s="45"/>
       <c r="B117" s="14"/>
       <c r="C117" s="14" t="s">
         <v>65</v>
@@ -9767,8 +9817,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A118" s="36"/>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A118" s="45"/>
       <c r="B118" s="14"/>
       <c r="C118" s="14" t="s">
         <v>53</v>
@@ -9778,8 +9828,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A119" s="36"/>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A119" s="45"/>
       <c r="B119" s="14"/>
       <c r="C119" s="14" t="s">
         <v>66</v>
@@ -9789,8 +9839,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A120" s="36"/>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A120" s="45"/>
       <c r="B120" s="14"/>
       <c r="C120" s="14" t="s">
         <v>52</v>
@@ -9800,8 +9850,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A121" s="36"/>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A121" s="45"/>
       <c r="B121" s="14"/>
       <c r="C121" s="14" t="s">
         <v>67</v>
@@ -9811,8 +9861,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A122" s="36"/>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A122" s="45"/>
       <c r="B122" s="14"/>
       <c r="C122" s="14" t="s">
         <v>68</v>
@@ -9822,8 +9872,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A123" s="36"/>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A123" s="45"/>
       <c r="B123" s="14"/>
       <c r="C123" s="14" t="s">
         <v>97</v>
@@ -9833,8 +9883,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A124" s="36"/>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A124" s="45"/>
       <c r="B124" s="14"/>
       <c r="C124" s="22" t="s">
         <v>236</v>
@@ -9845,8 +9895,8 @@
       </c>
       <c r="E124" s="14"/>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A125" s="36"/>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A125" s="45"/>
       <c r="D125">
         <f>-SUM(D116:D124)</f>
         <v>0</v>
@@ -9856,7 +9906,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A127" s="11" t="s">
         <v>109</v>
       </c>
@@ -9871,7 +9921,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A128" s="12"/>
       <c r="B128" s="12"/>
       <c r="C128" s="12" t="s">
@@ -9884,7 +9934,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A129" s="12"/>
       <c r="B129" s="12"/>
       <c r="C129" s="12"/>
@@ -9895,7 +9945,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A130" s="12"/>
       <c r="B130" s="12"/>
       <c r="C130" s="12" t="s">
@@ -9906,7 +9956,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A131" s="12"/>
       <c r="B131" s="12"/>
       <c r="C131" s="12" t="s">
@@ -9917,7 +9967,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A132" s="12"/>
       <c r="B132" s="12"/>
       <c r="C132" s="12" t="s">
@@ -9928,7 +9978,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A133" s="12"/>
       <c r="B133" s="12"/>
       <c r="C133" s="22" t="s">
@@ -9940,7 +9990,7 @@
       </c>
       <c r="E133" s="12"/>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A134"/>
       <c r="D134">
         <f>-SUM(D127:D133)</f>
@@ -9951,7 +10001,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A135" s="11" t="s">
         <v>109</v>
       </c>
@@ -9966,7 +10016,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A136" s="12"/>
       <c r="B136" s="12"/>
       <c r="C136" s="12" t="s">
@@ -9977,7 +10027,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A137" s="12"/>
       <c r="B137" s="12"/>
       <c r="C137" s="12" t="s">
@@ -9988,7 +10038,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A138" s="12"/>
       <c r="B138" s="12"/>
       <c r="C138" s="12" t="s">
@@ -10001,7 +10051,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A139" s="12"/>
       <c r="B139" s="12"/>
       <c r="C139" s="12"/>
@@ -10012,7 +10062,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A140" s="12"/>
       <c r="B140" s="12"/>
       <c r="C140" s="12"/>
@@ -10023,7 +10073,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A141" s="12"/>
       <c r="B141" s="12"/>
       <c r="C141" s="12"/>
@@ -10034,7 +10084,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A142" s="11"/>
       <c r="B142" s="12"/>
       <c r="C142" s="22" t="s">
@@ -10046,7 +10096,7 @@
       </c>
       <c r="E142" s="12"/>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.2">
       <c r="D143">
         <f>-SUM(D135:D142)</f>
         <v>0</v>
@@ -10056,7 +10106,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A144" s="15" t="s">
         <v>125</v>
       </c>
@@ -10071,7 +10121,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A145" s="15"/>
       <c r="B145" s="13"/>
       <c r="C145" s="13" t="s">
@@ -10082,7 +10132,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A146" s="15"/>
       <c r="B146" s="13"/>
       <c r="C146" s="13" t="s">
@@ -10093,7 +10143,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A147" s="15"/>
       <c r="B147" s="13"/>
       <c r="C147" s="13" t="s">
@@ -10104,7 +10154,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A148" s="15"/>
       <c r="B148" s="13"/>
       <c r="C148" s="13" t="s">
@@ -10115,7 +10165,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A149" s="15"/>
       <c r="B149" s="13"/>
       <c r="C149" s="22" t="s">
@@ -10127,7 +10177,7 @@
       </c>
       <c r="E149" s="13"/>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.2">
       <c r="D150">
         <f>-SUM(D144:D149)</f>
         <v>0</v>
@@ -10137,7 +10187,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A151" s="16" t="s">
         <v>125</v>
       </c>
@@ -10152,7 +10202,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A152" s="16"/>
       <c r="B152" s="14"/>
       <c r="C152" s="14" t="s">
@@ -10163,7 +10213,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A153" s="16"/>
       <c r="B153" s="14"/>
       <c r="C153" s="14" t="s">
@@ -10174,7 +10224,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A154" s="16"/>
       <c r="B154" s="14"/>
       <c r="C154" s="22" t="s">
@@ -10186,7 +10236,7 @@
       </c>
       <c r="E154" s="14"/>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.2">
       <c r="D155">
         <f>-SUM(D151:D154)</f>
         <v>0</v>
@@ -10196,7 +10246,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A157" s="16" t="s">
         <v>119</v>
       </c>
@@ -10209,7 +10259,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A158" s="16"/>
       <c r="B158" s="14" t="s">
         <v>121</v>
@@ -10220,7 +10270,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A159" s="16"/>
       <c r="B159" s="14" t="s">
         <v>224</v>
@@ -10231,7 +10281,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A160" s="16"/>
       <c r="B160" s="14" t="s">
         <v>232</v>
@@ -10242,7 +10292,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A161" s="16"/>
       <c r="B161" s="14" t="s">
         <v>225</v>
@@ -10253,7 +10303,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A162" s="16"/>
       <c r="B162" s="14"/>
       <c r="C162" s="22" t="s">
@@ -10265,7 +10315,7 @@
       </c>
       <c r="E162" s="14"/>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.2">
       <c r="D163">
         <f>-SUM(D157:D162)</f>
         <v>0</v>
@@ -10275,7 +10325,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A164" s="11" t="s">
         <v>206</v>
       </c>
@@ -10288,7 +10338,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A165" s="11"/>
       <c r="B165" s="12" t="s">
         <v>65</v>
@@ -10299,7 +10349,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A166" s="11"/>
       <c r="B166" s="12" t="s">
         <v>50</v>
@@ -10310,7 +10360,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A167" s="11"/>
       <c r="B167" s="12" t="s">
         <v>207</v>
@@ -10321,7 +10371,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A168" s="11"/>
       <c r="B168" s="12" t="s">
         <v>51</v>
@@ -10332,7 +10382,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A169" s="11"/>
       <c r="B169" s="12" t="s">
         <v>234</v>
@@ -10343,7 +10393,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A170" s="11"/>
       <c r="B170" s="12"/>
       <c r="C170" s="22" t="s">
@@ -10355,7 +10405,7 @@
       </c>
       <c r="E170" s="12"/>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.2">
       <c r="D171">
         <f>-SUM(D164:D170)</f>
         <v>0</v>
@@ -10365,7 +10415,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A172" s="15" t="s">
         <v>130</v>
       </c>
@@ -10378,7 +10428,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A173" s="15"/>
       <c r="B173" s="13" t="s">
         <v>235</v>
@@ -10389,7 +10439,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A174" s="15"/>
       <c r="B174" s="13" t="s">
         <v>8</v>
@@ -10400,7 +10450,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A175" s="15"/>
       <c r="B175" s="13" t="s">
         <v>132</v>
@@ -10411,7 +10461,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A176" s="15"/>
       <c r="B176" s="13" t="s">
         <v>133</v>
@@ -10422,7 +10472,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A177" s="15"/>
       <c r="B177" s="13" t="s">
         <v>134</v>
@@ -10433,7 +10483,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A178" s="15"/>
       <c r="B178" s="13"/>
       <c r="C178" s="22" t="s">
@@ -10445,7 +10495,7 @@
       </c>
       <c r="E178" s="13"/>
     </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.2">
       <c r="D179">
         <f>-SUM(D172:D178)</f>
         <v>0</v>
@@ -10455,7 +10505,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A180" s="16" t="s">
         <v>135</v>
       </c>
@@ -10468,7 +10518,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A181" s="16"/>
       <c r="B181" s="14" t="s">
         <v>233</v>
@@ -10479,7 +10529,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A182" s="16"/>
       <c r="B182" s="14" t="s">
         <v>136</v>
@@ -10490,7 +10540,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A183" s="16"/>
       <c r="B183" s="14" t="s">
         <v>137</v>
@@ -10501,7 +10551,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A184" s="16"/>
       <c r="B184" s="14" t="s">
         <v>55</v>
@@ -10512,7 +10562,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A185" s="16"/>
       <c r="B185" s="14" t="s">
         <v>54</v>
@@ -10523,7 +10573,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A186" s="16"/>
       <c r="B186" s="14" t="s">
         <v>138</v>
@@ -10534,7 +10584,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A187" s="16"/>
       <c r="B187" s="14" t="s">
         <v>139</v>
@@ -10545,7 +10595,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A188" s="16"/>
       <c r="B188" s="14" t="s">
         <v>140</v>
@@ -10556,7 +10606,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A189" s="16"/>
       <c r="B189" s="14" t="s">
         <v>141</v>
@@ -10567,7 +10617,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A190" s="16"/>
       <c r="B190" s="14"/>
       <c r="C190" s="22" t="s">
@@ -10579,7 +10629,7 @@
       </c>
       <c r="E190" s="14"/>
     </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.2">
       <c r="D191">
         <f>-SUM(D180:D190)</f>
         <v>0</v>
@@ -10589,7 +10639,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A194" s="7" t="s">
         <v>171</v>
       </c>
@@ -10604,7 +10654,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A195" s="7"/>
       <c r="B195" s="8"/>
       <c r="C195" s="8" t="s">
@@ -10615,7 +10665,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A196" s="7"/>
       <c r="B196" s="8"/>
       <c r="C196" s="8" t="s">
@@ -10626,7 +10676,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A197" s="7"/>
       <c r="B197" s="8" t="s">
         <v>176</v>
@@ -10639,7 +10689,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A198" s="7"/>
       <c r="B198" s="8"/>
       <c r="C198" s="8" t="s">
@@ -10650,7 +10700,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A199" s="7"/>
       <c r="B199" s="8"/>
       <c r="C199" s="8" t="s">
@@ -10661,7 +10711,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A200" s="7"/>
       <c r="B200" s="8"/>
       <c r="C200" s="8" t="s">
@@ -10672,7 +10722,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A201" s="7"/>
       <c r="B201" s="8"/>
       <c r="C201" s="8" t="s">
@@ -10683,7 +10733,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A202" s="7"/>
       <c r="B202" s="8" t="s">
         <v>182</v>
@@ -10694,7 +10744,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A203" s="7"/>
       <c r="B203" s="8" t="s">
         <v>204</v>
@@ -10707,7 +10757,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A204" s="7"/>
       <c r="B204" s="8"/>
       <c r="C204" s="8" t="s">
@@ -10718,7 +10768,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A205" s="7"/>
       <c r="B205" s="8"/>
       <c r="C205" s="8" t="s">
@@ -10729,7 +10779,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A206" s="7"/>
       <c r="B206" s="8"/>
       <c r="C206" s="8" t="s">
@@ -10740,7 +10790,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A207" s="7"/>
       <c r="B207" s="8" t="str">
         <f>Report!B408</f>
@@ -10755,7 +10805,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A208" s="7"/>
       <c r="B208" s="8"/>
       <c r="C208" s="8" t="str">
@@ -10767,7 +10817,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A209" s="7"/>
       <c r="B209" s="8"/>
       <c r="C209" s="8" t="str">
@@ -10779,7 +10829,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A210" s="7"/>
       <c r="B210" s="8"/>
       <c r="C210" s="8" t="str">
@@ -10791,7 +10841,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A211" s="7"/>
       <c r="B211" s="8"/>
       <c r="C211" s="8" t="str">
@@ -10803,7 +10853,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A212" s="7"/>
       <c r="B212" s="8"/>
       <c r="C212" s="22" t="s">
@@ -10815,7 +10865,7 @@
       </c>
       <c r="E212" s="8"/>
     </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:7" x14ac:dyDescent="0.2">
       <c r="D213">
         <f>-SUM(D194:D212)</f>
         <v>0</v>
@@ -10825,7 +10875,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A218" s="7"/>
       <c r="B218" t="s">
         <v>213</v>
@@ -10843,7 +10893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A219" s="11" t="s">
         <v>395</v>
       </c>
@@ -10863,7 +10913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A220" s="15" t="s">
         <v>403</v>
       </c>
@@ -10883,7 +10933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A221" s="16" t="s">
         <v>396</v>
       </c>
@@ -10903,7 +10953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="226" spans="4:7" x14ac:dyDescent="0.2">
       <c r="F226" t="s">
         <v>260</v>
       </c>
@@ -10911,7 +10961,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="227" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="227" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D227" t="s">
         <v>262</v>
       </c>
@@ -10919,7 +10969,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="228" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="228" spans="4:7" x14ac:dyDescent="0.2">
       <c r="F228">
         <v>45</v>
       </c>
@@ -10927,7 +10977,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="229" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="229" spans="4:7" x14ac:dyDescent="0.2">
       <c r="F229">
         <f>F228+(F237-F228)/9</f>
         <v>50</v>
@@ -10936,7 +10986,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="230" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="230" spans="4:7" x14ac:dyDescent="0.2">
       <c r="F230">
         <f>F229+(F237-F228)/9</f>
         <v>55</v>
@@ -10945,7 +10995,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="231" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="231" spans="4:7" x14ac:dyDescent="0.2">
       <c r="F231">
         <f>F230+(F237-F228)/9</f>
         <v>60</v>
@@ -10954,7 +11004,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="232" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="232" spans="4:7" x14ac:dyDescent="0.2">
       <c r="F232">
         <f>F231+(F237-F228)/9</f>
         <v>65</v>
@@ -10963,7 +11013,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="233" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="233" spans="4:7" x14ac:dyDescent="0.2">
       <c r="F233">
         <f>F232+(F237-F228)/9</f>
         <v>70</v>
@@ -10972,7 +11022,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="234" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="234" spans="4:7" x14ac:dyDescent="0.2">
       <c r="F234">
         <f>F233+(F237-F228)/9</f>
         <v>75</v>
@@ -10981,7 +11031,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="235" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="235" spans="4:7" x14ac:dyDescent="0.2">
       <c r="F235">
         <f>F234+(F237-F228)/9</f>
         <v>80</v>
@@ -10990,7 +11040,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="236" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="236" spans="4:7" x14ac:dyDescent="0.2">
       <c r="F236">
         <f>F235+(F237-F228)/9</f>
         <v>85</v>
@@ -10999,7 +11049,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="237" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="237" spans="4:7" x14ac:dyDescent="0.2">
       <c r="F237">
         <v>90</v>
       </c>
@@ -11007,12 +11057,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="238" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="238" spans="4:7" x14ac:dyDescent="0.2">
       <c r="E238" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="1047724" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="1047724" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E1047724" s="8"/>
     </row>
   </sheetData>
@@ -11036,25 +11086,25 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D37"/>
-  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="35.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.44140625" style="20"/>
+    <col min="2" max="2" width="35.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5" style="20"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A1" s="37" t="s">
+    <row r="1" spans="1:4" ht="26" x14ac:dyDescent="0.3">
+      <c r="A1" s="46" t="s">
         <v>253</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="1"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
         <v>237</v>
       </c>
@@ -11062,7 +11112,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
         <v>42</v>
       </c>
@@ -11070,7 +11120,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
         <v>239</v>
       </c>
@@ -11078,7 +11128,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
         <v>240</v>
       </c>
@@ -11086,7 +11136,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B8" t="s">
         <v>241</v>
       </c>
@@ -11094,7 +11144,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
         <v>242</v>
       </c>
@@ -11102,7 +11152,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
         <v>204</v>
       </c>
@@ -11110,7 +11160,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B11" t="s">
         <v>238</v>
       </c>
@@ -11118,7 +11168,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B12" t="s">
         <v>244</v>
       </c>
@@ -11126,7 +11176,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
         <v>243</v>
       </c>
@@ -11134,7 +11184,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B14" t="s">
         <v>245</v>
       </c>
@@ -11142,7 +11192,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B15" t="s">
         <v>246</v>
       </c>
@@ -11150,7 +11200,7 @@
         <v>-0.3</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
         <v>252</v>
       </c>
@@ -11158,7 +11208,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B17" t="s">
         <v>254</v>
       </c>
@@ -11166,7 +11216,7 @@
         <v>-0.2</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B18" t="s">
         <v>255</v>
       </c>
@@ -11174,7 +11224,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>42</v>
       </c>
@@ -11188,7 +11238,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="C23" t="s">
         <v>174</v>
       </c>
@@ -11196,7 +11246,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="C24" t="s">
         <v>175</v>
       </c>
@@ -11204,7 +11254,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B25" t="s">
         <v>176</v>
       </c>
@@ -11215,7 +11265,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="C26" t="s">
         <v>178</v>
       </c>
@@ -11223,7 +11273,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="C27" t="s">
         <v>179</v>
       </c>
@@ -11231,7 +11281,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="C28" t="s">
         <v>180</v>
       </c>
@@ -11239,12 +11289,12 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B30" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B31" t="s">
         <v>192</v>
       </c>
@@ -11255,7 +11305,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="C32" t="s">
         <v>196</v>
       </c>
@@ -11263,7 +11313,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:4" x14ac:dyDescent="0.2">
       <c r="C33" t="s">
         <v>179</v>
       </c>
@@ -11271,7 +11321,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B34" t="s">
         <v>250</v>
       </c>
@@ -11279,7 +11329,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B35" t="s">
         <v>197</v>
       </c>
@@ -11290,7 +11340,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:4" x14ac:dyDescent="0.2">
       <c r="C36" t="s">
         <v>199</v>
       </c>
@@ -11298,7 +11348,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:4" x14ac:dyDescent="0.2">
       <c r="C37" t="s">
         <v>200</v>
       </c>

--- a/ProjectManagement/EvaluationHWAndProject.xlsx
+++ b/ProjectManagement/EvaluationHWAndProject.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sid/Documents/GitHub/ML26-03-Car-Licence-Plate-Identification-with-a-Jetson-Nano/ProjectManagement/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEC02876-4F2A-B74C-9F3B-C449DF6DD26A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EC0CD03-7D39-7B42-B784-8DB2B4BBC4D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="22600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8259,7 +8259,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="533" spans="1:6" ht="32" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A533" s="14"/>
       <c r="B533" s="14" t="s">
         <v>408</v>
@@ -8417,7 +8417,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="547" spans="1:8" ht="64" x14ac:dyDescent="0.2">
+    <row r="547" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A547" s="15" t="s">
         <v>375</v>
       </c>
@@ -8433,7 +8433,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="548" spans="1:8" ht="48" x14ac:dyDescent="0.2">
+    <row r="548" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A548" s="13"/>
       <c r="B548" s="13" t="s">
         <v>416</v>
@@ -8447,7 +8447,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="549" spans="1:8" ht="48" x14ac:dyDescent="0.2">
+    <row r="549" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A549" s="13"/>
       <c r="B549" s="13" t="s">
         <v>419</v>
@@ -8461,7 +8461,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="550" spans="1:8" ht="48" x14ac:dyDescent="0.2">
+    <row r="550" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A550" s="13"/>
       <c r="B550" s="13" t="s">
         <v>420</v>
